--- a/Kapabilite/Kapabilite 2026.xlsx
+++ b/Kapabilite/Kapabilite 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Kapabilite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A723F9D9-11B4-4A9F-8F8B-4BABD000E894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34501D0D-0CF4-4E99-B689-8249CCDBE466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8FA9AADE-0AF1-42A7-AB4A-1A5F3041D90E}"/>
   </bookViews>
@@ -591,598 +591,7 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{54E630F8-1119-49C1-96CD-67D14AC27434}"/>
     <cellStyle name="Yüzde 2" xfId="2" xr:uid="{84D3FCC6-BF51-44C7-A8B3-68B6CBCF5C91}"/>
   </cellStyles>
-  <dxfs count="59">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{5A48E859-7578-4CD2-8153-E9E8C7122537}"/>
   </tableStyles>
@@ -3883,27 +3292,27 @@
       </c>
       <c r="N3" s="8">
         <f t="shared" ref="N3:N25" si="0">IFERROR(AVERAGE(T3,Z3,AF3,AL3,AR3,AX3,BD3,BJ3,BP3,BV3,CB3,CH3)," ")</f>
-        <v>127625</v>
+        <v>132500</v>
       </c>
       <c r="O3" s="8">
         <f t="shared" ref="O3:O25" si="1">IFERROR(AVERAGE(U3,AA3,AG3,AM3,AS3,AY3,BE3,BK3,BQ3,BW3,CC3,CI3)," ")</f>
-        <v>45357.75</v>
+        <v>47058.6</v>
       </c>
       <c r="P3" s="8">
         <f t="shared" ref="P3:P25" si="2">IFERROR(SUM(V3,AB3,AH3,AN3,AT3,AZ3,BF3,BL3,BR3,BX3,CD3,CJ3)," ")</f>
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="Q3" s="9">
         <f t="shared" ref="Q3:Q25" si="3">IFERROR(SUM(T3,Z3,AF3,AL3,AR3,AX3,BD3,BJ3,BP3,BV3,CB3,CH3)/P3*3," ")</f>
-        <v>16121.052631578947</v>
+        <v>16425.619834710746</v>
       </c>
       <c r="R3" s="9">
         <f t="shared" ref="R3:R25" si="4">IFERROR(SUM(U3,AA3,AG3,AM3,AS3,AY3,BE3,BK3,BQ3,BW3,CC3,CI3)/P3*3," ")</f>
-        <v>5729.4</v>
+        <v>5833.7107438016528</v>
       </c>
       <c r="S3" s="10">
         <f t="shared" ref="S3:S25" si="5">IFERROR(AVERAGE(Y3,AE3,AK3,AQ3,AW3,BC3,BI3,BO3,BU3,CA3,CG3,CM3)," ")</f>
-        <v>9.8814674950391215</v>
+        <v>9.9051739960312979</v>
       </c>
       <c r="T3" s="11">
         <v>24000</v>
@@ -3977,12 +3386,24 @@
       <c r="AQ3" s="13">
         <v>10.048380818895399</v>
       </c>
-      <c r="AR3" s="11"/>
-      <c r="AS3" s="11"/>
-      <c r="AT3" s="11"/>
-      <c r="AU3" s="12"/>
-      <c r="AV3" s="12"/>
-      <c r="AW3" s="13"/>
+      <c r="AR3" s="11">
+        <v>152000</v>
+      </c>
+      <c r="AS3" s="11">
+        <v>53862</v>
+      </c>
+      <c r="AT3" s="11">
+        <v>26</v>
+      </c>
+      <c r="AU3" s="12">
+        <v>17538.461538461539</v>
+      </c>
+      <c r="AV3" s="12">
+        <v>6214.8461538461543</v>
+      </c>
+      <c r="AW3" s="13">
+        <v>10</v>
+      </c>
       <c r="AX3" s="11"/>
       <c r="AY3" s="11"/>
       <c r="AZ3" s="11"/>
@@ -4066,27 +3487,27 @@
       </c>
       <c r="N4" s="8">
         <f t="shared" si="0"/>
-        <v>318283.25</v>
+        <v>291482.59999999998</v>
       </c>
       <c r="O4" s="8">
         <f t="shared" si="1"/>
-        <v>12511.25</v>
+        <v>11375.8</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" si="2"/>
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="Q4" s="9">
         <f t="shared" si="3"/>
-        <v>18362.495192307691</v>
+        <v>18293.887029288704</v>
       </c>
       <c r="R4" s="9">
         <f t="shared" si="4"/>
-        <v>721.80288461538464</v>
+        <v>713.96234309623435</v>
       </c>
       <c r="S4" s="10">
         <f t="shared" si="5"/>
-        <v>2.7275438709129745</v>
+        <v>2.7120350967303795</v>
       </c>
       <c r="T4" s="11">
         <v>328790</v>
@@ -4160,12 +3581,24 @@
       <c r="AQ4" s="13">
         <v>2.845704294961501</v>
       </c>
-      <c r="AR4" s="11"/>
-      <c r="AS4" s="11"/>
-      <c r="AT4" s="11"/>
-      <c r="AU4" s="12"/>
-      <c r="AV4" s="12"/>
-      <c r="AW4" s="13"/>
+      <c r="AR4" s="11">
+        <v>184280</v>
+      </c>
+      <c r="AS4" s="11">
+        <v>6834</v>
+      </c>
+      <c r="AT4" s="11">
+        <v>31</v>
+      </c>
+      <c r="AU4" s="12">
+        <v>17833.54838709678</v>
+      </c>
+      <c r="AV4" s="12">
+        <v>661.35483870967732</v>
+      </c>
+      <c r="AW4" s="13">
+        <v>2.65</v>
+      </c>
       <c r="AX4" s="11"/>
       <c r="AY4" s="11"/>
       <c r="AZ4" s="11"/>
@@ -4249,27 +3682,27 @@
       </c>
       <c r="N5" s="8">
         <f t="shared" si="0"/>
-        <v>348568</v>
+        <v>322214.40000000002</v>
       </c>
       <c r="O5" s="8">
         <f t="shared" si="1"/>
-        <v>13901.25</v>
+        <v>12729</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="2"/>
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="Q5" s="9">
         <f t="shared" si="3"/>
-        <v>17574.857142857145</v>
+        <v>17900.8</v>
       </c>
       <c r="R5" s="9">
         <f t="shared" si="4"/>
-        <v>700.90336134453787</v>
+        <v>707.16666666666674</v>
       </c>
       <c r="S5" s="10">
         <f t="shared" si="5"/>
-        <v>2.7503669973030478</v>
+        <v>2.7302935978424383</v>
       </c>
       <c r="T5" s="11">
         <v>373478</v>
@@ -4343,12 +3776,24 @@
       <c r="AQ5" s="13">
         <v>2.65</v>
       </c>
-      <c r="AR5" s="11"/>
-      <c r="AS5" s="11"/>
-      <c r="AT5" s="11"/>
-      <c r="AU5" s="12"/>
-      <c r="AV5" s="12"/>
-      <c r="AW5" s="13"/>
+      <c r="AR5" s="11">
+        <v>216800</v>
+      </c>
+      <c r="AS5" s="11">
+        <v>8040</v>
+      </c>
+      <c r="AT5" s="11">
+        <v>32</v>
+      </c>
+      <c r="AU5" s="12">
+        <v>20325</v>
+      </c>
+      <c r="AV5" s="12">
+        <v>753.75</v>
+      </c>
+      <c r="AW5" s="13">
+        <v>2.65</v>
+      </c>
       <c r="AX5" s="11"/>
       <c r="AY5" s="11"/>
       <c r="AZ5" s="11"/>
@@ -4432,27 +3877,27 @@
       </c>
       <c r="N6" s="8">
         <f t="shared" si="0"/>
-        <v>249809.5</v>
+        <v>230567.8</v>
       </c>
       <c r="O6" s="8">
         <f t="shared" si="1"/>
-        <v>18949</v>
+        <v>17745</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="2"/>
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="Q6" s="9">
         <f t="shared" si="3"/>
-        <v>13442.663677130044</v>
+        <v>13405.10465116279</v>
       </c>
       <c r="R6" s="9">
         <f t="shared" si="4"/>
-        <v>1019.677130044843</v>
+        <v>1031.6860465116279</v>
       </c>
       <c r="S6" s="10">
         <f t="shared" si="5"/>
-        <v>3.765591873649957</v>
+        <v>3.8009092890365421</v>
       </c>
       <c r="T6" s="11">
         <v>274253</v>
@@ -4526,12 +3971,24 @@
       <c r="AQ6" s="13">
         <v>3.160190579850235</v>
       </c>
-      <c r="AR6" s="11"/>
-      <c r="AS6" s="11"/>
-      <c r="AT6" s="11"/>
-      <c r="AU6" s="12"/>
-      <c r="AV6" s="12"/>
-      <c r="AW6" s="13"/>
+      <c r="AR6" s="11">
+        <v>153601</v>
+      </c>
+      <c r="AS6" s="11">
+        <v>12929</v>
+      </c>
+      <c r="AT6" s="11">
+        <v>35</v>
+      </c>
+      <c r="AU6" s="12">
+        <v>13165.8</v>
+      </c>
+      <c r="AV6" s="12">
+        <v>1108.2</v>
+      </c>
+      <c r="AW6" s="13">
+        <v>3.9421789505828828</v>
+      </c>
       <c r="AX6" s="11"/>
       <c r="AY6" s="11"/>
       <c r="AZ6" s="11"/>
@@ -4615,27 +4072,27 @@
       </c>
       <c r="N7" s="8">
         <f t="shared" si="0"/>
-        <v>317286.25</v>
+        <v>286948.8</v>
       </c>
       <c r="O7" s="8">
         <f t="shared" si="1"/>
-        <v>55435</v>
+        <v>49383.6</v>
       </c>
       <c r="P7" s="8">
         <f t="shared" si="2"/>
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="Q7" s="9">
         <f t="shared" si="3"/>
-        <v>16340.922746781114</v>
+        <v>16491.310344827587</v>
       </c>
       <c r="R7" s="9">
         <f t="shared" si="4"/>
-        <v>2855.0214592274679</v>
+        <v>2838.1379310344828</v>
       </c>
       <c r="S7" s="10">
         <f t="shared" si="5"/>
-        <v>5.4624999505548377</v>
+        <v>5.4356128505172432</v>
       </c>
       <c r="T7" s="11">
         <v>355184</v>
@@ -4709,12 +4166,24 @@
       <c r="AQ7" s="13">
         <v>5.768933920271218</v>
       </c>
-      <c r="AR7" s="11"/>
-      <c r="AS7" s="11"/>
-      <c r="AT7" s="11"/>
-      <c r="AU7" s="12"/>
-      <c r="AV7" s="12"/>
-      <c r="AW7" s="13"/>
+      <c r="AR7" s="11">
+        <v>165599</v>
+      </c>
+      <c r="AS7" s="11">
+        <v>25178</v>
+      </c>
+      <c r="AT7" s="11">
+        <v>28</v>
+      </c>
+      <c r="AU7" s="12">
+        <v>17742.75</v>
+      </c>
+      <c r="AV7" s="12">
+        <v>2697.6428571428569</v>
+      </c>
+      <c r="AW7" s="13">
+        <v>5.3280644503668686</v>
+      </c>
       <c r="AX7" s="11"/>
       <c r="AY7" s="11"/>
       <c r="AZ7" s="11"/>
@@ -4798,27 +4267,27 @@
       </c>
       <c r="N8" s="8">
         <f t="shared" si="0"/>
-        <v>306758.75</v>
+        <v>279219</v>
       </c>
       <c r="O8" s="8">
         <f t="shared" si="1"/>
-        <v>39832.25</v>
+        <v>35661</v>
       </c>
       <c r="P8" s="8">
         <f t="shared" si="2"/>
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="Q8" s="9">
         <f t="shared" si="3"/>
-        <v>15532.088607594937</v>
+        <v>15512.166666666668</v>
       </c>
       <c r="R8" s="9">
         <f t="shared" si="4"/>
-        <v>2016.8227848101264</v>
+        <v>1981.1666666666667</v>
       </c>
       <c r="S8" s="10">
         <f t="shared" si="5"/>
-        <v>4.9389387258075645</v>
+        <v>4.8707332969122179</v>
       </c>
       <c r="T8" s="11">
         <v>330292</v>
@@ -4892,12 +4361,24 @@
       <c r="AQ8" s="13">
         <v>4.9406099004204904</v>
       </c>
-      <c r="AR8" s="11"/>
-      <c r="AS8" s="11"/>
-      <c r="AT8" s="11"/>
-      <c r="AU8" s="12"/>
-      <c r="AV8" s="12"/>
-      <c r="AW8" s="13"/>
+      <c r="AR8" s="11">
+        <v>169060</v>
+      </c>
+      <c r="AS8" s="11">
+        <v>18976</v>
+      </c>
+      <c r="AT8" s="11">
+        <v>33</v>
+      </c>
+      <c r="AU8" s="12">
+        <v>15369.09090909091</v>
+      </c>
+      <c r="AV8" s="12">
+        <v>1725.090909090909</v>
+      </c>
+      <c r="AW8" s="13">
+        <v>4.5979115813308313</v>
+      </c>
       <c r="AX8" s="11"/>
       <c r="AY8" s="11"/>
       <c r="AZ8" s="11"/>
@@ -4981,27 +4462,27 @@
       </c>
       <c r="N9" s="8">
         <f t="shared" si="0"/>
-        <v>282009.25</v>
+        <v>260545</v>
       </c>
       <c r="O9" s="8">
         <f t="shared" si="1"/>
-        <v>10295.5</v>
+        <v>9270.6</v>
       </c>
       <c r="P9" s="8">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="Q9" s="9">
         <f t="shared" si="3"/>
-        <v>16920.555</v>
+        <v>17066.266375545852</v>
       </c>
       <c r="R9" s="9">
         <f t="shared" si="4"/>
-        <v>617.73</v>
+        <v>607.24454148471614</v>
       </c>
       <c r="S9" s="10">
         <f t="shared" si="5"/>
-        <v>2.6280263844421854</v>
+        <v>2.5774431336336314</v>
       </c>
       <c r="T9" s="11">
         <v>341336</v>
@@ -5075,12 +4556,24 @@
       <c r="AQ9" s="13">
         <v>2.704660491996294</v>
       </c>
-      <c r="AR9" s="11"/>
-      <c r="AS9" s="11"/>
-      <c r="AT9" s="11"/>
-      <c r="AU9" s="12"/>
-      <c r="AV9" s="12"/>
-      <c r="AW9" s="13"/>
+      <c r="AR9" s="11">
+        <v>174688</v>
+      </c>
+      <c r="AS9" s="11">
+        <v>5171</v>
+      </c>
+      <c r="AT9" s="11">
+        <v>29</v>
+      </c>
+      <c r="AU9" s="12">
+        <v>18071.172413793101</v>
+      </c>
+      <c r="AV9" s="12">
+        <v>534.93103448275861</v>
+      </c>
+      <c r="AW9" s="13">
+        <v>2.3751101303994142</v>
+      </c>
       <c r="AX9" s="11"/>
       <c r="AY9" s="11"/>
       <c r="AZ9" s="11"/>
@@ -5164,27 +4657,27 @@
       </c>
       <c r="N10" s="8">
         <f t="shared" si="0"/>
-        <v>253859.5</v>
+        <v>234901.8</v>
       </c>
       <c r="O10" s="8">
         <f t="shared" si="1"/>
-        <v>8955.25</v>
+        <v>8511.6</v>
       </c>
       <c r="P10" s="8">
         <f t="shared" si="2"/>
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="Q10" s="9">
         <f t="shared" si="3"/>
-        <v>20445.060402684565</v>
+        <v>20020.039772727272</v>
       </c>
       <c r="R10" s="9">
         <f t="shared" si="4"/>
-        <v>721.22818791946315</v>
+        <v>725.4204545454545</v>
       </c>
       <c r="S10" s="10">
         <f t="shared" si="5"/>
-        <v>2.5518515625459948</v>
+        <v>2.6200833794076646</v>
       </c>
       <c r="T10" s="11">
         <v>350996</v>
@@ -5258,12 +4751,24 @@
       <c r="AQ10" s="13">
         <v>2.6639572256709658</v>
       </c>
-      <c r="AR10" s="11"/>
-      <c r="AS10" s="11"/>
-      <c r="AT10" s="11"/>
-      <c r="AU10" s="12"/>
-      <c r="AV10" s="12"/>
-      <c r="AW10" s="13"/>
+      <c r="AR10" s="11">
+        <v>159071</v>
+      </c>
+      <c r="AS10" s="11">
+        <v>6737</v>
+      </c>
+      <c r="AT10" s="11">
+        <v>27</v>
+      </c>
+      <c r="AU10" s="12">
+        <v>17674.555555555551</v>
+      </c>
+      <c r="AV10" s="12">
+        <v>748.55555555555554</v>
+      </c>
+      <c r="AW10" s="13">
+        <v>2.8930106468543428</v>
+      </c>
       <c r="AX10" s="11"/>
       <c r="AY10" s="11"/>
       <c r="AZ10" s="11"/>
@@ -5347,27 +4852,27 @@
       </c>
       <c r="N11" s="8">
         <f t="shared" si="0"/>
-        <v>249762.75</v>
+        <v>230035.6</v>
       </c>
       <c r="O11" s="8">
         <f t="shared" si="1"/>
-        <v>8011.5</v>
+        <v>7732.6</v>
       </c>
       <c r="P11" s="8">
         <f t="shared" si="2"/>
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="Q11" s="9">
         <f t="shared" si="3"/>
-        <v>18275.323170731706</v>
+        <v>18551.258064516129</v>
       </c>
       <c r="R11" s="9">
         <f t="shared" si="4"/>
-        <v>586.20731707317077</v>
+        <v>623.59677419354841</v>
       </c>
       <c r="S11" s="10">
         <f t="shared" si="5"/>
-        <v>2.4949779834751773</v>
+        <v>2.5846508188687514</v>
       </c>
       <c r="T11" s="11">
         <v>395887</v>
@@ -5441,12 +4946,24 @@
       <c r="AQ11" s="13">
         <v>2.5318898396207312</v>
       </c>
-      <c r="AR11" s="11"/>
-      <c r="AS11" s="11"/>
-      <c r="AT11" s="11"/>
-      <c r="AU11" s="12"/>
-      <c r="AV11" s="12"/>
-      <c r="AW11" s="13"/>
+      <c r="AR11" s="11">
+        <v>151127</v>
+      </c>
+      <c r="AS11" s="11">
+        <v>6617</v>
+      </c>
+      <c r="AT11" s="11">
+        <v>22</v>
+      </c>
+      <c r="AU11" s="12">
+        <v>20608.227272727268</v>
+      </c>
+      <c r="AV11" s="12">
+        <v>902.31818181818176</v>
+      </c>
+      <c r="AW11" s="13">
+        <v>2.9433421604430472</v>
+      </c>
       <c r="AX11" s="11"/>
       <c r="AY11" s="11"/>
       <c r="AZ11" s="11"/>
@@ -5530,27 +5047,27 @@
       </c>
       <c r="N12" s="8">
         <f t="shared" si="0"/>
-        <v>270931.5</v>
+        <v>246577.6</v>
       </c>
       <c r="O12" s="8">
         <f t="shared" si="1"/>
-        <v>22269</v>
+        <v>19798.599999999999</v>
       </c>
       <c r="P12" s="8">
         <f t="shared" si="2"/>
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="Q12" s="9">
         <f t="shared" si="3"/>
-        <v>17293.5</v>
+        <v>17283.47663551402</v>
       </c>
       <c r="R12" s="9">
         <f t="shared" si="4"/>
-        <v>1421.4255319148938</v>
+        <v>1387.752336448598</v>
       </c>
       <c r="S12" s="10">
         <f t="shared" si="5"/>
-        <v>3.9176746643790956</v>
+        <v>3.8412333329862975</v>
       </c>
       <c r="T12" s="11">
         <v>290616</v>
@@ -5624,12 +5141,24 @@
       <c r="AQ12" s="13">
         <v>3.985730089804453</v>
       </c>
-      <c r="AR12" s="11"/>
-      <c r="AS12" s="11"/>
-      <c r="AT12" s="11"/>
-      <c r="AU12" s="12"/>
-      <c r="AV12" s="12"/>
-      <c r="AW12" s="13"/>
+      <c r="AR12" s="11">
+        <v>149162</v>
+      </c>
+      <c r="AS12" s="11">
+        <v>9917</v>
+      </c>
+      <c r="AT12" s="11">
+        <v>26</v>
+      </c>
+      <c r="AU12" s="12">
+        <v>17211</v>
+      </c>
+      <c r="AV12" s="12">
+        <v>1144.2692307692309</v>
+      </c>
+      <c r="AW12" s="13">
+        <v>3.5354680074151048</v>
+      </c>
       <c r="AX12" s="11"/>
       <c r="AY12" s="11"/>
       <c r="AZ12" s="11"/>
@@ -5713,27 +5242,27 @@
       </c>
       <c r="N13" s="8">
         <f t="shared" si="0"/>
-        <v>252677.25</v>
+        <v>252367</v>
       </c>
       <c r="O13" s="8">
         <f t="shared" si="1"/>
-        <v>14171</v>
+        <v>13199.4</v>
       </c>
       <c r="P13" s="8">
         <f t="shared" si="2"/>
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="Q13" s="9">
         <f t="shared" si="3"/>
-        <v>14507.784688995216</v>
+        <v>15325.931174089068</v>
       </c>
       <c r="R13" s="9">
         <f t="shared" si="4"/>
-        <v>813.645933014354</v>
+        <v>801.58299595141705</v>
       </c>
       <c r="S13" s="10">
         <f t="shared" si="5"/>
-        <v>3.3702026068918109</v>
+        <v>3.2261620855134487</v>
       </c>
       <c r="T13" s="11">
         <v>214482</v>
@@ -5807,12 +5336,24 @@
       <c r="AQ13" s="13">
         <v>2.8262899639630561</v>
       </c>
-      <c r="AR13" s="11"/>
-      <c r="AS13" s="11"/>
-      <c r="AT13" s="11"/>
-      <c r="AU13" s="12"/>
-      <c r="AV13" s="12"/>
-      <c r="AW13" s="13"/>
+      <c r="AR13" s="11">
+        <v>251126</v>
+      </c>
+      <c r="AS13" s="11">
+        <v>9313</v>
+      </c>
+      <c r="AT13" s="11">
+        <v>38</v>
+      </c>
+      <c r="AU13" s="12">
+        <v>19825.73684210526</v>
+      </c>
+      <c r="AV13" s="12">
+        <v>735.23684210526312</v>
+      </c>
+      <c r="AW13" s="13">
+        <v>2.65</v>
+      </c>
       <c r="AX13" s="11"/>
       <c r="AY13" s="11"/>
       <c r="AZ13" s="11"/>
@@ -5896,27 +5437,27 @@
       </c>
       <c r="N14" s="8">
         <f t="shared" si="0"/>
-        <v>298425.25</v>
+        <v>286493.59999999998</v>
       </c>
       <c r="O14" s="8">
         <f t="shared" si="1"/>
-        <v>175971</v>
+        <v>163365.6</v>
       </c>
       <c r="P14" s="8">
         <f t="shared" si="2"/>
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="Q14" s="9">
         <f t="shared" si="3"/>
-        <v>13880.244186046511</v>
+        <v>14372.58862876254</v>
       </c>
       <c r="R14" s="9">
         <f t="shared" si="4"/>
-        <v>8184.6976744186049</v>
+        <v>8195.5986622073578</v>
       </c>
       <c r="S14" s="10">
         <f t="shared" si="5"/>
-        <v>10.490491241686197</v>
+        <v>10.2347397582199</v>
       </c>
       <c r="T14" s="11">
         <v>358878</v>
@@ -5990,12 +5531,24 @@
       <c r="AQ14" s="13">
         <v>10.633408700310561</v>
       </c>
-      <c r="AR14" s="11"/>
-      <c r="AS14" s="11"/>
-      <c r="AT14" s="11"/>
-      <c r="AU14" s="12"/>
-      <c r="AV14" s="12"/>
-      <c r="AW14" s="13"/>
+      <c r="AR14" s="11">
+        <v>238767</v>
+      </c>
+      <c r="AS14" s="11">
+        <v>112944</v>
+      </c>
+      <c r="AT14" s="11">
+        <v>41</v>
+      </c>
+      <c r="AU14" s="12">
+        <v>17470.756097560981</v>
+      </c>
+      <c r="AV14" s="12">
+        <v>8264.1951219512193</v>
+      </c>
+      <c r="AW14" s="13">
+        <v>9.2117338243547167</v>
+      </c>
       <c r="AX14" s="11"/>
       <c r="AY14" s="11"/>
       <c r="AZ14" s="11"/>
@@ -6079,27 +5632,27 @@
       </c>
       <c r="N15" s="8">
         <f t="shared" si="0"/>
-        <v>161387.5</v>
+        <v>147759.4</v>
       </c>
       <c r="O15" s="8">
         <f t="shared" si="1"/>
-        <v>70501</v>
+        <v>64001</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" si="2"/>
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="Q15" s="9">
         <f t="shared" si="3"/>
-        <v>9880.8673469387759</v>
+        <v>9807.0398230088504</v>
       </c>
       <c r="R15" s="9">
         <f t="shared" si="4"/>
-        <v>4316.3877551020414</v>
+        <v>4247.853982300885</v>
       </c>
       <c r="S15" s="10">
         <f t="shared" si="5"/>
-        <v>10.461353938009287</v>
+        <v>10.375393518812256</v>
       </c>
       <c r="T15" s="11">
         <v>184929</v>
@@ -6173,12 +5726,24 @@
       <c r="AQ15" s="13">
         <v>10.981926665590031</v>
       </c>
-      <c r="AR15" s="11"/>
-      <c r="AS15" s="11"/>
-      <c r="AT15" s="11"/>
-      <c r="AU15" s="12"/>
-      <c r="AV15" s="12"/>
-      <c r="AW15" s="13"/>
+      <c r="AR15" s="11">
+        <v>93247</v>
+      </c>
+      <c r="AS15" s="11">
+        <v>38001</v>
+      </c>
+      <c r="AT15" s="11">
+        <v>30</v>
+      </c>
+      <c r="AU15" s="12">
+        <v>9324.6999999999989</v>
+      </c>
+      <c r="AV15" s="12">
+        <v>3800.1</v>
+      </c>
+      <c r="AW15" s="13">
+        <v>10.03155184202414</v>
+      </c>
       <c r="AX15" s="11"/>
       <c r="AY15" s="11"/>
       <c r="AZ15" s="11"/>
@@ -6262,27 +5827,27 @@
       </c>
       <c r="N16" s="8">
         <f t="shared" si="0"/>
-        <v>103422.5</v>
+        <v>97967.2</v>
       </c>
       <c r="O16" s="8">
         <f t="shared" si="1"/>
-        <v>172856</v>
+        <v>163480.20000000001</v>
       </c>
       <c r="P16" s="8">
         <f t="shared" si="2"/>
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="Q16" s="9">
         <f t="shared" si="3"/>
-        <v>5666.9863013698632</v>
+        <v>5630.2988505747126</v>
       </c>
       <c r="R16" s="9">
         <f t="shared" si="4"/>
-        <v>9471.5616438356155</v>
+        <v>9395.4137931034475</v>
       </c>
       <c r="S16" s="10">
         <f t="shared" si="5"/>
-        <v>20.567132257983999</v>
+        <v>20.557025616252552</v>
       </c>
       <c r="T16" s="11">
         <v>114329</v>
@@ -6356,12 +5921,24 @@
       <c r="AQ16" s="13">
         <v>21.462824398127811</v>
       </c>
-      <c r="AR16" s="11"/>
-      <c r="AS16" s="11"/>
-      <c r="AT16" s="11"/>
-      <c r="AU16" s="12"/>
-      <c r="AV16" s="12"/>
-      <c r="AW16" s="13"/>
+      <c r="AR16" s="11">
+        <v>76146</v>
+      </c>
+      <c r="AS16" s="11">
+        <v>125977</v>
+      </c>
+      <c r="AT16" s="11">
+        <v>42</v>
+      </c>
+      <c r="AU16" s="12">
+        <v>5439</v>
+      </c>
+      <c r="AV16" s="12">
+        <v>8998.3571428571413</v>
+      </c>
+      <c r="AW16" s="13">
+        <v>20.516599049326778</v>
+      </c>
       <c r="AX16" s="11"/>
       <c r="AY16" s="11"/>
       <c r="AZ16" s="11"/>
@@ -6445,27 +6022,27 @@
       </c>
       <c r="N17" s="8">
         <f t="shared" si="0"/>
-        <v>288988.75</v>
+        <v>271529.8</v>
       </c>
       <c r="O17" s="8">
         <f t="shared" si="1"/>
-        <v>4787.5</v>
+        <v>4352</v>
       </c>
       <c r="P17" s="8">
         <f t="shared" si="2"/>
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="Q17" s="9">
         <f t="shared" si="3"/>
-        <v>19159.475138121546</v>
+        <v>19771.587378640776</v>
       </c>
       <c r="R17" s="9">
         <f t="shared" si="4"/>
-        <v>317.40331491712709</v>
+        <v>316.89320388349512</v>
       </c>
       <c r="S17" s="10">
         <f t="shared" si="5"/>
-        <v>1.8067844900334729</v>
+        <v>1.7638920652301995</v>
       </c>
       <c r="T17" s="11">
         <v>317353</v>
@@ -6539,12 +6116,24 @@
       <c r="AQ17" s="13">
         <v>1.826606287709216</v>
       </c>
-      <c r="AR17" s="11"/>
-      <c r="AS17" s="11"/>
-      <c r="AT17" s="11"/>
-      <c r="AU17" s="12"/>
-      <c r="AV17" s="12"/>
-      <c r="AW17" s="13"/>
+      <c r="AR17" s="11">
+        <v>201694</v>
+      </c>
+      <c r="AS17" s="11">
+        <v>2610</v>
+      </c>
+      <c r="AT17" s="11">
+        <v>25</v>
+      </c>
+      <c r="AU17" s="12">
+        <v>24203.279999999999</v>
+      </c>
+      <c r="AV17" s="12">
+        <v>313.2</v>
+      </c>
+      <c r="AW17" s="13">
+        <v>1.592322366017106</v>
+      </c>
       <c r="AX17" s="11"/>
       <c r="AY17" s="11"/>
       <c r="AZ17" s="11"/>
@@ -6628,27 +6217,27 @@
       </c>
       <c r="N18" s="8">
         <f t="shared" si="0"/>
-        <v>238826.75</v>
+        <v>237305</v>
       </c>
       <c r="O18" s="8">
         <f t="shared" si="1"/>
-        <v>8134</v>
+        <v>8222</v>
       </c>
       <c r="P18" s="8">
         <f t="shared" si="2"/>
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="Q18" s="9">
         <f t="shared" si="3"/>
-        <v>17912.006249999999</v>
+        <v>18348.324742268043</v>
       </c>
       <c r="R18" s="9">
         <f t="shared" si="4"/>
-        <v>610.04999999999995</v>
+        <v>635.7216494845361</v>
       </c>
       <c r="S18" s="10">
         <f t="shared" si="5"/>
-        <v>2.5394657534013043</v>
+        <v>2.5615726027210437</v>
       </c>
       <c r="T18" s="11">
         <v>208128</v>
@@ -6722,12 +6311,24 @@
       <c r="AQ18" s="13">
         <v>2.65</v>
       </c>
-      <c r="AR18" s="11"/>
-      <c r="AS18" s="11"/>
-      <c r="AT18" s="11"/>
-      <c r="AU18" s="12"/>
-      <c r="AV18" s="12"/>
-      <c r="AW18" s="13"/>
+      <c r="AR18" s="11">
+        <v>231218</v>
+      </c>
+      <c r="AS18" s="11">
+        <v>8574</v>
+      </c>
+      <c r="AT18" s="11">
+        <v>34</v>
+      </c>
+      <c r="AU18" s="12">
+        <v>20401.588235294119</v>
+      </c>
+      <c r="AV18" s="12">
+        <v>756.52941176470586</v>
+      </c>
+      <c r="AW18" s="13">
+        <v>2.65</v>
+      </c>
       <c r="AX18" s="11"/>
       <c r="AY18" s="11"/>
       <c r="AZ18" s="11"/>
@@ -6811,27 +6412,27 @@
       </c>
       <c r="N19" s="8">
         <f t="shared" si="0"/>
-        <v>88108.5</v>
+        <v>84456.4</v>
       </c>
       <c r="O19" s="8">
         <f t="shared" si="1"/>
-        <v>298435</v>
+        <v>275943.2</v>
       </c>
       <c r="P19" s="8">
         <f t="shared" si="2"/>
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="Q19" s="9">
         <f t="shared" si="3"/>
-        <v>4480.093220338983</v>
+        <v>4640.461538461539</v>
       </c>
       <c r="R19" s="9">
         <f t="shared" si="4"/>
-        <v>15174.661016949154</v>
+        <v>15161.714285714284</v>
       </c>
       <c r="S19" s="10">
         <f t="shared" si="5"/>
-        <v>28.303469530999646</v>
+        <v>27.755807850366672</v>
       </c>
       <c r="T19" s="11">
         <v>82762</v>
@@ -6905,12 +6506,24 @@
       <c r="AQ19" s="13">
         <v>29.084067906325629</v>
       </c>
-      <c r="AR19" s="11"/>
-      <c r="AS19" s="11"/>
-      <c r="AT19" s="11"/>
-      <c r="AU19" s="12"/>
-      <c r="AV19" s="12"/>
-      <c r="AW19" s="13"/>
+      <c r="AR19" s="11">
+        <v>69848</v>
+      </c>
+      <c r="AS19" s="11">
+        <v>185976</v>
+      </c>
+      <c r="AT19" s="11">
+        <v>37</v>
+      </c>
+      <c r="AU19" s="12">
+        <v>5663.3513513513517</v>
+      </c>
+      <c r="AV19" s="12">
+        <v>15079.13513513513</v>
+      </c>
+      <c r="AW19" s="13">
+        <v>25.565161127834781</v>
+      </c>
       <c r="AX19" s="11"/>
       <c r="AY19" s="11"/>
       <c r="AZ19" s="11"/>
@@ -6994,27 +6607,27 @@
       </c>
       <c r="N20" s="8">
         <f t="shared" si="0"/>
-        <v>139889</v>
+        <v>126533.6</v>
       </c>
       <c r="O20" s="8">
         <f t="shared" si="1"/>
-        <v>18315.75</v>
+        <v>16575.2</v>
       </c>
       <c r="P20" s="8">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="Q20" s="9">
         <f t="shared" si="3"/>
-        <v>11657.416666666668</v>
+        <v>11503.054545454546</v>
       </c>
       <c r="R20" s="9">
         <f t="shared" si="4"/>
-        <v>1526.3125</v>
+        <v>1506.8363636363636</v>
       </c>
       <c r="S20" s="10">
         <f t="shared" si="5"/>
-        <v>5.7299945263764167</v>
+        <v>5.7263527576821316</v>
       </c>
       <c r="T20" s="11">
         <v>173630</v>
@@ -7088,12 +6701,24 @@
       <c r="AQ20" s="13">
         <v>5.9298617385891674</v>
       </c>
-      <c r="AR20" s="11"/>
-      <c r="AS20" s="11"/>
-      <c r="AT20" s="11"/>
-      <c r="AU20" s="12"/>
-      <c r="AV20" s="12"/>
-      <c r="AW20" s="13"/>
+      <c r="AR20" s="11">
+        <v>73112</v>
+      </c>
+      <c r="AS20" s="11">
+        <v>9613</v>
+      </c>
+      <c r="AT20" s="11">
+        <v>21</v>
+      </c>
+      <c r="AU20" s="12">
+        <v>10444.571428571429</v>
+      </c>
+      <c r="AV20" s="12">
+        <v>1373.285714285714</v>
+      </c>
+      <c r="AW20" s="13">
+        <v>5.711785682904992</v>
+      </c>
       <c r="AX20" s="11"/>
       <c r="AY20" s="11"/>
       <c r="AZ20" s="11"/>
@@ -7177,27 +6802,27 @@
       </c>
       <c r="N21" s="8">
         <f t="shared" si="0"/>
-        <v>477752.25</v>
+        <v>442830.2</v>
       </c>
       <c r="O21" s="8">
         <f t="shared" si="1"/>
-        <v>130712.5</v>
+        <v>123190</v>
       </c>
       <c r="P21" s="8">
         <f t="shared" si="2"/>
-        <v>274</v>
+        <v>324</v>
       </c>
       <c r="Q21" s="9">
         <f t="shared" si="3"/>
-        <v>20923.456204379563</v>
+        <v>20501.398148148146</v>
       </c>
       <c r="R21" s="9">
         <f t="shared" si="4"/>
-        <v>5724.6350364963509</v>
+        <v>5703.2407407407409</v>
       </c>
       <c r="S21" s="10">
         <f t="shared" si="5"/>
-        <v>7.0083332200790878</v>
+        <v>7.0700301366989562</v>
       </c>
       <c r="T21" s="11">
         <v>514374</v>
@@ -7271,12 +6896,24 @@
       <c r="AQ21" s="13">
         <v>7.3330665056004296</v>
       </c>
-      <c r="AR21" s="11"/>
-      <c r="AS21" s="11"/>
-      <c r="AT21" s="11"/>
-      <c r="AU21" s="12"/>
-      <c r="AV21" s="12"/>
-      <c r="AW21" s="13"/>
+      <c r="AR21" s="11">
+        <v>303142</v>
+      </c>
+      <c r="AS21" s="11">
+        <v>93100</v>
+      </c>
+      <c r="AT21" s="11">
+        <v>50</v>
+      </c>
+      <c r="AU21" s="12">
+        <v>18188.52</v>
+      </c>
+      <c r="AV21" s="12">
+        <v>5586</v>
+      </c>
+      <c r="AW21" s="13">
+        <v>7.3168178031784334</v>
+      </c>
       <c r="AX21" s="11"/>
       <c r="AY21" s="11"/>
       <c r="AZ21" s="11"/>
@@ -7360,27 +6997,27 @@
       </c>
       <c r="N22" s="8">
         <f t="shared" si="0"/>
-        <v>463614</v>
+        <v>444940.6</v>
       </c>
       <c r="O22" s="8">
         <f t="shared" si="1"/>
-        <v>112487.5</v>
+        <v>109319.6</v>
       </c>
       <c r="P22" s="8">
         <f t="shared" si="2"/>
-        <v>267</v>
+        <v>317</v>
       </c>
       <c r="Q22" s="9">
         <f t="shared" si="3"/>
-        <v>20836.584269662922</v>
+        <v>21053.971608832806</v>
       </c>
       <c r="R22" s="9">
         <f t="shared" si="4"/>
-        <v>5055.6179775280898</v>
+        <v>5172.8517350157726</v>
       </c>
       <c r="S22" s="10">
         <f t="shared" si="5"/>
-        <v>6.5131813845211823</v>
+        <v>6.5841163085307643</v>
       </c>
       <c r="T22" s="11">
         <v>555592</v>
@@ -7454,12 +7091,24 @@
       <c r="AQ22" s="13">
         <v>6.6638334975759808</v>
       </c>
-      <c r="AR22" s="11"/>
-      <c r="AS22" s="11"/>
-      <c r="AT22" s="11"/>
-      <c r="AU22" s="12"/>
-      <c r="AV22" s="12"/>
-      <c r="AW22" s="13"/>
+      <c r="AR22" s="11">
+        <v>370247</v>
+      </c>
+      <c r="AS22" s="11">
+        <v>96648</v>
+      </c>
+      <c r="AT22" s="11">
+        <v>50</v>
+      </c>
+      <c r="AU22" s="12">
+        <v>22214.82</v>
+      </c>
+      <c r="AV22" s="12">
+        <v>5798.88</v>
+      </c>
+      <c r="AW22" s="13">
+        <v>6.8678560045690933</v>
+      </c>
       <c r="AX22" s="11"/>
       <c r="AY22" s="11"/>
       <c r="AZ22" s="11"/>
@@ -7543,27 +7192,27 @@
       </c>
       <c r="N23" s="8">
         <f t="shared" si="0"/>
-        <v>316762.5</v>
+        <v>295502</v>
       </c>
       <c r="O23" s="8">
         <f t="shared" si="1"/>
-        <v>11850.75</v>
+        <v>11041.4</v>
       </c>
       <c r="P23" s="8">
         <f t="shared" si="2"/>
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="Q23" s="9">
         <f t="shared" si="3"/>
-        <v>19197.727272727272</v>
+        <v>19612.964601769912</v>
       </c>
       <c r="R23" s="9">
         <f t="shared" si="4"/>
-        <v>718.22727272727275</v>
+        <v>732.83628318584078</v>
       </c>
       <c r="S23" s="10">
         <f t="shared" si="5"/>
-        <v>2.660440094975689</v>
+        <v>2.6583520759805515</v>
       </c>
       <c r="T23" s="11">
         <v>295520</v>
@@ -7637,12 +7286,24 @@
       <c r="AQ23" s="13">
         <v>2.65</v>
       </c>
-      <c r="AR23" s="11"/>
-      <c r="AS23" s="11"/>
-      <c r="AT23" s="11"/>
-      <c r="AU23" s="12"/>
-      <c r="AV23" s="12"/>
-      <c r="AW23" s="13"/>
+      <c r="AR23" s="11">
+        <v>210460</v>
+      </c>
+      <c r="AS23" s="11">
+        <v>7804</v>
+      </c>
+      <c r="AT23" s="11">
+        <v>28</v>
+      </c>
+      <c r="AU23" s="12">
+        <v>22549.28571428571</v>
+      </c>
+      <c r="AV23" s="12">
+        <v>836.14285714285711</v>
+      </c>
+      <c r="AW23" s="13">
+        <v>2.65</v>
+      </c>
       <c r="AX23" s="11"/>
       <c r="AY23" s="11"/>
       <c r="AZ23" s="11"/>
@@ -7726,27 +7387,27 @@
       </c>
       <c r="N24" s="8">
         <f t="shared" si="0"/>
-        <v>255210.75</v>
+        <v>234302</v>
       </c>
       <c r="O24" s="8">
         <f t="shared" si="1"/>
-        <v>4193</v>
+        <v>3785.8</v>
       </c>
       <c r="P24" s="8">
         <f t="shared" si="2"/>
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="Q24" s="9">
         <f t="shared" si="3"/>
-        <v>20148.217105263157</v>
+        <v>19856.101694915254</v>
       </c>
       <c r="R24" s="9">
         <f t="shared" si="4"/>
-        <v>331.02631578947364</v>
+        <v>320.83050847457628</v>
       </c>
       <c r="S24" s="10">
         <f t="shared" si="5"/>
-        <v>1.8024976015708716</v>
+        <v>1.7773381096516829</v>
       </c>
       <c r="T24" s="11">
         <v>328339</v>
@@ -7820,12 +7481,24 @@
       <c r="AQ24" s="13">
         <v>1.7875288749791121</v>
       </c>
-      <c r="AR24" s="11"/>
-      <c r="AS24" s="11"/>
-      <c r="AT24" s="11"/>
-      <c r="AU24" s="12"/>
-      <c r="AV24" s="12"/>
-      <c r="AW24" s="13"/>
+      <c r="AR24" s="11">
+        <v>150667</v>
+      </c>
+      <c r="AS24" s="11">
+        <v>2157</v>
+      </c>
+      <c r="AT24" s="11">
+        <v>25</v>
+      </c>
+      <c r="AU24" s="12">
+        <v>18080.04</v>
+      </c>
+      <c r="AV24" s="12">
+        <v>258.83999999999997</v>
+      </c>
+      <c r="AW24" s="13">
+        <v>1.676700141974929</v>
+      </c>
       <c r="AX24" s="11"/>
       <c r="AY24" s="11"/>
       <c r="AZ24" s="11"/>
@@ -7909,27 +7582,27 @@
       </c>
       <c r="N25" s="8">
         <f t="shared" si="0"/>
-        <v>286207.25</v>
+        <v>256307.4</v>
       </c>
       <c r="O25" s="8">
         <f t="shared" si="1"/>
-        <v>19589</v>
+        <v>17360.8</v>
       </c>
       <c r="P25" s="8">
         <f t="shared" si="2"/>
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="Q25" s="9">
         <f t="shared" si="3"/>
-        <v>15196.845132743361</v>
+        <v>15196.090909090908</v>
       </c>
       <c r="R25" s="9">
         <f t="shared" si="4"/>
-        <v>1040.1238938053098</v>
+        <v>1029.296442687747</v>
       </c>
       <c r="S25" s="10">
         <f t="shared" si="5"/>
-        <v>3.6499041810798039</v>
+        <v>3.6234123470483239</v>
       </c>
       <c r="T25" s="11">
         <v>254251</v>
@@ -8003,12 +7676,24 @@
       <c r="AQ25" s="13">
         <v>3.9465406255382849</v>
       </c>
-      <c r="AR25" s="11"/>
-      <c r="AS25" s="11"/>
-      <c r="AT25" s="11"/>
-      <c r="AU25" s="12"/>
-      <c r="AV25" s="12"/>
-      <c r="AW25" s="13"/>
+      <c r="AR25" s="11">
+        <v>136708</v>
+      </c>
+      <c r="AS25" s="11">
+        <v>8448</v>
+      </c>
+      <c r="AT25" s="11">
+        <v>27</v>
+      </c>
+      <c r="AU25" s="12">
+        <v>15189.777777777779</v>
+      </c>
+      <c r="AV25" s="12">
+        <v>938.66666666666674</v>
+      </c>
+      <c r="AW25" s="13">
+        <v>3.517445010922406</v>
+      </c>
       <c r="AX25" s="11"/>
       <c r="AY25" s="11"/>
       <c r="AZ25" s="11"/>
@@ -8092,27 +7777,27 @@
       </c>
       <c r="N26" s="8">
         <f t="shared" ref="N26:N52" si="6">IFERROR(AVERAGE(T26,Z26,AF26,AL26,AR26,AX26,BD26,BJ26,BP26,BV26,CB26,CH26)," ")</f>
-        <v>340038.5</v>
+        <v>298980.59999999998</v>
       </c>
       <c r="O26" s="8">
         <f t="shared" ref="O26:O52" si="7">IFERROR(AVERAGE(U26,AA26,AG26,AM26,AS26,AY26,BE26,BK26,BQ26,BW26,CC26,CI26)," ")</f>
-        <v>25235.5</v>
+        <v>21874.2</v>
       </c>
       <c r="P26" s="8">
         <f t="shared" ref="P26:P52" si="8">IFERROR(SUM(V26,AB26,AH26,AN26,AT26,AZ26,BF26,BL26,BR26,BX26,CD26,CJ26)," ")</f>
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="Q26" s="9">
         <f t="shared" ref="Q26:Q52" si="9">IFERROR(SUM(T26,Z26,AF26,AL26,AR26,AX26,BD26,BJ26,BP26,BV26,CB26,CH26)/P26*3," ")</f>
-        <v>17217.139240506327</v>
+        <v>16367.551094890512</v>
       </c>
       <c r="R26" s="9">
         <f t="shared" ref="R26:R52" si="10">IFERROR(SUM(U26,AA26,AG26,AM26,AS26,AY26,BE26,BK26,BQ26,BW26,CC26,CI26)/P26*3," ")</f>
-        <v>1277.746835443038</v>
+        <v>1197.492700729927</v>
       </c>
       <c r="S26" s="10">
         <f t="shared" ref="S26:S52" si="11">IFERROR(AVERAGE(Y26,AE26,AK26,AQ26,AW26,BC26,BI26,BO26,BU26,CA26,CG26,CM26)," ")</f>
-        <v>3.8084794492313714</v>
+        <v>3.7544996965308322</v>
       </c>
       <c r="T26" s="11">
         <v>319242</v>
@@ -8186,12 +7871,24 @@
       <c r="AQ26" s="13">
         <v>3.9255564083642152</v>
       </c>
-      <c r="AR26" s="11"/>
-      <c r="AS26" s="11"/>
-      <c r="AT26" s="11"/>
-      <c r="AU26" s="12"/>
-      <c r="AV26" s="12"/>
-      <c r="AW26" s="13"/>
+      <c r="AR26" s="11">
+        <v>134749</v>
+      </c>
+      <c r="AS26" s="11">
+        <v>8429</v>
+      </c>
+      <c r="AT26" s="11">
+        <v>37</v>
+      </c>
+      <c r="AU26" s="12">
+        <v>10925.5945945946</v>
+      </c>
+      <c r="AV26" s="12">
+        <v>683.43243243243239</v>
+      </c>
+      <c r="AW26" s="13">
+        <v>3.5385806857286748</v>
+      </c>
       <c r="AX26" s="11"/>
       <c r="AY26" s="11"/>
       <c r="AZ26" s="11"/>
@@ -8434,27 +8131,27 @@
       </c>
       <c r="N28" s="8">
         <f t="shared" si="6"/>
-        <v>301499</v>
+        <v>282603.8</v>
       </c>
       <c r="O28" s="8">
         <f t="shared" si="7"/>
-        <v>83713.75</v>
+        <v>80446.399999999994</v>
       </c>
       <c r="P28" s="8">
         <f t="shared" si="8"/>
-        <v>267</v>
+        <v>309</v>
       </c>
       <c r="Q28" s="9">
         <f t="shared" si="9"/>
-        <v>13550.516853932584</v>
+        <v>13718.631067961165</v>
       </c>
       <c r="R28" s="9">
         <f t="shared" si="10"/>
-        <v>3762.4157303370785</v>
+        <v>3905.1650485436894</v>
       </c>
       <c r="S28" s="10">
         <f t="shared" si="11"/>
-        <v>7.2772394132718237</v>
+        <v>7.3993950340047663</v>
       </c>
       <c r="T28" s="11">
         <v>362826</v>
@@ -8528,12 +8225,24 @@
       <c r="AQ28" s="13">
         <v>7.4044616792696578</v>
       </c>
-      <c r="AR28" s="11"/>
-      <c r="AS28" s="11"/>
-      <c r="AT28" s="11"/>
-      <c r="AU28" s="12"/>
-      <c r="AV28" s="12"/>
-      <c r="AW28" s="13"/>
+      <c r="AR28" s="11">
+        <v>207023</v>
+      </c>
+      <c r="AS28" s="11">
+        <v>67377</v>
+      </c>
+      <c r="AT28" s="11">
+        <v>42</v>
+      </c>
+      <c r="AU28" s="12">
+        <v>14787.357142857139</v>
+      </c>
+      <c r="AV28" s="12">
+        <v>4812.6428571428569</v>
+      </c>
+      <c r="AW28" s="13">
+        <v>7.888017516936535</v>
+      </c>
       <c r="AX28" s="11"/>
       <c r="AY28" s="11"/>
       <c r="AZ28" s="11"/>
@@ -8800,27 +8509,27 @@
       </c>
       <c r="N30" s="8">
         <f t="shared" si="6"/>
-        <v>174884.5</v>
+        <v>161468.79999999999</v>
       </c>
       <c r="O30" s="8">
         <f t="shared" si="7"/>
-        <v>134199.25</v>
+        <v>123072.2</v>
       </c>
       <c r="P30" s="8">
         <f t="shared" si="8"/>
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="Q30" s="9">
         <f t="shared" si="9"/>
-        <v>10545.798994974875</v>
+        <v>10716.955752212391</v>
       </c>
       <c r="R30" s="9">
         <f t="shared" si="10"/>
-        <v>8092.417085427136</v>
+        <v>8168.5088495575219</v>
       </c>
       <c r="S30" s="10">
         <f t="shared" si="11"/>
-        <v>13.806517678227081</v>
+        <v>13.744057091487928</v>
       </c>
       <c r="T30" s="11">
         <v>169875</v>
@@ -8894,12 +8603,24 @@
       <c r="AQ30" s="13">
         <v>13.65612096274366</v>
       </c>
-      <c r="AR30" s="11"/>
-      <c r="AS30" s="11"/>
-      <c r="AT30" s="11"/>
-      <c r="AU30" s="12"/>
-      <c r="AV30" s="12"/>
-      <c r="AW30" s="13"/>
+      <c r="AR30" s="11">
+        <v>107806</v>
+      </c>
+      <c r="AS30" s="11">
+        <v>78564</v>
+      </c>
+      <c r="AT30" s="11">
+        <v>27</v>
+      </c>
+      <c r="AU30" s="12">
+        <v>11978.444444444451</v>
+      </c>
+      <c r="AV30" s="12">
+        <v>8729.3333333333339</v>
+      </c>
+      <c r="AW30" s="13">
+        <v>13.49421474453132</v>
+      </c>
       <c r="AX30" s="11"/>
       <c r="AY30" s="11"/>
       <c r="AZ30" s="11"/>
@@ -8983,27 +8704,27 @@
       </c>
       <c r="N31" s="8">
         <f t="shared" si="6"/>
-        <v>100975.33333333333</v>
+        <v>91060.5</v>
       </c>
       <c r="O31" s="8">
         <f t="shared" si="7"/>
-        <v>3699.6666666666665</v>
+        <v>3317.25</v>
       </c>
       <c r="P31" s="8">
         <f t="shared" si="8"/>
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="Q31" s="9">
         <f t="shared" si="9"/>
-        <v>13170.695652173912</v>
+        <v>12706.116279069767</v>
       </c>
       <c r="R31" s="9">
         <f t="shared" si="10"/>
-        <v>482.56521739130437</v>
+        <v>462.87209302325579</v>
       </c>
       <c r="S31" s="10">
         <f t="shared" si="11"/>
-        <v>2.6670955916892942</v>
+        <v>2.6642849188631521</v>
       </c>
       <c r="T31" s="11"/>
       <c r="U31" s="11"/>
@@ -9065,12 +8786,24 @@
       <c r="AQ31" s="13">
         <v>2.79173317547535</v>
       </c>
-      <c r="AR31" s="11"/>
-      <c r="AS31" s="11"/>
-      <c r="AT31" s="11"/>
-      <c r="AU31" s="12"/>
-      <c r="AV31" s="12"/>
-      <c r="AW31" s="13"/>
+      <c r="AR31" s="11">
+        <v>61316</v>
+      </c>
+      <c r="AS31" s="11">
+        <v>2170</v>
+      </c>
+      <c r="AT31" s="11">
+        <v>17</v>
+      </c>
+      <c r="AU31" s="12">
+        <v>10820.47058823529</v>
+      </c>
+      <c r="AV31" s="12">
+        <v>382.94117647058818</v>
+      </c>
+      <c r="AW31" s="13">
+        <v>2.6558529003847262</v>
+      </c>
       <c r="AX31" s="11"/>
       <c r="AY31" s="11"/>
       <c r="AZ31" s="11"/>
@@ -9154,23 +8887,23 @@
       </c>
       <c r="N32" s="8">
         <f t="shared" si="6"/>
-        <v>209285</v>
+        <v>197428</v>
       </c>
       <c r="O32" s="8">
         <f t="shared" si="7"/>
-        <v>74284</v>
+        <v>70077.2</v>
       </c>
       <c r="P32" s="8">
         <f t="shared" si="8"/>
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="Q32" s="9">
         <f t="shared" si="9"/>
-        <v>17562.377622377622</v>
+        <v>17523.195266272189</v>
       </c>
       <c r="R32" s="9">
         <f t="shared" si="10"/>
-        <v>6233.6223776223778</v>
+        <v>6219.8698224852069</v>
       </c>
       <c r="S32" s="10">
         <f t="shared" si="11"/>
@@ -9248,12 +8981,24 @@
       <c r="AQ32" s="13">
         <v>10</v>
       </c>
-      <c r="AR32" s="11"/>
-      <c r="AS32" s="11"/>
-      <c r="AT32" s="11"/>
-      <c r="AU32" s="12"/>
-      <c r="AV32" s="12"/>
-      <c r="AW32" s="13"/>
+      <c r="AR32" s="11">
+        <v>150000</v>
+      </c>
+      <c r="AS32" s="11">
+        <v>53250</v>
+      </c>
+      <c r="AT32" s="11">
+        <v>26</v>
+      </c>
+      <c r="AU32" s="12">
+        <v>17307.692307692309</v>
+      </c>
+      <c r="AV32" s="12">
+        <v>6144.2307692307686</v>
+      </c>
+      <c r="AW32" s="13">
+        <v>10</v>
+      </c>
       <c r="AX32" s="11"/>
       <c r="AY32" s="11"/>
       <c r="AZ32" s="11"/>
@@ -9508,27 +9253,27 @@
       </c>
       <c r="N34" s="8">
         <f t="shared" si="6"/>
-        <v>22319</v>
+        <v>20948.400000000001</v>
       </c>
       <c r="O34" s="8">
         <f t="shared" si="7"/>
-        <v>100441.5</v>
+        <v>92985.2</v>
       </c>
       <c r="P34" s="8">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="Q34" s="9">
         <f t="shared" si="9"/>
-        <v>3524.0526315789475</v>
+        <v>3611.7931034482758</v>
       </c>
       <c r="R34" s="9">
         <f t="shared" si="10"/>
-        <v>15859.184210526315</v>
+        <v>16031.931034482759</v>
       </c>
       <c r="S34" s="10">
         <f t="shared" si="11"/>
-        <v>36.851068359701159</v>
+        <v>35.763325988811125</v>
       </c>
       <c r="T34" s="11">
         <v>44447</v>
@@ -9602,12 +9347,24 @@
       <c r="AQ34" s="13">
         <v>46.826751967797072</v>
       </c>
-      <c r="AR34" s="11"/>
-      <c r="AS34" s="11"/>
-      <c r="AT34" s="11"/>
-      <c r="AU34" s="12"/>
-      <c r="AV34" s="12"/>
-      <c r="AW34" s="13"/>
+      <c r="AR34" s="11">
+        <v>15466</v>
+      </c>
+      <c r="AS34" s="11">
+        <v>63160</v>
+      </c>
+      <c r="AT34" s="11">
+        <v>11</v>
+      </c>
+      <c r="AU34" s="12">
+        <v>4218</v>
+      </c>
+      <c r="AV34" s="12">
+        <v>17225.45454545454</v>
+      </c>
+      <c r="AW34" s="13">
+        <v>31.41235650525098</v>
+      </c>
       <c r="AX34" s="11"/>
       <c r="AY34" s="11"/>
       <c r="AZ34" s="11"/>
@@ -9691,27 +9448,27 @@
       </c>
       <c r="N35" s="8">
         <f t="shared" si="6"/>
-        <v>25363</v>
+        <v>29845.5</v>
       </c>
       <c r="O35" s="8">
         <f t="shared" si="7"/>
-        <v>1220</v>
+        <v>1717</v>
       </c>
       <c r="P35" s="8">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="Q35" s="9">
         <f t="shared" si="9"/>
-        <v>9511.125</v>
+        <v>7785.782608695652</v>
       </c>
       <c r="R35" s="9">
         <f t="shared" si="10"/>
-        <v>457.5</v>
+        <v>447.91304347826087</v>
       </c>
       <c r="S35" s="10">
         <f t="shared" si="11"/>
-        <v>3.103806941398267</v>
+        <v>3.3623704450056979</v>
       </c>
       <c r="T35" s="11">
         <v>25363</v>
@@ -9749,12 +9506,24 @@
       <c r="AO35" s="12"/>
       <c r="AP35" s="12"/>
       <c r="AQ35" s="13"/>
-      <c r="AR35" s="11"/>
-      <c r="AS35" s="11"/>
-      <c r="AT35" s="11"/>
-      <c r="AU35" s="12"/>
-      <c r="AV35" s="12"/>
-      <c r="AW35" s="13"/>
+      <c r="AR35" s="11">
+        <v>34328</v>
+      </c>
+      <c r="AS35" s="11">
+        <v>2214</v>
+      </c>
+      <c r="AT35" s="11">
+        <v>15</v>
+      </c>
+      <c r="AU35" s="12">
+        <v>6865.6</v>
+      </c>
+      <c r="AV35" s="12">
+        <v>442.8</v>
+      </c>
+      <c r="AW35" s="13">
+        <v>3.6209339486131289</v>
+      </c>
       <c r="AX35" s="11"/>
       <c r="AY35" s="11"/>
       <c r="AZ35" s="11"/>
@@ -9838,27 +9607,27 @@
       </c>
       <c r="N36" s="8">
         <f t="shared" si="6"/>
-        <v>38475.25</v>
+        <v>41199.800000000003</v>
       </c>
       <c r="O36" s="8">
         <f t="shared" si="7"/>
-        <v>3510.75</v>
+        <v>3619.6</v>
       </c>
       <c r="P36" s="8">
         <f t="shared" si="8"/>
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="Q36" s="9">
         <f t="shared" si="9"/>
-        <v>12825.083333333332</v>
+        <v>12117.588235294117</v>
       </c>
       <c r="R36" s="9">
         <f t="shared" si="10"/>
-        <v>1170.25</v>
+        <v>1064.5882352941176</v>
       </c>
       <c r="S36" s="10">
         <f t="shared" si="11"/>
-        <v>10.960906890960137</v>
+        <v>9.5561888418230687</v>
       </c>
       <c r="T36" s="11">
         <v>68082</v>
@@ -9932,12 +9701,24 @@
       <c r="AQ36" s="13">
         <v>4.1296708072771144</v>
       </c>
-      <c r="AR36" s="11"/>
-      <c r="AS36" s="11"/>
-      <c r="AT36" s="11"/>
-      <c r="AU36" s="12"/>
-      <c r="AV36" s="12"/>
-      <c r="AW36" s="13"/>
+      <c r="AR36" s="11">
+        <v>52098</v>
+      </c>
+      <c r="AS36" s="11">
+        <v>4055</v>
+      </c>
+      <c r="AT36" s="11">
+        <v>15</v>
+      </c>
+      <c r="AU36" s="12">
+        <v>10419.6</v>
+      </c>
+      <c r="AV36" s="12">
+        <v>811</v>
+      </c>
+      <c r="AW36" s="13">
+        <v>3.9373166452747959</v>
+      </c>
       <c r="AX36" s="11"/>
       <c r="AY36" s="11"/>
       <c r="AZ36" s="11"/>
@@ -10021,27 +9802,27 @@
       </c>
       <c r="N37" s="8">
         <f t="shared" si="6"/>
-        <v>68582.75</v>
+        <v>67434.2</v>
       </c>
       <c r="O37" s="8">
         <f t="shared" si="7"/>
-        <v>6122.75</v>
+        <v>5528.6</v>
       </c>
       <c r="P37" s="8">
         <f t="shared" si="8"/>
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="Q37" s="9">
         <f t="shared" si="9"/>
-        <v>9682.2705882352948</v>
+        <v>10217.30303030303</v>
       </c>
       <c r="R37" s="9">
         <f t="shared" si="10"/>
-        <v>864.38823529411764</v>
+        <v>837.66666666666674</v>
       </c>
       <c r="S37" s="10">
         <f t="shared" si="11"/>
-        <v>3.5923636074556686</v>
+        <v>3.5156997310536533</v>
       </c>
       <c r="T37" s="11">
         <v>60720</v>
@@ -10115,12 +9896,24 @@
       <c r="AQ37" s="13">
         <v>3.847762152139766</v>
       </c>
-      <c r="AR37" s="11"/>
-      <c r="AS37" s="11"/>
-      <c r="AT37" s="11"/>
-      <c r="AU37" s="12"/>
-      <c r="AV37" s="12"/>
-      <c r="AW37" s="13"/>
+      <c r="AR37" s="11">
+        <v>62840</v>
+      </c>
+      <c r="AS37" s="11">
+        <v>3152</v>
+      </c>
+      <c r="AT37" s="11">
+        <v>14</v>
+      </c>
+      <c r="AU37" s="12">
+        <v>13465.71428571429</v>
+      </c>
+      <c r="AV37" s="12">
+        <v>675.42857142857144</v>
+      </c>
+      <c r="AW37" s="13">
+        <v>3.2090442254455911</v>
+      </c>
       <c r="AX37" s="11"/>
       <c r="AY37" s="11"/>
       <c r="AZ37" s="11"/>
@@ -10202,29 +9995,29 @@
       <c r="M38" s="10">
         <v>5.3803530180983188</v>
       </c>
-      <c r="N38" s="8" t="str">
+      <c r="N38" s="8">
         <f t="shared" si="6"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="O38" s="8" t="str">
+        <v>32903</v>
+      </c>
+      <c r="O38" s="8">
         <f t="shared" si="7"/>
-        <v xml:space="preserve"> </v>
+        <v>5350</v>
       </c>
       <c r="P38" s="8">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Q38" s="9" t="str">
+        <v>19</v>
+      </c>
+      <c r="Q38" s="9">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="R38" s="9" t="str">
+        <v>5195.2105263157891</v>
+      </c>
+      <c r="R38" s="9">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="S38" s="10" t="str">
+        <v>844.73684210526312</v>
+      </c>
+      <c r="S38" s="10">
         <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <v>5.5839326303001471</v>
       </c>
       <c r="T38" s="11"/>
       <c r="U38" s="11"/>
@@ -10250,12 +10043,24 @@
       <c r="AO38" s="12"/>
       <c r="AP38" s="12"/>
       <c r="AQ38" s="13"/>
-      <c r="AR38" s="11"/>
-      <c r="AS38" s="11"/>
-      <c r="AT38" s="11"/>
-      <c r="AU38" s="12"/>
-      <c r="AV38" s="12"/>
-      <c r="AW38" s="13"/>
+      <c r="AR38" s="11">
+        <v>32903</v>
+      </c>
+      <c r="AS38" s="11">
+        <v>5350</v>
+      </c>
+      <c r="AT38" s="11">
+        <v>19</v>
+      </c>
+      <c r="AU38" s="12">
+        <v>5195.2105263157891</v>
+      </c>
+      <c r="AV38" s="12">
+        <v>844.73684210526312</v>
+      </c>
+      <c r="AW38" s="13">
+        <v>5.5839326303001471</v>
+      </c>
       <c r="AX38" s="11"/>
       <c r="AY38" s="11"/>
       <c r="AZ38" s="11"/>
@@ -10780,27 +10585,27 @@
       </c>
       <c r="N42" s="8">
         <f t="shared" si="6"/>
-        <v>18608.75</v>
+        <v>16613</v>
       </c>
       <c r="O42" s="8">
         <f t="shared" si="7"/>
-        <v>46047.75</v>
+        <v>40794</v>
       </c>
       <c r="P42" s="8">
         <f t="shared" si="8"/>
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="Q42" s="9">
         <f t="shared" si="9"/>
-        <v>4213.3018867924529</v>
+        <v>4153.25</v>
       </c>
       <c r="R42" s="9">
         <f t="shared" si="10"/>
-        <v>10425.905660377359</v>
+        <v>10198.5</v>
       </c>
       <c r="S42" s="10">
         <f t="shared" si="11"/>
-        <v>22.885766547076475</v>
+        <v>22.610371211861718</v>
       </c>
       <c r="T42" s="11">
         <v>16200</v>
@@ -10874,12 +10679,24 @@
       <c r="AQ42" s="13">
         <v>24.696839033927329</v>
       </c>
-      <c r="AR42" s="11"/>
-      <c r="AS42" s="11"/>
-      <c r="AT42" s="11"/>
-      <c r="AU42" s="12"/>
-      <c r="AV42" s="12"/>
-      <c r="AW42" s="13"/>
+      <c r="AR42" s="11">
+        <v>8630</v>
+      </c>
+      <c r="AS42" s="11">
+        <v>19779</v>
+      </c>
+      <c r="AT42" s="11">
+        <v>7</v>
+      </c>
+      <c r="AU42" s="12">
+        <v>3698.571428571428</v>
+      </c>
+      <c r="AV42" s="12">
+        <v>8476.7142857142862</v>
+      </c>
+      <c r="AW42" s="13">
+        <v>21.508789871002691</v>
+      </c>
       <c r="AX42" s="11"/>
       <c r="AY42" s="11"/>
       <c r="AZ42" s="11"/>
@@ -10963,27 +10780,27 @@
       </c>
       <c r="N43" s="8">
         <f t="shared" si="6"/>
-        <v>352856.75</v>
+        <v>345869.6</v>
       </c>
       <c r="O43" s="8">
         <f t="shared" si="7"/>
-        <v>13156.25</v>
+        <v>13120.8</v>
       </c>
       <c r="P43" s="8">
         <f t="shared" si="8"/>
-        <v>190</v>
+        <v>231</v>
       </c>
       <c r="Q43" s="9">
         <f t="shared" si="9"/>
-        <v>22285.689473684211</v>
+        <v>22459.064935064933</v>
       </c>
       <c r="R43" s="9">
         <f t="shared" si="10"/>
-        <v>830.92105263157896</v>
+        <v>852</v>
       </c>
       <c r="S43" s="10">
         <f t="shared" si="11"/>
-        <v>2.656826435279104</v>
+        <v>2.6845918694457991</v>
       </c>
       <c r="T43" s="11">
         <v>178860</v>
@@ -11057,12 +10874,24 @@
       <c r="AQ43" s="13">
         <v>2.727524745674474</v>
       </c>
-      <c r="AR43" s="11"/>
-      <c r="AS43" s="11"/>
-      <c r="AT43" s="11"/>
-      <c r="AU43" s="12"/>
-      <c r="AV43" s="12"/>
-      <c r="AW43" s="13"/>
+      <c r="AR43" s="11">
+        <v>317921</v>
+      </c>
+      <c r="AS43" s="11">
+        <v>12979</v>
+      </c>
+      <c r="AT43" s="11">
+        <v>41</v>
+      </c>
+      <c r="AU43" s="12">
+        <v>23262.512195121952</v>
+      </c>
+      <c r="AV43" s="12">
+        <v>949.68292682926835</v>
+      </c>
+      <c r="AW43" s="13">
+        <v>2.795653606112579</v>
+      </c>
       <c r="AX43" s="11"/>
       <c r="AY43" s="11"/>
       <c r="AZ43" s="11"/>
@@ -11146,27 +10975,27 @@
       </c>
       <c r="N44" s="8">
         <f t="shared" si="6"/>
-        <v>344710</v>
+        <v>342378.4</v>
       </c>
       <c r="O44" s="8">
         <f t="shared" si="7"/>
-        <v>13153</v>
+        <v>13040.6</v>
       </c>
       <c r="P44" s="8">
         <f t="shared" si="8"/>
-        <v>182</v>
+        <v>226</v>
       </c>
       <c r="Q44" s="9">
         <f t="shared" si="9"/>
-        <v>22728.13186813187</v>
+        <v>22724.230088495577</v>
       </c>
       <c r="R44" s="9">
         <f t="shared" si="10"/>
-        <v>867.23076923076928</v>
+        <v>865.52654867256638</v>
       </c>
       <c r="S44" s="10">
         <f t="shared" si="11"/>
-        <v>2.6820395777431871</v>
+        <v>2.6815542739087879</v>
       </c>
       <c r="T44" s="11">
         <v>184368</v>
@@ -11240,12 +11069,24 @@
       <c r="AQ44" s="13">
         <v>2.8268047151973499</v>
       </c>
-      <c r="AR44" s="11"/>
-      <c r="AS44" s="11"/>
-      <c r="AT44" s="11"/>
-      <c r="AU44" s="12"/>
-      <c r="AV44" s="12"/>
-      <c r="AW44" s="13"/>
+      <c r="AR44" s="11">
+        <v>333052</v>
+      </c>
+      <c r="AS44" s="11">
+        <v>12591</v>
+      </c>
+      <c r="AT44" s="11">
+        <v>44</v>
+      </c>
+      <c r="AU44" s="12">
+        <v>22708.090909090912</v>
+      </c>
+      <c r="AV44" s="12">
+        <v>858.47727272727275</v>
+      </c>
+      <c r="AW44" s="13">
+        <v>2.6796130585711908</v>
+      </c>
       <c r="AX44" s="11"/>
       <c r="AY44" s="11"/>
       <c r="AZ44" s="11"/>
@@ -11329,27 +11170,27 @@
       </c>
       <c r="N45" s="8">
         <f t="shared" si="6"/>
-        <v>279698.75</v>
+        <v>260191.8</v>
       </c>
       <c r="O45" s="8">
         <f t="shared" si="7"/>
-        <v>5112</v>
+        <v>5025.6000000000004</v>
       </c>
       <c r="P45" s="8">
         <f t="shared" si="8"/>
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="Q45" s="9">
         <f t="shared" si="9"/>
-        <v>22081.480263157893</v>
+        <v>20759.984042553191</v>
       </c>
       <c r="R45" s="9">
         <f t="shared" si="10"/>
-        <v>403.57894736842104</v>
+        <v>400.97872340425533</v>
       </c>
       <c r="S45" s="10">
         <f t="shared" si="11"/>
-        <v>1.8991374990045109</v>
+        <v>1.9716880358686482</v>
       </c>
       <c r="T45" s="11">
         <v>281804</v>
@@ -11423,12 +11264,24 @@
       <c r="AQ45" s="13">
         <v>1.805194551747145</v>
       </c>
-      <c r="AR45" s="11"/>
-      <c r="AS45" s="11"/>
-      <c r="AT45" s="11"/>
-      <c r="AU45" s="12"/>
-      <c r="AV45" s="12"/>
-      <c r="AW45" s="13"/>
+      <c r="AR45" s="11">
+        <v>182164</v>
+      </c>
+      <c r="AS45" s="11">
+        <v>4680</v>
+      </c>
+      <c r="AT45" s="11">
+        <v>36</v>
+      </c>
+      <c r="AU45" s="12">
+        <v>15180.33333333333</v>
+      </c>
+      <c r="AV45" s="12">
+        <v>390</v>
+      </c>
+      <c r="AW45" s="13">
+        <v>2.261890183325197</v>
+      </c>
       <c r="AX45" s="11"/>
       <c r="AY45" s="11"/>
       <c r="AZ45" s="11"/>
@@ -11512,27 +11365,27 @@
       </c>
       <c r="N46" s="8">
         <f t="shared" si="6"/>
-        <v>294408.5</v>
+        <v>267964.59999999998</v>
       </c>
       <c r="O46" s="8">
         <f t="shared" si="7"/>
-        <v>5115.5</v>
+        <v>5024.2</v>
       </c>
       <c r="P46" s="8">
         <f t="shared" si="8"/>
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="Q46" s="9">
         <f t="shared" si="9"/>
-        <v>24534.041666666664</v>
+        <v>22455.134078212293</v>
       </c>
       <c r="R46" s="9">
         <f t="shared" si="10"/>
-        <v>426.29166666666669</v>
+        <v>421.02234636871515</v>
       </c>
       <c r="S46" s="10">
         <f t="shared" si="11"/>
-        <v>1.8530348569394217</v>
+        <v>1.9611200295533742</v>
       </c>
       <c r="T46" s="11">
         <v>407925</v>
@@ -11606,12 +11459,24 @@
       <c r="AQ46" s="13">
         <v>1.8453318354694479</v>
       </c>
-      <c r="AR46" s="11"/>
-      <c r="AS46" s="11"/>
-      <c r="AT46" s="11"/>
-      <c r="AU46" s="12"/>
-      <c r="AV46" s="12"/>
-      <c r="AW46" s="13"/>
+      <c r="AR46" s="11">
+        <v>162189</v>
+      </c>
+      <c r="AS46" s="11">
+        <v>4659</v>
+      </c>
+      <c r="AT46" s="11">
+        <v>35</v>
+      </c>
+      <c r="AU46" s="12">
+        <v>13901.914285714291</v>
+      </c>
+      <c r="AV46" s="12">
+        <v>399.34285714285721</v>
+      </c>
+      <c r="AW46" s="13">
+        <v>2.393460720009184</v>
+      </c>
       <c r="AX46" s="11"/>
       <c r="AY46" s="11"/>
       <c r="AZ46" s="11"/>
@@ -11695,27 +11560,27 @@
       </c>
       <c r="N47" s="8">
         <f t="shared" si="6"/>
-        <v>237353.5</v>
+        <v>226047.2</v>
       </c>
       <c r="O47" s="8">
         <f t="shared" si="7"/>
-        <v>18205</v>
+        <v>17131.2</v>
       </c>
       <c r="P47" s="8">
         <f t="shared" si="8"/>
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="Q47" s="9">
         <f t="shared" si="9"/>
-        <v>12330.051948051949</v>
+        <v>12558.177777777779</v>
       </c>
       <c r="R47" s="9">
         <f t="shared" si="10"/>
-        <v>945.71428571428578</v>
+        <v>951.73333333333335</v>
       </c>
       <c r="S47" s="10">
         <f t="shared" si="11"/>
-        <v>3.8986458889914624</v>
+        <v>3.8714494822338699</v>
       </c>
       <c r="T47" s="11">
         <v>211685</v>
@@ -11789,12 +11654,24 @@
       <c r="AQ47" s="13">
         <v>3.996457551724284</v>
       </c>
-      <c r="AR47" s="11"/>
-      <c r="AS47" s="11"/>
-      <c r="AT47" s="11"/>
-      <c r="AU47" s="12"/>
-      <c r="AV47" s="12"/>
-      <c r="AW47" s="13"/>
+      <c r="AR47" s="11">
+        <v>180822</v>
+      </c>
+      <c r="AS47" s="11">
+        <v>12836</v>
+      </c>
+      <c r="AT47" s="11">
+        <v>39</v>
+      </c>
+      <c r="AU47" s="12">
+        <v>13909.38461538461</v>
+      </c>
+      <c r="AV47" s="12">
+        <v>987.38461538461547</v>
+      </c>
+      <c r="AW47" s="13">
+        <v>3.7626638552035012</v>
+      </c>
       <c r="AX47" s="11"/>
       <c r="AY47" s="11"/>
       <c r="AZ47" s="11"/>
@@ -11878,27 +11755,27 @@
       </c>
       <c r="N48" s="8">
         <f t="shared" si="6"/>
-        <v>230831.5</v>
+        <v>212283.4</v>
       </c>
       <c r="O48" s="8">
         <f t="shared" si="7"/>
-        <v>17536</v>
+        <v>16338.2</v>
       </c>
       <c r="P48" s="8">
         <f t="shared" si="8"/>
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="Q48" s="9">
         <f t="shared" si="9"/>
-        <v>11939.560344827585</v>
+        <v>12061.556818181818</v>
       </c>
       <c r="R48" s="9">
         <f t="shared" si="10"/>
-        <v>907.0344827586207</v>
+        <v>928.30681818181824</v>
       </c>
       <c r="S48" s="10">
         <f t="shared" si="11"/>
-        <v>3.8622636912136121</v>
+        <v>3.9111874481699389</v>
       </c>
       <c r="T48" s="11">
         <v>225871</v>
@@ -11972,12 +11849,24 @@
       <c r="AQ48" s="13">
         <v>3.8847292706152681</v>
       </c>
-      <c r="AR48" s="11"/>
-      <c r="AS48" s="11"/>
-      <c r="AT48" s="11"/>
-      <c r="AU48" s="12"/>
-      <c r="AV48" s="12"/>
-      <c r="AW48" s="13"/>
+      <c r="AR48" s="11">
+        <v>138091</v>
+      </c>
+      <c r="AS48" s="11">
+        <v>11547</v>
+      </c>
+      <c r="AT48" s="11">
+        <v>32</v>
+      </c>
+      <c r="AU48" s="12">
+        <v>12946.03125</v>
+      </c>
+      <c r="AV48" s="12">
+        <v>1082.53125</v>
+      </c>
+      <c r="AW48" s="13">
+        <v>4.1068824759952438</v>
+      </c>
       <c r="AX48" s="11"/>
       <c r="AY48" s="11"/>
       <c r="AZ48" s="11"/>
@@ -12061,27 +11950,27 @@
       </c>
       <c r="N49" s="8">
         <f t="shared" si="6"/>
-        <v>226970.5</v>
+        <v>202038</v>
       </c>
       <c r="O49" s="8">
         <f t="shared" si="7"/>
-        <v>41950.75</v>
+        <v>38803.800000000003</v>
       </c>
       <c r="P49" s="8">
         <f t="shared" si="8"/>
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="Q49" s="9">
         <f t="shared" si="9"/>
-        <v>15387.830508474577</v>
+        <v>15077.462686567163</v>
       </c>
       <c r="R49" s="9">
         <f t="shared" si="10"/>
-        <v>2844.1186440677966</v>
+        <v>2895.8059701492539</v>
       </c>
       <c r="S49" s="10">
         <f t="shared" si="11"/>
-        <v>6.0035981961346208</v>
+        <v>6.167864521976214</v>
       </c>
       <c r="T49" s="11">
         <v>268651</v>
@@ -12155,12 +12044,24 @@
       <c r="AQ49" s="13">
         <v>6.8243094731344884</v>
       </c>
-      <c r="AR49" s="11"/>
-      <c r="AS49" s="11"/>
-      <c r="AT49" s="11"/>
-      <c r="AU49" s="12"/>
-      <c r="AV49" s="12"/>
-      <c r="AW49" s="13"/>
+      <c r="AR49" s="11">
+        <v>102308</v>
+      </c>
+      <c r="AS49" s="11">
+        <v>26216</v>
+      </c>
+      <c r="AT49" s="11">
+        <v>24</v>
+      </c>
+      <c r="AU49" s="12">
+        <v>12788.5</v>
+      </c>
+      <c r="AV49" s="12">
+        <v>3277</v>
+      </c>
+      <c r="AW49" s="13">
+        <v>6.8249298253425854</v>
+      </c>
       <c r="AX49" s="11"/>
       <c r="AY49" s="11"/>
       <c r="AZ49" s="11"/>
@@ -12244,23 +12145,23 @@
       </c>
       <c r="N50" s="8">
         <f t="shared" si="6"/>
-        <v>333535</v>
+        <v>336236</v>
       </c>
       <c r="O50" s="8">
         <f t="shared" si="7"/>
-        <v>12369.25</v>
+        <v>12469</v>
       </c>
       <c r="P50" s="8">
         <f t="shared" si="8"/>
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="Q50" s="9">
         <f t="shared" si="9"/>
-        <v>23823.928571428572</v>
+        <v>24483.203883495145</v>
       </c>
       <c r="R50" s="9">
         <f t="shared" si="10"/>
-        <v>883.51785714285722</v>
+        <v>907.93689320388353</v>
       </c>
       <c r="S50" s="10">
         <f t="shared" si="11"/>
@@ -12338,12 +12239,24 @@
       <c r="AQ50" s="13">
         <v>2.65</v>
       </c>
-      <c r="AR50" s="11"/>
-      <c r="AS50" s="11"/>
-      <c r="AT50" s="11"/>
-      <c r="AU50" s="12"/>
-      <c r="AV50" s="12"/>
-      <c r="AW50" s="13"/>
+      <c r="AR50" s="11">
+        <v>347040</v>
+      </c>
+      <c r="AS50" s="11">
+        <v>12868</v>
+      </c>
+      <c r="AT50" s="11">
+        <v>38</v>
+      </c>
+      <c r="AU50" s="12">
+        <v>27397.89473684211</v>
+      </c>
+      <c r="AV50" s="12">
+        <v>1015.894736842105</v>
+      </c>
+      <c r="AW50" s="13">
+        <v>2.65</v>
+      </c>
       <c r="AX50" s="11"/>
       <c r="AY50" s="11"/>
       <c r="AZ50" s="11"/>
@@ -12427,23 +12340,23 @@
       </c>
       <c r="N51" s="8">
         <f t="shared" si="6"/>
-        <v>350030</v>
+        <v>359836</v>
       </c>
       <c r="O51" s="8">
         <f t="shared" si="7"/>
-        <v>12980.75</v>
+        <v>13344.4</v>
       </c>
       <c r="P51" s="8">
         <f t="shared" si="8"/>
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="Q51" s="9">
         <f t="shared" si="9"/>
-        <v>24563.508771929824</v>
+        <v>25825.55023923445</v>
       </c>
       <c r="R51" s="9">
         <f t="shared" si="10"/>
-        <v>910.92982456140362</v>
+        <v>957.73205741626793</v>
       </c>
       <c r="S51" s="10">
         <f t="shared" si="11"/>
@@ -12521,12 +12434,24 @@
       <c r="AQ51" s="13">
         <v>2.65</v>
       </c>
-      <c r="AR51" s="11"/>
-      <c r="AS51" s="11"/>
-      <c r="AT51" s="11"/>
-      <c r="AU51" s="12"/>
-      <c r="AV51" s="12"/>
-      <c r="AW51" s="13"/>
+      <c r="AR51" s="11">
+        <v>399060</v>
+      </c>
+      <c r="AS51" s="11">
+        <v>14799</v>
+      </c>
+      <c r="AT51" s="11">
+        <v>38</v>
+      </c>
+      <c r="AU51" s="12">
+        <v>31504.736842105271</v>
+      </c>
+      <c r="AV51" s="12">
+        <v>1168.3421052631579</v>
+      </c>
+      <c r="AW51" s="13">
+        <v>2.65</v>
+      </c>
       <c r="AX51" s="11"/>
       <c r="AY51" s="11"/>
       <c r="AZ51" s="11"/>
@@ -12610,27 +12535,27 @@
       </c>
       <c r="N52" s="8">
         <f t="shared" si="6"/>
-        <v>51635.25</v>
+        <v>48248.6</v>
       </c>
       <c r="O52" s="8">
         <f t="shared" si="7"/>
-        <v>113420.75</v>
+        <v>111525</v>
       </c>
       <c r="P52" s="8">
         <f t="shared" si="8"/>
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="Q52" s="9">
         <f t="shared" si="9"/>
-        <v>5684.6146788990827</v>
+        <v>5610.3023255813951</v>
       </c>
       <c r="R52" s="9">
         <f t="shared" si="10"/>
-        <v>12486.688073394496</v>
+        <v>12968.023255813952</v>
       </c>
       <c r="S52" s="10">
         <f t="shared" si="11"/>
-        <v>23.366408657016667</v>
+        <v>24.086234744086354</v>
       </c>
       <c r="T52" s="11">
         <v>62208</v>
@@ -12704,12 +12629,24 @@
       <c r="AQ52" s="13">
         <v>24.3368598517911</v>
       </c>
-      <c r="AR52" s="11"/>
-      <c r="AS52" s="11"/>
-      <c r="AT52" s="11"/>
-      <c r="AU52" s="12"/>
-      <c r="AV52" s="12"/>
-      <c r="AW52" s="13"/>
+      <c r="AR52" s="11">
+        <v>34702</v>
+      </c>
+      <c r="AS52" s="11">
+        <v>103942</v>
+      </c>
+      <c r="AT52" s="11">
+        <v>20</v>
+      </c>
+      <c r="AU52" s="12">
+        <v>5205.2999999999993</v>
+      </c>
+      <c r="AV52" s="12">
+        <v>15591.3</v>
+      </c>
+      <c r="AW52" s="13">
+        <v>26.965539092365109</v>
+      </c>
       <c r="AX52" s="11"/>
       <c r="AY52" s="11"/>
       <c r="AZ52" s="11"/>
@@ -12779,11 +12716,11 @@
       <c r="M53" s="14"/>
       <c r="N53" s="14">
         <f>SUM(N3:N52)</f>
-        <v>10327790.083333332</v>
+        <v>9764429.2499999981</v>
       </c>
       <c r="O53" s="14">
         <f>SUM(O3:O52)</f>
-        <v>2094439.75</v>
+        <v>1973150.8833333333</v>
       </c>
       <c r="P53" s="14"/>
       <c r="Q53" s="14"/>
@@ -12839,11 +12776,11 @@
       <c r="AQ53" s="14"/>
       <c r="AR53" s="14">
         <f>SUM(AR3:AR52)</f>
-        <v>0</v>
+        <v>7146278</v>
       </c>
       <c r="AS53" s="14">
         <f>SUM(AS3:AS52)</f>
-        <v>0</v>
+        <v>1380043</v>
       </c>
       <c r="AT53" s="14"/>
       <c r="AU53" s="14"/>
@@ -13530,27 +13467,27 @@
       </c>
       <c r="N58" s="8">
         <f t="shared" si="12"/>
-        <v>4737481.75</v>
+        <v>4402178.8</v>
       </c>
       <c r="O58" s="8">
         <f t="shared" si="13"/>
-        <v>51563.75</v>
+        <v>48528.6</v>
       </c>
       <c r="P58" s="8">
         <f t="shared" si="14"/>
-        <v>282</v>
+        <v>334</v>
       </c>
       <c r="Q58" s="9">
         <f t="shared" si="15"/>
-        <v>201594.96808510637</v>
+        <v>197702.64071856288</v>
       </c>
       <c r="R58" s="9">
         <f t="shared" si="16"/>
-        <v>2194.2021276595747</v>
+        <v>2179.4281437125751</v>
       </c>
       <c r="S58" s="10">
         <f t="shared" si="17"/>
-        <v>1.3274298775766193</v>
+        <v>1.3396388513500848</v>
       </c>
       <c r="T58" s="11">
         <v>4555723</v>
@@ -13624,12 +13561,24 @@
       <c r="AQ58" s="13">
         <v>1.31978687700285</v>
       </c>
-      <c r="AR58" s="11"/>
-      <c r="AS58" s="11"/>
-      <c r="AT58" s="11"/>
-      <c r="AU58" s="12"/>
-      <c r="AV58" s="12"/>
-      <c r="AW58" s="13"/>
+      <c r="AR58" s="11">
+        <v>3060967</v>
+      </c>
+      <c r="AS58" s="11">
+        <v>36388</v>
+      </c>
+      <c r="AT58" s="11">
+        <v>52</v>
+      </c>
+      <c r="AU58" s="12">
+        <v>176594.25</v>
+      </c>
+      <c r="AV58" s="12">
+        <v>2099.3076923076919</v>
+      </c>
+      <c r="AW58" s="13">
+        <v>1.388474746443946</v>
+      </c>
       <c r="AX58" s="11"/>
       <c r="AY58" s="11"/>
       <c r="AZ58" s="11"/>
@@ -13854,27 +13803,27 @@
       </c>
       <c r="N60" s="8">
         <f t="shared" si="12"/>
-        <v>3231201.5</v>
+        <v>3128602.6</v>
       </c>
       <c r="O60" s="8">
         <f t="shared" si="13"/>
-        <v>8097.75</v>
+        <v>8034.6</v>
       </c>
       <c r="P60" s="8">
         <f t="shared" si="14"/>
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="Q60" s="9">
         <f t="shared" si="15"/>
-        <v>199868.13402061854</v>
+        <v>196355.81171548116</v>
       </c>
       <c r="R60" s="9">
         <f t="shared" si="16"/>
-        <v>500.89175257731955</v>
+        <v>504.26359832635984</v>
       </c>
       <c r="S60" s="10">
         <f t="shared" si="17"/>
-        <v>0.63147412042919537</v>
+        <v>0.64132439165172694</v>
       </c>
       <c r="T60" s="11">
         <v>2164532</v>
@@ -13948,12 +13897,24 @@
       <c r="AQ60" s="13">
         <v>0.67439910224963162</v>
       </c>
-      <c r="AR60" s="11"/>
-      <c r="AS60" s="11"/>
-      <c r="AT60" s="11"/>
-      <c r="AU60" s="12"/>
-      <c r="AV60" s="12"/>
-      <c r="AW60" s="13"/>
+      <c r="AR60" s="11">
+        <v>2718207</v>
+      </c>
+      <c r="AS60" s="11">
+        <v>7782</v>
+      </c>
+      <c r="AT60" s="11">
+        <v>45</v>
+      </c>
+      <c r="AU60" s="12">
+        <v>181213.8</v>
+      </c>
+      <c r="AV60" s="12">
+        <v>518.79999999999995</v>
+      </c>
+      <c r="AW60" s="13">
+        <v>0.68072547654185334</v>
+      </c>
       <c r="AX60" s="11"/>
       <c r="AY60" s="11"/>
       <c r="AZ60" s="11"/>
@@ -14040,27 +14001,27 @@
       </c>
       <c r="N61" s="8">
         <f t="shared" si="12"/>
-        <v>2878654.6666666665</v>
+        <v>3105867</v>
       </c>
       <c r="O61" s="8">
         <f t="shared" si="13"/>
-        <v>6192</v>
+        <v>6108.25</v>
       </c>
       <c r="P61" s="8">
         <f t="shared" si="14"/>
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="Q61" s="9">
         <f t="shared" si="15"/>
-        <v>193342.4776119403</v>
+        <v>208214.54748603352</v>
       </c>
       <c r="R61" s="9">
         <f t="shared" si="16"/>
-        <v>415.88059701492534</v>
+        <v>409.49162011173189</v>
       </c>
       <c r="S61" s="10">
         <f t="shared" si="17"/>
-        <v>0.59310052086524845</v>
+        <v>0.56954532951104564</v>
       </c>
       <c r="T61" s="11"/>
       <c r="U61" s="11"/>
@@ -14122,12 +14083,24 @@
       <c r="AQ61" s="13">
         <v>0.50997603154759741</v>
       </c>
-      <c r="AR61" s="11"/>
-      <c r="AS61" s="11"/>
-      <c r="AT61" s="11"/>
-      <c r="AU61" s="12"/>
-      <c r="AV61" s="12"/>
-      <c r="AW61" s="13"/>
+      <c r="AR61" s="11">
+        <v>3787504</v>
+      </c>
+      <c r="AS61" s="11">
+        <v>5857</v>
+      </c>
+      <c r="AT61" s="11">
+        <v>45</v>
+      </c>
+      <c r="AU61" s="12">
+        <v>252500.26666666669</v>
+      </c>
+      <c r="AV61" s="12">
+        <v>390.4666666666667</v>
+      </c>
+      <c r="AW61" s="13">
+        <v>0.49887975544843738</v>
+      </c>
       <c r="AX61" s="11"/>
       <c r="AY61" s="11"/>
       <c r="AZ61" s="11"/>
@@ -14214,27 +14187,27 @@
       </c>
       <c r="N62" s="8">
         <f t="shared" si="12"/>
-        <v>3402174.25</v>
+        <v>3563489.2</v>
       </c>
       <c r="O62" s="8">
         <f t="shared" si="13"/>
-        <v>6629.25</v>
+        <v>7585</v>
       </c>
       <c r="P62" s="8">
         <f t="shared" si="14"/>
-        <v>186</v>
+        <v>230</v>
       </c>
       <c r="Q62" s="9">
         <f t="shared" si="15"/>
-        <v>219495.11290322579</v>
+        <v>232401.46956521738</v>
       </c>
       <c r="R62" s="9">
         <f t="shared" si="16"/>
-        <v>427.69354838709677</v>
+        <v>494.67391304347825</v>
       </c>
       <c r="S62" s="10">
         <f t="shared" si="17"/>
-        <v>0.54302556662120127</v>
+        <v>0.566420453296961</v>
       </c>
       <c r="T62" s="11">
         <v>2675265</v>
@@ -14308,12 +14281,24 @@
       <c r="AQ62" s="13">
         <v>0.53628938069175069</v>
       </c>
-      <c r="AR62" s="11"/>
-      <c r="AS62" s="11"/>
-      <c r="AT62" s="11"/>
-      <c r="AU62" s="12"/>
-      <c r="AV62" s="12"/>
-      <c r="AW62" s="13"/>
+      <c r="AR62" s="11">
+        <v>4208749</v>
+      </c>
+      <c r="AS62" s="11">
+        <v>11408</v>
+      </c>
+      <c r="AT62" s="11">
+        <v>44</v>
+      </c>
+      <c r="AU62" s="12">
+        <v>286960.15909090912</v>
+      </c>
+      <c r="AV62" s="12">
+        <v>777.81818181818176</v>
+      </c>
+      <c r="AW62" s="13">
+        <v>0.66</v>
+      </c>
       <c r="AX62" s="11"/>
       <c r="AY62" s="11"/>
       <c r="AZ62" s="11"/>
@@ -14400,27 +14385,27 @@
       </c>
       <c r="N63" s="8">
         <f t="shared" si="12"/>
-        <v>9753615.75</v>
+        <v>9701326</v>
       </c>
       <c r="O63" s="8">
         <f t="shared" si="13"/>
-        <v>10593</v>
+        <v>10280.6</v>
       </c>
       <c r="P63" s="8">
         <f t="shared" si="14"/>
-        <v>289</v>
+        <v>342</v>
       </c>
       <c r="Q63" s="9">
         <f t="shared" si="15"/>
-        <v>404994.42560553632</v>
+        <v>425496.75438596494</v>
       </c>
       <c r="R63" s="9">
         <f t="shared" si="16"/>
-        <v>439.84775086505192</v>
+        <v>450.90350877192981</v>
       </c>
       <c r="S63" s="10">
         <f t="shared" si="17"/>
-        <v>0.41942585000884092</v>
+        <v>0.41391790428412933</v>
       </c>
       <c r="T63" s="11">
         <v>9298604</v>
@@ -14494,12 +14479,24 @@
       <c r="AQ63" s="13">
         <v>0.42050458176459038</v>
       </c>
-      <c r="AR63" s="11"/>
-      <c r="AS63" s="11"/>
-      <c r="AT63" s="11"/>
-      <c r="AU63" s="12"/>
-      <c r="AV63" s="12"/>
-      <c r="AW63" s="13"/>
+      <c r="AR63" s="11">
+        <v>9492167</v>
+      </c>
+      <c r="AS63" s="11">
+        <v>9031</v>
+      </c>
+      <c r="AT63" s="11">
+        <v>53</v>
+      </c>
+      <c r="AU63" s="12">
+        <v>537292.47169811325</v>
+      </c>
+      <c r="AV63" s="12">
+        <v>511.18867924528303</v>
+      </c>
+      <c r="AW63" s="13">
+        <v>0.39188612138528323</v>
+      </c>
       <c r="AX63" s="11"/>
       <c r="AY63" s="11"/>
       <c r="AZ63" s="11"/>
@@ -14586,27 +14583,27 @@
       </c>
       <c r="N64" s="8">
         <f t="shared" si="12"/>
-        <v>8916268.5</v>
+        <v>8982609.4000000004</v>
       </c>
       <c r="O64" s="8">
         <f t="shared" si="13"/>
-        <v>11513</v>
+        <v>10965.4</v>
       </c>
       <c r="P64" s="8">
         <f t="shared" si="14"/>
-        <v>287</v>
+        <v>340</v>
       </c>
       <c r="Q64" s="9">
         <f t="shared" si="15"/>
-        <v>372805.65156794427</v>
+        <v>396291.59117647063</v>
       </c>
       <c r="R64" s="9">
         <f t="shared" si="16"/>
-        <v>481.3797909407665</v>
+        <v>483.76764705882351</v>
       </c>
       <c r="S64" s="10">
         <f t="shared" si="17"/>
-        <v>0.46820482652839285</v>
+        <v>0.45279295452128998</v>
       </c>
       <c r="T64" s="11">
         <v>10280587</v>
@@ -14680,12 +14677,24 @@
       <c r="AQ64" s="13">
         <v>0.40117159001918462</v>
       </c>
-      <c r="AR64" s="11"/>
-      <c r="AS64" s="11"/>
-      <c r="AT64" s="11"/>
-      <c r="AU64" s="12"/>
-      <c r="AV64" s="12"/>
-      <c r="AW64" s="13"/>
+      <c r="AR64" s="11">
+        <v>9247973</v>
+      </c>
+      <c r="AS64" s="11">
+        <v>8775</v>
+      </c>
+      <c r="AT64" s="11">
+        <v>53</v>
+      </c>
+      <c r="AU64" s="12">
+        <v>523470.16981132072</v>
+      </c>
+      <c r="AV64" s="12">
+        <v>496.69811320754718</v>
+      </c>
+      <c r="AW64" s="13">
+        <v>0.39114546649287851</v>
+      </c>
       <c r="AX64" s="11"/>
       <c r="AY64" s="11"/>
       <c r="AZ64" s="11"/>
@@ -14772,27 +14781,27 @@
       </c>
       <c r="N65" s="8">
         <f t="shared" si="12"/>
-        <v>9609848.75</v>
+        <v>9041490.1999999993</v>
       </c>
       <c r="O65" s="8">
         <f t="shared" si="13"/>
-        <v>12357</v>
+        <v>13532.4</v>
       </c>
       <c r="P65" s="8">
         <f t="shared" si="14"/>
-        <v>289</v>
+        <v>341</v>
       </c>
       <c r="Q65" s="9">
         <f t="shared" si="15"/>
-        <v>399024.86159169552</v>
+        <v>397719.51026392961</v>
       </c>
       <c r="R65" s="9">
         <f t="shared" si="16"/>
-        <v>513.09342560553637</v>
+        <v>595.26686217008796</v>
       </c>
       <c r="S65" s="10">
         <f t="shared" si="17"/>
-        <v>0.45597381289197031</v>
+        <v>0.49643445927647445</v>
       </c>
       <c r="T65" s="11">
         <v>9995292</v>
@@ -14866,12 +14875,24 @@
       <c r="AQ65" s="13">
         <v>0.5928777069292217</v>
       </c>
-      <c r="AR65" s="11"/>
-      <c r="AS65" s="11"/>
-      <c r="AT65" s="11"/>
-      <c r="AU65" s="12"/>
-      <c r="AV65" s="12"/>
-      <c r="AW65" s="13"/>
+      <c r="AR65" s="11">
+        <v>6768056</v>
+      </c>
+      <c r="AS65" s="11">
+        <v>18234</v>
+      </c>
+      <c r="AT65" s="11">
+        <v>52</v>
+      </c>
+      <c r="AU65" s="12">
+        <v>390464.76923076919</v>
+      </c>
+      <c r="AV65" s="12">
+        <v>1051.9615384615381</v>
+      </c>
+      <c r="AW65" s="13">
+        <v>0.65827704481449123</v>
+      </c>
       <c r="AX65" s="11"/>
       <c r="AY65" s="11"/>
       <c r="AZ65" s="11"/>
@@ -14958,27 +14979,27 @@
       </c>
       <c r="N66" s="8">
         <f t="shared" si="12"/>
-        <v>9477174</v>
+        <v>8896592.8000000007</v>
       </c>
       <c r="O66" s="8">
         <f t="shared" si="13"/>
-        <v>17021.25</v>
+        <v>15976.4</v>
       </c>
       <c r="P66" s="8">
         <f t="shared" si="14"/>
-        <v>287</v>
+        <v>338</v>
       </c>
       <c r="Q66" s="9">
         <f t="shared" si="15"/>
-        <v>396258.14634146338</v>
+        <v>394819.20710059174</v>
       </c>
       <c r="R66" s="9">
         <f t="shared" si="16"/>
-        <v>711.68989547038336</v>
+        <v>709.01183431952666</v>
       </c>
       <c r="S66" s="10">
         <f t="shared" si="17"/>
-        <v>0.53763871053227397</v>
+        <v>0.53753522313929736</v>
       </c>
       <c r="T66" s="11">
         <v>8918165</v>
@@ -15052,12 +15073,24 @@
       <c r="AQ66" s="13">
         <v>0.51493521176078927</v>
       </c>
-      <c r="AR66" s="11"/>
-      <c r="AS66" s="11"/>
-      <c r="AT66" s="11"/>
-      <c r="AU66" s="12"/>
-      <c r="AV66" s="12"/>
-      <c r="AW66" s="13"/>
+      <c r="AR66" s="11">
+        <v>6574268</v>
+      </c>
+      <c r="AS66" s="11">
+        <v>11797</v>
+      </c>
+      <c r="AT66" s="11">
+        <v>51</v>
+      </c>
+      <c r="AU66" s="12">
+        <v>386721.6470588235</v>
+      </c>
+      <c r="AV66" s="12">
+        <v>693.94117647058829</v>
+      </c>
+      <c r="AW66" s="13">
+        <v>0.53712127356739103</v>
+      </c>
       <c r="AX66" s="11"/>
       <c r="AY66" s="11"/>
       <c r="AZ66" s="11"/>
@@ -15144,27 +15177,27 @@
       </c>
       <c r="N67" s="8">
         <f t="shared" si="12"/>
-        <v>5327302.25</v>
+        <v>4930378</v>
       </c>
       <c r="O67" s="8">
         <f t="shared" si="13"/>
-        <v>12448.5</v>
+        <v>11537.2</v>
       </c>
       <c r="P67" s="8">
         <f t="shared" si="14"/>
-        <v>294</v>
+        <v>345</v>
       </c>
       <c r="Q67" s="9">
         <f t="shared" si="15"/>
-        <v>217440.9081632653</v>
+        <v>214364.26086956519</v>
       </c>
       <c r="R67" s="9">
         <f t="shared" si="16"/>
-        <v>508.10204081632651</v>
+        <v>501.61739130434779</v>
       </c>
       <c r="S67" s="10">
         <f t="shared" si="17"/>
-        <v>0.61146722438661105</v>
+        <v>0.61335626169895208</v>
       </c>
       <c r="T67" s="11">
         <v>5935742</v>
@@ -15238,12 +15271,24 @@
       <c r="AQ67" s="13">
         <v>0.63585220556039124</v>
       </c>
-      <c r="AR67" s="11"/>
-      <c r="AS67" s="11"/>
-      <c r="AT67" s="11"/>
-      <c r="AU67" s="12"/>
-      <c r="AV67" s="12"/>
-      <c r="AW67" s="13"/>
+      <c r="AR67" s="11">
+        <v>3342681</v>
+      </c>
+      <c r="AS67" s="11">
+        <v>7892</v>
+      </c>
+      <c r="AT67" s="11">
+        <v>51</v>
+      </c>
+      <c r="AU67" s="12">
+        <v>196628.29411764699</v>
+      </c>
+      <c r="AV67" s="12">
+        <v>464.23529411764707</v>
+      </c>
+      <c r="AW67" s="13">
+        <v>0.62091241094831573</v>
+      </c>
       <c r="AX67" s="11"/>
       <c r="AY67" s="11"/>
       <c r="AZ67" s="11"/>
@@ -15330,27 +15375,27 @@
       </c>
       <c r="N68" s="8">
         <f t="shared" si="12"/>
-        <v>6537613.25</v>
+        <v>6072847.2000000002</v>
       </c>
       <c r="O68" s="8">
         <f t="shared" si="13"/>
-        <v>17397</v>
+        <v>15708</v>
       </c>
       <c r="P68" s="8">
         <f t="shared" si="14"/>
-        <v>297</v>
+        <v>348</v>
       </c>
       <c r="Q68" s="9">
         <f t="shared" si="15"/>
-        <v>264145.98989898991</v>
+        <v>261760.6551724138</v>
       </c>
       <c r="R68" s="9">
         <f t="shared" si="16"/>
-        <v>702.90909090909099</v>
+        <v>677.06896551724139</v>
       </c>
       <c r="S68" s="10">
         <f t="shared" si="17"/>
-        <v>0.65495461304072045</v>
+        <v>0.64126761574065128</v>
       </c>
       <c r="T68" s="11">
         <v>6055582</v>
@@ -15424,12 +15469,24 @@
       <c r="AQ68" s="13">
         <v>0.64724543874857365</v>
       </c>
-      <c r="AR68" s="11"/>
-      <c r="AS68" s="11"/>
-      <c r="AT68" s="11"/>
-      <c r="AU68" s="12"/>
-      <c r="AV68" s="12"/>
-      <c r="AW68" s="13"/>
+      <c r="AR68" s="11">
+        <v>4213783</v>
+      </c>
+      <c r="AS68" s="11">
+        <v>8952</v>
+      </c>
+      <c r="AT68" s="11">
+        <v>51</v>
+      </c>
+      <c r="AU68" s="12">
+        <v>247869.5882352941</v>
+      </c>
+      <c r="AV68" s="12">
+        <v>526.58823529411768</v>
+      </c>
+      <c r="AW68" s="13">
+        <v>0.58651962654037459</v>
+      </c>
       <c r="AX68" s="11"/>
       <c r="AY68" s="11"/>
       <c r="AZ68" s="11"/>
@@ -15516,27 +15573,27 @@
       </c>
       <c r="N69" s="8">
         <f t="shared" si="12"/>
-        <v>5641553.75</v>
+        <v>5439183</v>
       </c>
       <c r="O69" s="8">
         <f t="shared" si="13"/>
-        <v>14131.75</v>
+        <v>13756.4</v>
       </c>
       <c r="P69" s="8">
         <f t="shared" si="14"/>
-        <v>297</v>
+        <v>349</v>
       </c>
       <c r="Q69" s="9">
         <f t="shared" si="15"/>
-        <v>227941.56565656565</v>
+        <v>233775.77363896847</v>
       </c>
       <c r="R69" s="9">
         <f t="shared" si="16"/>
-        <v>570.97979797979804</v>
+        <v>591.24928366762174</v>
       </c>
       <c r="S69" s="10">
         <f t="shared" si="17"/>
-        <v>0.63341096553604315</v>
+        <v>0.63778893712835372</v>
       </c>
       <c r="T69" s="11">
         <v>4627717</v>
@@ -15610,12 +15667,24 @@
       <c r="AQ69" s="13">
         <v>0.62907611329484114</v>
       </c>
-      <c r="AR69" s="11"/>
-      <c r="AS69" s="11"/>
-      <c r="AT69" s="11"/>
-      <c r="AU69" s="12"/>
-      <c r="AV69" s="12"/>
-      <c r="AW69" s="13"/>
+      <c r="AR69" s="11">
+        <v>4629700</v>
+      </c>
+      <c r="AS69" s="11">
+        <v>12255</v>
+      </c>
+      <c r="AT69" s="11">
+        <v>52</v>
+      </c>
+      <c r="AU69" s="12">
+        <v>267098.07692307688</v>
+      </c>
+      <c r="AV69" s="12">
+        <v>707.01923076923083</v>
+      </c>
+      <c r="AW69" s="13">
+        <v>0.65530082349759566</v>
+      </c>
       <c r="AX69" s="11"/>
       <c r="AY69" s="11"/>
       <c r="AZ69" s="11"/>
@@ -15702,27 +15771,27 @@
       </c>
       <c r="N70" s="8">
         <f t="shared" si="12"/>
-        <v>3083073.25</v>
+        <v>3256837</v>
       </c>
       <c r="O70" s="8">
         <f t="shared" si="13"/>
-        <v>7807.25</v>
+        <v>8350</v>
       </c>
       <c r="P70" s="8">
         <f t="shared" si="14"/>
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="Q70" s="9">
         <f t="shared" si="15"/>
-        <v>231230.49375000002</v>
+        <v>241844.33168316833</v>
       </c>
       <c r="R70" s="9">
         <f t="shared" si="16"/>
-        <v>585.54375000000005</v>
+        <v>620.04950495049502</v>
       </c>
       <c r="S70" s="10">
         <f t="shared" si="17"/>
-        <v>0.64125294189952553</v>
+        <v>0.64396570987672885</v>
       </c>
       <c r="T70" s="11">
         <v>640528</v>
@@ -15796,12 +15865,24 @@
       <c r="AQ70" s="13">
         <v>0.65942029230180643</v>
       </c>
-      <c r="AR70" s="11"/>
-      <c r="AS70" s="11"/>
-      <c r="AT70" s="11"/>
-      <c r="AU70" s="12"/>
-      <c r="AV70" s="12"/>
-      <c r="AW70" s="13"/>
+      <c r="AR70" s="11">
+        <v>3951892</v>
+      </c>
+      <c r="AS70" s="11">
+        <v>10521</v>
+      </c>
+      <c r="AT70" s="11">
+        <v>42</v>
+      </c>
+      <c r="AU70" s="12">
+        <v>282278</v>
+      </c>
+      <c r="AV70" s="12">
+        <v>751.5</v>
+      </c>
+      <c r="AW70" s="13">
+        <v>0.65481678178554181</v>
+      </c>
       <c r="AX70" s="11"/>
       <c r="AY70" s="11"/>
       <c r="AZ70" s="11"/>
@@ -16224,27 +16305,27 @@
       </c>
       <c r="N73" s="8">
         <f t="shared" si="12"/>
-        <v>4729170.25</v>
+        <v>4250952.2</v>
       </c>
       <c r="O73" s="8">
         <f t="shared" si="13"/>
-        <v>7909</v>
+        <v>6948.4</v>
       </c>
       <c r="P73" s="8">
         <f t="shared" si="14"/>
-        <v>281</v>
+        <v>331</v>
       </c>
       <c r="Q73" s="9">
         <f t="shared" si="15"/>
-        <v>201957.44839857653</v>
+        <v>192641.33836858007</v>
       </c>
       <c r="R73" s="9">
         <f t="shared" si="16"/>
-        <v>337.75088967971533</v>
+        <v>314.88217522658613</v>
       </c>
       <c r="S73" s="10">
         <f t="shared" si="17"/>
-        <v>0.51617229483375549</v>
+        <v>0.50419738004520653</v>
       </c>
       <c r="T73" s="11">
         <v>6999813</v>
@@ -16318,12 +16399,24 @@
       <c r="AQ73" s="13">
         <v>0.52584416781677801</v>
       </c>
-      <c r="AR73" s="11"/>
-      <c r="AS73" s="11"/>
-      <c r="AT73" s="11"/>
-      <c r="AU73" s="12"/>
-      <c r="AV73" s="12"/>
-      <c r="AW73" s="13"/>
+      <c r="AR73" s="11">
+        <v>2338080</v>
+      </c>
+      <c r="AS73" s="11">
+        <v>3106</v>
+      </c>
+      <c r="AT73" s="11">
+        <v>50</v>
+      </c>
+      <c r="AU73" s="12">
+        <v>140284.79999999999</v>
+      </c>
+      <c r="AV73" s="12">
+        <v>186.36</v>
+      </c>
+      <c r="AW73" s="13">
+        <v>0.45629772089101051</v>
+      </c>
       <c r="AX73" s="11"/>
       <c r="AY73" s="11"/>
       <c r="AZ73" s="11"/>
@@ -16410,27 +16503,27 @@
       </c>
       <c r="N74" s="8">
         <f t="shared" si="12"/>
-        <v>5513350.5</v>
+        <v>4710087.5999999996</v>
       </c>
       <c r="O74" s="8">
         <f t="shared" si="13"/>
-        <v>9004.75</v>
+        <v>7442</v>
       </c>
       <c r="P74" s="8">
         <f t="shared" si="14"/>
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="Q74" s="9">
         <f t="shared" si="15"/>
-        <v>253487.37931034481</v>
+        <v>239495.97966101693</v>
       </c>
       <c r="R74" s="9">
         <f t="shared" si="16"/>
-        <v>414.0114942528736</v>
+        <v>378.40677966101697</v>
       </c>
       <c r="S74" s="10">
         <f t="shared" si="17"/>
-        <v>0.49795274305409082</v>
+        <v>0.46837159742183471</v>
       </c>
       <c r="T74" s="11">
         <v>6713836</v>
@@ -16504,12 +16597,24 @@
       <c r="AQ74" s="13">
         <v>0.47789143752387048</v>
       </c>
-      <c r="AR74" s="11"/>
-      <c r="AS74" s="11"/>
-      <c r="AT74" s="11"/>
-      <c r="AU74" s="12"/>
-      <c r="AV74" s="12"/>
-      <c r="AW74" s="13"/>
+      <c r="AR74" s="11">
+        <v>1497036</v>
+      </c>
+      <c r="AS74" s="11">
+        <v>1191</v>
+      </c>
+      <c r="AT74" s="11">
+        <v>34</v>
+      </c>
+      <c r="AU74" s="12">
+        <v>132091.4117647059</v>
+      </c>
+      <c r="AV74" s="12">
+        <v>105.08823529411769</v>
+      </c>
+      <c r="AW74" s="13">
+        <v>0.35004701489281043</v>
+      </c>
       <c r="AX74" s="11"/>
       <c r="AY74" s="11"/>
       <c r="AZ74" s="11"/>
@@ -16596,27 +16701,27 @@
       </c>
       <c r="N75" s="8">
         <f t="shared" si="12"/>
-        <v>1116940.335</v>
+        <v>1050422.868</v>
       </c>
       <c r="O75" s="8">
         <f t="shared" si="13"/>
-        <v>165643</v>
+        <v>155164.79999999999</v>
       </c>
       <c r="P75" s="8">
         <f t="shared" si="14"/>
-        <v>301</v>
+        <v>353</v>
       </c>
       <c r="Q75" s="9">
         <f t="shared" si="15"/>
-        <v>44529.182790697669</v>
+        <v>44635.532634560906</v>
       </c>
       <c r="R75" s="9">
         <f t="shared" si="16"/>
-        <v>6603.7076411960134</v>
+        <v>6593.4050991501408</v>
       </c>
       <c r="S75" s="10">
         <f t="shared" si="17"/>
-        <v>4.9171299163713655</v>
+        <v>4.9014767858737391</v>
       </c>
       <c r="T75" s="11">
         <v>1253986.8999999999</v>
@@ -16690,12 +16795,24 @@
       <c r="AQ75" s="13">
         <v>5.1541088179686314</v>
       </c>
-      <c r="AR75" s="11"/>
-      <c r="AS75" s="11"/>
-      <c r="AT75" s="11"/>
-      <c r="AU75" s="12"/>
-      <c r="AV75" s="12"/>
-      <c r="AW75" s="13"/>
+      <c r="AR75" s="11">
+        <v>784353</v>
+      </c>
+      <c r="AS75" s="11">
+        <v>113252</v>
+      </c>
+      <c r="AT75" s="11">
+        <v>52</v>
+      </c>
+      <c r="AU75" s="12">
+        <v>45251.134615384617</v>
+      </c>
+      <c r="AV75" s="12">
+        <v>6533.7692307692314</v>
+      </c>
+      <c r="AW75" s="13">
+        <v>4.8388642638832344</v>
+      </c>
       <c r="AX75" s="11"/>
       <c r="AY75" s="11"/>
       <c r="AZ75" s="11"/>
@@ -16782,27 +16899,27 @@
       </c>
       <c r="N76" s="8">
         <f t="shared" si="12"/>
-        <v>3371564.8</v>
+        <v>3139559.6399999997</v>
       </c>
       <c r="O76" s="8">
         <f t="shared" si="13"/>
-        <v>58459</v>
+        <v>53729</v>
       </c>
       <c r="P76" s="8">
         <f t="shared" si="14"/>
-        <v>296</v>
+        <v>347</v>
       </c>
       <c r="Q76" s="9">
         <f t="shared" si="15"/>
-        <v>136685.05945945944</v>
+        <v>135715.83458213258</v>
       </c>
       <c r="R76" s="9">
         <f t="shared" si="16"/>
-        <v>2369.9594594594591</v>
+        <v>2322.579250720461</v>
       </c>
       <c r="S76" s="10">
         <f t="shared" si="17"/>
-        <v>1.6715884185388679</v>
+        <v>1.6564954715158904</v>
       </c>
       <c r="T76" s="11">
         <v>3600483.2</v>
@@ -16876,12 +16993,24 @@
       <c r="AQ76" s="13">
         <v>1.661478332448175</v>
       </c>
-      <c r="AR76" s="11"/>
-      <c r="AS76" s="11"/>
-      <c r="AT76" s="11"/>
-      <c r="AU76" s="12"/>
-      <c r="AV76" s="12"/>
-      <c r="AW76" s="13"/>
+      <c r="AR76" s="11">
+        <v>2211539</v>
+      </c>
+      <c r="AS76" s="11">
+        <v>34809</v>
+      </c>
+      <c r="AT76" s="11">
+        <v>51</v>
+      </c>
+      <c r="AU76" s="12">
+        <v>130090.5294117647</v>
+      </c>
+      <c r="AV76" s="12">
+        <v>2047.588235294118</v>
+      </c>
+      <c r="AW76" s="13">
+        <v>1.59612368342398</v>
+      </c>
       <c r="AX76" s="11"/>
       <c r="AY76" s="11"/>
       <c r="AZ76" s="11"/>
@@ -16968,27 +17097,27 @@
       </c>
       <c r="N77" s="8">
         <f t="shared" si="12"/>
-        <v>4577840</v>
+        <v>4288535</v>
       </c>
       <c r="O77" s="8">
         <f t="shared" si="13"/>
-        <v>20248.75</v>
+        <v>19207.8</v>
       </c>
       <c r="P77" s="8">
         <f t="shared" si="14"/>
-        <v>299</v>
+        <v>352</v>
       </c>
       <c r="Q77" s="9">
         <f t="shared" si="15"/>
-        <v>183726.02006688961</v>
+        <v>182750.07102272726</v>
       </c>
       <c r="R77" s="9">
         <f t="shared" si="16"/>
-        <v>812.65886287625415</v>
+        <v>818.5142045454545</v>
       </c>
       <c r="S77" s="10">
         <f t="shared" si="17"/>
-        <v>0.84455524678428695</v>
+        <v>0.85182290769886038</v>
       </c>
       <c r="T77" s="11">
         <v>4959341</v>
@@ -17062,12 +17191,24 @@
       <c r="AQ77" s="13">
         <v>0.84496855797024173</v>
       </c>
-      <c r="AR77" s="11"/>
-      <c r="AS77" s="11"/>
-      <c r="AT77" s="11"/>
-      <c r="AU77" s="12"/>
-      <c r="AV77" s="12"/>
-      <c r="AW77" s="13"/>
+      <c r="AR77" s="11">
+        <v>3131315</v>
+      </c>
+      <c r="AS77" s="11">
+        <v>15044</v>
+      </c>
+      <c r="AT77" s="11">
+        <v>53</v>
+      </c>
+      <c r="AU77" s="12">
+        <v>177244.24528301891</v>
+      </c>
+      <c r="AV77" s="12">
+        <v>851.54716981132083</v>
+      </c>
+      <c r="AW77" s="13">
+        <v>0.88089355135715419</v>
+      </c>
       <c r="AX77" s="11"/>
       <c r="AY77" s="11"/>
       <c r="AZ77" s="11"/>
@@ -17154,27 +17295,27 @@
       </c>
       <c r="N78" s="8">
         <f t="shared" si="12"/>
-        <v>5435702.5</v>
+        <v>5061373.4000000004</v>
       </c>
       <c r="O78" s="8">
         <f t="shared" si="13"/>
-        <v>35324.25</v>
+        <v>34135.199999999997</v>
       </c>
       <c r="P78" s="8">
         <f t="shared" si="14"/>
-        <v>304</v>
+        <v>357</v>
       </c>
       <c r="Q78" s="9">
         <f t="shared" si="15"/>
-        <v>214567.20394736843</v>
+        <v>212662.74789915964</v>
       </c>
       <c r="R78" s="9">
         <f t="shared" si="16"/>
-        <v>1394.3782894736842</v>
+        <v>1434.2521008403362</v>
       </c>
       <c r="S78" s="10">
         <f t="shared" si="17"/>
-        <v>1.0209211694107219</v>
+        <v>1.0482940431267838</v>
       </c>
       <c r="T78" s="11">
         <v>5415922</v>
@@ -17248,12 +17389,24 @@
       <c r="AQ78" s="13">
         <v>1.0551932274946521</v>
       </c>
-      <c r="AR78" s="11"/>
-      <c r="AS78" s="11"/>
-      <c r="AT78" s="11"/>
-      <c r="AU78" s="12"/>
-      <c r="AV78" s="12"/>
-      <c r="AW78" s="13"/>
+      <c r="AR78" s="11">
+        <v>3564057</v>
+      </c>
+      <c r="AS78" s="11">
+        <v>29379</v>
+      </c>
+      <c r="AT78" s="11">
+        <v>53</v>
+      </c>
+      <c r="AU78" s="12">
+        <v>201739.0754716981</v>
+      </c>
+      <c r="AV78" s="12">
+        <v>1662.9622641509429</v>
+      </c>
+      <c r="AW78" s="13">
+        <v>1.157785537991032</v>
+      </c>
       <c r="AX78" s="11"/>
       <c r="AY78" s="11"/>
       <c r="AZ78" s="11"/>
@@ -17340,27 +17493,27 @@
       </c>
       <c r="N79" s="8">
         <f t="shared" ref="N79:N111" si="18">IFERROR(AVERAGE(T79,Z79,AF79,AL79,AR79,AX79,BD79,BJ79,BP79,BV79,CB79,CH79)," ")</f>
-        <v>5240174.5</v>
+        <v>4877409.5999999996</v>
       </c>
       <c r="O79" s="8">
         <f t="shared" ref="O79:O111" si="19">IFERROR(AVERAGE(U79,AA79,AG79,AM79,AS79,AY79,BE79,BK79,BQ79,BW79,CC79,CI79)," ")</f>
-        <v>31753.25</v>
+        <v>30302.400000000001</v>
       </c>
       <c r="P79" s="8">
         <f t="shared" ref="P79:P111" si="20">IFERROR(SUM(V79,AB79,AH79,AN79,AT79,AZ79,BF79,BL79,BR79,BX79,CD79,CJ79)," ")</f>
-        <v>300</v>
+        <v>353</v>
       </c>
       <c r="Q79" s="9">
         <f t="shared" ref="Q79:Q109" si="21">IFERROR(SUM(T79,Z79,AF79,AL79,AR79,AX79,BD79,BJ79,BP79,BV79,CB79,CH79)/P79*3," ")</f>
-        <v>209606.97999999998</v>
+        <v>207255.3654390935</v>
       </c>
       <c r="R79" s="9">
         <f t="shared" ref="R79:R111" si="22">IFERROR(SUM(U79,AA79,AG79,AM79,AS79,AY79,BE79,BK79,BQ79,BW79,CC79,CI79)/P79*3," ")</f>
-        <v>1270.1300000000001</v>
+        <v>1287.6373937677054</v>
       </c>
       <c r="S79" s="10">
         <f t="shared" ref="S79:S111" si="23">IFERROR(AVERAGE(Y79,AE79,AK79,AQ79,AW79,BC79,BI79,BO79,BU79,CA79,CG79,CM79)," ")</f>
-        <v>0.98717849528847634</v>
+        <v>1.004989508312601</v>
       </c>
       <c r="T79" s="11">
         <v>5601093</v>
@@ -17434,12 +17587,24 @@
       <c r="AQ79" s="13">
         <v>1.023785642822034</v>
       </c>
-      <c r="AR79" s="11"/>
-      <c r="AS79" s="11"/>
-      <c r="AT79" s="11"/>
-      <c r="AU79" s="12"/>
-      <c r="AV79" s="12"/>
-      <c r="AW79" s="13"/>
+      <c r="AR79" s="11">
+        <v>3426350</v>
+      </c>
+      <c r="AS79" s="11">
+        <v>24499</v>
+      </c>
+      <c r="AT79" s="11">
+        <v>53</v>
+      </c>
+      <c r="AU79" s="12">
+        <v>193944.33962264151</v>
+      </c>
+      <c r="AV79" s="12">
+        <v>1386.7358490566039</v>
+      </c>
+      <c r="AW79" s="13">
+        <v>1.0762335604091</v>
+      </c>
       <c r="AX79" s="11"/>
       <c r="AY79" s="11"/>
       <c r="AZ79" s="11"/>
@@ -17526,27 +17691,27 @@
       </c>
       <c r="N80" s="8">
         <f t="shared" si="18"/>
-        <v>5336503</v>
+        <v>4921562.4000000004</v>
       </c>
       <c r="O80" s="8">
         <f t="shared" si="19"/>
-        <v>171887</v>
+        <v>158321.60000000001</v>
       </c>
       <c r="P80" s="8">
         <f t="shared" si="20"/>
-        <v>293</v>
+        <v>335</v>
       </c>
       <c r="Q80" s="9">
         <f t="shared" si="21"/>
-        <v>218559.84982935153</v>
+        <v>220368.46567164181</v>
       </c>
       <c r="R80" s="9">
         <f t="shared" si="22"/>
-        <v>7039.7406143344715</v>
+        <v>7089.0268656716416</v>
       </c>
       <c r="S80" s="10">
         <f t="shared" si="23"/>
-        <v>2.2843456458251561</v>
+        <v>2.2821275074797951</v>
       </c>
       <c r="T80" s="11">
         <v>5213937</v>
@@ -17620,12 +17785,24 @@
       <c r="AQ80" s="13">
         <v>2.1819274733639622</v>
       </c>
-      <c r="AR80" s="11"/>
-      <c r="AS80" s="11"/>
-      <c r="AT80" s="11"/>
-      <c r="AU80" s="12"/>
-      <c r="AV80" s="12"/>
-      <c r="AW80" s="13"/>
+      <c r="AR80" s="11">
+        <v>3261800</v>
+      </c>
+      <c r="AS80" s="11">
+        <v>104060</v>
+      </c>
+      <c r="AT80" s="11">
+        <v>42</v>
+      </c>
+      <c r="AU80" s="12">
+        <v>232985.71428571429</v>
+      </c>
+      <c r="AV80" s="12">
+        <v>7432.8571428571431</v>
+      </c>
+      <c r="AW80" s="13">
+        <v>2.273254954098352</v>
+      </c>
       <c r="AX80" s="11"/>
       <c r="AY80" s="11"/>
       <c r="AZ80" s="11"/>
@@ -17712,27 +17889,27 @@
       </c>
       <c r="N81" s="8">
         <f t="shared" si="18"/>
-        <v>2781091.5</v>
+        <v>2641745.4</v>
       </c>
       <c r="O81" s="8">
         <f t="shared" si="19"/>
-        <v>59147.5</v>
+        <v>55700.4</v>
       </c>
       <c r="P81" s="8">
         <f t="shared" si="20"/>
-        <v>267</v>
+        <v>319</v>
       </c>
       <c r="Q81" s="9">
         <f t="shared" si="21"/>
-        <v>124992.8764044944</v>
+        <v>124220.00313479625</v>
       </c>
       <c r="R81" s="9">
         <f t="shared" si="22"/>
-        <v>2658.3146067415728</v>
+        <v>2619.1410658307209</v>
       </c>
       <c r="S81" s="10">
         <f t="shared" si="23"/>
-        <v>1.8764295479647684</v>
+        <v>1.8619062747611461</v>
       </c>
       <c r="T81" s="11">
         <v>3606826</v>
@@ -17806,12 +17983,24 @@
       <c r="AQ81" s="13">
         <v>1.85569720590816</v>
       </c>
-      <c r="AR81" s="11"/>
-      <c r="AS81" s="11"/>
-      <c r="AT81" s="11"/>
-      <c r="AU81" s="12"/>
-      <c r="AV81" s="12"/>
-      <c r="AW81" s="13"/>
+      <c r="AR81" s="11">
+        <v>2084361</v>
+      </c>
+      <c r="AS81" s="11">
+        <v>41912</v>
+      </c>
+      <c r="AT81" s="11">
+        <v>52</v>
+      </c>
+      <c r="AU81" s="12">
+        <v>120251.5961538462</v>
+      </c>
+      <c r="AV81" s="12">
+        <v>2418</v>
+      </c>
+      <c r="AW81" s="13">
+        <v>1.8038131819466581</v>
+      </c>
       <c r="AX81" s="11"/>
       <c r="AY81" s="11"/>
       <c r="AZ81" s="11"/>
@@ -17898,27 +18087,27 @@
       </c>
       <c r="N82" s="8">
         <f t="shared" si="18"/>
-        <v>3099956.75</v>
+        <v>2875665</v>
       </c>
       <c r="O82" s="8">
         <f t="shared" si="19"/>
-        <v>56688</v>
+        <v>52701.8</v>
       </c>
       <c r="P82" s="8">
         <f t="shared" si="20"/>
-        <v>276</v>
+        <v>327</v>
       </c>
       <c r="Q82" s="9">
         <f t="shared" si="21"/>
-        <v>134780.72826086957</v>
+        <v>131911.23853211009</v>
       </c>
       <c r="R82" s="9">
         <f t="shared" si="22"/>
-        <v>2464.695652173913</v>
+        <v>2417.5137614678897</v>
       </c>
       <c r="S82" s="10">
         <f t="shared" si="23"/>
-        <v>1.7463113489407327</v>
+        <v>1.7441308954061987</v>
       </c>
       <c r="T82" s="11">
         <v>4247045</v>
@@ -17992,12 +18181,24 @@
       <c r="AQ82" s="13">
         <v>1.67811182304474</v>
       </c>
-      <c r="AR82" s="11"/>
-      <c r="AS82" s="11"/>
-      <c r="AT82" s="11"/>
-      <c r="AU82" s="12"/>
-      <c r="AV82" s="12"/>
-      <c r="AW82" s="13"/>
+      <c r="AR82" s="11">
+        <v>1978498</v>
+      </c>
+      <c r="AS82" s="11">
+        <v>36757</v>
+      </c>
+      <c r="AT82" s="11">
+        <v>51</v>
+      </c>
+      <c r="AU82" s="12">
+        <v>116382.23529411769</v>
+      </c>
+      <c r="AV82" s="12">
+        <v>2162.1764705882351</v>
+      </c>
+      <c r="AW82" s="13">
+        <v>1.735409081268064</v>
+      </c>
       <c r="AX82" s="11"/>
       <c r="AY82" s="11"/>
       <c r="AZ82" s="11"/>
@@ -18084,27 +18285,27 @@
       </c>
       <c r="N83" s="8">
         <f t="shared" si="18"/>
-        <v>2385176.375</v>
+        <v>2278448.1</v>
       </c>
       <c r="O83" s="8">
         <f t="shared" si="19"/>
-        <v>68820.25</v>
+        <v>65066.400000000001</v>
       </c>
       <c r="P83" s="8">
         <f t="shared" si="20"/>
-        <v>269</v>
+        <v>321</v>
       </c>
       <c r="Q83" s="9">
         <f t="shared" si="21"/>
-        <v>106401.92007434944</v>
+        <v>106469.53738317758</v>
       </c>
       <c r="R83" s="9">
         <f t="shared" si="22"/>
-        <v>3070.0483271375465</v>
+        <v>3040.4859813084113</v>
       </c>
       <c r="S83" s="10">
         <f t="shared" si="23"/>
-        <v>2.1640151650321378</v>
+        <v>2.1497025405264849</v>
       </c>
       <c r="T83" s="11">
         <v>3362634.5</v>
@@ -18178,12 +18379,24 @@
       <c r="AQ83" s="13">
         <v>2.265013355436523</v>
       </c>
-      <c r="AR83" s="11"/>
-      <c r="AS83" s="11"/>
-      <c r="AT83" s="11"/>
-      <c r="AU83" s="12"/>
-      <c r="AV83" s="12"/>
-      <c r="AW83" s="13"/>
+      <c r="AR83" s="11">
+        <v>1851535</v>
+      </c>
+      <c r="AS83" s="11">
+        <v>50051</v>
+      </c>
+      <c r="AT83" s="11">
+        <v>52</v>
+      </c>
+      <c r="AU83" s="12">
+        <v>106819.32692307689</v>
+      </c>
+      <c r="AV83" s="12">
+        <v>2887.5576923076919</v>
+      </c>
+      <c r="AW83" s="13">
+        <v>2.092452042503874</v>
+      </c>
       <c r="AX83" s="11"/>
       <c r="AY83" s="11"/>
       <c r="AZ83" s="11"/>
@@ -18270,27 +18483,27 @@
       </c>
       <c r="N84" s="8">
         <f t="shared" si="18"/>
-        <v>2250012.625</v>
+        <v>2154352.2999999998</v>
       </c>
       <c r="O84" s="8">
         <f t="shared" si="19"/>
-        <v>157081.75</v>
+        <v>151170.4</v>
       </c>
       <c r="P84" s="8">
         <f t="shared" si="20"/>
-        <v>299</v>
+        <v>352</v>
       </c>
       <c r="Q84" s="9">
         <f t="shared" si="21"/>
-        <v>90301.510033444807</v>
+        <v>91804.785511363632</v>
       </c>
       <c r="R84" s="9">
         <f t="shared" si="22"/>
-        <v>6304.2842809364538</v>
+        <v>6441.920454545454</v>
       </c>
       <c r="S84" s="10">
         <f t="shared" si="23"/>
-        <v>3.3632737249243032</v>
+        <v>3.3737691089413948</v>
       </c>
       <c r="T84" s="11">
         <v>2176614</v>
@@ -18364,12 +18577,24 @@
       <c r="AQ84" s="13">
         <v>3.2099311603494498</v>
       </c>
-      <c r="AR84" s="11"/>
-      <c r="AS84" s="11"/>
-      <c r="AT84" s="11"/>
-      <c r="AU84" s="12"/>
-      <c r="AV84" s="12"/>
-      <c r="AW84" s="13"/>
+      <c r="AR84" s="11">
+        <v>1771711</v>
+      </c>
+      <c r="AS84" s="11">
+        <v>127525</v>
+      </c>
+      <c r="AT84" s="11">
+        <v>53</v>
+      </c>
+      <c r="AU84" s="12">
+        <v>100285.52830188681</v>
+      </c>
+      <c r="AV84" s="12">
+        <v>7218.3962264150941</v>
+      </c>
+      <c r="AW84" s="13">
+        <v>3.4157506450097612</v>
+      </c>
       <c r="AX84" s="11"/>
       <c r="AY84" s="11"/>
       <c r="AZ84" s="11"/>
@@ -18456,27 +18681,27 @@
       </c>
       <c r="N85" s="8">
         <f t="shared" si="18"/>
-        <v>1428403.25</v>
+        <v>1280434.6000000001</v>
       </c>
       <c r="O85" s="8">
         <f t="shared" si="19"/>
-        <v>131467</v>
+        <v>123983.6</v>
       </c>
       <c r="P85" s="8">
         <f t="shared" si="20"/>
-        <v>299</v>
+        <v>349</v>
       </c>
       <c r="Q85" s="9">
         <f t="shared" si="21"/>
-        <v>57327.220735785959</v>
+        <v>55033.005730659017</v>
       </c>
       <c r="R85" s="9">
         <f t="shared" si="22"/>
-        <v>5276.2675585284287</v>
+        <v>5328.8080229226362</v>
       </c>
       <c r="S85" s="10">
         <f t="shared" si="23"/>
-        <v>3.8811075404523243</v>
+        <v>4.0460728617047872</v>
       </c>
       <c r="T85" s="11">
         <v>1663594</v>
@@ -18550,12 +18775,24 @@
       <c r="AQ85" s="13">
         <v>3.9253263829149851</v>
       </c>
-      <c r="AR85" s="11"/>
-      <c r="AS85" s="11"/>
-      <c r="AT85" s="11"/>
-      <c r="AU85" s="12"/>
-      <c r="AV85" s="12"/>
-      <c r="AW85" s="13"/>
+      <c r="AR85" s="11">
+        <v>688560</v>
+      </c>
+      <c r="AS85" s="11">
+        <v>94050</v>
+      </c>
+      <c r="AT85" s="11">
+        <v>50</v>
+      </c>
+      <c r="AU85" s="12">
+        <v>41313.600000000013</v>
+      </c>
+      <c r="AV85" s="12">
+        <v>5643</v>
+      </c>
+      <c r="AW85" s="13">
+        <v>4.7059341467146378</v>
+      </c>
       <c r="AX85" s="11"/>
       <c r="AY85" s="11"/>
       <c r="AZ85" s="11"/>
@@ -18642,27 +18879,27 @@
       </c>
       <c r="N86" s="8">
         <f t="shared" si="18"/>
-        <v>3256233.75</v>
+        <v>3025197.8</v>
       </c>
       <c r="O86" s="8">
         <f t="shared" si="19"/>
-        <v>80977.5</v>
+        <v>73806.399999999994</v>
       </c>
       <c r="P86" s="8">
         <f t="shared" si="20"/>
-        <v>301</v>
+        <v>352</v>
       </c>
       <c r="Q86" s="9">
         <f t="shared" si="21"/>
-        <v>129816.62790697673</v>
+        <v>128914.67897727274</v>
       </c>
       <c r="R86" s="9">
         <f t="shared" si="22"/>
-        <v>3228.3388704318936</v>
+        <v>3145.159090909091</v>
       </c>
       <c r="S86" s="10">
         <f t="shared" si="23"/>
-        <v>2.0072712891781777</v>
+        <v>1.978866741165163</v>
       </c>
       <c r="T86" s="11">
         <v>3712214</v>
@@ -18736,12 +18973,24 @@
       <c r="AQ86" s="13">
         <v>2.058833276916884</v>
       </c>
-      <c r="AR86" s="11"/>
-      <c r="AS86" s="11"/>
-      <c r="AT86" s="11"/>
-      <c r="AU86" s="12"/>
-      <c r="AV86" s="12"/>
-      <c r="AW86" s="13"/>
+      <c r="AR86" s="11">
+        <v>2101054</v>
+      </c>
+      <c r="AS86" s="11">
+        <v>45122</v>
+      </c>
+      <c r="AT86" s="11">
+        <v>51</v>
+      </c>
+      <c r="AU86" s="12">
+        <v>123591.4117647059</v>
+      </c>
+      <c r="AV86" s="12">
+        <v>2654.2352941176468</v>
+      </c>
+      <c r="AW86" s="13">
+        <v>1.8652485491131039</v>
+      </c>
       <c r="AX86" s="11"/>
       <c r="AY86" s="11"/>
       <c r="AZ86" s="11"/>
@@ -18828,27 +19077,27 @@
       </c>
       <c r="N87" s="8">
         <f t="shared" si="18"/>
-        <v>3018737</v>
+        <v>2877775.6</v>
       </c>
       <c r="O87" s="8">
         <f t="shared" si="19"/>
-        <v>73682.75</v>
+        <v>69890.399999999994</v>
       </c>
       <c r="P87" s="8">
         <f t="shared" si="20"/>
-        <v>302</v>
+        <v>355</v>
       </c>
       <c r="Q87" s="9">
         <f t="shared" si="21"/>
-        <v>119949.81456953642</v>
+        <v>121596.15211267606</v>
       </c>
       <c r="R87" s="9">
         <f t="shared" si="22"/>
-        <v>2927.7913907284765</v>
+        <v>2953.1154929577465</v>
       </c>
       <c r="S87" s="10">
         <f t="shared" si="23"/>
-        <v>1.9886962032632618</v>
+        <v>1.9822645927281435</v>
       </c>
       <c r="T87" s="11">
         <v>2997988</v>
@@ -18922,12 +19171,24 @@
       <c r="AQ87" s="13">
         <v>2.0634827995565921</v>
       </c>
-      <c r="AR87" s="11"/>
-      <c r="AS87" s="11"/>
-      <c r="AT87" s="11"/>
-      <c r="AU87" s="12"/>
-      <c r="AV87" s="12"/>
-      <c r="AW87" s="13"/>
+      <c r="AR87" s="11">
+        <v>2313930</v>
+      </c>
+      <c r="AS87" s="11">
+        <v>54721</v>
+      </c>
+      <c r="AT87" s="11">
+        <v>53</v>
+      </c>
+      <c r="AU87" s="12">
+        <v>130977.1698113208</v>
+      </c>
+      <c r="AV87" s="12">
+        <v>3097.415094339623</v>
+      </c>
+      <c r="AW87" s="13">
+        <v>1.9565381505876711</v>
+      </c>
       <c r="AX87" s="11"/>
       <c r="AY87" s="11"/>
       <c r="AZ87" s="11"/>
@@ -19014,27 +19275,27 @@
       </c>
       <c r="N88" s="8">
         <f t="shared" si="18"/>
-        <v>2615663.75</v>
+        <v>2522817.4</v>
       </c>
       <c r="O88" s="8">
         <f t="shared" si="19"/>
-        <v>66795</v>
+        <v>64390.8</v>
       </c>
       <c r="P88" s="8">
         <f t="shared" si="20"/>
-        <v>301</v>
+        <v>354</v>
       </c>
       <c r="Q88" s="9">
         <f t="shared" si="21"/>
-        <v>104278.95348837209</v>
+        <v>106899.04237288135</v>
       </c>
       <c r="R88" s="9">
         <f t="shared" si="22"/>
-        <v>2662.9235880398669</v>
+        <v>2728.4237288135596</v>
       </c>
       <c r="S88" s="10">
         <f t="shared" si="23"/>
-        <v>2.0525302479216951</v>
+        <v>2.0481246253453946</v>
       </c>
       <c r="T88" s="11">
         <v>2265706</v>
@@ -19108,12 +19369,24 @@
       <c r="AQ88" s="13">
         <v>2.0226398230645519</v>
       </c>
-      <c r="AR88" s="11"/>
-      <c r="AS88" s="11"/>
-      <c r="AT88" s="11"/>
-      <c r="AU88" s="12"/>
-      <c r="AV88" s="12"/>
-      <c r="AW88" s="13"/>
+      <c r="AR88" s="11">
+        <v>2151432</v>
+      </c>
+      <c r="AS88" s="11">
+        <v>54774</v>
+      </c>
+      <c r="AT88" s="11">
+        <v>53</v>
+      </c>
+      <c r="AU88" s="12">
+        <v>121779.1698113208</v>
+      </c>
+      <c r="AV88" s="12">
+        <v>3100.415094339623</v>
+      </c>
+      <c r="AW88" s="13">
+        <v>2.0305021350401931</v>
+      </c>
       <c r="AX88" s="11"/>
       <c r="AY88" s="11"/>
       <c r="AZ88" s="11"/>
@@ -19200,27 +19473,27 @@
       </c>
       <c r="N89" s="8">
         <f t="shared" si="18"/>
-        <v>3133296.16</v>
+        <v>2940099.3280000002</v>
       </c>
       <c r="O89" s="8">
         <f t="shared" si="19"/>
-        <v>28902</v>
+        <v>26358.799999999999</v>
       </c>
       <c r="P89" s="8">
         <f t="shared" si="20"/>
-        <v>299</v>
+        <v>350</v>
       </c>
       <c r="Q89" s="9">
         <f t="shared" si="21"/>
-        <v>125751.01645484951</v>
+        <v>126004.25691428572</v>
       </c>
       <c r="R89" s="9">
         <f t="shared" si="22"/>
-        <v>1159.9464882943143</v>
+        <v>1129.6628571428571</v>
       </c>
       <c r="S89" s="10">
         <f t="shared" si="23"/>
-        <v>1.2225882044822469</v>
+        <v>1.1979375226438498</v>
       </c>
       <c r="T89" s="11">
         <v>3721474.08</v>
@@ -19294,12 +19567,24 @@
       <c r="AQ89" s="13">
         <v>1.2113894326934389</v>
       </c>
-      <c r="AR89" s="11"/>
-      <c r="AS89" s="11"/>
-      <c r="AT89" s="11"/>
-      <c r="AU89" s="12"/>
-      <c r="AV89" s="12"/>
-      <c r="AW89" s="13"/>
+      <c r="AR89" s="11">
+        <v>2167312</v>
+      </c>
+      <c r="AS89" s="11">
+        <v>16186</v>
+      </c>
+      <c r="AT89" s="11">
+        <v>51</v>
+      </c>
+      <c r="AU89" s="12">
+        <v>127488.9411764706</v>
+      </c>
+      <c r="AV89" s="12">
+        <v>952.11764705882354</v>
+      </c>
+      <c r="AW89" s="13">
+        <v>1.099334795290261</v>
+      </c>
       <c r="AX89" s="11"/>
       <c r="AY89" s="11"/>
       <c r="AZ89" s="11"/>
@@ -19386,27 +19671,27 @@
       </c>
       <c r="N90" s="8">
         <f t="shared" si="18"/>
-        <v>5186384.25</v>
+        <v>4750034.2</v>
       </c>
       <c r="O90" s="8">
         <f t="shared" si="19"/>
-        <v>60045.25</v>
+        <v>55514.2</v>
       </c>
       <c r="P90" s="8">
         <f t="shared" si="20"/>
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="Q90" s="9">
         <f t="shared" si="21"/>
-        <v>206081.49337748345</v>
+        <v>201272.63559322036</v>
       </c>
       <c r="R90" s="9">
         <f t="shared" si="22"/>
-        <v>2385.9039735099336</v>
+        <v>2352.2966101694915</v>
       </c>
       <c r="S90" s="10">
         <f t="shared" si="23"/>
-        <v>1.3758827208404918</v>
+        <v>1.3847751220137852</v>
       </c>
       <c r="T90" s="11">
         <v>4835277</v>
@@ -19480,12 +19765,24 @@
       <c r="AQ90" s="13">
         <v>1.3989784998484389</v>
       </c>
-      <c r="AR90" s="11"/>
-      <c r="AS90" s="11"/>
-      <c r="AT90" s="11"/>
-      <c r="AU90" s="12"/>
-      <c r="AV90" s="12"/>
-      <c r="AW90" s="13"/>
+      <c r="AR90" s="11">
+        <v>3004634</v>
+      </c>
+      <c r="AS90" s="11">
+        <v>37390</v>
+      </c>
+      <c r="AT90" s="11">
+        <v>52</v>
+      </c>
+      <c r="AU90" s="12">
+        <v>173344.26923076919</v>
+      </c>
+      <c r="AV90" s="12">
+        <v>2157.1153846153852</v>
+      </c>
+      <c r="AW90" s="13">
+        <v>1.4203447267069591</v>
+      </c>
       <c r="AX90" s="11"/>
       <c r="AY90" s="11"/>
       <c r="AZ90" s="11"/>
@@ -19572,27 +19869,27 @@
       </c>
       <c r="N91" s="8">
         <f t="shared" si="18"/>
-        <v>6612854.0999999996</v>
+        <v>6129660.2799999993</v>
       </c>
       <c r="O91" s="8">
         <f t="shared" si="19"/>
-        <v>53203.5</v>
+        <v>49250.8</v>
       </c>
       <c r="P91" s="8">
         <f t="shared" si="20"/>
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="Q91" s="9">
         <f t="shared" si="21"/>
-        <v>268997.45491525426</v>
+        <v>270426.1888235294</v>
       </c>
       <c r="R91" s="9">
         <f t="shared" si="22"/>
-        <v>2164.2101694915254</v>
+        <v>2172.8294117647056</v>
       </c>
       <c r="S91" s="10">
         <f t="shared" si="23"/>
-        <v>1.1437698011505282</v>
+        <v>1.1427079086995928</v>
       </c>
       <c r="T91" s="11">
         <v>7274414.3999999994</v>
@@ -19666,12 +19963,24 @@
       <c r="AQ91" s="13">
         <v>1.1176470588531979</v>
       </c>
-      <c r="AR91" s="11"/>
-      <c r="AS91" s="11"/>
-      <c r="AT91" s="11"/>
-      <c r="AU91" s="12"/>
-      <c r="AV91" s="12"/>
-      <c r="AW91" s="13"/>
+      <c r="AR91" s="11">
+        <v>4196885</v>
+      </c>
+      <c r="AS91" s="11">
+        <v>33440</v>
+      </c>
+      <c r="AT91" s="11">
+        <v>45</v>
+      </c>
+      <c r="AU91" s="12">
+        <v>279792.33333333331</v>
+      </c>
+      <c r="AV91" s="12">
+        <v>2229.333333333333</v>
+      </c>
+      <c r="AW91" s="13">
+        <v>1.138460338895851</v>
+      </c>
       <c r="AX91" s="11"/>
       <c r="AY91" s="11"/>
       <c r="AZ91" s="11"/>
@@ -19758,27 +20067,27 @@
       </c>
       <c r="N92" s="8">
         <f t="shared" si="18"/>
-        <v>5745171</v>
+        <v>5484248.7999999998</v>
       </c>
       <c r="O92" s="8">
         <f t="shared" si="19"/>
-        <v>33906.25</v>
+        <v>32080</v>
       </c>
       <c r="P92" s="8">
         <f t="shared" si="20"/>
-        <v>296</v>
+        <v>348</v>
       </c>
       <c r="Q92" s="9">
         <f t="shared" si="21"/>
-        <v>232912.33783783784</v>
+        <v>236390.03448275864</v>
       </c>
       <c r="R92" s="9">
         <f t="shared" si="22"/>
-        <v>1374.5777027027027</v>
+        <v>1382.7586206896551</v>
       </c>
       <c r="S92" s="10">
         <f t="shared" si="23"/>
-        <v>0.97732704710884888</v>
+        <v>0.97179521362270971</v>
       </c>
       <c r="T92" s="11">
         <v>5879996</v>
@@ -19852,12 +20161,24 @@
       <c r="AQ92" s="13">
         <v>0.94194832367564074</v>
       </c>
-      <c r="AR92" s="11"/>
-      <c r="AS92" s="11"/>
-      <c r="AT92" s="11"/>
-      <c r="AU92" s="12"/>
-      <c r="AV92" s="12"/>
-      <c r="AW92" s="13"/>
+      <c r="AR92" s="11">
+        <v>4440560</v>
+      </c>
+      <c r="AS92" s="11">
+        <v>24775</v>
+      </c>
+      <c r="AT92" s="11">
+        <v>52</v>
+      </c>
+      <c r="AU92" s="12">
+        <v>256186.15384615379</v>
+      </c>
+      <c r="AV92" s="12">
+        <v>1429.3269230769231</v>
+      </c>
+      <c r="AW92" s="13">
+        <v>0.94966787967815314</v>
+      </c>
       <c r="AX92" s="11"/>
       <c r="AY92" s="11"/>
       <c r="AZ92" s="11"/>
@@ -19944,27 +20265,27 @@
       </c>
       <c r="N93" s="8">
         <f t="shared" si="18"/>
-        <v>3308968.1799999997</v>
+        <v>3226013.3439999996</v>
       </c>
       <c r="O93" s="8">
         <f t="shared" si="19"/>
-        <v>17270.25</v>
+        <v>16822.599999999999</v>
       </c>
       <c r="P93" s="8">
         <f t="shared" si="20"/>
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="Q93" s="9">
         <f t="shared" si="21"/>
-        <v>136922.82124137931</v>
+        <v>141906.7453372434</v>
       </c>
       <c r="R93" s="9">
         <f t="shared" si="22"/>
-        <v>714.63103448275865</v>
+        <v>739.99706744868035</v>
       </c>
       <c r="S93" s="10">
         <f t="shared" si="23"/>
-        <v>0.90324665083148015</v>
+        <v>0.90610091026862472</v>
       </c>
       <c r="T93" s="11">
         <v>4307185.76</v>
@@ -20038,12 +20359,24 @@
       <c r="AQ93" s="13">
         <v>0.78581730566733698</v>
       </c>
-      <c r="AR93" s="11"/>
-      <c r="AS93" s="11"/>
-      <c r="AT93" s="11"/>
-      <c r="AU93" s="12"/>
-      <c r="AV93" s="12"/>
-      <c r="AW93" s="13"/>
+      <c r="AR93" s="11">
+        <v>2894194</v>
+      </c>
+      <c r="AS93" s="11">
+        <v>15032</v>
+      </c>
+      <c r="AT93" s="11">
+        <v>51</v>
+      </c>
+      <c r="AU93" s="12">
+        <v>170246.70588235301</v>
+      </c>
+      <c r="AV93" s="12">
+        <v>884.23529411764707</v>
+      </c>
+      <c r="AW93" s="13">
+        <v>0.91751794801720277</v>
+      </c>
       <c r="AX93" s="11"/>
       <c r="AY93" s="11"/>
       <c r="AZ93" s="11"/>
@@ -20130,27 +20463,27 @@
       </c>
       <c r="N94" s="8">
         <f t="shared" si="18"/>
-        <v>4150243.44</v>
+        <v>3790428.5519999997</v>
       </c>
       <c r="O94" s="8">
         <f t="shared" si="19"/>
-        <v>13322.5</v>
+        <v>12543.4</v>
       </c>
       <c r="P94" s="8">
         <f t="shared" si="20"/>
-        <v>281</v>
+        <v>326</v>
       </c>
       <c r="Q94" s="9">
         <f t="shared" si="21"/>
-        <v>177234.5953024911</v>
+        <v>174406.2217177914</v>
       </c>
       <c r="R94" s="9">
         <f t="shared" si="22"/>
-        <v>568.93238434163698</v>
+        <v>577.15030674846616</v>
       </c>
       <c r="S94" s="10">
         <f t="shared" si="23"/>
-        <v>0.71088823645734034</v>
+        <v>0.73030874816492397</v>
       </c>
       <c r="T94" s="11">
         <v>5182499.76</v>
@@ -20224,12 +20557,24 @@
       <c r="AQ94" s="13">
         <v>0.77498479645577334</v>
       </c>
-      <c r="AR94" s="11"/>
-      <c r="AS94" s="11"/>
-      <c r="AT94" s="11"/>
-      <c r="AU94" s="12"/>
-      <c r="AV94" s="12"/>
-      <c r="AW94" s="13"/>
+      <c r="AR94" s="11">
+        <v>2351169</v>
+      </c>
+      <c r="AS94" s="11">
+        <v>9427</v>
+      </c>
+      <c r="AT94" s="11">
+        <v>45</v>
+      </c>
+      <c r="AU94" s="12">
+        <v>156744.6</v>
+      </c>
+      <c r="AV94" s="12">
+        <v>628.4666666666667</v>
+      </c>
+      <c r="AW94" s="13">
+        <v>0.80799079499525805</v>
+      </c>
       <c r="AX94" s="11"/>
       <c r="AY94" s="11"/>
       <c r="AZ94" s="11"/>
@@ -20316,27 +20661,27 @@
       </c>
       <c r="N95" s="8">
         <f t="shared" si="18"/>
-        <v>2931904</v>
+        <v>2528792</v>
       </c>
       <c r="O95" s="8">
         <f t="shared" si="19"/>
-        <v>19344</v>
+        <v>16613</v>
       </c>
       <c r="P95" s="8">
         <f t="shared" si="20"/>
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="Q95" s="9">
         <f t="shared" si="21"/>
-        <v>148450.83544303797</v>
+        <v>144778.16793893132</v>
       </c>
       <c r="R95" s="9">
         <f t="shared" si="22"/>
-        <v>979.44303797468342</v>
+        <v>951.12595419847321</v>
       </c>
       <c r="S95" s="10">
         <f t="shared" si="23"/>
-        <v>1.0396297692074408</v>
+        <v>1.0319948222351258</v>
       </c>
       <c r="T95" s="11">
         <v>3447426</v>
@@ -20410,12 +20755,24 @@
       <c r="AQ95" s="13">
         <v>1.065364796022803</v>
       </c>
-      <c r="AR95" s="11"/>
-      <c r="AS95" s="11"/>
-      <c r="AT95" s="11"/>
-      <c r="AU95" s="12"/>
-      <c r="AV95" s="12"/>
-      <c r="AW95" s="13"/>
+      <c r="AR95" s="11">
+        <v>916344</v>
+      </c>
+      <c r="AS95" s="11">
+        <v>5689</v>
+      </c>
+      <c r="AT95" s="11">
+        <v>25</v>
+      </c>
+      <c r="AU95" s="12">
+        <v>109961.28</v>
+      </c>
+      <c r="AV95" s="12">
+        <v>682.68000000000006</v>
+      </c>
+      <c r="AW95" s="13">
+        <v>1.0014550343458659</v>
+      </c>
       <c r="AX95" s="11"/>
       <c r="AY95" s="11"/>
       <c r="AZ95" s="11"/>
@@ -20502,27 +20859,27 @@
       </c>
       <c r="N96" s="8">
         <f t="shared" si="18"/>
-        <v>1254044.5</v>
+        <v>1277146</v>
       </c>
       <c r="O96" s="8">
         <f t="shared" si="19"/>
-        <v>7674.5</v>
+        <v>8077.2</v>
       </c>
       <c r="P96" s="8">
         <f t="shared" si="20"/>
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="Q96" s="9">
         <f t="shared" si="21"/>
-        <v>121359.14516129032</v>
+        <v>121248.03797468354</v>
       </c>
       <c r="R96" s="9">
         <f t="shared" si="22"/>
-        <v>742.69354838709683</v>
+        <v>766.82278481012656</v>
       </c>
       <c r="S96" s="10">
         <f t="shared" si="23"/>
-        <v>0.99080365023428185</v>
+        <v>1.0062433909627952</v>
       </c>
       <c r="T96" s="11">
         <v>224676</v>
@@ -20596,12 +20953,24 @@
       <c r="AQ96" s="13">
         <v>1.1346672045299131</v>
       </c>
-      <c r="AR96" s="11"/>
-      <c r="AS96" s="11"/>
-      <c r="AT96" s="11"/>
-      <c r="AU96" s="12"/>
-      <c r="AV96" s="12"/>
-      <c r="AW96" s="13"/>
+      <c r="AR96" s="11">
+        <v>1369552</v>
+      </c>
+      <c r="AS96" s="11">
+        <v>9688</v>
+      </c>
+      <c r="AT96" s="11">
+        <v>34</v>
+      </c>
+      <c r="AU96" s="12">
+        <v>120842.82352941181</v>
+      </c>
+      <c r="AV96" s="12">
+        <v>854.82352941176464</v>
+      </c>
+      <c r="AW96" s="13">
+        <v>1.0680023538768491</v>
+      </c>
       <c r="AX96" s="11"/>
       <c r="AY96" s="11"/>
       <c r="AZ96" s="11"/>
@@ -20688,27 +21057,27 @@
       </c>
       <c r="N97" s="8">
         <f t="shared" si="18"/>
-        <v>3591561</v>
+        <v>3282436.4</v>
       </c>
       <c r="O97" s="8">
         <f t="shared" si="19"/>
-        <v>15097.75</v>
+        <v>13797.4</v>
       </c>
       <c r="P97" s="8">
         <f t="shared" si="20"/>
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="Q97" s="9">
         <f t="shared" si="21"/>
-        <v>189862.25550660794</v>
+        <v>185798.28679245283</v>
       </c>
       <c r="R97" s="9">
         <f t="shared" si="22"/>
-        <v>798.11894273127757</v>
+        <v>780.98490566037742</v>
       </c>
       <c r="S97" s="10">
         <f t="shared" si="23"/>
-        <v>0.82026486716624403</v>
+        <v>0.8202118937329953</v>
       </c>
       <c r="T97" s="11">
         <v>3842266</v>
@@ -20782,12 +21151,24 @@
       <c r="AQ97" s="13">
         <v>0.8199557845766916</v>
       </c>
-      <c r="AR97" s="11"/>
-      <c r="AS97" s="11"/>
-      <c r="AT97" s="11"/>
-      <c r="AU97" s="12"/>
-      <c r="AV97" s="12"/>
-      <c r="AW97" s="13"/>
+      <c r="AR97" s="11">
+        <v>2045938</v>
+      </c>
+      <c r="AS97" s="11">
+        <v>8596</v>
+      </c>
+      <c r="AT97" s="11">
+        <v>38</v>
+      </c>
+      <c r="AU97" s="12">
+        <v>161521.4210526316</v>
+      </c>
+      <c r="AV97" s="12">
+        <v>678.63157894736844</v>
+      </c>
+      <c r="AW97" s="13">
+        <v>0.82</v>
+      </c>
       <c r="AX97" s="11"/>
       <c r="AY97" s="11"/>
       <c r="AZ97" s="11"/>
@@ -20874,27 +21255,27 @@
       </c>
       <c r="N98" s="8">
         <f t="shared" si="18"/>
-        <v>3988588.75</v>
+        <v>3425136.4</v>
       </c>
       <c r="O98" s="8">
         <f t="shared" si="19"/>
-        <v>29052</v>
+        <v>25468.6</v>
       </c>
       <c r="P98" s="8">
         <f t="shared" si="20"/>
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="Q98" s="9">
         <f t="shared" si="21"/>
-        <v>179936.33458646617</v>
+        <v>171256.82</v>
       </c>
       <c r="R98" s="9">
         <f t="shared" si="22"/>
-        <v>1310.6165413533834</v>
+        <v>1273.43</v>
       </c>
       <c r="S98" s="10">
         <f t="shared" si="23"/>
-        <v>1.0864426196299171</v>
+        <v>1.117266178336435</v>
       </c>
       <c r="T98" s="11">
         <v>5398924</v>
@@ -20968,12 +21349,24 @@
       <c r="AQ98" s="13">
         <v>1.137143450331179</v>
       </c>
-      <c r="AR98" s="11"/>
-      <c r="AS98" s="11"/>
-      <c r="AT98" s="11"/>
-      <c r="AU98" s="12"/>
-      <c r="AV98" s="12"/>
-      <c r="AW98" s="13"/>
+      <c r="AR98" s="11">
+        <v>1171327</v>
+      </c>
+      <c r="AS98" s="11">
+        <v>11135</v>
+      </c>
+      <c r="AT98" s="11">
+        <v>34</v>
+      </c>
+      <c r="AU98" s="12">
+        <v>103352.3823529412</v>
+      </c>
+      <c r="AV98" s="12">
+        <v>982.5</v>
+      </c>
+      <c r="AW98" s="13">
+        <v>1.240560413162507</v>
+      </c>
       <c r="AX98" s="11"/>
       <c r="AY98" s="11"/>
       <c r="AZ98" s="11"/>
@@ -21060,27 +21453,27 @@
       </c>
       <c r="N99" s="8">
         <f t="shared" si="18"/>
-        <v>5127523.5</v>
+        <v>4730343</v>
       </c>
       <c r="O99" s="8">
         <f t="shared" si="19"/>
-        <v>25790.5</v>
+        <v>23722</v>
       </c>
       <c r="P99" s="8">
         <f t="shared" si="20"/>
-        <v>296</v>
+        <v>348</v>
       </c>
       <c r="Q99" s="9">
         <f t="shared" si="21"/>
-        <v>207872.57432432432</v>
+        <v>203894.0948275862</v>
       </c>
       <c r="R99" s="9">
         <f t="shared" si="22"/>
-        <v>1045.5608108108108</v>
+        <v>1022.5</v>
       </c>
       <c r="S99" s="10">
         <f t="shared" si="23"/>
-        <v>0.896559253060077</v>
+        <v>0.89550810807422909</v>
       </c>
       <c r="T99" s="11">
         <v>4901698</v>
@@ -21154,12 +21547,24 @@
       <c r="AQ99" s="13">
         <v>0.90306811716940927</v>
       </c>
-      <c r="AR99" s="11"/>
-      <c r="AS99" s="11"/>
-      <c r="AT99" s="11"/>
-      <c r="AU99" s="12"/>
-      <c r="AV99" s="12"/>
-      <c r="AW99" s="13"/>
+      <c r="AR99" s="11">
+        <v>3141621</v>
+      </c>
+      <c r="AS99" s="11">
+        <v>15448</v>
+      </c>
+      <c r="AT99" s="11">
+        <v>52</v>
+      </c>
+      <c r="AU99" s="12">
+        <v>181247.3653846154</v>
+      </c>
+      <c r="AV99" s="12">
+        <v>891.23076923076928</v>
+      </c>
+      <c r="AW99" s="13">
+        <v>0.89130352813083735</v>
+      </c>
       <c r="AX99" s="11"/>
       <c r="AY99" s="11"/>
       <c r="AZ99" s="11"/>
@@ -21246,27 +21651,27 @@
       </c>
       <c r="N100" s="8">
         <f t="shared" si="18"/>
-        <v>5165920</v>
+        <v>4864199</v>
       </c>
       <c r="O100" s="8">
         <f t="shared" si="19"/>
-        <v>43842.25</v>
+        <v>41956.6</v>
       </c>
       <c r="P100" s="8">
         <f t="shared" si="20"/>
-        <v>298</v>
+        <v>351</v>
       </c>
       <c r="Q100" s="9">
         <f t="shared" si="21"/>
-        <v>208023.62416107382</v>
+        <v>207871.75213675215</v>
       </c>
       <c r="R100" s="9">
         <f t="shared" si="22"/>
-        <v>1765.4597315436242</v>
+        <v>1793.017094017094</v>
       </c>
       <c r="S100" s="10">
         <f t="shared" si="23"/>
-        <v>1.1755213422916502</v>
+        <v>1.1876597285203288</v>
       </c>
       <c r="T100" s="11">
         <v>5648674</v>
@@ -21340,12 +21745,24 @@
       <c r="AQ100" s="13">
         <v>1.229500273524424</v>
       </c>
-      <c r="AR100" s="11"/>
-      <c r="AS100" s="11"/>
-      <c r="AT100" s="11"/>
-      <c r="AU100" s="12"/>
-      <c r="AV100" s="12"/>
-      <c r="AW100" s="13"/>
+      <c r="AR100" s="11">
+        <v>3657315</v>
+      </c>
+      <c r="AS100" s="11">
+        <v>34414</v>
+      </c>
+      <c r="AT100" s="11">
+        <v>53</v>
+      </c>
+      <c r="AU100" s="12">
+        <v>207017.83018867919</v>
+      </c>
+      <c r="AV100" s="12">
+        <v>1947.9622641509429</v>
+      </c>
+      <c r="AW100" s="13">
+        <v>1.2362132734350431</v>
+      </c>
       <c r="AX100" s="11"/>
       <c r="AY100" s="11"/>
       <c r="AZ100" s="11"/>
@@ -21432,27 +21849,27 @@
       </c>
       <c r="N101" s="8">
         <f t="shared" si="18"/>
-        <v>4703563.75</v>
+        <v>4379177</v>
       </c>
       <c r="O101" s="8">
         <f t="shared" si="19"/>
-        <v>24413.75</v>
+        <v>23118.2</v>
       </c>
       <c r="P101" s="8">
         <f t="shared" si="20"/>
-        <v>296</v>
+        <v>349</v>
       </c>
       <c r="Q101" s="9">
         <f t="shared" si="21"/>
-        <v>190685.01689189189</v>
+        <v>188216.77650429797</v>
       </c>
       <c r="R101" s="9">
         <f t="shared" si="22"/>
-        <v>989.74662162162156</v>
+        <v>993.61891117478513</v>
       </c>
       <c r="S101" s="10">
         <f t="shared" si="23"/>
-        <v>0.91694550995026214</v>
+        <v>0.92737271013635847</v>
       </c>
       <c r="T101" s="11">
         <v>5198390</v>
@@ -21526,12 +21943,24 @@
       <c r="AQ101" s="13">
         <v>1.004793548297559</v>
       </c>
-      <c r="AR101" s="11"/>
-      <c r="AS101" s="11"/>
-      <c r="AT101" s="11"/>
-      <c r="AU101" s="12"/>
-      <c r="AV101" s="12"/>
-      <c r="AW101" s="13"/>
+      <c r="AR101" s="11">
+        <v>3081630</v>
+      </c>
+      <c r="AS101" s="11">
+        <v>17936</v>
+      </c>
+      <c r="AT101" s="11">
+        <v>53</v>
+      </c>
+      <c r="AU101" s="12">
+        <v>174431.8867924528</v>
+      </c>
+      <c r="AV101" s="12">
+        <v>1015.245283018868</v>
+      </c>
+      <c r="AW101" s="13">
+        <v>0.9690815108807439</v>
+      </c>
       <c r="AX101" s="11"/>
       <c r="AY101" s="11"/>
       <c r="AZ101" s="11"/>
@@ -21618,27 +22047,27 @@
       </c>
       <c r="N102" s="8">
         <f t="shared" si="18"/>
-        <v>2436156.2999999998</v>
+        <v>2285247.04</v>
       </c>
       <c r="O102" s="8">
         <f t="shared" si="19"/>
-        <v>76596.25</v>
+        <v>70996.800000000003</v>
       </c>
       <c r="P102" s="8">
         <f t="shared" si="20"/>
-        <v>298</v>
+        <v>348</v>
       </c>
       <c r="Q102" s="9">
         <f t="shared" si="21"/>
-        <v>98100.253691275168</v>
+        <v>98502.027586206881</v>
       </c>
       <c r="R102" s="9">
         <f t="shared" si="22"/>
-        <v>3084.4127516778522</v>
+        <v>3060.2068965517242</v>
       </c>
       <c r="S102" s="10">
         <f t="shared" si="23"/>
-        <v>2.2417829489555281</v>
+        <v>2.2261150194662904</v>
       </c>
       <c r="T102" s="11">
         <v>2396165.2000000002</v>
@@ -21712,12 +22141,24 @@
       <c r="AQ102" s="13">
         <v>2.2548065063809029</v>
       </c>
-      <c r="AR102" s="11"/>
-      <c r="AS102" s="11"/>
-      <c r="AT102" s="11"/>
-      <c r="AU102" s="12"/>
-      <c r="AV102" s="12"/>
-      <c r="AW102" s="13"/>
+      <c r="AR102" s="11">
+        <v>1681610</v>
+      </c>
+      <c r="AS102" s="11">
+        <v>48599</v>
+      </c>
+      <c r="AT102" s="11">
+        <v>50</v>
+      </c>
+      <c r="AU102" s="12">
+        <v>100896.6</v>
+      </c>
+      <c r="AV102" s="12">
+        <v>2915.94</v>
+      </c>
+      <c r="AW102" s="13">
+        <v>2.1634433015093388</v>
+      </c>
       <c r="AX102" s="11"/>
       <c r="AY102" s="11"/>
       <c r="AZ102" s="11"/>
@@ -21804,27 +22245,27 @@
       </c>
       <c r="N103" s="8">
         <f t="shared" si="18"/>
-        <v>282287.25</v>
+        <v>249480.6</v>
       </c>
       <c r="O103" s="8">
         <f t="shared" si="19"/>
-        <v>125811.75</v>
+        <v>116788.8</v>
       </c>
       <c r="P103" s="8">
         <f t="shared" si="20"/>
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="Q103" s="9">
         <f t="shared" si="21"/>
-        <v>11844.220279720281</v>
+        <v>11038.964601769912</v>
       </c>
       <c r="R103" s="9">
         <f t="shared" si="22"/>
-        <v>5278.8146853146854</v>
+        <v>5167.646017699115</v>
       </c>
       <c r="S103" s="10">
         <f t="shared" si="23"/>
-        <v>8.5756779122739708</v>
+        <v>8.9646792606102466</v>
       </c>
       <c r="T103" s="11">
         <v>274124</v>
@@ -21898,12 +22339,24 @@
       <c r="AQ103" s="13">
         <v>9.3031146098002289</v>
       </c>
-      <c r="AR103" s="11"/>
-      <c r="AS103" s="11"/>
-      <c r="AT103" s="11"/>
-      <c r="AU103" s="12"/>
-      <c r="AV103" s="12"/>
-      <c r="AW103" s="13"/>
+      <c r="AR103" s="11">
+        <v>118254</v>
+      </c>
+      <c r="AS103" s="11">
+        <v>80697</v>
+      </c>
+      <c r="AT103" s="11">
+        <v>53</v>
+      </c>
+      <c r="AU103" s="12">
+        <v>6693.6226415094334</v>
+      </c>
+      <c r="AV103" s="12">
+        <v>4567.7547169811323</v>
+      </c>
+      <c r="AW103" s="13">
+        <v>10.52068465395535</v>
+      </c>
       <c r="AX103" s="11"/>
       <c r="AY103" s="11"/>
       <c r="AZ103" s="11"/>
@@ -21990,27 +22443,27 @@
       </c>
       <c r="N104" s="8">
         <f t="shared" si="18"/>
-        <v>3432157.67</v>
+        <v>4534358.3360000001</v>
       </c>
       <c r="O104" s="8">
         <f t="shared" si="19"/>
-        <v>4575</v>
+        <v>5351</v>
       </c>
       <c r="P104" s="8">
         <f t="shared" si="20"/>
-        <v>241</v>
+        <v>293</v>
       </c>
       <c r="Q104" s="9">
         <f t="shared" si="21"/>
-        <v>170895.81759336099</v>
+        <v>232134.38580204779</v>
       </c>
       <c r="R104" s="9">
         <f t="shared" si="22"/>
-        <v>227.80082987551867</v>
+        <v>273.94197952218428</v>
       </c>
       <c r="S104" s="10">
         <f t="shared" si="23"/>
-        <v>0.44863033525047402</v>
+        <v>0.43724599914479417</v>
       </c>
       <c r="T104" s="11">
         <v>2471269.08</v>
@@ -22084,12 +22537,24 @@
       <c r="AQ104" s="13">
         <v>0.50572229535480118</v>
       </c>
-      <c r="AR104" s="11"/>
-      <c r="AS104" s="11"/>
-      <c r="AT104" s="11"/>
-      <c r="AU104" s="12"/>
-      <c r="AV104" s="12"/>
-      <c r="AW104" s="13"/>
+      <c r="AR104" s="11">
+        <v>8943161</v>
+      </c>
+      <c r="AS104" s="11">
+        <v>8455</v>
+      </c>
+      <c r="AT104" s="11">
+        <v>52</v>
+      </c>
+      <c r="AU104" s="12">
+        <v>515951.59615384613</v>
+      </c>
+      <c r="AV104" s="12">
+        <v>487.78846153846149</v>
+      </c>
+      <c r="AW104" s="13">
+        <v>0.39170865472207478</v>
+      </c>
       <c r="AX104" s="11"/>
       <c r="AY104" s="11"/>
       <c r="AZ104" s="11"/>
@@ -22176,27 +22641,27 @@
       </c>
       <c r="N105" s="8">
         <f t="shared" si="18"/>
-        <v>3074533.6575000002</v>
+        <v>3210140.1260000002</v>
       </c>
       <c r="O105" s="8">
         <f t="shared" si="19"/>
-        <v>4796.75</v>
+        <v>5602</v>
       </c>
       <c r="P105" s="8">
         <f t="shared" si="20"/>
-        <v>270</v>
+        <v>316</v>
       </c>
       <c r="Q105" s="9">
         <f t="shared" si="21"/>
-        <v>136645.94033333333</v>
+        <v>152380.06927215192</v>
       </c>
       <c r="R105" s="9">
         <f t="shared" si="22"/>
-        <v>213.18888888888887</v>
+        <v>265.91772151898738</v>
       </c>
       <c r="S105" s="10">
         <f t="shared" si="23"/>
-        <v>0.48371819207276412</v>
+        <v>0.50980286730721702</v>
       </c>
       <c r="T105" s="11">
         <v>2163577.9500000002</v>
@@ -22270,12 +22735,24 @@
       <c r="AQ105" s="13">
         <v>0.55095584434102574</v>
       </c>
-      <c r="AR105" s="11"/>
-      <c r="AS105" s="11"/>
-      <c r="AT105" s="11"/>
-      <c r="AU105" s="12"/>
-      <c r="AV105" s="12"/>
-      <c r="AW105" s="13"/>
+      <c r="AR105" s="11">
+        <v>3752566</v>
+      </c>
+      <c r="AS105" s="11">
+        <v>8823</v>
+      </c>
+      <c r="AT105" s="11">
+        <v>46</v>
+      </c>
+      <c r="AU105" s="12">
+        <v>244732.5652173913</v>
+      </c>
+      <c r="AV105" s="12">
+        <v>575.41304347826087</v>
+      </c>
+      <c r="AW105" s="13">
+        <v>0.61414156824502897</v>
+      </c>
       <c r="AX105" s="11"/>
       <c r="AY105" s="11"/>
       <c r="AZ105" s="11"/>
@@ -22362,27 +22839,27 @@
       </c>
       <c r="N106" s="8">
         <f t="shared" si="18"/>
-        <v>9789021</v>
+        <v>9191696</v>
       </c>
       <c r="O106" s="8">
         <f t="shared" si="19"/>
-        <v>178329.75</v>
+        <v>165833.4</v>
       </c>
       <c r="P106" s="8">
         <f t="shared" si="20"/>
-        <v>279</v>
+        <v>327</v>
       </c>
       <c r="Q106" s="9">
         <f t="shared" si="21"/>
-        <v>421033.16129032255</v>
+        <v>421637.43119266059</v>
       </c>
       <c r="R106" s="9">
         <f t="shared" si="22"/>
-        <v>7670.0967741935474</v>
+        <v>7607.0366972477068</v>
       </c>
       <c r="S106" s="10">
         <f t="shared" si="23"/>
-        <v>1.716487193823985</v>
+        <v>1.7050834072020151</v>
       </c>
       <c r="T106" s="11">
         <v>10039950</v>
@@ -22456,12 +22933,24 @@
       <c r="AQ106" s="13">
         <v>1.6483479868220821</v>
       </c>
-      <c r="AR106" s="11"/>
-      <c r="AS106" s="11"/>
-      <c r="AT106" s="11"/>
-      <c r="AU106" s="12"/>
-      <c r="AV106" s="12"/>
-      <c r="AW106" s="13"/>
+      <c r="AR106" s="11">
+        <v>6802396</v>
+      </c>
+      <c r="AS106" s="11">
+        <v>115848</v>
+      </c>
+      <c r="AT106" s="11">
+        <v>48</v>
+      </c>
+      <c r="AU106" s="12">
+        <v>425149.75</v>
+      </c>
+      <c r="AV106" s="12">
+        <v>7240.5</v>
+      </c>
+      <c r="AW106" s="13">
+        <v>1.659468260714136</v>
+      </c>
       <c r="AX106" s="11"/>
       <c r="AY106" s="11"/>
       <c r="AZ106" s="11"/>
@@ -22548,27 +23037,27 @@
       </c>
       <c r="N107" s="8">
         <f t="shared" si="18"/>
-        <v>4340493.75</v>
+        <v>3872995.4</v>
       </c>
       <c r="O107" s="8">
         <f t="shared" si="19"/>
-        <v>227167</v>
+        <v>207591.2</v>
       </c>
       <c r="P107" s="8">
         <f t="shared" si="20"/>
-        <v>295</v>
+        <v>343</v>
       </c>
       <c r="Q107" s="9">
         <f t="shared" si="21"/>
-        <v>176562.45762711865</v>
+        <v>169372.97667638486</v>
       </c>
       <c r="R107" s="9">
         <f t="shared" si="22"/>
-        <v>9240.6915254237283</v>
+        <v>9078.3323615160334</v>
       </c>
       <c r="S107" s="10">
         <f t="shared" si="23"/>
-        <v>2.8991343822013644</v>
+        <v>2.9661944750306333</v>
       </c>
       <c r="T107" s="11">
         <v>4508101</v>
@@ -22642,12 +23131,24 @@
       <c r="AQ107" s="13">
         <v>2.9423938694210299</v>
       </c>
-      <c r="AR107" s="11"/>
-      <c r="AS107" s="11"/>
-      <c r="AT107" s="11"/>
-      <c r="AU107" s="12"/>
-      <c r="AV107" s="12"/>
-      <c r="AW107" s="13"/>
+      <c r="AR107" s="11">
+        <v>2003002</v>
+      </c>
+      <c r="AS107" s="11">
+        <v>129288</v>
+      </c>
+      <c r="AT107" s="11">
+        <v>48</v>
+      </c>
+      <c r="AU107" s="12">
+        <v>125187.625</v>
+      </c>
+      <c r="AV107" s="12">
+        <v>8080.5</v>
+      </c>
+      <c r="AW107" s="13">
+        <v>3.2344348463477082</v>
+      </c>
       <c r="AX107" s="11"/>
       <c r="AY107" s="11"/>
       <c r="AZ107" s="11"/>
@@ -22734,27 +23235,27 @@
       </c>
       <c r="N108" s="8">
         <f t="shared" si="18"/>
-        <v>4639965.25</v>
+        <v>4603831.4000000004</v>
       </c>
       <c r="O108" s="8">
         <f t="shared" si="19"/>
-        <v>211263.75</v>
+        <v>191312.8</v>
       </c>
       <c r="P108" s="8">
         <f t="shared" si="20"/>
-        <v>288</v>
+        <v>335</v>
       </c>
       <c r="Q108" s="9">
         <f t="shared" si="21"/>
-        <v>193331.88541666666</v>
+        <v>206141.70447761196</v>
       </c>
       <c r="R108" s="9">
         <f t="shared" si="22"/>
-        <v>8802.65625</v>
+        <v>8566.2447761194035</v>
       </c>
       <c r="S108" s="10">
         <f t="shared" si="23"/>
-        <v>2.7816724271349482</v>
+        <v>2.6276618853911602</v>
       </c>
       <c r="T108" s="11">
         <v>3557826</v>
@@ -22828,12 +23329,24 @@
       <c r="AQ108" s="13">
         <v>2.1719636954714021</v>
       </c>
-      <c r="AR108" s="11"/>
-      <c r="AS108" s="11"/>
-      <c r="AT108" s="11"/>
-      <c r="AU108" s="12"/>
-      <c r="AV108" s="12"/>
-      <c r="AW108" s="13"/>
+      <c r="AR108" s="11">
+        <v>4459296</v>
+      </c>
+      <c r="AS108" s="11">
+        <v>111509</v>
+      </c>
+      <c r="AT108" s="11">
+        <v>47</v>
+      </c>
+      <c r="AU108" s="12">
+        <v>284635.91489361698</v>
+      </c>
+      <c r="AV108" s="12">
+        <v>7117.5957446808507</v>
+      </c>
+      <c r="AW108" s="13">
+        <v>2.0116197184160072</v>
+      </c>
       <c r="AX108" s="11"/>
       <c r="AY108" s="11"/>
       <c r="AZ108" s="11"/>
@@ -22920,27 +23433,27 @@
       </c>
       <c r="N109" s="8">
         <f t="shared" si="18"/>
-        <v>2145526.25</v>
+        <v>1956430.2</v>
       </c>
       <c r="O109" s="8">
         <f t="shared" si="19"/>
-        <v>235210.5</v>
+        <v>217086.2</v>
       </c>
       <c r="P109" s="8">
         <f t="shared" si="20"/>
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="Q109" s="9">
         <f t="shared" si="21"/>
-        <v>139169.2702702703</v>
+        <v>134002.0684931507</v>
       </c>
       <c r="R109" s="9">
         <f t="shared" si="22"/>
-        <v>15256.897297297297</v>
+        <v>14868.917808219179</v>
       </c>
       <c r="S109" s="10">
         <f t="shared" si="23"/>
-        <v>4.2090978060078275</v>
+        <v>4.2512632657211196</v>
       </c>
       <c r="T109" s="11">
         <v>3150735</v>
@@ -23014,12 +23527,24 @@
       <c r="AQ109" s="13">
         <v>4.2978152416803432</v>
       </c>
-      <c r="AR109" s="11"/>
-      <c r="AS109" s="11"/>
-      <c r="AT109" s="11"/>
-      <c r="AU109" s="12"/>
-      <c r="AV109" s="12"/>
-      <c r="AW109" s="13"/>
+      <c r="AR109" s="11">
+        <v>1200046</v>
+      </c>
+      <c r="AS109" s="11">
+        <v>144589</v>
+      </c>
+      <c r="AT109" s="11">
+        <v>34</v>
+      </c>
+      <c r="AU109" s="12">
+        <v>105886.4117647059</v>
+      </c>
+      <c r="AV109" s="12">
+        <v>12757.85294117647</v>
+      </c>
+      <c r="AW109" s="13">
+        <v>4.4199251045742862</v>
+      </c>
       <c r="AX109" s="11"/>
       <c r="AY109" s="11"/>
       <c r="AZ109" s="11"/>
@@ -23106,27 +23631,27 @@
       </c>
       <c r="N110" s="8">
         <f t="shared" si="18"/>
-        <v>856201.25</v>
+        <v>752366</v>
       </c>
       <c r="O110" s="8">
         <f t="shared" si="19"/>
-        <v>195166.75</v>
+        <v>178433.8</v>
       </c>
       <c r="P110" s="8">
         <f t="shared" si="20"/>
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="Q110" s="9">
         <f t="shared" ref="Q110:Q111" si="24">IFERROR(SUM(T110,Z110,AF110,AL110,AR110,AX110,BD110,BJ110,BP110,BV110,CB110,CH110)/P110*3," ")</f>
-        <v>55839.211956521736</v>
+        <v>52247.638888888891</v>
       </c>
       <c r="R110" s="9">
         <f t="shared" si="22"/>
-        <v>12728.266304347828</v>
+        <v>12391.236111111113</v>
       </c>
       <c r="S110" s="10">
         <f t="shared" si="23"/>
-        <v>6.1549159447203419</v>
+        <v>6.3886506269897225</v>
       </c>
       <c r="T110" s="11">
         <v>1383825</v>
@@ -23200,12 +23725,24 @@
       <c r="AQ110" s="13">
         <v>7.0049541312486694</v>
       </c>
-      <c r="AR110" s="11"/>
-      <c r="AS110" s="11"/>
-      <c r="AT110" s="11"/>
-      <c r="AU110" s="12"/>
-      <c r="AV110" s="12"/>
-      <c r="AW110" s="13"/>
+      <c r="AR110" s="11">
+        <v>337025</v>
+      </c>
+      <c r="AS110" s="11">
+        <v>111502</v>
+      </c>
+      <c r="AT110" s="11">
+        <v>32</v>
+      </c>
+      <c r="AU110" s="12">
+        <v>31596.09375</v>
+      </c>
+      <c r="AV110" s="12">
+        <v>10453.3125</v>
+      </c>
+      <c r="AW110" s="13">
+        <v>7.323589356067246</v>
+      </c>
       <c r="AX110" s="11"/>
       <c r="AY110" s="11"/>
       <c r="AZ110" s="11"/>
@@ -23292,27 +23829,27 @@
       </c>
       <c r="N111" s="8">
         <f t="shared" si="18"/>
-        <v>3335585.25</v>
+        <v>2717683.6</v>
       </c>
       <c r="O111" s="8">
         <f t="shared" si="19"/>
-        <v>15423.25</v>
+        <v>12593.2</v>
       </c>
       <c r="P111" s="8">
         <f t="shared" si="20"/>
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="Q111" s="9">
         <f t="shared" si="24"/>
-        <v>152194.00380228137</v>
+        <v>149323.27472527474</v>
       </c>
       <c r="R111" s="9">
         <f t="shared" si="22"/>
-        <v>703.72243346007599</v>
+        <v>691.93406593406598</v>
       </c>
       <c r="S111" s="10">
         <f t="shared" si="23"/>
-        <v>0.87362827753349115</v>
+        <v>0.88193307549590672</v>
       </c>
       <c r="T111" s="11">
         <v>3953686</v>
@@ -23386,12 +23923,24 @@
       <c r="AQ111" s="13">
         <v>1.030271901843052</v>
       </c>
-      <c r="AR111" s="11"/>
-      <c r="AS111" s="11"/>
-      <c r="AT111" s="11"/>
-      <c r="AU111" s="12"/>
-      <c r="AV111" s="12"/>
-      <c r="AW111" s="13"/>
+      <c r="AR111" s="11">
+        <v>246077</v>
+      </c>
+      <c r="AS111" s="11">
+        <v>1273</v>
+      </c>
+      <c r="AT111" s="11">
+        <v>10</v>
+      </c>
+      <c r="AU111" s="12">
+        <v>73823.100000000006</v>
+      </c>
+      <c r="AV111" s="12">
+        <v>381.9</v>
+      </c>
+      <c r="AW111" s="13">
+        <v>0.91515226734556909</v>
+      </c>
       <c r="AX111" s="11"/>
       <c r="AY111" s="11"/>
       <c r="AZ111" s="11"/>
@@ -23464,11 +24013,11 @@
       <c r="M112" s="22"/>
       <c r="N112" s="14">
         <f>SUM(N57:N111)</f>
-        <v>221139103.80916664</v>
+        <v>209814354.11399996</v>
       </c>
       <c r="O112" s="14">
         <f>SUM(O57:O111)</f>
-        <v>3024855</v>
+        <v>2817245.75</v>
       </c>
       <c r="P112" s="14"/>
       <c r="Q112" s="14"/>
@@ -23524,11 +24073,11 @@
       <c r="AQ112" s="24"/>
       <c r="AR112" s="14">
         <f>SUM(AR57:AR111)</f>
-        <v>0</v>
+        <v>161133472</v>
       </c>
       <c r="AS112" s="14">
         <f>SUM(AS57:AS111)</f>
-        <v>0</v>
+        <v>1978883</v>
       </c>
       <c r="AT112" s="14"/>
       <c r="AU112" s="14"/>
@@ -24078,27 +24627,27 @@
       </c>
       <c r="N116" s="8">
         <f t="shared" ref="N116:O118" si="25">IFERROR(AVERAGE(T116,Z116,AF116,AL116,AR116,AX116,BD116,BJ116,BP116,BV116,CB116,CH116)," ")</f>
-        <v>2504085.75</v>
+        <v>2328601.2000000002</v>
       </c>
       <c r="O116" s="8">
         <f t="shared" si="25"/>
-        <v>376578</v>
+        <v>353104</v>
       </c>
       <c r="P116" s="8">
         <f>IFERROR(SUM(V116,AB116,AH116,AN116,AT116,AZ116,BF116,BL116,BR116,BX116,CD116,CJ116)," ")</f>
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="Q116" s="9">
         <f>IFERROR(SUM(T116,Z116,AF116,AL116,AR116,AX116,BD116,BJ116,BP116,BV116,CB116,CH116)/P116*3," ")</f>
-        <v>268294.90178571432</v>
+        <v>268684.75384615385</v>
       </c>
       <c r="R116" s="9">
         <f>IFERROR(SUM(U116,AA116,AG116,AM116,AS116,AY116,BE116,BK116,BQ116,BW116,CC116,CI116)/P116*3," ")</f>
-        <v>40347.642857142855</v>
+        <v>40742.769230769227</v>
       </c>
       <c r="S116" s="10">
         <f>IFERROR(AVERAGE(Y116,AE116,AK116,AQ116,AW116,BC116,BI116,BO116,BU116,CA116,CG116,CM116)," ")</f>
-        <v>4.9730196708922394</v>
+        <v>4.9949592229449653</v>
       </c>
       <c r="T116" s="11">
         <v>3772092</v>
@@ -24172,12 +24721,24 @@
       <c r="AQ116" s="13">
         <v>4.8745583826523786</v>
       </c>
-      <c r="AR116" s="11"/>
-      <c r="AS116" s="11"/>
-      <c r="AT116" s="11"/>
-      <c r="AU116" s="12"/>
-      <c r="AV116" s="12"/>
-      <c r="AW116" s="13"/>
+      <c r="AR116" s="11">
+        <v>1626663</v>
+      </c>
+      <c r="AS116" s="11">
+        <v>259208</v>
+      </c>
+      <c r="AT116" s="11">
+        <v>18</v>
+      </c>
+      <c r="AU116" s="12">
+        <v>271110.5</v>
+      </c>
+      <c r="AV116" s="12">
+        <v>43201.333333333343</v>
+      </c>
+      <c r="AW116" s="13">
+        <v>5.0827174311558654</v>
+      </c>
       <c r="AX116" s="11"/>
       <c r="AY116" s="11"/>
       <c r="AZ116" s="11"/>
@@ -24262,27 +24823,27 @@
       </c>
       <c r="N117" s="8">
         <f t="shared" si="25"/>
-        <v>2654608.5</v>
+        <v>2424220.2000000002</v>
       </c>
       <c r="O117" s="8">
         <f t="shared" si="25"/>
-        <v>398333</v>
+        <v>367036.4</v>
       </c>
       <c r="P117" s="8">
         <f>IFERROR(SUM(V117,AB117,AH117,AN117,AT117,AZ117,BF117,BL117,BR117,BX117,CD117,CJ117)," ")</f>
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="Q117" s="9">
         <f>IFERROR(SUM(T117,Z117,AF117,AL117,AR117,AX117,BD117,BJ117,BP117,BV117,CB117,CH117)/P117*3," ")</f>
-        <v>269960.18644067796</v>
+        <v>265425.56934306567</v>
       </c>
       <c r="R117" s="9">
         <f>IFERROR(SUM(U117,AA117,AG117,AM117,AS117,AY117,BE117,BK117,BQ117,BW117,CC117,CI117)/P117*3," ")</f>
-        <v>40508.4406779661</v>
+        <v>40186.46715328467</v>
       </c>
       <c r="S117" s="10">
         <f>IFERROR(AVERAGE(Y117,AE117,AK117,AQ117,AW117,BC117,BI117,BO117,BU117,CA117,CG117,CM117)," ")</f>
-        <v>4.965343804125153</v>
+        <v>4.9939161440763957</v>
       </c>
       <c r="T117" s="11">
         <v>4072469</v>
@@ -24356,12 +24917,24 @@
       <c r="AQ117" s="13">
         <v>4.8823744841849717</v>
       </c>
-      <c r="AR117" s="11"/>
-      <c r="AS117" s="11"/>
-      <c r="AT117" s="11"/>
-      <c r="AU117" s="12"/>
-      <c r="AV117" s="12"/>
-      <c r="AW117" s="13"/>
+      <c r="AR117" s="11">
+        <v>1502667</v>
+      </c>
+      <c r="AS117" s="11">
+        <v>241850</v>
+      </c>
+      <c r="AT117" s="11">
+        <v>19</v>
+      </c>
+      <c r="AU117" s="12">
+        <v>237263.21052631579</v>
+      </c>
+      <c r="AV117" s="12">
+        <v>38186.84210526316</v>
+      </c>
+      <c r="AW117" s="13">
+        <v>5.1082055038813658</v>
+      </c>
       <c r="AX117" s="11"/>
       <c r="AY117" s="11"/>
       <c r="AZ117" s="11"/>
@@ -24445,27 +25018,27 @@
       </c>
       <c r="N118" s="8">
         <f t="shared" si="25"/>
-        <v>715606.6</v>
+        <v>670562.28</v>
       </c>
       <c r="O118" s="8">
         <f t="shared" si="25"/>
-        <v>791858.25</v>
+        <v>742491.6</v>
       </c>
       <c r="P118" s="8">
         <f>IFERROR(SUM(V118,AB118,AH118,AN118,AT118,AZ118,BF118,BL118,BR118,BX118,CD118,CJ118)," ")</f>
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="Q118" s="9">
         <f>IFERROR(SUM(T118,Z118,AF118,AL118,AR118,AX118,BD118,BJ118,BP118,BV118,CB118,CH118)/P118*3," ")</f>
-        <v>84189.01176470588</v>
+        <v>85240.967796610174</v>
       </c>
       <c r="R118" s="9">
         <f>IFERROR(SUM(U118,AA118,AG118,AM118,AS118,AY118,BE118,BK118,BQ118,BW118,CC118,CI118)/P118*3," ")</f>
-        <v>93159.794117647063</v>
+        <v>94384.525423728817</v>
       </c>
       <c r="S118" s="10">
         <f>IFERROR(AVERAGE(Y118,AE118,AK118,AQ118,AW118,BC118,BI118,BO118,BU118,CA118,CG118,CM118)," ")</f>
-        <v>14.979314516320638</v>
+        <v>14.965751705544694</v>
       </c>
       <c r="T118" s="11">
         <v>1050265</v>
@@ -24539,12 +25112,24 @@
       <c r="AQ118" s="13">
         <v>14.966763579216821</v>
       </c>
-      <c r="AR118" s="11"/>
-      <c r="AS118" s="11"/>
-      <c r="AT118" s="11"/>
-      <c r="AU118" s="12"/>
-      <c r="AV118" s="12"/>
-      <c r="AW118" s="13"/>
+      <c r="AR118" s="11">
+        <v>490385</v>
+      </c>
+      <c r="AS118" s="11">
+        <v>545025</v>
+      </c>
+      <c r="AT118" s="11">
+        <v>16</v>
+      </c>
+      <c r="AU118" s="12">
+        <v>91947.1875</v>
+      </c>
+      <c r="AV118" s="12">
+        <v>102192.1875</v>
+      </c>
+      <c r="AW118" s="13">
+        <v>14.91150046244092</v>
+      </c>
       <c r="AX118" s="11"/>
       <c r="AY118" s="11"/>
       <c r="AZ118" s="11"/>
@@ -24614,11 +25199,11 @@
       <c r="M119" s="22"/>
       <c r="N119" s="14">
         <f>SUM(N116:N118)</f>
-        <v>5874300.8499999996</v>
+        <v>5423383.6800000006</v>
       </c>
       <c r="O119" s="14">
         <f>SUM(O116:O118)</f>
-        <v>1566769.25</v>
+        <v>1462632</v>
       </c>
       <c r="P119" s="14"/>
       <c r="Q119" s="14"/>
@@ -24674,11 +25259,11 @@
       <c r="AQ119" s="14"/>
       <c r="AR119" s="14">
         <f>SUM(AR116:AR118)</f>
-        <v>0</v>
+        <v>3619715</v>
       </c>
       <c r="AS119" s="14">
         <f>SUM(AS116:AS118)</f>
-        <v>0</v>
+        <v>1046083</v>
       </c>
       <c r="AT119" s="14"/>
       <c r="AU119" s="14"/>
@@ -24784,6 +25369,35 @@
   </sheetData>
   <autoFilter ref="A2:CM53" xr:uid="{B264AC42-3408-4CC4-A254-80BEFA0AA9F5}"/>
   <mergeCells count="45">
+    <mergeCell ref="CB114:CG114"/>
+    <mergeCell ref="CH114:CM114"/>
+    <mergeCell ref="N114:S114"/>
+    <mergeCell ref="AX114:BC114"/>
+    <mergeCell ref="BD114:BI114"/>
+    <mergeCell ref="BJ114:BO114"/>
+    <mergeCell ref="BP114:BU114"/>
+    <mergeCell ref="BV114:CA114"/>
+    <mergeCell ref="T114:Y114"/>
+    <mergeCell ref="Z114:AE114"/>
+    <mergeCell ref="AF114:AK114"/>
+    <mergeCell ref="AL114:AQ114"/>
+    <mergeCell ref="AR114:AW114"/>
+    <mergeCell ref="BP55:BU55"/>
+    <mergeCell ref="BV55:CA55"/>
+    <mergeCell ref="CB55:CG55"/>
+    <mergeCell ref="CH55:CM55"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="AL55:AQ55"/>
+    <mergeCell ref="AR55:AW55"/>
+    <mergeCell ref="AX55:BC55"/>
+    <mergeCell ref="BD55:BI55"/>
+    <mergeCell ref="BJ55:BO55"/>
+    <mergeCell ref="T1:Y1"/>
+    <mergeCell ref="Z1:AE1"/>
+    <mergeCell ref="AF1:AK1"/>
+    <mergeCell ref="T55:Y55"/>
+    <mergeCell ref="Z55:AE55"/>
+    <mergeCell ref="AF55:AK55"/>
     <mergeCell ref="B114:G114"/>
     <mergeCell ref="H114:M114"/>
     <mergeCell ref="CB1:CG1"/>
@@ -24800,35 +25414,6 @@
     <mergeCell ref="AL1:AQ1"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H1:M1"/>
-    <mergeCell ref="T1:Y1"/>
-    <mergeCell ref="Z1:AE1"/>
-    <mergeCell ref="AF1:AK1"/>
-    <mergeCell ref="T55:Y55"/>
-    <mergeCell ref="Z55:AE55"/>
-    <mergeCell ref="AF55:AK55"/>
-    <mergeCell ref="BP55:BU55"/>
-    <mergeCell ref="BV55:CA55"/>
-    <mergeCell ref="CB55:CG55"/>
-    <mergeCell ref="CH55:CM55"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="AL55:AQ55"/>
-    <mergeCell ref="AR55:AW55"/>
-    <mergeCell ref="AX55:BC55"/>
-    <mergeCell ref="BD55:BI55"/>
-    <mergeCell ref="BJ55:BO55"/>
-    <mergeCell ref="CB114:CG114"/>
-    <mergeCell ref="CH114:CM114"/>
-    <mergeCell ref="N114:S114"/>
-    <mergeCell ref="AX114:BC114"/>
-    <mergeCell ref="BD114:BI114"/>
-    <mergeCell ref="BJ114:BO114"/>
-    <mergeCell ref="BP114:BU114"/>
-    <mergeCell ref="BV114:CA114"/>
-    <mergeCell ref="T114:Y114"/>
-    <mergeCell ref="Z114:AE114"/>
-    <mergeCell ref="AF114:AK114"/>
-    <mergeCell ref="AL114:AQ114"/>
-    <mergeCell ref="AR114:AW114"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Kapabilite/Kapabilite 2026.xlsx
+++ b/Kapabilite/Kapabilite 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Kapabilite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34501D0D-0CF4-4E99-B689-8249CCDBE466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DD363D-E439-484D-A223-1890364870EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8FA9AADE-0AF1-42A7-AB4A-1A5F3041D90E}"/>
   </bookViews>
@@ -3292,27 +3292,27 @@
       </c>
       <c r="N3" s="8">
         <f t="shared" ref="N3:N25" si="0">IFERROR(AVERAGE(T3,Z3,AF3,AL3,AR3,AX3,BD3,BJ3,BP3,BV3,CB3,CH3)," ")</f>
-        <v>132500</v>
+        <v>150083.33333333334</v>
       </c>
       <c r="O3" s="8">
         <f t="shared" ref="O3:O25" si="1">IFERROR(AVERAGE(U3,AA3,AG3,AM3,AS3,AY3,BE3,BK3,BQ3,BW3,CC3,CI3)," ")</f>
-        <v>47058.6</v>
+        <v>53383.5</v>
       </c>
       <c r="P3" s="8">
         <f t="shared" ref="P3:P25" si="2">IFERROR(SUM(V3,AB3,AH3,AN3,AT3,AZ3,BF3,BL3,BR3,BX3,CD3,CJ3)," ")</f>
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="Q3" s="9">
         <f t="shared" ref="Q3:Q25" si="3">IFERROR(SUM(T3,Z3,AF3,AL3,AR3,AX3,BD3,BJ3,BP3,BV3,CB3,CH3)/P3*3," ")</f>
-        <v>16425.619834710746</v>
+        <v>15891.176470588234</v>
       </c>
       <c r="R3" s="9">
         <f t="shared" ref="R3:R25" si="4">IFERROR(SUM(U3,AA3,AG3,AM3,AS3,AY3,BE3,BK3,BQ3,BW3,CC3,CI3)/P3*3," ")</f>
-        <v>5833.7107438016528</v>
+        <v>5652.3705882352933</v>
       </c>
       <c r="S3" s="10">
         <f t="shared" ref="S3:S25" si="5">IFERROR(AVERAGE(Y3,AE3,AK3,AQ3,AW3,BC3,BI3,BO3,BU3,CA3,CG3,CM3)," ")</f>
-        <v>9.9051739960312979</v>
+        <v>9.9246507546036327</v>
       </c>
       <c r="T3" s="11">
         <v>24000</v>
@@ -3404,12 +3404,24 @@
       <c r="AW3" s="13">
         <v>10</v>
       </c>
-      <c r="AX3" s="11"/>
-      <c r="AY3" s="11"/>
-      <c r="AZ3" s="11"/>
-      <c r="BA3" s="12"/>
-      <c r="BB3" s="12"/>
-      <c r="BC3" s="13"/>
+      <c r="AX3" s="11">
+        <v>238000</v>
+      </c>
+      <c r="AY3" s="11">
+        <v>85008</v>
+      </c>
+      <c r="AZ3" s="11">
+        <v>49</v>
+      </c>
+      <c r="BA3" s="12">
+        <v>14571.428571428571</v>
+      </c>
+      <c r="BB3" s="12">
+        <v>5204.5714285714284</v>
+      </c>
+      <c r="BC3" s="13">
+        <v>10.02203454746531</v>
+      </c>
       <c r="BD3" s="11"/>
       <c r="BE3" s="11"/>
       <c r="BF3" s="11"/>
@@ -3487,27 +3499,27 @@
       </c>
       <c r="N4" s="8">
         <f t="shared" si="0"/>
-        <v>291482.59999999998</v>
+        <v>292725.5</v>
       </c>
       <c r="O4" s="8">
         <f t="shared" si="1"/>
-        <v>11375.8</v>
+        <v>11327</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" si="2"/>
-        <v>239</v>
+        <v>286</v>
       </c>
       <c r="Q4" s="9">
         <f t="shared" si="3"/>
-        <v>18293.887029288704</v>
+        <v>18423.283216783217</v>
       </c>
       <c r="R4" s="9">
         <f t="shared" si="4"/>
-        <v>713.96234309623435</v>
+        <v>712.88811188811189</v>
       </c>
       <c r="S4" s="10">
         <f t="shared" si="5"/>
-        <v>2.7120350967303795</v>
+        <v>2.7016959139419829</v>
       </c>
       <c r="T4" s="11">
         <v>328790</v>
@@ -3599,12 +3611,24 @@
       <c r="AW4" s="13">
         <v>2.65</v>
       </c>
-      <c r="AX4" s="11"/>
-      <c r="AY4" s="11"/>
-      <c r="AZ4" s="11"/>
-      <c r="BA4" s="12"/>
-      <c r="BB4" s="12"/>
-      <c r="BC4" s="13"/>
+      <c r="AX4" s="11">
+        <v>298940</v>
+      </c>
+      <c r="AY4" s="11">
+        <v>11083</v>
+      </c>
+      <c r="AZ4" s="11">
+        <v>47</v>
+      </c>
+      <c r="BA4" s="12">
+        <v>19081.276595744679</v>
+      </c>
+      <c r="BB4" s="12">
+        <v>707.42553191489355</v>
+      </c>
+      <c r="BC4" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BD4" s="11"/>
       <c r="BE4" s="11"/>
       <c r="BF4" s="11"/>
@@ -3682,27 +3706,27 @@
       </c>
       <c r="N5" s="8">
         <f t="shared" si="0"/>
-        <v>322214.40000000002</v>
+        <v>328365.33333333331</v>
       </c>
       <c r="O5" s="8">
         <f t="shared" si="1"/>
-        <v>12729</v>
+        <v>12827.166666666666</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="2"/>
-        <v>270</v>
+        <v>327</v>
       </c>
       <c r="Q5" s="9">
         <f t="shared" si="3"/>
-        <v>17900.8</v>
+        <v>18075.155963302754</v>
       </c>
       <c r="R5" s="9">
         <f t="shared" si="4"/>
-        <v>707.16666666666674</v>
+        <v>706.0825688073395</v>
       </c>
       <c r="S5" s="10">
         <f t="shared" si="5"/>
-        <v>2.7302935978424383</v>
+        <v>2.7169113315353655</v>
       </c>
       <c r="T5" s="11">
         <v>373478</v>
@@ -3794,12 +3818,24 @@
       <c r="AW5" s="13">
         <v>2.65</v>
       </c>
-      <c r="AX5" s="11"/>
-      <c r="AY5" s="11"/>
-      <c r="AZ5" s="11"/>
-      <c r="BA5" s="12"/>
-      <c r="BB5" s="12"/>
-      <c r="BC5" s="13"/>
+      <c r="AX5" s="11">
+        <v>359120</v>
+      </c>
+      <c r="AY5" s="11">
+        <v>13318</v>
+      </c>
+      <c r="AZ5" s="11">
+        <v>57</v>
+      </c>
+      <c r="BA5" s="12">
+        <v>18901.05263157895</v>
+      </c>
+      <c r="BB5" s="12">
+        <v>700.9473684210526</v>
+      </c>
+      <c r="BC5" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BD5" s="11"/>
       <c r="BE5" s="11"/>
       <c r="BF5" s="11"/>
@@ -3877,27 +3913,27 @@
       </c>
       <c r="N6" s="8">
         <f t="shared" si="0"/>
-        <v>230567.8</v>
+        <v>233849.5</v>
       </c>
       <c r="O6" s="8">
         <f t="shared" si="1"/>
-        <v>17745</v>
+        <v>18052.333333333332</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="2"/>
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="Q6" s="9">
         <f t="shared" si="3"/>
-        <v>13405.10465116279</v>
+        <v>13278.520504731863</v>
       </c>
       <c r="R6" s="9">
         <f t="shared" si="4"/>
-        <v>1031.6860465116279</v>
+        <v>1025.0536277602523</v>
       </c>
       <c r="S6" s="10">
         <f t="shared" si="5"/>
-        <v>3.8009092890365421</v>
+        <v>3.8051549970925009</v>
       </c>
       <c r="T6" s="11">
         <v>274253</v>
@@ -3989,12 +4025,24 @@
       <c r="AW6" s="13">
         <v>3.9421789505828828</v>
       </c>
-      <c r="AX6" s="11"/>
-      <c r="AY6" s="11"/>
-      <c r="AZ6" s="11"/>
-      <c r="BA6" s="12"/>
-      <c r="BB6" s="12"/>
-      <c r="BC6" s="13"/>
+      <c r="AX6" s="11">
+        <v>250258</v>
+      </c>
+      <c r="AY6" s="11">
+        <v>19589</v>
+      </c>
+      <c r="AZ6" s="11">
+        <v>59</v>
+      </c>
+      <c r="BA6" s="12">
+        <v>12724.983050847461</v>
+      </c>
+      <c r="BB6" s="12">
+        <v>996.05084745762724</v>
+      </c>
+      <c r="BC6" s="13">
+        <v>3.8263835373722959</v>
+      </c>
       <c r="BD6" s="11"/>
       <c r="BE6" s="11"/>
       <c r="BF6" s="11"/>
@@ -4072,27 +4120,27 @@
       </c>
       <c r="N7" s="8">
         <f t="shared" si="0"/>
-        <v>286948.8</v>
+        <v>307191.83333333331</v>
       </c>
       <c r="O7" s="8">
         <f t="shared" si="1"/>
-        <v>49383.6</v>
+        <v>54621.833333333336</v>
       </c>
       <c r="P7" s="8">
         <f t="shared" si="2"/>
-        <v>261</v>
+        <v>324</v>
       </c>
       <c r="Q7" s="9">
         <f t="shared" si="3"/>
-        <v>16491.310344827587</v>
+        <v>17066.212962962964</v>
       </c>
       <c r="R7" s="9">
         <f t="shared" si="4"/>
-        <v>2838.1379310344828</v>
+        <v>3034.5462962962965</v>
       </c>
       <c r="S7" s="10">
         <f t="shared" si="5"/>
-        <v>5.4356128505172432</v>
+        <v>5.5347062425130273</v>
       </c>
       <c r="T7" s="11">
         <v>355184</v>
@@ -4184,12 +4232,24 @@
       <c r="AW7" s="13">
         <v>5.3280644503668686</v>
       </c>
-      <c r="AX7" s="11"/>
-      <c r="AY7" s="11"/>
-      <c r="AZ7" s="11"/>
-      <c r="BA7" s="12"/>
-      <c r="BB7" s="12"/>
-      <c r="BC7" s="13"/>
+      <c r="AX7" s="11">
+        <v>408407</v>
+      </c>
+      <c r="AY7" s="11">
+        <v>80813</v>
+      </c>
+      <c r="AZ7" s="11">
+        <v>63</v>
+      </c>
+      <c r="BA7" s="12">
+        <v>19447.952380952382</v>
+      </c>
+      <c r="BB7" s="12">
+        <v>3848.238095238095</v>
+      </c>
+      <c r="BC7" s="13">
+        <v>6.0301732024919481</v>
+      </c>
       <c r="BD7" s="11"/>
       <c r="BE7" s="11"/>
       <c r="BF7" s="11"/>
@@ -4267,27 +4327,27 @@
       </c>
       <c r="N8" s="8">
         <f t="shared" si="0"/>
-        <v>279219</v>
+        <v>286387.16666666669</v>
       </c>
       <c r="O8" s="8">
         <f t="shared" si="1"/>
-        <v>35661</v>
+        <v>37217.833333333336</v>
       </c>
       <c r="P8" s="8">
         <f t="shared" si="2"/>
-        <v>270</v>
+        <v>336</v>
       </c>
       <c r="Q8" s="9">
         <f t="shared" si="3"/>
-        <v>15512.166666666668</v>
+        <v>15342.169642857143</v>
       </c>
       <c r="R8" s="9">
         <f t="shared" si="4"/>
-        <v>1981.1666666666667</v>
+        <v>1993.8125</v>
       </c>
       <c r="S8" s="10">
         <f t="shared" si="5"/>
-        <v>4.8707332969122179</v>
+        <v>4.9055327480869622</v>
       </c>
       <c r="T8" s="11">
         <v>330292</v>
@@ -4379,12 +4439,24 @@
       <c r="AW8" s="13">
         <v>4.5979115813308313</v>
       </c>
-      <c r="AX8" s="11"/>
-      <c r="AY8" s="11"/>
-      <c r="AZ8" s="11"/>
-      <c r="BA8" s="12"/>
-      <c r="BB8" s="12"/>
-      <c r="BC8" s="13"/>
+      <c r="AX8" s="11">
+        <v>322228</v>
+      </c>
+      <c r="AY8" s="11">
+        <v>45002</v>
+      </c>
+      <c r="AZ8" s="11">
+        <v>66</v>
+      </c>
+      <c r="BA8" s="12">
+        <v>14646.72727272727</v>
+      </c>
+      <c r="BB8" s="12">
+        <v>2045.545454545455</v>
+      </c>
+      <c r="BC8" s="13">
+        <v>5.0795300039606852</v>
+      </c>
       <c r="BD8" s="11"/>
       <c r="BE8" s="11"/>
       <c r="BF8" s="11"/>
@@ -4462,27 +4534,27 @@
       </c>
       <c r="N9" s="8">
         <f t="shared" si="0"/>
-        <v>260545</v>
+        <v>270394.16666666669</v>
       </c>
       <c r="O9" s="8">
         <f t="shared" si="1"/>
-        <v>9270.6</v>
+        <v>9700.6666666666661</v>
       </c>
       <c r="P9" s="8">
         <f t="shared" si="2"/>
-        <v>229</v>
+        <v>281</v>
       </c>
       <c r="Q9" s="9">
         <f t="shared" si="3"/>
-        <v>17066.266375545852</v>
+        <v>17320.622775800712</v>
       </c>
       <c r="R9" s="9">
         <f t="shared" si="4"/>
-        <v>607.24454148471614</v>
+        <v>621.39501779359432</v>
       </c>
       <c r="S9" s="10">
         <f t="shared" si="5"/>
-        <v>2.5774431336336314</v>
+        <v>2.5895359446946928</v>
       </c>
       <c r="T9" s="11">
         <v>341336</v>
@@ -4574,12 +4646,24 @@
       <c r="AW9" s="13">
         <v>2.3751101303994142</v>
       </c>
-      <c r="AX9" s="11"/>
-      <c r="AY9" s="11"/>
-      <c r="AZ9" s="11"/>
-      <c r="BA9" s="12"/>
-      <c r="BB9" s="12"/>
-      <c r="BC9" s="13"/>
+      <c r="AX9" s="11">
+        <v>319640</v>
+      </c>
+      <c r="AY9" s="11">
+        <v>11851</v>
+      </c>
+      <c r="AZ9" s="11">
+        <v>52</v>
+      </c>
+      <c r="BA9" s="12">
+        <v>18440.76923076923</v>
+      </c>
+      <c r="BB9" s="12">
+        <v>683.71153846153845</v>
+      </c>
+      <c r="BC9" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BD9" s="11"/>
       <c r="BE9" s="11"/>
       <c r="BF9" s="11"/>
@@ -4657,27 +4741,27 @@
       </c>
       <c r="N10" s="8">
         <f t="shared" si="0"/>
-        <v>234901.8</v>
+        <v>243623.33333333334</v>
       </c>
       <c r="O10" s="8">
         <f t="shared" si="1"/>
-        <v>8511.6</v>
+        <v>8572.8333333333339</v>
       </c>
       <c r="P10" s="8">
         <f t="shared" si="2"/>
-        <v>176</v>
+        <v>225</v>
       </c>
       <c r="Q10" s="9">
         <f t="shared" si="3"/>
-        <v>20020.039772727272</v>
+        <v>19489.866666666669</v>
       </c>
       <c r="R10" s="9">
         <f t="shared" si="4"/>
-        <v>725.4204545454545</v>
+        <v>685.8266666666666</v>
       </c>
       <c r="S10" s="10">
         <f t="shared" si="5"/>
-        <v>2.6200833794076646</v>
+        <v>2.5970490365913728</v>
       </c>
       <c r="T10" s="11">
         <v>350996</v>
@@ -4769,12 +4853,24 @@
       <c r="AW10" s="13">
         <v>2.8930106468543428</v>
       </c>
-      <c r="AX10" s="11"/>
-      <c r="AY10" s="11"/>
-      <c r="AZ10" s="11"/>
-      <c r="BA10" s="12"/>
-      <c r="BB10" s="12"/>
-      <c r="BC10" s="13"/>
+      <c r="AX10" s="11">
+        <v>287231</v>
+      </c>
+      <c r="AY10" s="11">
+        <v>8879</v>
+      </c>
+      <c r="AZ10" s="11">
+        <v>49</v>
+      </c>
+      <c r="BA10" s="12">
+        <v>17585.571428571431</v>
+      </c>
+      <c r="BB10" s="12">
+        <v>543.61224489795927</v>
+      </c>
+      <c r="BC10" s="13">
+        <v>2.4818773225099151</v>
+      </c>
       <c r="BD10" s="11"/>
       <c r="BE10" s="11"/>
       <c r="BF10" s="11"/>
@@ -4852,27 +4948,27 @@
       </c>
       <c r="N11" s="8">
         <f t="shared" si="0"/>
-        <v>230035.6</v>
+        <v>243761</v>
       </c>
       <c r="O11" s="8">
         <f t="shared" si="1"/>
-        <v>7732.6</v>
+        <v>8335</v>
       </c>
       <c r="P11" s="8">
         <f t="shared" si="2"/>
-        <v>186</v>
+        <v>244</v>
       </c>
       <c r="Q11" s="9">
         <f t="shared" si="3"/>
-        <v>18551.258064516129</v>
+        <v>17982.368852459018</v>
       </c>
       <c r="R11" s="9">
         <f t="shared" si="4"/>
-        <v>623.59677419354841</v>
+        <v>614.87704918032784</v>
       </c>
       <c r="S11" s="10">
         <f t="shared" si="5"/>
-        <v>2.5846508188687514</v>
+        <v>2.6021411531773544</v>
       </c>
       <c r="T11" s="11">
         <v>395887</v>
@@ -4964,12 +5060,24 @@
       <c r="AW11" s="13">
         <v>2.9433421604430472</v>
       </c>
-      <c r="AX11" s="11"/>
-      <c r="AY11" s="11"/>
-      <c r="AZ11" s="11"/>
-      <c r="BA11" s="12"/>
-      <c r="BB11" s="12"/>
-      <c r="BC11" s="13"/>
+      <c r="AX11" s="11">
+        <v>312388</v>
+      </c>
+      <c r="AY11" s="11">
+        <v>11347</v>
+      </c>
+      <c r="AZ11" s="11">
+        <v>58</v>
+      </c>
+      <c r="BA11" s="12">
+        <v>16158</v>
+      </c>
+      <c r="BB11" s="12">
+        <v>586.91379310344826</v>
+      </c>
+      <c r="BC11" s="13">
+        <v>2.6895928247203709</v>
+      </c>
       <c r="BD11" s="11"/>
       <c r="BE11" s="11"/>
       <c r="BF11" s="11"/>
@@ -5047,27 +5155,27 @@
       </c>
       <c r="N12" s="8">
         <f t="shared" si="0"/>
-        <v>246577.6</v>
+        <v>259383.33333333334</v>
       </c>
       <c r="O12" s="8">
         <f t="shared" si="1"/>
-        <v>19798.599999999999</v>
+        <v>19175.833333333332</v>
       </c>
       <c r="P12" s="8">
         <f t="shared" si="2"/>
-        <v>214</v>
+        <v>264</v>
       </c>
       <c r="Q12" s="9">
         <f t="shared" si="3"/>
-        <v>17283.47663551402</v>
+        <v>17685.227272727272</v>
       </c>
       <c r="R12" s="9">
         <f t="shared" si="4"/>
-        <v>1387.752336448598</v>
+        <v>1307.4431818181818</v>
       </c>
       <c r="S12" s="10">
         <f t="shared" si="5"/>
-        <v>3.8412333329862975</v>
+        <v>3.7116019823397246</v>
       </c>
       <c r="T12" s="11">
         <v>290616</v>
@@ -5159,12 +5267,24 @@
       <c r="AW12" s="13">
         <v>3.5354680074151048</v>
       </c>
-      <c r="AX12" s="11"/>
-      <c r="AY12" s="11"/>
-      <c r="AZ12" s="11"/>
-      <c r="BA12" s="12"/>
-      <c r="BB12" s="12"/>
-      <c r="BC12" s="13"/>
+      <c r="AX12" s="11">
+        <v>323412</v>
+      </c>
+      <c r="AY12" s="11">
+        <v>16062</v>
+      </c>
+      <c r="AZ12" s="11">
+        <v>50</v>
+      </c>
+      <c r="BA12" s="12">
+        <v>19404.72</v>
+      </c>
+      <c r="BB12" s="12">
+        <v>963.72</v>
+      </c>
+      <c r="BC12" s="13">
+        <v>3.063445229106863</v>
+      </c>
       <c r="BD12" s="11"/>
       <c r="BE12" s="11"/>
       <c r="BF12" s="11"/>
@@ -5242,27 +5362,27 @@
       </c>
       <c r="N13" s="8">
         <f t="shared" si="0"/>
-        <v>252367</v>
+        <v>275539.5</v>
       </c>
       <c r="O13" s="8">
         <f t="shared" si="1"/>
-        <v>13199.4</v>
+        <v>13461</v>
       </c>
       <c r="P13" s="8">
         <f t="shared" si="2"/>
-        <v>247</v>
+        <v>306</v>
       </c>
       <c r="Q13" s="9">
         <f t="shared" si="3"/>
-        <v>15325.931174089068</v>
+        <v>16208.205882352941</v>
       </c>
       <c r="R13" s="9">
         <f t="shared" si="4"/>
-        <v>801.58299595141705</v>
+        <v>791.82352941176464</v>
       </c>
       <c r="S13" s="10">
         <f t="shared" si="5"/>
-        <v>3.2261620855134487</v>
+        <v>3.134362269817935</v>
       </c>
       <c r="T13" s="11">
         <v>214482</v>
@@ -5354,12 +5474,24 @@
       <c r="AW13" s="13">
         <v>2.65</v>
       </c>
-      <c r="AX13" s="11"/>
-      <c r="AY13" s="11"/>
-      <c r="AZ13" s="11"/>
-      <c r="BA13" s="12"/>
-      <c r="BB13" s="12"/>
-      <c r="BC13" s="13"/>
+      <c r="AX13" s="11">
+        <v>391402</v>
+      </c>
+      <c r="AY13" s="11">
+        <v>14769</v>
+      </c>
+      <c r="AZ13" s="11">
+        <v>59</v>
+      </c>
+      <c r="BA13" s="12">
+        <v>19901.796610169491</v>
+      </c>
+      <c r="BB13" s="12">
+        <v>750.96610169491521</v>
+      </c>
+      <c r="BC13" s="13">
+        <v>2.6753631913403679</v>
+      </c>
       <c r="BD13" s="11"/>
       <c r="BE13" s="11"/>
       <c r="BF13" s="11"/>
@@ -5437,27 +5569,27 @@
       </c>
       <c r="N14" s="8">
         <f t="shared" si="0"/>
-        <v>286493.59999999998</v>
+        <v>292457.83333333331</v>
       </c>
       <c r="O14" s="8">
         <f t="shared" si="1"/>
-        <v>163365.6</v>
+        <v>162649.83333333334</v>
       </c>
       <c r="P14" s="8">
         <f t="shared" si="2"/>
-        <v>299</v>
+        <v>363</v>
       </c>
       <c r="Q14" s="9">
         <f t="shared" si="3"/>
-        <v>14372.58862876254</v>
+        <v>14502.041322314049</v>
       </c>
       <c r="R14" s="9">
         <f t="shared" si="4"/>
-        <v>8195.5986622073578</v>
+        <v>8065.2809917355371</v>
       </c>
       <c r="S14" s="10">
         <f t="shared" si="5"/>
-        <v>10.2347397582199</v>
+        <v>10.11391237978791</v>
       </c>
       <c r="T14" s="11">
         <v>358878</v>
@@ -5549,12 +5681,24 @@
       <c r="AW14" s="13">
         <v>9.2117338243547167</v>
       </c>
-      <c r="AX14" s="11"/>
-      <c r="AY14" s="11"/>
-      <c r="AZ14" s="11"/>
-      <c r="BA14" s="12"/>
-      <c r="BB14" s="12"/>
-      <c r="BC14" s="13"/>
+      <c r="AX14" s="11">
+        <v>322279</v>
+      </c>
+      <c r="AY14" s="11">
+        <v>159071</v>
+      </c>
+      <c r="AZ14" s="11">
+        <v>64</v>
+      </c>
+      <c r="BA14" s="12">
+        <v>15106.828125</v>
+      </c>
+      <c r="BB14" s="12">
+        <v>7456.453125</v>
+      </c>
+      <c r="BC14" s="13">
+        <v>9.5097754876279517</v>
+      </c>
       <c r="BD14" s="11"/>
       <c r="BE14" s="11"/>
       <c r="BF14" s="11"/>
@@ -5632,27 +5776,27 @@
       </c>
       <c r="N15" s="8">
         <f t="shared" si="0"/>
-        <v>147759.4</v>
+        <v>148229</v>
       </c>
       <c r="O15" s="8">
         <f t="shared" si="1"/>
-        <v>64001</v>
+        <v>63156</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" si="2"/>
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="Q15" s="9">
         <f t="shared" si="3"/>
-        <v>9807.0398230088504</v>
+        <v>9563.1612903225796</v>
       </c>
       <c r="R15" s="9">
         <f t="shared" si="4"/>
-        <v>4247.853982300885</v>
+        <v>4074.5806451612907</v>
       </c>
       <c r="S15" s="10">
         <f t="shared" si="5"/>
-        <v>10.375393518812256</v>
+        <v>10.292684049542915</v>
       </c>
       <c r="T15" s="11">
         <v>184929</v>
@@ -5744,12 +5888,24 @@
       <c r="AW15" s="13">
         <v>10.03155184202414</v>
       </c>
-      <c r="AX15" s="11"/>
-      <c r="AY15" s="11"/>
-      <c r="AZ15" s="11"/>
-      <c r="BA15" s="12"/>
-      <c r="BB15" s="12"/>
-      <c r="BC15" s="13"/>
+      <c r="AX15" s="11">
+        <v>150577</v>
+      </c>
+      <c r="AY15" s="11">
+        <v>58931</v>
+      </c>
+      <c r="AZ15" s="11">
+        <v>53</v>
+      </c>
+      <c r="BA15" s="12">
+        <v>8523.2264150943392</v>
+      </c>
+      <c r="BB15" s="12">
+        <v>3335.716981132075</v>
+      </c>
+      <c r="BC15" s="13">
+        <v>9.8791367031962007</v>
+      </c>
       <c r="BD15" s="11"/>
       <c r="BE15" s="11"/>
       <c r="BF15" s="11"/>
@@ -5827,27 +5983,27 @@
       </c>
       <c r="N16" s="8">
         <f t="shared" si="0"/>
-        <v>97967.2</v>
+        <v>105328.66666666667</v>
       </c>
       <c r="O16" s="8">
         <f t="shared" si="1"/>
-        <v>163480.20000000001</v>
+        <v>173866.5</v>
       </c>
       <c r="P16" s="8">
         <f t="shared" si="2"/>
-        <v>261</v>
+        <v>331</v>
       </c>
       <c r="Q16" s="9">
         <f t="shared" si="3"/>
-        <v>5630.2988505747126</v>
+        <v>5727.8429003021147</v>
       </c>
       <c r="R16" s="9">
         <f t="shared" si="4"/>
-        <v>9395.4137931034475</v>
+        <v>9454.9758308157107</v>
       </c>
       <c r="S16" s="10">
         <f t="shared" si="5"/>
-        <v>20.557025616252552</v>
+        <v>20.521158201702054</v>
       </c>
       <c r="T16" s="11">
         <v>114329</v>
@@ -5939,12 +6095,24 @@
       <c r="AW16" s="13">
         <v>20.516599049326778</v>
       </c>
-      <c r="AX16" s="11"/>
-      <c r="AY16" s="11"/>
-      <c r="AZ16" s="11"/>
-      <c r="BA16" s="12"/>
-      <c r="BB16" s="12"/>
-      <c r="BC16" s="13"/>
+      <c r="AX16" s="11">
+        <v>142136</v>
+      </c>
+      <c r="AY16" s="11">
+        <v>225798</v>
+      </c>
+      <c r="AZ16" s="11">
+        <v>70</v>
+      </c>
+      <c r="BA16" s="12">
+        <v>6091.5428571428574</v>
+      </c>
+      <c r="BB16" s="12">
+        <v>9677.057142857142</v>
+      </c>
+      <c r="BC16" s="13">
+        <v>20.341821128949569</v>
+      </c>
       <c r="BD16" s="11"/>
       <c r="BE16" s="11"/>
       <c r="BF16" s="11"/>
@@ -6022,27 +6190,27 @@
       </c>
       <c r="N17" s="8">
         <f t="shared" si="0"/>
-        <v>271529.8</v>
+        <v>288772</v>
       </c>
       <c r="O17" s="8">
         <f t="shared" si="1"/>
-        <v>4352</v>
+        <v>4447</v>
       </c>
       <c r="P17" s="8">
         <f t="shared" si="2"/>
-        <v>206</v>
+        <v>262</v>
       </c>
       <c r="Q17" s="9">
         <f t="shared" si="3"/>
-        <v>19771.587378640776</v>
+        <v>19839.297709923663</v>
       </c>
       <c r="R17" s="9">
         <f t="shared" si="4"/>
-        <v>316.89320388349512</v>
+        <v>305.51908396946567</v>
       </c>
       <c r="S17" s="10">
         <f t="shared" si="5"/>
-        <v>1.7638920652301995</v>
+        <v>1.7380189531315526</v>
       </c>
       <c r="T17" s="11">
         <v>317353</v>
@@ -6134,12 +6302,24 @@
       <c r="AW17" s="13">
         <v>1.592322366017106</v>
       </c>
-      <c r="AX17" s="11"/>
-      <c r="AY17" s="11"/>
-      <c r="AZ17" s="11"/>
-      <c r="BA17" s="12"/>
-      <c r="BB17" s="12"/>
-      <c r="BC17" s="13"/>
+      <c r="AX17" s="11">
+        <v>374983</v>
+      </c>
+      <c r="AY17" s="11">
+        <v>4922</v>
+      </c>
+      <c r="AZ17" s="11">
+        <v>56</v>
+      </c>
+      <c r="BA17" s="12">
+        <v>20088.375</v>
+      </c>
+      <c r="BB17" s="12">
+        <v>263.67857142857139</v>
+      </c>
+      <c r="BC17" s="13">
+        <v>1.6086533926383191</v>
+      </c>
       <c r="BD17" s="11"/>
       <c r="BE17" s="11"/>
       <c r="BF17" s="11"/>
@@ -6217,27 +6397,27 @@
       </c>
       <c r="N18" s="8">
         <f t="shared" si="0"/>
-        <v>237305</v>
+        <v>258009.83333333334</v>
       </c>
       <c r="O18" s="8">
         <f t="shared" si="1"/>
-        <v>8222</v>
+        <v>8516.5</v>
       </c>
       <c r="P18" s="8">
         <f t="shared" si="2"/>
-        <v>194</v>
+        <v>247</v>
       </c>
       <c r="Q18" s="9">
         <f t="shared" si="3"/>
-        <v>18348.324742268043</v>
+        <v>18802.336032388663</v>
       </c>
       <c r="R18" s="9">
         <f t="shared" si="4"/>
-        <v>635.7216494845361</v>
+        <v>620.63562753036445</v>
       </c>
       <c r="S18" s="10">
         <f t="shared" si="5"/>
-        <v>2.5615726027210437</v>
+        <v>2.5178478934014596</v>
       </c>
       <c r="T18" s="11">
         <v>208128</v>
@@ -6329,12 +6509,24 @@
       <c r="AW18" s="13">
         <v>2.65</v>
       </c>
-      <c r="AX18" s="11"/>
-      <c r="AY18" s="11"/>
-      <c r="AZ18" s="11"/>
-      <c r="BA18" s="12"/>
-      <c r="BB18" s="12"/>
-      <c r="BC18" s="13"/>
+      <c r="AX18" s="11">
+        <v>361534</v>
+      </c>
+      <c r="AY18" s="11">
+        <v>9989</v>
+      </c>
+      <c r="AZ18" s="11">
+        <v>53</v>
+      </c>
+      <c r="BA18" s="12">
+        <v>20464.188679245279</v>
+      </c>
+      <c r="BB18" s="12">
+        <v>565.41509433962256</v>
+      </c>
+      <c r="BC18" s="13">
+        <v>2.299224346803542</v>
+      </c>
       <c r="BD18" s="11"/>
       <c r="BE18" s="11"/>
       <c r="BF18" s="11"/>
@@ -6412,27 +6604,27 @@
       </c>
       <c r="N19" s="8">
         <f t="shared" si="0"/>
-        <v>84456.4</v>
+        <v>86617.80333333333</v>
       </c>
       <c r="O19" s="8">
         <f t="shared" si="1"/>
-        <v>275943.2</v>
+        <v>279160.83333333331</v>
       </c>
       <c r="P19" s="8">
         <f t="shared" si="2"/>
-        <v>273</v>
+        <v>334</v>
       </c>
       <c r="Q19" s="9">
         <f t="shared" si="3"/>
-        <v>4640.461538461539</v>
+        <v>4668.025329341317</v>
       </c>
       <c r="R19" s="9">
         <f t="shared" si="4"/>
-        <v>15161.714285714284</v>
+        <v>15044.595808383234</v>
       </c>
       <c r="S19" s="10">
         <f t="shared" si="5"/>
-        <v>27.755807850366672</v>
+        <v>27.614101112654108</v>
       </c>
       <c r="T19" s="11">
         <v>82762</v>
@@ -6524,12 +6716,24 @@
       <c r="AW19" s="13">
         <v>25.565161127834781</v>
       </c>
-      <c r="AX19" s="11"/>
-      <c r="AY19" s="11"/>
-      <c r="AZ19" s="11"/>
-      <c r="BA19" s="12"/>
-      <c r="BB19" s="12"/>
-      <c r="BC19" s="13"/>
+      <c r="AX19" s="11">
+        <v>97424.82</v>
+      </c>
+      <c r="AY19" s="11">
+        <v>295249</v>
+      </c>
+      <c r="AZ19" s="11">
+        <v>61</v>
+      </c>
+      <c r="BA19" s="12">
+        <v>4791.3845901639343</v>
+      </c>
+      <c r="BB19" s="12">
+        <v>14520.442622950821</v>
+      </c>
+      <c r="BC19" s="13">
+        <v>26.905567424091291</v>
+      </c>
       <c r="BD19" s="11"/>
       <c r="BE19" s="11"/>
       <c r="BF19" s="11"/>
@@ -6607,27 +6811,27 @@
       </c>
       <c r="N20" s="8">
         <f t="shared" si="0"/>
-        <v>126533.6</v>
+        <v>125470.5</v>
       </c>
       <c r="O20" s="8">
         <f t="shared" si="1"/>
-        <v>16575.2</v>
+        <v>16333.5</v>
       </c>
       <c r="P20" s="8">
         <f t="shared" si="2"/>
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="Q20" s="9">
         <f t="shared" si="3"/>
-        <v>11503.054545454546</v>
+        <v>11180.539603960397</v>
       </c>
       <c r="R20" s="9">
         <f t="shared" si="4"/>
-        <v>1506.8363636363636</v>
+        <v>1455.4603960396039</v>
       </c>
       <c r="S20" s="10">
         <f t="shared" si="5"/>
-        <v>5.7263527576821316</v>
+        <v>5.7059387069912075</v>
       </c>
       <c r="T20" s="11">
         <v>173630</v>
@@ -6719,12 +6923,24 @@
       <c r="AW20" s="13">
         <v>5.711785682904992</v>
       </c>
-      <c r="AX20" s="11"/>
-      <c r="AY20" s="11"/>
-      <c r="AZ20" s="11"/>
-      <c r="BA20" s="12"/>
-      <c r="BB20" s="12"/>
-      <c r="BC20" s="13"/>
+      <c r="AX20" s="11">
+        <v>120155</v>
+      </c>
+      <c r="AY20" s="11">
+        <v>15125</v>
+      </c>
+      <c r="AZ20" s="11">
+        <v>37</v>
+      </c>
+      <c r="BA20" s="12">
+        <v>9742.2972972972966</v>
+      </c>
+      <c r="BB20" s="12">
+        <v>1226.351351351351</v>
+      </c>
+      <c r="BC20" s="13">
+        <v>5.603868453536581</v>
+      </c>
       <c r="BD20" s="11"/>
       <c r="BE20" s="11"/>
       <c r="BF20" s="11"/>
@@ -6802,27 +7018,27 @@
       </c>
       <c r="N21" s="8">
         <f t="shared" si="0"/>
-        <v>442830.2</v>
+        <v>450611.66666666669</v>
       </c>
       <c r="O21" s="8">
         <f t="shared" si="1"/>
-        <v>123190</v>
+        <v>125173.33333333333</v>
       </c>
       <c r="P21" s="8">
         <f t="shared" si="2"/>
-        <v>324</v>
+        <v>394</v>
       </c>
       <c r="Q21" s="9">
         <f t="shared" si="3"/>
-        <v>20501.398148148146</v>
+        <v>20586.319796954314</v>
       </c>
       <c r="R21" s="9">
         <f t="shared" si="4"/>
-        <v>5703.2407407407409</v>
+        <v>5718.5786802030452</v>
       </c>
       <c r="S21" s="10">
         <f t="shared" si="5"/>
-        <v>7.0700301366989562</v>
+        <v>7.0817269510923637</v>
       </c>
       <c r="T21" s="11">
         <v>514374</v>
@@ -6914,12 +7130,24 @@
       <c r="AW21" s="13">
         <v>7.3168178031784334</v>
       </c>
-      <c r="AX21" s="11"/>
-      <c r="AY21" s="11"/>
-      <c r="AZ21" s="11"/>
-      <c r="BA21" s="12"/>
-      <c r="BB21" s="12"/>
-      <c r="BC21" s="13"/>
+      <c r="AX21" s="11">
+        <v>489519</v>
+      </c>
+      <c r="AY21" s="11">
+        <v>135090</v>
+      </c>
+      <c r="AZ21" s="11">
+        <v>70</v>
+      </c>
+      <c r="BA21" s="12">
+        <v>20979.38571428572</v>
+      </c>
+      <c r="BB21" s="12">
+        <v>5789.5714285714284</v>
+      </c>
+      <c r="BC21" s="13">
+        <v>7.1402110230593987</v>
+      </c>
       <c r="BD21" s="11"/>
       <c r="BE21" s="11"/>
       <c r="BF21" s="11"/>
@@ -6997,27 +7225,27 @@
       </c>
       <c r="N22" s="8">
         <f t="shared" si="0"/>
-        <v>444940.6</v>
+        <v>450455.5</v>
       </c>
       <c r="O22" s="8">
         <f t="shared" si="1"/>
-        <v>109319.6</v>
+        <v>111704.83333333333</v>
       </c>
       <c r="P22" s="8">
         <f t="shared" si="2"/>
-        <v>317</v>
+        <v>388</v>
       </c>
       <c r="Q22" s="9">
         <f t="shared" si="3"/>
-        <v>21053.971608832806</v>
+        <v>20897.420103092783</v>
       </c>
       <c r="R22" s="9">
         <f t="shared" si="4"/>
-        <v>5172.8517350157726</v>
+        <v>5182.182989690722</v>
       </c>
       <c r="S22" s="10">
         <f t="shared" si="5"/>
-        <v>6.5841163085307643</v>
+        <v>6.6185035299889767</v>
       </c>
       <c r="T22" s="11">
         <v>555592</v>
@@ -7109,12 +7337,24 @@
       <c r="AW22" s="13">
         <v>6.8678560045690933</v>
       </c>
-      <c r="AX22" s="11"/>
-      <c r="AY22" s="11"/>
-      <c r="AZ22" s="11"/>
-      <c r="BA22" s="12"/>
-      <c r="BB22" s="12"/>
-      <c r="BC22" s="13"/>
+      <c r="AX22" s="11">
+        <v>478030</v>
+      </c>
+      <c r="AY22" s="11">
+        <v>123631</v>
+      </c>
+      <c r="AZ22" s="11">
+        <v>71</v>
+      </c>
+      <c r="BA22" s="12">
+        <v>20198.45070422535</v>
+      </c>
+      <c r="BB22" s="12">
+        <v>5223.8450704225352</v>
+      </c>
+      <c r="BC22" s="13">
+        <v>6.7904396372800404</v>
+      </c>
       <c r="BD22" s="11"/>
       <c r="BE22" s="11"/>
       <c r="BF22" s="11"/>
@@ -7192,27 +7432,27 @@
       </c>
       <c r="N23" s="8">
         <f t="shared" si="0"/>
-        <v>295502</v>
+        <v>307512.5</v>
       </c>
       <c r="O23" s="8">
         <f t="shared" si="1"/>
-        <v>11041.4</v>
+        <v>11472.333333333334</v>
       </c>
       <c r="P23" s="8">
         <f t="shared" si="2"/>
-        <v>226</v>
+        <v>287</v>
       </c>
       <c r="Q23" s="9">
         <f t="shared" si="3"/>
-        <v>19612.964601769912</v>
+        <v>19286.498257839721</v>
       </c>
       <c r="R23" s="9">
         <f t="shared" si="4"/>
-        <v>732.83628318584078</v>
+        <v>719.51916376306622</v>
       </c>
       <c r="S23" s="10">
         <f t="shared" si="5"/>
-        <v>2.6583520759805515</v>
+        <v>2.656960063317126</v>
       </c>
       <c r="T23" s="11">
         <v>295520</v>
@@ -7304,12 +7544,24 @@
       <c r="AW23" s="13">
         <v>2.65</v>
       </c>
-      <c r="AX23" s="11"/>
-      <c r="AY23" s="11"/>
-      <c r="AZ23" s="11"/>
-      <c r="BA23" s="12"/>
-      <c r="BB23" s="12"/>
-      <c r="BC23" s="13"/>
+      <c r="AX23" s="11">
+        <v>367565</v>
+      </c>
+      <c r="AY23" s="11">
+        <v>13627</v>
+      </c>
+      <c r="AZ23" s="11">
+        <v>61</v>
+      </c>
+      <c r="BA23" s="12">
+        <v>18076.96721311476</v>
+      </c>
+      <c r="BB23" s="12">
+        <v>670.18032786885249</v>
+      </c>
+      <c r="BC23" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BD23" s="11"/>
       <c r="BE23" s="11"/>
       <c r="BF23" s="11"/>
@@ -7387,27 +7639,27 @@
       </c>
       <c r="N24" s="8">
         <f t="shared" si="0"/>
-        <v>234302</v>
+        <v>219855.83333333334</v>
       </c>
       <c r="O24" s="8">
         <f t="shared" si="1"/>
-        <v>3785.8</v>
+        <v>3524.3333333333335</v>
       </c>
       <c r="P24" s="8">
         <f t="shared" si="2"/>
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="Q24" s="9">
         <f t="shared" si="3"/>
-        <v>19856.101694915254</v>
+        <v>19688.582089552241</v>
       </c>
       <c r="R24" s="9">
         <f t="shared" si="4"/>
-        <v>320.83050847457628</v>
+        <v>315.61194029850748</v>
       </c>
       <c r="S24" s="10">
         <f t="shared" si="5"/>
-        <v>1.7773381096516829</v>
+        <v>1.7690582197839098</v>
       </c>
       <c r="T24" s="11">
         <v>328339</v>
@@ -7499,12 +7751,24 @@
       <c r="AW24" s="13">
         <v>1.676700141974929</v>
       </c>
-      <c r="AX24" s="11"/>
-      <c r="AY24" s="11"/>
-      <c r="AZ24" s="11"/>
-      <c r="BA24" s="12"/>
-      <c r="BB24" s="12"/>
-      <c r="BC24" s="13"/>
+      <c r="AX24" s="11">
+        <v>147625</v>
+      </c>
+      <c r="AY24" s="11">
+        <v>2217</v>
+      </c>
+      <c r="AZ24" s="11">
+        <v>24</v>
+      </c>
+      <c r="BA24" s="12">
+        <v>18453.125</v>
+      </c>
+      <c r="BB24" s="12">
+        <v>277.125</v>
+      </c>
+      <c r="BC24" s="13">
+        <v>1.7276587704450439</v>
+      </c>
       <c r="BD24" s="11"/>
       <c r="BE24" s="11"/>
       <c r="BF24" s="11"/>
@@ -7582,27 +7846,27 @@
       </c>
       <c r="N25" s="8">
         <f t="shared" si="0"/>
-        <v>256307.4</v>
+        <v>260788.83333333334</v>
       </c>
       <c r="O25" s="8">
         <f t="shared" si="1"/>
-        <v>17360.8</v>
+        <v>18001.333333333332</v>
       </c>
       <c r="P25" s="8">
         <f t="shared" si="2"/>
-        <v>253</v>
+        <v>314</v>
       </c>
       <c r="Q25" s="9">
         <f t="shared" si="3"/>
-        <v>15196.090909090908</v>
+        <v>14949.678343949043</v>
       </c>
       <c r="R25" s="9">
         <f t="shared" si="4"/>
-        <v>1029.296442687747</v>
+        <v>1031.9235668789809</v>
       </c>
       <c r="S25" s="10">
         <f t="shared" si="5"/>
-        <v>3.6234123470483239</v>
+        <v>3.6601529019213435</v>
       </c>
       <c r="T25" s="11">
         <v>254251</v>
@@ -7694,12 +7958,24 @@
       <c r="AW25" s="13">
         <v>3.517445010922406</v>
       </c>
-      <c r="AX25" s="11"/>
-      <c r="AY25" s="11"/>
-      <c r="AZ25" s="11"/>
-      <c r="BA25" s="12"/>
-      <c r="BB25" s="12"/>
-      <c r="BC25" s="13"/>
+      <c r="AX25" s="11">
+        <v>283196</v>
+      </c>
+      <c r="AY25" s="11">
+        <v>21204</v>
+      </c>
+      <c r="AZ25" s="11">
+        <v>61</v>
+      </c>
+      <c r="BA25" s="12">
+        <v>13927.672131147539</v>
+      </c>
+      <c r="BB25" s="12">
+        <v>1042.8196721311469</v>
+      </c>
+      <c r="BC25" s="13">
+        <v>3.8438556762864411</v>
+      </c>
       <c r="BD25" s="11"/>
       <c r="BE25" s="11"/>
       <c r="BF25" s="11"/>
@@ -7777,27 +8053,27 @@
       </c>
       <c r="N26" s="8">
         <f t="shared" ref="N26:N52" si="6">IFERROR(AVERAGE(T26,Z26,AF26,AL26,AR26,AX26,BD26,BJ26,BP26,BV26,CB26,CH26)," ")</f>
-        <v>298980.59999999998</v>
+        <v>308210.16666666669</v>
       </c>
       <c r="O26" s="8">
         <f t="shared" ref="O26:O52" si="7">IFERROR(AVERAGE(U26,AA26,AG26,AM26,AS26,AY26,BE26,BK26,BQ26,BW26,CC26,CI26)," ")</f>
-        <v>21874.2</v>
+        <v>23270.5</v>
       </c>
       <c r="P26" s="8">
         <f t="shared" ref="P26:P52" si="8">IFERROR(SUM(V26,AB26,AH26,AN26,AT26,AZ26,BF26,BL26,BR26,BX26,CD26,CJ26)," ")</f>
-        <v>274</v>
+        <v>336</v>
       </c>
       <c r="Q26" s="9">
         <f t="shared" ref="Q26:Q52" si="9">IFERROR(SUM(T26,Z26,AF26,AL26,AR26,AX26,BD26,BJ26,BP26,BV26,CB26,CH26)/P26*3," ")</f>
-        <v>16367.551094890512</v>
+        <v>16511.258928571428</v>
       </c>
       <c r="R26" s="9">
         <f t="shared" ref="R26:R52" si="10">IFERROR(SUM(U26,AA26,AG26,AM26,AS26,AY26,BE26,BK26,BQ26,BW26,CC26,CI26)/P26*3," ")</f>
-        <v>1197.492700729927</v>
+        <v>1246.6339285714284</v>
       </c>
       <c r="S26" s="10">
         <f t="shared" ref="S26:S52" si="11">IFERROR(AVERAGE(Y26,AE26,AK26,AQ26,AW26,BC26,BI26,BO26,BU26,CA26,CG26,CM26)," ")</f>
-        <v>3.7544996965308322</v>
+        <v>3.8155164885547275</v>
       </c>
       <c r="T26" s="11">
         <v>319242</v>
@@ -7889,12 +8165,24 @@
       <c r="AW26" s="13">
         <v>3.5385806857286748</v>
       </c>
-      <c r="AX26" s="11"/>
-      <c r="AY26" s="11"/>
-      <c r="AZ26" s="11"/>
-      <c r="BA26" s="12"/>
-      <c r="BB26" s="12"/>
-      <c r="BC26" s="13"/>
+      <c r="AX26" s="11">
+        <v>354358</v>
+      </c>
+      <c r="AY26" s="11">
+        <v>30252</v>
+      </c>
+      <c r="AZ26" s="11">
+        <v>62</v>
+      </c>
+      <c r="BA26" s="12">
+        <v>17146.354838709671</v>
+      </c>
+      <c r="BB26" s="12">
+        <v>1463.8064516129029</v>
+      </c>
+      <c r="BC26" s="13">
+        <v>4.1206004486742041</v>
+      </c>
       <c r="BD26" s="11"/>
       <c r="BE26" s="11"/>
       <c r="BF26" s="11"/>
@@ -8131,27 +8419,27 @@
       </c>
       <c r="N28" s="8">
         <f t="shared" si="6"/>
-        <v>282603.8</v>
+        <v>279018.16666666669</v>
       </c>
       <c r="O28" s="8">
         <f t="shared" si="7"/>
-        <v>80446.399999999994</v>
+        <v>79197.833333333328</v>
       </c>
       <c r="P28" s="8">
         <f t="shared" si="8"/>
-        <v>309</v>
+        <v>370</v>
       </c>
       <c r="Q28" s="9">
         <f t="shared" si="9"/>
-        <v>13718.631067961165</v>
+        <v>13573.856756756757</v>
       </c>
       <c r="R28" s="9">
         <f t="shared" si="10"/>
-        <v>3905.1650485436894</v>
+        <v>3852.8675675675677</v>
       </c>
       <c r="S28" s="10">
         <f t="shared" si="11"/>
-        <v>7.3993950340047663</v>
+        <v>7.3866362727218968</v>
       </c>
       <c r="T28" s="11">
         <v>362826</v>
@@ -8243,12 +8531,24 @@
       <c r="AW28" s="13">
         <v>7.888017516936535</v>
       </c>
-      <c r="AX28" s="11"/>
-      <c r="AY28" s="11"/>
-      <c r="AZ28" s="11"/>
-      <c r="BA28" s="12"/>
-      <c r="BB28" s="12"/>
-      <c r="BC28" s="13"/>
+      <c r="AX28" s="11">
+        <v>261090</v>
+      </c>
+      <c r="AY28" s="11">
+        <v>72955</v>
+      </c>
+      <c r="AZ28" s="11">
+        <v>61</v>
+      </c>
+      <c r="BA28" s="12">
+        <v>12840.49180327869</v>
+      </c>
+      <c r="BB28" s="12">
+        <v>3587.9508196721308</v>
+      </c>
+      <c r="BC28" s="13">
+        <v>7.3228424663075469</v>
+      </c>
       <c r="BD28" s="11"/>
       <c r="BE28" s="11"/>
       <c r="BF28" s="11"/>
@@ -8326,27 +8626,27 @@
       </c>
       <c r="N29" s="8">
         <f t="shared" si="6"/>
-        <v>63048.25</v>
+        <v>64769.8</v>
       </c>
       <c r="O29" s="8">
         <f t="shared" si="7"/>
-        <v>37928.5</v>
+        <v>34780.800000000003</v>
       </c>
       <c r="P29" s="8">
         <f t="shared" si="8"/>
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="Q29" s="9">
         <f t="shared" si="9"/>
-        <v>12402.934426229509</v>
+        <v>13879.242857142857</v>
       </c>
       <c r="R29" s="9">
         <f t="shared" si="10"/>
-        <v>7461.3442622950824</v>
+        <v>7453.028571428571</v>
       </c>
       <c r="S29" s="10">
         <f t="shared" si="11"/>
-        <v>12.26560940419459</v>
+        <v>11.441056672138732</v>
       </c>
       <c r="T29" s="11">
         <v>83538</v>
@@ -8426,12 +8726,24 @@
       <c r="AU29" s="12"/>
       <c r="AV29" s="12"/>
       <c r="AW29" s="13"/>
-      <c r="AX29" s="11"/>
-      <c r="AY29" s="11"/>
-      <c r="AZ29" s="11"/>
-      <c r="BA29" s="12"/>
-      <c r="BB29" s="12"/>
-      <c r="BC29" s="13"/>
+      <c r="AX29" s="11">
+        <v>71656</v>
+      </c>
+      <c r="AY29" s="11">
+        <v>22190</v>
+      </c>
+      <c r="AZ29" s="11">
+        <v>9</v>
+      </c>
+      <c r="BA29" s="12">
+        <v>23885.333333333328</v>
+      </c>
+      <c r="BB29" s="12">
+        <v>7396.666666666667</v>
+      </c>
+      <c r="BC29" s="13">
+        <v>8.1428457439153004</v>
+      </c>
       <c r="BD29" s="11"/>
       <c r="BE29" s="11"/>
       <c r="BF29" s="11"/>
@@ -8509,27 +8821,27 @@
       </c>
       <c r="N30" s="8">
         <f t="shared" si="6"/>
-        <v>161468.79999999999</v>
+        <v>161825</v>
       </c>
       <c r="O30" s="8">
         <f t="shared" si="7"/>
-        <v>123072.2</v>
+        <v>126883.83333333333</v>
       </c>
       <c r="P30" s="8">
         <f t="shared" si="8"/>
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="Q30" s="9">
         <f t="shared" si="9"/>
-        <v>10716.955752212391</v>
+        <v>10366.014234875445</v>
       </c>
       <c r="R30" s="9">
         <f t="shared" si="10"/>
-        <v>8168.5088495575219</v>
+        <v>8127.790035587188</v>
       </c>
       <c r="S30" s="10">
         <f t="shared" si="11"/>
-        <v>13.744057091487928</v>
+        <v>13.977577357057838</v>
       </c>
       <c r="T30" s="11">
         <v>169875</v>
@@ -8621,12 +8933,24 @@
       <c r="AW30" s="13">
         <v>13.49421474453132</v>
       </c>
-      <c r="AX30" s="11"/>
-      <c r="AY30" s="11"/>
-      <c r="AZ30" s="11"/>
-      <c r="BA30" s="12"/>
-      <c r="BB30" s="12"/>
-      <c r="BC30" s="13"/>
+      <c r="AX30" s="11">
+        <v>163606</v>
+      </c>
+      <c r="AY30" s="11">
+        <v>145942</v>
+      </c>
+      <c r="AZ30" s="11">
+        <v>55</v>
+      </c>
+      <c r="BA30" s="12">
+        <v>8923.9636363636364</v>
+      </c>
+      <c r="BB30" s="12">
+        <v>7960.4727272727268</v>
+      </c>
+      <c r="BC30" s="13">
+        <v>15.14517868490738</v>
+      </c>
       <c r="BD30" s="11"/>
       <c r="BE30" s="11"/>
       <c r="BF30" s="11"/>
@@ -8704,27 +9028,27 @@
       </c>
       <c r="N31" s="8">
         <f t="shared" si="6"/>
-        <v>91060.5</v>
+        <v>93861</v>
       </c>
       <c r="O31" s="8">
         <f t="shared" si="7"/>
-        <v>3317.25</v>
+        <v>3379.6</v>
       </c>
       <c r="P31" s="8">
         <f t="shared" si="8"/>
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="Q31" s="9">
         <f t="shared" si="9"/>
-        <v>12706.116279069767</v>
+        <v>12570.669642857145</v>
       </c>
       <c r="R31" s="9">
         <f t="shared" si="10"/>
-        <v>462.87209302325579</v>
+        <v>452.625</v>
       </c>
       <c r="S31" s="10">
         <f t="shared" si="11"/>
-        <v>2.6642849188631521</v>
+        <v>2.6550958073826409</v>
       </c>
       <c r="T31" s="11"/>
       <c r="U31" s="11"/>
@@ -8804,12 +9128,24 @@
       <c r="AW31" s="13">
         <v>2.6558529003847262</v>
       </c>
-      <c r="AX31" s="11"/>
-      <c r="AY31" s="11"/>
-      <c r="AZ31" s="11"/>
-      <c r="BA31" s="12"/>
-      <c r="BB31" s="12"/>
-      <c r="BC31" s="13"/>
+      <c r="AX31" s="11">
+        <v>105063</v>
+      </c>
+      <c r="AY31" s="11">
+        <v>3629</v>
+      </c>
+      <c r="AZ31" s="11">
+        <v>26</v>
+      </c>
+      <c r="BA31" s="12">
+        <v>12122.653846153849</v>
+      </c>
+      <c r="BB31" s="12">
+        <v>418.73076923076923</v>
+      </c>
+      <c r="BC31" s="13">
+        <v>2.6183393614605972</v>
+      </c>
       <c r="BD31" s="11"/>
       <c r="BE31" s="11"/>
       <c r="BF31" s="11"/>
@@ -8887,23 +9223,23 @@
       </c>
       <c r="N32" s="8">
         <f t="shared" si="6"/>
-        <v>197428</v>
+        <v>196190</v>
       </c>
       <c r="O32" s="8">
         <f t="shared" si="7"/>
-        <v>70077.2</v>
+        <v>69639.333333333328</v>
       </c>
       <c r="P32" s="8">
         <f t="shared" si="8"/>
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="Q32" s="9">
         <f t="shared" si="9"/>
-        <v>17523.195266272189</v>
+        <v>17226.439024390245</v>
       </c>
       <c r="R32" s="9">
         <f t="shared" si="10"/>
-        <v>6219.8698224852069</v>
+        <v>6114.6731707317076</v>
       </c>
       <c r="S32" s="10">
         <f t="shared" si="11"/>
@@ -8999,12 +9335,24 @@
       <c r="AW32" s="13">
         <v>10</v>
       </c>
-      <c r="AX32" s="11"/>
-      <c r="AY32" s="11"/>
-      <c r="AZ32" s="11"/>
-      <c r="BA32" s="12"/>
-      <c r="BB32" s="12"/>
-      <c r="BC32" s="13"/>
+      <c r="AX32" s="11">
+        <v>190000</v>
+      </c>
+      <c r="AY32" s="11">
+        <v>67450</v>
+      </c>
+      <c r="AZ32" s="11">
+        <v>36</v>
+      </c>
+      <c r="BA32" s="12">
+        <v>15833.33333333333</v>
+      </c>
+      <c r="BB32" s="12">
+        <v>5620.833333333333</v>
+      </c>
+      <c r="BC32" s="13">
+        <v>10</v>
+      </c>
       <c r="BD32" s="11"/>
       <c r="BE32" s="11"/>
       <c r="BF32" s="11"/>
@@ -9082,27 +9430,27 @@
       </c>
       <c r="N33" s="8">
         <f t="shared" si="6"/>
-        <v>89187.333333333328</v>
+        <v>66890.75</v>
       </c>
       <c r="O33" s="8">
         <f t="shared" si="7"/>
-        <v>37646</v>
+        <v>28234.5</v>
       </c>
       <c r="P33" s="8">
         <f t="shared" si="8"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q33" s="9">
         <f t="shared" si="9"/>
-        <v>15145.018867924529</v>
+        <v>14864.611111111111</v>
       </c>
       <c r="R33" s="9">
         <f t="shared" si="10"/>
-        <v>6392.7169811320746</v>
+        <v>6274.333333333333</v>
       </c>
       <c r="S33" s="10">
         <f t="shared" si="11"/>
-        <v>9.8049361731698994</v>
+        <v>7.7737021298774245</v>
       </c>
       <c r="T33" s="11">
         <v>31296</v>
@@ -9170,12 +9518,24 @@
       <c r="AU33" s="12"/>
       <c r="AV33" s="12"/>
       <c r="AW33" s="13"/>
-      <c r="AX33" s="11"/>
-      <c r="AY33" s="11"/>
-      <c r="AZ33" s="11"/>
-      <c r="BA33" s="12"/>
-      <c r="BB33" s="12"/>
-      <c r="BC33" s="13"/>
+      <c r="AX33" s="11">
+        <v>1</v>
+      </c>
+      <c r="AY33" s="11">
+        <v>0</v>
+      </c>
+      <c r="AZ33" s="11">
+        <v>1</v>
+      </c>
+      <c r="BA33" s="12">
+        <v>3</v>
+      </c>
+      <c r="BB33" s="12">
+        <v>0</v>
+      </c>
+      <c r="BC33" s="13">
+        <v>1.68</v>
+      </c>
       <c r="BD33" s="11"/>
       <c r="BE33" s="11"/>
       <c r="BF33" s="11"/>
@@ -9253,27 +9613,27 @@
       </c>
       <c r="N34" s="8">
         <f t="shared" si="6"/>
-        <v>20948.400000000001</v>
+        <v>18977.5</v>
       </c>
       <c r="O34" s="8">
         <f t="shared" si="7"/>
-        <v>92985.2</v>
+        <v>83578</v>
       </c>
       <c r="P34" s="8">
         <f t="shared" si="8"/>
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="Q34" s="9">
         <f t="shared" si="9"/>
-        <v>3611.7931034482758</v>
+        <v>3558.28125</v>
       </c>
       <c r="R34" s="9">
         <f t="shared" si="10"/>
-        <v>16031.931034482759</v>
+        <v>15670.875</v>
       </c>
       <c r="S34" s="10">
         <f t="shared" si="11"/>
-        <v>35.763325988811125</v>
+        <v>35.141098531069908</v>
       </c>
       <c r="T34" s="11">
         <v>44447</v>
@@ -9365,12 +9725,24 @@
       <c r="AW34" s="13">
         <v>31.41235650525098</v>
       </c>
-      <c r="AX34" s="11"/>
-      <c r="AY34" s="11"/>
-      <c r="AZ34" s="11"/>
-      <c r="BA34" s="12"/>
-      <c r="BB34" s="12"/>
-      <c r="BC34" s="13"/>
+      <c r="AX34" s="11">
+        <v>9123</v>
+      </c>
+      <c r="AY34" s="11">
+        <v>36542</v>
+      </c>
+      <c r="AZ34" s="11">
+        <v>9</v>
+      </c>
+      <c r="BA34" s="12">
+        <v>3041</v>
+      </c>
+      <c r="BB34" s="12">
+        <v>12180.66666666667</v>
+      </c>
+      <c r="BC34" s="13">
+        <v>32.029961242363832</v>
+      </c>
       <c r="BD34" s="11"/>
       <c r="BE34" s="11"/>
       <c r="BF34" s="11"/>
@@ -9448,27 +9820,27 @@
       </c>
       <c r="N35" s="8">
         <f t="shared" si="6"/>
-        <v>29845.5</v>
+        <v>49057.333333333336</v>
       </c>
       <c r="O35" s="8">
         <f t="shared" si="7"/>
-        <v>1717</v>
+        <v>2515.6666666666665</v>
       </c>
       <c r="P35" s="8">
         <f t="shared" si="8"/>
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="Q35" s="9">
         <f t="shared" si="9"/>
-        <v>7785.782608695652</v>
+        <v>9598.173913043478</v>
       </c>
       <c r="R35" s="9">
         <f t="shared" si="10"/>
-        <v>447.91304347826087</v>
+        <v>492.195652173913</v>
       </c>
       <c r="S35" s="10">
         <f t="shared" si="11"/>
-        <v>3.3623704450056979</v>
+        <v>3.2582329753167181</v>
       </c>
       <c r="T35" s="11">
         <v>25363</v>
@@ -9524,12 +9896,24 @@
       <c r="AW35" s="13">
         <v>3.6209339486131289</v>
       </c>
-      <c r="AX35" s="11"/>
-      <c r="AY35" s="11"/>
-      <c r="AZ35" s="11"/>
-      <c r="BA35" s="12"/>
-      <c r="BB35" s="12"/>
-      <c r="BC35" s="13"/>
+      <c r="AX35" s="11">
+        <v>87481</v>
+      </c>
+      <c r="AY35" s="11">
+        <v>4113</v>
+      </c>
+      <c r="AZ35" s="11">
+        <v>23</v>
+      </c>
+      <c r="BA35" s="12">
+        <v>11410.5652173913</v>
+      </c>
+      <c r="BB35" s="12">
+        <v>536.47826086956525</v>
+      </c>
+      <c r="BC35" s="13">
+        <v>3.0499580359387588</v>
+      </c>
       <c r="BD35" s="11"/>
       <c r="BE35" s="11"/>
       <c r="BF35" s="11"/>
@@ -9607,27 +9991,27 @@
       </c>
       <c r="N36" s="8">
         <f t="shared" si="6"/>
-        <v>41199.800000000003</v>
+        <v>49994</v>
       </c>
       <c r="O36" s="8">
         <f t="shared" si="7"/>
-        <v>3619.6</v>
+        <v>3872.8333333333335</v>
       </c>
       <c r="P36" s="8">
         <f t="shared" si="8"/>
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="Q36" s="9">
         <f t="shared" si="9"/>
-        <v>12117.588235294117</v>
+        <v>11537.076923076922</v>
       </c>
       <c r="R36" s="9">
         <f t="shared" si="10"/>
-        <v>1064.5882352941176</v>
+        <v>893.73076923076928</v>
       </c>
       <c r="S36" s="10">
         <f t="shared" si="11"/>
-        <v>9.5561888418230687</v>
+        <v>8.520570861114706</v>
       </c>
       <c r="T36" s="11">
         <v>68082</v>
@@ -9719,12 +10103,24 @@
       <c r="AW36" s="13">
         <v>3.9373166452747959</v>
       </c>
-      <c r="AX36" s="11"/>
-      <c r="AY36" s="11"/>
-      <c r="AZ36" s="11"/>
-      <c r="BA36" s="12"/>
-      <c r="BB36" s="12"/>
-      <c r="BC36" s="13"/>
+      <c r="AX36" s="11">
+        <v>93965</v>
+      </c>
+      <c r="AY36" s="11">
+        <v>5139</v>
+      </c>
+      <c r="AZ36" s="11">
+        <v>27</v>
+      </c>
+      <c r="BA36" s="12">
+        <v>10440.555555555549</v>
+      </c>
+      <c r="BB36" s="12">
+        <v>571</v>
+      </c>
+      <c r="BC36" s="13">
+        <v>3.3424809575728851</v>
+      </c>
       <c r="BD36" s="11"/>
       <c r="BE36" s="11"/>
       <c r="BF36" s="11"/>
@@ -9802,27 +10198,27 @@
       </c>
       <c r="N37" s="8">
         <f t="shared" si="6"/>
-        <v>67434.2</v>
+        <v>70926.166666666672</v>
       </c>
       <c r="O37" s="8">
         <f t="shared" si="7"/>
-        <v>5528.6</v>
+        <v>5475.666666666667</v>
       </c>
       <c r="P37" s="8">
         <f t="shared" si="8"/>
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="Q37" s="9">
         <f t="shared" si="9"/>
-        <v>10217.30303030303</v>
+        <v>10132.309523809523</v>
       </c>
       <c r="R37" s="9">
         <f t="shared" si="10"/>
-        <v>837.66666666666674</v>
+        <v>782.23809523809518</v>
       </c>
       <c r="S37" s="10">
         <f t="shared" si="11"/>
-        <v>3.5156997310536533</v>
+        <v>3.5022134901769935</v>
       </c>
       <c r="T37" s="11">
         <v>60720</v>
@@ -9914,12 +10310,24 @@
       <c r="AW37" s="13">
         <v>3.2090442254455911</v>
       </c>
-      <c r="AX37" s="11"/>
-      <c r="AY37" s="11"/>
-      <c r="AZ37" s="11"/>
-      <c r="BA37" s="12"/>
-      <c r="BB37" s="12"/>
-      <c r="BC37" s="13"/>
+      <c r="AX37" s="11">
+        <v>88386</v>
+      </c>
+      <c r="AY37" s="11">
+        <v>5211</v>
+      </c>
+      <c r="AZ37" s="11">
+        <v>27</v>
+      </c>
+      <c r="BA37" s="12">
+        <v>9820.6666666666679</v>
+      </c>
+      <c r="BB37" s="12">
+        <v>579</v>
+      </c>
+      <c r="BC37" s="13">
+        <v>3.434782285793696</v>
+      </c>
       <c r="BD37" s="11"/>
       <c r="BE37" s="11"/>
       <c r="BF37" s="11"/>
@@ -10279,27 +10687,27 @@
       </c>
       <c r="N40" s="8">
         <f t="shared" si="6"/>
-        <v>62438.666666666664</v>
+        <v>54688.5</v>
       </c>
       <c r="O40" s="8">
         <f t="shared" si="7"/>
-        <v>8699.3333333333339</v>
+        <v>8422</v>
       </c>
       <c r="P40" s="8">
         <f t="shared" si="8"/>
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="Q40" s="9">
         <f t="shared" si="9"/>
-        <v>7593.8918918918926</v>
+        <v>6981.510638297872</v>
       </c>
       <c r="R40" s="9">
         <f t="shared" si="10"/>
-        <v>1058.0270270270271</v>
+        <v>1075.1489361702129</v>
       </c>
       <c r="S40" s="10">
         <f t="shared" si="11"/>
-        <v>4.8936850319471823</v>
+        <v>5.3953658687188852</v>
       </c>
       <c r="T40" s="11">
         <v>111399</v>
@@ -10367,12 +10775,24 @@
       <c r="AU40" s="12"/>
       <c r="AV40" s="12"/>
       <c r="AW40" s="13"/>
-      <c r="AX40" s="11"/>
-      <c r="AY40" s="11"/>
-      <c r="AZ40" s="11"/>
-      <c r="BA40" s="12"/>
-      <c r="BB40" s="12"/>
-      <c r="BC40" s="13"/>
+      <c r="AX40" s="11">
+        <v>31438</v>
+      </c>
+      <c r="AY40" s="11">
+        <v>7590</v>
+      </c>
+      <c r="AZ40" s="11">
+        <v>20</v>
+      </c>
+      <c r="BA40" s="12">
+        <v>4715.7000000000007</v>
+      </c>
+      <c r="BB40" s="12">
+        <v>1138.5</v>
+      </c>
+      <c r="BC40" s="13">
+        <v>6.9004083790339958</v>
+      </c>
       <c r="BD40" s="11"/>
       <c r="BE40" s="11"/>
       <c r="BF40" s="11"/>
@@ -10585,27 +11005,27 @@
       </c>
       <c r="N42" s="8">
         <f t="shared" si="6"/>
-        <v>16613</v>
+        <v>18845.833333333332</v>
       </c>
       <c r="O42" s="8">
         <f t="shared" si="7"/>
-        <v>40794</v>
+        <v>46034</v>
       </c>
       <c r="P42" s="8">
         <f t="shared" si="8"/>
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="Q42" s="9">
         <f t="shared" si="9"/>
-        <v>4153.25</v>
+        <v>4136.8902439024387</v>
       </c>
       <c r="R42" s="9">
         <f t="shared" si="10"/>
-        <v>10198.5</v>
+        <v>10105.024390243903</v>
       </c>
       <c r="S42" s="10">
         <f t="shared" si="11"/>
-        <v>22.610371211861718</v>
+        <v>22.544267029174573</v>
       </c>
       <c r="T42" s="11">
         <v>16200</v>
@@ -10697,12 +11117,24 @@
       <c r="AW42" s="13">
         <v>21.508789871002691</v>
       </c>
-      <c r="AX42" s="11"/>
-      <c r="AY42" s="11"/>
-      <c r="AZ42" s="11"/>
-      <c r="BA42" s="12"/>
-      <c r="BB42" s="12"/>
-      <c r="BC42" s="13"/>
+      <c r="AX42" s="11">
+        <v>30010</v>
+      </c>
+      <c r="AY42" s="11">
+        <v>72234</v>
+      </c>
+      <c r="AZ42" s="11">
+        <v>22</v>
+      </c>
+      <c r="BA42" s="12">
+        <v>4092.272727272727</v>
+      </c>
+      <c r="BB42" s="12">
+        <v>9850.0909090909099</v>
+      </c>
+      <c r="BC42" s="13">
+        <v>22.213746115738829</v>
+      </c>
       <c r="BD42" s="11"/>
       <c r="BE42" s="11"/>
       <c r="BF42" s="11"/>
@@ -10780,27 +11212,27 @@
       </c>
       <c r="N43" s="8">
         <f t="shared" si="6"/>
-        <v>345869.6</v>
+        <v>364652</v>
       </c>
       <c r="O43" s="8">
         <f t="shared" si="7"/>
-        <v>13120.8</v>
+        <v>14022.333333333334</v>
       </c>
       <c r="P43" s="8">
         <f t="shared" si="8"/>
-        <v>231</v>
+        <v>298</v>
       </c>
       <c r="Q43" s="9">
         <f t="shared" si="9"/>
-        <v>22459.064935064933</v>
+        <v>22025.959731543626</v>
       </c>
       <c r="R43" s="9">
         <f t="shared" si="10"/>
-        <v>852</v>
+        <v>846.98657718120808</v>
       </c>
       <c r="S43" s="10">
         <f t="shared" si="11"/>
-        <v>2.6845918694457991</v>
+        <v>2.6992076139422978</v>
       </c>
       <c r="T43" s="11">
         <v>178860</v>
@@ -10892,12 +11324,24 @@
       <c r="AW43" s="13">
         <v>2.795653606112579</v>
       </c>
-      <c r="AX43" s="11"/>
-      <c r="AY43" s="11"/>
-      <c r="AZ43" s="11"/>
-      <c r="BA43" s="12"/>
-      <c r="BB43" s="12"/>
-      <c r="BC43" s="13"/>
+      <c r="AX43" s="11">
+        <v>458564</v>
+      </c>
+      <c r="AY43" s="11">
+        <v>18530</v>
+      </c>
+      <c r="AZ43" s="11">
+        <v>67</v>
+      </c>
+      <c r="BA43" s="12">
+        <v>20532.716417910451</v>
+      </c>
+      <c r="BB43" s="12">
+        <v>829.70149253731336</v>
+      </c>
+      <c r="BC43" s="13">
+        <v>2.7722863364247941</v>
+      </c>
       <c r="BD43" s="11"/>
       <c r="BE43" s="11"/>
       <c r="BF43" s="11"/>
@@ -10975,27 +11419,27 @@
       </c>
       <c r="N44" s="8">
         <f t="shared" si="6"/>
-        <v>342378.4</v>
+        <v>354171.83333333331</v>
       </c>
       <c r="O44" s="8">
         <f t="shared" si="7"/>
-        <v>13040.6</v>
+        <v>13624.833333333334</v>
       </c>
       <c r="P44" s="8">
         <f t="shared" si="8"/>
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="Q44" s="9">
         <f t="shared" si="9"/>
-        <v>22724.230088495577</v>
+        <v>22606.712765957447</v>
       </c>
       <c r="R44" s="9">
         <f t="shared" si="10"/>
-        <v>865.52654867256638</v>
+        <v>869.67021276595733</v>
       </c>
       <c r="S44" s="10">
         <f t="shared" si="11"/>
-        <v>2.6815542739087879</v>
+        <v>2.6964304612228123</v>
       </c>
       <c r="T44" s="11">
         <v>184368</v>
@@ -11087,12 +11531,24 @@
       <c r="AW44" s="13">
         <v>2.6796130585711908</v>
       </c>
-      <c r="AX44" s="11"/>
-      <c r="AY44" s="11"/>
-      <c r="AZ44" s="11"/>
-      <c r="BA44" s="12"/>
-      <c r="BB44" s="12"/>
-      <c r="BC44" s="13"/>
+      <c r="AX44" s="11">
+        <v>413139</v>
+      </c>
+      <c r="AY44" s="11">
+        <v>16546</v>
+      </c>
+      <c r="AZ44" s="11">
+        <v>56</v>
+      </c>
+      <c r="BA44" s="12">
+        <v>22132.446428571431</v>
+      </c>
+      <c r="BB44" s="12">
+        <v>886.39285714285711</v>
+      </c>
+      <c r="BC44" s="13">
+        <v>2.7708113977929338</v>
+      </c>
       <c r="BD44" s="11"/>
       <c r="BE44" s="11"/>
       <c r="BF44" s="11"/>
@@ -11170,27 +11626,27 @@
       </c>
       <c r="N45" s="8">
         <f t="shared" si="6"/>
-        <v>260191.8</v>
+        <v>258210.16666666666</v>
       </c>
       <c r="O45" s="8">
         <f t="shared" si="7"/>
-        <v>5025.6000000000004</v>
+        <v>5145.833333333333</v>
       </c>
       <c r="P45" s="8">
         <f t="shared" si="8"/>
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="Q45" s="9">
         <f t="shared" si="9"/>
-        <v>20759.984042553191</v>
+        <v>19693.995762711864</v>
       </c>
       <c r="R45" s="9">
         <f t="shared" si="10"/>
-        <v>400.97872340425533</v>
+        <v>392.47881355932202</v>
       </c>
       <c r="S45" s="10">
         <f t="shared" si="11"/>
-        <v>1.9716880358686482</v>
+        <v>2.001348894170246</v>
       </c>
       <c r="T45" s="11">
         <v>281804</v>
@@ -11282,12 +11738,24 @@
       <c r="AW45" s="13">
         <v>2.261890183325197</v>
       </c>
-      <c r="AX45" s="11"/>
-      <c r="AY45" s="11"/>
-      <c r="AZ45" s="11"/>
-      <c r="BA45" s="12"/>
-      <c r="BB45" s="12"/>
-      <c r="BC45" s="13"/>
+      <c r="AX45" s="11">
+        <v>248302</v>
+      </c>
+      <c r="AY45" s="11">
+        <v>5747</v>
+      </c>
+      <c r="AZ45" s="11">
+        <v>48</v>
+      </c>
+      <c r="BA45" s="12">
+        <v>15518.875</v>
+      </c>
+      <c r="BB45" s="12">
+        <v>359.1875</v>
+      </c>
+      <c r="BC45" s="13">
+        <v>2.1496531856782362</v>
+      </c>
       <c r="BD45" s="11"/>
       <c r="BE45" s="11"/>
       <c r="BF45" s="11"/>
@@ -11365,27 +11833,27 @@
       </c>
       <c r="N46" s="8">
         <f t="shared" si="6"/>
-        <v>267964.59999999998</v>
+        <v>265010.16666666669</v>
       </c>
       <c r="O46" s="8">
         <f t="shared" si="7"/>
-        <v>5024.2</v>
+        <v>5062.833333333333</v>
       </c>
       <c r="P46" s="8">
         <f t="shared" si="8"/>
-        <v>179</v>
+        <v>227</v>
       </c>
       <c r="Q46" s="9">
         <f t="shared" si="9"/>
-        <v>22455.134078212293</v>
+        <v>21014.022026431718</v>
       </c>
       <c r="R46" s="9">
         <f t="shared" si="10"/>
-        <v>421.02234636871515</v>
+        <v>401.45814977973566</v>
       </c>
       <c r="S46" s="10">
         <f t="shared" si="11"/>
-        <v>1.9611200295533742</v>
+        <v>1.9753226751853967</v>
       </c>
       <c r="T46" s="11">
         <v>407925</v>
@@ -11477,12 +11945,24 @@
       <c r="AW46" s="13">
         <v>2.393460720009184</v>
       </c>
-      <c r="AX46" s="11"/>
-      <c r="AY46" s="11"/>
-      <c r="AZ46" s="11"/>
-      <c r="BA46" s="12"/>
-      <c r="BB46" s="12"/>
-      <c r="BC46" s="13"/>
+      <c r="AX46" s="11">
+        <v>250238</v>
+      </c>
+      <c r="AY46" s="11">
+        <v>5256</v>
+      </c>
+      <c r="AZ46" s="11">
+        <v>48</v>
+      </c>
+      <c r="BA46" s="12">
+        <v>15639.875</v>
+      </c>
+      <c r="BB46" s="12">
+        <v>328.5</v>
+      </c>
+      <c r="BC46" s="13">
+        <v>2.04633590334551</v>
+      </c>
       <c r="BD46" s="11"/>
       <c r="BE46" s="11"/>
       <c r="BF46" s="11"/>
@@ -11560,27 +12040,27 @@
       </c>
       <c r="N47" s="8">
         <f t="shared" si="6"/>
-        <v>226047.2</v>
+        <v>244477.33333333334</v>
       </c>
       <c r="O47" s="8">
         <f t="shared" si="7"/>
-        <v>17131.2</v>
+        <v>19025</v>
       </c>
       <c r="P47" s="8">
         <f t="shared" si="8"/>
-        <v>270</v>
+        <v>342</v>
       </c>
       <c r="Q47" s="9">
         <f t="shared" si="9"/>
-        <v>12558.177777777779</v>
+        <v>12867.228070175439</v>
       </c>
       <c r="R47" s="9">
         <f t="shared" si="10"/>
-        <v>951.73333333333335</v>
+        <v>1001.3157894736843</v>
       </c>
       <c r="S47" s="10">
         <f t="shared" si="11"/>
-        <v>3.8714494822338699</v>
+        <v>3.9127757564354919</v>
       </c>
       <c r="T47" s="11">
         <v>211685</v>
@@ -11672,12 +12152,24 @@
       <c r="AW47" s="13">
         <v>3.7626638552035012</v>
       </c>
-      <c r="AX47" s="11"/>
-      <c r="AY47" s="11"/>
-      <c r="AZ47" s="11"/>
-      <c r="BA47" s="12"/>
-      <c r="BB47" s="12"/>
-      <c r="BC47" s="13"/>
+      <c r="AX47" s="11">
+        <v>336628</v>
+      </c>
+      <c r="AY47" s="11">
+        <v>28494</v>
+      </c>
+      <c r="AZ47" s="11">
+        <v>72</v>
+      </c>
+      <c r="BA47" s="12">
+        <v>14026.16666666667</v>
+      </c>
+      <c r="BB47" s="12">
+        <v>1187.25</v>
+      </c>
+      <c r="BC47" s="13">
+        <v>4.1194071274436004</v>
+      </c>
       <c r="BD47" s="11"/>
       <c r="BE47" s="11"/>
       <c r="BF47" s="11"/>
@@ -11755,27 +12247,27 @@
       </c>
       <c r="N48" s="8">
         <f t="shared" si="6"/>
-        <v>212283.4</v>
+        <v>230106.5</v>
       </c>
       <c r="O48" s="8">
         <f t="shared" si="7"/>
-        <v>16338.2</v>
+        <v>18061.333333333332</v>
       </c>
       <c r="P48" s="8">
         <f t="shared" si="8"/>
-        <v>264</v>
+        <v>339</v>
       </c>
       <c r="Q48" s="9">
         <f t="shared" si="9"/>
-        <v>12061.556818181818</v>
+        <v>12218.044247787609</v>
       </c>
       <c r="R48" s="9">
         <f t="shared" si="10"/>
-        <v>928.30681818181824</v>
+        <v>959.00884955752213</v>
       </c>
       <c r="S48" s="10">
         <f t="shared" si="11"/>
-        <v>3.9111874481699389</v>
+        <v>3.9426887569967448</v>
       </c>
       <c r="T48" s="11">
         <v>225871</v>
@@ -11867,12 +12359,24 @@
       <c r="AW48" s="13">
         <v>4.1068824759952438</v>
       </c>
-      <c r="AX48" s="11"/>
-      <c r="AY48" s="11"/>
-      <c r="AZ48" s="11"/>
-      <c r="BA48" s="12"/>
-      <c r="BB48" s="12"/>
-      <c r="BC48" s="13"/>
+      <c r="AX48" s="11">
+        <v>319222</v>
+      </c>
+      <c r="AY48" s="11">
+        <v>26677</v>
+      </c>
+      <c r="AZ48" s="11">
+        <v>75</v>
+      </c>
+      <c r="BA48" s="12">
+        <v>12768.88</v>
+      </c>
+      <c r="BB48" s="12">
+        <v>1067.08</v>
+      </c>
+      <c r="BC48" s="13">
+        <v>4.1001953011307766</v>
+      </c>
       <c r="BD48" s="11"/>
       <c r="BE48" s="11"/>
       <c r="BF48" s="11"/>
@@ -11950,27 +12454,27 @@
       </c>
       <c r="N49" s="8">
         <f t="shared" si="6"/>
-        <v>202038</v>
+        <v>179671.66666666666</v>
       </c>
       <c r="O49" s="8">
         <f t="shared" si="7"/>
-        <v>38803.800000000003</v>
+        <v>35513.166666666664</v>
       </c>
       <c r="P49" s="8">
         <f t="shared" si="8"/>
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="Q49" s="9">
         <f t="shared" si="9"/>
-        <v>15077.462686567163</v>
+        <v>14767.534246575342</v>
       </c>
       <c r="R49" s="9">
         <f t="shared" si="10"/>
-        <v>2895.8059701492539</v>
+        <v>2918.8904109589039</v>
       </c>
       <c r="S49" s="10">
         <f t="shared" si="11"/>
-        <v>6.167864521976214</v>
+        <v>6.345041735349926</v>
       </c>
       <c r="T49" s="11">
         <v>268651</v>
@@ -12062,12 +12566,24 @@
       <c r="AW49" s="13">
         <v>6.8249298253425854</v>
       </c>
-      <c r="AX49" s="11"/>
-      <c r="AY49" s="11"/>
-      <c r="AZ49" s="11"/>
-      <c r="BA49" s="12"/>
-      <c r="BB49" s="12"/>
-      <c r="BC49" s="13"/>
+      <c r="AX49" s="11">
+        <v>67840</v>
+      </c>
+      <c r="AY49" s="11">
+        <v>19060</v>
+      </c>
+      <c r="AZ49" s="11">
+        <v>18</v>
+      </c>
+      <c r="BA49" s="12">
+        <v>11306.66666666667</v>
+      </c>
+      <c r="BB49" s="12">
+        <v>3176.666666666667</v>
+      </c>
+      <c r="BC49" s="13">
+        <v>7.2309278022184831</v>
+      </c>
       <c r="BD49" s="11"/>
       <c r="BE49" s="11"/>
       <c r="BF49" s="11"/>
@@ -12145,23 +12661,23 @@
       </c>
       <c r="N50" s="8">
         <f t="shared" si="6"/>
-        <v>336236</v>
+        <v>368906.66666666669</v>
       </c>
       <c r="O50" s="8">
         <f t="shared" si="7"/>
-        <v>12469</v>
+        <v>13680.666666666666</v>
       </c>
       <c r="P50" s="8">
         <f t="shared" si="8"/>
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="Q50" s="9">
         <f t="shared" si="9"/>
-        <v>24483.203883495145</v>
+        <v>25248.365019011409</v>
       </c>
       <c r="R50" s="9">
         <f t="shared" si="10"/>
-        <v>907.93689320388353</v>
+        <v>936.319391634981</v>
       </c>
       <c r="S50" s="10">
         <f t="shared" si="11"/>
@@ -12257,12 +12773,24 @@
       <c r="AW50" s="13">
         <v>2.65</v>
       </c>
-      <c r="AX50" s="11"/>
-      <c r="AY50" s="11"/>
-      <c r="AZ50" s="11"/>
-      <c r="BA50" s="12"/>
-      <c r="BB50" s="12"/>
-      <c r="BC50" s="13"/>
+      <c r="AX50" s="11">
+        <v>532260</v>
+      </c>
+      <c r="AY50" s="11">
+        <v>19739</v>
+      </c>
+      <c r="AZ50" s="11">
+        <v>57</v>
+      </c>
+      <c r="BA50" s="12">
+        <v>28013.684210526309</v>
+      </c>
+      <c r="BB50" s="12">
+        <v>1038.894736842105</v>
+      </c>
+      <c r="BC50" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BD50" s="11"/>
       <c r="BE50" s="11"/>
       <c r="BF50" s="11"/>
@@ -12340,23 +12868,23 @@
       </c>
       <c r="N51" s="8">
         <f t="shared" si="6"/>
-        <v>359836</v>
+        <v>394713.33333333331</v>
       </c>
       <c r="O51" s="8">
         <f t="shared" si="7"/>
-        <v>13344.4</v>
+        <v>14637.833333333334</v>
       </c>
       <c r="P51" s="8">
         <f t="shared" si="8"/>
-        <v>209</v>
+        <v>272</v>
       </c>
       <c r="Q51" s="9">
         <f t="shared" si="9"/>
-        <v>25825.55023923445</v>
+        <v>26120.73529411765</v>
       </c>
       <c r="R51" s="9">
         <f t="shared" si="10"/>
-        <v>957.73205741626793</v>
+        <v>968.68014705882342</v>
       </c>
       <c r="S51" s="10">
         <f t="shared" si="11"/>
@@ -12452,12 +12980,24 @@
       <c r="AW51" s="13">
         <v>2.65</v>
       </c>
-      <c r="AX51" s="11"/>
-      <c r="AY51" s="11"/>
-      <c r="AZ51" s="11"/>
-      <c r="BA51" s="12"/>
-      <c r="BB51" s="12"/>
-      <c r="BC51" s="13"/>
+      <c r="AX51" s="11">
+        <v>569100</v>
+      </c>
+      <c r="AY51" s="11">
+        <v>21105</v>
+      </c>
+      <c r="AZ51" s="11">
+        <v>63</v>
+      </c>
+      <c r="BA51" s="12">
+        <v>27100</v>
+      </c>
+      <c r="BB51" s="12">
+        <v>1005</v>
+      </c>
+      <c r="BC51" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BD51" s="11"/>
       <c r="BE51" s="11"/>
       <c r="BF51" s="11"/>
@@ -12535,27 +13075,27 @@
       </c>
       <c r="N52" s="8">
         <f t="shared" si="6"/>
-        <v>48248.6</v>
+        <v>44471.833333333336</v>
       </c>
       <c r="O52" s="8">
         <f t="shared" si="7"/>
-        <v>111525</v>
+        <v>103341.33333333333</v>
       </c>
       <c r="P52" s="8">
         <f t="shared" si="8"/>
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="Q52" s="9">
         <f t="shared" si="9"/>
-        <v>5610.3023255813951</v>
+        <v>5677.2553191489369</v>
       </c>
       <c r="R52" s="9">
         <f t="shared" si="10"/>
-        <v>12968.023255813952</v>
+        <v>13192.51063829787</v>
       </c>
       <c r="S52" s="10">
         <f t="shared" si="11"/>
-        <v>24.086234744086354</v>
+        <v>24.128020210838759</v>
       </c>
       <c r="T52" s="11">
         <v>62208</v>
@@ -12647,12 +13187,24 @@
       <c r="AW52" s="13">
         <v>26.965539092365109</v>
       </c>
-      <c r="AX52" s="11"/>
-      <c r="AY52" s="11"/>
-      <c r="AZ52" s="11"/>
-      <c r="BA52" s="12"/>
-      <c r="BB52" s="12"/>
-      <c r="BC52" s="13"/>
+      <c r="AX52" s="11">
+        <v>25588</v>
+      </c>
+      <c r="AY52" s="11">
+        <v>62423</v>
+      </c>
+      <c r="AZ52" s="11">
+        <v>12</v>
+      </c>
+      <c r="BA52" s="12">
+        <v>6397</v>
+      </c>
+      <c r="BB52" s="12">
+        <v>15605.75</v>
+      </c>
+      <c r="BC52" s="13">
+        <v>24.3369475446008</v>
+      </c>
       <c r="BD52" s="11"/>
       <c r="BE52" s="11"/>
       <c r="BF52" s="11"/>
@@ -12716,11 +13268,11 @@
       <c r="M53" s="14"/>
       <c r="N53" s="14">
         <f>SUM(N3:N52)</f>
-        <v>9764429.2499999981</v>
+        <v>10070851.686666667</v>
       </c>
       <c r="O53" s="14">
         <f>SUM(O3:O52)</f>
-        <v>1973150.8833333333</v>
+        <v>1988601.066666666</v>
       </c>
       <c r="P53" s="14"/>
       <c r="Q53" s="14"/>
@@ -12788,11 +13340,11 @@
       <c r="AW53" s="14"/>
       <c r="AX53" s="14">
         <f>SUM(AX3:AX52)</f>
-        <v>0</v>
+        <v>11553107.82</v>
       </c>
       <c r="AY53" s="14">
         <f>SUM(AY3:AY52)</f>
-        <v>0</v>
+        <v>2079399</v>
       </c>
       <c r="AZ53" s="14"/>
       <c r="BA53" s="14"/>
@@ -13327,29 +13879,29 @@
       <c r="M57" s="10">
         <v>2.368836869937013</v>
       </c>
-      <c r="N57" s="8" t="str">
+      <c r="N57" s="8">
         <f t="shared" ref="N57:N78" si="12">IFERROR(AVERAGE(T57,Z57,AF57,AL57,AR57,AX57,BD57,BJ57,BP57,BV57,CB57,CH57)," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="O57" s="8" t="str">
+        <v>280490</v>
+      </c>
+      <c r="O57" s="8">
         <f t="shared" ref="O57:O78" si="13">IFERROR(AVERAGE(U57,AA57,AG57,AM57,AS57,AY57,BE57,BK57,BQ57,BW57,CC57,CI57)," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>14231</v>
       </c>
       <c r="P57" s="8">
         <f t="shared" ref="P57:P78" si="14">IFERROR(SUM(V57,AB57,AH57,AN57,AT57,AZ57,BF57,BL57,BR57,BX57,CD57,CJ57)," ")</f>
-        <v>0</v>
-      </c>
-      <c r="Q57" s="9" t="str">
+        <v>10</v>
+      </c>
+      <c r="Q57" s="9">
         <f t="shared" ref="Q57:Q78" si="15">IFERROR(SUM(T57,Z57,AF57,AL57,AR57,AX57,BD57,BJ57,BP57,BV57,CB57,CH57)/P57*3," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="R57" s="9" t="str">
+        <v>84147</v>
+      </c>
+      <c r="R57" s="9">
         <f t="shared" ref="R57:R78" si="16">IFERROR(SUM(U57,AA57,AG57,AM57,AS57,AY57,BE57,BK57,BQ57,BW57,CC57,CI57)/P57*3," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="S57" s="10" t="str">
+        <v>4269.2999999999993</v>
+      </c>
+      <c r="S57" s="10">
         <f t="shared" ref="S57:S78" si="17">IFERROR(AVERAGE(Y57,AE57,AK57,AQ57,AW57,BC57,BI57,BO57,BU57,CA57,CG57,CM57)," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>2.8674059405138981</v>
       </c>
       <c r="T57" s="11"/>
       <c r="U57" s="11"/>
@@ -13381,12 +13933,24 @@
       <c r="AU57" s="12"/>
       <c r="AV57" s="12"/>
       <c r="AW57" s="13"/>
-      <c r="AX57" s="11"/>
-      <c r="AY57" s="11"/>
-      <c r="AZ57" s="11"/>
-      <c r="BA57" s="12"/>
-      <c r="BB57" s="12"/>
-      <c r="BC57" s="13"/>
+      <c r="AX57" s="11">
+        <v>280490</v>
+      </c>
+      <c r="AY57" s="11">
+        <v>14231</v>
+      </c>
+      <c r="AZ57" s="11">
+        <v>10</v>
+      </c>
+      <c r="BA57" s="12">
+        <v>84147</v>
+      </c>
+      <c r="BB57" s="12">
+        <v>4269.2999999999993</v>
+      </c>
+      <c r="BC57" s="13">
+        <v>2.8674059405138981</v>
+      </c>
       <c r="BD57" s="11"/>
       <c r="BE57" s="11"/>
       <c r="BF57" s="11"/>
@@ -13467,27 +14031,27 @@
       </c>
       <c r="N58" s="8">
         <f t="shared" si="12"/>
-        <v>4402178.8</v>
+        <v>4404797.333333333</v>
       </c>
       <c r="O58" s="8">
         <f t="shared" si="13"/>
-        <v>48528.6</v>
+        <v>48707.166666666664</v>
       </c>
       <c r="P58" s="8">
         <f t="shared" si="14"/>
-        <v>334</v>
+        <v>407</v>
       </c>
       <c r="Q58" s="9">
         <f t="shared" si="15"/>
-        <v>197702.64071856288</v>
+        <v>194806.76167076168</v>
       </c>
       <c r="R58" s="9">
         <f t="shared" si="16"/>
-        <v>2179.4281437125751</v>
+        <v>2154.1253071253072</v>
       </c>
       <c r="S58" s="10">
         <f t="shared" si="17"/>
-        <v>1.3396388513500848</v>
+        <v>1.341224420296024</v>
       </c>
       <c r="T58" s="11">
         <v>4555723</v>
@@ -13579,12 +14143,24 @@
       <c r="AW58" s="13">
         <v>1.388474746443946</v>
       </c>
-      <c r="AX58" s="11"/>
-      <c r="AY58" s="11"/>
-      <c r="AZ58" s="11"/>
-      <c r="BA58" s="12"/>
-      <c r="BB58" s="12"/>
-      <c r="BC58" s="13"/>
+      <c r="AX58" s="11">
+        <v>4417890</v>
+      </c>
+      <c r="AY58" s="11">
+        <v>49600</v>
+      </c>
+      <c r="AZ58" s="11">
+        <v>73</v>
+      </c>
+      <c r="BA58" s="12">
+        <v>181557.12328767119</v>
+      </c>
+      <c r="BB58" s="12">
+        <v>2038.3561643835619</v>
+      </c>
+      <c r="BC58" s="13">
+        <v>1.3491522650257199</v>
+      </c>
       <c r="BD58" s="11"/>
       <c r="BE58" s="11"/>
       <c r="BF58" s="11"/>
@@ -13803,27 +14379,27 @@
       </c>
       <c r="N60" s="8">
         <f t="shared" si="12"/>
-        <v>3128602.6</v>
+        <v>3415673.5</v>
       </c>
       <c r="O60" s="8">
         <f t="shared" si="13"/>
-        <v>8034.6</v>
+        <v>8695</v>
       </c>
       <c r="P60" s="8">
         <f t="shared" si="14"/>
-        <v>239</v>
+        <v>313</v>
       </c>
       <c r="Q60" s="9">
         <f t="shared" si="15"/>
-        <v>196355.81171548116</v>
+        <v>196428.50798722045</v>
       </c>
       <c r="R60" s="9">
         <f t="shared" si="16"/>
-        <v>504.26359832635984</v>
+        <v>500.03194888178916</v>
       </c>
       <c r="S60" s="10">
         <f t="shared" si="17"/>
-        <v>0.64132439165172694</v>
+        <v>0.63980983320435858</v>
       </c>
       <c r="T60" s="11">
         <v>2164532</v>
@@ -13915,12 +14491,24 @@
       <c r="AW60" s="13">
         <v>0.68072547654185334</v>
       </c>
-      <c r="AX60" s="11"/>
-      <c r="AY60" s="11"/>
-      <c r="AZ60" s="11"/>
-      <c r="BA60" s="12"/>
-      <c r="BB60" s="12"/>
-      <c r="BC60" s="13"/>
+      <c r="AX60" s="11">
+        <v>4851028</v>
+      </c>
+      <c r="AY60" s="11">
+        <v>11997</v>
+      </c>
+      <c r="AZ60" s="11">
+        <v>74</v>
+      </c>
+      <c r="BA60" s="12">
+        <v>196663.29729729731</v>
+      </c>
+      <c r="BB60" s="12">
+        <v>486.36486486486478</v>
+      </c>
+      <c r="BC60" s="13">
+        <v>0.63223704096751654</v>
+      </c>
       <c r="BD60" s="11"/>
       <c r="BE60" s="11"/>
       <c r="BF60" s="11"/>
@@ -14001,27 +14589,27 @@
       </c>
       <c r="N61" s="8">
         <f t="shared" si="12"/>
-        <v>3105867</v>
+        <v>3308453.8</v>
       </c>
       <c r="O61" s="8">
         <f t="shared" si="13"/>
-        <v>6108.25</v>
+        <v>6972.2</v>
       </c>
       <c r="P61" s="8">
         <f t="shared" si="14"/>
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="Q61" s="9">
         <f t="shared" si="15"/>
-        <v>208214.54748603352</v>
+        <v>205920.36099585064</v>
       </c>
       <c r="R61" s="9">
         <f t="shared" si="16"/>
-        <v>409.49162011173189</v>
+        <v>433.95435684647299</v>
       </c>
       <c r="S61" s="10">
         <f t="shared" si="17"/>
-        <v>0.56954532951104564</v>
+        <v>0.58321553631183687</v>
       </c>
       <c r="T61" s="11"/>
       <c r="U61" s="11"/>
@@ -14101,12 +14689,24 @@
       <c r="AW61" s="13">
         <v>0.49887975544843738</v>
       </c>
-      <c r="AX61" s="11"/>
-      <c r="AY61" s="11"/>
-      <c r="AZ61" s="11"/>
-      <c r="BA61" s="12"/>
-      <c r="BB61" s="12"/>
-      <c r="BC61" s="13"/>
+      <c r="AX61" s="11">
+        <v>4118801</v>
+      </c>
+      <c r="AY61" s="11">
+        <v>10428</v>
+      </c>
+      <c r="AZ61" s="11">
+        <v>62</v>
+      </c>
+      <c r="BA61" s="12">
+        <v>199296.82258064521</v>
+      </c>
+      <c r="BB61" s="12">
+        <v>504.58064516129031</v>
+      </c>
+      <c r="BC61" s="13">
+        <v>0.63789636351500167</v>
+      </c>
       <c r="BD61" s="11"/>
       <c r="BE61" s="11"/>
       <c r="BF61" s="11"/>
@@ -14187,27 +14787,27 @@
       </c>
       <c r="N62" s="8">
         <f t="shared" si="12"/>
-        <v>3563489.2</v>
+        <v>3983634.6666666665</v>
       </c>
       <c r="O62" s="8">
         <f t="shared" si="13"/>
-        <v>7585</v>
+        <v>9070</v>
       </c>
       <c r="P62" s="8">
         <f t="shared" si="14"/>
-        <v>230</v>
+        <v>305</v>
       </c>
       <c r="Q62" s="9">
         <f t="shared" si="15"/>
-        <v>232401.46956521738</v>
+        <v>235099.75081967213</v>
       </c>
       <c r="R62" s="9">
         <f t="shared" si="16"/>
-        <v>494.67391304347825</v>
+        <v>535.27868852459017</v>
       </c>
       <c r="S62" s="10">
         <f t="shared" si="17"/>
-        <v>0.566420453296961</v>
+        <v>0.58201704441413427</v>
       </c>
       <c r="T62" s="11">
         <v>2675265</v>
@@ -14299,12 +14899,24 @@
       <c r="AW62" s="13">
         <v>0.66</v>
       </c>
-      <c r="AX62" s="11"/>
-      <c r="AY62" s="11"/>
-      <c r="AZ62" s="11"/>
-      <c r="BA62" s="12"/>
-      <c r="BB62" s="12"/>
-      <c r="BC62" s="13"/>
+      <c r="AX62" s="11">
+        <v>6084362</v>
+      </c>
+      <c r="AY62" s="11">
+        <v>16495</v>
+      </c>
+      <c r="AZ62" s="11">
+        <v>75</v>
+      </c>
+      <c r="BA62" s="12">
+        <v>243374.48</v>
+      </c>
+      <c r="BB62" s="12">
+        <v>659.8</v>
+      </c>
+      <c r="BC62" s="13">
+        <v>0.66</v>
+      </c>
       <c r="BD62" s="11"/>
       <c r="BE62" s="11"/>
       <c r="BF62" s="11"/>
@@ -14385,27 +14997,27 @@
       </c>
       <c r="N63" s="8">
         <f t="shared" si="12"/>
-        <v>9701326</v>
+        <v>9850120.166666666</v>
       </c>
       <c r="O63" s="8">
         <f t="shared" si="13"/>
-        <v>10280.6</v>
+        <v>10147.833333333334</v>
       </c>
       <c r="P63" s="8">
         <f t="shared" si="14"/>
-        <v>342</v>
+        <v>416</v>
       </c>
       <c r="Q63" s="9">
         <f t="shared" si="15"/>
-        <v>425496.75438596494</v>
+        <v>426207.12259615387</v>
       </c>
       <c r="R63" s="9">
         <f t="shared" si="16"/>
-        <v>450.90350877192981</v>
+        <v>439.08894230769232</v>
       </c>
       <c r="S63" s="10">
         <f t="shared" si="17"/>
-        <v>0.41391790428412933</v>
+        <v>0.40825304716319449</v>
       </c>
       <c r="T63" s="11">
         <v>9298604</v>
@@ -14497,12 +15109,24 @@
       <c r="AW63" s="13">
         <v>0.39188612138528323</v>
       </c>
-      <c r="AX63" s="11"/>
-      <c r="AY63" s="11"/>
-      <c r="AZ63" s="11"/>
-      <c r="BA63" s="12"/>
-      <c r="BB63" s="12"/>
-      <c r="BC63" s="13"/>
+      <c r="AX63" s="11">
+        <v>10594091</v>
+      </c>
+      <c r="AY63" s="11">
+        <v>9484</v>
+      </c>
+      <c r="AZ63" s="11">
+        <v>74</v>
+      </c>
+      <c r="BA63" s="12">
+        <v>429490.17567567568</v>
+      </c>
+      <c r="BB63" s="12">
+        <v>384.48648648648651</v>
+      </c>
+      <c r="BC63" s="13">
+        <v>0.3799287615585204</v>
+      </c>
       <c r="BD63" s="11"/>
       <c r="BE63" s="11"/>
       <c r="BF63" s="11"/>
@@ -14583,27 +15207,27 @@
       </c>
       <c r="N64" s="8">
         <f t="shared" si="12"/>
-        <v>8982609.4000000004</v>
+        <v>9307202</v>
       </c>
       <c r="O64" s="8">
         <f t="shared" si="13"/>
-        <v>10965.4</v>
+        <v>10775.833333333334</v>
       </c>
       <c r="P64" s="8">
         <f t="shared" si="14"/>
-        <v>340</v>
+        <v>417</v>
       </c>
       <c r="Q64" s="9">
         <f t="shared" si="15"/>
-        <v>396291.59117647063</v>
+        <v>401749.72661870508</v>
       </c>
       <c r="R64" s="9">
         <f t="shared" si="16"/>
-        <v>483.76764705882351</v>
+        <v>465.14388489208636</v>
       </c>
       <c r="S64" s="10">
         <f t="shared" si="17"/>
-        <v>0.45279295452128998</v>
+        <v>0.440761062794299</v>
       </c>
       <c r="T64" s="11">
         <v>10280587</v>
@@ -14695,12 +15319,24 @@
       <c r="AW64" s="13">
         <v>0.39114546649287851</v>
       </c>
-      <c r="AX64" s="11"/>
-      <c r="AY64" s="11"/>
-      <c r="AZ64" s="11"/>
-      <c r="BA64" s="12"/>
-      <c r="BB64" s="12"/>
-      <c r="BC64" s="13"/>
+      <c r="AX64" s="11">
+        <v>10930165</v>
+      </c>
+      <c r="AY64" s="11">
+        <v>9828</v>
+      </c>
+      <c r="AZ64" s="11">
+        <v>77</v>
+      </c>
+      <c r="BA64" s="12">
+        <v>425850.5844155844</v>
+      </c>
+      <c r="BB64" s="12">
+        <v>382.90909090909088</v>
+      </c>
+      <c r="BC64" s="13">
+        <v>0.38060160415934408</v>
+      </c>
       <c r="BD64" s="11"/>
       <c r="BE64" s="11"/>
       <c r="BF64" s="11"/>
@@ -14781,27 +15417,27 @@
       </c>
       <c r="N65" s="8">
         <f t="shared" si="12"/>
-        <v>9041490.1999999993</v>
+        <v>9098804.666666666</v>
       </c>
       <c r="O65" s="8">
         <f t="shared" si="13"/>
-        <v>13532.4</v>
+        <v>13473.666666666666</v>
       </c>
       <c r="P65" s="8">
         <f t="shared" si="14"/>
-        <v>341</v>
+        <v>417</v>
       </c>
       <c r="Q65" s="9">
         <f t="shared" si="15"/>
-        <v>397719.51026392961</v>
+        <v>392754.1582733813</v>
       </c>
       <c r="R65" s="9">
         <f t="shared" si="16"/>
-        <v>595.26686217008796</v>
+        <v>581.59712230215825</v>
       </c>
       <c r="S65" s="10">
         <f t="shared" si="17"/>
-        <v>0.49643445927647445</v>
+        <v>0.49289780204562605</v>
       </c>
       <c r="T65" s="11">
         <v>9995292</v>
@@ -14893,12 +15529,24 @@
       <c r="AW65" s="13">
         <v>0.65827704481449123</v>
       </c>
-      <c r="AX65" s="11"/>
-      <c r="AY65" s="11"/>
-      <c r="AZ65" s="11"/>
-      <c r="BA65" s="12"/>
-      <c r="BB65" s="12"/>
-      <c r="BC65" s="13"/>
+      <c r="AX65" s="11">
+        <v>9385377</v>
+      </c>
+      <c r="AY65" s="11">
+        <v>13180</v>
+      </c>
+      <c r="AZ65" s="11">
+        <v>76</v>
+      </c>
+      <c r="BA65" s="12">
+        <v>370475.40789473691</v>
+      </c>
+      <c r="BB65" s="12">
+        <v>520.26315789473688</v>
+      </c>
+      <c r="BC65" s="13">
+        <v>0.47521451589138392</v>
+      </c>
       <c r="BD65" s="11"/>
       <c r="BE65" s="11"/>
       <c r="BF65" s="11"/>
@@ -14979,27 +15627,27 @@
       </c>
       <c r="N66" s="8">
         <f t="shared" si="12"/>
-        <v>8896592.8000000007</v>
+        <v>8526236.833333334</v>
       </c>
       <c r="O66" s="8">
         <f t="shared" si="13"/>
-        <v>15976.4</v>
+        <v>14715.5</v>
       </c>
       <c r="P66" s="8">
         <f t="shared" si="14"/>
-        <v>338</v>
+        <v>407</v>
       </c>
       <c r="Q66" s="9">
         <f t="shared" si="15"/>
-        <v>394819.20710059174</v>
+        <v>377081.72727272729</v>
       </c>
       <c r="R66" s="9">
         <f t="shared" si="16"/>
-        <v>709.01183431952666</v>
+        <v>650.80835380835379</v>
       </c>
       <c r="S66" s="10">
         <f t="shared" si="17"/>
-        <v>0.53753522313929736</v>
+        <v>0.52318120780634259</v>
       </c>
       <c r="T66" s="11">
         <v>8918165</v>
@@ -15091,12 +15739,24 @@
       <c r="AW66" s="13">
         <v>0.53712127356739103</v>
       </c>
-      <c r="AX66" s="11"/>
-      <c r="AY66" s="11"/>
-      <c r="AZ66" s="11"/>
-      <c r="BA66" s="12"/>
-      <c r="BB66" s="12"/>
-      <c r="BC66" s="13"/>
+      <c r="AX66" s="11">
+        <v>6674457</v>
+      </c>
+      <c r="AY66" s="11">
+        <v>8411</v>
+      </c>
+      <c r="AZ66" s="11">
+        <v>69</v>
+      </c>
+      <c r="BA66" s="12">
+        <v>290193.78260869568</v>
+      </c>
+      <c r="BB66" s="12">
+        <v>365.69565217391312</v>
+      </c>
+      <c r="BC66" s="13">
+        <v>0.45141113114156911</v>
+      </c>
       <c r="BD66" s="11"/>
       <c r="BE66" s="11"/>
       <c r="BF66" s="11"/>
@@ -15177,27 +15837,27 @@
       </c>
       <c r="N67" s="8">
         <f t="shared" si="12"/>
-        <v>4930378</v>
+        <v>4928894.5</v>
       </c>
       <c r="O67" s="8">
         <f t="shared" si="13"/>
-        <v>11537.2</v>
+        <v>11289.833333333334</v>
       </c>
       <c r="P67" s="8">
         <f t="shared" si="14"/>
-        <v>345</v>
+        <v>416</v>
       </c>
       <c r="Q67" s="9">
         <f t="shared" si="15"/>
-        <v>214364.26086956519</v>
+        <v>213269.47355769231</v>
       </c>
       <c r="R67" s="9">
         <f t="shared" si="16"/>
-        <v>501.61739130434779</v>
+        <v>488.50240384615381</v>
       </c>
       <c r="S67" s="10">
         <f t="shared" si="17"/>
-        <v>0.61335626169895208</v>
+        <v>0.60728487117891505</v>
       </c>
       <c r="T67" s="11">
         <v>5935742</v>
@@ -15289,12 +15949,24 @@
       <c r="AW67" s="13">
         <v>0.62091241094831573</v>
       </c>
-      <c r="AX67" s="11"/>
-      <c r="AY67" s="11"/>
-      <c r="AZ67" s="11"/>
-      <c r="BA67" s="12"/>
-      <c r="BB67" s="12"/>
-      <c r="BC67" s="13"/>
+      <c r="AX67" s="11">
+        <v>4921477</v>
+      </c>
+      <c r="AY67" s="11">
+        <v>10053</v>
+      </c>
+      <c r="AZ67" s="11">
+        <v>71</v>
+      </c>
+      <c r="BA67" s="12">
+        <v>207949.7323943662</v>
+      </c>
+      <c r="BB67" s="12">
+        <v>424.77464788732402</v>
+      </c>
+      <c r="BC67" s="13">
+        <v>0.57692791857872994</v>
+      </c>
       <c r="BD67" s="11"/>
       <c r="BE67" s="11"/>
       <c r="BF67" s="11"/>
@@ -15375,27 +16047,27 @@
       </c>
       <c r="N68" s="8">
         <f t="shared" si="12"/>
-        <v>6072847.2000000002</v>
+        <v>5984337</v>
       </c>
       <c r="O68" s="8">
         <f t="shared" si="13"/>
-        <v>15708</v>
+        <v>15354.666666666666</v>
       </c>
       <c r="P68" s="8">
         <f t="shared" si="14"/>
-        <v>348</v>
+        <v>422</v>
       </c>
       <c r="Q68" s="9">
         <f t="shared" si="15"/>
-        <v>261760.6551724138</v>
+        <v>255256.08056872038</v>
       </c>
       <c r="R68" s="9">
         <f t="shared" si="16"/>
-        <v>677.06896551724139</v>
+        <v>654.93838862559244</v>
       </c>
       <c r="S68" s="10">
         <f t="shared" si="17"/>
-        <v>0.64126761574065128</v>
+        <v>0.63930404035849786</v>
       </c>
       <c r="T68" s="11">
         <v>6055582</v>
@@ -15487,12 +16159,24 @@
       <c r="AW68" s="13">
         <v>0.58651962654037459</v>
       </c>
-      <c r="AX68" s="11"/>
-      <c r="AY68" s="11"/>
-      <c r="AZ68" s="11"/>
-      <c r="BA68" s="12"/>
-      <c r="BB68" s="12"/>
-      <c r="BC68" s="13"/>
+      <c r="AX68" s="11">
+        <v>5541786</v>
+      </c>
+      <c r="AY68" s="11">
+        <v>13588</v>
+      </c>
+      <c r="AZ68" s="11">
+        <v>74</v>
+      </c>
+      <c r="BA68" s="12">
+        <v>224667</v>
+      </c>
+      <c r="BB68" s="12">
+        <v>550.86486486486478</v>
+      </c>
+      <c r="BC68" s="13">
+        <v>0.62948616344773023</v>
+      </c>
       <c r="BD68" s="11"/>
       <c r="BE68" s="11"/>
       <c r="BF68" s="11"/>
@@ -15573,27 +16257,27 @@
       </c>
       <c r="N69" s="8">
         <f t="shared" si="12"/>
-        <v>5439183</v>
+        <v>5790235</v>
       </c>
       <c r="O69" s="8">
         <f t="shared" si="13"/>
-        <v>13756.4</v>
+        <v>14847.666666666666</v>
       </c>
       <c r="P69" s="8">
         <f t="shared" si="14"/>
-        <v>349</v>
+        <v>421</v>
       </c>
       <c r="Q69" s="9">
         <f t="shared" si="15"/>
-        <v>233775.77363896847</v>
+        <v>247563.49168646082</v>
       </c>
       <c r="R69" s="9">
         <f t="shared" si="16"/>
-        <v>591.24928366762174</v>
+        <v>634.81710213776728</v>
       </c>
       <c r="S69" s="10">
         <f t="shared" si="17"/>
-        <v>0.63778893712835372</v>
+        <v>0.64126258743148057</v>
       </c>
       <c r="T69" s="11">
         <v>4627717</v>
@@ -15685,12 +16369,24 @@
       <c r="AW69" s="13">
         <v>0.65530082349759566</v>
       </c>
-      <c r="AX69" s="11"/>
-      <c r="AY69" s="11"/>
-      <c r="AZ69" s="11"/>
-      <c r="BA69" s="12"/>
-      <c r="BB69" s="12"/>
-      <c r="BC69" s="13"/>
+      <c r="AX69" s="11">
+        <v>7545495</v>
+      </c>
+      <c r="AY69" s="11">
+        <v>20304</v>
+      </c>
+      <c r="AZ69" s="11">
+        <v>72</v>
+      </c>
+      <c r="BA69" s="12">
+        <v>314395.625</v>
+      </c>
+      <c r="BB69" s="12">
+        <v>846</v>
+      </c>
+      <c r="BC69" s="13">
+        <v>0.65863083894711516</v>
+      </c>
       <c r="BD69" s="11"/>
       <c r="BE69" s="11"/>
       <c r="BF69" s="11"/>
@@ -15771,27 +16467,27 @@
       </c>
       <c r="N70" s="8">
         <f t="shared" si="12"/>
-        <v>3256837</v>
+        <v>3752381.5</v>
       </c>
       <c r="O70" s="8">
         <f t="shared" si="13"/>
-        <v>8350</v>
+        <v>9775.1666666666661</v>
       </c>
       <c r="P70" s="8">
         <f t="shared" si="14"/>
-        <v>202</v>
+        <v>277</v>
       </c>
       <c r="Q70" s="9">
         <f t="shared" si="15"/>
-        <v>241844.33168316833</v>
+        <v>243837.06498194946</v>
       </c>
       <c r="R70" s="9">
         <f t="shared" si="16"/>
-        <v>620.04950495049502</v>
+        <v>635.20938628158842</v>
       </c>
       <c r="S70" s="10">
         <f t="shared" si="17"/>
-        <v>0.64396570987672885</v>
+        <v>0.64662721993525674</v>
       </c>
       <c r="T70" s="11">
         <v>640528</v>
@@ -15883,12 +16579,24 @@
       <c r="AW70" s="13">
         <v>0.65481678178554181</v>
       </c>
-      <c r="AX70" s="11"/>
-      <c r="AY70" s="11"/>
-      <c r="AZ70" s="11"/>
-      <c r="BA70" s="12"/>
-      <c r="BB70" s="12"/>
-      <c r="BC70" s="13"/>
+      <c r="AX70" s="11">
+        <v>6230104</v>
+      </c>
+      <c r="AY70" s="11">
+        <v>16901</v>
+      </c>
+      <c r="AZ70" s="11">
+        <v>75</v>
+      </c>
+      <c r="BA70" s="12">
+        <v>249204.16</v>
+      </c>
+      <c r="BB70" s="12">
+        <v>676.04</v>
+      </c>
+      <c r="BC70" s="13">
+        <v>0.65993477022789648</v>
+      </c>
       <c r="BD70" s="11"/>
       <c r="BE70" s="11"/>
       <c r="BF70" s="11"/>
@@ -16305,27 +17013,27 @@
       </c>
       <c r="N73" s="8">
         <f t="shared" si="12"/>
-        <v>4250952.2</v>
+        <v>4342708.333333333</v>
       </c>
       <c r="O73" s="8">
         <f t="shared" si="13"/>
-        <v>6948.4</v>
+        <v>7542.333333333333</v>
       </c>
       <c r="P73" s="8">
         <f t="shared" si="14"/>
-        <v>331</v>
+        <v>403</v>
       </c>
       <c r="Q73" s="9">
         <f t="shared" si="15"/>
-        <v>192641.33836858007</v>
+        <v>193967.12158808933</v>
       </c>
       <c r="R73" s="9">
         <f t="shared" si="16"/>
-        <v>314.88217522658613</v>
+        <v>336.87841191067002</v>
       </c>
       <c r="S73" s="10">
         <f t="shared" si="17"/>
-        <v>0.50419738004520653</v>
+        <v>0.51875957011845664</v>
       </c>
       <c r="T73" s="11">
         <v>6999813</v>
@@ -16417,12 +17125,24 @@
       <c r="AW73" s="13">
         <v>0.45629772089101051</v>
       </c>
-      <c r="AX73" s="11"/>
-      <c r="AY73" s="11"/>
-      <c r="AZ73" s="11"/>
-      <c r="BA73" s="12"/>
-      <c r="BB73" s="12"/>
-      <c r="BC73" s="13"/>
+      <c r="AX73" s="11">
+        <v>4801489</v>
+      </c>
+      <c r="AY73" s="11">
+        <v>10512</v>
+      </c>
+      <c r="AZ73" s="11">
+        <v>72</v>
+      </c>
+      <c r="BA73" s="12">
+        <v>200062.04166666669</v>
+      </c>
+      <c r="BB73" s="12">
+        <v>438</v>
+      </c>
+      <c r="BC73" s="13">
+        <v>0.59157052048470737</v>
+      </c>
       <c r="BD73" s="11"/>
       <c r="BE73" s="11"/>
       <c r="BF73" s="11"/>
@@ -16503,27 +17223,27 @@
       </c>
       <c r="N74" s="8">
         <f t="shared" si="12"/>
-        <v>4710087.5999999996</v>
+        <v>4354110</v>
       </c>
       <c r="O74" s="8">
         <f t="shared" si="13"/>
-        <v>7442</v>
+        <v>6690</v>
       </c>
       <c r="P74" s="8">
         <f t="shared" si="14"/>
-        <v>295</v>
+        <v>357</v>
       </c>
       <c r="Q74" s="9">
         <f t="shared" si="15"/>
-        <v>239495.97966101693</v>
+        <v>219534.95798319328</v>
       </c>
       <c r="R74" s="9">
         <f t="shared" si="16"/>
-        <v>378.40677966101697</v>
+        <v>337.31092436974791</v>
       </c>
       <c r="S74" s="10">
         <f t="shared" si="17"/>
-        <v>0.46837159742183471</v>
+        <v>0.4620853726893665</v>
       </c>
       <c r="T74" s="11">
         <v>6713836</v>
@@ -16615,12 +17335,24 @@
       <c r="AW74" s="13">
         <v>0.35004701489281043</v>
       </c>
-      <c r="AX74" s="11"/>
-      <c r="AY74" s="11"/>
-      <c r="AZ74" s="11"/>
-      <c r="BA74" s="12"/>
-      <c r="BB74" s="12"/>
-      <c r="BC74" s="13"/>
+      <c r="AX74" s="11">
+        <v>2574222</v>
+      </c>
+      <c r="AY74" s="11">
+        <v>2930</v>
+      </c>
+      <c r="AZ74" s="11">
+        <v>62</v>
+      </c>
+      <c r="BA74" s="12">
+        <v>124559.1290322581</v>
+      </c>
+      <c r="BB74" s="12">
+        <v>141.7741935483871</v>
+      </c>
+      <c r="BC74" s="13">
+        <v>0.43065424902702543</v>
+      </c>
       <c r="BD74" s="11"/>
       <c r="BE74" s="11"/>
       <c r="BF74" s="11"/>
@@ -16701,27 +17433,27 @@
       </c>
       <c r="N75" s="8">
         <f t="shared" si="12"/>
-        <v>1050422.868</v>
+        <v>1081576.7233333334</v>
       </c>
       <c r="O75" s="8">
         <f t="shared" si="13"/>
-        <v>155164.79999999999</v>
+        <v>155353</v>
       </c>
       <c r="P75" s="8">
         <f t="shared" si="14"/>
-        <v>353</v>
+        <v>428</v>
       </c>
       <c r="Q75" s="9">
         <f t="shared" si="15"/>
-        <v>44635.532634560906</v>
+        <v>45486.871542056069</v>
       </c>
       <c r="R75" s="9">
         <f t="shared" si="16"/>
-        <v>6593.4050991501408</v>
+        <v>6533.5373831775696</v>
       </c>
       <c r="S75" s="10">
         <f t="shared" si="17"/>
-        <v>4.9014767858737391</v>
+        <v>4.8388014068699254</v>
       </c>
       <c r="T75" s="11">
         <v>1253986.8999999999</v>
@@ -16813,12 +17545,24 @@
       <c r="AW75" s="13">
         <v>4.8388642638832344</v>
       </c>
-      <c r="AX75" s="11"/>
-      <c r="AY75" s="11"/>
-      <c r="AZ75" s="11"/>
-      <c r="BA75" s="12"/>
-      <c r="BB75" s="12"/>
-      <c r="BC75" s="13"/>
+      <c r="AX75" s="11">
+        <v>1237346</v>
+      </c>
+      <c r="AY75" s="11">
+        <v>156294</v>
+      </c>
+      <c r="AZ75" s="11">
+        <v>75</v>
+      </c>
+      <c r="BA75" s="12">
+        <v>49493.84</v>
+      </c>
+      <c r="BB75" s="12">
+        <v>6251.76</v>
+      </c>
+      <c r="BC75" s="13">
+        <v>4.5254245118508543</v>
+      </c>
       <c r="BD75" s="11"/>
       <c r="BE75" s="11"/>
       <c r="BF75" s="11"/>
@@ -16899,27 +17643,27 @@
       </c>
       <c r="N76" s="8">
         <f t="shared" si="12"/>
-        <v>3139559.6399999997</v>
+        <v>3115434.6999999997</v>
       </c>
       <c r="O76" s="8">
         <f t="shared" si="13"/>
-        <v>53729</v>
+        <v>52764.5</v>
       </c>
       <c r="P76" s="8">
         <f t="shared" si="14"/>
-        <v>347</v>
+        <v>423</v>
       </c>
       <c r="Q76" s="9">
         <f t="shared" si="15"/>
-        <v>135715.83458213258</v>
+        <v>132571.68936170213</v>
       </c>
       <c r="R76" s="9">
         <f t="shared" si="16"/>
-        <v>2322.579250720461</v>
+        <v>2245.2978723404258</v>
       </c>
       <c r="S76" s="10">
         <f t="shared" si="17"/>
-        <v>1.6564954715158904</v>
+        <v>1.6487309747128009</v>
       </c>
       <c r="T76" s="11">
         <v>3600483.2</v>
@@ -17011,12 +17755,24 @@
       <c r="AW76" s="13">
         <v>1.59612368342398</v>
       </c>
-      <c r="AX76" s="11"/>
-      <c r="AY76" s="11"/>
-      <c r="AZ76" s="11"/>
-      <c r="BA76" s="12"/>
-      <c r="BB76" s="12"/>
-      <c r="BC76" s="13"/>
+      <c r="AX76" s="11">
+        <v>2994810</v>
+      </c>
+      <c r="AY76" s="11">
+        <v>47942</v>
+      </c>
+      <c r="AZ76" s="11">
+        <v>76</v>
+      </c>
+      <c r="BA76" s="12">
+        <v>118216.18421052631</v>
+      </c>
+      <c r="BB76" s="12">
+        <v>1892.447368421052</v>
+      </c>
+      <c r="BC76" s="13">
+        <v>1.609908490697354</v>
+      </c>
       <c r="BD76" s="11"/>
       <c r="BE76" s="11"/>
       <c r="BF76" s="11"/>
@@ -17097,27 +17853,27 @@
       </c>
       <c r="N77" s="8">
         <f t="shared" si="12"/>
-        <v>4288535</v>
+        <v>4424585.833333333</v>
       </c>
       <c r="O77" s="8">
         <f t="shared" si="13"/>
-        <v>19207.8</v>
+        <v>20308.333333333332</v>
       </c>
       <c r="P77" s="8">
         <f t="shared" si="14"/>
-        <v>352</v>
+        <v>432</v>
       </c>
       <c r="Q77" s="9">
         <f t="shared" si="15"/>
-        <v>182750.07102272726</v>
+        <v>184357.74305555556</v>
       </c>
       <c r="R77" s="9">
         <f t="shared" si="16"/>
-        <v>818.5142045454545</v>
+        <v>846.18055555555543</v>
       </c>
       <c r="S77" s="10">
         <f t="shared" si="17"/>
-        <v>0.85182290769886038</v>
+        <v>0.86051871654804579</v>
       </c>
       <c r="T77" s="11">
         <v>4959341</v>
@@ -17209,12 +17965,24 @@
       <c r="AW77" s="13">
         <v>0.88089355135715419</v>
       </c>
-      <c r="AX77" s="11"/>
-      <c r="AY77" s="11"/>
-      <c r="AZ77" s="11"/>
-      <c r="BA77" s="12"/>
-      <c r="BB77" s="12"/>
-      <c r="BC77" s="13"/>
+      <c r="AX77" s="11">
+        <v>5104840</v>
+      </c>
+      <c r="AY77" s="11">
+        <v>25811</v>
+      </c>
+      <c r="AZ77" s="11">
+        <v>80</v>
+      </c>
+      <c r="BA77" s="12">
+        <v>191431.5</v>
+      </c>
+      <c r="BB77" s="12">
+        <v>967.91249999999991</v>
+      </c>
+      <c r="BC77" s="13">
+        <v>0.90399776079397332</v>
+      </c>
       <c r="BD77" s="11"/>
       <c r="BE77" s="11"/>
       <c r="BF77" s="11"/>
@@ -17295,27 +18063,27 @@
       </c>
       <c r="N78" s="8">
         <f t="shared" si="12"/>
-        <v>5061373.4000000004</v>
+        <v>5096673</v>
       </c>
       <c r="O78" s="8">
         <f t="shared" si="13"/>
-        <v>34135.199999999997</v>
+        <v>35338.5</v>
       </c>
       <c r="P78" s="8">
         <f t="shared" si="14"/>
-        <v>357</v>
+        <v>434</v>
       </c>
       <c r="Q78" s="9">
         <f t="shared" si="15"/>
-        <v>212662.74789915964</v>
+        <v>211382.75115207373</v>
       </c>
       <c r="R78" s="9">
         <f t="shared" si="16"/>
-        <v>1434.2521008403362</v>
+        <v>1465.6520737327189</v>
       </c>
       <c r="S78" s="10">
         <f t="shared" si="17"/>
-        <v>1.0482940431267838</v>
+        <v>1.0612919402421765</v>
       </c>
       <c r="T78" s="11">
         <v>5415922</v>
@@ -17407,12 +18175,24 @@
       <c r="AW78" s="13">
         <v>1.157785537991032</v>
       </c>
-      <c r="AX78" s="11"/>
-      <c r="AY78" s="11"/>
-      <c r="AZ78" s="11"/>
-      <c r="BA78" s="12"/>
-      <c r="BB78" s="12"/>
-      <c r="BC78" s="13"/>
+      <c r="AX78" s="11">
+        <v>5273171</v>
+      </c>
+      <c r="AY78" s="11">
+        <v>41355</v>
+      </c>
+      <c r="AZ78" s="11">
+        <v>77</v>
+      </c>
+      <c r="BA78" s="12">
+        <v>205448.22077922069</v>
+      </c>
+      <c r="BB78" s="12">
+        <v>1611.2337662337659</v>
+      </c>
+      <c r="BC78" s="13">
+        <v>1.1262814258191409</v>
+      </c>
       <c r="BD78" s="11"/>
       <c r="BE78" s="11"/>
       <c r="BF78" s="11"/>
@@ -17493,27 +18273,27 @@
       </c>
       <c r="N79" s="8">
         <f t="shared" ref="N79:N111" si="18">IFERROR(AVERAGE(T79,Z79,AF79,AL79,AR79,AX79,BD79,BJ79,BP79,BV79,CB79,CH79)," ")</f>
-        <v>4877409.5999999996</v>
+        <v>5022860.166666667</v>
       </c>
       <c r="O79" s="8">
         <f t="shared" ref="O79:O111" si="19">IFERROR(AVERAGE(U79,AA79,AG79,AM79,AS79,AY79,BE79,BK79,BQ79,BW79,CC79,CI79)," ")</f>
-        <v>30302.400000000001</v>
+        <v>30029.833333333332</v>
       </c>
       <c r="P79" s="8">
         <f t="shared" ref="P79:P111" si="20">IFERROR(SUM(V79,AB79,AH79,AN79,AT79,AZ79,BF79,BL79,BR79,BX79,CD79,CJ79)," ")</f>
-        <v>353</v>
+        <v>430</v>
       </c>
       <c r="Q79" s="9">
         <f t="shared" ref="Q79:Q109" si="21">IFERROR(SUM(T79,Z79,AF79,AL79,AR79,AX79,BD79,BJ79,BP79,BV79,CB79,CH79)/P79*3," ")</f>
-        <v>207255.3654390935</v>
+        <v>210259.26279069768</v>
       </c>
       <c r="R79" s="9">
         <f t="shared" ref="R79:R111" si="22">IFERROR(SUM(U79,AA79,AG79,AM79,AS79,AY79,BE79,BK79,BQ79,BW79,CC79,CI79)/P79*3," ")</f>
-        <v>1287.6373937677054</v>
+        <v>1257.0627906976745</v>
       </c>
       <c r="S79" s="10">
         <f t="shared" ref="S79:S111" si="23">IFERROR(AVERAGE(Y79,AE79,AK79,AQ79,AW79,BC79,BI79,BO79,BU79,CA79,CG79,CM79)," ")</f>
-        <v>1.004989508312601</v>
+        <v>0.98680274518980704</v>
       </c>
       <c r="T79" s="11">
         <v>5601093</v>
@@ -17605,12 +18385,24 @@
       <c r="AW79" s="13">
         <v>1.0762335604091</v>
       </c>
-      <c r="AX79" s="11"/>
-      <c r="AY79" s="11"/>
-      <c r="AZ79" s="11"/>
-      <c r="BA79" s="12"/>
-      <c r="BB79" s="12"/>
-      <c r="BC79" s="13"/>
+      <c r="AX79" s="11">
+        <v>5750113</v>
+      </c>
+      <c r="AY79" s="11">
+        <v>28667</v>
+      </c>
+      <c r="AZ79" s="11">
+        <v>77</v>
+      </c>
+      <c r="BA79" s="12">
+        <v>224030.37662337659</v>
+      </c>
+      <c r="BB79" s="12">
+        <v>1116.896103896104</v>
+      </c>
+      <c r="BC79" s="13">
+        <v>0.89586892957583686</v>
+      </c>
       <c r="BD79" s="11"/>
       <c r="BE79" s="11"/>
       <c r="BF79" s="11"/>
@@ -17691,27 +18483,27 @@
       </c>
       <c r="N80" s="8">
         <f t="shared" si="18"/>
-        <v>4921562.4000000004</v>
+        <v>4955324.833333333</v>
       </c>
       <c r="O80" s="8">
         <f t="shared" si="19"/>
-        <v>158321.60000000001</v>
+        <v>159602.83333333334</v>
       </c>
       <c r="P80" s="8">
         <f t="shared" si="20"/>
-        <v>335</v>
+        <v>401</v>
       </c>
       <c r="Q80" s="9">
         <f t="shared" si="21"/>
-        <v>220368.46567164181</v>
+        <v>222433.53366583542</v>
       </c>
       <c r="R80" s="9">
         <f t="shared" si="22"/>
-        <v>7089.0268656716416</v>
+        <v>7164.216957605985</v>
       </c>
       <c r="S80" s="10">
         <f t="shared" si="23"/>
-        <v>2.2821275074797951</v>
+        <v>2.2835670819043292</v>
       </c>
       <c r="T80" s="11">
         <v>5213937</v>
@@ -17803,12 +18595,24 @@
       <c r="AW80" s="13">
         <v>2.273254954098352</v>
       </c>
-      <c r="AX80" s="11"/>
-      <c r="AY80" s="11"/>
-      <c r="AZ80" s="11"/>
-      <c r="BA80" s="12"/>
-      <c r="BB80" s="12"/>
-      <c r="BC80" s="13"/>
+      <c r="AX80" s="11">
+        <v>5124137</v>
+      </c>
+      <c r="AY80" s="11">
+        <v>166009</v>
+      </c>
+      <c r="AZ80" s="11">
+        <v>66</v>
+      </c>
+      <c r="BA80" s="12">
+        <v>232915.31818181821</v>
+      </c>
+      <c r="BB80" s="12">
+        <v>7545.8636363636369</v>
+      </c>
+      <c r="BC80" s="13">
+        <v>2.290764954026999</v>
+      </c>
       <c r="BD80" s="11"/>
       <c r="BE80" s="11"/>
       <c r="BF80" s="11"/>
@@ -17889,27 +18693,27 @@
       </c>
       <c r="N81" s="8">
         <f t="shared" si="18"/>
-        <v>2641745.4</v>
+        <v>2715452</v>
       </c>
       <c r="O81" s="8">
         <f t="shared" si="19"/>
-        <v>55700.4</v>
+        <v>55796.333333333336</v>
       </c>
       <c r="P81" s="8">
         <f t="shared" si="20"/>
-        <v>319</v>
+        <v>393</v>
       </c>
       <c r="Q81" s="9">
         <f t="shared" si="21"/>
-        <v>124220.00313479625</v>
+        <v>124371.84732824427</v>
       </c>
       <c r="R81" s="9">
         <f t="shared" si="22"/>
-        <v>2619.1410658307209</v>
+        <v>2555.5572519083967</v>
       </c>
       <c r="S81" s="10">
         <f t="shared" si="23"/>
-        <v>1.8619062747611461</v>
+        <v>1.8380651011573486</v>
       </c>
       <c r="T81" s="11">
         <v>3606826</v>
@@ -18001,12 +18805,24 @@
       <c r="AW81" s="13">
         <v>1.8038131819466581</v>
       </c>
-      <c r="AX81" s="11"/>
-      <c r="AY81" s="11"/>
-      <c r="AZ81" s="11"/>
-      <c r="BA81" s="12"/>
-      <c r="BB81" s="12"/>
-      <c r="BC81" s="13"/>
+      <c r="AX81" s="11">
+        <v>3083985</v>
+      </c>
+      <c r="AY81" s="11">
+        <v>56276</v>
+      </c>
+      <c r="AZ81" s="11">
+        <v>74</v>
+      </c>
+      <c r="BA81" s="12">
+        <v>125026.41891891891</v>
+      </c>
+      <c r="BB81" s="12">
+        <v>2281.4594594594591</v>
+      </c>
+      <c r="BC81" s="13">
+        <v>1.7188592331383601</v>
+      </c>
       <c r="BD81" s="11"/>
       <c r="BE81" s="11"/>
       <c r="BF81" s="11"/>
@@ -18087,27 +18903,27 @@
       </c>
       <c r="N82" s="8">
         <f t="shared" si="18"/>
-        <v>2875665</v>
+        <v>2802313.3333333335</v>
       </c>
       <c r="O82" s="8">
         <f t="shared" si="19"/>
-        <v>52701.8</v>
+        <v>51030.166666666664</v>
       </c>
       <c r="P82" s="8">
         <f t="shared" si="20"/>
-        <v>327</v>
+        <v>397</v>
       </c>
       <c r="Q82" s="9">
         <f t="shared" si="21"/>
-        <v>131911.23853211009</v>
+        <v>127057.02770780856</v>
       </c>
       <c r="R82" s="9">
         <f t="shared" si="22"/>
-        <v>2417.5137614678897</v>
+        <v>2313.7103274559195</v>
       </c>
       <c r="S82" s="10">
         <f t="shared" si="23"/>
-        <v>1.7441308954061987</v>
+        <v>1.7343205707935578</v>
       </c>
       <c r="T82" s="11">
         <v>4247045</v>
@@ -18199,12 +19015,24 @@
       <c r="AW82" s="13">
         <v>1.735409081268064</v>
       </c>
-      <c r="AX82" s="11"/>
-      <c r="AY82" s="11"/>
-      <c r="AZ82" s="11"/>
-      <c r="BA82" s="12"/>
-      <c r="BB82" s="12"/>
-      <c r="BC82" s="13"/>
+      <c r="AX82" s="11">
+        <v>2435555</v>
+      </c>
+      <c r="AY82" s="11">
+        <v>42672</v>
+      </c>
+      <c r="AZ82" s="11">
+        <v>70</v>
+      </c>
+      <c r="BA82" s="12">
+        <v>104380.92857142859</v>
+      </c>
+      <c r="BB82" s="12">
+        <v>1828.8</v>
+      </c>
+      <c r="BC82" s="13">
+        <v>1.685268947730354</v>
+      </c>
       <c r="BD82" s="11"/>
       <c r="BE82" s="11"/>
       <c r="BF82" s="11"/>
@@ -18285,27 +19113,27 @@
       </c>
       <c r="N83" s="8">
         <f t="shared" si="18"/>
-        <v>2278448.1</v>
+        <v>2356305.9166666665</v>
       </c>
       <c r="O83" s="8">
         <f t="shared" si="19"/>
-        <v>65066.400000000001</v>
+        <v>66408.666666666672</v>
       </c>
       <c r="P83" s="8">
         <f t="shared" si="20"/>
-        <v>321</v>
+        <v>396</v>
       </c>
       <c r="Q83" s="9">
         <f t="shared" si="21"/>
-        <v>106469.53738317758</v>
+        <v>107104.81439393939</v>
       </c>
       <c r="R83" s="9">
         <f t="shared" si="22"/>
-        <v>3040.4859813084113</v>
+        <v>3018.5757575757575</v>
       </c>
       <c r="S83" s="10">
         <f t="shared" si="23"/>
-        <v>2.1497025405264849</v>
+        <v>2.1375415625117511</v>
       </c>
       <c r="T83" s="11">
         <v>3362634.5</v>
@@ -18397,12 +19225,24 @@
       <c r="AW83" s="13">
         <v>2.092452042503874</v>
       </c>
-      <c r="AX83" s="11"/>
-      <c r="AY83" s="11"/>
-      <c r="AZ83" s="11"/>
-      <c r="BA83" s="12"/>
-      <c r="BB83" s="12"/>
-      <c r="BC83" s="13"/>
+      <c r="AX83" s="11">
+        <v>2745595</v>
+      </c>
+      <c r="AY83" s="11">
+        <v>73120</v>
+      </c>
+      <c r="AZ83" s="11">
+        <v>75</v>
+      </c>
+      <c r="BA83" s="12">
+        <v>109823.8</v>
+      </c>
+      <c r="BB83" s="12">
+        <v>2924.8</v>
+      </c>
+      <c r="BC83" s="13">
+        <v>2.076736672438082</v>
+      </c>
       <c r="BD83" s="11"/>
       <c r="BE83" s="11"/>
       <c r="BF83" s="11"/>
@@ -18483,27 +19323,27 @@
       </c>
       <c r="N84" s="8">
         <f t="shared" si="18"/>
-        <v>2154352.2999999998</v>
+        <v>2182741.5833333335</v>
       </c>
       <c r="O84" s="8">
         <f t="shared" si="19"/>
-        <v>151170.4</v>
+        <v>155613.66666666666</v>
       </c>
       <c r="P84" s="8">
         <f t="shared" si="20"/>
-        <v>352</v>
+        <v>432</v>
       </c>
       <c r="Q84" s="9">
         <f t="shared" si="21"/>
-        <v>91804.785511363632</v>
+        <v>90947.565972222219</v>
       </c>
       <c r="R84" s="9">
         <f t="shared" si="22"/>
-        <v>6441.920454545454</v>
+        <v>6483.9027777777783</v>
       </c>
       <c r="S84" s="10">
         <f t="shared" si="23"/>
-        <v>3.3737691089413948</v>
+        <v>3.398409723711493</v>
       </c>
       <c r="T84" s="11">
         <v>2176614</v>
@@ -18595,12 +19435,24 @@
       <c r="AW84" s="13">
         <v>3.4157506450097612</v>
       </c>
-      <c r="AX84" s="11"/>
-      <c r="AY84" s="11"/>
-      <c r="AZ84" s="11"/>
-      <c r="BA84" s="12"/>
-      <c r="BB84" s="12"/>
-      <c r="BC84" s="13"/>
+      <c r="AX84" s="11">
+        <v>2324688</v>
+      </c>
+      <c r="AY84" s="11">
+        <v>177830</v>
+      </c>
+      <c r="AZ84" s="11">
+        <v>80</v>
+      </c>
+      <c r="BA84" s="12">
+        <v>87175.799999999988</v>
+      </c>
+      <c r="BB84" s="12">
+        <v>6668.625</v>
+      </c>
+      <c r="BC84" s="13">
+        <v>3.5216127975619811</v>
+      </c>
       <c r="BD84" s="11"/>
       <c r="BE84" s="11"/>
       <c r="BF84" s="11"/>
@@ -18681,27 +19533,27 @@
       </c>
       <c r="N85" s="8">
         <f t="shared" si="18"/>
-        <v>1280434.6000000001</v>
+        <v>1233398.5</v>
       </c>
       <c r="O85" s="8">
         <f t="shared" si="19"/>
-        <v>123983.6</v>
+        <v>123393.5</v>
       </c>
       <c r="P85" s="8">
         <f t="shared" si="20"/>
-        <v>349</v>
+        <v>420</v>
       </c>
       <c r="Q85" s="9">
         <f t="shared" si="21"/>
-        <v>55033.005730659017</v>
+        <v>52859.935714285719</v>
       </c>
       <c r="R85" s="9">
         <f t="shared" si="22"/>
-        <v>5328.8080229226362</v>
+        <v>5288.2928571428574</v>
       </c>
       <c r="S85" s="10">
         <f t="shared" si="23"/>
-        <v>4.0460728617047872</v>
+        <v>4.1089559222048742</v>
       </c>
       <c r="T85" s="11">
         <v>1663594</v>
@@ -18793,12 +19645,24 @@
       <c r="AW85" s="13">
         <v>4.7059341467146378</v>
       </c>
-      <c r="AX85" s="11"/>
-      <c r="AY85" s="11"/>
-      <c r="AZ85" s="11"/>
-      <c r="BA85" s="12"/>
-      <c r="BB85" s="12"/>
-      <c r="BC85" s="13"/>
+      <c r="AX85" s="11">
+        <v>998218</v>
+      </c>
+      <c r="AY85" s="11">
+        <v>120443</v>
+      </c>
+      <c r="AZ85" s="11">
+        <v>71</v>
+      </c>
+      <c r="BA85" s="12">
+        <v>42178.225352112677</v>
+      </c>
+      <c r="BB85" s="12">
+        <v>5089.140845070423</v>
+      </c>
+      <c r="BC85" s="13">
+        <v>4.423371224705309</v>
+      </c>
       <c r="BD85" s="11"/>
       <c r="BE85" s="11"/>
       <c r="BF85" s="11"/>
@@ -18879,27 +19743,27 @@
       </c>
       <c r="N86" s="8">
         <f t="shared" si="18"/>
-        <v>3025197.8</v>
+        <v>3011711.1666666665</v>
       </c>
       <c r="O86" s="8">
         <f t="shared" si="19"/>
-        <v>73806.399999999994</v>
+        <v>73500.833333333328</v>
       </c>
       <c r="P86" s="8">
         <f t="shared" si="20"/>
-        <v>352</v>
+        <v>430</v>
       </c>
       <c r="Q86" s="9">
         <f t="shared" si="21"/>
-        <v>128914.67897727274</v>
+        <v>126071.63023255815</v>
       </c>
       <c r="R86" s="9">
         <f t="shared" si="22"/>
-        <v>3145.159090909091</v>
+        <v>3076.7790697674418</v>
       </c>
       <c r="S86" s="10">
         <f t="shared" si="23"/>
-        <v>1.978866741165163</v>
+        <v>1.9806204367251627</v>
       </c>
       <c r="T86" s="11">
         <v>3712214</v>
@@ -18991,12 +19855,24 @@
       <c r="AW86" s="13">
         <v>1.8652485491131039</v>
       </c>
-      <c r="AX86" s="11"/>
-      <c r="AY86" s="11"/>
-      <c r="AZ86" s="11"/>
-      <c r="BA86" s="12"/>
-      <c r="BB86" s="12"/>
-      <c r="BC86" s="13"/>
+      <c r="AX86" s="11">
+        <v>2944278</v>
+      </c>
+      <c r="AY86" s="11">
+        <v>71973</v>
+      </c>
+      <c r="AZ86" s="11">
+        <v>78</v>
+      </c>
+      <c r="BA86" s="12">
+        <v>113241.4615384615</v>
+      </c>
+      <c r="BB86" s="12">
+        <v>2768.1923076923081</v>
+      </c>
+      <c r="BC86" s="13">
+        <v>1.9893889145251611</v>
+      </c>
       <c r="BD86" s="11"/>
       <c r="BE86" s="11"/>
       <c r="BF86" s="11"/>
@@ -19077,27 +19953,27 @@
       </c>
       <c r="N87" s="8">
         <f t="shared" si="18"/>
-        <v>2877775.6</v>
+        <v>2927074.6666666665</v>
       </c>
       <c r="O87" s="8">
         <f t="shared" si="19"/>
-        <v>69890.399999999994</v>
+        <v>70338.166666666672</v>
       </c>
       <c r="P87" s="8">
         <f t="shared" si="20"/>
-        <v>355</v>
+        <v>430</v>
       </c>
       <c r="Q87" s="9">
         <f t="shared" si="21"/>
-        <v>121596.15211267606</v>
+        <v>122528.70697674419</v>
       </c>
       <c r="R87" s="9">
         <f t="shared" si="22"/>
-        <v>2953.1154929577465</v>
+        <v>2944.3883720930235</v>
       </c>
       <c r="S87" s="10">
         <f t="shared" si="23"/>
-        <v>1.9822645927281435</v>
+        <v>1.9726610598792726</v>
       </c>
       <c r="T87" s="11">
         <v>2997988</v>
@@ -19189,12 +20065,24 @@
       <c r="AW87" s="13">
         <v>1.9565381505876711</v>
       </c>
-      <c r="AX87" s="11"/>
-      <c r="AY87" s="11"/>
-      <c r="AZ87" s="11"/>
-      <c r="BA87" s="12"/>
-      <c r="BB87" s="12"/>
-      <c r="BC87" s="13"/>
+      <c r="AX87" s="11">
+        <v>3173570</v>
+      </c>
+      <c r="AY87" s="11">
+        <v>72577</v>
+      </c>
+      <c r="AZ87" s="11">
+        <v>75</v>
+      </c>
+      <c r="BA87" s="12">
+        <v>126942.8</v>
+      </c>
+      <c r="BB87" s="12">
+        <v>2903.08</v>
+      </c>
+      <c r="BC87" s="13">
+        <v>1.924643395634918</v>
+      </c>
       <c r="BD87" s="11"/>
       <c r="BE87" s="11"/>
       <c r="BF87" s="11"/>
@@ -19275,27 +20163,27 @@
       </c>
       <c r="N88" s="8">
         <f t="shared" si="18"/>
-        <v>2522817.4</v>
+        <v>2649996.8333333335</v>
       </c>
       <c r="O88" s="8">
         <f t="shared" si="19"/>
-        <v>64390.8</v>
+        <v>66860.833333333328</v>
       </c>
       <c r="P88" s="8">
         <f t="shared" si="20"/>
-        <v>354</v>
+        <v>431</v>
       </c>
       <c r="Q88" s="9">
         <f t="shared" si="21"/>
-        <v>106899.04237288135</v>
+        <v>110672.72157772622</v>
       </c>
       <c r="R88" s="9">
         <f t="shared" si="22"/>
-        <v>2728.4237288135596</v>
+        <v>2792.3317865429235</v>
       </c>
       <c r="S88" s="10">
         <f t="shared" si="23"/>
-        <v>2.0481246253453946</v>
+        <v>2.0361562915446427</v>
       </c>
       <c r="T88" s="11">
         <v>2265706</v>
@@ -19387,12 +20275,24 @@
       <c r="AW88" s="13">
         <v>2.0305021350401931</v>
       </c>
-      <c r="AX88" s="11"/>
-      <c r="AY88" s="11"/>
-      <c r="AZ88" s="11"/>
-      <c r="BA88" s="12"/>
-      <c r="BB88" s="12"/>
-      <c r="BC88" s="13"/>
+      <c r="AX88" s="11">
+        <v>3285894</v>
+      </c>
+      <c r="AY88" s="11">
+        <v>79211</v>
+      </c>
+      <c r="AZ88" s="11">
+        <v>77</v>
+      </c>
+      <c r="BA88" s="12">
+        <v>128021.8441558442</v>
+      </c>
+      <c r="BB88" s="12">
+        <v>3086.1428571428569</v>
+      </c>
+      <c r="BC88" s="13">
+        <v>1.976314622540883</v>
+      </c>
       <c r="BD88" s="11"/>
       <c r="BE88" s="11"/>
       <c r="BF88" s="11"/>
@@ -19473,27 +20373,27 @@
       </c>
       <c r="N89" s="8">
         <f t="shared" si="18"/>
-        <v>2940099.3280000002</v>
+        <v>3046513.6066666669</v>
       </c>
       <c r="O89" s="8">
         <f t="shared" si="19"/>
-        <v>26358.799999999999</v>
+        <v>28318.833333333332</v>
       </c>
       <c r="P89" s="8">
         <f t="shared" si="20"/>
-        <v>350</v>
+        <v>426</v>
       </c>
       <c r="Q89" s="9">
         <f t="shared" si="21"/>
-        <v>126004.25691428572</v>
+        <v>128725.92704225353</v>
       </c>
       <c r="R89" s="9">
         <f t="shared" si="22"/>
-        <v>1129.6628571428571</v>
+        <v>1196.5704225352113</v>
       </c>
       <c r="S89" s="10">
         <f t="shared" si="23"/>
-        <v>1.1979375226438498</v>
+        <v>1.2172049656313837</v>
       </c>
       <c r="T89" s="11">
         <v>3721474.08</v>
@@ -19585,12 +20485,24 @@
       <c r="AW89" s="13">
         <v>1.099334795290261</v>
       </c>
-      <c r="AX89" s="11"/>
-      <c r="AY89" s="11"/>
-      <c r="AZ89" s="11"/>
-      <c r="BA89" s="12"/>
-      <c r="BB89" s="12"/>
-      <c r="BC89" s="13"/>
+      <c r="AX89" s="11">
+        <v>3578585</v>
+      </c>
+      <c r="AY89" s="11">
+        <v>38119</v>
+      </c>
+      <c r="AZ89" s="11">
+        <v>76</v>
+      </c>
+      <c r="BA89" s="12">
+        <v>141259.93421052629</v>
+      </c>
+      <c r="BB89" s="12">
+        <v>1504.6973684210529</v>
+      </c>
+      <c r="BC89" s="13">
+        <v>1.313542180569053</v>
+      </c>
       <c r="BD89" s="11"/>
       <c r="BE89" s="11"/>
       <c r="BF89" s="11"/>
@@ -19671,27 +20583,27 @@
       </c>
       <c r="N90" s="8">
         <f t="shared" si="18"/>
-        <v>4750034.2</v>
+        <v>4665152.166666667</v>
       </c>
       <c r="O90" s="8">
         <f t="shared" si="19"/>
-        <v>55514.2</v>
+        <v>54953.666666666664</v>
       </c>
       <c r="P90" s="8">
         <f t="shared" si="20"/>
-        <v>354</v>
+        <v>430</v>
       </c>
       <c r="Q90" s="9">
         <f t="shared" si="21"/>
-        <v>201272.63559322036</v>
+        <v>195285.43953488371</v>
       </c>
       <c r="R90" s="9">
         <f t="shared" si="22"/>
-        <v>2352.2966101694915</v>
+        <v>2300.3860465116277</v>
       </c>
       <c r="S90" s="10">
         <f t="shared" si="23"/>
-        <v>1.3847751220137852</v>
+        <v>1.3892472571709444</v>
       </c>
       <c r="T90" s="11">
         <v>4835277</v>
@@ -19783,12 +20695,24 @@
       <c r="AW90" s="13">
         <v>1.4203447267069591</v>
       </c>
-      <c r="AX90" s="11"/>
-      <c r="AY90" s="11"/>
-      <c r="AZ90" s="11"/>
-      <c r="BA90" s="12"/>
-      <c r="BB90" s="12"/>
-      <c r="BC90" s="13"/>
+      <c r="AX90" s="11">
+        <v>4240742</v>
+      </c>
+      <c r="AY90" s="11">
+        <v>52151</v>
+      </c>
+      <c r="AZ90" s="11">
+        <v>76</v>
+      </c>
+      <c r="BA90" s="12">
+        <v>167397.71052631579</v>
+      </c>
+      <c r="BB90" s="12">
+        <v>2058.5921052631579</v>
+      </c>
+      <c r="BC90" s="13">
+        <v>1.4116079329567419</v>
+      </c>
       <c r="BD90" s="11"/>
       <c r="BE90" s="11"/>
       <c r="BF90" s="11"/>
@@ -19869,27 +20793,27 @@
       </c>
       <c r="N91" s="8">
         <f t="shared" si="18"/>
-        <v>6129660.2799999993</v>
+        <v>6146994.3999999994</v>
       </c>
       <c r="O91" s="8">
         <f t="shared" si="19"/>
-        <v>49250.8</v>
+        <v>48904.333333333336</v>
       </c>
       <c r="P91" s="8">
         <f t="shared" si="20"/>
-        <v>340</v>
+        <v>416</v>
       </c>
       <c r="Q91" s="9">
         <f t="shared" si="21"/>
-        <v>270426.1888235294</v>
+        <v>265975.7192307692</v>
       </c>
       <c r="R91" s="9">
         <f t="shared" si="22"/>
-        <v>2172.8294117647056</v>
+        <v>2116.0528846153848</v>
       </c>
       <c r="S91" s="10">
         <f t="shared" si="23"/>
-        <v>1.1427079086995928</v>
+        <v>1.1370940678961918</v>
       </c>
       <c r="T91" s="11">
         <v>7274414.3999999994</v>
@@ -19981,12 +20905,24 @@
       <c r="AW91" s="13">
         <v>1.138460338895851</v>
       </c>
-      <c r="AX91" s="11"/>
-      <c r="AY91" s="11"/>
-      <c r="AZ91" s="11"/>
-      <c r="BA91" s="12"/>
-      <c r="BB91" s="12"/>
-      <c r="BC91" s="13"/>
+      <c r="AX91" s="11">
+        <v>6233665</v>
+      </c>
+      <c r="AY91" s="11">
+        <v>47172</v>
+      </c>
+      <c r="AZ91" s="11">
+        <v>76</v>
+      </c>
+      <c r="BA91" s="12">
+        <v>246065.7236842105</v>
+      </c>
+      <c r="BB91" s="12">
+        <v>1862.052631578948</v>
+      </c>
+      <c r="BC91" s="13">
+        <v>1.1090248638791871</v>
+      </c>
       <c r="BD91" s="11"/>
       <c r="BE91" s="11"/>
       <c r="BF91" s="11"/>
@@ -20067,27 +21003,27 @@
       </c>
       <c r="N92" s="8">
         <f t="shared" si="18"/>
-        <v>5484248.7999999998</v>
+        <v>5479008.166666667</v>
       </c>
       <c r="O92" s="8">
         <f t="shared" si="19"/>
-        <v>32080</v>
+        <v>31738.5</v>
       </c>
       <c r="P92" s="8">
         <f t="shared" si="20"/>
-        <v>348</v>
+        <v>425</v>
       </c>
       <c r="Q92" s="9">
         <f t="shared" si="21"/>
-        <v>236390.03448275864</v>
+        <v>232052.11058823531</v>
       </c>
       <c r="R92" s="9">
         <f t="shared" si="22"/>
-        <v>1382.7586206896551</v>
+        <v>1344.2188235294118</v>
       </c>
       <c r="S92" s="10">
         <f t="shared" si="23"/>
-        <v>0.97179521362270971</v>
+        <v>0.96693022272234108</v>
       </c>
       <c r="T92" s="11">
         <v>5879996</v>
@@ -20179,12 +21115,24 @@
       <c r="AW92" s="13">
         <v>0.94966787967815314</v>
       </c>
-      <c r="AX92" s="11"/>
-      <c r="AY92" s="11"/>
-      <c r="AZ92" s="11"/>
-      <c r="BA92" s="12"/>
-      <c r="BB92" s="12"/>
-      <c r="BC92" s="13"/>
+      <c r="AX92" s="11">
+        <v>5452805</v>
+      </c>
+      <c r="AY92" s="11">
+        <v>30031</v>
+      </c>
+      <c r="AZ92" s="11">
+        <v>77</v>
+      </c>
+      <c r="BA92" s="12">
+        <v>212446.9480519481</v>
+      </c>
+      <c r="BB92" s="12">
+        <v>1170.0389610389609</v>
+      </c>
+      <c r="BC92" s="13">
+        <v>0.94260526822049751</v>
+      </c>
       <c r="BD92" s="11"/>
       <c r="BE92" s="11"/>
       <c r="BF92" s="11"/>
@@ -20265,27 +21213,27 @@
       </c>
       <c r="N93" s="8">
         <f t="shared" si="18"/>
-        <v>3226013.3439999996</v>
+        <v>3484388.9533333331</v>
       </c>
       <c r="O93" s="8">
         <f t="shared" si="19"/>
-        <v>16822.599999999999</v>
+        <v>18292.166666666668</v>
       </c>
       <c r="P93" s="8">
         <f t="shared" si="20"/>
-        <v>341</v>
+        <v>418</v>
       </c>
       <c r="Q93" s="9">
         <f t="shared" si="21"/>
-        <v>141906.7453372434</v>
+        <v>150045.45732057415</v>
       </c>
       <c r="R93" s="9">
         <f t="shared" si="22"/>
-        <v>739.99706744868035</v>
+        <v>787.70095693779899</v>
       </c>
       <c r="S93" s="10">
         <f t="shared" si="23"/>
-        <v>0.90610091026862472</v>
+        <v>0.91039000719490382</v>
       </c>
       <c r="T93" s="11">
         <v>4307185.76</v>
@@ -20377,12 +21325,24 @@
       <c r="AW93" s="13">
         <v>0.91751794801720277</v>
       </c>
-      <c r="AX93" s="11"/>
-      <c r="AY93" s="11"/>
-      <c r="AZ93" s="11"/>
-      <c r="BA93" s="12"/>
-      <c r="BB93" s="12"/>
-      <c r="BC93" s="13"/>
+      <c r="AX93" s="11">
+        <v>4776267</v>
+      </c>
+      <c r="AY93" s="11">
+        <v>25640</v>
+      </c>
+      <c r="AZ93" s="11">
+        <v>77</v>
+      </c>
+      <c r="BA93" s="12">
+        <v>186088.32467532469</v>
+      </c>
+      <c r="BB93" s="12">
+        <v>998.96103896103887</v>
+      </c>
+      <c r="BC93" s="13">
+        <v>0.93183549182629888</v>
+      </c>
       <c r="BD93" s="11"/>
       <c r="BE93" s="11"/>
       <c r="BF93" s="11"/>
@@ -20463,27 +21423,27 @@
       </c>
       <c r="N94" s="8">
         <f t="shared" si="18"/>
-        <v>3790428.5519999997</v>
+        <v>3899754.6266666665</v>
       </c>
       <c r="O94" s="8">
         <f t="shared" si="19"/>
-        <v>12543.4</v>
+        <v>13108</v>
       </c>
       <c r="P94" s="8">
         <f t="shared" si="20"/>
-        <v>326</v>
+        <v>398</v>
       </c>
       <c r="Q94" s="9">
         <f t="shared" si="21"/>
-        <v>174406.2217177914</v>
+        <v>176370.81226130651</v>
       </c>
       <c r="R94" s="9">
         <f t="shared" si="22"/>
-        <v>577.15030674846616</v>
+        <v>592.8241206030151</v>
       </c>
       <c r="S94" s="10">
         <f t="shared" si="23"/>
-        <v>0.73030874816492397</v>
+        <v>0.73530767376272665</v>
       </c>
       <c r="T94" s="11">
         <v>5182499.76</v>
@@ -20575,12 +21535,24 @@
       <c r="AW94" s="13">
         <v>0.80799079499525805</v>
       </c>
-      <c r="AX94" s="11"/>
-      <c r="AY94" s="11"/>
-      <c r="AZ94" s="11"/>
-      <c r="BA94" s="12"/>
-      <c r="BB94" s="12"/>
-      <c r="BC94" s="13"/>
+      <c r="AX94" s="11">
+        <v>4446385</v>
+      </c>
+      <c r="AY94" s="11">
+        <v>15931</v>
+      </c>
+      <c r="AZ94" s="11">
+        <v>72</v>
+      </c>
+      <c r="BA94" s="12">
+        <v>185266.04166666669</v>
+      </c>
+      <c r="BB94" s="12">
+        <v>663.79166666666663</v>
+      </c>
+      <c r="BC94" s="13">
+        <v>0.76030230175174052</v>
+      </c>
       <c r="BD94" s="11"/>
       <c r="BE94" s="11"/>
       <c r="BF94" s="11"/>
@@ -20661,27 +21633,27 @@
       </c>
       <c r="N95" s="8">
         <f t="shared" si="18"/>
-        <v>2528792</v>
+        <v>2537815.1666666665</v>
       </c>
       <c r="O95" s="8">
         <f t="shared" si="19"/>
-        <v>16613</v>
+        <v>16470.333333333332</v>
       </c>
       <c r="P95" s="8">
         <f t="shared" si="20"/>
-        <v>262</v>
+        <v>327</v>
       </c>
       <c r="Q95" s="9">
         <f t="shared" si="21"/>
-        <v>144778.16793893132</v>
+        <v>139696.24770642203</v>
       </c>
       <c r="R95" s="9">
         <f t="shared" si="22"/>
-        <v>951.12595419847321</v>
+        <v>906.62385321100919</v>
       </c>
       <c r="S95" s="10">
         <f t="shared" si="23"/>
-        <v>1.0319948222351258</v>
+        <v>1.0253178612713516</v>
       </c>
       <c r="T95" s="11">
         <v>3447426</v>
@@ -20773,12 +21745,24 @@
       <c r="AW95" s="13">
         <v>1.0014550343458659</v>
       </c>
-      <c r="AX95" s="11"/>
-      <c r="AY95" s="11"/>
-      <c r="AZ95" s="11"/>
-      <c r="BA95" s="12"/>
-      <c r="BB95" s="12"/>
-      <c r="BC95" s="13"/>
+      <c r="AX95" s="11">
+        <v>2582931</v>
+      </c>
+      <c r="AY95" s="11">
+        <v>15757</v>
+      </c>
+      <c r="AZ95" s="11">
+        <v>65</v>
+      </c>
+      <c r="BA95" s="12">
+        <v>119212.2</v>
+      </c>
+      <c r="BB95" s="12">
+        <v>727.2461538461539</v>
+      </c>
+      <c r="BC95" s="13">
+        <v>0.99193305645248109</v>
+      </c>
       <c r="BD95" s="11"/>
       <c r="BE95" s="11"/>
       <c r="BF95" s="11"/>
@@ -20859,27 +21843,27 @@
       </c>
       <c r="N96" s="8">
         <f t="shared" si="18"/>
-        <v>1277146</v>
+        <v>1472096.6666666667</v>
       </c>
       <c r="O96" s="8">
         <f t="shared" si="19"/>
-        <v>8077.2</v>
+        <v>9157.5</v>
       </c>
       <c r="P96" s="8">
         <f t="shared" si="20"/>
-        <v>158</v>
+        <v>224</v>
       </c>
       <c r="Q96" s="9">
         <f t="shared" si="21"/>
-        <v>121248.03797468354</v>
+        <v>118293.48214285716</v>
       </c>
       <c r="R96" s="9">
         <f t="shared" si="22"/>
-        <v>766.82278481012656</v>
+        <v>735.87053571428578</v>
       </c>
       <c r="S96" s="10">
         <f t="shared" si="23"/>
-        <v>1.0062433909627952</v>
+        <v>1.0021692088226952</v>
       </c>
       <c r="T96" s="11">
         <v>224676</v>
@@ -20971,12 +21955,24 @@
       <c r="AW96" s="13">
         <v>1.0680023538768491</v>
       </c>
-      <c r="AX96" s="11"/>
-      <c r="AY96" s="11"/>
-      <c r="AZ96" s="11"/>
-      <c r="BA96" s="12"/>
-      <c r="BB96" s="12"/>
-      <c r="BC96" s="13"/>
+      <c r="AX96" s="11">
+        <v>2446850</v>
+      </c>
+      <c r="AY96" s="11">
+        <v>14559</v>
+      </c>
+      <c r="AZ96" s="11">
+        <v>66</v>
+      </c>
+      <c r="BA96" s="12">
+        <v>111220.4545454545</v>
+      </c>
+      <c r="BB96" s="12">
+        <v>661.77272727272725</v>
+      </c>
+      <c r="BC96" s="13">
+        <v>0.98179829812219543</v>
+      </c>
       <c r="BD96" s="11"/>
       <c r="BE96" s="11"/>
       <c r="BF96" s="11"/>
@@ -21057,27 +22053,27 @@
       </c>
       <c r="N97" s="8">
         <f t="shared" si="18"/>
-        <v>3282436.4</v>
+        <v>3353397.3333333335</v>
       </c>
       <c r="O97" s="8">
         <f t="shared" si="19"/>
-        <v>13797.4</v>
+        <v>14094.666666666666</v>
       </c>
       <c r="P97" s="8">
         <f t="shared" si="20"/>
-        <v>265</v>
+        <v>325</v>
       </c>
       <c r="Q97" s="9">
         <f t="shared" si="21"/>
-        <v>185798.28679245283</v>
+        <v>185726.62153846154</v>
       </c>
       <c r="R97" s="9">
         <f t="shared" si="22"/>
-        <v>780.98490566037742</v>
+        <v>780.62769230769231</v>
       </c>
       <c r="S97" s="10">
         <f t="shared" si="23"/>
-        <v>0.8202118937329953</v>
+        <v>0.82016587111327555</v>
       </c>
       <c r="T97" s="11">
         <v>3842266</v>
@@ -21169,12 +22165,24 @@
       <c r="AW97" s="13">
         <v>0.82</v>
       </c>
-      <c r="AX97" s="11"/>
-      <c r="AY97" s="11"/>
-      <c r="AZ97" s="11"/>
-      <c r="BA97" s="12"/>
-      <c r="BB97" s="12"/>
-      <c r="BC97" s="13"/>
+      <c r="AX97" s="11">
+        <v>3708202</v>
+      </c>
+      <c r="AY97" s="11">
+        <v>15581</v>
+      </c>
+      <c r="AZ97" s="11">
+        <v>60</v>
+      </c>
+      <c r="BA97" s="12">
+        <v>185410.1</v>
+      </c>
+      <c r="BB97" s="12">
+        <v>779.05</v>
+      </c>
+      <c r="BC97" s="13">
+        <v>0.81993575801467711</v>
+      </c>
       <c r="BD97" s="11"/>
       <c r="BE97" s="11"/>
       <c r="BF97" s="11"/>
@@ -21255,27 +22263,27 @@
       </c>
       <c r="N98" s="8">
         <f t="shared" si="18"/>
-        <v>3425136.4</v>
+        <v>3265935.3984999997</v>
       </c>
       <c r="O98" s="8">
         <f t="shared" si="19"/>
-        <v>25468.6</v>
+        <v>24100.166666666668</v>
       </c>
       <c r="P98" s="8">
         <f t="shared" si="20"/>
-        <v>300</v>
+        <v>363</v>
       </c>
       <c r="Q98" s="9">
         <f t="shared" si="21"/>
-        <v>171256.82</v>
+        <v>161947.20984297519</v>
       </c>
       <c r="R98" s="9">
         <f t="shared" si="22"/>
-        <v>1273.43</v>
+        <v>1195.0495867768595</v>
       </c>
       <c r="S98" s="10">
         <f t="shared" si="23"/>
-        <v>1.117266178336435</v>
+        <v>1.1085543250272167</v>
       </c>
       <c r="T98" s="11">
         <v>5398924</v>
@@ -21367,12 +22375,24 @@
       <c r="AW98" s="13">
         <v>1.240560413162507</v>
       </c>
-      <c r="AX98" s="11"/>
-      <c r="AY98" s="11"/>
-      <c r="AZ98" s="11"/>
-      <c r="BA98" s="12"/>
-      <c r="BB98" s="12"/>
-      <c r="BC98" s="13"/>
+      <c r="AX98" s="11">
+        <v>2469930.3909999998</v>
+      </c>
+      <c r="AY98" s="11">
+        <v>17258</v>
+      </c>
+      <c r="AZ98" s="11">
+        <v>63</v>
+      </c>
+      <c r="BA98" s="12">
+        <v>117615.7329047619</v>
+      </c>
+      <c r="BB98" s="12">
+        <v>821.80952380952385</v>
+      </c>
+      <c r="BC98" s="13">
+        <v>1.064995058481125</v>
+      </c>
       <c r="BD98" s="11"/>
       <c r="BE98" s="11"/>
       <c r="BF98" s="11"/>
@@ -21453,27 +22473,27 @@
       </c>
       <c r="N99" s="8">
         <f t="shared" si="18"/>
-        <v>4730343</v>
+        <v>4876590.166666667</v>
       </c>
       <c r="O99" s="8">
         <f t="shared" si="19"/>
-        <v>23722</v>
+        <v>25432.333333333332</v>
       </c>
       <c r="P99" s="8">
         <f t="shared" si="20"/>
-        <v>348</v>
+        <v>426</v>
       </c>
       <c r="Q99" s="9">
         <f t="shared" si="21"/>
-        <v>203894.0948275862</v>
+        <v>206053.1056338028</v>
       </c>
       <c r="R99" s="9">
         <f t="shared" si="22"/>
-        <v>1022.5</v>
+        <v>1074.605633802817</v>
       </c>
       <c r="S99" s="10">
         <f t="shared" si="23"/>
-        <v>0.89550810807422909</v>
+        <v>0.9114388172553598</v>
       </c>
       <c r="T99" s="11">
         <v>4901698</v>
@@ -21565,12 +22585,24 @@
       <c r="AW99" s="13">
         <v>0.89130352813083735</v>
       </c>
-      <c r="AX99" s="11"/>
-      <c r="AY99" s="11"/>
-      <c r="AZ99" s="11"/>
-      <c r="BA99" s="12"/>
-      <c r="BB99" s="12"/>
-      <c r="BC99" s="13"/>
+      <c r="AX99" s="11">
+        <v>5607826</v>
+      </c>
+      <c r="AY99" s="11">
+        <v>33984</v>
+      </c>
+      <c r="AZ99" s="11">
+        <v>78</v>
+      </c>
+      <c r="BA99" s="12">
+        <v>215685.6153846154</v>
+      </c>
+      <c r="BB99" s="12">
+        <v>1307.0769230769231</v>
+      </c>
+      <c r="BC99" s="13">
+        <v>0.99109236316101301</v>
+      </c>
       <c r="BD99" s="11"/>
       <c r="BE99" s="11"/>
       <c r="BF99" s="11"/>
@@ -21651,27 +22683,27 @@
       </c>
       <c r="N100" s="8">
         <f t="shared" si="18"/>
-        <v>4864199</v>
+        <v>4913783.5</v>
       </c>
       <c r="O100" s="8">
         <f t="shared" si="19"/>
-        <v>41956.6</v>
+        <v>41642.5</v>
       </c>
       <c r="P100" s="8">
         <f t="shared" si="20"/>
-        <v>351</v>
+        <v>428</v>
       </c>
       <c r="Q100" s="9">
         <f t="shared" si="21"/>
-        <v>207871.75213675215</v>
+        <v>206654.44626168223</v>
       </c>
       <c r="R100" s="9">
         <f t="shared" si="22"/>
-        <v>1793.017094017094</v>
+        <v>1751.320093457944</v>
       </c>
       <c r="S100" s="10">
         <f t="shared" si="23"/>
-        <v>1.1876597285203288</v>
+        <v>1.1765955363404135</v>
       </c>
       <c r="T100" s="11">
         <v>5648674</v>
@@ -21763,12 +22795,24 @@
       <c r="AW100" s="13">
         <v>1.2362132734350431</v>
       </c>
-      <c r="AX100" s="11"/>
-      <c r="AY100" s="11"/>
-      <c r="AZ100" s="11"/>
-      <c r="BA100" s="12"/>
-      <c r="BB100" s="12"/>
-      <c r="BC100" s="13"/>
+      <c r="AX100" s="11">
+        <v>5161706</v>
+      </c>
+      <c r="AY100" s="11">
+        <v>40072</v>
+      </c>
+      <c r="AZ100" s="11">
+        <v>77</v>
+      </c>
+      <c r="BA100" s="12">
+        <v>201105.42857142861</v>
+      </c>
+      <c r="BB100" s="12">
+        <v>1561.2467532467531</v>
+      </c>
+      <c r="BC100" s="13">
+        <v>1.121274575440838</v>
+      </c>
       <c r="BD100" s="11"/>
       <c r="BE100" s="11"/>
       <c r="BF100" s="11"/>
@@ -21849,27 +22893,27 @@
       </c>
       <c r="N101" s="8">
         <f t="shared" si="18"/>
-        <v>4379177</v>
+        <v>4527442.833333333</v>
       </c>
       <c r="O101" s="8">
         <f t="shared" si="19"/>
-        <v>23118.2</v>
+        <v>23541</v>
       </c>
       <c r="P101" s="8">
         <f t="shared" si="20"/>
-        <v>349</v>
+        <v>429</v>
       </c>
       <c r="Q101" s="9">
         <f t="shared" si="21"/>
-        <v>188216.77650429797</v>
+        <v>189962.63636363635</v>
       </c>
       <c r="R101" s="9">
         <f t="shared" si="22"/>
-        <v>993.61891117478513</v>
+        <v>987.73426573426582</v>
       </c>
       <c r="S101" s="10">
         <f t="shared" si="23"/>
-        <v>0.92737271013635847</v>
+        <v>0.92044694981113351</v>
       </c>
       <c r="T101" s="11">
         <v>5198390</v>
@@ -21961,12 +23005,24 @@
       <c r="AW101" s="13">
         <v>0.9690815108807439</v>
       </c>
-      <c r="AX101" s="11"/>
-      <c r="AY101" s="11"/>
-      <c r="AZ101" s="11"/>
-      <c r="BA101" s="12"/>
-      <c r="BB101" s="12"/>
-      <c r="BC101" s="13"/>
+      <c r="AX101" s="11">
+        <v>5268772</v>
+      </c>
+      <c r="AY101" s="11">
+        <v>25655</v>
+      </c>
+      <c r="AZ101" s="11">
+        <v>80</v>
+      </c>
+      <c r="BA101" s="12">
+        <v>197578.95</v>
+      </c>
+      <c r="BB101" s="12">
+        <v>962.0625</v>
+      </c>
+      <c r="BC101" s="13">
+        <v>0.88581814818500904</v>
+      </c>
       <c r="BD101" s="11"/>
       <c r="BE101" s="11"/>
       <c r="BF101" s="11"/>
@@ -22047,27 +23103,27 @@
       </c>
       <c r="N102" s="8">
         <f t="shared" si="18"/>
-        <v>2285247.04</v>
+        <v>2272203.8666666667</v>
       </c>
       <c r="O102" s="8">
         <f t="shared" si="19"/>
-        <v>70996.800000000003</v>
+        <v>69329.333333333328</v>
       </c>
       <c r="P102" s="8">
         <f t="shared" si="20"/>
-        <v>348</v>
+        <v>427</v>
       </c>
       <c r="Q102" s="9">
         <f t="shared" si="21"/>
-        <v>98502.027586206881</v>
+        <v>95783.76955503512</v>
       </c>
       <c r="R102" s="9">
         <f t="shared" si="22"/>
-        <v>3060.2068965517242</v>
+        <v>2922.5480093676815</v>
       </c>
       <c r="S102" s="10">
         <f t="shared" si="23"/>
-        <v>2.2261150194662904</v>
+        <v>2.2077548992400788</v>
       </c>
       <c r="T102" s="11">
         <v>2396165.2000000002</v>
@@ -22159,12 +23215,24 @@
       <c r="AW102" s="13">
         <v>2.1634433015093388</v>
       </c>
-      <c r="AX102" s="11"/>
-      <c r="AY102" s="11"/>
-      <c r="AZ102" s="11"/>
-      <c r="BA102" s="12"/>
-      <c r="BB102" s="12"/>
-      <c r="BC102" s="13"/>
+      <c r="AX102" s="11">
+        <v>2206988</v>
+      </c>
+      <c r="AY102" s="11">
+        <v>60992</v>
+      </c>
+      <c r="AZ102" s="11">
+        <v>79</v>
+      </c>
+      <c r="BA102" s="12">
+        <v>83809.670886075939</v>
+      </c>
+      <c r="BB102" s="12">
+        <v>2316.1518987341769</v>
+      </c>
+      <c r="BC102" s="13">
+        <v>2.1159542981090218</v>
+      </c>
       <c r="BD102" s="11"/>
       <c r="BE102" s="11"/>
       <c r="BF102" s="11"/>
@@ -22245,27 +23313,27 @@
       </c>
       <c r="N103" s="8">
         <f t="shared" si="18"/>
-        <v>249480.6</v>
+        <v>245888.16666666666</v>
       </c>
       <c r="O103" s="8">
         <f t="shared" si="19"/>
-        <v>116788.8</v>
+        <v>116150</v>
       </c>
       <c r="P103" s="8">
         <f t="shared" si="20"/>
-        <v>339</v>
+        <v>415</v>
       </c>
       <c r="Q103" s="9">
         <f t="shared" si="21"/>
-        <v>11038.964601769912</v>
+        <v>10665.028915662651</v>
       </c>
       <c r="R103" s="9">
         <f t="shared" si="22"/>
-        <v>5167.646017699115</v>
+        <v>5037.8313253012047</v>
       </c>
       <c r="S103" s="10">
         <f t="shared" si="23"/>
-        <v>8.9646792606102466</v>
+        <v>8.9649134656310938</v>
       </c>
       <c r="T103" s="11">
         <v>274124</v>
@@ -22357,12 +23425,24 @@
       <c r="AW103" s="13">
         <v>10.52068465395535</v>
       </c>
-      <c r="AX103" s="11"/>
-      <c r="AY103" s="11"/>
-      <c r="AZ103" s="11"/>
-      <c r="BA103" s="12"/>
-      <c r="BB103" s="12"/>
-      <c r="BC103" s="13"/>
+      <c r="AX103" s="11">
+        <v>227926</v>
+      </c>
+      <c r="AY103" s="11">
+        <v>112956</v>
+      </c>
+      <c r="AZ103" s="11">
+        <v>76</v>
+      </c>
+      <c r="BA103" s="12">
+        <v>8997.0789473684217</v>
+      </c>
+      <c r="BB103" s="12">
+        <v>4458.7894736842109</v>
+      </c>
+      <c r="BC103" s="13">
+        <v>8.9660844907353248</v>
+      </c>
       <c r="BD103" s="11"/>
       <c r="BE103" s="11"/>
       <c r="BF103" s="11"/>
@@ -22443,27 +23523,27 @@
       </c>
       <c r="N104" s="8">
         <f t="shared" si="18"/>
-        <v>4534358.3360000001</v>
+        <v>5085178.4466666663</v>
       </c>
       <c r="O104" s="8">
         <f t="shared" si="19"/>
-        <v>5351</v>
+        <v>7282.666666666667</v>
       </c>
       <c r="P104" s="8">
         <f t="shared" si="20"/>
-        <v>293</v>
+        <v>369</v>
       </c>
       <c r="Q104" s="9">
         <f t="shared" si="21"/>
-        <v>232134.38580204779</v>
+        <v>248057.48520325206</v>
       </c>
       <c r="R104" s="9">
         <f t="shared" si="22"/>
-        <v>273.94197952218428</v>
+        <v>355.2520325203252</v>
       </c>
       <c r="S104" s="10">
         <f t="shared" si="23"/>
-        <v>0.43724599914479417</v>
+        <v>0.46254911436655183</v>
       </c>
       <c r="T104" s="11">
         <v>2471269.08</v>
@@ -22555,12 +23635,24 @@
       <c r="AW104" s="13">
         <v>0.39170865472207478</v>
       </c>
-      <c r="AX104" s="11"/>
-      <c r="AY104" s="11"/>
-      <c r="AZ104" s="11"/>
-      <c r="BA104" s="12"/>
-      <c r="BB104" s="12"/>
-      <c r="BC104" s="13"/>
+      <c r="AX104" s="11">
+        <v>7839279</v>
+      </c>
+      <c r="AY104" s="11">
+        <v>16941</v>
+      </c>
+      <c r="AZ104" s="11">
+        <v>76</v>
+      </c>
+      <c r="BA104" s="12">
+        <v>309445.2236842105</v>
+      </c>
+      <c r="BB104" s="12">
+        <v>668.72368421052636</v>
+      </c>
+      <c r="BC104" s="13">
+        <v>0.58906469047534005</v>
+      </c>
       <c r="BD104" s="11"/>
       <c r="BE104" s="11"/>
       <c r="BF104" s="11"/>
@@ -22641,27 +23733,27 @@
       </c>
       <c r="N105" s="8">
         <f t="shared" si="18"/>
-        <v>3210140.1260000002</v>
+        <v>4374036.6050000004</v>
       </c>
       <c r="O105" s="8">
         <f t="shared" si="19"/>
-        <v>5602</v>
+        <v>6366.666666666667</v>
       </c>
       <c r="P105" s="8">
         <f t="shared" si="20"/>
-        <v>316</v>
+        <v>391</v>
       </c>
       <c r="Q105" s="9">
         <f t="shared" si="21"/>
-        <v>152380.06927215192</v>
+        <v>201362.29895140667</v>
       </c>
       <c r="R105" s="9">
         <f t="shared" si="22"/>
-        <v>265.91772151898738</v>
+        <v>293.09462915601023</v>
       </c>
       <c r="S105" s="10">
         <f t="shared" si="23"/>
-        <v>0.50980286730721702</v>
+        <v>0.49173078306500778</v>
       </c>
       <c r="T105" s="11">
         <v>2163577.9500000002</v>
@@ -22753,12 +23845,24 @@
       <c r="AW105" s="13">
         <v>0.61414156824502897</v>
       </c>
-      <c r="AX105" s="11"/>
-      <c r="AY105" s="11"/>
-      <c r="AZ105" s="11"/>
-      <c r="BA105" s="12"/>
-      <c r="BB105" s="12"/>
-      <c r="BC105" s="13"/>
+      <c r="AX105" s="11">
+        <v>10193519</v>
+      </c>
+      <c r="AY105" s="11">
+        <v>10190</v>
+      </c>
+      <c r="AZ105" s="11">
+        <v>75</v>
+      </c>
+      <c r="BA105" s="12">
+        <v>407740.76</v>
+      </c>
+      <c r="BB105" s="12">
+        <v>407.6</v>
+      </c>
+      <c r="BC105" s="13">
+        <v>0.40137036185396152</v>
+      </c>
       <c r="BD105" s="11"/>
       <c r="BE105" s="11"/>
       <c r="BF105" s="11"/>
@@ -22839,27 +23943,27 @@
       </c>
       <c r="N106" s="8">
         <f t="shared" si="18"/>
-        <v>9191696</v>
+        <v>9250149.166666666</v>
       </c>
       <c r="O106" s="8">
         <f t="shared" si="19"/>
-        <v>165833.4</v>
+        <v>168340</v>
       </c>
       <c r="P106" s="8">
         <f t="shared" si="20"/>
-        <v>327</v>
+        <v>401</v>
       </c>
       <c r="Q106" s="9">
         <f t="shared" si="21"/>
-        <v>421637.43119266059</v>
+        <v>415218.66583541152</v>
       </c>
       <c r="R106" s="9">
         <f t="shared" si="22"/>
-        <v>7607.0366972477068</v>
+        <v>7556.4089775561097</v>
       </c>
       <c r="S106" s="10">
         <f t="shared" si="23"/>
-        <v>1.7050834072020151</v>
+        <v>1.7127907794501767</v>
       </c>
       <c r="T106" s="11">
         <v>10039950</v>
@@ -22951,12 +24055,24 @@
       <c r="AW106" s="13">
         <v>1.659468260714136</v>
       </c>
-      <c r="AX106" s="11"/>
-      <c r="AY106" s="11"/>
-      <c r="AZ106" s="11"/>
-      <c r="BA106" s="12"/>
-      <c r="BB106" s="12"/>
-      <c r="BC106" s="13"/>
+      <c r="AX106" s="11">
+        <v>9542415</v>
+      </c>
+      <c r="AY106" s="11">
+        <v>180873</v>
+      </c>
+      <c r="AZ106" s="11">
+        <v>74</v>
+      </c>
+      <c r="BA106" s="12">
+        <v>386854.66216216207</v>
+      </c>
+      <c r="BB106" s="12">
+        <v>7332.6891891891883</v>
+      </c>
+      <c r="BC106" s="13">
+        <v>1.751327640690985</v>
+      </c>
       <c r="BD106" s="11"/>
       <c r="BE106" s="11"/>
       <c r="BF106" s="11"/>
@@ -23037,27 +24153,27 @@
       </c>
       <c r="N107" s="8">
         <f t="shared" si="18"/>
-        <v>3872995.4</v>
+        <v>3706640</v>
       </c>
       <c r="O107" s="8">
         <f t="shared" si="19"/>
-        <v>207591.2</v>
+        <v>200687</v>
       </c>
       <c r="P107" s="8">
         <f t="shared" si="20"/>
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="Q107" s="9">
         <f t="shared" si="21"/>
-        <v>169372.97667638486</v>
+        <v>168059.24433249369</v>
       </c>
       <c r="R107" s="9">
         <f t="shared" si="22"/>
-        <v>9078.3323615160334</v>
+        <v>9099.1586901763221</v>
       </c>
       <c r="S107" s="10">
         <f t="shared" si="23"/>
-        <v>2.9661944750306333</v>
+        <v>2.9819045872651109</v>
       </c>
       <c r="T107" s="11">
         <v>4508101</v>
@@ -23149,12 +24265,24 @@
       <c r="AW107" s="13">
         <v>3.2344348463477082</v>
       </c>
-      <c r="AX107" s="11"/>
-      <c r="AY107" s="11"/>
-      <c r="AZ107" s="11"/>
-      <c r="BA107" s="12"/>
-      <c r="BB107" s="12"/>
-      <c r="BC107" s="13"/>
+      <c r="AX107" s="11">
+        <v>2874863</v>
+      </c>
+      <c r="AY107" s="11">
+        <v>166166</v>
+      </c>
+      <c r="AZ107" s="11">
+        <v>54</v>
+      </c>
+      <c r="BA107" s="12">
+        <v>159714.61111111109</v>
+      </c>
+      <c r="BB107" s="12">
+        <v>9231.4444444444453</v>
+      </c>
+      <c r="BC107" s="13">
+        <v>3.0604551484374971</v>
+      </c>
       <c r="BD107" s="11"/>
       <c r="BE107" s="11"/>
       <c r="BF107" s="11"/>
@@ -23235,27 +24363,27 @@
       </c>
       <c r="N108" s="8">
         <f t="shared" si="18"/>
-        <v>4603831.4000000004</v>
+        <v>4491533.666666667</v>
       </c>
       <c r="O108" s="8">
         <f t="shared" si="19"/>
-        <v>191312.8</v>
+        <v>189728.66666666666</v>
       </c>
       <c r="P108" s="8">
         <f t="shared" si="20"/>
-        <v>335</v>
+        <v>397</v>
       </c>
       <c r="Q108" s="9">
         <f t="shared" si="21"/>
-        <v>206141.70447761196</v>
+        <v>203646.36272040301</v>
       </c>
       <c r="R108" s="9">
         <f t="shared" si="22"/>
-        <v>8566.2447761194035</v>
+        <v>8602.3073047858943</v>
       </c>
       <c r="S108" s="10">
         <f t="shared" si="23"/>
-        <v>2.6276618853911602</v>
+        <v>2.6460065858336987</v>
       </c>
       <c r="T108" s="11">
         <v>3557826</v>
@@ -23347,12 +24475,24 @@
       <c r="AW108" s="13">
         <v>2.0116197184160072</v>
       </c>
-      <c r="AX108" s="11"/>
-      <c r="AY108" s="11"/>
-      <c r="AZ108" s="11"/>
-      <c r="BA108" s="12"/>
-      <c r="BB108" s="12"/>
-      <c r="BC108" s="13"/>
+      <c r="AX108" s="11">
+        <v>3930045</v>
+      </c>
+      <c r="AY108" s="11">
+        <v>181808</v>
+      </c>
+      <c r="AZ108" s="11">
+        <v>62</v>
+      </c>
+      <c r="BA108" s="12">
+        <v>190163.46774193551</v>
+      </c>
+      <c r="BB108" s="12">
+        <v>8797.1612903225814</v>
+      </c>
+      <c r="BC108" s="13">
+        <v>2.7377300880463928</v>
+      </c>
       <c r="BD108" s="11"/>
       <c r="BE108" s="11"/>
       <c r="BF108" s="11"/>
@@ -23433,27 +24573,27 @@
       </c>
       <c r="N109" s="8">
         <f t="shared" si="18"/>
-        <v>1956430.2</v>
+        <v>2013652.5</v>
       </c>
       <c r="O109" s="8">
         <f t="shared" si="19"/>
-        <v>217086.2</v>
+        <v>227019.5</v>
       </c>
       <c r="P109" s="8">
         <f t="shared" si="20"/>
-        <v>219</v>
+        <v>272</v>
       </c>
       <c r="Q109" s="9">
         <f t="shared" si="21"/>
-        <v>134002.0684931507</v>
+        <v>133256.41544117648</v>
       </c>
       <c r="R109" s="9">
         <f t="shared" si="22"/>
-        <v>14868.917808219179</v>
+        <v>15023.349264705881</v>
       </c>
       <c r="S109" s="10">
         <f t="shared" si="23"/>
-        <v>4.2512632657211196</v>
+        <v>4.2788094808953483</v>
       </c>
       <c r="T109" s="11">
         <v>3150735</v>
@@ -23545,12 +24685,24 @@
       <c r="AW109" s="13">
         <v>4.4199251045742862</v>
       </c>
-      <c r="AX109" s="11"/>
-      <c r="AY109" s="11"/>
-      <c r="AZ109" s="11"/>
-      <c r="BA109" s="12"/>
-      <c r="BB109" s="12"/>
-      <c r="BC109" s="13"/>
+      <c r="AX109" s="11">
+        <v>2299764</v>
+      </c>
+      <c r="AY109" s="11">
+        <v>276686</v>
+      </c>
+      <c r="AZ109" s="11">
+        <v>53</v>
+      </c>
+      <c r="BA109" s="12">
+        <v>130175.320754717</v>
+      </c>
+      <c r="BB109" s="12">
+        <v>15661.47169811321</v>
+      </c>
+      <c r="BC109" s="13">
+        <v>4.4165405567664919</v>
+      </c>
       <c r="BD109" s="11"/>
       <c r="BE109" s="11"/>
       <c r="BF109" s="11"/>
@@ -23631,27 +24783,27 @@
       </c>
       <c r="N110" s="8">
         <f t="shared" si="18"/>
-        <v>752366</v>
+        <v>798056</v>
       </c>
       <c r="O110" s="8">
         <f t="shared" si="19"/>
-        <v>178433.8</v>
+        <v>186827.83333333334</v>
       </c>
       <c r="P110" s="8">
         <f t="shared" si="20"/>
-        <v>216</v>
+        <v>270</v>
       </c>
       <c r="Q110" s="9">
         <f t="shared" ref="Q110:Q111" si="24">IFERROR(SUM(T110,Z110,AF110,AL110,AR110,AX110,BD110,BJ110,BP110,BV110,CB110,CH110)/P110*3," ")</f>
-        <v>52247.638888888891</v>
+        <v>53203.73333333333</v>
       </c>
       <c r="R110" s="9">
         <f t="shared" si="22"/>
-        <v>12391.236111111113</v>
+        <v>12455.18888888889</v>
       </c>
       <c r="S110" s="10">
         <f t="shared" si="23"/>
-        <v>6.3886506269897225</v>
+        <v>6.325891135085187</v>
       </c>
       <c r="T110" s="11">
         <v>1383825</v>
@@ -23743,12 +24895,24 @@
       <c r="AW110" s="13">
         <v>7.323589356067246</v>
       </c>
-      <c r="AX110" s="11"/>
-      <c r="AY110" s="11"/>
-      <c r="AZ110" s="11"/>
-      <c r="BA110" s="12"/>
-      <c r="BB110" s="12"/>
-      <c r="BC110" s="13"/>
+      <c r="AX110" s="11">
+        <v>1026506</v>
+      </c>
+      <c r="AY110" s="11">
+        <v>228798</v>
+      </c>
+      <c r="AZ110" s="11">
+        <v>54</v>
+      </c>
+      <c r="BA110" s="12">
+        <v>57028.111111111109</v>
+      </c>
+      <c r="BB110" s="12">
+        <v>12711</v>
+      </c>
+      <c r="BC110" s="13">
+        <v>6.012093675562511</v>
+      </c>
       <c r="BD110" s="11"/>
       <c r="BE110" s="11"/>
       <c r="BF110" s="11"/>
@@ -24013,11 +25177,11 @@
       <c r="M112" s="22"/>
       <c r="N112" s="14">
         <f>SUM(N57:N111)</f>
-        <v>209814354.11399996</v>
+        <v>214682094.56016657</v>
       </c>
       <c r="O112" s="14">
         <f>SUM(O57:O111)</f>
-        <v>2817245.75</v>
+        <v>2860715.4</v>
       </c>
       <c r="P112" s="14"/>
       <c r="Q112" s="14"/>
@@ -24085,11 +25249,11 @@
       <c r="AW112" s="24"/>
       <c r="AX112" s="14">
         <f>SUM(AX57:AX111)</f>
-        <v>0</v>
+        <v>231543405.391</v>
       </c>
       <c r="AY112" s="14">
         <f>SUM(AY57:AY111)</f>
-        <v>0</v>
+        <v>2985442</v>
       </c>
       <c r="AZ112" s="14"/>
       <c r="BA112" s="14"/>
@@ -24627,27 +25791,27 @@
       </c>
       <c r="N116" s="8">
         <f t="shared" ref="N116:O118" si="25">IFERROR(AVERAGE(T116,Z116,AF116,AL116,AR116,AX116,BD116,BJ116,BP116,BV116,CB116,CH116)," ")</f>
-        <v>2328601.2000000002</v>
+        <v>2434370.3333333335</v>
       </c>
       <c r="O116" s="8">
         <f t="shared" si="25"/>
-        <v>353104</v>
+        <v>368802</v>
       </c>
       <c r="P116" s="8">
         <f>IFERROR(SUM(V116,AB116,AH116,AN116,AT116,AZ116,BF116,BL116,BR116,BX116,CD116,CJ116)," ")</f>
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="Q116" s="9">
         <f>IFERROR(SUM(T116,Z116,AF116,AL116,AR116,AX116,BD116,BJ116,BP116,BV116,CB116,CH116)/P116*3," ")</f>
-        <v>268684.75384615385</v>
+        <v>273866.66249999998</v>
       </c>
       <c r="R116" s="9">
         <f>IFERROR(SUM(U116,AA116,AG116,AM116,AS116,AY116,BE116,BK116,BQ116,BW116,CC116,CI116)/P116*3," ")</f>
-        <v>40742.769230769227</v>
+        <v>41490.225000000006</v>
       </c>
       <c r="S116" s="10">
         <f>IFERROR(AVERAGE(Y116,AE116,AK116,AQ116,AW116,BC116,BI116,BO116,BU116,CA116,CG116,CM116)," ")</f>
-        <v>4.9949592229449653</v>
+        <v>4.9869380444118301</v>
       </c>
       <c r="T116" s="11">
         <v>3772092</v>
@@ -24739,12 +25903,24 @@
       <c r="AW116" s="13">
         <v>5.0827174311558654</v>
       </c>
-      <c r="AX116" s="11"/>
-      <c r="AY116" s="11"/>
-      <c r="AZ116" s="11"/>
-      <c r="BA116" s="12"/>
-      <c r="BB116" s="12"/>
-      <c r="BC116" s="13"/>
+      <c r="AX116" s="11">
+        <v>2963216</v>
+      </c>
+      <c r="AY116" s="11">
+        <v>447292</v>
+      </c>
+      <c r="AZ116" s="11">
+        <v>30</v>
+      </c>
+      <c r="BA116" s="12">
+        <v>296321.59999999998</v>
+      </c>
+      <c r="BB116" s="12">
+        <v>44729.2</v>
+      </c>
+      <c r="BC116" s="13">
+        <v>4.9468321517461531</v>
+      </c>
       <c r="BD116" s="11"/>
       <c r="BE116" s="11"/>
       <c r="BF116" s="11"/>
@@ -24823,27 +25999,27 @@
       </c>
       <c r="N117" s="8">
         <f t="shared" si="25"/>
-        <v>2424220.2000000002</v>
+        <v>2506566.3333333335</v>
       </c>
       <c r="O117" s="8">
         <f t="shared" si="25"/>
-        <v>367036.4</v>
+        <v>378469.16666666669</v>
       </c>
       <c r="P117" s="8">
         <f>IFERROR(SUM(V117,AB117,AH117,AN117,AT117,AZ117,BF117,BL117,BR117,BX117,CD117,CJ117)," ")</f>
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="Q117" s="9">
         <f>IFERROR(SUM(T117,Z117,AF117,AL117,AR117,AX117,BD117,BJ117,BP117,BV117,CB117,CH117)/P117*3," ")</f>
-        <v>265425.56934306567</v>
+        <v>273443.59999999998</v>
       </c>
       <c r="R117" s="9">
         <f>IFERROR(SUM(U117,AA117,AG117,AM117,AS117,AY117,BE117,BK117,BQ117,BW117,CC117,CI117)/P117*3," ")</f>
-        <v>40186.46715328467</v>
+        <v>41287.545454545456</v>
       </c>
       <c r="S117" s="10">
         <f>IFERROR(AVERAGE(Y117,AE117,AK117,AQ117,AW117,BC117,BI117,BO117,BU117,CA117,CG117,CM117)," ")</f>
-        <v>4.9939161440763957</v>
+        <v>4.9814919247538372</v>
       </c>
       <c r="T117" s="11">
         <v>4072469</v>
@@ -24935,12 +26111,24 @@
       <c r="AW117" s="13">
         <v>5.1082055038813658</v>
       </c>
-      <c r="AX117" s="11"/>
-      <c r="AY117" s="11"/>
-      <c r="AZ117" s="11"/>
-      <c r="BA117" s="12"/>
-      <c r="BB117" s="12"/>
-      <c r="BC117" s="13"/>
+      <c r="AX117" s="11">
+        <v>2918297</v>
+      </c>
+      <c r="AY117" s="11">
+        <v>435633</v>
+      </c>
+      <c r="AZ117" s="11">
+        <v>28</v>
+      </c>
+      <c r="BA117" s="12">
+        <v>312674.67857142858</v>
+      </c>
+      <c r="BB117" s="12">
+        <v>46674.96428571429</v>
+      </c>
+      <c r="BC117" s="13">
+        <v>4.9193708281410453</v>
+      </c>
       <c r="BD117" s="11"/>
       <c r="BE117" s="11"/>
       <c r="BF117" s="11"/>
@@ -25018,27 +26206,27 @@
       </c>
       <c r="N118" s="8">
         <f t="shared" si="25"/>
-        <v>670562.28</v>
+        <v>686780.9</v>
       </c>
       <c r="O118" s="8">
         <f t="shared" si="25"/>
-        <v>742491.6</v>
+        <v>759364.5</v>
       </c>
       <c r="P118" s="8">
         <f>IFERROR(SUM(V118,AB118,AH118,AN118,AT118,AZ118,BF118,BL118,BR118,BX118,CD118,CJ118)," ")</f>
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="Q118" s="9">
         <f>IFERROR(SUM(T118,Z118,AF118,AL118,AR118,AX118,BD118,BJ118,BP118,BV118,CB118,CH118)/P118*3," ")</f>
-        <v>85240.967796610174</v>
+        <v>84095.62040816326</v>
       </c>
       <c r="R118" s="9">
         <f>IFERROR(SUM(U118,AA118,AG118,AM118,AS118,AY118,BE118,BK118,BQ118,BW118,CC118,CI118)/P118*3," ")</f>
-        <v>94384.525423728817</v>
+        <v>92983.408163265311</v>
       </c>
       <c r="S118" s="10">
         <f>IFERROR(AVERAGE(Y118,AE118,AK118,AQ118,AW118,BC118,BI118,BO118,BU118,CA118,CG118,CM118)," ")</f>
-        <v>14.965751705544694</v>
+        <v>14.942500638446596</v>
       </c>
       <c r="T118" s="11">
         <v>1050265</v>
@@ -25130,12 +26318,24 @@
       <c r="AW118" s="13">
         <v>14.91150046244092</v>
       </c>
-      <c r="AX118" s="11"/>
-      <c r="AY118" s="11"/>
-      <c r="AZ118" s="11"/>
-      <c r="BA118" s="12"/>
-      <c r="BB118" s="12"/>
-      <c r="BC118" s="13"/>
+      <c r="AX118" s="11">
+        <v>767874</v>
+      </c>
+      <c r="AY118" s="11">
+        <v>843729</v>
+      </c>
+      <c r="AZ118" s="11">
+        <v>29</v>
+      </c>
+      <c r="BA118" s="12">
+        <v>79435.241379310348</v>
+      </c>
+      <c r="BB118" s="12">
+        <v>87282.310344827594</v>
+      </c>
+      <c r="BC118" s="13">
+        <v>14.82624530295611</v>
+      </c>
       <c r="BD118" s="11"/>
       <c r="BE118" s="11"/>
       <c r="BF118" s="11"/>
@@ -25199,11 +26399,11 @@
       <c r="M119" s="22"/>
       <c r="N119" s="14">
         <f>SUM(N116:N118)</f>
-        <v>5423383.6800000006</v>
+        <v>5627717.5666666673</v>
       </c>
       <c r="O119" s="14">
         <f>SUM(O116:O118)</f>
-        <v>1462632</v>
+        <v>1506635.6666666667</v>
       </c>
       <c r="P119" s="14"/>
       <c r="Q119" s="14"/>
@@ -25271,11 +26471,11 @@
       <c r="AW119" s="14"/>
       <c r="AX119" s="14">
         <f>SUM(AX116:AX118)</f>
-        <v>0</v>
+        <v>6649387</v>
       </c>
       <c r="AY119" s="14">
         <f>SUM(AY116:AY118)</f>
-        <v>0</v>
+        <v>1726654</v>
       </c>
       <c r="AZ119" s="14"/>
       <c r="BA119" s="14"/>
@@ -25369,35 +26569,6 @@
   </sheetData>
   <autoFilter ref="A2:CM53" xr:uid="{B264AC42-3408-4CC4-A254-80BEFA0AA9F5}"/>
   <mergeCells count="45">
-    <mergeCell ref="CB114:CG114"/>
-    <mergeCell ref="CH114:CM114"/>
-    <mergeCell ref="N114:S114"/>
-    <mergeCell ref="AX114:BC114"/>
-    <mergeCell ref="BD114:BI114"/>
-    <mergeCell ref="BJ114:BO114"/>
-    <mergeCell ref="BP114:BU114"/>
-    <mergeCell ref="BV114:CA114"/>
-    <mergeCell ref="T114:Y114"/>
-    <mergeCell ref="Z114:AE114"/>
-    <mergeCell ref="AF114:AK114"/>
-    <mergeCell ref="AL114:AQ114"/>
-    <mergeCell ref="AR114:AW114"/>
-    <mergeCell ref="BP55:BU55"/>
-    <mergeCell ref="BV55:CA55"/>
-    <mergeCell ref="CB55:CG55"/>
-    <mergeCell ref="CH55:CM55"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="AL55:AQ55"/>
-    <mergeCell ref="AR55:AW55"/>
-    <mergeCell ref="AX55:BC55"/>
-    <mergeCell ref="BD55:BI55"/>
-    <mergeCell ref="BJ55:BO55"/>
-    <mergeCell ref="T1:Y1"/>
-    <mergeCell ref="Z1:AE1"/>
-    <mergeCell ref="AF1:AK1"/>
-    <mergeCell ref="T55:Y55"/>
-    <mergeCell ref="Z55:AE55"/>
-    <mergeCell ref="AF55:AK55"/>
     <mergeCell ref="B114:G114"/>
     <mergeCell ref="H114:M114"/>
     <mergeCell ref="CB1:CG1"/>
@@ -25414,6 +26585,35 @@
     <mergeCell ref="AL1:AQ1"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H1:M1"/>
+    <mergeCell ref="T1:Y1"/>
+    <mergeCell ref="Z1:AE1"/>
+    <mergeCell ref="AF1:AK1"/>
+    <mergeCell ref="T55:Y55"/>
+    <mergeCell ref="Z55:AE55"/>
+    <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="BP55:BU55"/>
+    <mergeCell ref="BV55:CA55"/>
+    <mergeCell ref="CB55:CG55"/>
+    <mergeCell ref="CH55:CM55"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="AL55:AQ55"/>
+    <mergeCell ref="AR55:AW55"/>
+    <mergeCell ref="AX55:BC55"/>
+    <mergeCell ref="BD55:BI55"/>
+    <mergeCell ref="BJ55:BO55"/>
+    <mergeCell ref="CB114:CG114"/>
+    <mergeCell ref="CH114:CM114"/>
+    <mergeCell ref="N114:S114"/>
+    <mergeCell ref="AX114:BC114"/>
+    <mergeCell ref="BD114:BI114"/>
+    <mergeCell ref="BJ114:BO114"/>
+    <mergeCell ref="BP114:BU114"/>
+    <mergeCell ref="BV114:CA114"/>
+    <mergeCell ref="T114:Y114"/>
+    <mergeCell ref="Z114:AE114"/>
+    <mergeCell ref="AF114:AK114"/>
+    <mergeCell ref="AL114:AQ114"/>
+    <mergeCell ref="AR114:AW114"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Kapabilite/Kapabilite 2026.xlsx
+++ b/Kapabilite/Kapabilite 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Kapabilite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DD363D-E439-484D-A223-1890364870EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06F9971-801B-4223-929F-4B916C483CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8FA9AADE-0AF1-42A7-AB4A-1A5F3041D90E}"/>
   </bookViews>
@@ -3292,27 +3292,27 @@
       </c>
       <c r="N3" s="8">
         <f t="shared" ref="N3:N25" si="0">IFERROR(AVERAGE(T3,Z3,AF3,AL3,AR3,AX3,BD3,BJ3,BP3,BV3,CB3,CH3)," ")</f>
-        <v>150083.33333333334</v>
+        <v>155700</v>
       </c>
       <c r="O3" s="8">
         <f t="shared" ref="O3:O25" si="1">IFERROR(AVERAGE(U3,AA3,AG3,AM3,AS3,AY3,BE3,BK3,BQ3,BW3,CC3,CI3)," ")</f>
-        <v>53383.5</v>
+        <v>55615.142857142855</v>
       </c>
       <c r="P3" s="8">
         <f t="shared" ref="P3:P25" si="2">IFERROR(SUM(V3,AB3,AH3,AN3,AT3,AZ3,BF3,BL3,BR3,BX3,CD3,CJ3)," ")</f>
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="Q3" s="9">
         <f t="shared" ref="Q3:Q25" si="3">IFERROR(SUM(T3,Z3,AF3,AL3,AR3,AX3,BD3,BJ3,BP3,BV3,CB3,CH3)/P3*3," ")</f>
-        <v>15891.176470588234</v>
+        <v>16106.896551724138</v>
       </c>
       <c r="R3" s="9">
         <f t="shared" ref="R3:R25" si="4">IFERROR(SUM(U3,AA3,AG3,AM3,AS3,AY3,BE3,BK3,BQ3,BW3,CC3,CI3)/P3*3," ")</f>
-        <v>5652.3705882352933</v>
+        <v>5753.2906403940888</v>
       </c>
       <c r="S3" s="10">
         <f t="shared" ref="S3:S25" si="5">IFERROR(AVERAGE(Y3,AE3,AK3,AQ3,AW3,BC3,BI3,BO3,BU3,CA3,CG3,CM3)," ")</f>
-        <v>9.9246507546036327</v>
+        <v>9.9354149325173999</v>
       </c>
       <c r="T3" s="11">
         <v>24000</v>
@@ -3422,12 +3422,24 @@
       <c r="BC3" s="13">
         <v>10.02203454746531</v>
       </c>
-      <c r="BD3" s="11"/>
-      <c r="BE3" s="11"/>
-      <c r="BF3" s="11"/>
-      <c r="BG3" s="12"/>
-      <c r="BH3" s="12"/>
-      <c r="BI3" s="13"/>
+      <c r="BD3" s="11">
+        <v>189400</v>
+      </c>
+      <c r="BE3" s="11">
+        <v>69005</v>
+      </c>
+      <c r="BF3" s="11">
+        <v>33</v>
+      </c>
+      <c r="BG3" s="12">
+        <v>17218.18181818182</v>
+      </c>
+      <c r="BH3" s="12">
+        <v>6273.181818181818</v>
+      </c>
+      <c r="BI3" s="13">
+        <v>10</v>
+      </c>
       <c r="BJ3" s="11"/>
       <c r="BK3" s="11"/>
       <c r="BL3" s="11"/>
@@ -3499,27 +3511,27 @@
       </c>
       <c r="N4" s="8">
         <f t="shared" si="0"/>
-        <v>292725.5</v>
+        <v>310950.42857142858</v>
       </c>
       <c r="O4" s="8">
         <f t="shared" si="1"/>
-        <v>11327</v>
+        <v>11935.142857142857</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" si="2"/>
-        <v>286</v>
+        <v>351</v>
       </c>
       <c r="Q4" s="9">
         <f t="shared" si="3"/>
-        <v>18423.283216783217</v>
+        <v>18603.871794871797</v>
       </c>
       <c r="R4" s="9">
         <f t="shared" si="4"/>
-        <v>712.88811188811189</v>
+        <v>714.0683760683761</v>
       </c>
       <c r="S4" s="10">
         <f t="shared" si="5"/>
-        <v>2.7016959139419829</v>
+        <v>2.6943107833788424</v>
       </c>
       <c r="T4" s="11">
         <v>328790</v>
@@ -3629,12 +3641,24 @@
       <c r="BC4" s="13">
         <v>2.65</v>
       </c>
-      <c r="BD4" s="11"/>
-      <c r="BE4" s="11"/>
-      <c r="BF4" s="11"/>
-      <c r="BG4" s="12"/>
-      <c r="BH4" s="12"/>
-      <c r="BI4" s="13"/>
+      <c r="BD4" s="11">
+        <v>420300</v>
+      </c>
+      <c r="BE4" s="11">
+        <v>15584</v>
+      </c>
+      <c r="BF4" s="11">
+        <v>65</v>
+      </c>
+      <c r="BG4" s="12">
+        <v>19398.461538461539</v>
+      </c>
+      <c r="BH4" s="12">
+        <v>719.26153846153852</v>
+      </c>
+      <c r="BI4" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BJ4" s="11"/>
       <c r="BK4" s="11"/>
       <c r="BL4" s="11"/>
@@ -3706,27 +3730,27 @@
       </c>
       <c r="N5" s="8">
         <f t="shared" si="0"/>
-        <v>328365.33333333331</v>
+        <v>334107.42857142858</v>
       </c>
       <c r="O5" s="8">
         <f t="shared" si="1"/>
-        <v>12827.166666666666</v>
+        <v>12947.285714285714</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="2"/>
-        <v>327</v>
+        <v>387</v>
       </c>
       <c r="Q5" s="9">
         <f t="shared" si="3"/>
-        <v>18075.155963302754</v>
+        <v>18129.860465116279</v>
       </c>
       <c r="R5" s="9">
         <f t="shared" si="4"/>
-        <v>706.0825688073395</v>
+        <v>702.56589147286832</v>
       </c>
       <c r="S5" s="10">
         <f t="shared" si="5"/>
-        <v>2.7169113315353655</v>
+        <v>2.7073525698874557</v>
       </c>
       <c r="T5" s="11">
         <v>373478</v>
@@ -3836,12 +3860,24 @@
       <c r="BC5" s="13">
         <v>2.65</v>
       </c>
-      <c r="BD5" s="11"/>
-      <c r="BE5" s="11"/>
-      <c r="BF5" s="11"/>
-      <c r="BG5" s="12"/>
-      <c r="BH5" s="12"/>
-      <c r="BI5" s="13"/>
+      <c r="BD5" s="11">
+        <v>368560</v>
+      </c>
+      <c r="BE5" s="11">
+        <v>13668</v>
+      </c>
+      <c r="BF5" s="11">
+        <v>60</v>
+      </c>
+      <c r="BG5" s="12">
+        <v>18428</v>
+      </c>
+      <c r="BH5" s="12">
+        <v>683.40000000000009</v>
+      </c>
+      <c r="BI5" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BJ5" s="11"/>
       <c r="BK5" s="11"/>
       <c r="BL5" s="11"/>
@@ -3913,27 +3949,27 @@
       </c>
       <c r="N6" s="8">
         <f t="shared" si="0"/>
-        <v>233849.5</v>
+        <v>235691</v>
       </c>
       <c r="O6" s="8">
         <f t="shared" si="1"/>
-        <v>18052.333333333332</v>
+        <v>18132.428571428572</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="2"/>
-        <v>317</v>
+        <v>366</v>
       </c>
       <c r="Q6" s="9">
         <f t="shared" si="3"/>
-        <v>13278.520504731863</v>
+        <v>13523.254098360656</v>
       </c>
       <c r="R6" s="9">
         <f t="shared" si="4"/>
-        <v>1025.0536277602523</v>
+        <v>1040.3852459016393</v>
       </c>
       <c r="S6" s="10">
         <f t="shared" si="5"/>
-        <v>3.8051549970925009</v>
+        <v>3.7991418251676627</v>
       </c>
       <c r="T6" s="11">
         <v>274253</v>
@@ -4043,12 +4079,24 @@
       <c r="BC6" s="13">
         <v>3.8263835373722959</v>
       </c>
-      <c r="BD6" s="11"/>
-      <c r="BE6" s="11"/>
-      <c r="BF6" s="11"/>
-      <c r="BG6" s="12"/>
-      <c r="BH6" s="12"/>
-      <c r="BI6" s="13"/>
+      <c r="BD6" s="11">
+        <v>246740</v>
+      </c>
+      <c r="BE6" s="11">
+        <v>18613</v>
+      </c>
+      <c r="BF6" s="11">
+        <v>49</v>
+      </c>
+      <c r="BG6" s="12">
+        <v>15106.5306122449</v>
+      </c>
+      <c r="BH6" s="12">
+        <v>1139.571428571428</v>
+      </c>
+      <c r="BI6" s="13">
+        <v>3.7630627936186332</v>
+      </c>
       <c r="BJ6" s="11"/>
       <c r="BK6" s="11"/>
       <c r="BL6" s="11"/>
@@ -4120,27 +4168,27 @@
       </c>
       <c r="N7" s="8">
         <f t="shared" si="0"/>
-        <v>307191.83333333331</v>
+        <v>313149.28571428574</v>
       </c>
       <c r="O7" s="8">
         <f t="shared" si="1"/>
-        <v>54621.833333333336</v>
+        <v>56645</v>
       </c>
       <c r="P7" s="8">
         <f t="shared" si="2"/>
-        <v>324</v>
+        <v>392</v>
       </c>
       <c r="Q7" s="9">
         <f t="shared" si="3"/>
-        <v>17066.212962962964</v>
+        <v>16775.854591836734</v>
       </c>
       <c r="R7" s="9">
         <f t="shared" si="4"/>
-        <v>3034.5462962962965</v>
+        <v>3034.5535714285716</v>
       </c>
       <c r="S7" s="10">
         <f t="shared" si="5"/>
-        <v>5.5347062425130273</v>
+        <v>5.6074104846583284</v>
       </c>
       <c r="T7" s="11">
         <v>355184</v>
@@ -4250,12 +4298,24 @@
       <c r="BC7" s="13">
         <v>6.0301732024919481</v>
       </c>
-      <c r="BD7" s="11"/>
-      <c r="BE7" s="11"/>
-      <c r="BF7" s="11"/>
-      <c r="BG7" s="12"/>
-      <c r="BH7" s="12"/>
-      <c r="BI7" s="13"/>
+      <c r="BD7" s="11">
+        <v>348894</v>
+      </c>
+      <c r="BE7" s="11">
+        <v>68784</v>
+      </c>
+      <c r="BF7" s="11">
+        <v>68</v>
+      </c>
+      <c r="BG7" s="12">
+        <v>15392.382352941169</v>
+      </c>
+      <c r="BH7" s="12">
+        <v>3034.588235294118</v>
+      </c>
+      <c r="BI7" s="13">
+        <v>6.0436359375301363</v>
+      </c>
       <c r="BJ7" s="11"/>
       <c r="BK7" s="11"/>
       <c r="BL7" s="11"/>
@@ -4327,27 +4387,27 @@
       </c>
       <c r="N8" s="8">
         <f t="shared" si="0"/>
-        <v>286387.16666666669</v>
+        <v>296529.14285714284</v>
       </c>
       <c r="O8" s="8">
         <f t="shared" si="1"/>
-        <v>37217.833333333336</v>
+        <v>37776.285714285717</v>
       </c>
       <c r="P8" s="8">
         <f t="shared" si="2"/>
-        <v>336</v>
+        <v>403</v>
       </c>
       <c r="Q8" s="9">
         <f t="shared" si="3"/>
-        <v>15342.169642857143</v>
+        <v>15451.890818858559</v>
       </c>
       <c r="R8" s="9">
         <f t="shared" si="4"/>
-        <v>1993.8125</v>
+        <v>1968.4913151364763</v>
       </c>
       <c r="S8" s="10">
         <f t="shared" si="5"/>
-        <v>4.9055327480869622</v>
+        <v>4.8700585650717398</v>
       </c>
       <c r="T8" s="11">
         <v>330292</v>
@@ -4457,12 +4517,24 @@
       <c r="BC8" s="13">
         <v>5.0795300039606852</v>
       </c>
-      <c r="BD8" s="11"/>
-      <c r="BE8" s="11"/>
-      <c r="BF8" s="11"/>
-      <c r="BG8" s="12"/>
-      <c r="BH8" s="12"/>
-      <c r="BI8" s="13"/>
+      <c r="BD8" s="11">
+        <v>357381</v>
+      </c>
+      <c r="BE8" s="11">
+        <v>41127</v>
+      </c>
+      <c r="BF8" s="11">
+        <v>67</v>
+      </c>
+      <c r="BG8" s="12">
+        <v>16002.13432835821</v>
+      </c>
+      <c r="BH8" s="12">
+        <v>1841.5074626865669</v>
+      </c>
+      <c r="BI8" s="13">
+        <v>4.6572134669804086</v>
+      </c>
       <c r="BJ8" s="11"/>
       <c r="BK8" s="11"/>
       <c r="BL8" s="11"/>
@@ -4534,27 +4606,27 @@
       </c>
       <c r="N9" s="8">
         <f t="shared" si="0"/>
-        <v>270394.16666666669</v>
+        <v>282256.71428571426</v>
       </c>
       <c r="O9" s="8">
         <f t="shared" si="1"/>
-        <v>9700.6666666666661</v>
+        <v>9990.8571428571431</v>
       </c>
       <c r="P9" s="8">
         <f t="shared" si="2"/>
-        <v>281</v>
+        <v>335</v>
       </c>
       <c r="Q9" s="9">
         <f t="shared" si="3"/>
-        <v>17320.622775800712</v>
+        <v>17693.70447761194</v>
       </c>
       <c r="R9" s="9">
         <f t="shared" si="4"/>
-        <v>621.39501779359432</v>
+        <v>626.29253731343283</v>
       </c>
       <c r="S9" s="10">
         <f t="shared" si="5"/>
-        <v>2.5895359446946928</v>
+        <v>2.5784585159813185</v>
       </c>
       <c r="T9" s="11">
         <v>341336</v>
@@ -4664,12 +4736,24 @@
       <c r="BC9" s="13">
         <v>2.65</v>
       </c>
-      <c r="BD9" s="11"/>
-      <c r="BE9" s="11"/>
-      <c r="BF9" s="11"/>
-      <c r="BG9" s="12"/>
-      <c r="BH9" s="12"/>
-      <c r="BI9" s="13"/>
+      <c r="BD9" s="11">
+        <v>353432</v>
+      </c>
+      <c r="BE9" s="11">
+        <v>11732</v>
+      </c>
+      <c r="BF9" s="11">
+        <v>54</v>
+      </c>
+      <c r="BG9" s="12">
+        <v>19635.111111111109</v>
+      </c>
+      <c r="BH9" s="12">
+        <v>651.77777777777783</v>
+      </c>
+      <c r="BI9" s="13">
+        <v>2.511993943701075</v>
+      </c>
       <c r="BJ9" s="11"/>
       <c r="BK9" s="11"/>
       <c r="BL9" s="11"/>
@@ -4741,27 +4825,27 @@
       </c>
       <c r="N10" s="8">
         <f t="shared" si="0"/>
-        <v>243623.33333333334</v>
+        <v>250575</v>
       </c>
       <c r="O10" s="8">
         <f t="shared" si="1"/>
-        <v>8572.8333333333339</v>
+        <v>8613.2857142857138</v>
       </c>
       <c r="P10" s="8">
         <f t="shared" si="2"/>
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="Q10" s="9">
         <f t="shared" si="3"/>
-        <v>19489.866666666669</v>
+        <v>19065.489130434784</v>
       </c>
       <c r="R10" s="9">
         <f t="shared" si="4"/>
-        <v>685.8266666666666</v>
+        <v>655.35869565217388</v>
       </c>
       <c r="S10" s="10">
         <f t="shared" si="5"/>
-        <v>2.5970490365913728</v>
+        <v>2.5766854551032119</v>
       </c>
       <c r="T10" s="11">
         <v>350996</v>
@@ -4871,12 +4955,24 @@
       <c r="BC10" s="13">
         <v>2.4818773225099151</v>
       </c>
-      <c r="BD10" s="11"/>
-      <c r="BE10" s="11"/>
-      <c r="BF10" s="11"/>
-      <c r="BG10" s="12"/>
-      <c r="BH10" s="12"/>
-      <c r="BI10" s="13"/>
+      <c r="BD10" s="11">
+        <v>292285</v>
+      </c>
+      <c r="BE10" s="11">
+        <v>8856</v>
+      </c>
+      <c r="BF10" s="11">
+        <v>51</v>
+      </c>
+      <c r="BG10" s="12">
+        <v>17193.23529411765</v>
+      </c>
+      <c r="BH10" s="12">
+        <v>520.94117647058829</v>
+      </c>
+      <c r="BI10" s="13">
+        <v>2.4545039661742458</v>
+      </c>
       <c r="BJ10" s="11"/>
       <c r="BK10" s="11"/>
       <c r="BL10" s="11"/>
@@ -4948,27 +5044,27 @@
       </c>
       <c r="N11" s="8">
         <f t="shared" si="0"/>
-        <v>243761</v>
+        <v>252245.57142857142</v>
       </c>
       <c r="O11" s="8">
         <f t="shared" si="1"/>
-        <v>8335</v>
+        <v>8991.4285714285706</v>
       </c>
       <c r="P11" s="8">
         <f t="shared" si="2"/>
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="Q11" s="9">
         <f t="shared" si="3"/>
-        <v>17982.368852459018</v>
+        <v>17775.69463087248</v>
       </c>
       <c r="R11" s="9">
         <f t="shared" si="4"/>
-        <v>614.87704918032784</v>
+        <v>633.62416107382546</v>
       </c>
       <c r="S11" s="10">
         <f t="shared" si="5"/>
-        <v>2.6021411531773544</v>
+        <v>2.6471432546095026</v>
       </c>
       <c r="T11" s="11">
         <v>395887</v>
@@ -5078,12 +5174,24 @@
       <c r="BC11" s="13">
         <v>2.6895928247203709</v>
       </c>
-      <c r="BD11" s="11"/>
-      <c r="BE11" s="11"/>
-      <c r="BF11" s="11"/>
-      <c r="BG11" s="12"/>
-      <c r="BH11" s="12"/>
-      <c r="BI11" s="13"/>
+      <c r="BD11" s="11">
+        <v>303153</v>
+      </c>
+      <c r="BE11" s="11">
+        <v>12930</v>
+      </c>
+      <c r="BF11" s="11">
+        <v>54</v>
+      </c>
+      <c r="BG11" s="12">
+        <v>16841.833333333328</v>
+      </c>
+      <c r="BH11" s="12">
+        <v>718.33333333333337</v>
+      </c>
+      <c r="BI11" s="13">
+        <v>2.917155863202392</v>
+      </c>
       <c r="BJ11" s="11"/>
       <c r="BK11" s="11"/>
       <c r="BL11" s="11"/>
@@ -5155,27 +5263,27 @@
       </c>
       <c r="N12" s="8">
         <f t="shared" si="0"/>
-        <v>259383.33333333334</v>
+        <v>259591.14285714287</v>
       </c>
       <c r="O12" s="8">
         <f t="shared" si="1"/>
-        <v>19175.833333333332</v>
+        <v>18726.571428571428</v>
       </c>
       <c r="P12" s="8">
         <f t="shared" si="2"/>
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="Q12" s="9">
         <f t="shared" si="3"/>
-        <v>17685.227272727272</v>
+        <v>17991.465346534653</v>
       </c>
       <c r="R12" s="9">
         <f t="shared" si="4"/>
-        <v>1307.4431818181818</v>
+        <v>1297.8811881188119</v>
       </c>
       <c r="S12" s="10">
         <f t="shared" si="5"/>
-        <v>3.7116019823397246</v>
+        <v>3.6664007873182465</v>
       </c>
       <c r="T12" s="11">
         <v>290616</v>
@@ -5285,12 +5393,24 @@
       <c r="BC12" s="13">
         <v>3.063445229106863</v>
       </c>
-      <c r="BD12" s="11"/>
-      <c r="BE12" s="11"/>
-      <c r="BF12" s="11"/>
-      <c r="BG12" s="12"/>
-      <c r="BH12" s="12"/>
-      <c r="BI12" s="13"/>
+      <c r="BD12" s="11">
+        <v>260838</v>
+      </c>
+      <c r="BE12" s="11">
+        <v>16031</v>
+      </c>
+      <c r="BF12" s="11">
+        <v>39</v>
+      </c>
+      <c r="BG12" s="12">
+        <v>20064.461538461539</v>
+      </c>
+      <c r="BH12" s="12">
+        <v>1233.153846153846</v>
+      </c>
+      <c r="BI12" s="13">
+        <v>3.395193617189376</v>
+      </c>
       <c r="BJ12" s="11"/>
       <c r="BK12" s="11"/>
       <c r="BL12" s="11"/>
@@ -5362,27 +5482,27 @@
       </c>
       <c r="N13" s="8">
         <f t="shared" si="0"/>
-        <v>275539.5</v>
+        <v>279476.85714285716</v>
       </c>
       <c r="O13" s="8">
         <f t="shared" si="1"/>
-        <v>13461</v>
+        <v>13076</v>
       </c>
       <c r="P13" s="8">
         <f t="shared" si="2"/>
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="Q13" s="9">
         <f t="shared" si="3"/>
-        <v>16208.205882352941</v>
+        <v>16532.4338028169</v>
       </c>
       <c r="R13" s="9">
         <f t="shared" si="4"/>
-        <v>791.82352941176464</v>
+        <v>773.50985915492959</v>
       </c>
       <c r="S13" s="10">
         <f t="shared" si="5"/>
-        <v>3.134362269817935</v>
+        <v>3.0674327207048462</v>
       </c>
       <c r="T13" s="11">
         <v>214482</v>
@@ -5492,12 +5612,24 @@
       <c r="BC13" s="13">
         <v>2.6753631913403679</v>
       </c>
-      <c r="BD13" s="11"/>
-      <c r="BE13" s="11"/>
-      <c r="BF13" s="11"/>
-      <c r="BG13" s="12"/>
-      <c r="BH13" s="12"/>
-      <c r="BI13" s="13"/>
+      <c r="BD13" s="11">
+        <v>303101</v>
+      </c>
+      <c r="BE13" s="11">
+        <v>10766</v>
+      </c>
+      <c r="BF13" s="11">
+        <v>49</v>
+      </c>
+      <c r="BG13" s="12">
+        <v>18557.204081632652</v>
+      </c>
+      <c r="BH13" s="12">
+        <v>659.14285714285711</v>
+      </c>
+      <c r="BI13" s="13">
+        <v>2.6658554260263121</v>
+      </c>
       <c r="BJ13" s="11"/>
       <c r="BK13" s="11"/>
       <c r="BL13" s="11"/>
@@ -5569,27 +5701,27 @@
       </c>
       <c r="N14" s="8">
         <f t="shared" si="0"/>
-        <v>292457.83333333331</v>
+        <v>295568.42857142858</v>
       </c>
       <c r="O14" s="8">
         <f t="shared" si="1"/>
-        <v>162649.83333333334</v>
+        <v>169712</v>
       </c>
       <c r="P14" s="8">
         <f t="shared" si="2"/>
-        <v>363</v>
+        <v>431</v>
       </c>
       <c r="Q14" s="9">
         <f t="shared" si="3"/>
-        <v>14502.041322314049</v>
+        <v>14401.245939675173</v>
       </c>
       <c r="R14" s="9">
         <f t="shared" si="4"/>
-        <v>8065.2809917355371</v>
+        <v>8269.0301624129934</v>
       </c>
       <c r="S14" s="10">
         <f t="shared" si="5"/>
-        <v>10.11391237978791</v>
+        <v>10.262607136040373</v>
       </c>
       <c r="T14" s="11">
         <v>358878</v>
@@ -5699,12 +5831,24 @@
       <c r="BC14" s="13">
         <v>9.5097754876279517</v>
       </c>
-      <c r="BD14" s="11"/>
-      <c r="BE14" s="11"/>
-      <c r="BF14" s="11"/>
-      <c r="BG14" s="12"/>
-      <c r="BH14" s="12"/>
-      <c r="BI14" s="13"/>
+      <c r="BD14" s="11">
+        <v>314232</v>
+      </c>
+      <c r="BE14" s="11">
+        <v>212085</v>
+      </c>
+      <c r="BF14" s="11">
+        <v>68</v>
+      </c>
+      <c r="BG14" s="12">
+        <v>13863.176470588231</v>
+      </c>
+      <c r="BH14" s="12">
+        <v>9356.6911764705874</v>
+      </c>
+      <c r="BI14" s="13">
+        <v>11.15477567355515</v>
+      </c>
       <c r="BJ14" s="11"/>
       <c r="BK14" s="11"/>
       <c r="BL14" s="11"/>
@@ -5776,27 +5920,27 @@
       </c>
       <c r="N15" s="8">
         <f t="shared" si="0"/>
-        <v>148229</v>
+        <v>148153.71428571429</v>
       </c>
       <c r="O15" s="8">
         <f t="shared" si="1"/>
-        <v>63156</v>
+        <v>62379.714285714283</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" si="2"/>
-        <v>279</v>
+        <v>329</v>
       </c>
       <c r="Q15" s="9">
         <f t="shared" si="3"/>
-        <v>9563.1612903225796</v>
+        <v>9456.6200607902738</v>
       </c>
       <c r="R15" s="9">
         <f t="shared" si="4"/>
-        <v>4074.5806451612907</v>
+        <v>3981.6838905775076</v>
       </c>
       <c r="S15" s="10">
         <f t="shared" si="5"/>
-        <v>10.292684049542915</v>
+        <v>10.239028797695918</v>
       </c>
       <c r="T15" s="11">
         <v>184929</v>
@@ -5906,12 +6050,24 @@
       <c r="BC15" s="13">
         <v>9.8791367031962007</v>
       </c>
-      <c r="BD15" s="11"/>
-      <c r="BE15" s="11"/>
-      <c r="BF15" s="11"/>
-      <c r="BG15" s="12"/>
-      <c r="BH15" s="12"/>
-      <c r="BI15" s="13"/>
+      <c r="BD15" s="11">
+        <v>147702</v>
+      </c>
+      <c r="BE15" s="11">
+        <v>57722</v>
+      </c>
+      <c r="BF15" s="11">
+        <v>50</v>
+      </c>
+      <c r="BG15" s="12">
+        <v>8862.119999999999</v>
+      </c>
+      <c r="BH15" s="12">
+        <v>3463.32</v>
+      </c>
+      <c r="BI15" s="13">
+        <v>9.9170972866139273</v>
+      </c>
       <c r="BJ15" s="11"/>
       <c r="BK15" s="11"/>
       <c r="BL15" s="11"/>
@@ -5983,27 +6139,27 @@
       </c>
       <c r="N16" s="8">
         <f t="shared" si="0"/>
-        <v>105328.66666666667</v>
+        <v>107260.28571428571</v>
       </c>
       <c r="O16" s="8">
         <f t="shared" si="1"/>
-        <v>173866.5</v>
+        <v>175604.71428571429</v>
       </c>
       <c r="P16" s="8">
         <f t="shared" si="2"/>
-        <v>331</v>
+        <v>395</v>
       </c>
       <c r="Q16" s="9">
         <f t="shared" si="3"/>
-        <v>5727.8429003021147</v>
+        <v>5702.4455696202531</v>
       </c>
       <c r="R16" s="9">
         <f t="shared" si="4"/>
-        <v>9454.9758308157107</v>
+        <v>9335.9468354430373</v>
       </c>
       <c r="S16" s="10">
         <f t="shared" si="5"/>
-        <v>20.521158201702054</v>
+        <v>20.448529338407564</v>
       </c>
       <c r="T16" s="11">
         <v>114329</v>
@@ -6113,12 +6269,24 @@
       <c r="BC16" s="13">
         <v>20.341821128949569</v>
       </c>
-      <c r="BD16" s="11"/>
-      <c r="BE16" s="11"/>
-      <c r="BF16" s="11"/>
-      <c r="BG16" s="12"/>
-      <c r="BH16" s="12"/>
-      <c r="BI16" s="13"/>
+      <c r="BD16" s="11">
+        <v>118850</v>
+      </c>
+      <c r="BE16" s="11">
+        <v>186034</v>
+      </c>
+      <c r="BF16" s="11">
+        <v>64</v>
+      </c>
+      <c r="BG16" s="12">
+        <v>5571.09375</v>
+      </c>
+      <c r="BH16" s="12">
+        <v>8720.34375</v>
+      </c>
+      <c r="BI16" s="13">
+        <v>20.01275615864062</v>
+      </c>
       <c r="BJ16" s="11"/>
       <c r="BK16" s="11"/>
       <c r="BL16" s="11"/>
@@ -6190,27 +6358,27 @@
       </c>
       <c r="N17" s="8">
         <f t="shared" si="0"/>
-        <v>288772</v>
+        <v>301763.71428571426</v>
       </c>
       <c r="O17" s="8">
         <f t="shared" si="1"/>
-        <v>4447</v>
+        <v>4550.2857142857147</v>
       </c>
       <c r="P17" s="8">
         <f t="shared" si="2"/>
-        <v>262</v>
+        <v>310</v>
       </c>
       <c r="Q17" s="9">
         <f t="shared" si="3"/>
-        <v>19839.297709923663</v>
+        <v>20442.058064516128</v>
       </c>
       <c r="R17" s="9">
         <f t="shared" si="4"/>
-        <v>305.51908396946567</v>
+        <v>308.24516129032259</v>
       </c>
       <c r="S17" s="10">
         <f t="shared" si="5"/>
-        <v>1.7380189531315526</v>
+        <v>1.7237896897128884</v>
       </c>
       <c r="T17" s="11">
         <v>317353</v>
@@ -6320,12 +6488,24 @@
       <c r="BC17" s="13">
         <v>1.6086533926383191</v>
       </c>
-      <c r="BD17" s="11"/>
-      <c r="BE17" s="11"/>
-      <c r="BF17" s="11"/>
-      <c r="BG17" s="12"/>
-      <c r="BH17" s="12"/>
-      <c r="BI17" s="13"/>
+      <c r="BD17" s="11">
+        <v>379714</v>
+      </c>
+      <c r="BE17" s="11">
+        <v>5170</v>
+      </c>
+      <c r="BF17" s="11">
+        <v>48</v>
+      </c>
+      <c r="BG17" s="12">
+        <v>23732.125</v>
+      </c>
+      <c r="BH17" s="12">
+        <v>323.125</v>
+      </c>
+      <c r="BI17" s="13">
+        <v>1.638414109200903</v>
+      </c>
       <c r="BJ17" s="11"/>
       <c r="BK17" s="11"/>
       <c r="BL17" s="11"/>
@@ -6397,27 +6577,27 @@
       </c>
       <c r="N18" s="8">
         <f t="shared" si="0"/>
-        <v>258009.83333333334</v>
+        <v>272533.85714285716</v>
       </c>
       <c r="O18" s="8">
         <f t="shared" si="1"/>
-        <v>8516.5</v>
+        <v>9253.5714285714294</v>
       </c>
       <c r="P18" s="8">
         <f t="shared" si="2"/>
-        <v>247</v>
+        <v>298</v>
       </c>
       <c r="Q18" s="9">
         <f t="shared" si="3"/>
-        <v>18802.336032388663</v>
+        <v>19205.406040268455</v>
       </c>
       <c r="R18" s="9">
         <f t="shared" si="4"/>
-        <v>620.63562753036445</v>
+        <v>652.09731543624162</v>
       </c>
       <c r="S18" s="10">
         <f t="shared" si="5"/>
-        <v>2.5178478934014596</v>
+        <v>2.5413787398104302</v>
       </c>
       <c r="T18" s="11">
         <v>208128</v>
@@ -6527,12 +6707,24 @@
       <c r="BC18" s="13">
         <v>2.299224346803542</v>
       </c>
-      <c r="BD18" s="11"/>
-      <c r="BE18" s="11"/>
-      <c r="BF18" s="11"/>
-      <c r="BG18" s="12"/>
-      <c r="BH18" s="12"/>
-      <c r="BI18" s="13"/>
+      <c r="BD18" s="11">
+        <v>359678</v>
+      </c>
+      <c r="BE18" s="11">
+        <v>13676</v>
+      </c>
+      <c r="BF18" s="11">
+        <v>51</v>
+      </c>
+      <c r="BG18" s="12">
+        <v>21157.52941176471</v>
+      </c>
+      <c r="BH18" s="12">
+        <v>804.47058823529414</v>
+      </c>
+      <c r="BI18" s="13">
+        <v>2.6825638182642542</v>
+      </c>
       <c r="BJ18" s="11"/>
       <c r="BK18" s="11"/>
       <c r="BL18" s="11"/>
@@ -6604,27 +6796,27 @@
       </c>
       <c r="N19" s="8">
         <f t="shared" si="0"/>
-        <v>86617.80333333333</v>
+        <v>88643.402857142864</v>
       </c>
       <c r="O19" s="8">
         <f t="shared" si="1"/>
-        <v>279160.83333333331</v>
+        <v>285159.28571428574</v>
       </c>
       <c r="P19" s="8">
         <f t="shared" si="2"/>
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="Q19" s="9">
         <f t="shared" si="3"/>
-        <v>4668.025329341317</v>
+        <v>4688.945743073049</v>
       </c>
       <c r="R19" s="9">
         <f t="shared" si="4"/>
-        <v>15044.595808383234</v>
+        <v>15083.992443324936</v>
       </c>
       <c r="S19" s="10">
         <f t="shared" si="5"/>
-        <v>27.614101112654108</v>
+        <v>27.644456218910385</v>
       </c>
       <c r="T19" s="11">
         <v>82762</v>
@@ -6734,12 +6926,24 @@
       <c r="BC19" s="13">
         <v>26.905567424091291</v>
       </c>
-      <c r="BD19" s="11"/>
-      <c r="BE19" s="11"/>
-      <c r="BF19" s="11"/>
-      <c r="BG19" s="12"/>
-      <c r="BH19" s="12"/>
-      <c r="BI19" s="13"/>
+      <c r="BD19" s="11">
+        <v>100797</v>
+      </c>
+      <c r="BE19" s="11">
+        <v>321150</v>
+      </c>
+      <c r="BF19" s="11">
+        <v>63</v>
+      </c>
+      <c r="BG19" s="12">
+        <v>4799.8571428571431</v>
+      </c>
+      <c r="BH19" s="12">
+        <v>15292.857142857139</v>
+      </c>
+      <c r="BI19" s="13">
+        <v>27.826586856448039</v>
+      </c>
       <c r="BJ19" s="11"/>
       <c r="BK19" s="11"/>
       <c r="BL19" s="11"/>
@@ -6811,27 +7015,27 @@
       </c>
       <c r="N20" s="8">
         <f t="shared" si="0"/>
-        <v>125470.5</v>
+        <v>129092.57142857143</v>
       </c>
       <c r="O20" s="8">
         <f t="shared" si="1"/>
-        <v>16333.5</v>
+        <v>16543.285714285714</v>
       </c>
       <c r="P20" s="8">
         <f t="shared" si="2"/>
-        <v>202</v>
+        <v>242</v>
       </c>
       <c r="Q20" s="9">
         <f t="shared" si="3"/>
-        <v>11180.539603960397</v>
+        <v>11202.247933884299</v>
       </c>
       <c r="R20" s="9">
         <f t="shared" si="4"/>
-        <v>1455.4603960396039</v>
+        <v>1435.5743801652893</v>
       </c>
       <c r="S20" s="10">
         <f t="shared" si="5"/>
-        <v>5.7059387069912075</v>
+        <v>5.6651271177596243</v>
       </c>
       <c r="T20" s="11">
         <v>173630</v>
@@ -6941,12 +7145,24 @@
       <c r="BC20" s="13">
         <v>5.603868453536581</v>
       </c>
-      <c r="BD20" s="11"/>
-      <c r="BE20" s="11"/>
-      <c r="BF20" s="11"/>
-      <c r="BG20" s="12"/>
-      <c r="BH20" s="12"/>
-      <c r="BI20" s="13"/>
+      <c r="BD20" s="11">
+        <v>150825</v>
+      </c>
+      <c r="BE20" s="11">
+        <v>17802</v>
+      </c>
+      <c r="BF20" s="11">
+        <v>40</v>
+      </c>
+      <c r="BG20" s="12">
+        <v>11311.875</v>
+      </c>
+      <c r="BH20" s="12">
+        <v>1335.15</v>
+      </c>
+      <c r="BI20" s="13">
+        <v>5.4202575823701258</v>
+      </c>
       <c r="BJ20" s="11"/>
       <c r="BK20" s="11"/>
       <c r="BL20" s="11"/>
@@ -7018,27 +7234,27 @@
       </c>
       <c r="N21" s="8">
         <f t="shared" si="0"/>
-        <v>450611.66666666669</v>
+        <v>451408.28571428574</v>
       </c>
       <c r="O21" s="8">
         <f t="shared" si="1"/>
-        <v>125173.33333333333</v>
+        <v>126742.57142857143</v>
       </c>
       <c r="P21" s="8">
         <f t="shared" si="2"/>
-        <v>394</v>
+        <v>457</v>
       </c>
       <c r="Q21" s="9">
         <f t="shared" si="3"/>
-        <v>20586.319796954314</v>
+        <v>20743.050328227571</v>
       </c>
       <c r="R21" s="9">
         <f t="shared" si="4"/>
-        <v>5718.5786802030452</v>
+        <v>5824.0568927789936</v>
       </c>
       <c r="S21" s="10">
         <f t="shared" si="5"/>
-        <v>7.0817269510923637</v>
+        <v>7.1194746076906688</v>
       </c>
       <c r="T21" s="11">
         <v>514374</v>
@@ -7148,12 +7364,24 @@
       <c r="BC21" s="13">
         <v>7.1402110230593987</v>
       </c>
-      <c r="BD21" s="11"/>
-      <c r="BE21" s="11"/>
-      <c r="BF21" s="11"/>
-      <c r="BG21" s="12"/>
-      <c r="BH21" s="12"/>
-      <c r="BI21" s="13"/>
+      <c r="BD21" s="11">
+        <v>456188</v>
+      </c>
+      <c r="BE21" s="11">
+        <v>136158</v>
+      </c>
+      <c r="BF21" s="11">
+        <v>63</v>
+      </c>
+      <c r="BG21" s="12">
+        <v>21723.238095238099</v>
+      </c>
+      <c r="BH21" s="12">
+        <v>6483.7142857142862</v>
+      </c>
+      <c r="BI21" s="13">
+        <v>7.3459605472804954</v>
+      </c>
       <c r="BJ21" s="11"/>
       <c r="BK21" s="11"/>
       <c r="BL21" s="11"/>
@@ -7225,27 +7453,27 @@
       </c>
       <c r="N22" s="8">
         <f t="shared" si="0"/>
-        <v>450455.5</v>
+        <v>463890.85714285716</v>
       </c>
       <c r="O22" s="8">
         <f t="shared" si="1"/>
-        <v>111704.83333333333</v>
+        <v>115191.85714285714</v>
       </c>
       <c r="P22" s="8">
         <f t="shared" si="2"/>
-        <v>388</v>
+        <v>466</v>
       </c>
       <c r="Q22" s="9">
         <f t="shared" si="3"/>
-        <v>20897.420103092783</v>
+        <v>20904.952789699571</v>
       </c>
       <c r="R22" s="9">
         <f t="shared" si="4"/>
-        <v>5182.182989690722</v>
+        <v>5191.0493562231759</v>
       </c>
       <c r="S22" s="10">
         <f t="shared" si="5"/>
-        <v>6.6185035299889767</v>
+        <v>6.6382495080633186</v>
       </c>
       <c r="T22" s="11">
         <v>555592</v>
@@ -7355,12 +7583,24 @@
       <c r="BC22" s="13">
         <v>6.7904396372800404</v>
       </c>
-      <c r="BD22" s="11"/>
-      <c r="BE22" s="11"/>
-      <c r="BF22" s="11"/>
-      <c r="BG22" s="12"/>
-      <c r="BH22" s="12"/>
-      <c r="BI22" s="13"/>
+      <c r="BD22" s="11">
+        <v>544503</v>
+      </c>
+      <c r="BE22" s="11">
+        <v>136114</v>
+      </c>
+      <c r="BF22" s="11">
+        <v>78</v>
+      </c>
+      <c r="BG22" s="12">
+        <v>20942.423076923082</v>
+      </c>
+      <c r="BH22" s="12">
+        <v>5235.1538461538457</v>
+      </c>
+      <c r="BI22" s="13">
+        <v>6.756725376509376</v>
+      </c>
       <c r="BJ22" s="11"/>
       <c r="BK22" s="11"/>
       <c r="BL22" s="11"/>
@@ -7432,27 +7672,27 @@
       </c>
       <c r="N23" s="8">
         <f t="shared" si="0"/>
-        <v>307512.5</v>
+        <v>317798.14285714284</v>
       </c>
       <c r="O23" s="8">
         <f t="shared" si="1"/>
-        <v>11472.333333333334</v>
+        <v>11843.142857142857</v>
       </c>
       <c r="P23" s="8">
         <f t="shared" si="2"/>
-        <v>287</v>
+        <v>346</v>
       </c>
       <c r="Q23" s="9">
         <f t="shared" si="3"/>
-        <v>19286.498257839721</v>
+        <v>19288.326589595374</v>
       </c>
       <c r="R23" s="9">
         <f t="shared" si="4"/>
-        <v>719.51916376306622</v>
+        <v>718.80346820809245</v>
       </c>
       <c r="S23" s="10">
         <f t="shared" si="5"/>
-        <v>2.656960063317126</v>
+        <v>2.6559657685575364</v>
       </c>
       <c r="T23" s="11">
         <v>295520</v>
@@ -7562,12 +7802,24 @@
       <c r="BC23" s="13">
         <v>2.65</v>
       </c>
-      <c r="BD23" s="11"/>
-      <c r="BE23" s="11"/>
-      <c r="BF23" s="11"/>
-      <c r="BG23" s="12"/>
-      <c r="BH23" s="12"/>
-      <c r="BI23" s="13"/>
+      <c r="BD23" s="11">
+        <v>379512</v>
+      </c>
+      <c r="BE23" s="11">
+        <v>14068</v>
+      </c>
+      <c r="BF23" s="11">
+        <v>59</v>
+      </c>
+      <c r="BG23" s="12">
+        <v>19297.22033898305</v>
+      </c>
+      <c r="BH23" s="12">
+        <v>715.32203389830511</v>
+      </c>
+      <c r="BI23" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BJ23" s="11"/>
       <c r="BK23" s="11"/>
       <c r="BL23" s="11"/>
@@ -7639,27 +7891,27 @@
       </c>
       <c r="N24" s="8">
         <f t="shared" si="0"/>
-        <v>219855.83333333334</v>
+        <v>237242.57142857142</v>
       </c>
       <c r="O24" s="8">
         <f t="shared" si="1"/>
-        <v>3524.3333333333335</v>
+        <v>3696.7142857142858</v>
       </c>
       <c r="P24" s="8">
         <f t="shared" si="2"/>
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="Q24" s="9">
         <f t="shared" si="3"/>
-        <v>19688.582089552241</v>
+        <v>20502.444444444445</v>
       </c>
       <c r="R24" s="9">
         <f t="shared" si="4"/>
-        <v>315.61194029850748</v>
+        <v>319.46913580246911</v>
       </c>
       <c r="S24" s="10">
         <f t="shared" si="5"/>
-        <v>1.7690582197839098</v>
+        <v>1.7527465452190039</v>
       </c>
       <c r="T24" s="11">
         <v>328339</v>
@@ -7769,12 +8021,24 @@
       <c r="BC24" s="13">
         <v>1.7276587704450439</v>
       </c>
-      <c r="BD24" s="11"/>
-      <c r="BE24" s="11"/>
-      <c r="BF24" s="11"/>
-      <c r="BG24" s="12"/>
-      <c r="BH24" s="12"/>
-      <c r="BI24" s="13"/>
+      <c r="BD24" s="11">
+        <v>341563</v>
+      </c>
+      <c r="BE24" s="11">
+        <v>4731</v>
+      </c>
+      <c r="BF24" s="11">
+        <v>42</v>
+      </c>
+      <c r="BG24" s="12">
+        <v>24397.357142857141</v>
+      </c>
+      <c r="BH24" s="12">
+        <v>337.92857142857139</v>
+      </c>
+      <c r="BI24" s="13">
+        <v>1.654876497829568</v>
+      </c>
       <c r="BJ24" s="11"/>
       <c r="BK24" s="11"/>
       <c r="BL24" s="11"/>
@@ -7846,27 +8110,27 @@
       </c>
       <c r="N25" s="8">
         <f t="shared" si="0"/>
-        <v>260788.83333333334</v>
+        <v>265108.71428571426</v>
       </c>
       <c r="O25" s="8">
         <f t="shared" si="1"/>
-        <v>18001.333333333332</v>
+        <v>18643</v>
       </c>
       <c r="P25" s="8">
         <f t="shared" si="2"/>
-        <v>314</v>
+        <v>377</v>
       </c>
       <c r="Q25" s="9">
         <f t="shared" si="3"/>
-        <v>14949.678343949043</v>
+        <v>14767.328912466844</v>
       </c>
       <c r="R25" s="9">
         <f t="shared" si="4"/>
-        <v>1031.9235668789809</v>
+        <v>1038.46949602122</v>
       </c>
       <c r="S25" s="10">
         <f t="shared" si="5"/>
-        <v>3.6601529019213435</v>
+        <v>3.6988292465955643</v>
       </c>
       <c r="T25" s="11">
         <v>254251</v>
@@ -7976,12 +8240,24 @@
       <c r="BC25" s="13">
         <v>3.8438556762864411</v>
       </c>
-      <c r="BD25" s="11"/>
-      <c r="BE25" s="11"/>
-      <c r="BF25" s="11"/>
-      <c r="BG25" s="12"/>
-      <c r="BH25" s="12"/>
-      <c r="BI25" s="13"/>
+      <c r="BD25" s="11">
+        <v>291028</v>
+      </c>
+      <c r="BE25" s="11">
+        <v>22493</v>
+      </c>
+      <c r="BF25" s="11">
+        <v>63</v>
+      </c>
+      <c r="BG25" s="12">
+        <v>13858.476190476191</v>
+      </c>
+      <c r="BH25" s="12">
+        <v>1071.0952380952381</v>
+      </c>
+      <c r="BI25" s="13">
+        <v>3.930887314640886</v>
+      </c>
       <c r="BJ25" s="11"/>
       <c r="BK25" s="11"/>
       <c r="BL25" s="11"/>
@@ -8053,27 +8329,27 @@
       </c>
       <c r="N26" s="8">
         <f t="shared" ref="N26:N52" si="6">IFERROR(AVERAGE(T26,Z26,AF26,AL26,AR26,AX26,BD26,BJ26,BP26,BV26,CB26,CH26)," ")</f>
-        <v>308210.16666666669</v>
+        <v>313798</v>
       </c>
       <c r="O26" s="8">
         <f t="shared" ref="O26:O52" si="7">IFERROR(AVERAGE(U26,AA26,AG26,AM26,AS26,AY26,BE26,BK26,BQ26,BW26,CC26,CI26)," ")</f>
-        <v>23270.5</v>
+        <v>24049.428571428572</v>
       </c>
       <c r="P26" s="8">
         <f t="shared" ref="P26:P52" si="8">IFERROR(SUM(V26,AB26,AH26,AN26,AT26,AZ26,BF26,BL26,BR26,BX26,CD26,CJ26)," ")</f>
-        <v>336</v>
+        <v>399</v>
       </c>
       <c r="Q26" s="9">
         <f t="shared" ref="Q26:Q52" si="9">IFERROR(SUM(T26,Z26,AF26,AL26,AR26,AX26,BD26,BJ26,BP26,BV26,CB26,CH26)/P26*3," ")</f>
-        <v>16511.258928571428</v>
+        <v>16515.684210526317</v>
       </c>
       <c r="R26" s="9">
         <f t="shared" ref="R26:R52" si="10">IFERROR(SUM(U26,AA26,AG26,AM26,AS26,AY26,BE26,BK26,BQ26,BW26,CC26,CI26)/P26*3," ")</f>
-        <v>1246.6339285714284</v>
+        <v>1265.7593984962405</v>
       </c>
       <c r="S26" s="10">
         <f t="shared" ref="S26:S52" si="11">IFERROR(AVERAGE(Y26,AE26,AK26,AQ26,AW26,BC26,BI26,BO26,BU26,CA26,CG26,CM26)," ")</f>
-        <v>3.8155164885547275</v>
+        <v>3.8504046403559715</v>
       </c>
       <c r="T26" s="11">
         <v>319242</v>
@@ -8183,12 +8459,24 @@
       <c r="BC26" s="13">
         <v>4.1206004486742041</v>
       </c>
-      <c r="BD26" s="11"/>
-      <c r="BE26" s="11"/>
-      <c r="BF26" s="11"/>
-      <c r="BG26" s="12"/>
-      <c r="BH26" s="12"/>
-      <c r="BI26" s="13"/>
+      <c r="BD26" s="11">
+        <v>347325</v>
+      </c>
+      <c r="BE26" s="11">
+        <v>28723</v>
+      </c>
+      <c r="BF26" s="11">
+        <v>63</v>
+      </c>
+      <c r="BG26" s="12">
+        <v>16539.285714285721</v>
+      </c>
+      <c r="BH26" s="12">
+        <v>1367.761904761905</v>
+      </c>
+      <c r="BI26" s="13">
+        <v>4.0597335511634371</v>
+      </c>
       <c r="BJ26" s="11"/>
       <c r="BK26" s="11"/>
       <c r="BL26" s="11"/>
@@ -8260,27 +8548,27 @@
       </c>
       <c r="N27" s="8">
         <f t="shared" si="6"/>
-        <v>14889</v>
+        <v>19410</v>
       </c>
       <c r="O27" s="8">
         <f t="shared" si="7"/>
-        <v>1170</v>
+        <v>1826</v>
       </c>
       <c r="P27" s="8">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Q27" s="9">
         <f t="shared" si="9"/>
-        <v>14889</v>
+        <v>12477.857142857145</v>
       </c>
       <c r="R27" s="9">
         <f t="shared" si="10"/>
-        <v>1170</v>
+        <v>1173.8571428571429</v>
       </c>
       <c r="S27" s="10">
         <f t="shared" si="11"/>
-        <v>4.0049999999999999</v>
+        <v>4.2324815492607613</v>
       </c>
       <c r="T27" s="11"/>
       <c r="U27" s="11"/>
@@ -8342,12 +8630,24 @@
       <c r="BA27" s="12"/>
       <c r="BB27" s="12"/>
       <c r="BC27" s="13"/>
-      <c r="BD27" s="11"/>
-      <c r="BE27" s="11"/>
-      <c r="BF27" s="11"/>
-      <c r="BG27" s="12"/>
-      <c r="BH27" s="12"/>
-      <c r="BI27" s="13"/>
+      <c r="BD27" s="11">
+        <v>28452</v>
+      </c>
+      <c r="BE27" s="11">
+        <v>3138</v>
+      </c>
+      <c r="BF27" s="11">
+        <v>8</v>
+      </c>
+      <c r="BG27" s="12">
+        <v>10669.5</v>
+      </c>
+      <c r="BH27" s="12">
+        <v>1176.75</v>
+      </c>
+      <c r="BI27" s="13">
+        <v>4.687444647782284</v>
+      </c>
       <c r="BJ27" s="11"/>
       <c r="BK27" s="11"/>
       <c r="BL27" s="11"/>
@@ -8419,27 +8719,27 @@
       </c>
       <c r="N28" s="8">
         <f t="shared" si="6"/>
-        <v>279018.16666666669</v>
+        <v>280717</v>
       </c>
       <c r="O28" s="8">
         <f t="shared" si="7"/>
-        <v>79197.833333333328</v>
+        <v>76913.428571428565</v>
       </c>
       <c r="P28" s="8">
         <f t="shared" si="8"/>
-        <v>370</v>
+        <v>437</v>
       </c>
       <c r="Q28" s="9">
         <f t="shared" si="9"/>
-        <v>13573.856756756757</v>
+        <v>13489.832951945082</v>
       </c>
       <c r="R28" s="9">
         <f t="shared" si="10"/>
-        <v>3852.8675675675677</v>
+        <v>3696.0686498855839</v>
       </c>
       <c r="S28" s="10">
         <f t="shared" si="11"/>
-        <v>7.3866362727218968</v>
+        <v>7.2535377061416897</v>
       </c>
       <c r="T28" s="11">
         <v>362826</v>
@@ -8549,12 +8849,24 @@
       <c r="BC28" s="13">
         <v>7.3228424663075469</v>
       </c>
-      <c r="BD28" s="11"/>
-      <c r="BE28" s="11"/>
-      <c r="BF28" s="11"/>
-      <c r="BG28" s="12"/>
-      <c r="BH28" s="12"/>
-      <c r="BI28" s="13"/>
+      <c r="BD28" s="11">
+        <v>290910</v>
+      </c>
+      <c r="BE28" s="11">
+        <v>63207</v>
+      </c>
+      <c r="BF28" s="11">
+        <v>67</v>
+      </c>
+      <c r="BG28" s="12">
+        <v>13025.820895522391</v>
+      </c>
+      <c r="BH28" s="12">
+        <v>2830.1641791044781</v>
+      </c>
+      <c r="BI28" s="13">
+        <v>6.4549463066604442</v>
+      </c>
       <c r="BJ28" s="11"/>
       <c r="BK28" s="11"/>
       <c r="BL28" s="11"/>
@@ -8626,27 +8938,27 @@
       </c>
       <c r="N29" s="8">
         <f t="shared" si="6"/>
-        <v>64769.8</v>
+        <v>62633.166666666664</v>
       </c>
       <c r="O29" s="8">
         <f t="shared" si="7"/>
-        <v>34780.800000000003</v>
+        <v>33123.833333333336</v>
       </c>
       <c r="P29" s="8">
         <f t="shared" si="8"/>
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="Q29" s="9">
         <f t="shared" si="9"/>
-        <v>13879.242857142857</v>
+        <v>14092.462500000001</v>
       </c>
       <c r="R29" s="9">
         <f t="shared" si="10"/>
-        <v>7453.028571428571</v>
+        <v>7452.8624999999993</v>
       </c>
       <c r="S29" s="10">
         <f t="shared" si="11"/>
-        <v>11.441056672138732</v>
+        <v>11.350575665257372</v>
       </c>
       <c r="T29" s="11">
         <v>83538</v>
@@ -8744,12 +9056,24 @@
       <c r="BC29" s="13">
         <v>8.1428457439153004</v>
       </c>
-      <c r="BD29" s="11"/>
-      <c r="BE29" s="11"/>
-      <c r="BF29" s="11"/>
-      <c r="BG29" s="12"/>
-      <c r="BH29" s="12"/>
-      <c r="BI29" s="13"/>
+      <c r="BD29" s="11">
+        <v>51950</v>
+      </c>
+      <c r="BE29" s="11">
+        <v>24839</v>
+      </c>
+      <c r="BF29" s="11">
+        <v>10</v>
+      </c>
+      <c r="BG29" s="12">
+        <v>15585</v>
+      </c>
+      <c r="BH29" s="12">
+        <v>7451.7000000000007</v>
+      </c>
+      <c r="BI29" s="13">
+        <v>10.89817063085056</v>
+      </c>
       <c r="BJ29" s="11"/>
       <c r="BK29" s="11"/>
       <c r="BL29" s="11"/>
@@ -8821,27 +9145,27 @@
       </c>
       <c r="N30" s="8">
         <f t="shared" si="6"/>
-        <v>161825</v>
+        <v>164642.85714285713</v>
       </c>
       <c r="O30" s="8">
         <f t="shared" si="7"/>
-        <v>126883.83333333333</v>
+        <v>128809.28571428571</v>
       </c>
       <c r="P30" s="8">
         <f t="shared" si="8"/>
-        <v>281</v>
+        <v>341</v>
       </c>
       <c r="Q30" s="9">
         <f t="shared" si="9"/>
-        <v>10366.014234875445</v>
+        <v>10139.296187683285</v>
       </c>
       <c r="R30" s="9">
         <f t="shared" si="10"/>
-        <v>8127.790035587188</v>
+        <v>7932.5366568914951</v>
       </c>
       <c r="S30" s="10">
         <f t="shared" si="11"/>
-        <v>13.977577357057838</v>
+        <v>13.951069132986433</v>
       </c>
       <c r="T30" s="11">
         <v>169875</v>
@@ -8951,12 +9275,24 @@
       <c r="BC30" s="13">
         <v>15.14517868490738</v>
       </c>
-      <c r="BD30" s="11"/>
-      <c r="BE30" s="11"/>
-      <c r="BF30" s="11"/>
-      <c r="BG30" s="12"/>
-      <c r="BH30" s="12"/>
-      <c r="BI30" s="13"/>
+      <c r="BD30" s="11">
+        <v>181550</v>
+      </c>
+      <c r="BE30" s="11">
+        <v>140362</v>
+      </c>
+      <c r="BF30" s="11">
+        <v>60</v>
+      </c>
+      <c r="BG30" s="12">
+        <v>9077.5</v>
+      </c>
+      <c r="BH30" s="12">
+        <v>7018.1</v>
+      </c>
+      <c r="BI30" s="13">
+        <v>13.79201978855801</v>
+      </c>
       <c r="BJ30" s="11"/>
       <c r="BK30" s="11"/>
       <c r="BL30" s="11"/>
@@ -9028,27 +9364,27 @@
       </c>
       <c r="N31" s="8">
         <f t="shared" si="6"/>
-        <v>93861</v>
+        <v>85216.833333333328</v>
       </c>
       <c r="O31" s="8">
         <f t="shared" si="7"/>
-        <v>3379.6</v>
+        <v>3037.6666666666665</v>
       </c>
       <c r="P31" s="8">
         <f t="shared" si="8"/>
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="9">
         <f t="shared" si="9"/>
-        <v>12570.669642857145</v>
+        <v>12572.975409836065</v>
       </c>
       <c r="R31" s="9">
         <f t="shared" si="10"/>
-        <v>452.625</v>
+        <v>448.18032786885249</v>
       </c>
       <c r="S31" s="10">
         <f t="shared" si="11"/>
-        <v>2.6550958073826409</v>
+        <v>2.6305315189596219</v>
       </c>
       <c r="T31" s="11"/>
       <c r="U31" s="11"/>
@@ -9146,12 +9482,24 @@
       <c r="BC31" s="13">
         <v>2.6183393614605972</v>
       </c>
-      <c r="BD31" s="11"/>
-      <c r="BE31" s="11"/>
-      <c r="BF31" s="11"/>
-      <c r="BG31" s="12"/>
-      <c r="BH31" s="12"/>
-      <c r="BI31" s="13"/>
+      <c r="BD31" s="11">
+        <v>41996</v>
+      </c>
+      <c r="BE31" s="11">
+        <v>1328</v>
+      </c>
+      <c r="BF31" s="11">
+        <v>10</v>
+      </c>
+      <c r="BG31" s="12">
+        <v>12598.8</v>
+      </c>
+      <c r="BH31" s="12">
+        <v>398.4</v>
+      </c>
+      <c r="BI31" s="13">
+        <v>2.5077100768445248</v>
+      </c>
       <c r="BJ31" s="11"/>
       <c r="BK31" s="11"/>
       <c r="BL31" s="11"/>
@@ -9223,23 +9571,23 @@
       </c>
       <c r="N32" s="8">
         <f t="shared" si="6"/>
-        <v>196190</v>
+        <v>211020</v>
       </c>
       <c r="O32" s="8">
         <f t="shared" si="7"/>
-        <v>69639.333333333328</v>
+        <v>74905.142857142855</v>
       </c>
       <c r="P32" s="8">
         <f t="shared" si="8"/>
-        <v>205</v>
+        <v>257</v>
       </c>
       <c r="Q32" s="9">
         <f t="shared" si="9"/>
-        <v>17226.439024390245</v>
+        <v>17242.879377431906</v>
       </c>
       <c r="R32" s="9">
         <f t="shared" si="10"/>
-        <v>6114.6731707317076</v>
+        <v>6120.6536964980542</v>
       </c>
       <c r="S32" s="10">
         <f t="shared" si="11"/>
@@ -9353,12 +9701,24 @@
       <c r="BC32" s="13">
         <v>10</v>
       </c>
-      <c r="BD32" s="11"/>
-      <c r="BE32" s="11"/>
-      <c r="BF32" s="11"/>
-      <c r="BG32" s="12"/>
-      <c r="BH32" s="12"/>
-      <c r="BI32" s="13"/>
+      <c r="BD32" s="11">
+        <v>300000</v>
+      </c>
+      <c r="BE32" s="11">
+        <v>106500</v>
+      </c>
+      <c r="BF32" s="11">
+        <v>52</v>
+      </c>
+      <c r="BG32" s="12">
+        <v>17307.692307692309</v>
+      </c>
+      <c r="BH32" s="12">
+        <v>6144.2307692307686</v>
+      </c>
+      <c r="BI32" s="13">
+        <v>10</v>
+      </c>
       <c r="BJ32" s="11"/>
       <c r="BK32" s="11"/>
       <c r="BL32" s="11"/>
@@ -9613,27 +9973,27 @@
       </c>
       <c r="N34" s="8">
         <f t="shared" si="6"/>
-        <v>18977.5</v>
+        <v>17603.571428571428</v>
       </c>
       <c r="O34" s="8">
         <f t="shared" si="7"/>
-        <v>83578</v>
+        <v>80373.28571428571</v>
       </c>
       <c r="P34" s="8">
         <f t="shared" si="8"/>
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="Q34" s="9">
         <f t="shared" si="9"/>
-        <v>3558.28125</v>
+        <v>3554.5673076923076</v>
       </c>
       <c r="R34" s="9">
         <f t="shared" si="10"/>
-        <v>15670.875</v>
+        <v>16229.221153846154</v>
       </c>
       <c r="S34" s="10">
         <f t="shared" si="11"/>
-        <v>35.141098531069908</v>
+        <v>35.832047054656606</v>
       </c>
       <c r="T34" s="11">
         <v>44447</v>
@@ -9743,12 +10103,24 @@
       <c r="BC34" s="13">
         <v>32.029961242363832</v>
       </c>
-      <c r="BD34" s="11"/>
-      <c r="BE34" s="11"/>
-      <c r="BF34" s="11"/>
-      <c r="BG34" s="12"/>
-      <c r="BH34" s="12"/>
-      <c r="BI34" s="13"/>
+      <c r="BD34" s="11">
+        <v>9360</v>
+      </c>
+      <c r="BE34" s="11">
+        <v>61145</v>
+      </c>
+      <c r="BF34" s="11">
+        <v>8</v>
+      </c>
+      <c r="BG34" s="12">
+        <v>3510</v>
+      </c>
+      <c r="BH34" s="12">
+        <v>22929.375</v>
+      </c>
+      <c r="BI34" s="13">
+        <v>39.977738196176773</v>
+      </c>
       <c r="BJ34" s="11"/>
       <c r="BK34" s="11"/>
       <c r="BL34" s="11"/>
@@ -9991,27 +10363,27 @@
       </c>
       <c r="N36" s="8">
         <f t="shared" si="6"/>
-        <v>49994</v>
+        <v>45159.428571428572</v>
       </c>
       <c r="O36" s="8">
         <f t="shared" si="7"/>
-        <v>3872.8333333333335</v>
+        <v>3490.1428571428573</v>
       </c>
       <c r="P36" s="8">
         <f t="shared" si="8"/>
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="Q36" s="9">
         <f t="shared" si="9"/>
-        <v>11537.076923076922</v>
+        <v>11289.857142857143</v>
       </c>
       <c r="R36" s="9">
         <f t="shared" si="10"/>
-        <v>893.73076923076928</v>
+        <v>872.53571428571422</v>
       </c>
       <c r="S36" s="10">
         <f t="shared" si="11"/>
-        <v>8.520570861114706</v>
+        <v>7.8533464523840335</v>
       </c>
       <c r="T36" s="11">
         <v>68082</v>
@@ -10121,12 +10493,24 @@
       <c r="BC36" s="13">
         <v>3.3424809575728851</v>
       </c>
-      <c r="BD36" s="11"/>
-      <c r="BE36" s="11"/>
-      <c r="BF36" s="11"/>
-      <c r="BG36" s="12"/>
-      <c r="BH36" s="12"/>
-      <c r="BI36" s="13"/>
+      <c r="BD36" s="11">
+        <v>16152</v>
+      </c>
+      <c r="BE36" s="11">
+        <v>1194</v>
+      </c>
+      <c r="BF36" s="11">
+        <v>6</v>
+      </c>
+      <c r="BG36" s="12">
+        <v>8076</v>
+      </c>
+      <c r="BH36" s="12">
+        <v>597</v>
+      </c>
+      <c r="BI36" s="13">
+        <v>3.85</v>
+      </c>
       <c r="BJ36" s="11"/>
       <c r="BK36" s="11"/>
       <c r="BL36" s="11"/>
@@ -10198,27 +10582,27 @@
       </c>
       <c r="N37" s="8">
         <f t="shared" si="6"/>
-        <v>70926.166666666672</v>
+        <v>63698.714285714283</v>
       </c>
       <c r="O37" s="8">
         <f t="shared" si="7"/>
-        <v>5475.666666666667</v>
+        <v>4887.1428571428569</v>
       </c>
       <c r="P37" s="8">
         <f t="shared" si="8"/>
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="Q37" s="9">
         <f t="shared" si="9"/>
-        <v>10132.309523809523</v>
+        <v>9982.63432835821</v>
       </c>
       <c r="R37" s="9">
         <f t="shared" si="10"/>
-        <v>782.23809523809518</v>
+        <v>765.8955223880597</v>
       </c>
       <c r="S37" s="10">
         <f t="shared" si="11"/>
-        <v>3.5022134901769935</v>
+        <v>3.5224409475083016</v>
       </c>
       <c r="T37" s="11">
         <v>60720</v>
@@ -10328,12 +10712,24 @@
       <c r="BC37" s="13">
         <v>3.434782285793696</v>
       </c>
-      <c r="BD37" s="11"/>
-      <c r="BE37" s="11"/>
-      <c r="BF37" s="11"/>
-      <c r="BG37" s="12"/>
-      <c r="BH37" s="12"/>
-      <c r="BI37" s="13"/>
+      <c r="BD37" s="11">
+        <v>20334</v>
+      </c>
+      <c r="BE37" s="11">
+        <v>1356</v>
+      </c>
+      <c r="BF37" s="11">
+        <v>8</v>
+      </c>
+      <c r="BG37" s="12">
+        <v>7625.25</v>
+      </c>
+      <c r="BH37" s="12">
+        <v>508.5</v>
+      </c>
+      <c r="BI37" s="13">
+        <v>3.6438056914961532</v>
+      </c>
       <c r="BJ37" s="11"/>
       <c r="BK37" s="11"/>
       <c r="BL37" s="11"/>
@@ -11005,27 +11401,27 @@
       </c>
       <c r="N42" s="8">
         <f t="shared" si="6"/>
-        <v>18845.833333333332</v>
+        <v>19953.571428571428</v>
       </c>
       <c r="O42" s="8">
         <f t="shared" si="7"/>
-        <v>46034</v>
+        <v>47971.428571428572</v>
       </c>
       <c r="P42" s="8">
         <f t="shared" si="8"/>
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="Q42" s="9">
         <f t="shared" si="9"/>
-        <v>4136.8902439024387</v>
+        <v>4275.7653061224491</v>
       </c>
       <c r="R42" s="9">
         <f t="shared" si="10"/>
-        <v>10105.024390243903</v>
+        <v>10279.591836734693</v>
       </c>
       <c r="S42" s="10">
         <f t="shared" si="11"/>
-        <v>22.544267029174573</v>
+        <v>22.35962288199687</v>
       </c>
       <c r="T42" s="11">
         <v>16200</v>
@@ -11135,12 +11531,24 @@
       <c r="BC42" s="13">
         <v>22.213746115738829</v>
       </c>
-      <c r="BD42" s="11"/>
-      <c r="BE42" s="11"/>
-      <c r="BF42" s="11"/>
-      <c r="BG42" s="12"/>
-      <c r="BH42" s="12"/>
-      <c r="BI42" s="13"/>
+      <c r="BD42" s="11">
+        <v>26600</v>
+      </c>
+      <c r="BE42" s="11">
+        <v>59596</v>
+      </c>
+      <c r="BF42" s="11">
+        <v>16</v>
+      </c>
+      <c r="BG42" s="12">
+        <v>4987.5</v>
+      </c>
+      <c r="BH42" s="12">
+        <v>11174.25</v>
+      </c>
+      <c r="BI42" s="13">
+        <v>21.25175799893065</v>
+      </c>
       <c r="BJ42" s="11"/>
       <c r="BK42" s="11"/>
       <c r="BL42" s="11"/>
@@ -11212,27 +11620,27 @@
       </c>
       <c r="N43" s="8">
         <f t="shared" si="6"/>
-        <v>364652</v>
+        <v>392132.42857142858</v>
       </c>
       <c r="O43" s="8">
         <f t="shared" si="7"/>
-        <v>14022.333333333334</v>
+        <v>14967.285714285714</v>
       </c>
       <c r="P43" s="8">
         <f t="shared" si="8"/>
-        <v>298</v>
+        <v>375</v>
       </c>
       <c r="Q43" s="9">
         <f t="shared" si="9"/>
-        <v>22025.959731543626</v>
+        <v>21959.416000000001</v>
       </c>
       <c r="R43" s="9">
         <f t="shared" si="10"/>
-        <v>846.98657718120808</v>
+        <v>838.16800000000012</v>
       </c>
       <c r="S43" s="10">
         <f t="shared" si="11"/>
-        <v>2.6992076139422978</v>
+        <v>2.6921779548076836</v>
       </c>
       <c r="T43" s="11">
         <v>178860</v>
@@ -11342,12 +11750,24 @@
       <c r="BC43" s="13">
         <v>2.7722863364247941</v>
       </c>
-      <c r="BD43" s="11"/>
-      <c r="BE43" s="11"/>
-      <c r="BF43" s="11"/>
-      <c r="BG43" s="12"/>
-      <c r="BH43" s="12"/>
-      <c r="BI43" s="13"/>
+      <c r="BD43" s="11">
+        <v>557015</v>
+      </c>
+      <c r="BE43" s="11">
+        <v>20637</v>
+      </c>
+      <c r="BF43" s="11">
+        <v>77</v>
+      </c>
+      <c r="BG43" s="12">
+        <v>21701.88311688312</v>
+      </c>
+      <c r="BH43" s="12">
+        <v>804.03896103896113</v>
+      </c>
+      <c r="BI43" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BJ43" s="11"/>
       <c r="BK43" s="11"/>
       <c r="BL43" s="11"/>
@@ -11419,27 +11839,27 @@
       </c>
       <c r="N44" s="8">
         <f t="shared" si="6"/>
-        <v>354171.83333333331</v>
+        <v>384850.85714285716</v>
       </c>
       <c r="O44" s="8">
         <f t="shared" si="7"/>
-        <v>13624.833333333334</v>
+        <v>14692</v>
       </c>
       <c r="P44" s="8">
         <f t="shared" si="8"/>
-        <v>282</v>
+        <v>354</v>
       </c>
       <c r="Q44" s="9">
         <f t="shared" si="9"/>
-        <v>22606.712765957447</v>
+        <v>22830.135593220337</v>
       </c>
       <c r="R44" s="9">
         <f t="shared" si="10"/>
-        <v>869.67021276595733</v>
+        <v>871.5593220338983</v>
       </c>
       <c r="S44" s="10">
         <f t="shared" si="11"/>
-        <v>2.6964304612228123</v>
+        <v>2.6897975381909816</v>
       </c>
       <c r="T44" s="11">
         <v>184368</v>
@@ -11549,12 +11969,24 @@
       <c r="BC44" s="13">
         <v>2.7708113977929338</v>
       </c>
-      <c r="BD44" s="11"/>
-      <c r="BE44" s="11"/>
-      <c r="BF44" s="11"/>
-      <c r="BG44" s="12"/>
-      <c r="BH44" s="12"/>
-      <c r="BI44" s="13"/>
+      <c r="BD44" s="11">
+        <v>568925</v>
+      </c>
+      <c r="BE44" s="11">
+        <v>21095</v>
+      </c>
+      <c r="BF44" s="11">
+        <v>72</v>
+      </c>
+      <c r="BG44" s="12">
+        <v>23705.208333333339</v>
+      </c>
+      <c r="BH44" s="12">
+        <v>878.95833333333326</v>
+      </c>
+      <c r="BI44" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BJ44" s="11"/>
       <c r="BK44" s="11"/>
       <c r="BL44" s="11"/>
@@ -11626,27 +12058,27 @@
       </c>
       <c r="N45" s="8">
         <f t="shared" si="6"/>
-        <v>258210.16666666666</v>
+        <v>262462.57142857142</v>
       </c>
       <c r="O45" s="8">
         <f t="shared" si="7"/>
-        <v>5145.833333333333</v>
+        <v>5497.4285714285716</v>
       </c>
       <c r="P45" s="8">
         <f t="shared" si="8"/>
-        <v>236</v>
+        <v>294</v>
       </c>
       <c r="Q45" s="9">
         <f t="shared" si="9"/>
-        <v>19693.995762711864</v>
+        <v>18747.326530612245</v>
       </c>
       <c r="R45" s="9">
         <f t="shared" si="10"/>
-        <v>392.47881355932202</v>
+        <v>392.67346938775506</v>
       </c>
       <c r="S45" s="10">
         <f t="shared" si="11"/>
-        <v>2.001348894170246</v>
+        <v>2.0433823725204263</v>
       </c>
       <c r="T45" s="11">
         <v>281804</v>
@@ -11756,12 +12188,24 @@
       <c r="BC45" s="13">
         <v>2.1496531856782362</v>
       </c>
-      <c r="BD45" s="11"/>
-      <c r="BE45" s="11"/>
-      <c r="BF45" s="11"/>
-      <c r="BG45" s="12"/>
-      <c r="BH45" s="12"/>
-      <c r="BI45" s="13"/>
+      <c r="BD45" s="11">
+        <v>287977</v>
+      </c>
+      <c r="BE45" s="11">
+        <v>7607</v>
+      </c>
+      <c r="BF45" s="11">
+        <v>58</v>
+      </c>
+      <c r="BG45" s="12">
+        <v>14895.36206896552</v>
+      </c>
+      <c r="BH45" s="12">
+        <v>393.4655172413793</v>
+      </c>
+      <c r="BI45" s="13">
+        <v>2.2955832426215079</v>
+      </c>
       <c r="BJ45" s="11"/>
       <c r="BK45" s="11"/>
       <c r="BL45" s="11"/>
@@ -11833,27 +12277,27 @@
       </c>
       <c r="N46" s="8">
         <f t="shared" si="6"/>
-        <v>265010.16666666669</v>
+        <v>266598.85714285716</v>
       </c>
       <c r="O46" s="8">
         <f t="shared" si="7"/>
-        <v>5062.833333333333</v>
+        <v>5245.7142857142853</v>
       </c>
       <c r="P46" s="8">
         <f t="shared" si="8"/>
-        <v>227</v>
+        <v>284</v>
       </c>
       <c r="Q46" s="9">
         <f t="shared" si="9"/>
-        <v>21014.022026431718</v>
+        <v>19713.295774647886</v>
       </c>
       <c r="R46" s="9">
         <f t="shared" si="10"/>
-        <v>401.45814977973566</v>
+        <v>387.88732394366195</v>
       </c>
       <c r="S46" s="10">
         <f t="shared" si="11"/>
-        <v>1.9753226751853967</v>
+        <v>1.9982905333516783</v>
       </c>
       <c r="T46" s="11">
         <v>407925</v>
@@ -11963,12 +12407,24 @@
       <c r="BC46" s="13">
         <v>2.04633590334551</v>
       </c>
-      <c r="BD46" s="11"/>
-      <c r="BE46" s="11"/>
-      <c r="BF46" s="11"/>
-      <c r="BG46" s="12"/>
-      <c r="BH46" s="12"/>
-      <c r="BI46" s="13"/>
+      <c r="BD46" s="11">
+        <v>276131</v>
+      </c>
+      <c r="BE46" s="11">
+        <v>6343</v>
+      </c>
+      <c r="BF46" s="11">
+        <v>57</v>
+      </c>
+      <c r="BG46" s="12">
+        <v>14533.21052631579</v>
+      </c>
+      <c r="BH46" s="12">
+        <v>333.84210526315792</v>
+      </c>
+      <c r="BI46" s="13">
+        <v>2.136097682349368</v>
+      </c>
       <c r="BJ46" s="11"/>
       <c r="BK46" s="11"/>
       <c r="BL46" s="11"/>
@@ -12040,27 +12496,27 @@
       </c>
       <c r="N47" s="8">
         <f t="shared" si="6"/>
-        <v>244477.33333333334</v>
+        <v>260525.28571428571</v>
       </c>
       <c r="O47" s="8">
         <f t="shared" si="7"/>
-        <v>19025</v>
+        <v>19894.714285714286</v>
       </c>
       <c r="P47" s="8">
         <f t="shared" si="8"/>
-        <v>342</v>
+        <v>396</v>
       </c>
       <c r="Q47" s="9">
         <f t="shared" si="9"/>
-        <v>12867.228070175439</v>
+        <v>13815.734848484848</v>
       </c>
       <c r="R47" s="9">
         <f t="shared" si="10"/>
-        <v>1001.3157894736843</v>
+        <v>1055.0227272727273</v>
       </c>
       <c r="S47" s="10">
         <f t="shared" si="11"/>
-        <v>3.9127757564354919</v>
+        <v>3.8898586561630633</v>
       </c>
       <c r="T47" s="11">
         <v>211685</v>
@@ -12170,12 +12626,24 @@
       <c r="BC47" s="13">
         <v>4.1194071274436004</v>
       </c>
-      <c r="BD47" s="11"/>
-      <c r="BE47" s="11"/>
-      <c r="BF47" s="11"/>
-      <c r="BG47" s="12"/>
-      <c r="BH47" s="12"/>
-      <c r="BI47" s="13"/>
+      <c r="BD47" s="11">
+        <v>356813</v>
+      </c>
+      <c r="BE47" s="11">
+        <v>25113</v>
+      </c>
+      <c r="BF47" s="11">
+        <v>54</v>
+      </c>
+      <c r="BG47" s="12">
+        <v>19822.944444444449</v>
+      </c>
+      <c r="BH47" s="12">
+        <v>1395.166666666667</v>
+      </c>
+      <c r="BI47" s="13">
+        <v>3.75235605452849</v>
+      </c>
       <c r="BJ47" s="11"/>
       <c r="BK47" s="11"/>
       <c r="BL47" s="11"/>
@@ -12247,27 +12715,27 @@
       </c>
       <c r="N48" s="8">
         <f t="shared" si="6"/>
-        <v>230106.5</v>
+        <v>240560.57142857142</v>
       </c>
       <c r="O48" s="8">
         <f t="shared" si="7"/>
-        <v>18061.333333333332</v>
+        <v>18480.428571428572</v>
       </c>
       <c r="P48" s="8">
         <f t="shared" si="8"/>
-        <v>339</v>
+        <v>398</v>
       </c>
       <c r="Q48" s="9">
         <f t="shared" si="9"/>
-        <v>12218.044247787609</v>
+        <v>12692.89447236181</v>
       </c>
       <c r="R48" s="9">
         <f t="shared" si="10"/>
-        <v>959.00884955752213</v>
+        <v>975.09798994974869</v>
       </c>
       <c r="S48" s="10">
         <f t="shared" si="11"/>
-        <v>3.9426887569967448</v>
+        <v>3.9115143102761407</v>
       </c>
       <c r="T48" s="11">
         <v>225871</v>
@@ -12377,12 +12845,24 @@
       <c r="BC48" s="13">
         <v>4.1001953011307766</v>
       </c>
-      <c r="BD48" s="11"/>
-      <c r="BE48" s="11"/>
-      <c r="BF48" s="11"/>
-      <c r="BG48" s="12"/>
-      <c r="BH48" s="12"/>
-      <c r="BI48" s="13"/>
+      <c r="BD48" s="11">
+        <v>303285</v>
+      </c>
+      <c r="BE48" s="11">
+        <v>20995</v>
+      </c>
+      <c r="BF48" s="11">
+        <v>59</v>
+      </c>
+      <c r="BG48" s="12">
+        <v>15421.271186440679</v>
+      </c>
+      <c r="BH48" s="12">
+        <v>1067.542372881356</v>
+      </c>
+      <c r="BI48" s="13">
+        <v>3.724467629952517</v>
+      </c>
       <c r="BJ48" s="11"/>
       <c r="BK48" s="11"/>
       <c r="BL48" s="11"/>
@@ -12454,27 +12934,27 @@
       </c>
       <c r="N49" s="8">
         <f t="shared" si="6"/>
-        <v>179671.66666666666</v>
+        <v>160869.85714285713</v>
       </c>
       <c r="O49" s="8">
         <f t="shared" si="7"/>
-        <v>35513.166666666664</v>
+        <v>31562.285714285714</v>
       </c>
       <c r="P49" s="8">
         <f t="shared" si="8"/>
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="Q49" s="9">
         <f t="shared" si="9"/>
-        <v>14767.534246575342</v>
+        <v>14499</v>
       </c>
       <c r="R49" s="9">
         <f t="shared" si="10"/>
-        <v>2918.8904109589039</v>
+        <v>2844.669527896996</v>
       </c>
       <c r="S49" s="10">
         <f t="shared" si="11"/>
-        <v>6.345041735349926</v>
+        <v>6.2236961008663965</v>
       </c>
       <c r="T49" s="11">
         <v>268651</v>
@@ -12584,12 +13064,24 @@
       <c r="BC49" s="13">
         <v>7.2309278022184831</v>
       </c>
-      <c r="BD49" s="11"/>
-      <c r="BE49" s="11"/>
-      <c r="BF49" s="11"/>
-      <c r="BG49" s="12"/>
-      <c r="BH49" s="12"/>
-      <c r="BI49" s="13"/>
+      <c r="BD49" s="11">
+        <v>48059</v>
+      </c>
+      <c r="BE49" s="11">
+        <v>7857</v>
+      </c>
+      <c r="BF49" s="11">
+        <v>14</v>
+      </c>
+      <c r="BG49" s="12">
+        <v>10298.357142857139</v>
+      </c>
+      <c r="BH49" s="12">
+        <v>1683.6428571428571</v>
+      </c>
+      <c r="BI49" s="13">
+        <v>5.4956222939652202</v>
+      </c>
       <c r="BJ49" s="11"/>
       <c r="BK49" s="11"/>
       <c r="BL49" s="11"/>
@@ -12661,23 +13153,23 @@
       </c>
       <c r="N50" s="8">
         <f t="shared" si="6"/>
-        <v>368906.66666666669</v>
+        <v>399828.57142857142</v>
       </c>
       <c r="O50" s="8">
         <f t="shared" si="7"/>
-        <v>13680.666666666666</v>
+        <v>14827.428571428571</v>
       </c>
       <c r="P50" s="8">
         <f t="shared" si="8"/>
-        <v>263</v>
+        <v>334</v>
       </c>
       <c r="Q50" s="9">
         <f t="shared" si="9"/>
-        <v>25248.365019011409</v>
+        <v>25138.922155688622</v>
       </c>
       <c r="R50" s="9">
         <f t="shared" si="10"/>
-        <v>936.319391634981</v>
+        <v>932.26347305389231</v>
       </c>
       <c r="S50" s="10">
         <f t="shared" si="11"/>
@@ -12791,12 +13283,24 @@
       <c r="BC50" s="13">
         <v>2.65</v>
       </c>
-      <c r="BD50" s="11"/>
-      <c r="BE50" s="11"/>
-      <c r="BF50" s="11"/>
-      <c r="BG50" s="12"/>
-      <c r="BH50" s="12"/>
-      <c r="BI50" s="13"/>
+      <c r="BD50" s="11">
+        <v>585360</v>
+      </c>
+      <c r="BE50" s="11">
+        <v>21708</v>
+      </c>
+      <c r="BF50" s="11">
+        <v>71</v>
+      </c>
+      <c r="BG50" s="12">
+        <v>24733.521126760559</v>
+      </c>
+      <c r="BH50" s="12">
+        <v>917.23943661971828</v>
+      </c>
+      <c r="BI50" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BJ50" s="11"/>
       <c r="BK50" s="11"/>
       <c r="BL50" s="11"/>
@@ -12868,23 +13372,23 @@
       </c>
       <c r="N51" s="8">
         <f t="shared" si="6"/>
-        <v>394713.33333333331</v>
+        <v>423497.14285714284</v>
       </c>
       <c r="O51" s="8">
         <f t="shared" si="7"/>
-        <v>14637.833333333334</v>
+        <v>15705.285714285714</v>
       </c>
       <c r="P51" s="8">
         <f t="shared" si="8"/>
-        <v>272</v>
+        <v>345</v>
       </c>
       <c r="Q51" s="9">
         <f t="shared" si="9"/>
-        <v>26120.73529411765</v>
+        <v>25778.086956521744</v>
       </c>
       <c r="R51" s="9">
         <f t="shared" si="10"/>
-        <v>968.68014705882342</v>
+        <v>955.97391304347832</v>
       </c>
       <c r="S51" s="10">
         <f t="shared" si="11"/>
@@ -12998,12 +13502,24 @@
       <c r="BC51" s="13">
         <v>2.65</v>
       </c>
-      <c r="BD51" s="11"/>
-      <c r="BE51" s="11"/>
-      <c r="BF51" s="11"/>
-      <c r="BG51" s="12"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51" s="13"/>
+      <c r="BD51" s="11">
+        <v>596200</v>
+      </c>
+      <c r="BE51" s="11">
+        <v>22110</v>
+      </c>
+      <c r="BF51" s="11">
+        <v>73</v>
+      </c>
+      <c r="BG51" s="12">
+        <v>24501.369863013701</v>
+      </c>
+      <c r="BH51" s="12">
+        <v>908.6301369863013</v>
+      </c>
+      <c r="BI51" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BJ51" s="11"/>
       <c r="BK51" s="11"/>
       <c r="BL51" s="11"/>
@@ -13075,27 +13591,27 @@
       </c>
       <c r="N52" s="8">
         <f t="shared" si="6"/>
-        <v>44471.833333333336</v>
+        <v>42736.428571428572</v>
       </c>
       <c r="O52" s="8">
         <f t="shared" si="7"/>
-        <v>103341.33333333333</v>
+        <v>100733.85714285714</v>
       </c>
       <c r="P52" s="8">
         <f t="shared" si="8"/>
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="Q52" s="9">
         <f t="shared" si="9"/>
-        <v>5677.2553191489369</v>
+        <v>5790.0967741935483</v>
       </c>
       <c r="R52" s="9">
         <f t="shared" si="10"/>
-        <v>13192.51063829787</v>
+        <v>13647.812903225806</v>
       </c>
       <c r="S52" s="10">
         <f t="shared" si="11"/>
-        <v>24.128020210838759</v>
+        <v>24.277553546427885</v>
       </c>
       <c r="T52" s="11">
         <v>62208</v>
@@ -13205,12 +13721,24 @@
       <c r="BC52" s="13">
         <v>24.3369475446008</v>
       </c>
-      <c r="BD52" s="11"/>
-      <c r="BE52" s="11"/>
-      <c r="BF52" s="11"/>
-      <c r="BG52" s="12"/>
-      <c r="BH52" s="12"/>
-      <c r="BI52" s="13"/>
+      <c r="BD52" s="11">
+        <v>32324</v>
+      </c>
+      <c r="BE52" s="11">
+        <v>85089</v>
+      </c>
+      <c r="BF52" s="11">
+        <v>14</v>
+      </c>
+      <c r="BG52" s="12">
+        <v>6926.5714285714284</v>
+      </c>
+      <c r="BH52" s="12">
+        <v>18233.357142857141</v>
+      </c>
+      <c r="BI52" s="13">
+        <v>25.174753559962621</v>
+      </c>
       <c r="BJ52" s="11"/>
       <c r="BK52" s="11"/>
       <c r="BL52" s="11"/>
@@ -13268,11 +13796,11 @@
       <c r="M53" s="14"/>
       <c r="N53" s="14">
         <f>SUM(N3:N52)</f>
-        <v>10070851.686666667</v>
+        <v>10370192.414761905</v>
       </c>
       <c r="O53" s="14">
         <f>SUM(O3:O52)</f>
-        <v>1988601.066666666</v>
+        <v>2017284.9523809529</v>
       </c>
       <c r="P53" s="14"/>
       <c r="Q53" s="14"/>
@@ -13352,11 +13880,11 @@
       <c r="BC53" s="14"/>
       <c r="BD53" s="14">
         <f>SUM(BD3:BD52)</f>
-        <v>0</v>
+        <v>11955394</v>
       </c>
       <c r="BE53" s="14">
         <f>SUM(BE3:BE52)</f>
-        <v>0</v>
+        <v>2144241</v>
       </c>
       <c r="BF53" s="14"/>
       <c r="BG53" s="14"/>
@@ -13881,27 +14409,27 @@
       </c>
       <c r="N57" s="8">
         <f t="shared" ref="N57:N78" si="12">IFERROR(AVERAGE(T57,Z57,AF57,AL57,AR57,AX57,BD57,BJ57,BP57,BV57,CB57,CH57)," ")</f>
-        <v>280490</v>
+        <v>151545</v>
       </c>
       <c r="O57" s="8">
         <f t="shared" ref="O57:O78" si="13">IFERROR(AVERAGE(U57,AA57,AG57,AM57,AS57,AY57,BE57,BK57,BQ57,BW57,CC57,CI57)," ")</f>
-        <v>14231</v>
+        <v>7742.5</v>
       </c>
       <c r="P57" s="8">
         <f t="shared" ref="P57:P78" si="14">IFERROR(SUM(V57,AB57,AH57,AN57,AT57,AZ57,BF57,BL57,BR57,BX57,CD57,CJ57)," ")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q57" s="9">
         <f t="shared" ref="Q57:Q78" si="15">IFERROR(SUM(T57,Z57,AF57,AL57,AR57,AX57,BD57,BJ57,BP57,BV57,CB57,CH57)/P57*3," ")</f>
-        <v>84147</v>
+        <v>82660.909090909088</v>
       </c>
       <c r="R57" s="9">
         <f t="shared" ref="R57:R78" si="16">IFERROR(SUM(U57,AA57,AG57,AM57,AS57,AY57,BE57,BK57,BQ57,BW57,CC57,CI57)/P57*3," ")</f>
-        <v>4269.2999999999993</v>
+        <v>4223.181818181818</v>
       </c>
       <c r="S57" s="10">
         <f t="shared" ref="S57:S78" si="17">IFERROR(AVERAGE(Y57,AE57,AK57,AQ57,AW57,BC57,BI57,BO57,BU57,CA57,CG57,CM57)," ")</f>
-        <v>2.8674059405138981</v>
+        <v>2.9337029702569488</v>
       </c>
       <c r="T57" s="11"/>
       <c r="U57" s="11"/>
@@ -13951,12 +14479,24 @@
       <c r="BC57" s="13">
         <v>2.8674059405138981</v>
       </c>
-      <c r="BD57" s="11"/>
-      <c r="BE57" s="11"/>
-      <c r="BF57" s="11"/>
-      <c r="BG57" s="12"/>
-      <c r="BH57" s="12"/>
-      <c r="BI57" s="13"/>
+      <c r="BD57" s="11">
+        <v>22600</v>
+      </c>
+      <c r="BE57" s="11">
+        <v>1254</v>
+      </c>
+      <c r="BF57" s="11">
+        <v>1</v>
+      </c>
+      <c r="BG57" s="12">
+        <v>67800</v>
+      </c>
+      <c r="BH57" s="12">
+        <v>3762</v>
+      </c>
+      <c r="BI57" s="13">
+        <v>3</v>
+      </c>
       <c r="BJ57" s="11"/>
       <c r="BK57" s="11"/>
       <c r="BL57" s="11"/>
@@ -14031,27 +14571,27 @@
       </c>
       <c r="N58" s="8">
         <f t="shared" si="12"/>
-        <v>4404797.333333333</v>
+        <v>4496208.7142857146</v>
       </c>
       <c r="O58" s="8">
         <f t="shared" si="13"/>
-        <v>48707.166666666664</v>
+        <v>50298.857142857145</v>
       </c>
       <c r="P58" s="8">
         <f t="shared" si="14"/>
-        <v>407</v>
+        <v>491</v>
       </c>
       <c r="Q58" s="9">
         <f t="shared" si="15"/>
-        <v>194806.76167076168</v>
+        <v>192302.20570264765</v>
       </c>
       <c r="R58" s="9">
         <f t="shared" si="16"/>
-        <v>2154.1253071253072</v>
+        <v>2151.2749490835031</v>
       </c>
       <c r="S58" s="10">
         <f t="shared" si="17"/>
-        <v>1.341224420296024</v>
+        <v>1.3477364743438982</v>
       </c>
       <c r="T58" s="11">
         <v>4555723</v>
@@ -14161,12 +14701,24 @@
       <c r="BC58" s="13">
         <v>1.3491522650257199</v>
       </c>
-      <c r="BD58" s="11"/>
-      <c r="BE58" s="11"/>
-      <c r="BF58" s="11"/>
-      <c r="BG58" s="12"/>
-      <c r="BH58" s="12"/>
-      <c r="BI58" s="13"/>
+      <c r="BD58" s="11">
+        <v>5044677</v>
+      </c>
+      <c r="BE58" s="11">
+        <v>59849</v>
+      </c>
+      <c r="BF58" s="11">
+        <v>84</v>
+      </c>
+      <c r="BG58" s="12">
+        <v>180167.03571428571</v>
+      </c>
+      <c r="BH58" s="12">
+        <v>2137.4642857142849</v>
+      </c>
+      <c r="BI58" s="13">
+        <v>1.386808798631143</v>
+      </c>
       <c r="BJ58" s="11"/>
       <c r="BK58" s="11"/>
       <c r="BL58" s="11"/>
@@ -14379,27 +14931,27 @@
       </c>
       <c r="N60" s="8">
         <f t="shared" si="12"/>
-        <v>3415673.5</v>
+        <v>3455264.1428571427</v>
       </c>
       <c r="O60" s="8">
         <f t="shared" si="13"/>
-        <v>8695</v>
+        <v>8756.2857142857138</v>
       </c>
       <c r="P60" s="8">
         <f t="shared" si="14"/>
-        <v>313</v>
+        <v>389</v>
       </c>
       <c r="Q60" s="9">
         <f t="shared" si="15"/>
-        <v>196428.50798722045</v>
+        <v>186530.96915167096</v>
       </c>
       <c r="R60" s="9">
         <f t="shared" si="16"/>
-        <v>500.03194888178916</v>
+        <v>472.70437017994857</v>
       </c>
       <c r="S60" s="10">
         <f t="shared" si="17"/>
-        <v>0.63980983320435858</v>
+        <v>0.6386638453313801</v>
       </c>
       <c r="T60" s="11">
         <v>2164532</v>
@@ -14509,12 +15061,24 @@
       <c r="BC60" s="13">
         <v>0.63223704096751654</v>
       </c>
-      <c r="BD60" s="11"/>
-      <c r="BE60" s="11"/>
-      <c r="BF60" s="11"/>
-      <c r="BG60" s="12"/>
-      <c r="BH60" s="12"/>
-      <c r="BI60" s="13"/>
+      <c r="BD60" s="11">
+        <v>3692808</v>
+      </c>
+      <c r="BE60" s="11">
+        <v>9124</v>
+      </c>
+      <c r="BF60" s="11">
+        <v>76</v>
+      </c>
+      <c r="BG60" s="12">
+        <v>145768.73684210531</v>
+      </c>
+      <c r="BH60" s="12">
+        <v>360.15789473684208</v>
+      </c>
+      <c r="BI60" s="13">
+        <v>0.63178791809350954</v>
+      </c>
       <c r="BJ60" s="11"/>
       <c r="BK60" s="11"/>
       <c r="BL60" s="11"/>
@@ -14589,27 +15153,27 @@
       </c>
       <c r="N61" s="8">
         <f t="shared" si="12"/>
-        <v>3308453.8</v>
+        <v>3628744.1666666665</v>
       </c>
       <c r="O61" s="8">
         <f t="shared" si="13"/>
-        <v>6972.2</v>
+        <v>8084.5</v>
       </c>
       <c r="P61" s="8">
         <f t="shared" si="14"/>
-        <v>241</v>
+        <v>313</v>
       </c>
       <c r="Q61" s="9">
         <f t="shared" si="15"/>
-        <v>205920.36099585064</v>
+        <v>208681.77316293929</v>
       </c>
       <c r="R61" s="9">
         <f t="shared" si="16"/>
-        <v>433.95435684647299</v>
+        <v>464.92332268370603</v>
       </c>
       <c r="S61" s="10">
         <f t="shared" si="17"/>
-        <v>0.58321553631183687</v>
+        <v>0.59400948667021758</v>
       </c>
       <c r="T61" s="11"/>
       <c r="U61" s="11"/>
@@ -14707,12 +15271,24 @@
       <c r="BC61" s="13">
         <v>0.63789636351500167</v>
       </c>
-      <c r="BD61" s="11"/>
-      <c r="BE61" s="11"/>
-      <c r="BF61" s="11"/>
-      <c r="BG61" s="12"/>
-      <c r="BH61" s="12"/>
-      <c r="BI61" s="13"/>
+      <c r="BD61" s="11">
+        <v>5230196</v>
+      </c>
+      <c r="BE61" s="11">
+        <v>13646</v>
+      </c>
+      <c r="BF61" s="11">
+        <v>72</v>
+      </c>
+      <c r="BG61" s="12">
+        <v>217924.83333333331</v>
+      </c>
+      <c r="BH61" s="12">
+        <v>568.58333333333326</v>
+      </c>
+      <c r="BI61" s="13">
+        <v>0.6479792384621208</v>
+      </c>
       <c r="BJ61" s="11"/>
       <c r="BK61" s="11"/>
       <c r="BL61" s="11"/>
@@ -14787,27 +15363,27 @@
       </c>
       <c r="N62" s="8">
         <f t="shared" si="12"/>
-        <v>3983634.6666666665</v>
+        <v>4264285.5714285718</v>
       </c>
       <c r="O62" s="8">
         <f t="shared" si="13"/>
-        <v>9070</v>
+        <v>10077.571428571429</v>
       </c>
       <c r="P62" s="8">
         <f t="shared" si="14"/>
-        <v>305</v>
+        <v>377</v>
       </c>
       <c r="Q62" s="9">
         <f t="shared" si="15"/>
-        <v>235099.75081967213</v>
+        <v>237533.14854111406</v>
       </c>
       <c r="R62" s="9">
         <f t="shared" si="16"/>
-        <v>535.27868852459017</v>
+        <v>561.35013262599466</v>
       </c>
       <c r="S62" s="10">
         <f t="shared" si="17"/>
-        <v>0.58201704441413427</v>
+        <v>0.59315746664068647</v>
       </c>
       <c r="T62" s="11">
         <v>2675265</v>
@@ -14917,12 +15493,24 @@
       <c r="BC62" s="13">
         <v>0.66</v>
       </c>
-      <c r="BD62" s="11"/>
-      <c r="BE62" s="11"/>
-      <c r="BF62" s="11"/>
-      <c r="BG62" s="12"/>
-      <c r="BH62" s="12"/>
-      <c r="BI62" s="13"/>
+      <c r="BD62" s="11">
+        <v>5948191</v>
+      </c>
+      <c r="BE62" s="11">
+        <v>16123</v>
+      </c>
+      <c r="BF62" s="11">
+        <v>72</v>
+      </c>
+      <c r="BG62" s="12">
+        <v>247841.29166666669</v>
+      </c>
+      <c r="BH62" s="12">
+        <v>671.79166666666663</v>
+      </c>
+      <c r="BI62" s="13">
+        <v>0.66</v>
+      </c>
       <c r="BJ62" s="11"/>
       <c r="BK62" s="11"/>
       <c r="BL62" s="11"/>
@@ -14997,27 +15585,27 @@
       </c>
       <c r="N63" s="8">
         <f t="shared" si="12"/>
-        <v>9850120.166666666</v>
+        <v>10080062.285714285</v>
       </c>
       <c r="O63" s="8">
         <f t="shared" si="13"/>
-        <v>10147.833333333334</v>
+        <v>10993</v>
       </c>
       <c r="P63" s="8">
         <f t="shared" si="14"/>
-        <v>416</v>
+        <v>498</v>
       </c>
       <c r="Q63" s="9">
         <f t="shared" si="15"/>
-        <v>426207.12259615387</v>
+        <v>425062.86746987957</v>
       </c>
       <c r="R63" s="9">
         <f t="shared" si="16"/>
-        <v>439.08894230769232</v>
+        <v>463.56024096385545</v>
       </c>
       <c r="S63" s="10">
         <f t="shared" si="17"/>
-        <v>0.40825304716319449</v>
+        <v>0.41784654893191719</v>
       </c>
       <c r="T63" s="11">
         <v>9298604</v>
@@ -15127,12 +15715,24 @@
       <c r="BC63" s="13">
         <v>0.3799287615585204</v>
       </c>
-      <c r="BD63" s="11"/>
-      <c r="BE63" s="11"/>
-      <c r="BF63" s="11"/>
-      <c r="BG63" s="12"/>
-      <c r="BH63" s="12"/>
-      <c r="BI63" s="13"/>
+      <c r="BD63" s="11">
+        <v>11459715</v>
+      </c>
+      <c r="BE63" s="11">
+        <v>16064</v>
+      </c>
+      <c r="BF63" s="11">
+        <v>82</v>
+      </c>
+      <c r="BG63" s="12">
+        <v>419257.86585365853</v>
+      </c>
+      <c r="BH63" s="12">
+        <v>587.70731707317077</v>
+      </c>
+      <c r="BI63" s="13">
+        <v>0.47540755954425312</v>
+      </c>
       <c r="BJ63" s="11"/>
       <c r="BK63" s="11"/>
       <c r="BL63" s="11"/>
@@ -15207,27 +15807,27 @@
       </c>
       <c r="N64" s="8">
         <f t="shared" si="12"/>
-        <v>9307202</v>
+        <v>9847720.7142857146</v>
       </c>
       <c r="O64" s="8">
         <f t="shared" si="13"/>
-        <v>10775.833333333334</v>
+        <v>10935</v>
       </c>
       <c r="P64" s="8">
         <f t="shared" si="14"/>
-        <v>417</v>
+        <v>501</v>
       </c>
       <c r="Q64" s="9">
         <f t="shared" si="15"/>
-        <v>401749.72661870508</v>
+        <v>412778.7125748503</v>
       </c>
       <c r="R64" s="9">
         <f t="shared" si="16"/>
-        <v>465.14388489208636</v>
+        <v>458.35329341317362</v>
       </c>
       <c r="S64" s="10">
         <f t="shared" si="17"/>
-        <v>0.440761062794299</v>
+        <v>0.43245768534274825</v>
       </c>
       <c r="T64" s="11">
         <v>10280587</v>
@@ -15337,12 +15937,24 @@
       <c r="BC64" s="13">
         <v>0.38060160415934408</v>
       </c>
-      <c r="BD64" s="11"/>
-      <c r="BE64" s="11"/>
-      <c r="BF64" s="11"/>
-      <c r="BG64" s="12"/>
-      <c r="BH64" s="12"/>
-      <c r="BI64" s="13"/>
+      <c r="BD64" s="11">
+        <v>13090833</v>
+      </c>
+      <c r="BE64" s="11">
+        <v>11890</v>
+      </c>
+      <c r="BF64" s="11">
+        <v>84</v>
+      </c>
+      <c r="BG64" s="12">
+        <v>467529.75</v>
+      </c>
+      <c r="BH64" s="12">
+        <v>424.64285714285711</v>
+      </c>
+      <c r="BI64" s="13">
+        <v>0.38263742063344391</v>
+      </c>
       <c r="BJ64" s="11"/>
       <c r="BK64" s="11"/>
       <c r="BL64" s="11"/>
@@ -15417,27 +16029,27 @@
       </c>
       <c r="N65" s="8">
         <f t="shared" si="12"/>
-        <v>9098804.666666666</v>
+        <v>9442024</v>
       </c>
       <c r="O65" s="8">
         <f t="shared" si="13"/>
-        <v>13473.666666666666</v>
+        <v>13088.142857142857</v>
       </c>
       <c r="P65" s="8">
         <f t="shared" si="14"/>
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="Q65" s="9">
         <f t="shared" si="15"/>
-        <v>392754.1582733813</v>
+        <v>402195.74847870186</v>
       </c>
       <c r="R65" s="9">
         <f t="shared" si="16"/>
-        <v>581.59712230215825</v>
+        <v>557.50709939148066</v>
       </c>
       <c r="S65" s="10">
         <f t="shared" si="17"/>
-        <v>0.49289780204562605</v>
+        <v>0.47802324360386461</v>
       </c>
       <c r="T65" s="11">
         <v>9995292</v>
@@ -15547,12 +16159,24 @@
       <c r="BC65" s="13">
         <v>0.47521451589138392</v>
       </c>
-      <c r="BD65" s="11"/>
-      <c r="BE65" s="11"/>
-      <c r="BF65" s="11"/>
-      <c r="BG65" s="12"/>
-      <c r="BH65" s="12"/>
-      <c r="BI65" s="13"/>
+      <c r="BD65" s="11">
+        <v>11501340</v>
+      </c>
+      <c r="BE65" s="11">
+        <v>10775</v>
+      </c>
+      <c r="BF65" s="11">
+        <v>76</v>
+      </c>
+      <c r="BG65" s="12">
+        <v>454000.26315789472</v>
+      </c>
+      <c r="BH65" s="12">
+        <v>425.32894736842098</v>
+      </c>
+      <c r="BI65" s="13">
+        <v>0.38877589295329629</v>
+      </c>
       <c r="BJ65" s="11"/>
       <c r="BK65" s="11"/>
       <c r="BL65" s="11"/>
@@ -15627,27 +16251,27 @@
       </c>
       <c r="N66" s="8">
         <f t="shared" si="12"/>
-        <v>8526236.833333334</v>
+        <v>8672073.8571428563</v>
       </c>
       <c r="O66" s="8">
         <f t="shared" si="13"/>
-        <v>14715.5</v>
+        <v>16253.142857142857</v>
       </c>
       <c r="P66" s="8">
         <f t="shared" si="14"/>
-        <v>407</v>
+        <v>492</v>
       </c>
       <c r="Q66" s="9">
         <f t="shared" si="15"/>
-        <v>377081.72727272729</v>
+        <v>370149.49390243902</v>
       </c>
       <c r="R66" s="9">
         <f t="shared" si="16"/>
-        <v>650.80835380835379</v>
+        <v>693.73170731707319</v>
       </c>
       <c r="S66" s="10">
         <f t="shared" si="17"/>
-        <v>0.52318120780634259</v>
+        <v>0.54209382316524801</v>
       </c>
       <c r="T66" s="11">
         <v>8918165</v>
@@ -15757,12 +16381,24 @@
       <c r="BC66" s="13">
         <v>0.45141113114156911</v>
       </c>
-      <c r="BD66" s="11"/>
-      <c r="BE66" s="11"/>
-      <c r="BF66" s="11"/>
-      <c r="BG66" s="12"/>
-      <c r="BH66" s="12"/>
-      <c r="BI66" s="13"/>
+      <c r="BD66" s="11">
+        <v>9547096</v>
+      </c>
+      <c r="BE66" s="11">
+        <v>25479</v>
+      </c>
+      <c r="BF66" s="11">
+        <v>85</v>
+      </c>
+      <c r="BG66" s="12">
+        <v>336956.32941176469</v>
+      </c>
+      <c r="BH66" s="12">
+        <v>899.25882352941176</v>
+      </c>
+      <c r="BI66" s="13">
+        <v>0.6555695153186798</v>
+      </c>
       <c r="BJ66" s="11"/>
       <c r="BK66" s="11"/>
       <c r="BL66" s="11"/>
@@ -15837,27 +16473,27 @@
       </c>
       <c r="N67" s="8">
         <f t="shared" si="12"/>
-        <v>4928894.5</v>
+        <v>4921576.7142857146</v>
       </c>
       <c r="O67" s="8">
         <f t="shared" si="13"/>
-        <v>11289.833333333334</v>
+        <v>11369.142857142857</v>
       </c>
       <c r="P67" s="8">
         <f t="shared" si="14"/>
-        <v>416</v>
+        <v>484</v>
       </c>
       <c r="Q67" s="9">
         <f t="shared" si="15"/>
-        <v>213269.47355769231</v>
+        <v>213539.48553719008</v>
       </c>
       <c r="R67" s="9">
         <f t="shared" si="16"/>
-        <v>488.50240384615381</v>
+        <v>493.28925619834706</v>
       </c>
       <c r="S67" s="10">
         <f t="shared" si="17"/>
-        <v>0.60728487117891505</v>
+        <v>0.61017466135145193</v>
       </c>
       <c r="T67" s="11">
         <v>5935742</v>
@@ -15967,12 +16603,24 @@
       <c r="BC67" s="13">
         <v>0.57692791857872994</v>
       </c>
-      <c r="BD67" s="11"/>
-      <c r="BE67" s="11"/>
-      <c r="BF67" s="11"/>
-      <c r="BG67" s="12"/>
-      <c r="BH67" s="12"/>
-      <c r="BI67" s="13"/>
+      <c r="BD67" s="11">
+        <v>4877670</v>
+      </c>
+      <c r="BE67" s="11">
+        <v>11845</v>
+      </c>
+      <c r="BF67" s="11">
+        <v>68</v>
+      </c>
+      <c r="BG67" s="12">
+        <v>215191.32352941169</v>
+      </c>
+      <c r="BH67" s="12">
+        <v>522.57352941176464</v>
+      </c>
+      <c r="BI67" s="13">
+        <v>0.62751340238667341</v>
+      </c>
       <c r="BJ67" s="11"/>
       <c r="BK67" s="11"/>
       <c r="BL67" s="11"/>
@@ -16047,27 +16695,27 @@
       </c>
       <c r="N68" s="8">
         <f t="shared" si="12"/>
-        <v>5984337</v>
+        <v>5929494.2857142854</v>
       </c>
       <c r="O68" s="8">
         <f t="shared" si="13"/>
-        <v>15354.666666666666</v>
+        <v>14879.142857142857</v>
       </c>
       <c r="P68" s="8">
         <f t="shared" si="14"/>
-        <v>422</v>
+        <v>496</v>
       </c>
       <c r="Q68" s="9">
         <f t="shared" si="15"/>
-        <v>255256.08056872038</v>
+        <v>251047.13709677418</v>
       </c>
       <c r="R68" s="9">
         <f t="shared" si="16"/>
-        <v>654.93838862559244</v>
+        <v>629.96370967741939</v>
       </c>
       <c r="S68" s="10">
         <f t="shared" si="17"/>
-        <v>0.63930404035849786</v>
+        <v>0.632147160874588</v>
       </c>
       <c r="T68" s="11">
         <v>6055582</v>
@@ -16177,12 +16825,24 @@
       <c r="BC68" s="13">
         <v>0.62948616344773023</v>
       </c>
-      <c r="BD68" s="11"/>
-      <c r="BE68" s="11"/>
-      <c r="BF68" s="11"/>
-      <c r="BG68" s="12"/>
-      <c r="BH68" s="12"/>
-      <c r="BI68" s="13"/>
+      <c r="BD68" s="11">
+        <v>5600438</v>
+      </c>
+      <c r="BE68" s="11">
+        <v>12026</v>
+      </c>
+      <c r="BF68" s="11">
+        <v>74</v>
+      </c>
+      <c r="BG68" s="12">
+        <v>227044.78378378379</v>
+      </c>
+      <c r="BH68" s="12">
+        <v>487.54054054054052</v>
+      </c>
+      <c r="BI68" s="13">
+        <v>0.58920588397112894</v>
+      </c>
       <c r="BJ68" s="11"/>
       <c r="BK68" s="11"/>
       <c r="BL68" s="11"/>
@@ -16257,27 +16917,27 @@
       </c>
       <c r="N69" s="8">
         <f t="shared" si="12"/>
-        <v>5790235</v>
+        <v>5876495.8571428573</v>
       </c>
       <c r="O69" s="8">
         <f t="shared" si="13"/>
-        <v>14847.666666666666</v>
+        <v>15107.714285714286</v>
       </c>
       <c r="P69" s="8">
         <f t="shared" si="14"/>
-        <v>421</v>
+        <v>494</v>
       </c>
       <c r="Q69" s="9">
         <f t="shared" si="15"/>
-        <v>247563.49168646082</v>
+        <v>249810.55263157896</v>
       </c>
       <c r="R69" s="9">
         <f t="shared" si="16"/>
-        <v>634.81710213776728</v>
+        <v>642.23076923076917</v>
       </c>
       <c r="S69" s="10">
         <f t="shared" si="17"/>
-        <v>0.64126258743148057</v>
+        <v>0.64234714537371318</v>
       </c>
       <c r="T69" s="11">
         <v>4627717</v>
@@ -16387,12 +17047,24 @@
       <c r="BC69" s="13">
         <v>0.65863083894711516</v>
       </c>
-      <c r="BD69" s="11"/>
-      <c r="BE69" s="11"/>
-      <c r="BF69" s="11"/>
-      <c r="BG69" s="12"/>
-      <c r="BH69" s="12"/>
-      <c r="BI69" s="13"/>
+      <c r="BD69" s="11">
+        <v>6394061</v>
+      </c>
+      <c r="BE69" s="11">
+        <v>16668</v>
+      </c>
+      <c r="BF69" s="11">
+        <v>73</v>
+      </c>
+      <c r="BG69" s="12">
+        <v>262769.63013698632</v>
+      </c>
+      <c r="BH69" s="12">
+        <v>684.98630136986299</v>
+      </c>
+      <c r="BI69" s="13">
+        <v>0.64885449302710929</v>
+      </c>
       <c r="BJ69" s="11"/>
       <c r="BK69" s="11"/>
       <c r="BL69" s="11"/>
@@ -16467,27 +17139,27 @@
       </c>
       <c r="N70" s="8">
         <f t="shared" si="12"/>
-        <v>3752381.5</v>
+        <v>4053747.1428571427</v>
       </c>
       <c r="O70" s="8">
         <f t="shared" si="13"/>
-        <v>9775.1666666666661</v>
+        <v>10642.571428571429</v>
       </c>
       <c r="P70" s="8">
         <f t="shared" si="14"/>
-        <v>277</v>
+        <v>350</v>
       </c>
       <c r="Q70" s="9">
         <f t="shared" si="15"/>
-        <v>243837.06498194946</v>
+        <v>243224.82857142857</v>
       </c>
       <c r="R70" s="9">
         <f t="shared" si="16"/>
-        <v>635.20938628158842</v>
+        <v>638.5542857142857</v>
       </c>
       <c r="S70" s="10">
         <f t="shared" si="17"/>
-        <v>0.64662721993525674</v>
+        <v>0.64849330674982752</v>
       </c>
       <c r="T70" s="11">
         <v>640528</v>
@@ -16597,12 +17269,24 @@
       <c r="BC70" s="13">
         <v>0.65993477022789648</v>
       </c>
-      <c r="BD70" s="11"/>
-      <c r="BE70" s="11"/>
-      <c r="BF70" s="11"/>
-      <c r="BG70" s="12"/>
-      <c r="BH70" s="12"/>
-      <c r="BI70" s="13"/>
+      <c r="BD70" s="11">
+        <v>5861941</v>
+      </c>
+      <c r="BE70" s="11">
+        <v>15847</v>
+      </c>
+      <c r="BF70" s="11">
+        <v>73</v>
+      </c>
+      <c r="BG70" s="12">
+        <v>240901.6849315069</v>
+      </c>
+      <c r="BH70" s="12">
+        <v>651.2465753424658</v>
+      </c>
+      <c r="BI70" s="13">
+        <v>0.65968982763725237</v>
+      </c>
       <c r="BJ70" s="11"/>
       <c r="BK70" s="11"/>
       <c r="BL70" s="11"/>
@@ -17013,27 +17697,27 @@
       </c>
       <c r="N73" s="8">
         <f t="shared" si="12"/>
-        <v>4342708.333333333</v>
+        <v>4145513.5714285714</v>
       </c>
       <c r="O73" s="8">
         <f t="shared" si="13"/>
-        <v>7542.333333333333</v>
+        <v>6933.7142857142853</v>
       </c>
       <c r="P73" s="8">
         <f t="shared" si="14"/>
-        <v>403</v>
+        <v>475</v>
       </c>
       <c r="Q73" s="9">
         <f t="shared" si="15"/>
-        <v>193967.12158808933</v>
+        <v>183275.33684210526</v>
       </c>
       <c r="R73" s="9">
         <f t="shared" si="16"/>
-        <v>336.87841191067002</v>
+        <v>306.54315789473685</v>
       </c>
       <c r="S73" s="10">
         <f t="shared" si="17"/>
-        <v>0.51875957011845664</v>
+        <v>0.50444141768251971</v>
       </c>
       <c r="T73" s="11">
         <v>6999813</v>
@@ -17143,12 +17827,24 @@
       <c r="BC73" s="13">
         <v>0.59157052048470737</v>
       </c>
-      <c r="BD73" s="11"/>
-      <c r="BE73" s="11"/>
-      <c r="BF73" s="11"/>
-      <c r="BG73" s="12"/>
-      <c r="BH73" s="12"/>
-      <c r="BI73" s="13"/>
+      <c r="BD73" s="11">
+        <v>2962345</v>
+      </c>
+      <c r="BE73" s="11">
+        <v>3282</v>
+      </c>
+      <c r="BF73" s="11">
+        <v>72</v>
+      </c>
+      <c r="BG73" s="12">
+        <v>123431.0416666667</v>
+      </c>
+      <c r="BH73" s="12">
+        <v>136.75</v>
+      </c>
+      <c r="BI73" s="13">
+        <v>0.41853250306689771</v>
+      </c>
       <c r="BJ73" s="11"/>
       <c r="BK73" s="11"/>
       <c r="BL73" s="11"/>
@@ -17223,27 +17919,27 @@
       </c>
       <c r="N74" s="8">
         <f t="shared" si="12"/>
-        <v>4354110</v>
+        <v>4069702.8571428573</v>
       </c>
       <c r="O74" s="8">
         <f t="shared" si="13"/>
-        <v>6690</v>
+        <v>6191</v>
       </c>
       <c r="P74" s="8">
         <f t="shared" si="14"/>
-        <v>357</v>
+        <v>426</v>
       </c>
       <c r="Q74" s="9">
         <f t="shared" si="15"/>
-        <v>219534.95798319328</v>
+        <v>200619.15492957749</v>
       </c>
       <c r="R74" s="9">
         <f t="shared" si="16"/>
-        <v>337.31092436974791</v>
+        <v>305.1901408450704</v>
       </c>
       <c r="S74" s="10">
         <f t="shared" si="17"/>
-        <v>0.4620853726893665</v>
+        <v>0.46253301866048979</v>
       </c>
       <c r="T74" s="11">
         <v>6713836</v>
@@ -17353,12 +18049,24 @@
       <c r="BC74" s="13">
         <v>0.43065424902702543</v>
       </c>
-      <c r="BD74" s="11"/>
-      <c r="BE74" s="11"/>
-      <c r="BF74" s="11"/>
-      <c r="BG74" s="12"/>
-      <c r="BH74" s="12"/>
-      <c r="BI74" s="13"/>
+      <c r="BD74" s="11">
+        <v>2363260</v>
+      </c>
+      <c r="BE74" s="11">
+        <v>3197</v>
+      </c>
+      <c r="BF74" s="11">
+        <v>69</v>
+      </c>
+      <c r="BG74" s="12">
+        <v>102750.4347826087</v>
+      </c>
+      <c r="BH74" s="12">
+        <v>139</v>
+      </c>
+      <c r="BI74" s="13">
+        <v>0.46521889448722958</v>
+      </c>
       <c r="BJ74" s="11"/>
       <c r="BK74" s="11"/>
       <c r="BL74" s="11"/>
@@ -17433,27 +18141,27 @@
       </c>
       <c r="N75" s="8">
         <f t="shared" si="12"/>
-        <v>1081576.7233333334</v>
+        <v>1080582.7628571428</v>
       </c>
       <c r="O75" s="8">
         <f t="shared" si="13"/>
-        <v>155353</v>
+        <v>153736.85714285713</v>
       </c>
       <c r="P75" s="8">
         <f t="shared" si="14"/>
-        <v>428</v>
+        <v>499</v>
       </c>
       <c r="Q75" s="9">
         <f t="shared" si="15"/>
-        <v>45486.871542056069</v>
+        <v>45475.426893787575</v>
       </c>
       <c r="R75" s="9">
         <f t="shared" si="16"/>
-        <v>6533.5373831775696</v>
+        <v>6469.8877755511021</v>
       </c>
       <c r="S75" s="10">
         <f t="shared" si="17"/>
-        <v>4.8388014068699254</v>
+        <v>4.8135973072996023</v>
       </c>
       <c r="T75" s="11">
         <v>1253986.8999999999</v>
@@ -17563,12 +18271,24 @@
       <c r="BC75" s="13">
         <v>4.5254245118508543</v>
       </c>
-      <c r="BD75" s="11"/>
-      <c r="BE75" s="11"/>
-      <c r="BF75" s="11"/>
-      <c r="BG75" s="12"/>
-      <c r="BH75" s="12"/>
-      <c r="BI75" s="13"/>
+      <c r="BD75" s="11">
+        <v>1074619</v>
+      </c>
+      <c r="BE75" s="11">
+        <v>144040</v>
+      </c>
+      <c r="BF75" s="11">
+        <v>71</v>
+      </c>
+      <c r="BG75" s="12">
+        <v>45406.436619718312</v>
+      </c>
+      <c r="BH75" s="12">
+        <v>6086.1971830985913</v>
+      </c>
+      <c r="BI75" s="13">
+        <v>4.6623727098776646</v>
+      </c>
       <c r="BJ75" s="11"/>
       <c r="BK75" s="11"/>
       <c r="BL75" s="11"/>
@@ -17643,27 +18363,27 @@
       </c>
       <c r="N76" s="8">
         <f t="shared" si="12"/>
-        <v>3115434.6999999997</v>
+        <v>3117399.6</v>
       </c>
       <c r="O76" s="8">
         <f t="shared" si="13"/>
-        <v>52764.5</v>
+        <v>54242.571428571428</v>
       </c>
       <c r="P76" s="8">
         <f t="shared" si="14"/>
-        <v>423</v>
+        <v>506</v>
       </c>
       <c r="Q76" s="9">
         <f t="shared" si="15"/>
-        <v>132571.68936170213</v>
+        <v>129378.2442687747</v>
       </c>
       <c r="R76" s="9">
         <f t="shared" si="16"/>
-        <v>2245.2978723404258</v>
+        <v>2251.1739130434785</v>
       </c>
       <c r="S76" s="10">
         <f t="shared" si="17"/>
-        <v>1.6487309747128009</v>
+        <v>1.6713747102303447</v>
       </c>
       <c r="T76" s="11">
         <v>3600483.2</v>
@@ -17773,12 +18493,24 @@
       <c r="BC76" s="13">
         <v>1.609908490697354</v>
       </c>
-      <c r="BD76" s="11"/>
-      <c r="BE76" s="11"/>
-      <c r="BF76" s="11"/>
-      <c r="BG76" s="12"/>
-      <c r="BH76" s="12"/>
-      <c r="BI76" s="13"/>
+      <c r="BD76" s="11">
+        <v>3129189</v>
+      </c>
+      <c r="BE76" s="11">
+        <v>63111</v>
+      </c>
+      <c r="BF76" s="11">
+        <v>83</v>
+      </c>
+      <c r="BG76" s="12">
+        <v>113103.21686746991</v>
+      </c>
+      <c r="BH76" s="12">
+        <v>2281.1204819277109</v>
+      </c>
+      <c r="BI76" s="13">
+        <v>1.807237123335607</v>
+      </c>
       <c r="BJ76" s="11"/>
       <c r="BK76" s="11"/>
       <c r="BL76" s="11"/>
@@ -17853,27 +18585,27 @@
       </c>
       <c r="N77" s="8">
         <f t="shared" si="12"/>
-        <v>4424585.833333333</v>
+        <v>4492558.4285714282</v>
       </c>
       <c r="O77" s="8">
         <f t="shared" si="13"/>
-        <v>20308.333333333332</v>
+        <v>21849.285714285714</v>
       </c>
       <c r="P77" s="8">
         <f t="shared" si="14"/>
-        <v>432</v>
+        <v>517</v>
       </c>
       <c r="Q77" s="9">
         <f t="shared" si="15"/>
-        <v>184357.74305555556</v>
+        <v>182483.03094777564</v>
       </c>
       <c r="R77" s="9">
         <f t="shared" si="16"/>
-        <v>846.18055555555543</v>
+        <v>887.4951644100579</v>
       </c>
       <c r="S77" s="10">
         <f t="shared" si="17"/>
-        <v>0.86051871654804579</v>
+        <v>0.88230401229994615</v>
       </c>
       <c r="T77" s="11">
         <v>4959341</v>
@@ -17983,12 +18715,24 @@
       <c r="BC77" s="13">
         <v>0.90399776079397332</v>
       </c>
-      <c r="BD77" s="11"/>
-      <c r="BE77" s="11"/>
-      <c r="BF77" s="11"/>
-      <c r="BG77" s="12"/>
-      <c r="BH77" s="12"/>
-      <c r="BI77" s="13"/>
+      <c r="BD77" s="11">
+        <v>4900394</v>
+      </c>
+      <c r="BE77" s="11">
+        <v>31095</v>
+      </c>
+      <c r="BF77" s="11">
+        <v>85</v>
+      </c>
+      <c r="BG77" s="12">
+        <v>172955.08235294119</v>
+      </c>
+      <c r="BH77" s="12">
+        <v>1097.4705882352939</v>
+      </c>
+      <c r="BI77" s="13">
+        <v>1.0130157868113481</v>
+      </c>
       <c r="BJ77" s="11"/>
       <c r="BK77" s="11"/>
       <c r="BL77" s="11"/>
@@ -18063,27 +18807,27 @@
       </c>
       <c r="N78" s="8">
         <f t="shared" si="12"/>
-        <v>5096673</v>
+        <v>5124027.4285714282</v>
       </c>
       <c r="O78" s="8">
         <f t="shared" si="13"/>
-        <v>35338.5</v>
+        <v>35952.571428571428</v>
       </c>
       <c r="P78" s="8">
         <f t="shared" si="14"/>
-        <v>434</v>
+        <v>520</v>
       </c>
       <c r="Q78" s="9">
         <f t="shared" si="15"/>
-        <v>211382.75115207373</v>
+        <v>206931.87692307692</v>
       </c>
       <c r="R78" s="9">
         <f t="shared" si="16"/>
-        <v>1465.6520737327189</v>
+        <v>1451.9307692307693</v>
       </c>
       <c r="S78" s="10">
         <f t="shared" si="17"/>
-        <v>1.0612919402421765</v>
+        <v>1.0669598800667122</v>
       </c>
       <c r="T78" s="11">
         <v>5415922</v>
@@ -18193,12 +18937,24 @@
       <c r="BC78" s="13">
         <v>1.1262814258191409</v>
       </c>
-      <c r="BD78" s="11"/>
-      <c r="BE78" s="11"/>
-      <c r="BF78" s="11"/>
-      <c r="BG78" s="12"/>
-      <c r="BH78" s="12"/>
-      <c r="BI78" s="13"/>
+      <c r="BD78" s="11">
+        <v>5288154</v>
+      </c>
+      <c r="BE78" s="11">
+        <v>39637</v>
+      </c>
+      <c r="BF78" s="11">
+        <v>86</v>
+      </c>
+      <c r="BG78" s="12">
+        <v>184470.48837209301</v>
+      </c>
+      <c r="BH78" s="12">
+        <v>1382.6860465116281</v>
+      </c>
+      <c r="BI78" s="13">
+        <v>1.100967519013925</v>
+      </c>
       <c r="BJ78" s="11"/>
       <c r="BK78" s="11"/>
       <c r="BL78" s="11"/>
@@ -18273,27 +19029,27 @@
       </c>
       <c r="N79" s="8">
         <f t="shared" ref="N79:N111" si="18">IFERROR(AVERAGE(T79,Z79,AF79,AL79,AR79,AX79,BD79,BJ79,BP79,BV79,CB79,CH79)," ")</f>
-        <v>5022860.166666667</v>
+        <v>5009190.2857142854</v>
       </c>
       <c r="O79" s="8">
         <f t="shared" ref="O79:O111" si="19">IFERROR(AVERAGE(U79,AA79,AG79,AM79,AS79,AY79,BE79,BK79,BQ79,BW79,CC79,CI79)," ")</f>
-        <v>30029.833333333332</v>
+        <v>29844.142857142859</v>
       </c>
       <c r="P79" s="8">
         <f t="shared" ref="P79:P111" si="20">IFERROR(SUM(V79,AB79,AH79,AN79,AT79,AZ79,BF79,BL79,BR79,BX79,CD79,CJ79)," ")</f>
-        <v>430</v>
+        <v>517</v>
       </c>
       <c r="Q79" s="9">
         <f t="shared" ref="Q79:Q109" si="21">IFERROR(SUM(T79,Z79,AF79,AL79,AR79,AX79,BD79,BJ79,BP79,BV79,CB79,CH79)/P79*3," ")</f>
-        <v>210259.26279069768</v>
+        <v>203468.07736943907</v>
       </c>
       <c r="R79" s="9">
         <f t="shared" ref="R79:R111" si="22">IFERROR(SUM(U79,AA79,AG79,AM79,AS79,AY79,BE79,BK79,BQ79,BW79,CC79,CI79)/P79*3," ")</f>
-        <v>1257.0627906976745</v>
+        <v>1212.2379110251452</v>
       </c>
       <c r="S79" s="10">
         <f t="shared" ref="S79:S111" si="23">IFERROR(AVERAGE(Y79,AE79,AK79,AQ79,AW79,BC79,BI79,BO79,BU79,CA79,CG79,CM79)," ")</f>
-        <v>0.98680274518980704</v>
+        <v>0.98467656584456709</v>
       </c>
       <c r="T79" s="11">
         <v>5601093</v>
@@ -18403,12 +19159,24 @@
       <c r="BC79" s="13">
         <v>0.89586892957583686</v>
       </c>
-      <c r="BD79" s="11"/>
-      <c r="BE79" s="11"/>
-      <c r="BF79" s="11"/>
-      <c r="BG79" s="12"/>
-      <c r="BH79" s="12"/>
-      <c r="BI79" s="13"/>
+      <c r="BD79" s="11">
+        <v>4927171</v>
+      </c>
+      <c r="BE79" s="11">
+        <v>28730</v>
+      </c>
+      <c r="BF79" s="11">
+        <v>87</v>
+      </c>
+      <c r="BG79" s="12">
+        <v>169902.44827586209</v>
+      </c>
+      <c r="BH79" s="12">
+        <v>990.68965517241384</v>
+      </c>
+      <c r="BI79" s="13">
+        <v>0.97191948977312792</v>
+      </c>
       <c r="BJ79" s="11"/>
       <c r="BK79" s="11"/>
       <c r="BL79" s="11"/>
@@ -18483,27 +19251,27 @@
       </c>
       <c r="N80" s="8">
         <f t="shared" si="18"/>
-        <v>4955324.833333333</v>
+        <v>5210447.8571428573</v>
       </c>
       <c r="O80" s="8">
         <f t="shared" si="19"/>
-        <v>159602.83333333334</v>
+        <v>169181.14285714287</v>
       </c>
       <c r="P80" s="8">
         <f t="shared" si="20"/>
-        <v>401</v>
+        <v>487</v>
       </c>
       <c r="Q80" s="9">
         <f t="shared" si="21"/>
-        <v>222433.53366583542</v>
+        <v>224680.50308008216</v>
       </c>
       <c r="R80" s="9">
         <f t="shared" si="22"/>
-        <v>7164.216957605985</v>
+        <v>7295.2854209445577</v>
       </c>
       <c r="S80" s="10">
         <f t="shared" si="23"/>
-        <v>2.2835670819043292</v>
+        <v>2.29078862800311</v>
       </c>
       <c r="T80" s="11">
         <v>5213937</v>
@@ -18613,12 +19381,24 @@
       <c r="BC80" s="13">
         <v>2.290764954026999</v>
       </c>
-      <c r="BD80" s="11"/>
-      <c r="BE80" s="11"/>
-      <c r="BF80" s="11"/>
-      <c r="BG80" s="12"/>
-      <c r="BH80" s="12"/>
-      <c r="BI80" s="13"/>
+      <c r="BD80" s="11">
+        <v>6741186</v>
+      </c>
+      <c r="BE80" s="11">
+        <v>226651</v>
+      </c>
+      <c r="BF80" s="11">
+        <v>86</v>
+      </c>
+      <c r="BG80" s="12">
+        <v>235157.65116279069</v>
+      </c>
+      <c r="BH80" s="12">
+        <v>7906.4302325581393</v>
+      </c>
+      <c r="BI80" s="13">
+        <v>2.3341179045957952</v>
+      </c>
       <c r="BJ80" s="11"/>
       <c r="BK80" s="11"/>
       <c r="BL80" s="11"/>
@@ -18693,27 +19473,27 @@
       </c>
       <c r="N81" s="8">
         <f t="shared" si="18"/>
-        <v>2715452</v>
+        <v>2769246.7142857141</v>
       </c>
       <c r="O81" s="8">
         <f t="shared" si="19"/>
-        <v>55796.333333333336</v>
+        <v>57078.142857142855</v>
       </c>
       <c r="P81" s="8">
         <f t="shared" si="20"/>
-        <v>393</v>
+        <v>478</v>
       </c>
       <c r="Q81" s="9">
         <f t="shared" si="21"/>
-        <v>124371.84732824427</v>
+        <v>121661.46652719665</v>
       </c>
       <c r="R81" s="9">
         <f t="shared" si="22"/>
-        <v>2555.5572519083967</v>
+        <v>2507.6171548117154</v>
       </c>
       <c r="S81" s="10">
         <f t="shared" si="23"/>
-        <v>1.8380651011573486</v>
+        <v>1.8385265627686549</v>
       </c>
       <c r="T81" s="11">
         <v>3606826</v>
@@ -18823,12 +19603,24 @@
       <c r="BC81" s="13">
         <v>1.7188592331383601</v>
       </c>
-      <c r="BD81" s="11"/>
-      <c r="BE81" s="11"/>
-      <c r="BF81" s="11"/>
-      <c r="BG81" s="12"/>
-      <c r="BH81" s="12"/>
-      <c r="BI81" s="13"/>
+      <c r="BD81" s="11">
+        <v>3092015</v>
+      </c>
+      <c r="BE81" s="11">
+        <v>64769</v>
+      </c>
+      <c r="BF81" s="11">
+        <v>85</v>
+      </c>
+      <c r="BG81" s="12">
+        <v>109129.9411764706</v>
+      </c>
+      <c r="BH81" s="12">
+        <v>2285.964705882353</v>
+      </c>
+      <c r="BI81" s="13">
+        <v>1.841295332436494</v>
+      </c>
       <c r="BJ81" s="11"/>
       <c r="BK81" s="11"/>
       <c r="BL81" s="11"/>
@@ -18903,27 +19695,27 @@
       </c>
       <c r="N82" s="8">
         <f t="shared" si="18"/>
-        <v>2802313.3333333335</v>
+        <v>2846613.8571428573</v>
       </c>
       <c r="O82" s="8">
         <f t="shared" si="19"/>
-        <v>51030.166666666664</v>
+        <v>52449.857142857145</v>
       </c>
       <c r="P82" s="8">
         <f t="shared" si="20"/>
-        <v>397</v>
+        <v>483</v>
       </c>
       <c r="Q82" s="9">
         <f t="shared" si="21"/>
-        <v>127057.02770780856</v>
+        <v>123765.81987577639</v>
       </c>
       <c r="R82" s="9">
         <f t="shared" si="22"/>
-        <v>2313.7103274559195</v>
+        <v>2280.4285714285716</v>
       </c>
       <c r="S82" s="10">
         <f t="shared" si="23"/>
-        <v>1.7343205707935578</v>
+        <v>1.7412318770756035</v>
       </c>
       <c r="T82" s="11">
         <v>4247045</v>
@@ -19033,12 +19825,24 @@
       <c r="BC82" s="13">
         <v>1.685268947730354</v>
       </c>
-      <c r="BD82" s="11"/>
-      <c r="BE82" s="11"/>
-      <c r="BF82" s="11"/>
-      <c r="BG82" s="12"/>
-      <c r="BH82" s="12"/>
-      <c r="BI82" s="13"/>
+      <c r="BD82" s="11">
+        <v>3112417</v>
+      </c>
+      <c r="BE82" s="11">
+        <v>60968</v>
+      </c>
+      <c r="BF82" s="11">
+        <v>86</v>
+      </c>
+      <c r="BG82" s="12">
+        <v>108572.6860465116</v>
+      </c>
+      <c r="BH82" s="12">
+        <v>2126.7906976744189</v>
+      </c>
+      <c r="BI82" s="13">
+        <v>1.782699714767876</v>
+      </c>
       <c r="BJ82" s="11"/>
       <c r="BK82" s="11"/>
       <c r="BL82" s="11"/>
@@ -19113,27 +19917,27 @@
       </c>
       <c r="N83" s="8">
         <f t="shared" si="18"/>
-        <v>2356305.9166666665</v>
+        <v>2359682.0714285714</v>
       </c>
       <c r="O83" s="8">
         <f t="shared" si="19"/>
-        <v>66408.666666666672</v>
+        <v>67984.857142857145</v>
       </c>
       <c r="P83" s="8">
         <f t="shared" si="20"/>
-        <v>396</v>
+        <v>478</v>
       </c>
       <c r="Q83" s="9">
         <f t="shared" si="21"/>
-        <v>107104.81439393939</v>
+        <v>103668.04079497908</v>
       </c>
       <c r="R83" s="9">
         <f t="shared" si="22"/>
-        <v>3018.5757575757575</v>
+        <v>2986.7824267782426</v>
       </c>
       <c r="S83" s="10">
         <f t="shared" si="23"/>
-        <v>2.1375415625117511</v>
+        <v>2.1601420552063963</v>
       </c>
       <c r="T83" s="11">
         <v>3362634.5</v>
@@ -19243,12 +20047,24 @@
       <c r="BC83" s="13">
         <v>2.076736672438082</v>
       </c>
-      <c r="BD83" s="11"/>
-      <c r="BE83" s="11"/>
-      <c r="BF83" s="11"/>
-      <c r="BG83" s="12"/>
-      <c r="BH83" s="12"/>
-      <c r="BI83" s="13"/>
+      <c r="BD83" s="11">
+        <v>2379939</v>
+      </c>
+      <c r="BE83" s="11">
+        <v>77442</v>
+      </c>
+      <c r="BF83" s="11">
+        <v>82</v>
+      </c>
+      <c r="BG83" s="12">
+        <v>87070.939024390245</v>
+      </c>
+      <c r="BH83" s="12">
+        <v>2833.2439024390242</v>
+      </c>
+      <c r="BI83" s="13">
+        <v>2.2957450113742661</v>
+      </c>
       <c r="BJ83" s="11"/>
       <c r="BK83" s="11"/>
       <c r="BL83" s="11"/>
@@ -19323,27 +20139,27 @@
       </c>
       <c r="N84" s="8">
         <f t="shared" si="18"/>
-        <v>2182741.5833333335</v>
+        <v>2194994.2142857141</v>
       </c>
       <c r="O84" s="8">
         <f t="shared" si="19"/>
-        <v>155613.66666666666</v>
+        <v>156378.85714285713</v>
       </c>
       <c r="P84" s="8">
         <f t="shared" si="20"/>
-        <v>432</v>
+        <v>516</v>
       </c>
       <c r="Q84" s="9">
         <f t="shared" si="21"/>
-        <v>90947.565972222219</v>
+        <v>89331.159883720931</v>
       </c>
       <c r="R84" s="9">
         <f t="shared" si="22"/>
-        <v>6483.9027777777783</v>
+        <v>6364.2558139534885</v>
       </c>
       <c r="S84" s="10">
         <f t="shared" si="23"/>
-        <v>3.398409723711493</v>
+        <v>3.3974354641212599</v>
       </c>
       <c r="T84" s="11">
         <v>2176614</v>
@@ -19453,12 +20269,24 @@
       <c r="BC84" s="13">
         <v>3.5216127975619811</v>
       </c>
-      <c r="BD84" s="11"/>
-      <c r="BE84" s="11"/>
-      <c r="BF84" s="11"/>
-      <c r="BG84" s="12"/>
-      <c r="BH84" s="12"/>
-      <c r="BI84" s="13"/>
+      <c r="BD84" s="11">
+        <v>2268510</v>
+      </c>
+      <c r="BE84" s="11">
+        <v>160970</v>
+      </c>
+      <c r="BF84" s="11">
+        <v>84</v>
+      </c>
+      <c r="BG84" s="12">
+        <v>81018.21428571429</v>
+      </c>
+      <c r="BH84" s="12">
+        <v>5748.9285714285716</v>
+      </c>
+      <c r="BI84" s="13">
+        <v>3.391589906579862</v>
+      </c>
       <c r="BJ84" s="11"/>
       <c r="BK84" s="11"/>
       <c r="BL84" s="11"/>
@@ -19533,27 +20361,27 @@
       </c>
       <c r="N85" s="8">
         <f t="shared" si="18"/>
-        <v>1233398.5</v>
+        <v>1250646.2857142857</v>
       </c>
       <c r="O85" s="8">
         <f t="shared" si="19"/>
-        <v>123393.5</v>
+        <v>127335.57142857143</v>
       </c>
       <c r="P85" s="8">
         <f t="shared" si="20"/>
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="Q85" s="9">
         <f t="shared" si="21"/>
-        <v>52859.935714285719</v>
+        <v>52527.144</v>
       </c>
       <c r="R85" s="9">
         <f t="shared" si="22"/>
-        <v>5288.2928571428574</v>
+        <v>5348.0940000000001</v>
       </c>
       <c r="S85" s="10">
         <f t="shared" si="23"/>
-        <v>4.1089559222048742</v>
+        <v>4.1293735513478831</v>
       </c>
       <c r="T85" s="11">
         <v>1663594</v>
@@ -19663,12 +20491,24 @@
       <c r="BC85" s="13">
         <v>4.423371224705309</v>
       </c>
-      <c r="BD85" s="11"/>
-      <c r="BE85" s="11"/>
-      <c r="BF85" s="11"/>
-      <c r="BG85" s="12"/>
-      <c r="BH85" s="12"/>
-      <c r="BI85" s="13"/>
+      <c r="BD85" s="11">
+        <v>1354133</v>
+      </c>
+      <c r="BE85" s="11">
+        <v>150988</v>
+      </c>
+      <c r="BF85" s="11">
+        <v>80</v>
+      </c>
+      <c r="BG85" s="12">
+        <v>50779.987500000003</v>
+      </c>
+      <c r="BH85" s="12">
+        <v>5662.0499999999993</v>
+      </c>
+      <c r="BI85" s="13">
+        <v>4.2518793262059331</v>
+      </c>
       <c r="BJ85" s="11"/>
       <c r="BK85" s="11"/>
       <c r="BL85" s="11"/>
@@ -19743,27 +20583,27 @@
       </c>
       <c r="N86" s="8">
         <f t="shared" si="18"/>
-        <v>3011711.1666666665</v>
+        <v>3039042</v>
       </c>
       <c r="O86" s="8">
         <f t="shared" si="19"/>
-        <v>73500.833333333328</v>
+        <v>73537.142857142855</v>
       </c>
       <c r="P86" s="8">
         <f t="shared" si="20"/>
-        <v>430</v>
+        <v>516</v>
       </c>
       <c r="Q86" s="9">
         <f t="shared" si="21"/>
-        <v>126071.63023255815</v>
+        <v>123681.94186046513</v>
       </c>
       <c r="R86" s="9">
         <f t="shared" si="22"/>
-        <v>3076.7790697674418</v>
+        <v>2992.7906976744184</v>
       </c>
       <c r="S86" s="10">
         <f t="shared" si="23"/>
-        <v>1.9806204367251627</v>
+        <v>1.9735126805530421</v>
       </c>
       <c r="T86" s="11">
         <v>3712214</v>
@@ -19873,12 +20713,24 @@
       <c r="BC86" s="13">
         <v>1.9893889145251611</v>
       </c>
-      <c r="BD86" s="11"/>
-      <c r="BE86" s="11"/>
-      <c r="BF86" s="11"/>
-      <c r="BG86" s="12"/>
-      <c r="BH86" s="12"/>
-      <c r="BI86" s="13"/>
+      <c r="BD86" s="11">
+        <v>3203027</v>
+      </c>
+      <c r="BE86" s="11">
+        <v>73755</v>
+      </c>
+      <c r="BF86" s="11">
+        <v>86</v>
+      </c>
+      <c r="BG86" s="12">
+        <v>111733.5</v>
+      </c>
+      <c r="BH86" s="12">
+        <v>2572.848837209302</v>
+      </c>
+      <c r="BI86" s="13">
+        <v>1.930866143520318</v>
+      </c>
       <c r="BJ86" s="11"/>
       <c r="BK86" s="11"/>
       <c r="BL86" s="11"/>
@@ -19953,27 +20805,27 @@
       </c>
       <c r="N87" s="8">
         <f t="shared" si="18"/>
-        <v>2927074.6666666665</v>
+        <v>2927838.4285714286</v>
       </c>
       <c r="O87" s="8">
         <f t="shared" si="19"/>
-        <v>70338.166666666672</v>
+        <v>71327</v>
       </c>
       <c r="P87" s="8">
         <f t="shared" si="20"/>
-        <v>430</v>
+        <v>510</v>
       </c>
       <c r="Q87" s="9">
         <f t="shared" si="21"/>
-        <v>122528.70697674419</v>
+        <v>120558.05294117649</v>
       </c>
       <c r="R87" s="9">
         <f t="shared" si="22"/>
-        <v>2944.3883720930235</v>
+        <v>2936.9941176470588</v>
       </c>
       <c r="S87" s="10">
         <f t="shared" si="23"/>
-        <v>1.9726610598792726</v>
+        <v>1.9857395315727995</v>
       </c>
       <c r="T87" s="11">
         <v>2997988</v>
@@ -20083,12 +20935,24 @@
       <c r="BC87" s="13">
         <v>1.924643395634918</v>
       </c>
-      <c r="BD87" s="11"/>
-      <c r="BE87" s="11"/>
-      <c r="BF87" s="11"/>
-      <c r="BG87" s="12"/>
-      <c r="BH87" s="12"/>
-      <c r="BI87" s="13"/>
+      <c r="BD87" s="11">
+        <v>2932421</v>
+      </c>
+      <c r="BE87" s="11">
+        <v>77260</v>
+      </c>
+      <c r="BF87" s="11">
+        <v>80</v>
+      </c>
+      <c r="BG87" s="12">
+        <v>109965.78750000001</v>
+      </c>
+      <c r="BH87" s="12">
+        <v>2897.25</v>
+      </c>
+      <c r="BI87" s="13">
+        <v>2.0642103617339611</v>
+      </c>
       <c r="BJ87" s="11"/>
       <c r="BK87" s="11"/>
       <c r="BL87" s="11"/>
@@ -20163,27 +21027,27 @@
       </c>
       <c r="N88" s="8">
         <f t="shared" si="18"/>
-        <v>2649996.8333333335</v>
+        <v>2714721.1428571427</v>
       </c>
       <c r="O88" s="8">
         <f t="shared" si="19"/>
-        <v>66860.833333333328</v>
+        <v>68419.28571428571</v>
       </c>
       <c r="P88" s="8">
         <f t="shared" si="20"/>
-        <v>431</v>
+        <v>512</v>
       </c>
       <c r="Q88" s="9">
         <f t="shared" si="21"/>
-        <v>110672.72157772622</v>
+        <v>111345.984375</v>
       </c>
       <c r="R88" s="9">
         <f t="shared" si="22"/>
-        <v>2792.3317865429235</v>
+        <v>2806.259765625</v>
       </c>
       <c r="S88" s="10">
         <f t="shared" si="23"/>
-        <v>2.0361562915446427</v>
+        <v>2.0329731409740215</v>
       </c>
       <c r="T88" s="11">
         <v>2265706</v>
@@ -20293,12 +21157,24 @@
       <c r="BC88" s="13">
         <v>1.976314622540883</v>
       </c>
-      <c r="BD88" s="11"/>
-      <c r="BE88" s="11"/>
-      <c r="BF88" s="11"/>
-      <c r="BG88" s="12"/>
-      <c r="BH88" s="12"/>
-      <c r="BI88" s="13"/>
+      <c r="BD88" s="11">
+        <v>3103067</v>
+      </c>
+      <c r="BE88" s="11">
+        <v>77770</v>
+      </c>
+      <c r="BF88" s="11">
+        <v>81</v>
+      </c>
+      <c r="BG88" s="12">
+        <v>114928.4074074074</v>
+      </c>
+      <c r="BH88" s="12">
+        <v>2880.37037037037</v>
+      </c>
+      <c r="BI88" s="13">
+        <v>2.0138742375502932</v>
+      </c>
       <c r="BJ88" s="11"/>
       <c r="BK88" s="11"/>
       <c r="BL88" s="11"/>
@@ -20373,27 +21249,27 @@
       </c>
       <c r="N89" s="8">
         <f t="shared" si="18"/>
-        <v>3046513.6066666669</v>
+        <v>3163622.9485714287</v>
       </c>
       <c r="O89" s="8">
         <f t="shared" si="19"/>
-        <v>28318.833333333332</v>
+        <v>30090.142857142859</v>
       </c>
       <c r="P89" s="8">
         <f t="shared" si="20"/>
-        <v>426</v>
+        <v>514</v>
       </c>
       <c r="Q89" s="9">
         <f t="shared" si="21"/>
-        <v>128725.92704225353</v>
+        <v>129253.07766536965</v>
       </c>
       <c r="R89" s="9">
         <f t="shared" si="22"/>
-        <v>1196.5704225352113</v>
+        <v>1229.3638132295719</v>
       </c>
       <c r="S89" s="10">
         <f t="shared" si="23"/>
-        <v>1.2172049656313837</v>
+        <v>1.2299359483897219</v>
       </c>
       <c r="T89" s="11">
         <v>3721474.08</v>
@@ -20503,12 +21379,24 @@
       <c r="BC89" s="13">
         <v>1.313542180569053</v>
       </c>
-      <c r="BD89" s="11"/>
-      <c r="BE89" s="11"/>
-      <c r="BF89" s="11"/>
-      <c r="BG89" s="12"/>
-      <c r="BH89" s="12"/>
-      <c r="BI89" s="13"/>
+      <c r="BD89" s="11">
+        <v>3866279</v>
+      </c>
+      <c r="BE89" s="11">
+        <v>40718</v>
+      </c>
+      <c r="BF89" s="11">
+        <v>88</v>
+      </c>
+      <c r="BG89" s="12">
+        <v>131804.96590909091</v>
+      </c>
+      <c r="BH89" s="12">
+        <v>1388.113636363636</v>
+      </c>
+      <c r="BI89" s="13">
+        <v>1.306321844939752</v>
+      </c>
       <c r="BJ89" s="11"/>
       <c r="BK89" s="11"/>
       <c r="BL89" s="11"/>
@@ -20583,27 +21471,27 @@
       </c>
       <c r="N90" s="8">
         <f t="shared" si="18"/>
-        <v>4665152.166666667</v>
+        <v>4691708.2857142854</v>
       </c>
       <c r="O90" s="8">
         <f t="shared" si="19"/>
-        <v>54953.666666666664</v>
+        <v>55058.142857142855</v>
       </c>
       <c r="P90" s="8">
         <f t="shared" si="20"/>
-        <v>430</v>
+        <v>516</v>
       </c>
       <c r="Q90" s="9">
         <f t="shared" si="21"/>
-        <v>195285.43953488371</v>
+        <v>190941.61627906977</v>
       </c>
       <c r="R90" s="9">
         <f t="shared" si="22"/>
-        <v>2300.3860465116277</v>
+        <v>2240.7383720930229</v>
       </c>
       <c r="S90" s="10">
         <f t="shared" si="23"/>
-        <v>1.3892472571709444</v>
+        <v>1.3856510678694072</v>
       </c>
       <c r="T90" s="11">
         <v>4835277</v>
@@ -20713,12 +21601,24 @@
       <c r="BC90" s="13">
         <v>1.4116079329567419</v>
       </c>
-      <c r="BD90" s="11"/>
-      <c r="BE90" s="11"/>
-      <c r="BF90" s="11"/>
-      <c r="BG90" s="12"/>
-      <c r="BH90" s="12"/>
-      <c r="BI90" s="13"/>
+      <c r="BD90" s="11">
+        <v>4851045</v>
+      </c>
+      <c r="BE90" s="11">
+        <v>55685</v>
+      </c>
+      <c r="BF90" s="11">
+        <v>86</v>
+      </c>
+      <c r="BG90" s="12">
+        <v>169222.5</v>
+      </c>
+      <c r="BH90" s="12">
+        <v>1942.5</v>
+      </c>
+      <c r="BI90" s="13">
+        <v>1.3640739320601829</v>
+      </c>
       <c r="BJ90" s="11"/>
       <c r="BK90" s="11"/>
       <c r="BL90" s="11"/>
@@ -20793,27 +21693,27 @@
       </c>
       <c r="N91" s="8">
         <f t="shared" si="18"/>
-        <v>6146994.3999999994</v>
+        <v>6425648.4857142856</v>
       </c>
       <c r="O91" s="8">
         <f t="shared" si="19"/>
-        <v>48904.333333333336</v>
+        <v>51484.571428571428</v>
       </c>
       <c r="P91" s="8">
         <f t="shared" si="20"/>
-        <v>416</v>
+        <v>502</v>
       </c>
       <c r="Q91" s="9">
         <f t="shared" si="21"/>
-        <v>265975.7192307692</v>
+        <v>268802.02828685258</v>
       </c>
       <c r="R91" s="9">
         <f t="shared" si="22"/>
-        <v>2116.0528846153848</v>
+        <v>2153.7370517928289</v>
       </c>
       <c r="S91" s="10">
         <f t="shared" si="23"/>
-        <v>1.1370940678961918</v>
+        <v>1.1403160241845023</v>
       </c>
       <c r="T91" s="11">
         <v>7274414.3999999994</v>
@@ -20923,12 +21823,24 @@
       <c r="BC91" s="13">
         <v>1.1090248638791871</v>
       </c>
-      <c r="BD91" s="11"/>
-      <c r="BE91" s="11"/>
-      <c r="BF91" s="11"/>
-      <c r="BG91" s="12"/>
-      <c r="BH91" s="12"/>
-      <c r="BI91" s="13"/>
+      <c r="BD91" s="11">
+        <v>8097573</v>
+      </c>
+      <c r="BE91" s="11">
+        <v>66966</v>
+      </c>
+      <c r="BF91" s="11">
+        <v>86</v>
+      </c>
+      <c r="BG91" s="12">
+        <v>282473.47674418602</v>
+      </c>
+      <c r="BH91" s="12">
+        <v>2336.0232558139528</v>
+      </c>
+      <c r="BI91" s="13">
+        <v>1.159647761914365</v>
+      </c>
       <c r="BJ91" s="11"/>
       <c r="BK91" s="11"/>
       <c r="BL91" s="11"/>
@@ -21003,27 +21915,27 @@
       </c>
       <c r="N92" s="8">
         <f t="shared" si="18"/>
-        <v>5479008.166666667</v>
+        <v>5459214.7142857146</v>
       </c>
       <c r="O92" s="8">
         <f t="shared" si="19"/>
-        <v>31738.5</v>
+        <v>31590.285714285714</v>
       </c>
       <c r="P92" s="8">
         <f t="shared" si="20"/>
-        <v>425</v>
+        <v>509</v>
       </c>
       <c r="Q92" s="9">
         <f t="shared" si="21"/>
-        <v>232052.11058823531</v>
+        <v>225232.82711198425</v>
       </c>
       <c r="R92" s="9">
         <f t="shared" si="22"/>
-        <v>1344.2188235294118</v>
+        <v>1303.3320235756385</v>
       </c>
       <c r="S92" s="10">
         <f t="shared" si="23"/>
-        <v>0.96693022272234108</v>
+        <v>0.96663592200382986</v>
       </c>
       <c r="T92" s="11">
         <v>5879996</v>
@@ -21133,12 +22045,24 @@
       <c r="BC92" s="13">
         <v>0.94260526822049751</v>
       </c>
-      <c r="BD92" s="11"/>
-      <c r="BE92" s="11"/>
-      <c r="BF92" s="11"/>
-      <c r="BG92" s="12"/>
-      <c r="BH92" s="12"/>
-      <c r="BI92" s="13"/>
+      <c r="BD92" s="11">
+        <v>5340454</v>
+      </c>
+      <c r="BE92" s="11">
+        <v>30701</v>
+      </c>
+      <c r="BF92" s="11">
+        <v>84</v>
+      </c>
+      <c r="BG92" s="12">
+        <v>190730.5</v>
+      </c>
+      <c r="BH92" s="12">
+        <v>1096.464285714286</v>
+      </c>
+      <c r="BI92" s="13">
+        <v>0.96487011769276232</v>
+      </c>
       <c r="BJ92" s="11"/>
       <c r="BK92" s="11"/>
       <c r="BL92" s="11"/>
@@ -21213,27 +22137,27 @@
       </c>
       <c r="N93" s="8">
         <f t="shared" si="18"/>
-        <v>3484388.9533333331</v>
+        <v>3518429.8171428568</v>
       </c>
       <c r="O93" s="8">
         <f t="shared" si="19"/>
-        <v>18292.166666666668</v>
+        <v>18812.142857142859</v>
       </c>
       <c r="P93" s="8">
         <f t="shared" si="20"/>
-        <v>418</v>
+        <v>495</v>
       </c>
       <c r="Q93" s="9">
         <f t="shared" si="21"/>
-        <v>150045.45732057415</v>
+        <v>149266.71951515149</v>
       </c>
       <c r="R93" s="9">
         <f t="shared" si="22"/>
-        <v>787.70095693779899</v>
+        <v>798.09090909090901</v>
       </c>
       <c r="S93" s="10">
         <f t="shared" si="23"/>
-        <v>0.91039000719490382</v>
+        <v>0.91972047566423709</v>
       </c>
       <c r="T93" s="11">
         <v>4307185.76</v>
@@ -21343,12 +22267,24 @@
       <c r="BC93" s="13">
         <v>0.93183549182629888</v>
       </c>
-      <c r="BD93" s="11"/>
-      <c r="BE93" s="11"/>
-      <c r="BF93" s="11"/>
-      <c r="BG93" s="12"/>
-      <c r="BH93" s="12"/>
-      <c r="BI93" s="13"/>
+      <c r="BD93" s="11">
+        <v>3722675</v>
+      </c>
+      <c r="BE93" s="11">
+        <v>21932</v>
+      </c>
+      <c r="BF93" s="11">
+        <v>77</v>
+      </c>
+      <c r="BG93" s="12">
+        <v>145039.28571428571</v>
+      </c>
+      <c r="BH93" s="12">
+        <v>854.49350649350652</v>
+      </c>
+      <c r="BI93" s="13">
+        <v>0.97570328648023741</v>
+      </c>
       <c r="BJ93" s="11"/>
       <c r="BK93" s="11"/>
       <c r="BL93" s="11"/>
@@ -21423,27 +22359,27 @@
       </c>
       <c r="N94" s="8">
         <f t="shared" si="18"/>
-        <v>3899754.6266666665</v>
+        <v>3813173.3942857138</v>
       </c>
       <c r="O94" s="8">
         <f t="shared" si="19"/>
-        <v>13108</v>
+        <v>13135.857142857143</v>
       </c>
       <c r="P94" s="8">
         <f t="shared" si="20"/>
-        <v>398</v>
+        <v>475</v>
       </c>
       <c r="Q94" s="9">
         <f t="shared" si="21"/>
-        <v>176370.81226130651</v>
+        <v>168582.40269473684</v>
       </c>
       <c r="R94" s="9">
         <f t="shared" si="22"/>
-        <v>592.8241206030151</v>
+        <v>580.7431578947369</v>
       </c>
       <c r="S94" s="10">
         <f t="shared" si="23"/>
-        <v>0.73530767376272665</v>
+        <v>0.74559570146365284</v>
       </c>
       <c r="T94" s="11">
         <v>5182499.76</v>
@@ -21553,12 +22489,24 @@
       <c r="BC94" s="13">
         <v>0.76030230175174052</v>
       </c>
-      <c r="BD94" s="11"/>
-      <c r="BE94" s="11"/>
-      <c r="BF94" s="11"/>
-      <c r="BG94" s="12"/>
-      <c r="BH94" s="12"/>
-      <c r="BI94" s="13"/>
+      <c r="BD94" s="11">
+        <v>3293686</v>
+      </c>
+      <c r="BE94" s="11">
+        <v>13303</v>
+      </c>
+      <c r="BF94" s="11">
+        <v>77</v>
+      </c>
+      <c r="BG94" s="12">
+        <v>128325.42857142859</v>
+      </c>
+      <c r="BH94" s="12">
+        <v>518.2987012987013</v>
+      </c>
+      <c r="BI94" s="13">
+        <v>0.80732386766920949</v>
+      </c>
       <c r="BJ94" s="11"/>
       <c r="BK94" s="11"/>
       <c r="BL94" s="11"/>
@@ -21633,27 +22581,27 @@
       </c>
       <c r="N95" s="8">
         <f t="shared" si="18"/>
-        <v>2537815.1666666665</v>
+        <v>2620015.2857142859</v>
       </c>
       <c r="O95" s="8">
         <f t="shared" si="19"/>
-        <v>16470.333333333332</v>
+        <v>16769.571428571428</v>
       </c>
       <c r="P95" s="8">
         <f t="shared" si="20"/>
-        <v>327</v>
+        <v>402</v>
       </c>
       <c r="Q95" s="9">
         <f t="shared" si="21"/>
-        <v>139696.24770642203</v>
+        <v>136866.47014925373</v>
       </c>
       <c r="R95" s="9">
         <f t="shared" si="22"/>
-        <v>906.62385321100919</v>
+        <v>876.0223880597016</v>
       </c>
       <c r="S95" s="10">
         <f t="shared" si="23"/>
-        <v>1.0253178612713516</v>
+        <v>1.01888844324309</v>
       </c>
       <c r="T95" s="11">
         <v>3447426</v>
@@ -21763,12 +22711,24 @@
       <c r="BC95" s="13">
         <v>0.99193305645248109</v>
       </c>
-      <c r="BD95" s="11"/>
-      <c r="BE95" s="11"/>
-      <c r="BF95" s="11"/>
-      <c r="BG95" s="12"/>
-      <c r="BH95" s="12"/>
-      <c r="BI95" s="13"/>
+      <c r="BD95" s="11">
+        <v>3113216</v>
+      </c>
+      <c r="BE95" s="11">
+        <v>18565</v>
+      </c>
+      <c r="BF95" s="11">
+        <v>75</v>
+      </c>
+      <c r="BG95" s="12">
+        <v>124528.64</v>
+      </c>
+      <c r="BH95" s="12">
+        <v>742.6</v>
+      </c>
+      <c r="BI95" s="13">
+        <v>0.98031193507352066</v>
+      </c>
       <c r="BJ95" s="11"/>
       <c r="BK95" s="11"/>
       <c r="BL95" s="11"/>
@@ -21843,27 +22803,27 @@
       </c>
       <c r="N96" s="8">
         <f t="shared" si="18"/>
-        <v>1472096.6666666667</v>
+        <v>1639744.5714285714</v>
       </c>
       <c r="O96" s="8">
         <f t="shared" si="19"/>
-        <v>9157.5</v>
+        <v>10644</v>
       </c>
       <c r="P96" s="8">
         <f t="shared" si="20"/>
-        <v>224</v>
+        <v>298</v>
       </c>
       <c r="Q96" s="9">
         <f t="shared" si="21"/>
-        <v>118293.48214285716</v>
+        <v>115552.46979865771</v>
       </c>
       <c r="R96" s="9">
         <f t="shared" si="22"/>
-        <v>735.87053571428578</v>
+        <v>750.08053691275177</v>
       </c>
       <c r="S96" s="10">
         <f t="shared" si="23"/>
-        <v>1.0021692088226952</v>
+        <v>1.0151477572689813</v>
       </c>
       <c r="T96" s="11">
         <v>224676</v>
@@ -21973,12 +22933,24 @@
       <c r="BC96" s="13">
         <v>0.98179829812219543</v>
       </c>
-      <c r="BD96" s="11"/>
-      <c r="BE96" s="11"/>
-      <c r="BF96" s="11"/>
-      <c r="BG96" s="12"/>
-      <c r="BH96" s="12"/>
-      <c r="BI96" s="13"/>
+      <c r="BD96" s="11">
+        <v>2645632</v>
+      </c>
+      <c r="BE96" s="11">
+        <v>19563</v>
+      </c>
+      <c r="BF96" s="11">
+        <v>74</v>
+      </c>
+      <c r="BG96" s="12">
+        <v>107255.3513513514</v>
+      </c>
+      <c r="BH96" s="12">
+        <v>793.09459459459458</v>
+      </c>
+      <c r="BI96" s="13">
+        <v>1.0930190479466979</v>
+      </c>
       <c r="BJ96" s="11"/>
       <c r="BK96" s="11"/>
       <c r="BL96" s="11"/>
@@ -22053,27 +23025,27 @@
       </c>
       <c r="N97" s="8">
         <f t="shared" si="18"/>
-        <v>3353397.3333333335</v>
+        <v>3173129.2857142859</v>
       </c>
       <c r="O97" s="8">
         <f t="shared" si="19"/>
-        <v>14094.666666666666</v>
+        <v>13335</v>
       </c>
       <c r="P97" s="8">
         <f t="shared" si="20"/>
-        <v>325</v>
+        <v>362</v>
       </c>
       <c r="Q97" s="9">
         <f t="shared" si="21"/>
-        <v>185726.62153846154</v>
+        <v>184076.56077348068</v>
       </c>
       <c r="R97" s="9">
         <f t="shared" si="22"/>
-        <v>780.62769230769231</v>
+        <v>773.57734806629833</v>
       </c>
       <c r="S97" s="10">
         <f t="shared" si="23"/>
-        <v>0.82016587111327555</v>
+        <v>0.82015598502444809</v>
       </c>
       <c r="T97" s="11">
         <v>3842266</v>
@@ -22183,12 +23155,24 @@
       <c r="BC97" s="13">
         <v>0.81993575801467711</v>
       </c>
-      <c r="BD97" s="11"/>
-      <c r="BE97" s="11"/>
-      <c r="BF97" s="11"/>
-      <c r="BG97" s="12"/>
-      <c r="BH97" s="12"/>
-      <c r="BI97" s="13"/>
+      <c r="BD97" s="11">
+        <v>2091521</v>
+      </c>
+      <c r="BE97" s="11">
+        <v>8777</v>
+      </c>
+      <c r="BF97" s="11">
+        <v>37</v>
+      </c>
+      <c r="BG97" s="12">
+        <v>169582.78378378379</v>
+      </c>
+      <c r="BH97" s="12">
+        <v>711.64864864864865</v>
+      </c>
+      <c r="BI97" s="13">
+        <v>0.82009666849148333</v>
+      </c>
       <c r="BJ97" s="11"/>
       <c r="BK97" s="11"/>
       <c r="BL97" s="11"/>
@@ -22263,27 +23247,27 @@
       </c>
       <c r="N98" s="8">
         <f t="shared" si="18"/>
-        <v>3265935.3984999997</v>
+        <v>3244265.0558571429</v>
       </c>
       <c r="O98" s="8">
         <f t="shared" si="19"/>
-        <v>24100.166666666668</v>
+        <v>23932.571428571428</v>
       </c>
       <c r="P98" s="8">
         <f t="shared" si="20"/>
-        <v>363</v>
+        <v>439</v>
       </c>
       <c r="Q98" s="9">
         <f t="shared" si="21"/>
-        <v>161947.20984297519</v>
+        <v>155192.63365148063</v>
       </c>
       <c r="R98" s="9">
         <f t="shared" si="22"/>
-        <v>1195.0495867768595</v>
+        <v>1144.8382687927108</v>
       </c>
       <c r="S98" s="10">
         <f t="shared" si="23"/>
-        <v>1.1085543250272167</v>
+        <v>1.1061986890904687</v>
       </c>
       <c r="T98" s="11">
         <v>5398924</v>
@@ -22393,12 +23377,24 @@
       <c r="BC98" s="13">
         <v>1.064995058481125</v>
       </c>
-      <c r="BD98" s="11"/>
-      <c r="BE98" s="11"/>
-      <c r="BF98" s="11"/>
-      <c r="BG98" s="12"/>
-      <c r="BH98" s="12"/>
-      <c r="BI98" s="13"/>
+      <c r="BD98" s="11">
+        <v>3114243</v>
+      </c>
+      <c r="BE98" s="11">
+        <v>22927</v>
+      </c>
+      <c r="BF98" s="11">
+        <v>76</v>
+      </c>
+      <c r="BG98" s="12">
+        <v>122930.64473684211</v>
+      </c>
+      <c r="BH98" s="12">
+        <v>905.01315789473688</v>
+      </c>
+      <c r="BI98" s="13">
+        <v>1.09206487346998</v>
+      </c>
       <c r="BJ98" s="11"/>
       <c r="BK98" s="11"/>
       <c r="BL98" s="11"/>
@@ -22473,27 +23469,27 @@
       </c>
       <c r="N99" s="8">
         <f t="shared" si="18"/>
-        <v>4876590.166666667</v>
+        <v>4945053.8571428573</v>
       </c>
       <c r="O99" s="8">
         <f t="shared" si="19"/>
-        <v>25432.333333333332</v>
+        <v>25546.714285714286</v>
       </c>
       <c r="P99" s="8">
         <f t="shared" si="20"/>
-        <v>426</v>
+        <v>512</v>
       </c>
       <c r="Q99" s="9">
         <f t="shared" si="21"/>
-        <v>206053.1056338028</v>
+        <v>202824.474609375</v>
       </c>
       <c r="R99" s="9">
         <f t="shared" si="22"/>
-        <v>1074.605633802817</v>
+        <v>1047.814453125</v>
       </c>
       <c r="S99" s="10">
         <f t="shared" si="23"/>
-        <v>0.9114388172553598</v>
+        <v>0.90813428706015287</v>
       </c>
       <c r="T99" s="11">
         <v>4901698</v>
@@ -22603,12 +23599,24 @@
       <c r="BC99" s="13">
         <v>0.99109236316101301</v>
       </c>
-      <c r="BD99" s="11"/>
-      <c r="BE99" s="11"/>
-      <c r="BF99" s="11"/>
-      <c r="BG99" s="12"/>
-      <c r="BH99" s="12"/>
-      <c r="BI99" s="13"/>
+      <c r="BD99" s="11">
+        <v>5355836</v>
+      </c>
+      <c r="BE99" s="11">
+        <v>26233</v>
+      </c>
+      <c r="BF99" s="11">
+        <v>86</v>
+      </c>
+      <c r="BG99" s="12">
+        <v>186831.48837209301</v>
+      </c>
+      <c r="BH99" s="12">
+        <v>915.10465116279067</v>
+      </c>
+      <c r="BI99" s="13">
+        <v>0.88830710588891093</v>
+      </c>
       <c r="BJ99" s="11"/>
       <c r="BK99" s="11"/>
       <c r="BL99" s="11"/>
@@ -22683,27 +23691,27 @@
       </c>
       <c r="N100" s="8">
         <f t="shared" si="18"/>
-        <v>4913783.5</v>
+        <v>5098965.2857142854</v>
       </c>
       <c r="O100" s="8">
         <f t="shared" si="19"/>
-        <v>41642.5</v>
+        <v>41944.857142857145</v>
       </c>
       <c r="P100" s="8">
         <f t="shared" si="20"/>
-        <v>428</v>
+        <v>514</v>
       </c>
       <c r="Q100" s="9">
         <f t="shared" si="21"/>
-        <v>206654.44626168223</v>
+        <v>208323.48443579767</v>
       </c>
       <c r="R100" s="9">
         <f t="shared" si="22"/>
-        <v>1751.320093457944</v>
+        <v>1713.7003891050583</v>
       </c>
       <c r="S100" s="10">
         <f t="shared" si="23"/>
-        <v>1.1765955363404135</v>
+        <v>1.1611067884095243</v>
       </c>
       <c r="T100" s="11">
         <v>5648674</v>
@@ -22813,12 +23821,24 @@
       <c r="BC100" s="13">
         <v>1.121274575440838</v>
       </c>
-      <c r="BD100" s="11"/>
-      <c r="BE100" s="11"/>
-      <c r="BF100" s="11"/>
-      <c r="BG100" s="12"/>
-      <c r="BH100" s="12"/>
-      <c r="BI100" s="13"/>
+      <c r="BD100" s="11">
+        <v>6210056</v>
+      </c>
+      <c r="BE100" s="11">
+        <v>43759</v>
+      </c>
+      <c r="BF100" s="11">
+        <v>86</v>
+      </c>
+      <c r="BG100" s="12">
+        <v>216629.8604651163</v>
+      </c>
+      <c r="BH100" s="12">
+        <v>1526.476744186047</v>
+      </c>
+      <c r="BI100" s="13">
+        <v>1.0681743008241891</v>
+      </c>
       <c r="BJ100" s="11"/>
       <c r="BK100" s="11"/>
       <c r="BL100" s="11"/>
@@ -22893,27 +23913,27 @@
       </c>
       <c r="N101" s="8">
         <f t="shared" si="18"/>
-        <v>4527442.833333333</v>
+        <v>4543410.8571428573</v>
       </c>
       <c r="O101" s="8">
         <f t="shared" si="19"/>
-        <v>23541</v>
+        <v>23226.571428571428</v>
       </c>
       <c r="P101" s="8">
         <f t="shared" si="20"/>
-        <v>429</v>
+        <v>514</v>
       </c>
       <c r="Q101" s="9">
         <f t="shared" si="21"/>
-        <v>189962.63636363635</v>
+        <v>185625.73540856031</v>
       </c>
       <c r="R101" s="9">
         <f t="shared" si="22"/>
-        <v>987.73426573426582</v>
+        <v>948.94552529182874</v>
       </c>
       <c r="S101" s="10">
         <f t="shared" si="23"/>
-        <v>0.92044694981113351</v>
+        <v>0.91225391260496991</v>
       </c>
       <c r="T101" s="11">
         <v>5198390</v>
@@ -23023,12 +24043,24 @@
       <c r="BC101" s="13">
         <v>0.88581814818500904</v>
       </c>
-      <c r="BD101" s="11"/>
-      <c r="BE101" s="11"/>
-      <c r="BF101" s="11"/>
-      <c r="BG101" s="12"/>
-      <c r="BH101" s="12"/>
-      <c r="BI101" s="13"/>
+      <c r="BD101" s="11">
+        <v>4639219</v>
+      </c>
+      <c r="BE101" s="11">
+        <v>21340</v>
+      </c>
+      <c r="BF101" s="11">
+        <v>85</v>
+      </c>
+      <c r="BG101" s="12">
+        <v>163737.14117647061</v>
+      </c>
+      <c r="BH101" s="12">
+        <v>753.17647058823536</v>
+      </c>
+      <c r="BI101" s="13">
+        <v>0.86309568936798775</v>
+      </c>
       <c r="BJ101" s="11"/>
       <c r="BK101" s="11"/>
       <c r="BL101" s="11"/>
@@ -23103,27 +24135,27 @@
       </c>
       <c r="N102" s="8">
         <f t="shared" si="18"/>
-        <v>2272203.8666666667</v>
+        <v>2235847.4571428569</v>
       </c>
       <c r="O102" s="8">
         <f t="shared" si="19"/>
-        <v>69329.333333333328</v>
+        <v>67272.28571428571</v>
       </c>
       <c r="P102" s="8">
         <f t="shared" si="20"/>
-        <v>427</v>
+        <v>501</v>
       </c>
       <c r="Q102" s="9">
         <f t="shared" si="21"/>
-        <v>95783.76955503512</v>
+        <v>93718.156886227545</v>
       </c>
       <c r="R102" s="9">
         <f t="shared" si="22"/>
-        <v>2922.5480093676815</v>
+        <v>2819.7964071856286</v>
       </c>
       <c r="S102" s="10">
         <f t="shared" si="23"/>
-        <v>2.2077548992400788</v>
+        <v>2.1924297337966427</v>
       </c>
       <c r="T102" s="11">
         <v>2396165.2000000002</v>
@@ -23233,12 +24265,24 @@
       <c r="BC102" s="13">
         <v>2.1159542981090218</v>
       </c>
-      <c r="BD102" s="11"/>
-      <c r="BE102" s="11"/>
-      <c r="BF102" s="11"/>
-      <c r="BG102" s="12"/>
-      <c r="BH102" s="12"/>
-      <c r="BI102" s="13"/>
+      <c r="BD102" s="11">
+        <v>2017709</v>
+      </c>
+      <c r="BE102" s="11">
+        <v>54930</v>
+      </c>
+      <c r="BF102" s="11">
+        <v>74</v>
+      </c>
+      <c r="BG102" s="12">
+        <v>81799.013513513506</v>
+      </c>
+      <c r="BH102" s="12">
+        <v>2226.8918918918921</v>
+      </c>
+      <c r="BI102" s="13">
+        <v>2.100478741136024</v>
+      </c>
       <c r="BJ102" s="11"/>
       <c r="BK102" s="11"/>
       <c r="BL102" s="11"/>
@@ -23313,27 +24357,27 @@
       </c>
       <c r="N103" s="8">
         <f t="shared" si="18"/>
-        <v>245888.16666666666</v>
+        <v>234127.14285714287</v>
       </c>
       <c r="O103" s="8">
         <f t="shared" si="19"/>
-        <v>116150</v>
+        <v>114155.28571428571</v>
       </c>
       <c r="P103" s="8">
         <f t="shared" si="20"/>
-        <v>415</v>
+        <v>488</v>
       </c>
       <c r="Q103" s="9">
         <f t="shared" si="21"/>
-        <v>10665.028915662651</v>
+        <v>10075.14344262295</v>
       </c>
       <c r="R103" s="9">
         <f t="shared" si="22"/>
-        <v>5037.8313253012047</v>
+        <v>4912.4200819672133</v>
       </c>
       <c r="S103" s="10">
         <f t="shared" si="23"/>
-        <v>8.9649134656310938</v>
+        <v>9.1222961948439529</v>
       </c>
       <c r="T103" s="11">
         <v>274124</v>
@@ -23443,12 +24487,24 @@
       <c r="BC103" s="13">
         <v>8.9660844907353248</v>
       </c>
-      <c r="BD103" s="11"/>
-      <c r="BE103" s="11"/>
-      <c r="BF103" s="11"/>
-      <c r="BG103" s="12"/>
-      <c r="BH103" s="12"/>
-      <c r="BI103" s="13"/>
+      <c r="BD103" s="11">
+        <v>163561</v>
+      </c>
+      <c r="BE103" s="11">
+        <v>102187</v>
+      </c>
+      <c r="BF103" s="11">
+        <v>73</v>
+      </c>
+      <c r="BG103" s="12">
+        <v>6721.6849315068494</v>
+      </c>
+      <c r="BH103" s="12">
+        <v>4199.465753424658</v>
+      </c>
+      <c r="BI103" s="13">
+        <v>10.066592570121109</v>
+      </c>
       <c r="BJ103" s="11"/>
       <c r="BK103" s="11"/>
       <c r="BL103" s="11"/>
@@ -23523,27 +24579,27 @@
       </c>
       <c r="N104" s="8">
         <f t="shared" si="18"/>
-        <v>5085178.4466666663</v>
+        <v>5597219.2400000002</v>
       </c>
       <c r="O104" s="8">
         <f t="shared" si="19"/>
-        <v>7282.666666666667</v>
+        <v>9508.8571428571431</v>
       </c>
       <c r="P104" s="8">
         <f t="shared" si="20"/>
-        <v>369</v>
+        <v>451</v>
       </c>
       <c r="Q104" s="9">
         <f t="shared" si="21"/>
-        <v>248057.48520325206</v>
+        <v>260624.39920177381</v>
       </c>
       <c r="R104" s="9">
         <f t="shared" si="22"/>
-        <v>355.2520325203252</v>
+        <v>442.76274944567626</v>
       </c>
       <c r="S104" s="10">
         <f t="shared" si="23"/>
-        <v>0.46254911436655183</v>
+        <v>0.4894729305488289</v>
       </c>
       <c r="T104" s="11">
         <v>2471269.08</v>
@@ -23653,12 +24709,24 @@
       <c r="BC104" s="13">
         <v>0.58906469047534005</v>
       </c>
-      <c r="BD104" s="11"/>
-      <c r="BE104" s="11"/>
-      <c r="BF104" s="11"/>
-      <c r="BG104" s="12"/>
-      <c r="BH104" s="12"/>
-      <c r="BI104" s="13"/>
+      <c r="BD104" s="11">
+        <v>8669464</v>
+      </c>
+      <c r="BE104" s="11">
+        <v>22866</v>
+      </c>
+      <c r="BF104" s="11">
+        <v>82</v>
+      </c>
+      <c r="BG104" s="12">
+        <v>317175.51219512202</v>
+      </c>
+      <c r="BH104" s="12">
+        <v>836.56097560975616</v>
+      </c>
+      <c r="BI104" s="13">
+        <v>0.65101582764249166</v>
+      </c>
       <c r="BJ104" s="11"/>
       <c r="BK104" s="11"/>
       <c r="BL104" s="11"/>
@@ -23733,27 +24801,27 @@
       </c>
       <c r="N105" s="8">
         <f t="shared" si="18"/>
-        <v>4374036.6050000004</v>
+        <v>5585726.0900000008</v>
       </c>
       <c r="O105" s="8">
         <f t="shared" si="19"/>
-        <v>6366.666666666667</v>
+        <v>7100.7142857142853</v>
       </c>
       <c r="P105" s="8">
         <f t="shared" si="20"/>
-        <v>391</v>
+        <v>472</v>
       </c>
       <c r="Q105" s="9">
         <f t="shared" si="21"/>
-        <v>201362.29895140667</v>
+        <v>248517.47434322035</v>
       </c>
       <c r="R105" s="9">
         <f t="shared" si="22"/>
-        <v>293.09462915601023</v>
+        <v>315.92161016949149</v>
       </c>
       <c r="S105" s="10">
         <f t="shared" si="23"/>
-        <v>0.49173078306500778</v>
+        <v>0.47576924262714954</v>
       </c>
       <c r="T105" s="11">
         <v>2163577.9500000002</v>
@@ -23863,12 +24931,24 @@
       <c r="BC105" s="13">
         <v>0.40137036185396152</v>
       </c>
-      <c r="BD105" s="11"/>
-      <c r="BE105" s="11"/>
-      <c r="BF105" s="11"/>
-      <c r="BG105" s="12"/>
-      <c r="BH105" s="12"/>
-      <c r="BI105" s="13"/>
+      <c r="BD105" s="11">
+        <v>12855863</v>
+      </c>
+      <c r="BE105" s="11">
+        <v>11505</v>
+      </c>
+      <c r="BF105" s="11">
+        <v>81</v>
+      </c>
+      <c r="BG105" s="12">
+        <v>476143.07407407399</v>
+      </c>
+      <c r="BH105" s="12">
+        <v>426.11111111111109</v>
+      </c>
+      <c r="BI105" s="13">
+        <v>0.38</v>
+      </c>
       <c r="BJ105" s="11"/>
       <c r="BK105" s="11"/>
       <c r="BL105" s="11"/>
@@ -23943,27 +25023,27 @@
       </c>
       <c r="N106" s="8">
         <f t="shared" si="18"/>
-        <v>9250149.166666666</v>
+        <v>9577969.5714285709</v>
       </c>
       <c r="O106" s="8">
         <f t="shared" si="19"/>
-        <v>168340</v>
+        <v>175108.85714285713</v>
       </c>
       <c r="P106" s="8">
         <f t="shared" si="20"/>
-        <v>401</v>
+        <v>486</v>
       </c>
       <c r="Q106" s="9">
         <f t="shared" si="21"/>
-        <v>415218.66583541152</v>
+        <v>413862.88271604938</v>
       </c>
       <c r="R106" s="9">
         <f t="shared" si="22"/>
-        <v>7556.4089775561097</v>
+        <v>7566.4320987654319</v>
       </c>
       <c r="S106" s="10">
         <f t="shared" si="23"/>
-        <v>1.7127907794501767</v>
+        <v>1.7163697000864959</v>
       </c>
       <c r="T106" s="11">
         <v>10039950</v>
@@ -24073,12 +25153,24 @@
       <c r="BC106" s="13">
         <v>1.751327640690985</v>
       </c>
-      <c r="BD106" s="11"/>
-      <c r="BE106" s="11"/>
-      <c r="BF106" s="11"/>
-      <c r="BG106" s="12"/>
-      <c r="BH106" s="12"/>
-      <c r="BI106" s="13"/>
+      <c r="BD106" s="11">
+        <v>11544892</v>
+      </c>
+      <c r="BE106" s="11">
+        <v>215722</v>
+      </c>
+      <c r="BF106" s="11">
+        <v>85</v>
+      </c>
+      <c r="BG106" s="12">
+        <v>407466.77647058817</v>
+      </c>
+      <c r="BH106" s="12">
+        <v>7613.7176470588238</v>
+      </c>
+      <c r="BI106" s="13">
+        <v>1.737843223904411</v>
+      </c>
       <c r="BJ106" s="11"/>
       <c r="BK106" s="11"/>
       <c r="BL106" s="11"/>
@@ -24153,27 +25245,27 @@
       </c>
       <c r="N107" s="8">
         <f t="shared" si="18"/>
-        <v>3706640</v>
+        <v>3753002.7142857141</v>
       </c>
       <c r="O107" s="8">
         <f t="shared" si="19"/>
-        <v>200687</v>
+        <v>195057</v>
       </c>
       <c r="P107" s="8">
         <f t="shared" si="20"/>
-        <v>397</v>
+        <v>480</v>
       </c>
       <c r="Q107" s="9">
         <f t="shared" si="21"/>
-        <v>168059.24433249369</v>
+        <v>164193.86874999999</v>
       </c>
       <c r="R107" s="9">
         <f t="shared" si="22"/>
-        <v>9099.1586901763221</v>
+        <v>8533.7437500000015</v>
       </c>
       <c r="S107" s="10">
         <f t="shared" si="23"/>
-        <v>2.9819045872651109</v>
+        <v>2.9195157116708201</v>
       </c>
       <c r="T107" s="11">
         <v>4508101</v>
@@ -24283,12 +25375,24 @@
       <c r="BC107" s="13">
         <v>3.0604551484374971</v>
       </c>
-      <c r="BD107" s="11"/>
-      <c r="BE107" s="11"/>
-      <c r="BF107" s="11"/>
-      <c r="BG107" s="12"/>
-      <c r="BH107" s="12"/>
-      <c r="BI107" s="13"/>
+      <c r="BD107" s="11">
+        <v>4031179</v>
+      </c>
+      <c r="BE107" s="11">
+        <v>161277</v>
+      </c>
+      <c r="BF107" s="11">
+        <v>83</v>
+      </c>
+      <c r="BG107" s="12">
+        <v>145705.26506024101</v>
+      </c>
+      <c r="BH107" s="12">
+        <v>5829.2891566265062</v>
+      </c>
+      <c r="BI107" s="13">
+        <v>2.545182458105077</v>
+      </c>
       <c r="BJ107" s="11"/>
       <c r="BK107" s="11"/>
       <c r="BL107" s="11"/>
@@ -24363,27 +25467,27 @@
       </c>
       <c r="N108" s="8">
         <f t="shared" si="18"/>
-        <v>4491533.666666667</v>
+        <v>4466628.2857142854</v>
       </c>
       <c r="O108" s="8">
         <f t="shared" si="19"/>
-        <v>189728.66666666666</v>
+        <v>198562.42857142858</v>
       </c>
       <c r="P108" s="8">
         <f t="shared" si="20"/>
-        <v>397</v>
+        <v>483</v>
       </c>
       <c r="Q108" s="9">
         <f t="shared" si="21"/>
-        <v>203646.36272040301</v>
+        <v>194201.2298136646</v>
       </c>
       <c r="R108" s="9">
         <f t="shared" si="22"/>
-        <v>8602.3073047858943</v>
+        <v>8633.1490683229822</v>
       </c>
       <c r="S108" s="10">
         <f t="shared" si="23"/>
-        <v>2.6460065858336987</v>
+        <v>2.7068605191912409</v>
       </c>
       <c r="T108" s="11">
         <v>3557826</v>
@@ -24493,12 +25597,24 @@
       <c r="BC108" s="13">
         <v>2.7377300880463928</v>
       </c>
-      <c r="BD108" s="11"/>
-      <c r="BE108" s="11"/>
-      <c r="BF108" s="11"/>
-      <c r="BG108" s="12"/>
-      <c r="BH108" s="12"/>
-      <c r="BI108" s="13"/>
+      <c r="BD108" s="11">
+        <v>4317196</v>
+      </c>
+      <c r="BE108" s="11">
+        <v>251565</v>
+      </c>
+      <c r="BF108" s="11">
+        <v>86</v>
+      </c>
+      <c r="BG108" s="12">
+        <v>150599.8604651163</v>
+      </c>
+      <c r="BH108" s="12">
+        <v>8775.5232558139542</v>
+      </c>
+      <c r="BI108" s="13">
+        <v>3.0719841193364918</v>
+      </c>
       <c r="BJ108" s="11"/>
       <c r="BK108" s="11"/>
       <c r="BL108" s="11"/>
@@ -24573,27 +25689,27 @@
       </c>
       <c r="N109" s="8">
         <f t="shared" si="18"/>
-        <v>2013652.5</v>
+        <v>2045165.2857142857</v>
       </c>
       <c r="O109" s="8">
         <f t="shared" si="19"/>
-        <v>227019.5</v>
+        <v>233699</v>
       </c>
       <c r="P109" s="8">
         <f t="shared" si="20"/>
-        <v>272</v>
+        <v>325</v>
       </c>
       <c r="Q109" s="9">
         <f t="shared" si="21"/>
-        <v>133256.41544117648</v>
+        <v>132149.14153846155</v>
       </c>
       <c r="R109" s="9">
         <f t="shared" si="22"/>
-        <v>15023.349264705881</v>
+        <v>15100.550769230769</v>
       </c>
       <c r="S109" s="10">
         <f t="shared" si="23"/>
-        <v>4.2788094808953483</v>
+        <v>4.3043069683353252</v>
       </c>
       <c r="T109" s="11">
         <v>3150735</v>
@@ -24703,12 +25819,24 @@
       <c r="BC109" s="13">
         <v>4.4165405567664919</v>
       </c>
-      <c r="BD109" s="11"/>
-      <c r="BE109" s="11"/>
-      <c r="BF109" s="11"/>
-      <c r="BG109" s="12"/>
-      <c r="BH109" s="12"/>
-      <c r="BI109" s="13"/>
+      <c r="BD109" s="11">
+        <v>2234242</v>
+      </c>
+      <c r="BE109" s="11">
+        <v>273776</v>
+      </c>
+      <c r="BF109" s="11">
+        <v>53</v>
+      </c>
+      <c r="BG109" s="12">
+        <v>126466.52830188681</v>
+      </c>
+      <c r="BH109" s="12">
+        <v>15496.75471698113</v>
+      </c>
+      <c r="BI109" s="13">
+        <v>4.4572918929751886</v>
+      </c>
       <c r="BJ109" s="11"/>
       <c r="BK109" s="11"/>
       <c r="BL109" s="11"/>
@@ -24783,27 +25911,27 @@
       </c>
       <c r="N110" s="8">
         <f t="shared" si="18"/>
-        <v>798056</v>
+        <v>800987.14285714284</v>
       </c>
       <c r="O110" s="8">
         <f t="shared" si="19"/>
-        <v>186827.83333333334</v>
+        <v>188087.85714285713</v>
       </c>
       <c r="P110" s="8">
         <f t="shared" si="20"/>
-        <v>270</v>
+        <v>329</v>
       </c>
       <c r="Q110" s="9">
         <f t="shared" ref="Q110:Q111" si="24">IFERROR(SUM(T110,Z110,AF110,AL110,AR110,AX110,BD110,BJ110,BP110,BV110,CB110,CH110)/P110*3," ")</f>
-        <v>53203.73333333333</v>
+        <v>51126.838905775076</v>
       </c>
       <c r="R110" s="9">
         <f t="shared" si="22"/>
-        <v>12455.18888888889</v>
+        <v>12005.607902735563</v>
       </c>
       <c r="S110" s="10">
         <f t="shared" si="23"/>
-        <v>6.325891135085187</v>
+        <v>6.3115558071003681</v>
       </c>
       <c r="T110" s="11">
         <v>1383825</v>
@@ -24913,12 +26041,24 @@
       <c r="BC110" s="13">
         <v>6.012093675562511</v>
       </c>
-      <c r="BD110" s="11"/>
-      <c r="BE110" s="11"/>
-      <c r="BF110" s="11"/>
-      <c r="BG110" s="12"/>
-      <c r="BH110" s="12"/>
-      <c r="BI110" s="13"/>
+      <c r="BD110" s="11">
+        <v>818574</v>
+      </c>
+      <c r="BE110" s="11">
+        <v>195648</v>
+      </c>
+      <c r="BF110" s="11">
+        <v>59</v>
+      </c>
+      <c r="BG110" s="12">
+        <v>41622.406779661018</v>
+      </c>
+      <c r="BH110" s="12">
+        <v>9948.203389830509</v>
+      </c>
+      <c r="BI110" s="13">
+        <v>6.2255438391914524</v>
+      </c>
       <c r="BJ110" s="11"/>
       <c r="BK110" s="11"/>
       <c r="BL110" s="11"/>
@@ -24993,27 +26133,27 @@
       </c>
       <c r="N111" s="8">
         <f t="shared" si="18"/>
-        <v>2717683.6</v>
+        <v>2940522.5</v>
       </c>
       <c r="O111" s="8">
         <f t="shared" si="19"/>
-        <v>12593.2</v>
+        <v>13332.333333333334</v>
       </c>
       <c r="P111" s="8">
         <f t="shared" si="20"/>
-        <v>273</v>
+        <v>340</v>
       </c>
       <c r="Q111" s="9">
         <f t="shared" si="24"/>
-        <v>149323.27472527474</v>
+        <v>155674.7205882353</v>
       </c>
       <c r="R111" s="9">
         <f t="shared" si="22"/>
-        <v>691.93406593406598</v>
+        <v>705.82941176470592</v>
       </c>
       <c r="S111" s="10">
         <f t="shared" si="23"/>
-        <v>0.88193307549590672</v>
+        <v>0.87181350554336268</v>
       </c>
       <c r="T111" s="11">
         <v>3953686</v>
@@ -25111,12 +26251,24 @@
       <c r="BA111" s="12"/>
       <c r="BB111" s="12"/>
       <c r="BC111" s="13"/>
-      <c r="BD111" s="11"/>
-      <c r="BE111" s="11"/>
-      <c r="BF111" s="11"/>
-      <c r="BG111" s="12"/>
-      <c r="BH111" s="12"/>
-      <c r="BI111" s="13"/>
+      <c r="BD111" s="11">
+        <v>4054717</v>
+      </c>
+      <c r="BE111" s="11">
+        <v>17028</v>
+      </c>
+      <c r="BF111" s="11">
+        <v>67</v>
+      </c>
+      <c r="BG111" s="12">
+        <v>181554.4925373134</v>
+      </c>
+      <c r="BH111" s="12">
+        <v>762.44776119402991</v>
+      </c>
+      <c r="BI111" s="13">
+        <v>0.82121565578064293</v>
+      </c>
       <c r="BJ111" s="11"/>
       <c r="BK111" s="11"/>
       <c r="BL111" s="11"/>
@@ -25177,11 +26329,11 @@
       <c r="M112" s="22"/>
       <c r="N112" s="14">
         <f>SUM(N57:N111)</f>
-        <v>214682094.56016657</v>
+        <v>219899698.23252383</v>
       </c>
       <c r="O112" s="14">
         <f>SUM(O57:O111)</f>
-        <v>2860715.4</v>
+        <v>2906134.1190476194</v>
       </c>
       <c r="P112" s="14"/>
       <c r="Q112" s="14"/>
@@ -25261,11 +26413,11 @@
       <c r="BC112" s="24"/>
       <c r="BD112" s="14">
         <f>SUM(BD57:BD111)</f>
-        <v>0</v>
+        <v>248152245</v>
       </c>
       <c r="BE112" s="14">
         <f>SUM(BE57:BE111)</f>
-        <v>0</v>
+        <v>3201228</v>
       </c>
       <c r="BF112" s="14"/>
       <c r="BG112" s="14"/>
@@ -25791,27 +26943,27 @@
       </c>
       <c r="N116" s="8">
         <f t="shared" ref="N116:O118" si="25">IFERROR(AVERAGE(T116,Z116,AF116,AL116,AR116,AX116,BD116,BJ116,BP116,BV116,CB116,CH116)," ")</f>
-        <v>2434370.3333333335</v>
+        <v>2791632.5714285714</v>
       </c>
       <c r="O116" s="8">
         <f t="shared" si="25"/>
-        <v>368802</v>
+        <v>427427.57142857142</v>
       </c>
       <c r="P116" s="8">
         <f>IFERROR(SUM(V116,AB116,AH116,AN116,AT116,AZ116,BF116,BL116,BR116,BX116,CD116,CJ116)," ")</f>
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="Q116" s="9">
         <f>IFERROR(SUM(T116,Z116,AF116,AL116,AR116,AX116,BD116,BJ116,BP116,BV116,CB116,CH116)/P116*3," ")</f>
-        <v>273866.66249999998</v>
+        <v>271408.72222222225</v>
       </c>
       <c r="R116" s="9">
         <f>IFERROR(SUM(U116,AA116,AG116,AM116,AS116,AY116,BE116,BK116,BQ116,BW116,CC116,CI116)/P116*3," ")</f>
-        <v>41490.225000000006</v>
+        <v>41555.458333333336</v>
       </c>
       <c r="S116" s="10">
         <f>IFERROR(AVERAGE(Y116,AE116,AK116,AQ116,AW116,BC116,BI116,BO116,BU116,CA116,CG116,CM116)," ")</f>
-        <v>4.9869380444118301</v>
+        <v>4.9972561875085395</v>
       </c>
       <c r="T116" s="11">
         <v>3772092</v>
@@ -25921,12 +27073,24 @@
       <c r="BC116" s="13">
         <v>4.9468321517461531</v>
       </c>
-      <c r="BD116" s="11"/>
-      <c r="BE116" s="11"/>
-      <c r="BF116" s="11"/>
-      <c r="BG116" s="12"/>
-      <c r="BH116" s="12"/>
-      <c r="BI116" s="13"/>
+      <c r="BD116" s="11">
+        <v>4935206</v>
+      </c>
+      <c r="BE116" s="11">
+        <v>779181</v>
+      </c>
+      <c r="BF116" s="11">
+        <v>56</v>
+      </c>
+      <c r="BG116" s="12">
+        <v>264386.03571428568</v>
+      </c>
+      <c r="BH116" s="12">
+        <v>41741.83928571429</v>
+      </c>
+      <c r="BI116" s="13">
+        <v>5.0591650460887978</v>
+      </c>
       <c r="BJ116" s="11"/>
       <c r="BK116" s="11"/>
       <c r="BL116" s="11"/>
@@ -25999,27 +27163,27 @@
       </c>
       <c r="N117" s="8">
         <f t="shared" si="25"/>
-        <v>2506566.3333333335</v>
+        <v>2920205.5714285714</v>
       </c>
       <c r="O117" s="8">
         <f t="shared" si="25"/>
-        <v>378469.16666666669</v>
+        <v>447181.85714285716</v>
       </c>
       <c r="P117" s="8">
         <f>IFERROR(SUM(V117,AB117,AH117,AN117,AT117,AZ117,BF117,BL117,BR117,BX117,CD117,CJ117)," ")</f>
-        <v>165</v>
+        <v>223</v>
       </c>
       <c r="Q117" s="9">
         <f>IFERROR(SUM(T117,Z117,AF117,AL117,AR117,AX117,BD117,BJ117,BP117,BV117,CB117,CH117)/P117*3," ")</f>
-        <v>273443.59999999998</v>
+        <v>274996.93721973093</v>
       </c>
       <c r="R117" s="9">
         <f>IFERROR(SUM(U117,AA117,AG117,AM117,AS117,AY117,BE117,BK117,BQ117,BW117,CC117,CI117)/P117*3," ")</f>
-        <v>41287.545454545456</v>
+        <v>42111.295964125558</v>
       </c>
       <c r="S117" s="10">
         <f>IFERROR(AVERAGE(Y117,AE117,AK117,AQ117,AW117,BC117,BI117,BO117,BU117,CA117,CG117,CM117)," ")</f>
-        <v>4.9814919247538372</v>
+        <v>4.9953776079595871</v>
       </c>
       <c r="T117" s="11">
         <v>4072469</v>
@@ -26129,12 +27293,24 @@
       <c r="BC117" s="13">
         <v>4.9193708281410453</v>
       </c>
-      <c r="BD117" s="11"/>
-      <c r="BE117" s="11"/>
-      <c r="BF117" s="11"/>
-      <c r="BG117" s="12"/>
-      <c r="BH117" s="12"/>
-      <c r="BI117" s="13"/>
+      <c r="BD117" s="11">
+        <v>5402041</v>
+      </c>
+      <c r="BE117" s="11">
+        <v>859458</v>
+      </c>
+      <c r="BF117" s="11">
+        <v>58</v>
+      </c>
+      <c r="BG117" s="12">
+        <v>279415.91379310342</v>
+      </c>
+      <c r="BH117" s="12">
+        <v>44454.724137931029</v>
+      </c>
+      <c r="BI117" s="13">
+        <v>5.0786917071940882</v>
+      </c>
       <c r="BJ117" s="11"/>
       <c r="BK117" s="11"/>
       <c r="BL117" s="11"/>
@@ -26206,27 +27382,27 @@
       </c>
       <c r="N118" s="8">
         <f t="shared" si="25"/>
-        <v>686780.9</v>
+        <v>790865.05714285723</v>
       </c>
       <c r="O118" s="8">
         <f t="shared" si="25"/>
-        <v>759364.5</v>
+        <v>886548.71428571432</v>
       </c>
       <c r="P118" s="8">
         <f>IFERROR(SUM(V118,AB118,AH118,AN118,AT118,AZ118,BF118,BL118,BR118,BX118,CD118,CJ118)," ")</f>
-        <v>147</v>
+        <v>199</v>
       </c>
       <c r="Q118" s="9">
         <f>IFERROR(SUM(T118,Z118,AF118,AL118,AR118,AX118,BD118,BJ118,BP118,BV118,CB118,CH118)/P118*3," ")</f>
-        <v>84095.62040816326</v>
+        <v>83458.121608040208</v>
       </c>
       <c r="R118" s="9">
         <f>IFERROR(SUM(U118,AA118,AG118,AM118,AS118,AY118,BE118,BK118,BQ118,BW118,CC118,CI118)/P118*3," ")</f>
-        <v>92983.408163265311</v>
+        <v>93555.391959799003</v>
       </c>
       <c r="S118" s="10">
         <f>IFERROR(AVERAGE(Y118,AE118,AK118,AQ118,AW118,BC118,BI118,BO118,BU118,CA118,CG118,CM118)," ")</f>
-        <v>14.942500638446596</v>
+        <v>14.989240452855627</v>
       </c>
       <c r="T118" s="11">
         <v>1050265</v>
@@ -26336,12 +27512,24 @@
       <c r="BC118" s="13">
         <v>14.82624530295611</v>
       </c>
-      <c r="BD118" s="11"/>
-      <c r="BE118" s="11"/>
-      <c r="BF118" s="11"/>
-      <c r="BG118" s="12"/>
-      <c r="BH118" s="12"/>
-      <c r="BI118" s="13"/>
+      <c r="BD118" s="11">
+        <v>1415370</v>
+      </c>
+      <c r="BE118" s="11">
+        <v>1649654</v>
+      </c>
+      <c r="BF118" s="11">
+        <v>52</v>
+      </c>
+      <c r="BG118" s="12">
+        <v>81655.961538461546</v>
+      </c>
+      <c r="BH118" s="12">
+        <v>95172.346153846156</v>
+      </c>
+      <c r="BI118" s="13">
+        <v>15.269679339309819</v>
+      </c>
       <c r="BJ118" s="11"/>
       <c r="BK118" s="11"/>
       <c r="BL118" s="11"/>
@@ -26399,11 +27587,11 @@
       <c r="M119" s="22"/>
       <c r="N119" s="14">
         <f>SUM(N116:N118)</f>
-        <v>5627717.5666666673</v>
+        <v>6502703.2000000002</v>
       </c>
       <c r="O119" s="14">
         <f>SUM(O116:O118)</f>
-        <v>1506635.6666666667</v>
+        <v>1761158.142857143</v>
       </c>
       <c r="P119" s="14"/>
       <c r="Q119" s="14"/>
@@ -26483,11 +27671,11 @@
       <c r="BC119" s="14"/>
       <c r="BD119" s="14">
         <f>SUM(BD116:BD118)</f>
-        <v>0</v>
+        <v>11752617</v>
       </c>
       <c r="BE119" s="14">
         <f>SUM(BE116:BE118)</f>
-        <v>0</v>
+        <v>3288293</v>
       </c>
       <c r="BF119" s="14"/>
       <c r="BG119" s="14"/>
@@ -26569,6 +27757,35 @@
   </sheetData>
   <autoFilter ref="A2:CM53" xr:uid="{B264AC42-3408-4CC4-A254-80BEFA0AA9F5}"/>
   <mergeCells count="45">
+    <mergeCell ref="CB114:CG114"/>
+    <mergeCell ref="CH114:CM114"/>
+    <mergeCell ref="N114:S114"/>
+    <mergeCell ref="AX114:BC114"/>
+    <mergeCell ref="BD114:BI114"/>
+    <mergeCell ref="BJ114:BO114"/>
+    <mergeCell ref="BP114:BU114"/>
+    <mergeCell ref="BV114:CA114"/>
+    <mergeCell ref="T114:Y114"/>
+    <mergeCell ref="Z114:AE114"/>
+    <mergeCell ref="AF114:AK114"/>
+    <mergeCell ref="AL114:AQ114"/>
+    <mergeCell ref="AR114:AW114"/>
+    <mergeCell ref="BP55:BU55"/>
+    <mergeCell ref="BV55:CA55"/>
+    <mergeCell ref="CB55:CG55"/>
+    <mergeCell ref="CH55:CM55"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="AL55:AQ55"/>
+    <mergeCell ref="AR55:AW55"/>
+    <mergeCell ref="AX55:BC55"/>
+    <mergeCell ref="BD55:BI55"/>
+    <mergeCell ref="BJ55:BO55"/>
+    <mergeCell ref="T1:Y1"/>
+    <mergeCell ref="Z1:AE1"/>
+    <mergeCell ref="AF1:AK1"/>
+    <mergeCell ref="T55:Y55"/>
+    <mergeCell ref="Z55:AE55"/>
+    <mergeCell ref="AF55:AK55"/>
     <mergeCell ref="B114:G114"/>
     <mergeCell ref="H114:M114"/>
     <mergeCell ref="CB1:CG1"/>
@@ -26585,35 +27802,6 @@
     <mergeCell ref="AL1:AQ1"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H1:M1"/>
-    <mergeCell ref="T1:Y1"/>
-    <mergeCell ref="Z1:AE1"/>
-    <mergeCell ref="AF1:AK1"/>
-    <mergeCell ref="T55:Y55"/>
-    <mergeCell ref="Z55:AE55"/>
-    <mergeCell ref="AF55:AK55"/>
-    <mergeCell ref="BP55:BU55"/>
-    <mergeCell ref="BV55:CA55"/>
-    <mergeCell ref="CB55:CG55"/>
-    <mergeCell ref="CH55:CM55"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="AL55:AQ55"/>
-    <mergeCell ref="AR55:AW55"/>
-    <mergeCell ref="AX55:BC55"/>
-    <mergeCell ref="BD55:BI55"/>
-    <mergeCell ref="BJ55:BO55"/>
-    <mergeCell ref="CB114:CG114"/>
-    <mergeCell ref="CH114:CM114"/>
-    <mergeCell ref="N114:S114"/>
-    <mergeCell ref="AX114:BC114"/>
-    <mergeCell ref="BD114:BI114"/>
-    <mergeCell ref="BJ114:BO114"/>
-    <mergeCell ref="BP114:BU114"/>
-    <mergeCell ref="BV114:CA114"/>
-    <mergeCell ref="T114:Y114"/>
-    <mergeCell ref="Z114:AE114"/>
-    <mergeCell ref="AF114:AK114"/>
-    <mergeCell ref="AL114:AQ114"/>
-    <mergeCell ref="AR114:AW114"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Kapabilite/Kapabilite 2026.xlsx
+++ b/Kapabilite/Kapabilite 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Kapabilite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06F9971-801B-4223-929F-4B916C483CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B66AE50-650E-4FA3-8C64-4FE6BC9633A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8FA9AADE-0AF1-42A7-AB4A-1A5F3041D90E}"/>
   </bookViews>
@@ -3292,27 +3292,27 @@
       </c>
       <c r="N3" s="8">
         <f t="shared" ref="N3:N25" si="0">IFERROR(AVERAGE(T3,Z3,AF3,AL3,AR3,AX3,BD3,BJ3,BP3,BV3,CB3,CH3)," ")</f>
-        <v>155700</v>
+        <v>152862.5</v>
       </c>
       <c r="O3" s="8">
         <f t="shared" ref="O3:O25" si="1">IFERROR(AVERAGE(U3,AA3,AG3,AM3,AS3,AY3,BE3,BK3,BQ3,BW3,CC3,CI3)," ")</f>
-        <v>55615.142857142855</v>
+        <v>54604.75</v>
       </c>
       <c r="P3" s="8">
         <f t="shared" ref="P3:P25" si="2">IFERROR(SUM(V3,AB3,AH3,AN3,AT3,AZ3,BF3,BL3,BR3,BX3,CD3,CJ3)," ")</f>
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="Q3" s="9">
         <f t="shared" ref="Q3:Q25" si="3">IFERROR(SUM(T3,Z3,AF3,AL3,AR3,AX3,BD3,BJ3,BP3,BV3,CB3,CH3)/P3*3," ")</f>
-        <v>16106.896551724138</v>
+        <v>15950.86956521739</v>
       </c>
       <c r="R3" s="9">
         <f t="shared" ref="R3:R25" si="4">IFERROR(SUM(U3,AA3,AG3,AM3,AS3,AY3,BE3,BK3,BQ3,BW3,CC3,CI3)/P3*3," ")</f>
-        <v>5753.2906403940888</v>
+        <v>5697.8869565217392</v>
       </c>
       <c r="S3" s="10">
         <f t="shared" ref="S3:S25" si="5">IFERROR(AVERAGE(Y3,AE3,AK3,AQ3,AW3,BC3,BI3,BO3,BU3,CA3,CG3,CM3)," ")</f>
-        <v>9.9354149325173999</v>
+        <v>9.9434880659527245</v>
       </c>
       <c r="T3" s="11">
         <v>24000</v>
@@ -3440,12 +3440,24 @@
       <c r="BI3" s="13">
         <v>10</v>
       </c>
-      <c r="BJ3" s="11"/>
-      <c r="BK3" s="11"/>
-      <c r="BL3" s="11"/>
-      <c r="BM3" s="12"/>
-      <c r="BN3" s="12"/>
-      <c r="BO3" s="13"/>
+      <c r="BJ3" s="11">
+        <v>133000</v>
+      </c>
+      <c r="BK3" s="11">
+        <v>47532</v>
+      </c>
+      <c r="BL3" s="11">
+        <v>27</v>
+      </c>
+      <c r="BM3" s="12">
+        <v>14777.777777777779</v>
+      </c>
+      <c r="BN3" s="12">
+        <v>5281.333333333333</v>
+      </c>
+      <c r="BO3" s="13">
+        <v>10</v>
+      </c>
       <c r="BP3" s="11"/>
       <c r="BQ3" s="11"/>
       <c r="BR3" s="11"/>
@@ -3511,27 +3523,27 @@
       </c>
       <c r="N4" s="8">
         <f t="shared" si="0"/>
-        <v>310950.42857142858</v>
+        <v>302963.625</v>
       </c>
       <c r="O4" s="8">
         <f t="shared" si="1"/>
-        <v>11935.142857142857</v>
+        <v>11755.75</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" si="2"/>
-        <v>351</v>
+        <v>388</v>
       </c>
       <c r="Q4" s="9">
         <f t="shared" si="3"/>
-        <v>18603.871794871797</v>
+        <v>18740.018041237112</v>
       </c>
       <c r="R4" s="9">
         <f t="shared" si="4"/>
-        <v>714.0683760683761</v>
+        <v>727.15979381443299</v>
       </c>
       <c r="S4" s="10">
         <f t="shared" si="5"/>
-        <v>2.6943107833788424</v>
+        <v>2.712755567850555</v>
       </c>
       <c r="T4" s="11">
         <v>328790</v>
@@ -3659,12 +3671,24 @@
       <c r="BI4" s="13">
         <v>2.65</v>
       </c>
-      <c r="BJ4" s="11"/>
-      <c r="BK4" s="11"/>
-      <c r="BL4" s="11"/>
-      <c r="BM4" s="12"/>
-      <c r="BN4" s="12"/>
-      <c r="BO4" s="13"/>
+      <c r="BJ4" s="11">
+        <v>247056</v>
+      </c>
+      <c r="BK4" s="11">
+        <v>10500</v>
+      </c>
+      <c r="BL4" s="11">
+        <v>37</v>
+      </c>
+      <c r="BM4" s="12">
+        <v>20031.56756756757</v>
+      </c>
+      <c r="BN4" s="12">
+        <v>851.35135135135147</v>
+      </c>
+      <c r="BO4" s="13">
+        <v>2.8418690591525442</v>
+      </c>
       <c r="BP4" s="11"/>
       <c r="BQ4" s="11"/>
       <c r="BR4" s="11"/>
@@ -3730,27 +3754,27 @@
       </c>
       <c r="N5" s="8">
         <f t="shared" si="0"/>
-        <v>334107.42857142858</v>
+        <v>321404</v>
       </c>
       <c r="O5" s="8">
         <f t="shared" si="1"/>
-        <v>12947.285714285714</v>
+        <v>12406.625</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="2"/>
-        <v>387</v>
+        <v>425</v>
       </c>
       <c r="Q5" s="9">
         <f t="shared" si="3"/>
-        <v>18129.860465116279</v>
+        <v>18149.872941176473</v>
       </c>
       <c r="R5" s="9">
         <f t="shared" si="4"/>
-        <v>702.56589147286832</v>
+        <v>700.6094117647059</v>
       </c>
       <c r="S5" s="10">
         <f t="shared" si="5"/>
-        <v>2.7073525698874557</v>
+        <v>2.7001834986515236</v>
       </c>
       <c r="T5" s="11">
         <v>373478</v>
@@ -3878,12 +3902,24 @@
       <c r="BI5" s="13">
         <v>2.65</v>
       </c>
-      <c r="BJ5" s="11"/>
-      <c r="BK5" s="11"/>
-      <c r="BL5" s="11"/>
-      <c r="BM5" s="12"/>
-      <c r="BN5" s="12"/>
-      <c r="BO5" s="13"/>
+      <c r="BJ5" s="11">
+        <v>232480</v>
+      </c>
+      <c r="BK5" s="11">
+        <v>8622</v>
+      </c>
+      <c r="BL5" s="11">
+        <v>38</v>
+      </c>
+      <c r="BM5" s="12">
+        <v>18353.684210526309</v>
+      </c>
+      <c r="BN5" s="12">
+        <v>680.68421052631584</v>
+      </c>
+      <c r="BO5" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BP5" s="11"/>
       <c r="BQ5" s="11"/>
       <c r="BR5" s="11"/>
@@ -3949,27 +3985,27 @@
       </c>
       <c r="N6" s="8">
         <f t="shared" si="0"/>
-        <v>235691</v>
+        <v>232148.625</v>
       </c>
       <c r="O6" s="8">
         <f t="shared" si="1"/>
-        <v>18132.428571428572</v>
+        <v>17335.25</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="2"/>
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="Q6" s="9">
         <f t="shared" si="3"/>
-        <v>13523.254098360656</v>
+        <v>13689.35380835381</v>
       </c>
       <c r="R6" s="9">
         <f t="shared" si="4"/>
-        <v>1040.3852459016393</v>
+        <v>1022.2260442260442</v>
       </c>
       <c r="S6" s="10">
         <f t="shared" si="5"/>
-        <v>3.7991418251676627</v>
+        <v>3.7336177874419785</v>
       </c>
       <c r="T6" s="11">
         <v>274253</v>
@@ -4097,12 +4133,24 @@
       <c r="BI6" s="13">
         <v>3.7630627936186332</v>
       </c>
-      <c r="BJ6" s="11"/>
-      <c r="BK6" s="11"/>
-      <c r="BL6" s="11"/>
-      <c r="BM6" s="12"/>
-      <c r="BN6" s="12"/>
-      <c r="BO6" s="13"/>
+      <c r="BJ6" s="11">
+        <v>207352</v>
+      </c>
+      <c r="BK6" s="11">
+        <v>11755</v>
+      </c>
+      <c r="BL6" s="11">
+        <v>41</v>
+      </c>
+      <c r="BM6" s="12">
+        <v>15172.09756097561</v>
+      </c>
+      <c r="BN6" s="12">
+        <v>860.12195121951208</v>
+      </c>
+      <c r="BO6" s="13">
+        <v>3.2749495233621899</v>
+      </c>
       <c r="BP6" s="11"/>
       <c r="BQ6" s="11"/>
       <c r="BR6" s="11"/>
@@ -4168,27 +4216,27 @@
       </c>
       <c r="N7" s="8">
         <f t="shared" si="0"/>
-        <v>313149.28571428574</v>
+        <v>303456.75</v>
       </c>
       <c r="O7" s="8">
         <f t="shared" si="1"/>
-        <v>56645</v>
+        <v>51669.875</v>
       </c>
       <c r="P7" s="8">
         <f t="shared" si="2"/>
-        <v>392</v>
+        <v>438</v>
       </c>
       <c r="Q7" s="9">
         <f t="shared" si="3"/>
-        <v>16775.854591836734</v>
+        <v>16627.767123287671</v>
       </c>
       <c r="R7" s="9">
         <f t="shared" si="4"/>
-        <v>3034.5535714285716</v>
+        <v>2831.2260273972602</v>
       </c>
       <c r="S7" s="10">
         <f t="shared" si="5"/>
-        <v>5.6074104846583284</v>
+        <v>5.3596046935575608</v>
       </c>
       <c r="T7" s="11">
         <v>355184</v>
@@ -4316,12 +4364,24 @@
       <c r="BI7" s="13">
         <v>6.0436359375301363</v>
       </c>
-      <c r="BJ7" s="11"/>
-      <c r="BK7" s="11"/>
-      <c r="BL7" s="11"/>
-      <c r="BM7" s="12"/>
-      <c r="BN7" s="12"/>
-      <c r="BO7" s="13"/>
+      <c r="BJ7" s="11">
+        <v>235609</v>
+      </c>
+      <c r="BK7" s="11">
+        <v>16844</v>
+      </c>
+      <c r="BL7" s="11">
+        <v>46</v>
+      </c>
+      <c r="BM7" s="12">
+        <v>15365.80434782609</v>
+      </c>
+      <c r="BN7" s="12">
+        <v>1098.521739130435</v>
+      </c>
+      <c r="BO7" s="13">
+        <v>3.624964155852187</v>
+      </c>
       <c r="BP7" s="11"/>
       <c r="BQ7" s="11"/>
       <c r="BR7" s="11"/>
@@ -4387,27 +4447,27 @@
       </c>
       <c r="N8" s="8">
         <f t="shared" si="0"/>
-        <v>296529.14285714284</v>
+        <v>288238.75</v>
       </c>
       <c r="O8" s="8">
         <f t="shared" si="1"/>
-        <v>37776.285714285717</v>
+        <v>35643.875</v>
       </c>
       <c r="P8" s="8">
         <f t="shared" si="2"/>
-        <v>403</v>
+        <v>445</v>
       </c>
       <c r="Q8" s="9">
         <f t="shared" si="3"/>
-        <v>15451.890818858559</v>
+        <v>15545.460674157304</v>
       </c>
       <c r="R8" s="9">
         <f t="shared" si="4"/>
-        <v>1968.4913151364763</v>
+        <v>1922.3662921348314</v>
       </c>
       <c r="S8" s="10">
         <f t="shared" si="5"/>
-        <v>4.8700585650717398</v>
+        <v>4.7768341272741015</v>
       </c>
       <c r="T8" s="11">
         <v>330292</v>
@@ -4535,12 +4595,24 @@
       <c r="BI8" s="13">
         <v>4.6572134669804086</v>
       </c>
-      <c r="BJ8" s="11"/>
-      <c r="BK8" s="11"/>
-      <c r="BL8" s="11"/>
-      <c r="BM8" s="12"/>
-      <c r="BN8" s="12"/>
-      <c r="BO8" s="13"/>
+      <c r="BJ8" s="11">
+        <v>230206</v>
+      </c>
+      <c r="BK8" s="11">
+        <v>20717</v>
+      </c>
+      <c r="BL8" s="11">
+        <v>42</v>
+      </c>
+      <c r="BM8" s="12">
+        <v>16443.285714285721</v>
+      </c>
+      <c r="BN8" s="12">
+        <v>1479.785714285714</v>
+      </c>
+      <c r="BO8" s="13">
+        <v>4.1242630626906278</v>
+      </c>
       <c r="BP8" s="11"/>
       <c r="BQ8" s="11"/>
       <c r="BR8" s="11"/>
@@ -4606,27 +4678,27 @@
       </c>
       <c r="N9" s="8">
         <f t="shared" si="0"/>
-        <v>282256.71428571426</v>
+        <v>273524.875</v>
       </c>
       <c r="O9" s="8">
         <f t="shared" si="1"/>
-        <v>9990.8571428571431</v>
+        <v>9514.125</v>
       </c>
       <c r="P9" s="8">
         <f t="shared" si="2"/>
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="Q9" s="9">
         <f t="shared" si="3"/>
-        <v>17693.70447761194</v>
+        <v>18034.607142857145</v>
       </c>
       <c r="R9" s="9">
         <f t="shared" si="4"/>
-        <v>626.29253731343283</v>
+        <v>627.30494505494505</v>
       </c>
       <c r="S9" s="10">
         <f t="shared" si="5"/>
-        <v>2.5784585159813185</v>
+        <v>2.5503337476803005</v>
       </c>
       <c r="T9" s="11">
         <v>341336</v>
@@ -4754,12 +4826,24 @@
       <c r="BI9" s="13">
         <v>2.511993943701075</v>
       </c>
-      <c r="BJ9" s="11"/>
-      <c r="BK9" s="11"/>
-      <c r="BL9" s="11"/>
-      <c r="BM9" s="12"/>
-      <c r="BN9" s="12"/>
-      <c r="BO9" s="13"/>
+      <c r="BJ9" s="11">
+        <v>212402</v>
+      </c>
+      <c r="BK9" s="11">
+        <v>6177</v>
+      </c>
+      <c r="BL9" s="11">
+        <v>29</v>
+      </c>
+      <c r="BM9" s="12">
+        <v>21972.62068965517</v>
+      </c>
+      <c r="BN9" s="12">
+        <v>639</v>
+      </c>
+      <c r="BO9" s="13">
+        <v>2.3534603695731731</v>
+      </c>
       <c r="BP9" s="11"/>
       <c r="BQ9" s="11"/>
       <c r="BR9" s="11"/>
@@ -4825,27 +4909,27 @@
       </c>
       <c r="N10" s="8">
         <f t="shared" si="0"/>
-        <v>250575</v>
+        <v>241338</v>
       </c>
       <c r="O10" s="8">
         <f t="shared" si="1"/>
-        <v>8613.2857142857138</v>
+        <v>8227.125</v>
       </c>
       <c r="P10" s="8">
         <f t="shared" si="2"/>
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="Q10" s="9">
         <f t="shared" si="3"/>
-        <v>19065.489130434784</v>
+        <v>18744.699029126212</v>
       </c>
       <c r="R10" s="9">
         <f t="shared" si="4"/>
-        <v>655.35869565217388</v>
+        <v>639</v>
       </c>
       <c r="S10" s="10">
         <f t="shared" si="5"/>
-        <v>2.5766854551032119</v>
+        <v>2.5664278675229109</v>
       </c>
       <c r="T10" s="11">
         <v>350996</v>
@@ -4973,12 +5057,24 @@
       <c r="BI10" s="13">
         <v>2.4545039661742458</v>
       </c>
-      <c r="BJ10" s="11"/>
-      <c r="BK10" s="11"/>
-      <c r="BL10" s="11"/>
-      <c r="BM10" s="12"/>
-      <c r="BN10" s="12"/>
-      <c r="BO10" s="13"/>
+      <c r="BJ10" s="11">
+        <v>176679</v>
+      </c>
+      <c r="BK10" s="11">
+        <v>5524</v>
+      </c>
+      <c r="BL10" s="11">
+        <v>33</v>
+      </c>
+      <c r="BM10" s="12">
+        <v>16061.72727272727</v>
+      </c>
+      <c r="BN10" s="12">
+        <v>502.18181818181819</v>
+      </c>
+      <c r="BO10" s="13">
+        <v>2.4946247544608049</v>
+      </c>
       <c r="BP10" s="11"/>
       <c r="BQ10" s="11"/>
       <c r="BR10" s="11"/>
@@ -5044,27 +5140,27 @@
       </c>
       <c r="N11" s="8">
         <f t="shared" si="0"/>
-        <v>252245.57142857142</v>
+        <v>250178.75</v>
       </c>
       <c r="O11" s="8">
         <f t="shared" si="1"/>
-        <v>8991.4285714285706</v>
+        <v>9127.125</v>
       </c>
       <c r="P11" s="8">
         <f t="shared" si="2"/>
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="Q11" s="9">
         <f t="shared" si="3"/>
-        <v>17775.69463087248</v>
+        <v>17764.171597633136</v>
       </c>
       <c r="R11" s="9">
         <f t="shared" si="4"/>
-        <v>633.62416107382546</v>
+        <v>648.07988165680479</v>
       </c>
       <c r="S11" s="10">
         <f t="shared" si="5"/>
-        <v>2.6471432546095026</v>
+        <v>2.6800548532145894</v>
       </c>
       <c r="T11" s="11">
         <v>395887</v>
@@ -5192,12 +5288,24 @@
       <c r="BI11" s="13">
         <v>2.917155863202392</v>
       </c>
-      <c r="BJ11" s="11"/>
-      <c r="BK11" s="11"/>
-      <c r="BL11" s="11"/>
-      <c r="BM11" s="12"/>
-      <c r="BN11" s="12"/>
-      <c r="BO11" s="13"/>
+      <c r="BJ11" s="11">
+        <v>235711</v>
+      </c>
+      <c r="BK11" s="11">
+        <v>10077</v>
+      </c>
+      <c r="BL11" s="11">
+        <v>40</v>
+      </c>
+      <c r="BM11" s="12">
+        <v>17678.325000000001</v>
+      </c>
+      <c r="BN11" s="12">
+        <v>755.77500000000009</v>
+      </c>
+      <c r="BO11" s="13">
+        <v>2.9104360434501961</v>
+      </c>
       <c r="BP11" s="11"/>
       <c r="BQ11" s="11"/>
       <c r="BR11" s="11"/>
@@ -5263,27 +5371,27 @@
       </c>
       <c r="N12" s="8">
         <f t="shared" si="0"/>
-        <v>259591.14285714287</v>
+        <v>249389</v>
       </c>
       <c r="O12" s="8">
         <f t="shared" si="1"/>
-        <v>18726.571428571428</v>
+        <v>17976.5</v>
       </c>
       <c r="P12" s="8">
         <f t="shared" si="2"/>
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="Q12" s="9">
         <f t="shared" si="3"/>
-        <v>17991.465346534653</v>
+        <v>17813.5</v>
       </c>
       <c r="R12" s="9">
         <f t="shared" si="4"/>
-        <v>1297.8811881188119</v>
+        <v>1284.0357142857142</v>
       </c>
       <c r="S12" s="10">
         <f t="shared" si="5"/>
-        <v>3.6664007873182465</v>
+        <v>3.665874533972719</v>
       </c>
       <c r="T12" s="11">
         <v>290616</v>
@@ -5411,12 +5519,24 @@
       <c r="BI12" s="13">
         <v>3.395193617189376</v>
       </c>
-      <c r="BJ12" s="11"/>
-      <c r="BK12" s="11"/>
-      <c r="BL12" s="11"/>
-      <c r="BM12" s="12"/>
-      <c r="BN12" s="12"/>
-      <c r="BO12" s="13"/>
+      <c r="BJ12" s="11">
+        <v>177974</v>
+      </c>
+      <c r="BK12" s="11">
+        <v>12726</v>
+      </c>
+      <c r="BL12" s="11">
+        <v>33</v>
+      </c>
+      <c r="BM12" s="12">
+        <v>16179.45454545454</v>
+      </c>
+      <c r="BN12" s="12">
+        <v>1156.909090909091</v>
+      </c>
+      <c r="BO12" s="13">
+        <v>3.6621907605540249</v>
+      </c>
       <c r="BP12" s="11"/>
       <c r="BQ12" s="11"/>
       <c r="BR12" s="11"/>
@@ -5482,27 +5602,27 @@
       </c>
       <c r="N13" s="8">
         <f t="shared" si="0"/>
-        <v>279476.85714285716</v>
+        <v>259294</v>
       </c>
       <c r="O13" s="8">
         <f t="shared" si="1"/>
-        <v>13076</v>
+        <v>12580</v>
       </c>
       <c r="P13" s="8">
         <f t="shared" si="2"/>
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="Q13" s="9">
         <f t="shared" si="3"/>
-        <v>16532.4338028169</v>
+        <v>16594.815999999999</v>
       </c>
       <c r="R13" s="9">
         <f t="shared" si="4"/>
-        <v>773.50985915492959</v>
+        <v>805.12</v>
       </c>
       <c r="S13" s="10">
         <f t="shared" si="5"/>
-        <v>3.0674327207048462</v>
+        <v>3.2031095142154542</v>
       </c>
       <c r="T13" s="11">
         <v>214482</v>
@@ -5630,12 +5750,24 @@
       <c r="BI13" s="13">
         <v>2.6658554260263121</v>
       </c>
-      <c r="BJ13" s="11"/>
-      <c r="BK13" s="11"/>
-      <c r="BL13" s="11"/>
-      <c r="BM13" s="12"/>
-      <c r="BN13" s="12"/>
-      <c r="BO13" s="13"/>
+      <c r="BJ13" s="11">
+        <v>118014</v>
+      </c>
+      <c r="BK13" s="11">
+        <v>9108</v>
+      </c>
+      <c r="BL13" s="11">
+        <v>20</v>
+      </c>
+      <c r="BM13" s="12">
+        <v>17702.099999999999</v>
+      </c>
+      <c r="BN13" s="12">
+        <v>1366.2</v>
+      </c>
+      <c r="BO13" s="13">
+        <v>4.1528470687897112</v>
+      </c>
       <c r="BP13" s="11"/>
       <c r="BQ13" s="11"/>
       <c r="BR13" s="11"/>
@@ -5701,27 +5833,27 @@
       </c>
       <c r="N14" s="8">
         <f t="shared" si="0"/>
-        <v>295568.42857142858</v>
+        <v>285904.5</v>
       </c>
       <c r="O14" s="8">
         <f t="shared" si="1"/>
-        <v>169712</v>
+        <v>162830.375</v>
       </c>
       <c r="P14" s="8">
         <f t="shared" si="2"/>
-        <v>431</v>
+        <v>482</v>
       </c>
       <c r="Q14" s="9">
         <f t="shared" si="3"/>
-        <v>14401.245939675173</v>
+        <v>14235.908713692945</v>
       </c>
       <c r="R14" s="9">
         <f t="shared" si="4"/>
-        <v>8269.0301624129934</v>
+        <v>8107.7365145228214</v>
       </c>
       <c r="S14" s="10">
         <f t="shared" si="5"/>
-        <v>10.262607136040373</v>
+        <v>10.201828150852705</v>
       </c>
       <c r="T14" s="11">
         <v>358878</v>
@@ -5849,12 +5981,24 @@
       <c r="BI14" s="13">
         <v>11.15477567355515</v>
       </c>
-      <c r="BJ14" s="11"/>
-      <c r="BK14" s="11"/>
-      <c r="BL14" s="11"/>
-      <c r="BM14" s="12"/>
-      <c r="BN14" s="12"/>
-      <c r="BO14" s="13"/>
+      <c r="BJ14" s="11">
+        <v>218257</v>
+      </c>
+      <c r="BK14" s="11">
+        <v>114659</v>
+      </c>
+      <c r="BL14" s="11">
+        <v>51</v>
+      </c>
+      <c r="BM14" s="12">
+        <v>12838.64705882353</v>
+      </c>
+      <c r="BN14" s="12">
+        <v>6744.6470588235288</v>
+      </c>
+      <c r="BO14" s="13">
+        <v>9.7763752545390368</v>
+      </c>
       <c r="BP14" s="11"/>
       <c r="BQ14" s="11"/>
       <c r="BR14" s="11"/>
@@ -5920,27 +6064,27 @@
       </c>
       <c r="N15" s="8">
         <f t="shared" si="0"/>
-        <v>148153.71428571429</v>
+        <v>136911.625</v>
       </c>
       <c r="O15" s="8">
         <f t="shared" si="1"/>
-        <v>62379.714285714283</v>
+        <v>58135.75</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" si="2"/>
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="Q15" s="9">
         <f t="shared" si="3"/>
-        <v>9456.6200607902738</v>
+        <v>9361.4786324786328</v>
       </c>
       <c r="R15" s="9">
         <f t="shared" si="4"/>
-        <v>3981.6838905775076</v>
+        <v>3975.0940170940171</v>
       </c>
       <c r="S15" s="10">
         <f t="shared" si="5"/>
-        <v>10.239028797695918</v>
+        <v>10.332080895055888</v>
       </c>
       <c r="T15" s="11">
         <v>184929</v>
@@ -6068,12 +6212,24 @@
       <c r="BI15" s="13">
         <v>9.9170972866139273</v>
       </c>
-      <c r="BJ15" s="11"/>
-      <c r="BK15" s="11"/>
-      <c r="BL15" s="11"/>
-      <c r="BM15" s="12"/>
-      <c r="BN15" s="12"/>
-      <c r="BO15" s="13"/>
+      <c r="BJ15" s="11">
+        <v>58217</v>
+      </c>
+      <c r="BK15" s="11">
+        <v>28428</v>
+      </c>
+      <c r="BL15" s="11">
+        <v>22</v>
+      </c>
+      <c r="BM15" s="12">
+        <v>7938.681818181818</v>
+      </c>
+      <c r="BN15" s="12">
+        <v>3876.545454545455</v>
+      </c>
+      <c r="BO15" s="13">
+        <v>10.98344557657569</v>
+      </c>
       <c r="BP15" s="11"/>
       <c r="BQ15" s="11"/>
       <c r="BR15" s="11"/>
@@ -6139,27 +6295,27 @@
       </c>
       <c r="N16" s="8">
         <f t="shared" si="0"/>
-        <v>107260.28571428571</v>
+        <v>106686.5</v>
       </c>
       <c r="O16" s="8">
         <f t="shared" si="1"/>
-        <v>175604.71428571429</v>
+        <v>174262.25</v>
       </c>
       <c r="P16" s="8">
         <f t="shared" si="2"/>
-        <v>395</v>
+        <v>443</v>
       </c>
       <c r="Q16" s="9">
         <f t="shared" si="3"/>
-        <v>5702.4455696202531</v>
+        <v>5779.8555304740403</v>
       </c>
       <c r="R16" s="9">
         <f t="shared" si="4"/>
-        <v>9335.9468354430373</v>
+        <v>9440.8442437923241</v>
       </c>
       <c r="S16" s="10">
         <f t="shared" si="5"/>
-        <v>20.448529338407564</v>
+        <v>20.452400203951587</v>
       </c>
       <c r="T16" s="11">
         <v>114329</v>
@@ -6287,12 +6443,24 @@
       <c r="BI16" s="13">
         <v>20.01275615864062</v>
       </c>
-      <c r="BJ16" s="11"/>
-      <c r="BK16" s="11"/>
-      <c r="BL16" s="11"/>
-      <c r="BM16" s="12"/>
-      <c r="BN16" s="12"/>
-      <c r="BO16" s="13"/>
+      <c r="BJ16" s="11">
+        <v>102670</v>
+      </c>
+      <c r="BK16" s="11">
+        <v>164865</v>
+      </c>
+      <c r="BL16" s="11">
+        <v>48</v>
+      </c>
+      <c r="BM16" s="12">
+        <v>6416.875</v>
+      </c>
+      <c r="BN16" s="12">
+        <v>10304.0625</v>
+      </c>
+      <c r="BO16" s="13">
+        <v>20.479496262759749</v>
+      </c>
       <c r="BP16" s="11"/>
       <c r="BQ16" s="11"/>
       <c r="BR16" s="11"/>
@@ -6358,27 +6526,27 @@
       </c>
       <c r="N17" s="8">
         <f t="shared" si="0"/>
-        <v>301763.71428571426</v>
+        <v>277811.25</v>
       </c>
       <c r="O17" s="8">
         <f t="shared" si="1"/>
-        <v>4550.2857142857147</v>
+        <v>4173.625</v>
       </c>
       <c r="P17" s="8">
         <f t="shared" si="2"/>
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="Q17" s="9">
         <f t="shared" si="3"/>
-        <v>20442.058064516128</v>
+        <v>20204.454545454544</v>
       </c>
       <c r="R17" s="9">
         <f t="shared" si="4"/>
-        <v>308.24516129032259</v>
+        <v>303.5363636363636</v>
       </c>
       <c r="S17" s="10">
         <f t="shared" si="5"/>
-        <v>1.7237896897128884</v>
+        <v>1.7155401236004568</v>
       </c>
       <c r="T17" s="11">
         <v>317353</v>
@@ -6506,12 +6674,24 @@
       <c r="BI17" s="13">
         <v>1.638414109200903</v>
       </c>
-      <c r="BJ17" s="11"/>
-      <c r="BK17" s="11"/>
-      <c r="BL17" s="11"/>
-      <c r="BM17" s="12"/>
-      <c r="BN17" s="12"/>
-      <c r="BO17" s="13"/>
+      <c r="BJ17" s="11">
+        <v>110144</v>
+      </c>
+      <c r="BK17" s="11">
+        <v>1537</v>
+      </c>
+      <c r="BL17" s="11">
+        <v>20</v>
+      </c>
+      <c r="BM17" s="12">
+        <v>16521.599999999999</v>
+      </c>
+      <c r="BN17" s="12">
+        <v>230.55</v>
+      </c>
+      <c r="BO17" s="13">
+        <v>1.657793160813436</v>
+      </c>
       <c r="BP17" s="11"/>
       <c r="BQ17" s="11"/>
       <c r="BR17" s="11"/>
@@ -6577,27 +6757,27 @@
       </c>
       <c r="N18" s="8">
         <f t="shared" si="0"/>
-        <v>272533.85714285716</v>
+        <v>260824.625</v>
       </c>
       <c r="O18" s="8">
         <f t="shared" si="1"/>
-        <v>9253.5714285714294</v>
+        <v>8926</v>
       </c>
       <c r="P18" s="8">
         <f t="shared" si="2"/>
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="Q18" s="9">
         <f t="shared" si="3"/>
-        <v>19205.406040268455</v>
+        <v>19260.895384615382</v>
       </c>
       <c r="R18" s="9">
         <f t="shared" si="4"/>
-        <v>652.09731543624162</v>
+        <v>659.15076923076924</v>
       </c>
       <c r="S18" s="10">
         <f t="shared" si="5"/>
-        <v>2.5413787398104302</v>
+        <v>2.5549563973341263</v>
       </c>
       <c r="T18" s="11">
         <v>208128</v>
@@ -6725,12 +6905,24 @@
       <c r="BI18" s="13">
         <v>2.6825638182642542</v>
       </c>
-      <c r="BJ18" s="11"/>
-      <c r="BK18" s="11"/>
-      <c r="BL18" s="11"/>
-      <c r="BM18" s="12"/>
-      <c r="BN18" s="12"/>
-      <c r="BO18" s="13"/>
+      <c r="BJ18" s="11">
+        <v>178860</v>
+      </c>
+      <c r="BK18" s="11">
+        <v>6633</v>
+      </c>
+      <c r="BL18" s="11">
+        <v>27</v>
+      </c>
+      <c r="BM18" s="12">
+        <v>19873.333333333328</v>
+      </c>
+      <c r="BN18" s="12">
+        <v>737</v>
+      </c>
+      <c r="BO18" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BP18" s="11"/>
       <c r="BQ18" s="11"/>
       <c r="BR18" s="11"/>
@@ -6796,27 +6988,27 @@
       </c>
       <c r="N19" s="8">
         <f t="shared" si="0"/>
-        <v>88643.402857142864</v>
+        <v>83986.102500000008</v>
       </c>
       <c r="O19" s="8">
         <f t="shared" si="1"/>
-        <v>285159.28571428574</v>
+        <v>269384.125</v>
       </c>
       <c r="P19" s="8">
         <f t="shared" si="2"/>
-        <v>397</v>
+        <v>443</v>
       </c>
       <c r="Q19" s="9">
         <f t="shared" si="3"/>
-        <v>4688.945743073049</v>
+        <v>4550.0371557562084</v>
       </c>
       <c r="R19" s="9">
         <f t="shared" si="4"/>
-        <v>15083.992443324936</v>
+        <v>14594.173814898419</v>
       </c>
       <c r="S19" s="10">
         <f t="shared" si="5"/>
-        <v>27.644456218910385</v>
+        <v>27.554903221521062</v>
       </c>
       <c r="T19" s="11">
         <v>82762</v>
@@ -6944,12 +7136,24 @@
       <c r="BI19" s="13">
         <v>27.826586856448039</v>
       </c>
-      <c r="BJ19" s="11"/>
-      <c r="BK19" s="11"/>
-      <c r="BL19" s="11"/>
-      <c r="BM19" s="12"/>
-      <c r="BN19" s="12"/>
-      <c r="BO19" s="13"/>
+      <c r="BJ19" s="11">
+        <v>51385</v>
+      </c>
+      <c r="BK19" s="11">
+        <v>158958</v>
+      </c>
+      <c r="BL19" s="11">
+        <v>46</v>
+      </c>
+      <c r="BM19" s="12">
+        <v>3351.195652173913</v>
+      </c>
+      <c r="BN19" s="12">
+        <v>10366.82608695652</v>
+      </c>
+      <c r="BO19" s="13">
+        <v>26.928032239795812</v>
+      </c>
       <c r="BP19" s="11"/>
       <c r="BQ19" s="11"/>
       <c r="BR19" s="11"/>
@@ -7015,27 +7219,27 @@
       </c>
       <c r="N20" s="8">
         <f t="shared" si="0"/>
-        <v>129092.57142857143</v>
+        <v>123496.375</v>
       </c>
       <c r="O20" s="8">
         <f t="shared" si="1"/>
-        <v>16543.285714285714</v>
+        <v>15893</v>
       </c>
       <c r="P20" s="8">
         <f t="shared" si="2"/>
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="Q20" s="9">
         <f t="shared" si="3"/>
-        <v>11202.247933884299</v>
+        <v>11142.530075187969</v>
       </c>
       <c r="R20" s="9">
         <f t="shared" si="4"/>
-        <v>1435.5743801652893</v>
+        <v>1433.9548872180451</v>
       </c>
       <c r="S20" s="10">
         <f t="shared" si="5"/>
-        <v>5.6651271177596243</v>
+        <v>5.6786888676282894</v>
       </c>
       <c r="T20" s="11">
         <v>173630</v>
@@ -7163,12 +7367,24 @@
       <c r="BI20" s="13">
         <v>5.4202575823701258</v>
       </c>
-      <c r="BJ20" s="11"/>
-      <c r="BK20" s="11"/>
-      <c r="BL20" s="11"/>
-      <c r="BM20" s="12"/>
-      <c r="BN20" s="12"/>
-      <c r="BO20" s="13"/>
+      <c r="BJ20" s="11">
+        <v>84323</v>
+      </c>
+      <c r="BK20" s="11">
+        <v>11341</v>
+      </c>
+      <c r="BL20" s="11">
+        <v>24</v>
+      </c>
+      <c r="BM20" s="12">
+        <v>10540.375</v>
+      </c>
+      <c r="BN20" s="12">
+        <v>1417.625</v>
+      </c>
+      <c r="BO20" s="13">
+        <v>5.7736211167089424</v>
+      </c>
       <c r="BP20" s="11"/>
       <c r="BQ20" s="11"/>
       <c r="BR20" s="11"/>
@@ -7234,27 +7450,27 @@
       </c>
       <c r="N21" s="8">
         <f t="shared" si="0"/>
-        <v>451408.28571428574</v>
+        <v>448765.5</v>
       </c>
       <c r="O21" s="8">
         <f t="shared" si="1"/>
-        <v>126742.57142857143</v>
+        <v>123958.125</v>
       </c>
       <c r="P21" s="8">
         <f t="shared" si="2"/>
-        <v>457</v>
+        <v>518</v>
       </c>
       <c r="Q21" s="9">
         <f t="shared" si="3"/>
-        <v>20743.050328227571</v>
+        <v>20792.223938223939</v>
       </c>
       <c r="R21" s="9">
         <f t="shared" si="4"/>
-        <v>5824.0568927789936</v>
+        <v>5743.233590733591</v>
       </c>
       <c r="S21" s="10">
         <f t="shared" si="5"/>
-        <v>7.1194746076906688</v>
+        <v>7.0767808981156684</v>
       </c>
       <c r="T21" s="11">
         <v>514374</v>
@@ -7382,12 +7598,24 @@
       <c r="BI21" s="13">
         <v>7.3459605472804954</v>
       </c>
-      <c r="BJ21" s="11"/>
-      <c r="BK21" s="11"/>
-      <c r="BL21" s="11"/>
-      <c r="BM21" s="12"/>
-      <c r="BN21" s="12"/>
-      <c r="BO21" s="13"/>
+      <c r="BJ21" s="11">
+        <v>430266</v>
+      </c>
+      <c r="BK21" s="11">
+        <v>104467</v>
+      </c>
+      <c r="BL21" s="11">
+        <v>61</v>
+      </c>
+      <c r="BM21" s="12">
+        <v>21160.62295081967</v>
+      </c>
+      <c r="BN21" s="12">
+        <v>5137.7213114754104</v>
+      </c>
+      <c r="BO21" s="13">
+        <v>6.7779249310906664</v>
+      </c>
       <c r="BP21" s="11"/>
       <c r="BQ21" s="11"/>
       <c r="BR21" s="11"/>
@@ -7453,27 +7681,27 @@
       </c>
       <c r="N22" s="8">
         <f t="shared" si="0"/>
-        <v>463890.85714285716</v>
+        <v>442402.5</v>
       </c>
       <c r="O22" s="8">
         <f t="shared" si="1"/>
-        <v>115191.85714285714</v>
+        <v>111660.75</v>
       </c>
       <c r="P22" s="8">
         <f t="shared" si="2"/>
-        <v>466</v>
+        <v>522</v>
       </c>
       <c r="Q22" s="9">
         <f t="shared" si="3"/>
-        <v>20904.952789699571</v>
+        <v>20340.344827586207</v>
       </c>
       <c r="R22" s="9">
         <f t="shared" si="4"/>
-        <v>5191.0493562231759</v>
+        <v>5133.8275862068967</v>
       </c>
       <c r="S22" s="10">
         <f t="shared" si="5"/>
-        <v>6.6382495080633186</v>
+        <v>6.6193053526414776</v>
       </c>
       <c r="T22" s="11">
         <v>555592</v>
@@ -7601,12 +7829,24 @@
       <c r="BI22" s="13">
         <v>6.756725376509376</v>
       </c>
-      <c r="BJ22" s="11"/>
-      <c r="BK22" s="11"/>
-      <c r="BL22" s="11"/>
-      <c r="BM22" s="12"/>
-      <c r="BN22" s="12"/>
-      <c r="BO22" s="13"/>
+      <c r="BJ22" s="11">
+        <v>291984</v>
+      </c>
+      <c r="BK22" s="11">
+        <v>86943</v>
+      </c>
+      <c r="BL22" s="11">
+        <v>56</v>
+      </c>
+      <c r="BM22" s="12">
+        <v>15642</v>
+      </c>
+      <c r="BN22" s="12">
+        <v>4657.6607142857138</v>
+      </c>
+      <c r="BO22" s="13">
+        <v>6.4866962646885931</v>
+      </c>
       <c r="BP22" s="11"/>
       <c r="BQ22" s="11"/>
       <c r="BR22" s="11"/>
@@ -7672,27 +7912,27 @@
       </c>
       <c r="N23" s="8">
         <f t="shared" si="0"/>
-        <v>317798.14285714284</v>
+        <v>313965.875</v>
       </c>
       <c r="O23" s="8">
         <f t="shared" si="1"/>
-        <v>11843.142857142857</v>
+        <v>11693.75</v>
       </c>
       <c r="P23" s="8">
         <f t="shared" si="2"/>
-        <v>346</v>
+        <v>394</v>
       </c>
       <c r="Q23" s="9">
         <f t="shared" si="3"/>
-        <v>19288.326589595374</v>
+        <v>19124.824873096448</v>
       </c>
       <c r="R23" s="9">
         <f t="shared" si="4"/>
-        <v>718.80346820809245</v>
+        <v>712.30964467005083</v>
       </c>
       <c r="S23" s="10">
         <f t="shared" si="5"/>
-        <v>2.6559657685575364</v>
+        <v>2.6552200474878442</v>
       </c>
       <c r="T23" s="11">
         <v>295520</v>
@@ -7820,12 +8060,24 @@
       <c r="BI23" s="13">
         <v>2.65</v>
       </c>
-      <c r="BJ23" s="11"/>
-      <c r="BK23" s="11"/>
-      <c r="BL23" s="11"/>
-      <c r="BM23" s="12"/>
-      <c r="BN23" s="12"/>
-      <c r="BO23" s="13"/>
+      <c r="BJ23" s="11">
+        <v>287140</v>
+      </c>
+      <c r="BK23" s="11">
+        <v>10648</v>
+      </c>
+      <c r="BL23" s="11">
+        <v>48</v>
+      </c>
+      <c r="BM23" s="12">
+        <v>17946.25</v>
+      </c>
+      <c r="BN23" s="12">
+        <v>665.5</v>
+      </c>
+      <c r="BO23" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BP23" s="11"/>
       <c r="BQ23" s="11"/>
       <c r="BR23" s="11"/>
@@ -7891,27 +8143,27 @@
       </c>
       <c r="N24" s="8">
         <f t="shared" si="0"/>
-        <v>237242.57142857142</v>
+        <v>226951.5</v>
       </c>
       <c r="O24" s="8">
         <f t="shared" si="1"/>
-        <v>3696.7142857142858</v>
+        <v>3553.25</v>
       </c>
       <c r="P24" s="8">
         <f t="shared" si="2"/>
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="Q24" s="9">
         <f t="shared" si="3"/>
-        <v>20502.444444444445</v>
+        <v>20631.954545454544</v>
       </c>
       <c r="R24" s="9">
         <f t="shared" si="4"/>
-        <v>319.46913580246911</v>
+        <v>323.02272727272725</v>
       </c>
       <c r="S24" s="10">
         <f t="shared" si="5"/>
-        <v>1.7527465452190039</v>
+        <v>1.7594304177339879</v>
       </c>
       <c r="T24" s="11">
         <v>328339</v>
@@ -8039,12 +8291,24 @@
       <c r="BI24" s="13">
         <v>1.654876497829568</v>
       </c>
-      <c r="BJ24" s="11"/>
-      <c r="BK24" s="11"/>
-      <c r="BL24" s="11"/>
-      <c r="BM24" s="12"/>
-      <c r="BN24" s="12"/>
-      <c r="BO24" s="13"/>
+      <c r="BJ24" s="11">
+        <v>154914</v>
+      </c>
+      <c r="BK24" s="11">
+        <v>2549</v>
+      </c>
+      <c r="BL24" s="11">
+        <v>21</v>
+      </c>
+      <c r="BM24" s="12">
+        <v>22130.571428571431</v>
+      </c>
+      <c r="BN24" s="12">
+        <v>364.14285714285711</v>
+      </c>
+      <c r="BO24" s="13">
+        <v>1.8062175253388759</v>
+      </c>
       <c r="BP24" s="11"/>
       <c r="BQ24" s="11"/>
       <c r="BR24" s="11"/>
@@ -8110,27 +8374,27 @@
       </c>
       <c r="N25" s="8">
         <f t="shared" si="0"/>
-        <v>265108.71428571426</v>
+        <v>247929.75</v>
       </c>
       <c r="O25" s="8">
         <f t="shared" si="1"/>
-        <v>18643</v>
+        <v>17698</v>
       </c>
       <c r="P25" s="8">
         <f t="shared" si="2"/>
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="Q25" s="9">
         <f t="shared" si="3"/>
-        <v>14767.328912466844</v>
+        <v>14372.739130434784</v>
       </c>
       <c r="R25" s="9">
         <f t="shared" si="4"/>
-        <v>1038.46949602122</v>
+        <v>1025.9710144927537</v>
       </c>
       <c r="S25" s="10">
         <f t="shared" si="5"/>
-        <v>3.6988292465955643</v>
+        <v>3.7525954345849284</v>
       </c>
       <c r="T25" s="11">
         <v>254251</v>
@@ -8258,12 +8522,24 @@
       <c r="BI25" s="13">
         <v>3.930887314640886</v>
       </c>
-      <c r="BJ25" s="11"/>
-      <c r="BK25" s="11"/>
-      <c r="BL25" s="11"/>
-      <c r="BM25" s="12"/>
-      <c r="BN25" s="12"/>
-      <c r="BO25" s="13"/>
+      <c r="BJ25" s="11">
+        <v>127677</v>
+      </c>
+      <c r="BK25" s="11">
+        <v>11083</v>
+      </c>
+      <c r="BL25" s="11">
+        <v>37</v>
+      </c>
+      <c r="BM25" s="12">
+        <v>10352.18918918919</v>
+      </c>
+      <c r="BN25" s="12">
+        <v>898.62162162162156</v>
+      </c>
+      <c r="BO25" s="13">
+        <v>4.1289587505104786</v>
+      </c>
       <c r="BP25" s="11"/>
       <c r="BQ25" s="11"/>
       <c r="BR25" s="11"/>
@@ -8329,27 +8605,27 @@
       </c>
       <c r="N26" s="8">
         <f t="shared" ref="N26:N52" si="6">IFERROR(AVERAGE(T26,Z26,AF26,AL26,AR26,AX26,BD26,BJ26,BP26,BV26,CB26,CH26)," ")</f>
-        <v>313798</v>
+        <v>302225.625</v>
       </c>
       <c r="O26" s="8">
         <f t="shared" ref="O26:O52" si="7">IFERROR(AVERAGE(U26,AA26,AG26,AM26,AS26,AY26,BE26,BK26,BQ26,BW26,CC26,CI26)," ")</f>
-        <v>24049.428571428572</v>
+        <v>23538.5</v>
       </c>
       <c r="P26" s="8">
         <f t="shared" ref="P26:P52" si="8">IFERROR(SUM(V26,AB26,AH26,AN26,AT26,AZ26,BF26,BL26,BR26,BX26,CD26,CJ26)," ")</f>
-        <v>399</v>
+        <v>440</v>
       </c>
       <c r="Q26" s="9">
         <f t="shared" ref="Q26:Q52" si="9">IFERROR(SUM(T26,Z26,AF26,AL26,AR26,AX26,BD26,BJ26,BP26,BV26,CB26,CH26)/P26*3," ")</f>
-        <v>16515.684210526317</v>
+        <v>16485.034090909092</v>
       </c>
       <c r="R26" s="9">
         <f t="shared" ref="R26:R52" si="10">IFERROR(SUM(U26,AA26,AG26,AM26,AS26,AY26,BE26,BK26,BQ26,BW26,CC26,CI26)/P26*3," ")</f>
-        <v>1265.7593984962405</v>
+        <v>1283.9181818181819</v>
       </c>
       <c r="S26" s="10">
         <f t="shared" ref="S26:S52" si="11">IFERROR(AVERAGE(Y26,AE26,AK26,AQ26,AW26,BC26,BI26,BO26,BU26,CA26,CG26,CM26)," ")</f>
-        <v>3.8504046403559715</v>
+        <v>3.8989845915233627</v>
       </c>
       <c r="T26" s="11">
         <v>319242</v>
@@ -8477,12 +8753,24 @@
       <c r="BI26" s="13">
         <v>4.0597335511634371</v>
       </c>
-      <c r="BJ26" s="11"/>
-      <c r="BK26" s="11"/>
-      <c r="BL26" s="11"/>
-      <c r="BM26" s="12"/>
-      <c r="BN26" s="12"/>
-      <c r="BO26" s="13"/>
+      <c r="BJ26" s="11">
+        <v>221219</v>
+      </c>
+      <c r="BK26" s="11">
+        <v>19962</v>
+      </c>
+      <c r="BL26" s="11">
+        <v>41</v>
+      </c>
+      <c r="BM26" s="12">
+        <v>16186.756097560979</v>
+      </c>
+      <c r="BN26" s="12">
+        <v>1460.6341463414631</v>
+      </c>
+      <c r="BO26" s="13">
+        <v>4.2390442496951026</v>
+      </c>
       <c r="BP26" s="11"/>
       <c r="BQ26" s="11"/>
       <c r="BR26" s="11"/>
@@ -8719,27 +9007,27 @@
       </c>
       <c r="N28" s="8">
         <f t="shared" si="6"/>
-        <v>280717</v>
+        <v>276374</v>
       </c>
       <c r="O28" s="8">
         <f t="shared" si="7"/>
-        <v>76913.428571428565</v>
+        <v>74228.625</v>
       </c>
       <c r="P28" s="8">
         <f t="shared" si="8"/>
-        <v>437</v>
+        <v>492</v>
       </c>
       <c r="Q28" s="9">
         <f t="shared" si="9"/>
-        <v>13489.832951945082</v>
+        <v>13481.658536585366</v>
       </c>
       <c r="R28" s="9">
         <f t="shared" si="10"/>
-        <v>3696.0686498855839</v>
+        <v>3620.9085365853662</v>
       </c>
       <c r="S28" s="10">
         <f t="shared" si="11"/>
-        <v>7.2535377061416897</v>
+        <v>7.1694781515971577</v>
       </c>
       <c r="T28" s="11">
         <v>362826</v>
@@ -8867,12 +9155,24 @@
       <c r="BI28" s="13">
         <v>6.4549463066604442</v>
       </c>
-      <c r="BJ28" s="11"/>
-      <c r="BK28" s="11"/>
-      <c r="BL28" s="11"/>
-      <c r="BM28" s="12"/>
-      <c r="BN28" s="12"/>
-      <c r="BO28" s="13"/>
+      <c r="BJ28" s="11">
+        <v>245973</v>
+      </c>
+      <c r="BK28" s="11">
+        <v>55435</v>
+      </c>
+      <c r="BL28" s="11">
+        <v>55</v>
+      </c>
+      <c r="BM28" s="12">
+        <v>13416.709090909089</v>
+      </c>
+      <c r="BN28" s="12">
+        <v>3023.727272727273</v>
+      </c>
+      <c r="BO28" s="13">
+        <v>6.581061269785434</v>
+      </c>
       <c r="BP28" s="11"/>
       <c r="BQ28" s="11"/>
       <c r="BR28" s="11"/>
@@ -8938,27 +9238,27 @@
       </c>
       <c r="N29" s="8">
         <f t="shared" si="6"/>
-        <v>62633.166666666664</v>
+        <v>58413.285714285717</v>
       </c>
       <c r="O29" s="8">
         <f t="shared" si="7"/>
-        <v>33123.833333333336</v>
+        <v>31546.428571428572</v>
       </c>
       <c r="P29" s="8">
         <f t="shared" si="8"/>
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="Q29" s="9">
         <f t="shared" si="9"/>
-        <v>14092.462500000001</v>
+        <v>13333.467391304348</v>
       </c>
       <c r="R29" s="9">
         <f t="shared" si="10"/>
-        <v>7452.8624999999993</v>
+        <v>7200.8152173913049</v>
       </c>
       <c r="S29" s="10">
         <f t="shared" si="11"/>
-        <v>11.350575665257372</v>
+        <v>11.546681875280466</v>
       </c>
       <c r="T29" s="11">
         <v>83538</v>
@@ -9074,12 +9374,24 @@
       <c r="BI29" s="13">
         <v>10.89817063085056</v>
       </c>
-      <c r="BJ29" s="11"/>
-      <c r="BK29" s="11"/>
-      <c r="BL29" s="11"/>
-      <c r="BM29" s="12"/>
-      <c r="BN29" s="12"/>
-      <c r="BO29" s="13"/>
+      <c r="BJ29" s="11">
+        <v>33094</v>
+      </c>
+      <c r="BK29" s="11">
+        <v>22082</v>
+      </c>
+      <c r="BL29" s="11">
+        <v>12</v>
+      </c>
+      <c r="BM29" s="12">
+        <v>8273.5</v>
+      </c>
+      <c r="BN29" s="12">
+        <v>5520.5</v>
+      </c>
+      <c r="BO29" s="13">
+        <v>12.723319135419031</v>
+      </c>
       <c r="BP29" s="11"/>
       <c r="BQ29" s="11"/>
       <c r="BR29" s="11"/>
@@ -9145,27 +9457,27 @@
       </c>
       <c r="N30" s="8">
         <f t="shared" si="6"/>
-        <v>164642.85714285713</v>
+        <v>160421.5</v>
       </c>
       <c r="O30" s="8">
         <f t="shared" si="7"/>
-        <v>128809.28571428571</v>
+        <v>124292.625</v>
       </c>
       <c r="P30" s="8">
         <f t="shared" si="8"/>
-        <v>341</v>
+        <v>380</v>
       </c>
       <c r="Q30" s="9">
         <f t="shared" si="9"/>
-        <v>10139.296187683285</v>
+        <v>10131.884210526316</v>
       </c>
       <c r="R30" s="9">
         <f t="shared" si="10"/>
-        <v>7932.5366568914951</v>
+        <v>7850.0605263157895</v>
       </c>
       <c r="S30" s="10">
         <f t="shared" si="11"/>
-        <v>13.951069132986433</v>
+        <v>13.898252246606713</v>
       </c>
       <c r="T30" s="11">
         <v>169875</v>
@@ -9293,12 +9605,24 @@
       <c r="BI30" s="13">
         <v>13.79201978855801</v>
       </c>
-      <c r="BJ30" s="11"/>
-      <c r="BK30" s="11"/>
-      <c r="BL30" s="11"/>
-      <c r="BM30" s="12"/>
-      <c r="BN30" s="12"/>
-      <c r="BO30" s="13"/>
+      <c r="BJ30" s="11">
+        <v>130872</v>
+      </c>
+      <c r="BK30" s="11">
+        <v>92676</v>
+      </c>
+      <c r="BL30" s="11">
+        <v>39</v>
+      </c>
+      <c r="BM30" s="12">
+        <v>10067.07692307692</v>
+      </c>
+      <c r="BN30" s="12">
+        <v>7128.9230769230771</v>
+      </c>
+      <c r="BO30" s="13">
+        <v>13.528534041948671</v>
+      </c>
       <c r="BP30" s="11"/>
       <c r="BQ30" s="11"/>
       <c r="BR30" s="11"/>
@@ -9571,23 +9895,23 @@
       </c>
       <c r="N32" s="8">
         <f t="shared" si="6"/>
-        <v>211020</v>
+        <v>204642.5</v>
       </c>
       <c r="O32" s="8">
         <f t="shared" si="7"/>
-        <v>74905.142857142855</v>
+        <v>72642</v>
       </c>
       <c r="P32" s="8">
         <f t="shared" si="8"/>
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="Q32" s="9">
         <f t="shared" si="9"/>
-        <v>17242.879377431906</v>
+        <v>17233.052631578947</v>
       </c>
       <c r="R32" s="9">
         <f t="shared" si="10"/>
-        <v>6120.6536964980542</v>
+        <v>6117.2210526315794</v>
       </c>
       <c r="S32" s="10">
         <f t="shared" si="11"/>
@@ -9719,12 +10043,24 @@
       <c r="BI32" s="13">
         <v>10</v>
       </c>
-      <c r="BJ32" s="11"/>
-      <c r="BK32" s="11"/>
-      <c r="BL32" s="11"/>
-      <c r="BM32" s="12"/>
-      <c r="BN32" s="12"/>
-      <c r="BO32" s="13"/>
+      <c r="BJ32" s="11">
+        <v>160000</v>
+      </c>
+      <c r="BK32" s="11">
+        <v>56800</v>
+      </c>
+      <c r="BL32" s="11">
+        <v>28</v>
+      </c>
+      <c r="BM32" s="12">
+        <v>17142.857142857141</v>
+      </c>
+      <c r="BN32" s="12">
+        <v>6085.7142857142862</v>
+      </c>
+      <c r="BO32" s="13">
+        <v>10</v>
+      </c>
       <c r="BP32" s="11"/>
       <c r="BQ32" s="11"/>
       <c r="BR32" s="11"/>
@@ -9973,27 +10309,27 @@
       </c>
       <c r="N34" s="8">
         <f t="shared" si="6"/>
-        <v>17603.571428571428</v>
+        <v>16830.875</v>
       </c>
       <c r="O34" s="8">
         <f t="shared" si="7"/>
-        <v>80373.28571428571</v>
+        <v>77122.375</v>
       </c>
       <c r="P34" s="8">
         <f t="shared" si="8"/>
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="Q34" s="9">
         <f t="shared" si="9"/>
-        <v>3554.5673076923076</v>
+        <v>3482.25</v>
       </c>
       <c r="R34" s="9">
         <f t="shared" si="10"/>
-        <v>16229.221153846154</v>
+        <v>15956.353448275862</v>
       </c>
       <c r="S34" s="10">
         <f t="shared" si="11"/>
-        <v>35.832047054656606</v>
+        <v>35.636123810739406</v>
       </c>
       <c r="T34" s="11">
         <v>44447</v>
@@ -10121,12 +10457,24 @@
       <c r="BI34" s="13">
         <v>39.977738196176773</v>
       </c>
-      <c r="BJ34" s="11"/>
-      <c r="BK34" s="11"/>
-      <c r="BL34" s="11"/>
-      <c r="BM34" s="12"/>
-      <c r="BN34" s="12"/>
-      <c r="BO34" s="13"/>
+      <c r="BJ34" s="11">
+        <v>11422</v>
+      </c>
+      <c r="BK34" s="11">
+        <v>54366</v>
+      </c>
+      <c r="BL34" s="11">
+        <v>12</v>
+      </c>
+      <c r="BM34" s="12">
+        <v>2855.5</v>
+      </c>
+      <c r="BN34" s="12">
+        <v>13591.5</v>
+      </c>
+      <c r="BO34" s="13">
+        <v>34.264661103319</v>
+      </c>
       <c r="BP34" s="11"/>
       <c r="BQ34" s="11"/>
       <c r="BR34" s="11"/>
@@ -11083,27 +11431,27 @@
       </c>
       <c r="N40" s="8">
         <f t="shared" si="6"/>
-        <v>54688.5</v>
+        <v>50271.199999999997</v>
       </c>
       <c r="O40" s="8">
         <f t="shared" si="7"/>
-        <v>8422</v>
+        <v>7773.4</v>
       </c>
       <c r="P40" s="8">
         <f t="shared" si="8"/>
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="Q40" s="9">
         <f t="shared" si="9"/>
-        <v>6981.510638297872</v>
+        <v>6793.405405405405</v>
       </c>
       <c r="R40" s="9">
         <f t="shared" si="10"/>
-        <v>1075.1489361702129</v>
+        <v>1050.4594594594594</v>
       </c>
       <c r="S40" s="10">
         <f t="shared" si="11"/>
-        <v>5.3953658687188852</v>
+        <v>5.4152190886422362</v>
       </c>
       <c r="T40" s="11">
         <v>111399</v>
@@ -11195,12 +11543,24 @@
       <c r="BG40" s="12"/>
       <c r="BH40" s="12"/>
       <c r="BI40" s="13"/>
-      <c r="BJ40" s="11"/>
-      <c r="BK40" s="11"/>
-      <c r="BL40" s="11"/>
-      <c r="BM40" s="12"/>
-      <c r="BN40" s="12"/>
-      <c r="BO40" s="13"/>
+      <c r="BJ40" s="11">
+        <v>32602</v>
+      </c>
+      <c r="BK40" s="11">
+        <v>5179</v>
+      </c>
+      <c r="BL40" s="11">
+        <v>17</v>
+      </c>
+      <c r="BM40" s="12">
+        <v>5753.2941176470586</v>
+      </c>
+      <c r="BN40" s="12">
+        <v>913.94117647058818</v>
+      </c>
+      <c r="BO40" s="13">
+        <v>5.4946319683356393</v>
+      </c>
       <c r="BP40" s="11"/>
       <c r="BQ40" s="11"/>
       <c r="BR40" s="11"/>
@@ -11401,27 +11761,27 @@
       </c>
       <c r="N42" s="8">
         <f t="shared" si="6"/>
-        <v>19953.571428571428</v>
+        <v>20153.125</v>
       </c>
       <c r="O42" s="8">
         <f t="shared" si="7"/>
-        <v>47971.428571428572</v>
+        <v>47050.875</v>
       </c>
       <c r="P42" s="8">
         <f t="shared" si="8"/>
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="Q42" s="9">
         <f t="shared" si="9"/>
-        <v>4275.7653061224491</v>
+        <v>4357.4324324324325</v>
       </c>
       <c r="R42" s="9">
         <f t="shared" si="10"/>
-        <v>10279.591836734693</v>
+        <v>10173.162162162163</v>
       </c>
       <c r="S42" s="10">
         <f t="shared" si="11"/>
-        <v>22.35962288199687</v>
+        <v>22.031062457539218</v>
       </c>
       <c r="T42" s="11">
         <v>16200</v>
@@ -11549,12 +11909,24 @@
       <c r="BI42" s="13">
         <v>21.25175799893065</v>
       </c>
-      <c r="BJ42" s="11"/>
-      <c r="BK42" s="11"/>
-      <c r="BL42" s="11"/>
-      <c r="BM42" s="12"/>
-      <c r="BN42" s="12"/>
-      <c r="BO42" s="13"/>
+      <c r="BJ42" s="11">
+        <v>21550</v>
+      </c>
+      <c r="BK42" s="11">
+        <v>40607</v>
+      </c>
+      <c r="BL42" s="11">
+        <v>13</v>
+      </c>
+      <c r="BM42" s="12">
+        <v>4973.0769230769229</v>
+      </c>
+      <c r="BN42" s="12">
+        <v>9370.8461538461543</v>
+      </c>
+      <c r="BO42" s="13">
+        <v>19.73113948633566</v>
+      </c>
       <c r="BP42" s="11"/>
       <c r="BQ42" s="11"/>
       <c r="BR42" s="11"/>
@@ -11620,27 +11992,27 @@
       </c>
       <c r="N43" s="8">
         <f t="shared" si="6"/>
-        <v>392132.42857142858</v>
+        <v>383006.875</v>
       </c>
       <c r="O43" s="8">
         <f t="shared" si="7"/>
-        <v>14967.285714285714</v>
+        <v>14673.875</v>
       </c>
       <c r="P43" s="8">
         <f t="shared" si="8"/>
-        <v>375</v>
+        <v>421</v>
       </c>
       <c r="Q43" s="9">
         <f t="shared" si="9"/>
-        <v>21959.416000000001</v>
+        <v>21834.121140142517</v>
       </c>
       <c r="R43" s="9">
         <f t="shared" si="10"/>
-        <v>838.16800000000012</v>
+        <v>836.51543942992885</v>
       </c>
       <c r="S43" s="10">
         <f t="shared" si="11"/>
-        <v>2.6921779548076836</v>
+        <v>2.698129523077176</v>
       </c>
       <c r="T43" s="11">
         <v>178860</v>
@@ -11768,12 +12140,24 @@
       <c r="BI43" s="13">
         <v>2.65</v>
       </c>
-      <c r="BJ43" s="11"/>
-      <c r="BK43" s="11"/>
-      <c r="BL43" s="11"/>
-      <c r="BM43" s="12"/>
-      <c r="BN43" s="12"/>
-      <c r="BO43" s="13"/>
+      <c r="BJ43" s="11">
+        <v>319128</v>
+      </c>
+      <c r="BK43" s="11">
+        <v>12620</v>
+      </c>
+      <c r="BL43" s="11">
+        <v>46</v>
+      </c>
+      <c r="BM43" s="12">
+        <v>20812.695652173908</v>
+      </c>
+      <c r="BN43" s="12">
+        <v>823.04347826086951</v>
+      </c>
+      <c r="BO43" s="13">
+        <v>2.739790500963621</v>
+      </c>
       <c r="BP43" s="11"/>
       <c r="BQ43" s="11"/>
       <c r="BR43" s="11"/>
@@ -11839,27 +12223,27 @@
       </c>
       <c r="N44" s="8">
         <f t="shared" si="6"/>
-        <v>384850.85714285716</v>
+        <v>377616</v>
       </c>
       <c r="O44" s="8">
         <f t="shared" si="7"/>
-        <v>14692</v>
+        <v>14560</v>
       </c>
       <c r="P44" s="8">
         <f t="shared" si="8"/>
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="Q44" s="9">
         <f t="shared" si="9"/>
-        <v>22830.135593220337</v>
+        <v>22656.959999999999</v>
       </c>
       <c r="R44" s="9">
         <f t="shared" si="10"/>
-        <v>871.5593220338983</v>
+        <v>873.59999999999991</v>
       </c>
       <c r="S44" s="10">
         <f t="shared" si="11"/>
-        <v>2.6897975381909816</v>
+        <v>2.7055134522803974</v>
       </c>
       <c r="T44" s="11">
         <v>184368</v>
@@ -11987,12 +12371,24 @@
       <c r="BI44" s="13">
         <v>2.65</v>
       </c>
-      <c r="BJ44" s="11"/>
-      <c r="BK44" s="11"/>
-      <c r="BL44" s="11"/>
-      <c r="BM44" s="12"/>
-      <c r="BN44" s="12"/>
-      <c r="BO44" s="13"/>
+      <c r="BJ44" s="11">
+        <v>326972</v>
+      </c>
+      <c r="BK44" s="11">
+        <v>13636</v>
+      </c>
+      <c r="BL44" s="11">
+        <v>46</v>
+      </c>
+      <c r="BM44" s="12">
+        <v>21324.26086956522</v>
+      </c>
+      <c r="BN44" s="12">
+        <v>889.30434782608688</v>
+      </c>
+      <c r="BO44" s="13">
+        <v>2.8155248509063062</v>
+      </c>
       <c r="BP44" s="11"/>
       <c r="BQ44" s="11"/>
       <c r="BR44" s="11"/>
@@ -12058,27 +12454,27 @@
       </c>
       <c r="N45" s="8">
         <f t="shared" si="6"/>
-        <v>262462.57142857142</v>
+        <v>250260.5</v>
       </c>
       <c r="O45" s="8">
         <f t="shared" si="7"/>
-        <v>5497.4285714285716</v>
+        <v>5311.875</v>
       </c>
       <c r="P45" s="8">
         <f t="shared" si="8"/>
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="Q45" s="9">
         <f t="shared" si="9"/>
-        <v>18747.326530612245</v>
+        <v>18311.743902439022</v>
       </c>
       <c r="R45" s="9">
         <f t="shared" si="10"/>
-        <v>392.67346938775506</v>
+        <v>388.67378048780489</v>
       </c>
       <c r="S45" s="10">
         <f t="shared" si="11"/>
-        <v>2.0433823725204263</v>
+        <v>2.0618063397178892</v>
       </c>
       <c r="T45" s="11">
         <v>281804</v>
@@ -12206,12 +12602,24 @@
       <c r="BI45" s="13">
         <v>2.2955832426215079</v>
       </c>
-      <c r="BJ45" s="11"/>
-      <c r="BK45" s="11"/>
-      <c r="BL45" s="11"/>
-      <c r="BM45" s="12"/>
-      <c r="BN45" s="12"/>
-      <c r="BO45" s="13"/>
+      <c r="BJ45" s="11">
+        <v>164846</v>
+      </c>
+      <c r="BK45" s="11">
+        <v>4013</v>
+      </c>
+      <c r="BL45" s="11">
+        <v>34</v>
+      </c>
+      <c r="BM45" s="12">
+        <v>14545.23529411765</v>
+      </c>
+      <c r="BN45" s="12">
+        <v>354.08823529411768</v>
+      </c>
+      <c r="BO45" s="13">
+        <v>2.190774110100131</v>
+      </c>
       <c r="BP45" s="11"/>
       <c r="BQ45" s="11"/>
       <c r="BR45" s="11"/>
@@ -12277,27 +12685,27 @@
       </c>
       <c r="N46" s="8">
         <f t="shared" si="6"/>
-        <v>266598.85714285716</v>
+        <v>251224.625</v>
       </c>
       <c r="O46" s="8">
         <f t="shared" si="7"/>
-        <v>5245.7142857142853</v>
+        <v>5002.125</v>
       </c>
       <c r="P46" s="8">
         <f t="shared" si="8"/>
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="Q46" s="9">
         <f t="shared" si="9"/>
-        <v>19713.295774647886</v>
+        <v>19140.923809523811</v>
       </c>
       <c r="R46" s="9">
         <f t="shared" si="10"/>
-        <v>387.88732394366195</v>
+        <v>381.1142857142857</v>
       </c>
       <c r="S46" s="10">
         <f t="shared" si="11"/>
-        <v>1.9982905333516783</v>
+        <v>2.0129927454895618</v>
       </c>
       <c r="T46" s="11">
         <v>407925</v>
@@ -12425,12 +12833,24 @@
       <c r="BI46" s="13">
         <v>2.136097682349368</v>
       </c>
-      <c r="BJ46" s="11"/>
-      <c r="BK46" s="11"/>
-      <c r="BL46" s="11"/>
-      <c r="BM46" s="12"/>
-      <c r="BN46" s="12"/>
-      <c r="BO46" s="13"/>
+      <c r="BJ46" s="11">
+        <v>143605</v>
+      </c>
+      <c r="BK46" s="11">
+        <v>3297</v>
+      </c>
+      <c r="BL46" s="11">
+        <v>31</v>
+      </c>
+      <c r="BM46" s="12">
+        <v>13897.258064516131</v>
+      </c>
+      <c r="BN46" s="12">
+        <v>319.06451612903231</v>
+      </c>
+      <c r="BO46" s="13">
+        <v>2.115908230454747</v>
+      </c>
       <c r="BP46" s="11"/>
       <c r="BQ46" s="11"/>
       <c r="BR46" s="11"/>
@@ -12496,27 +12916,27 @@
       </c>
       <c r="N47" s="8">
         <f t="shared" si="6"/>
-        <v>260525.28571428571</v>
+        <v>253426.375</v>
       </c>
       <c r="O47" s="8">
         <f t="shared" si="7"/>
-        <v>19894.714285714286</v>
+        <v>18965.125</v>
       </c>
       <c r="P47" s="8">
         <f t="shared" si="8"/>
-        <v>396</v>
+        <v>444</v>
       </c>
       <c r="Q47" s="9">
         <f t="shared" si="9"/>
-        <v>13815.734848484848</v>
+        <v>13698.722972972973</v>
       </c>
       <c r="R47" s="9">
         <f t="shared" si="10"/>
-        <v>1055.0227272727273</v>
+        <v>1025.1418918918919</v>
       </c>
       <c r="S47" s="10">
         <f t="shared" si="11"/>
-        <v>3.8898586561630633</v>
+        <v>3.8354629280213421</v>
       </c>
       <c r="T47" s="11">
         <v>211685</v>
@@ -12644,12 +13064,24 @@
       <c r="BI47" s="13">
         <v>3.75235605452849</v>
       </c>
-      <c r="BJ47" s="11"/>
-      <c r="BK47" s="11"/>
-      <c r="BL47" s="11"/>
-      <c r="BM47" s="12"/>
-      <c r="BN47" s="12"/>
-      <c r="BO47" s="13"/>
+      <c r="BJ47" s="11">
+        <v>203734</v>
+      </c>
+      <c r="BK47" s="11">
+        <v>12458</v>
+      </c>
+      <c r="BL47" s="11">
+        <v>48</v>
+      </c>
+      <c r="BM47" s="12">
+        <v>12733.375</v>
+      </c>
+      <c r="BN47" s="12">
+        <v>778.625</v>
+      </c>
+      <c r="BO47" s="13">
+        <v>3.454692831029293</v>
+      </c>
       <c r="BP47" s="11"/>
       <c r="BQ47" s="11"/>
       <c r="BR47" s="11"/>
@@ -12715,27 +13147,27 @@
       </c>
       <c r="N48" s="8">
         <f t="shared" si="6"/>
-        <v>240560.57142857142</v>
+        <v>236276.5</v>
       </c>
       <c r="O48" s="8">
         <f t="shared" si="7"/>
-        <v>18480.428571428572</v>
+        <v>18119.25</v>
       </c>
       <c r="P48" s="8">
         <f t="shared" si="8"/>
-        <v>398</v>
+        <v>442</v>
       </c>
       <c r="Q48" s="9">
         <f t="shared" si="9"/>
-        <v>12692.89447236181</v>
+        <v>12829.493212669684</v>
       </c>
       <c r="R48" s="9">
         <f t="shared" si="10"/>
-        <v>975.09798994974869</v>
+        <v>983.8506787330316</v>
       </c>
       <c r="S48" s="10">
         <f t="shared" si="11"/>
-        <v>3.9115143102761407</v>
+        <v>3.9083513808156853</v>
       </c>
       <c r="T48" s="11">
         <v>225871</v>
@@ -12863,12 +13295,24 @@
       <c r="BI48" s="13">
         <v>3.724467629952517</v>
       </c>
-      <c r="BJ48" s="11"/>
-      <c r="BK48" s="11"/>
-      <c r="BL48" s="11"/>
-      <c r="BM48" s="12"/>
-      <c r="BN48" s="12"/>
-      <c r="BO48" s="13"/>
+      <c r="BJ48" s="11">
+        <v>206288</v>
+      </c>
+      <c r="BK48" s="11">
+        <v>15591</v>
+      </c>
+      <c r="BL48" s="11">
+        <v>44</v>
+      </c>
+      <c r="BM48" s="12">
+        <v>14065.09090909091</v>
+      </c>
+      <c r="BN48" s="12">
+        <v>1063.022727272727</v>
+      </c>
+      <c r="BO48" s="13">
+        <v>3.8862108745924959</v>
+      </c>
       <c r="BP48" s="11"/>
       <c r="BQ48" s="11"/>
       <c r="BR48" s="11"/>
@@ -12934,27 +13378,27 @@
       </c>
       <c r="N49" s="8">
         <f t="shared" si="6"/>
-        <v>160869.85714285713</v>
+        <v>163548.125</v>
       </c>
       <c r="O49" s="8">
         <f t="shared" si="7"/>
-        <v>31562.285714285714</v>
+        <v>33127.75</v>
       </c>
       <c r="P49" s="8">
         <f t="shared" si="8"/>
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="Q49" s="9">
         <f t="shared" si="9"/>
-        <v>14499</v>
+        <v>14068.655913978495</v>
       </c>
       <c r="R49" s="9">
         <f t="shared" si="10"/>
-        <v>2844.669527896996</v>
+        <v>2849.6989247311831</v>
       </c>
       <c r="S49" s="10">
         <f t="shared" si="11"/>
-        <v>6.2236961008663965</v>
+        <v>6.2878980010289576</v>
       </c>
       <c r="T49" s="11">
         <v>268651</v>
@@ -13082,12 +13526,24 @@
       <c r="BI49" s="13">
         <v>5.4956222939652202</v>
       </c>
-      <c r="BJ49" s="11"/>
-      <c r="BK49" s="11"/>
-      <c r="BL49" s="11"/>
-      <c r="BM49" s="12"/>
-      <c r="BN49" s="12"/>
-      <c r="BO49" s="13"/>
+      <c r="BJ49" s="11">
+        <v>182296</v>
+      </c>
+      <c r="BK49" s="11">
+        <v>44086</v>
+      </c>
+      <c r="BL49" s="11">
+        <v>46</v>
+      </c>
+      <c r="BM49" s="12">
+        <v>11888.86956521739</v>
+      </c>
+      <c r="BN49" s="12">
+        <v>2875.173913043478</v>
+      </c>
+      <c r="BO49" s="13">
+        <v>6.7373113021668889</v>
+      </c>
       <c r="BP49" s="11"/>
       <c r="BQ49" s="11"/>
       <c r="BR49" s="11"/>
@@ -13153,23 +13609,23 @@
       </c>
       <c r="N50" s="8">
         <f t="shared" si="6"/>
-        <v>399828.57142857142</v>
+        <v>385757.5</v>
       </c>
       <c r="O50" s="8">
         <f t="shared" si="7"/>
-        <v>14827.428571428571</v>
+        <v>14305.625</v>
       </c>
       <c r="P50" s="8">
         <f t="shared" si="8"/>
-        <v>334</v>
+        <v>371</v>
       </c>
       <c r="Q50" s="9">
         <f t="shared" si="9"/>
-        <v>25138.922155688622</v>
+        <v>24954.663072776282</v>
       </c>
       <c r="R50" s="9">
         <f t="shared" si="10"/>
-        <v>932.26347305389231</v>
+        <v>925.43126684636127</v>
       </c>
       <c r="S50" s="10">
         <f t="shared" si="11"/>
@@ -13301,12 +13757,24 @@
       <c r="BI50" s="13">
         <v>2.65</v>
       </c>
-      <c r="BJ50" s="11"/>
-      <c r="BK50" s="11"/>
-      <c r="BL50" s="11"/>
-      <c r="BM50" s="12"/>
-      <c r="BN50" s="12"/>
-      <c r="BO50" s="13"/>
+      <c r="BJ50" s="11">
+        <v>287260</v>
+      </c>
+      <c r="BK50" s="11">
+        <v>10653</v>
+      </c>
+      <c r="BL50" s="11">
+        <v>37</v>
+      </c>
+      <c r="BM50" s="12">
+        <v>23291.35135135135</v>
+      </c>
+      <c r="BN50" s="12">
+        <v>863.75675675675666</v>
+      </c>
+      <c r="BO50" s="13">
+        <v>2.65</v>
+      </c>
       <c r="BP50" s="11"/>
       <c r="BQ50" s="11"/>
       <c r="BR50" s="11"/>
@@ -13372,27 +13840,27 @@
       </c>
       <c r="N51" s="8">
         <f t="shared" si="6"/>
-        <v>423497.14285714284</v>
+        <v>405949.5</v>
       </c>
       <c r="O51" s="8">
         <f t="shared" si="7"/>
-        <v>15705.285714285714</v>
+        <v>15146.5</v>
       </c>
       <c r="P51" s="8">
         <f t="shared" si="8"/>
-        <v>345</v>
+        <v>382</v>
       </c>
       <c r="Q51" s="9">
         <f t="shared" si="9"/>
-        <v>25778.086956521744</v>
+        <v>25504.680628272254</v>
       </c>
       <c r="R51" s="9">
         <f t="shared" si="10"/>
-        <v>955.97391304347832</v>
+        <v>951.61256544502612</v>
       </c>
       <c r="S51" s="10">
         <f t="shared" si="11"/>
-        <v>2.65</v>
+        <v>2.6614655037084161</v>
       </c>
       <c r="T51" s="11">
         <v>318760</v>
@@ -13520,12 +13988,24 @@
       <c r="BI51" s="13">
         <v>2.65</v>
       </c>
-      <c r="BJ51" s="11"/>
-      <c r="BK51" s="11"/>
-      <c r="BL51" s="11"/>
-      <c r="BM51" s="12"/>
-      <c r="BN51" s="12"/>
-      <c r="BO51" s="13"/>
+      <c r="BJ51" s="11">
+        <v>283116</v>
+      </c>
+      <c r="BK51" s="11">
+        <v>11235</v>
+      </c>
+      <c r="BL51" s="11">
+        <v>37</v>
+      </c>
+      <c r="BM51" s="12">
+        <v>22955.35135135135</v>
+      </c>
+      <c r="BN51" s="12">
+        <v>910.94594594594594</v>
+      </c>
+      <c r="BO51" s="13">
+        <v>2.7417240296673282</v>
+      </c>
       <c r="BP51" s="11"/>
       <c r="BQ51" s="11"/>
       <c r="BR51" s="11"/>
@@ -13591,27 +14071,27 @@
       </c>
       <c r="N52" s="8">
         <f t="shared" si="6"/>
-        <v>42736.428571428572</v>
+        <v>41586.375</v>
       </c>
       <c r="O52" s="8">
         <f t="shared" si="7"/>
-        <v>100733.85714285714</v>
+        <v>100230.25</v>
       </c>
       <c r="P52" s="8">
         <f t="shared" si="8"/>
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="Q52" s="9">
         <f t="shared" si="9"/>
-        <v>5790.0967741935483</v>
+        <v>5670.869318181818</v>
       </c>
       <c r="R52" s="9">
         <f t="shared" si="10"/>
-        <v>13647.812903225806</v>
+        <v>13667.761363636364</v>
       </c>
       <c r="S52" s="10">
         <f t="shared" si="11"/>
-        <v>24.277553546427885</v>
+        <v>24.582618689670912</v>
       </c>
       <c r="T52" s="11">
         <v>62208</v>
@@ -13739,12 +14219,24 @@
       <c r="BI52" s="13">
         <v>25.174753559962621</v>
       </c>
-      <c r="BJ52" s="11"/>
-      <c r="BK52" s="11"/>
-      <c r="BL52" s="11"/>
-      <c r="BM52" s="12"/>
-      <c r="BN52" s="12"/>
-      <c r="BO52" s="13"/>
+      <c r="BJ52" s="11">
+        <v>33536</v>
+      </c>
+      <c r="BK52" s="11">
+        <v>96705</v>
+      </c>
+      <c r="BL52" s="11">
+        <v>21</v>
+      </c>
+      <c r="BM52" s="12">
+        <v>4790.8571428571431</v>
+      </c>
+      <c r="BN52" s="12">
+        <v>13815</v>
+      </c>
+      <c r="BO52" s="13">
+        <v>26.71807469237212</v>
+      </c>
       <c r="BP52" s="11"/>
       <c r="BQ52" s="11"/>
       <c r="BR52" s="11"/>
@@ -13796,11 +14288,11 @@
       <c r="M53" s="14"/>
       <c r="N53" s="14">
         <f>SUM(N3:N52)</f>
-        <v>10370192.414761905</v>
+        <v>10030755.522738095</v>
       </c>
       <c r="O53" s="14">
         <f>SUM(O3:O52)</f>
-        <v>2017284.9523809529</v>
+        <v>1949988.3226190479</v>
       </c>
       <c r="P53" s="14"/>
       <c r="Q53" s="14"/>
@@ -13892,11 +14384,11 @@
       <c r="BI53" s="14"/>
       <c r="BJ53" s="14">
         <f>SUM(BJ3:BJ52)</f>
-        <v>0</v>
+        <v>7309833</v>
       </c>
       <c r="BK53" s="14">
         <f>SUM(BK3:BK52)</f>
-        <v>0</v>
+        <v>1433094</v>
       </c>
       <c r="BL53" s="14"/>
       <c r="BM53" s="14"/>
@@ -14409,27 +14901,27 @@
       </c>
       <c r="N57" s="8">
         <f t="shared" ref="N57:N78" si="12">IFERROR(AVERAGE(T57,Z57,AF57,AL57,AR57,AX57,BD57,BJ57,BP57,BV57,CB57,CH57)," ")</f>
-        <v>151545</v>
+        <v>111258</v>
       </c>
       <c r="O57" s="8">
         <f t="shared" ref="O57:O78" si="13">IFERROR(AVERAGE(U57,AA57,AG57,AM57,AS57,AY57,BE57,BK57,BQ57,BW57,CC57,CI57)," ")</f>
-        <v>7742.5</v>
+        <v>5771</v>
       </c>
       <c r="P57" s="8">
         <f t="shared" ref="P57:P78" si="14">IFERROR(SUM(V57,AB57,AH57,AN57,AT57,AZ57,BF57,BL57,BR57,BX57,CD57,CJ57)," ")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q57" s="9">
         <f t="shared" ref="Q57:Q78" si="15">IFERROR(SUM(T57,Z57,AF57,AL57,AR57,AX57,BD57,BJ57,BP57,BV57,CB57,CH57)/P57*3," ")</f>
-        <v>82660.909090909088</v>
+        <v>77024.769230769234</v>
       </c>
       <c r="R57" s="9">
         <f t="shared" ref="R57:R78" si="16">IFERROR(SUM(U57,AA57,AG57,AM57,AS57,AY57,BE57,BK57,BQ57,BW57,CC57,CI57)/P57*3," ")</f>
-        <v>4223.181818181818</v>
+        <v>3995.3076923076924</v>
       </c>
       <c r="S57" s="10">
         <f t="shared" ref="S57:S78" si="17">IFERROR(AVERAGE(Y57,AE57,AK57,AQ57,AW57,BC57,BI57,BO57,BU57,CA57,CG57,CM57)," ")</f>
-        <v>2.9337029702569488</v>
+        <v>2.991721357390047</v>
       </c>
       <c r="T57" s="11"/>
       <c r="U57" s="11"/>
@@ -14497,12 +14989,24 @@
       <c r="BI57" s="13">
         <v>3</v>
       </c>
-      <c r="BJ57" s="11"/>
-      <c r="BK57" s="11"/>
-      <c r="BL57" s="11"/>
-      <c r="BM57" s="12"/>
-      <c r="BN57" s="12"/>
-      <c r="BO57" s="13"/>
+      <c r="BJ57" s="11">
+        <v>30684</v>
+      </c>
+      <c r="BK57" s="11">
+        <v>1828</v>
+      </c>
+      <c r="BL57" s="11">
+        <v>2</v>
+      </c>
+      <c r="BM57" s="12">
+        <v>46026</v>
+      </c>
+      <c r="BN57" s="12">
+        <v>2742</v>
+      </c>
+      <c r="BO57" s="13">
+        <v>3.1077581316562428</v>
+      </c>
       <c r="BP57" s="11"/>
       <c r="BQ57" s="11"/>
       <c r="BR57" s="11"/>
@@ -14571,27 +15075,27 @@
       </c>
       <c r="N58" s="8">
         <f t="shared" si="12"/>
-        <v>4496208.7142857146</v>
+        <v>4323008.125</v>
       </c>
       <c r="O58" s="8">
         <f t="shared" si="13"/>
-        <v>50298.857142857145</v>
+        <v>48609.375</v>
       </c>
       <c r="P58" s="8">
         <f t="shared" si="14"/>
-        <v>491</v>
+        <v>553</v>
       </c>
       <c r="Q58" s="9">
         <f t="shared" si="15"/>
-        <v>192302.20570264765</v>
+        <v>187616.98915009041</v>
       </c>
       <c r="R58" s="9">
         <f t="shared" si="16"/>
-        <v>2151.2749490835031</v>
+        <v>2109.6292947558768</v>
       </c>
       <c r="S58" s="10">
         <f t="shared" si="17"/>
-        <v>1.3477364743438982</v>
+        <v>1.3522274003296841</v>
       </c>
       <c r="T58" s="11">
         <v>4555723</v>
@@ -14719,12 +15223,24 @@
       <c r="BI58" s="13">
         <v>1.386808798631143</v>
       </c>
-      <c r="BJ58" s="11"/>
-      <c r="BK58" s="11"/>
-      <c r="BL58" s="11"/>
-      <c r="BM58" s="12"/>
-      <c r="BN58" s="12"/>
-      <c r="BO58" s="13"/>
+      <c r="BJ58" s="11">
+        <v>3110604</v>
+      </c>
+      <c r="BK58" s="11">
+        <v>36783</v>
+      </c>
+      <c r="BL58" s="11">
+        <v>62</v>
+      </c>
+      <c r="BM58" s="12">
+        <v>150513.09677419349</v>
+      </c>
+      <c r="BN58" s="12">
+        <v>1779.822580645161</v>
+      </c>
+      <c r="BO58" s="13">
+        <v>1.383663882230187</v>
+      </c>
       <c r="BP58" s="11"/>
       <c r="BQ58" s="11"/>
       <c r="BR58" s="11"/>
@@ -14931,27 +15447,27 @@
       </c>
       <c r="N60" s="8">
         <f t="shared" si="12"/>
-        <v>3455264.1428571427</v>
+        <v>3351228.375</v>
       </c>
       <c r="O60" s="8">
         <f t="shared" si="13"/>
-        <v>8756.2857142857138</v>
+        <v>8446.125</v>
       </c>
       <c r="P60" s="8">
         <f t="shared" si="14"/>
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="Q60" s="9">
         <f t="shared" si="15"/>
-        <v>186530.96915167096</v>
+        <v>187919.3481308411</v>
       </c>
       <c r="R60" s="9">
         <f t="shared" si="16"/>
-        <v>472.70437017994857</v>
+        <v>473.61448598130835</v>
       </c>
       <c r="S60" s="10">
         <f t="shared" si="17"/>
-        <v>0.6386638453313801</v>
+        <v>0.63648397516289434</v>
       </c>
       <c r="T60" s="11">
         <v>2164532</v>
@@ -15079,12 +15595,24 @@
       <c r="BI60" s="13">
         <v>0.63178791809350954</v>
       </c>
-      <c r="BJ60" s="11"/>
-      <c r="BK60" s="11"/>
-      <c r="BL60" s="11"/>
-      <c r="BM60" s="12"/>
-      <c r="BN60" s="12"/>
-      <c r="BO60" s="13"/>
+      <c r="BJ60" s="11">
+        <v>2622978</v>
+      </c>
+      <c r="BK60" s="11">
+        <v>6275</v>
+      </c>
+      <c r="BL60" s="11">
+        <v>39</v>
+      </c>
+      <c r="BM60" s="12">
+        <v>201767.5384615385</v>
+      </c>
+      <c r="BN60" s="12">
+        <v>482.69230769230762</v>
+      </c>
+      <c r="BO60" s="13">
+        <v>0.62122488398349429</v>
+      </c>
       <c r="BP60" s="11"/>
       <c r="BQ60" s="11"/>
       <c r="BR60" s="11"/>
@@ -15153,27 +15681,27 @@
       </c>
       <c r="N61" s="8">
         <f t="shared" si="12"/>
-        <v>3628744.1666666665</v>
+        <v>3477844.5714285714</v>
       </c>
       <c r="O61" s="8">
         <f t="shared" si="13"/>
-        <v>8084.5</v>
+        <v>7895.4285714285716</v>
       </c>
       <c r="P61" s="8">
         <f t="shared" si="14"/>
-        <v>313</v>
+        <v>354</v>
       </c>
       <c r="Q61" s="9">
         <f t="shared" si="15"/>
-        <v>208681.77316293929</v>
+        <v>206312.81355932204</v>
       </c>
       <c r="R61" s="9">
         <f t="shared" si="16"/>
-        <v>464.92332268370603</v>
+        <v>468.37288135593218</v>
       </c>
       <c r="S61" s="10">
         <f t="shared" si="17"/>
-        <v>0.59400948667021758</v>
+        <v>0.60209499316025161</v>
       </c>
       <c r="T61" s="11"/>
       <c r="U61" s="11"/>
@@ -15289,12 +15817,24 @@
       <c r="BI61" s="13">
         <v>0.6479792384621208</v>
       </c>
-      <c r="BJ61" s="11"/>
-      <c r="BK61" s="11"/>
-      <c r="BL61" s="11"/>
-      <c r="BM61" s="12"/>
-      <c r="BN61" s="12"/>
-      <c r="BO61" s="13"/>
+      <c r="BJ61" s="11">
+        <v>2572447</v>
+      </c>
+      <c r="BK61" s="11">
+        <v>6761</v>
+      </c>
+      <c r="BL61" s="11">
+        <v>41</v>
+      </c>
+      <c r="BM61" s="12">
+        <v>188227.8292682927</v>
+      </c>
+      <c r="BN61" s="12">
+        <v>494.70731707317083</v>
+      </c>
+      <c r="BO61" s="13">
+        <v>0.65060803210045537</v>
+      </c>
       <c r="BP61" s="11"/>
       <c r="BQ61" s="11"/>
       <c r="BR61" s="11"/>
@@ -15363,27 +15903,27 @@
       </c>
       <c r="N62" s="8">
         <f t="shared" si="12"/>
-        <v>4264285.5714285718</v>
+        <v>4118778.5</v>
       </c>
       <c r="O62" s="8">
         <f t="shared" si="13"/>
-        <v>10077.571428571429</v>
+        <v>9573</v>
       </c>
       <c r="P62" s="8">
         <f t="shared" si="14"/>
-        <v>377</v>
+        <v>419</v>
       </c>
       <c r="Q62" s="9">
         <f t="shared" si="15"/>
-        <v>237533.14854111406</v>
+        <v>235920.48687350837</v>
       </c>
       <c r="R62" s="9">
         <f t="shared" si="16"/>
-        <v>561.35013262599466</v>
+        <v>548.3341288782816</v>
       </c>
       <c r="S62" s="10">
         <f t="shared" si="17"/>
-        <v>0.59315746664068647</v>
+        <v>0.58892513286071557</v>
       </c>
       <c r="T62" s="11">
         <v>2675265</v>
@@ -15511,12 +16051,24 @@
       <c r="BI62" s="13">
         <v>0.66</v>
       </c>
-      <c r="BJ62" s="11"/>
-      <c r="BK62" s="11"/>
-      <c r="BL62" s="11"/>
-      <c r="BM62" s="12"/>
-      <c r="BN62" s="12"/>
-      <c r="BO62" s="13"/>
+      <c r="BJ62" s="11">
+        <v>3100229</v>
+      </c>
+      <c r="BK62" s="11">
+        <v>6041</v>
+      </c>
+      <c r="BL62" s="11">
+        <v>42</v>
+      </c>
+      <c r="BM62" s="12">
+        <v>221444.92857142861</v>
+      </c>
+      <c r="BN62" s="12">
+        <v>431.5</v>
+      </c>
+      <c r="BO62" s="13">
+        <v>0.5592987964009194</v>
+      </c>
       <c r="BP62" s="11"/>
       <c r="BQ62" s="11"/>
       <c r="BR62" s="11"/>
@@ -15585,27 +16137,27 @@
       </c>
       <c r="N63" s="8">
         <f t="shared" si="12"/>
-        <v>10080062.285714285</v>
+        <v>9817942.875</v>
       </c>
       <c r="O63" s="8">
         <f t="shared" si="13"/>
-        <v>10993</v>
+        <v>11213.875</v>
       </c>
       <c r="P63" s="8">
         <f t="shared" si="14"/>
-        <v>498</v>
+        <v>561</v>
       </c>
       <c r="Q63" s="9">
         <f t="shared" si="15"/>
-        <v>425062.86746987957</v>
+        <v>420018.94652406417</v>
       </c>
       <c r="R63" s="9">
         <f t="shared" si="16"/>
-        <v>463.56024096385545</v>
+        <v>479.73796791443851</v>
       </c>
       <c r="S63" s="10">
         <f t="shared" si="17"/>
-        <v>0.41784654893191719</v>
+        <v>0.42903464856728324</v>
       </c>
       <c r="T63" s="11">
         <v>9298604</v>
@@ -15733,12 +16285,24 @@
       <c r="BI63" s="13">
         <v>0.47540755954425312</v>
       </c>
-      <c r="BJ63" s="11"/>
-      <c r="BK63" s="11"/>
-      <c r="BL63" s="11"/>
-      <c r="BM63" s="12"/>
-      <c r="BN63" s="12"/>
-      <c r="BO63" s="13"/>
+      <c r="BJ63" s="11">
+        <v>7983107</v>
+      </c>
+      <c r="BK63" s="11">
+        <v>12760</v>
+      </c>
+      <c r="BL63" s="11">
+        <v>63</v>
+      </c>
+      <c r="BM63" s="12">
+        <v>380147.95238095243</v>
+      </c>
+      <c r="BN63" s="12">
+        <v>607.61904761904759</v>
+      </c>
+      <c r="BO63" s="13">
+        <v>0.50735134601484555</v>
+      </c>
       <c r="BP63" s="11"/>
       <c r="BQ63" s="11"/>
       <c r="BR63" s="11"/>
@@ -15807,27 +16371,27 @@
       </c>
       <c r="N64" s="8">
         <f t="shared" si="12"/>
-        <v>9847720.7142857146</v>
+        <v>9493976.125</v>
       </c>
       <c r="O64" s="8">
         <f t="shared" si="13"/>
-        <v>10935</v>
+        <v>10658.75</v>
       </c>
       <c r="P64" s="8">
         <f t="shared" si="14"/>
-        <v>501</v>
+        <v>562</v>
       </c>
       <c r="Q64" s="9">
         <f t="shared" si="15"/>
-        <v>412778.7125748503</v>
+        <v>405436.70284697507</v>
       </c>
       <c r="R64" s="9">
         <f t="shared" si="16"/>
-        <v>458.35329341317362</v>
+        <v>455.17793594306056</v>
       </c>
       <c r="S64" s="10">
         <f t="shared" si="17"/>
-        <v>0.43245768534274825</v>
+        <v>0.43441929189169565</v>
       </c>
       <c r="T64" s="11">
         <v>10280587</v>
@@ -15955,12 +16519,24 @@
       <c r="BI64" s="13">
         <v>0.38263742063344391</v>
       </c>
-      <c r="BJ64" s="11"/>
-      <c r="BK64" s="11"/>
-      <c r="BL64" s="11"/>
-      <c r="BM64" s="12"/>
-      <c r="BN64" s="12"/>
-      <c r="BO64" s="13"/>
+      <c r="BJ64" s="11">
+        <v>7017764</v>
+      </c>
+      <c r="BK64" s="11">
+        <v>8725</v>
+      </c>
+      <c r="BL64" s="11">
+        <v>61</v>
+      </c>
+      <c r="BM64" s="12">
+        <v>345135.93442622951</v>
+      </c>
+      <c r="BN64" s="12">
+        <v>429.09836065573768</v>
+      </c>
+      <c r="BO64" s="13">
+        <v>0.44815053773432728</v>
+      </c>
       <c r="BP64" s="11"/>
       <c r="BQ64" s="11"/>
       <c r="BR64" s="11"/>
@@ -16029,27 +16605,27 @@
       </c>
       <c r="N65" s="8">
         <f t="shared" si="12"/>
-        <v>9442024</v>
+        <v>9353513.875</v>
       </c>
       <c r="O65" s="8">
         <f t="shared" si="13"/>
-        <v>13088.142857142857</v>
+        <v>12590.75</v>
       </c>
       <c r="P65" s="8">
         <f t="shared" si="14"/>
-        <v>493</v>
+        <v>555</v>
       </c>
       <c r="Q65" s="9">
         <f t="shared" si="15"/>
-        <v>402195.74847870186</v>
+        <v>404476.27567567566</v>
       </c>
       <c r="R65" s="9">
         <f t="shared" si="16"/>
-        <v>557.50709939148066</v>
+        <v>544.46486486486492</v>
       </c>
       <c r="S65" s="10">
         <f t="shared" si="17"/>
-        <v>0.47802324360386461</v>
+        <v>0.4695416915621744</v>
       </c>
       <c r="T65" s="11">
         <v>9995292</v>
@@ -16177,12 +16753,24 @@
       <c r="BI65" s="13">
         <v>0.38877589295329629</v>
       </c>
-      <c r="BJ65" s="11"/>
-      <c r="BK65" s="11"/>
-      <c r="BL65" s="11"/>
-      <c r="BM65" s="12"/>
-      <c r="BN65" s="12"/>
-      <c r="BO65" s="13"/>
+      <c r="BJ65" s="11">
+        <v>8733943</v>
+      </c>
+      <c r="BK65" s="11">
+        <v>9109</v>
+      </c>
+      <c r="BL65" s="11">
+        <v>62</v>
+      </c>
+      <c r="BM65" s="12">
+        <v>422610.14516129042</v>
+      </c>
+      <c r="BN65" s="12">
+        <v>440.75806451612902</v>
+      </c>
+      <c r="BO65" s="13">
+        <v>0.41017082727034287</v>
+      </c>
       <c r="BP65" s="11"/>
       <c r="BQ65" s="11"/>
       <c r="BR65" s="11"/>
@@ -16251,27 +16839,27 @@
       </c>
       <c r="N66" s="8">
         <f t="shared" si="12"/>
-        <v>8672073.8571428563</v>
+        <v>8428097.625</v>
       </c>
       <c r="O66" s="8">
         <f t="shared" si="13"/>
-        <v>16253.142857142857</v>
+        <v>16486.625</v>
       </c>
       <c r="P66" s="8">
         <f t="shared" si="14"/>
-        <v>492</v>
+        <v>554</v>
       </c>
       <c r="Q66" s="9">
         <f t="shared" si="15"/>
-        <v>370149.49390243902</v>
+        <v>365116.14259927801</v>
       </c>
       <c r="R66" s="9">
         <f t="shared" si="16"/>
-        <v>693.73170731707319</v>
+        <v>714.22202166064983</v>
       </c>
       <c r="S66" s="10">
         <f t="shared" si="17"/>
-        <v>0.54209382316524801</v>
+        <v>0.5566167687374125</v>
       </c>
       <c r="T66" s="11">
         <v>8918165</v>
@@ -16399,12 +16987,24 @@
       <c r="BI66" s="13">
         <v>0.6555695153186798</v>
       </c>
-      <c r="BJ66" s="11"/>
-      <c r="BK66" s="11"/>
-      <c r="BL66" s="11"/>
-      <c r="BM66" s="12"/>
-      <c r="BN66" s="12"/>
-      <c r="BO66" s="13"/>
+      <c r="BJ66" s="11">
+        <v>6720264</v>
+      </c>
+      <c r="BK66" s="11">
+        <v>18121</v>
+      </c>
+      <c r="BL66" s="11">
+        <v>62</v>
+      </c>
+      <c r="BM66" s="12">
+        <v>325174.06451612897</v>
+      </c>
+      <c r="BN66" s="12">
+        <v>876.82258064516122</v>
+      </c>
+      <c r="BO66" s="13">
+        <v>0.65827738774256395</v>
+      </c>
       <c r="BP66" s="11"/>
       <c r="BQ66" s="11"/>
       <c r="BR66" s="11"/>
@@ -16473,27 +17073,27 @@
       </c>
       <c r="N67" s="8">
         <f t="shared" si="12"/>
-        <v>4921576.7142857146</v>
+        <v>4879102.5</v>
       </c>
       <c r="O67" s="8">
         <f t="shared" si="13"/>
-        <v>11369.142857142857</v>
+        <v>10909.125</v>
       </c>
       <c r="P67" s="8">
         <f t="shared" si="14"/>
-        <v>484</v>
+        <v>545</v>
       </c>
       <c r="Q67" s="9">
         <f t="shared" si="15"/>
-        <v>213539.48553719008</v>
+        <v>214859.55963302753</v>
       </c>
       <c r="R67" s="9">
         <f t="shared" si="16"/>
-        <v>493.28925619834706</v>
+        <v>480.40183486238539</v>
       </c>
       <c r="S67" s="10">
         <f t="shared" si="17"/>
-        <v>0.61017466135145193</v>
+        <v>0.59912062748123884</v>
       </c>
       <c r="T67" s="11">
         <v>5935742</v>
@@ -16621,12 +17221,24 @@
       <c r="BI67" s="13">
         <v>0.62751340238667341</v>
       </c>
-      <c r="BJ67" s="11"/>
-      <c r="BK67" s="11"/>
-      <c r="BL67" s="11"/>
-      <c r="BM67" s="12"/>
-      <c r="BN67" s="12"/>
-      <c r="BO67" s="13"/>
+      <c r="BJ67" s="11">
+        <v>4581783</v>
+      </c>
+      <c r="BK67" s="11">
+        <v>7689</v>
+      </c>
+      <c r="BL67" s="11">
+        <v>61</v>
+      </c>
+      <c r="BM67" s="12">
+        <v>225333.59016393439</v>
+      </c>
+      <c r="BN67" s="12">
+        <v>378.14754098360658</v>
+      </c>
+      <c r="BO67" s="13">
+        <v>0.52174239038974679</v>
+      </c>
       <c r="BP67" s="11"/>
       <c r="BQ67" s="11"/>
       <c r="BR67" s="11"/>
@@ -16695,27 +17307,27 @@
       </c>
       <c r="N68" s="8">
         <f t="shared" si="12"/>
-        <v>5929494.2857142854</v>
+        <v>5916400.5</v>
       </c>
       <c r="O68" s="8">
         <f t="shared" si="13"/>
-        <v>14879.142857142857</v>
+        <v>13898.375</v>
       </c>
       <c r="P68" s="8">
         <f t="shared" si="14"/>
-        <v>496</v>
+        <v>557</v>
       </c>
       <c r="Q68" s="9">
         <f t="shared" si="15"/>
-        <v>251047.13709677418</v>
+        <v>254925.69479353679</v>
       </c>
       <c r="R68" s="9">
         <f t="shared" si="16"/>
-        <v>629.96370967741939</v>
+        <v>598.85278276481154</v>
       </c>
       <c r="S68" s="10">
         <f t="shared" si="17"/>
-        <v>0.632147160874588</v>
+        <v>0.6085998229198718</v>
       </c>
       <c r="T68" s="11">
         <v>6055582</v>
@@ -16843,12 +17455,24 @@
       <c r="BI68" s="13">
         <v>0.58920588397112894</v>
       </c>
-      <c r="BJ68" s="11"/>
-      <c r="BK68" s="11"/>
-      <c r="BL68" s="11"/>
-      <c r="BM68" s="12"/>
-      <c r="BN68" s="12"/>
-      <c r="BO68" s="13"/>
+      <c r="BJ68" s="11">
+        <v>5824744</v>
+      </c>
+      <c r="BK68" s="11">
+        <v>7033</v>
+      </c>
+      <c r="BL68" s="11">
+        <v>61</v>
+      </c>
+      <c r="BM68" s="12">
+        <v>286462.81967213121</v>
+      </c>
+      <c r="BN68" s="12">
+        <v>345.88524590163928</v>
+      </c>
+      <c r="BO68" s="13">
+        <v>0.44376845723685832</v>
+      </c>
       <c r="BP68" s="11"/>
       <c r="BQ68" s="11"/>
       <c r="BR68" s="11"/>
@@ -16917,27 +17541,27 @@
       </c>
       <c r="N69" s="8">
         <f t="shared" si="12"/>
-        <v>5876495.8571428573</v>
+        <v>5828218</v>
       </c>
       <c r="O69" s="8">
         <f t="shared" si="13"/>
-        <v>15107.714285714286</v>
+        <v>14943.125</v>
       </c>
       <c r="P69" s="8">
         <f t="shared" si="14"/>
-        <v>494</v>
+        <v>555</v>
       </c>
       <c r="Q69" s="9">
         <f t="shared" si="15"/>
-        <v>249810.55263157896</v>
+        <v>252031.04864864863</v>
       </c>
       <c r="R69" s="9">
         <f t="shared" si="16"/>
-        <v>642.23076923076917</v>
+        <v>646.18918918918916</v>
       </c>
       <c r="S69" s="10">
         <f t="shared" si="17"/>
-        <v>0.64234714537371318</v>
+        <v>0.64179583398334472</v>
       </c>
       <c r="T69" s="11">
         <v>4627717</v>
@@ -17065,12 +17689,24 @@
       <c r="BI69" s="13">
         <v>0.64885449302710929</v>
       </c>
-      <c r="BJ69" s="11"/>
-      <c r="BK69" s="11"/>
-      <c r="BL69" s="11"/>
-      <c r="BM69" s="12"/>
-      <c r="BN69" s="12"/>
-      <c r="BO69" s="13"/>
+      <c r="BJ69" s="11">
+        <v>5490273</v>
+      </c>
+      <c r="BK69" s="11">
+        <v>13791</v>
+      </c>
+      <c r="BL69" s="11">
+        <v>61</v>
+      </c>
+      <c r="BM69" s="12">
+        <v>270013.42622950819</v>
+      </c>
+      <c r="BN69" s="12">
+        <v>678.24590163934431</v>
+      </c>
+      <c r="BO69" s="13">
+        <v>0.63793665425076584</v>
+      </c>
       <c r="BP69" s="11"/>
       <c r="BQ69" s="11"/>
       <c r="BR69" s="11"/>
@@ -17139,27 +17775,27 @@
       </c>
       <c r="N70" s="8">
         <f t="shared" si="12"/>
-        <v>4053747.1428571427</v>
+        <v>3947243.25</v>
       </c>
       <c r="O70" s="8">
         <f t="shared" si="13"/>
-        <v>10642.571428571429</v>
+        <v>10343.25</v>
       </c>
       <c r="P70" s="8">
         <f t="shared" si="14"/>
-        <v>350</v>
+        <v>393</v>
       </c>
       <c r="Q70" s="9">
         <f t="shared" si="15"/>
-        <v>243224.82857142857</v>
+        <v>241053.02290076335</v>
       </c>
       <c r="R70" s="9">
         <f t="shared" si="16"/>
-        <v>638.5542857142857</v>
+        <v>631.64885496183206</v>
       </c>
       <c r="S70" s="10">
         <f t="shared" si="17"/>
-        <v>0.64849330674982752</v>
+        <v>0.64799104349749836</v>
       </c>
       <c r="T70" s="11">
         <v>640528</v>
@@ -17287,12 +17923,24 @@
       <c r="BI70" s="13">
         <v>0.65968982763725237</v>
       </c>
-      <c r="BJ70" s="11"/>
-      <c r="BK70" s="11"/>
-      <c r="BL70" s="11"/>
-      <c r="BM70" s="12"/>
-      <c r="BN70" s="12"/>
-      <c r="BO70" s="13"/>
+      <c r="BJ70" s="11">
+        <v>3201716</v>
+      </c>
+      <c r="BK70" s="11">
+        <v>8248</v>
+      </c>
+      <c r="BL70" s="11">
+        <v>43</v>
+      </c>
+      <c r="BM70" s="12">
+        <v>223375.53488372089</v>
+      </c>
+      <c r="BN70" s="12">
+        <v>575.44186046511629</v>
+      </c>
+      <c r="BO70" s="13">
+        <v>0.64447520073119435</v>
+      </c>
       <c r="BP70" s="11"/>
       <c r="BQ70" s="11"/>
       <c r="BR70" s="11"/>
@@ -17697,27 +18345,27 @@
       </c>
       <c r="N73" s="8">
         <f t="shared" si="12"/>
-        <v>4145513.5714285714</v>
+        <v>3899899.125</v>
       </c>
       <c r="O73" s="8">
         <f t="shared" si="13"/>
-        <v>6933.7142857142853</v>
+        <v>6421.75</v>
       </c>
       <c r="P73" s="8">
         <f t="shared" si="14"/>
-        <v>475</v>
+        <v>531</v>
       </c>
       <c r="Q73" s="9">
         <f t="shared" si="15"/>
-        <v>183275.33684210526</v>
+        <v>176266.62711864407</v>
       </c>
       <c r="R73" s="9">
         <f t="shared" si="16"/>
-        <v>306.54315789473685</v>
+        <v>290.24858757062145</v>
       </c>
       <c r="S73" s="10">
         <f t="shared" si="17"/>
-        <v>0.50444141768251971</v>
+        <v>0.49763624047220473</v>
       </c>
       <c r="T73" s="11">
         <v>6999813</v>
@@ -17845,12 +18493,24 @@
       <c r="BI73" s="13">
         <v>0.41853250306689771</v>
       </c>
-      <c r="BJ73" s="11"/>
-      <c r="BK73" s="11"/>
-      <c r="BL73" s="11"/>
-      <c r="BM73" s="12"/>
-      <c r="BN73" s="12"/>
-      <c r="BO73" s="13"/>
+      <c r="BJ73" s="11">
+        <v>2180598</v>
+      </c>
+      <c r="BK73" s="11">
+        <v>2838</v>
+      </c>
+      <c r="BL73" s="11">
+        <v>56</v>
+      </c>
+      <c r="BM73" s="12">
+        <v>116817.75</v>
+      </c>
+      <c r="BN73" s="12">
+        <v>152.03571428571431</v>
+      </c>
+      <c r="BO73" s="13">
+        <v>0.45</v>
+      </c>
       <c r="BP73" s="11"/>
       <c r="BQ73" s="11"/>
       <c r="BR73" s="11"/>
@@ -17919,27 +18579,27 @@
       </c>
       <c r="N74" s="8">
         <f t="shared" si="12"/>
-        <v>4069702.8571428573</v>
+        <v>3763396.25</v>
       </c>
       <c r="O74" s="8">
         <f t="shared" si="13"/>
-        <v>6191</v>
+        <v>5604.25</v>
       </c>
       <c r="P74" s="8">
         <f t="shared" si="14"/>
-        <v>426</v>
+        <v>467</v>
       </c>
       <c r="Q74" s="9">
         <f t="shared" si="15"/>
-        <v>200619.15492957749</v>
+        <v>193407.9443254818</v>
       </c>
       <c r="R74" s="9">
         <f t="shared" si="16"/>
-        <v>305.1901408450704</v>
+        <v>288.01284796573879</v>
       </c>
       <c r="S74" s="10">
         <f t="shared" si="17"/>
-        <v>0.46253301866048979</v>
+        <v>0.45245332357218404</v>
       </c>
       <c r="T74" s="11">
         <v>6713836</v>
@@ -18067,12 +18727,24 @@
       <c r="BI74" s="13">
         <v>0.46521889448722958</v>
       </c>
-      <c r="BJ74" s="11"/>
-      <c r="BK74" s="11"/>
-      <c r="BL74" s="11"/>
-      <c r="BM74" s="12"/>
-      <c r="BN74" s="12"/>
-      <c r="BO74" s="13"/>
+      <c r="BJ74" s="11">
+        <v>1619250</v>
+      </c>
+      <c r="BK74" s="11">
+        <v>1497</v>
+      </c>
+      <c r="BL74" s="11">
+        <v>41</v>
+      </c>
+      <c r="BM74" s="12">
+        <v>118481.7073170732</v>
+      </c>
+      <c r="BN74" s="12">
+        <v>109.5365853658537</v>
+      </c>
+      <c r="BO74" s="13">
+        <v>0.38189545795404362</v>
+      </c>
       <c r="BP74" s="11"/>
       <c r="BQ74" s="11"/>
       <c r="BR74" s="11"/>
@@ -18141,27 +18813,27 @@
       </c>
       <c r="N75" s="8">
         <f t="shared" si="12"/>
-        <v>1080582.7628571428</v>
+        <v>1038565.9175</v>
       </c>
       <c r="O75" s="8">
         <f t="shared" si="13"/>
-        <v>153736.85714285713</v>
+        <v>147691.5</v>
       </c>
       <c r="P75" s="8">
         <f t="shared" si="14"/>
-        <v>499</v>
+        <v>554</v>
       </c>
       <c r="Q75" s="9">
         <f t="shared" si="15"/>
-        <v>45475.426893787575</v>
+        <v>44992.025306859206</v>
       </c>
       <c r="R75" s="9">
         <f t="shared" si="16"/>
-        <v>6469.8877755511021</v>
+        <v>6398.1877256317694</v>
       </c>
       <c r="S75" s="10">
         <f t="shared" si="17"/>
-        <v>4.8135973072996023</v>
+        <v>4.8107413076772536</v>
       </c>
       <c r="T75" s="11">
         <v>1253986.8999999999</v>
@@ -18289,12 +18961,24 @@
       <c r="BI75" s="13">
         <v>4.6623727098776646</v>
       </c>
-      <c r="BJ75" s="11"/>
-      <c r="BK75" s="11"/>
-      <c r="BL75" s="11"/>
-      <c r="BM75" s="12"/>
-      <c r="BN75" s="12"/>
-      <c r="BO75" s="13"/>
+      <c r="BJ75" s="11">
+        <v>744448</v>
+      </c>
+      <c r="BK75" s="11">
+        <v>105374</v>
+      </c>
+      <c r="BL75" s="11">
+        <v>55</v>
+      </c>
+      <c r="BM75" s="12">
+        <v>40606.254545454547</v>
+      </c>
+      <c r="BN75" s="12">
+        <v>5747.6727272727276</v>
+      </c>
+      <c r="BO75" s="13">
+        <v>4.7907493103208107</v>
+      </c>
       <c r="BP75" s="11"/>
       <c r="BQ75" s="11"/>
       <c r="BR75" s="11"/>
@@ -18363,27 +19047,27 @@
       </c>
       <c r="N76" s="8">
         <f t="shared" si="12"/>
-        <v>3117399.6</v>
+        <v>3003257.2749999999</v>
       </c>
       <c r="O76" s="8">
         <f t="shared" si="13"/>
-        <v>54242.571428571428</v>
+        <v>51741.5</v>
       </c>
       <c r="P76" s="8">
         <f t="shared" si="14"/>
-        <v>506</v>
+        <v>566</v>
       </c>
       <c r="Q76" s="9">
         <f t="shared" si="15"/>
-        <v>129378.2442687747</v>
+        <v>127346.59823321554</v>
       </c>
       <c r="R76" s="9">
         <f t="shared" si="16"/>
-        <v>2251.1739130434785</v>
+        <v>2193.9858657243813</v>
       </c>
       <c r="S76" s="10">
         <f t="shared" si="17"/>
-        <v>1.6713747102303447</v>
+        <v>1.6606342419609244</v>
       </c>
       <c r="T76" s="11">
         <v>3600483.2</v>
@@ -18511,12 +19195,24 @@
       <c r="BI76" s="13">
         <v>1.807237123335607</v>
       </c>
-      <c r="BJ76" s="11"/>
-      <c r="BK76" s="11"/>
-      <c r="BL76" s="11"/>
-      <c r="BM76" s="12"/>
-      <c r="BN76" s="12"/>
-      <c r="BO76" s="13"/>
+      <c r="BJ76" s="11">
+        <v>2204261</v>
+      </c>
+      <c r="BK76" s="11">
+        <v>34234</v>
+      </c>
+      <c r="BL76" s="11">
+        <v>60</v>
+      </c>
+      <c r="BM76" s="12">
+        <v>110213.05</v>
+      </c>
+      <c r="BN76" s="12">
+        <v>1711.7</v>
+      </c>
+      <c r="BO76" s="13">
+        <v>1.585450964074981</v>
+      </c>
       <c r="BP76" s="11"/>
       <c r="BQ76" s="11"/>
       <c r="BR76" s="11"/>
@@ -18585,27 +19281,27 @@
       </c>
       <c r="N77" s="8">
         <f t="shared" si="12"/>
-        <v>4492558.4285714282</v>
+        <v>4348357.5</v>
       </c>
       <c r="O77" s="8">
         <f t="shared" si="13"/>
-        <v>21849.285714285714</v>
+        <v>21563.75</v>
       </c>
       <c r="P77" s="8">
         <f t="shared" si="14"/>
-        <v>517</v>
+        <v>580</v>
       </c>
       <c r="Q77" s="9">
         <f t="shared" si="15"/>
-        <v>182483.03094777564</v>
+        <v>179932.03448275864</v>
       </c>
       <c r="R77" s="9">
         <f t="shared" si="16"/>
-        <v>887.4951644100579</v>
+        <v>892.29310344827582</v>
       </c>
       <c r="S77" s="10">
         <f t="shared" si="17"/>
-        <v>0.88230401229994615</v>
+        <v>0.89364060366177678</v>
       </c>
       <c r="T77" s="11">
         <v>4959341</v>
@@ -18733,12 +19429,24 @@
       <c r="BI77" s="13">
         <v>1.0130157868113481</v>
       </c>
-      <c r="BJ77" s="11"/>
-      <c r="BK77" s="11"/>
-      <c r="BL77" s="11"/>
-      <c r="BM77" s="12"/>
-      <c r="BN77" s="12"/>
-      <c r="BO77" s="13"/>
+      <c r="BJ77" s="11">
+        <v>3338951</v>
+      </c>
+      <c r="BK77" s="11">
+        <v>19565</v>
+      </c>
+      <c r="BL77" s="11">
+        <v>63</v>
+      </c>
+      <c r="BM77" s="12">
+        <v>158997.66666666669</v>
+      </c>
+      <c r="BN77" s="12">
+        <v>931.66666666666663</v>
+      </c>
+      <c r="BO77" s="13">
+        <v>0.97299674319459106</v>
+      </c>
       <c r="BP77" s="11"/>
       <c r="BQ77" s="11"/>
       <c r="BR77" s="11"/>
@@ -18807,27 +19515,27 @@
       </c>
       <c r="N78" s="8">
         <f t="shared" si="12"/>
-        <v>5124027.4285714282</v>
+        <v>4903196.375</v>
       </c>
       <c r="O78" s="8">
         <f t="shared" si="13"/>
-        <v>35952.571428571428</v>
+        <v>34376.75</v>
       </c>
       <c r="P78" s="8">
         <f t="shared" si="14"/>
-        <v>520</v>
+        <v>581</v>
       </c>
       <c r="Q78" s="9">
         <f t="shared" si="15"/>
-        <v>206931.87692307692</v>
+        <v>202541.67469879516</v>
       </c>
       <c r="R78" s="9">
         <f t="shared" si="16"/>
-        <v>1451.9307692307693</v>
+        <v>1420.0378657487092</v>
       </c>
       <c r="S78" s="10">
         <f t="shared" si="17"/>
-        <v>1.0669598800667122</v>
+        <v>1.0660843399011115</v>
       </c>
       <c r="T78" s="11">
         <v>5415922</v>
@@ -18955,12 +19663,24 @@
       <c r="BI78" s="13">
         <v>1.100967519013925</v>
       </c>
-      <c r="BJ78" s="11"/>
-      <c r="BK78" s="11"/>
-      <c r="BL78" s="11"/>
-      <c r="BM78" s="12"/>
-      <c r="BN78" s="12"/>
-      <c r="BO78" s="13"/>
+      <c r="BJ78" s="11">
+        <v>3357379</v>
+      </c>
+      <c r="BK78" s="11">
+        <v>23346</v>
+      </c>
+      <c r="BL78" s="11">
+        <v>61</v>
+      </c>
+      <c r="BM78" s="12">
+        <v>165117</v>
+      </c>
+      <c r="BN78" s="12">
+        <v>1148.1639344262289</v>
+      </c>
+      <c r="BO78" s="13">
+        <v>1.0599555587419069</v>
+      </c>
       <c r="BP78" s="11"/>
       <c r="BQ78" s="11"/>
       <c r="BR78" s="11"/>
@@ -19029,27 +19749,27 @@
       </c>
       <c r="N79" s="8">
         <f t="shared" ref="N79:N111" si="18">IFERROR(AVERAGE(T79,Z79,AF79,AL79,AR79,AX79,BD79,BJ79,BP79,BV79,CB79,CH79)," ")</f>
-        <v>5009190.2857142854</v>
+        <v>4857321.25</v>
       </c>
       <c r="O79" s="8">
         <f t="shared" ref="O79:O111" si="19">IFERROR(AVERAGE(U79,AA79,AG79,AM79,AS79,AY79,BE79,BK79,BQ79,BW79,CC79,CI79)," ")</f>
-        <v>29844.142857142859</v>
+        <v>28527</v>
       </c>
       <c r="P79" s="8">
         <f t="shared" ref="P79:P111" si="20">IFERROR(SUM(V79,AB79,AH79,AN79,AT79,AZ79,BF79,BL79,BR79,BX79,CD79,CJ79)," ")</f>
-        <v>517</v>
+        <v>578</v>
       </c>
       <c r="Q79" s="9">
         <f t="shared" ref="Q79:Q109" si="21">IFERROR(SUM(T79,Z79,AF79,AL79,AR79,AX79,BD79,BJ79,BP79,BV79,CB79,CH79)/P79*3," ")</f>
-        <v>203468.07736943907</v>
+        <v>201688.07958477509</v>
       </c>
       <c r="R79" s="9">
         <f t="shared" ref="R79:R111" si="22">IFERROR(SUM(U79,AA79,AG79,AM79,AS79,AY79,BE79,BK79,BQ79,BW79,CC79,CI79)/P79*3," ")</f>
-        <v>1212.2379110251452</v>
+        <v>1184.5121107266436</v>
       </c>
       <c r="S79" s="10">
         <f t="shared" ref="S79:S111" si="23">IFERROR(AVERAGE(Y79,AE79,AK79,AQ79,AW79,BC79,BI79,BO79,BU79,CA79,CG79,CM79)," ")</f>
-        <v>0.98467656584456709</v>
+        <v>0.97508965710472684</v>
       </c>
       <c r="T79" s="11">
         <v>5601093</v>
@@ -19177,12 +19897,24 @@
       <c r="BI79" s="13">
         <v>0.97191948977312792</v>
       </c>
-      <c r="BJ79" s="11"/>
-      <c r="BK79" s="11"/>
-      <c r="BL79" s="11"/>
-      <c r="BM79" s="12"/>
-      <c r="BN79" s="12"/>
-      <c r="BO79" s="13"/>
+      <c r="BJ79" s="11">
+        <v>3794238</v>
+      </c>
+      <c r="BK79" s="11">
+        <v>19307</v>
+      </c>
+      <c r="BL79" s="11">
+        <v>61</v>
+      </c>
+      <c r="BM79" s="12">
+        <v>186601.86885245901</v>
+      </c>
+      <c r="BN79" s="12">
+        <v>949.52459016393448</v>
+      </c>
+      <c r="BO79" s="13">
+        <v>0.90798129592584531</v>
+      </c>
       <c r="BP79" s="11"/>
       <c r="BQ79" s="11"/>
       <c r="BR79" s="11"/>
@@ -19251,27 +19983,27 @@
       </c>
       <c r="N80" s="8">
         <f t="shared" si="18"/>
-        <v>5210447.8571428573</v>
+        <v>5147925</v>
       </c>
       <c r="O80" s="8">
         <f t="shared" si="19"/>
-        <v>169181.14285714287</v>
+        <v>165743.625</v>
       </c>
       <c r="P80" s="8">
         <f t="shared" si="20"/>
-        <v>487</v>
+        <v>546</v>
       </c>
       <c r="Q80" s="9">
         <f t="shared" si="21"/>
-        <v>224680.50308008216</v>
+        <v>226282.41758241755</v>
       </c>
       <c r="R80" s="9">
         <f t="shared" si="22"/>
-        <v>7295.2854209445577</v>
+        <v>7285.4340659340651</v>
       </c>
       <c r="S80" s="10">
         <f t="shared" si="23"/>
-        <v>2.29078862800311</v>
+        <v>2.2804400544006733</v>
       </c>
       <c r="T80" s="11">
         <v>5213937</v>
@@ -19399,12 +20131,24 @@
       <c r="BI80" s="13">
         <v>2.3341179045957952</v>
       </c>
-      <c r="BJ80" s="11"/>
-      <c r="BK80" s="11"/>
-      <c r="BL80" s="11"/>
-      <c r="BM80" s="12"/>
-      <c r="BN80" s="12"/>
-      <c r="BO80" s="13"/>
+      <c r="BJ80" s="11">
+        <v>4710265</v>
+      </c>
+      <c r="BK80" s="11">
+        <v>141681</v>
+      </c>
+      <c r="BL80" s="11">
+        <v>59</v>
+      </c>
+      <c r="BM80" s="12">
+        <v>239505</v>
+      </c>
+      <c r="BN80" s="12">
+        <v>7204.1186440677984</v>
+      </c>
+      <c r="BO80" s="13">
+        <v>2.2080000391836161</v>
+      </c>
       <c r="BP80" s="11"/>
       <c r="BQ80" s="11"/>
       <c r="BR80" s="11"/>
@@ -19473,27 +20217,27 @@
       </c>
       <c r="N81" s="8">
         <f t="shared" si="18"/>
-        <v>2769246.7142857141</v>
+        <v>2751672.125</v>
       </c>
       <c r="O81" s="8">
         <f t="shared" si="19"/>
-        <v>57078.142857142855</v>
+        <v>55670.75</v>
       </c>
       <c r="P81" s="8">
         <f t="shared" si="20"/>
-        <v>478</v>
+        <v>538</v>
       </c>
       <c r="Q81" s="9">
         <f t="shared" si="21"/>
-        <v>121661.46652719665</v>
+        <v>122751.17286245353</v>
       </c>
       <c r="R81" s="9">
         <f t="shared" si="22"/>
-        <v>2507.6171548117154</v>
+        <v>2483.4535315985131</v>
       </c>
       <c r="S81" s="10">
         <f t="shared" si="23"/>
-        <v>1.8385265627686549</v>
+        <v>1.8186638349710138</v>
       </c>
       <c r="T81" s="11">
         <v>3606826</v>
@@ -19621,12 +20365,24 @@
       <c r="BI81" s="13">
         <v>1.841295332436494</v>
       </c>
-      <c r="BJ81" s="11"/>
-      <c r="BK81" s="11"/>
-      <c r="BL81" s="11"/>
-      <c r="BM81" s="12"/>
-      <c r="BN81" s="12"/>
-      <c r="BO81" s="13"/>
+      <c r="BJ81" s="11">
+        <v>2628650</v>
+      </c>
+      <c r="BK81" s="11">
+        <v>45819</v>
+      </c>
+      <c r="BL81" s="11">
+        <v>60</v>
+      </c>
+      <c r="BM81" s="12">
+        <v>131432.5</v>
+      </c>
+      <c r="BN81" s="12">
+        <v>2290.9499999999998</v>
+      </c>
+      <c r="BO81" s="13">
+        <v>1.679624740387526</v>
+      </c>
       <c r="BP81" s="11"/>
       <c r="BQ81" s="11"/>
       <c r="BR81" s="11"/>
@@ -19695,27 +20451,27 @@
       </c>
       <c r="N82" s="8">
         <f t="shared" si="18"/>
-        <v>2846613.8571428573</v>
+        <v>2829917.25</v>
       </c>
       <c r="O82" s="8">
         <f t="shared" si="19"/>
-        <v>52449.857142857145</v>
+        <v>51810.625</v>
       </c>
       <c r="P82" s="8">
         <f t="shared" si="20"/>
-        <v>483</v>
+        <v>543</v>
       </c>
       <c r="Q82" s="9">
         <f t="shared" si="21"/>
-        <v>123765.81987577639</v>
+        <v>125079.21546961325</v>
       </c>
       <c r="R82" s="9">
         <f t="shared" si="22"/>
-        <v>2280.4285714285716</v>
+        <v>2289.9723756906078</v>
       </c>
       <c r="S82" s="10">
         <f t="shared" si="23"/>
-        <v>1.7412318770756035</v>
+        <v>1.733819797305312</v>
       </c>
       <c r="T82" s="11">
         <v>4247045</v>
@@ -19843,12 +20599,24 @@
       <c r="BI82" s="13">
         <v>1.782699714767876</v>
       </c>
-      <c r="BJ82" s="11"/>
-      <c r="BK82" s="11"/>
-      <c r="BL82" s="11"/>
-      <c r="BM82" s="12"/>
-      <c r="BN82" s="12"/>
-      <c r="BO82" s="13"/>
+      <c r="BJ82" s="11">
+        <v>2713041</v>
+      </c>
+      <c r="BK82" s="11">
+        <v>47336</v>
+      </c>
+      <c r="BL82" s="11">
+        <v>60</v>
+      </c>
+      <c r="BM82" s="12">
+        <v>135652.04999999999</v>
+      </c>
+      <c r="BN82" s="12">
+        <v>2366.8000000000002</v>
+      </c>
+      <c r="BO82" s="13">
+        <v>1.681935238913272</v>
+      </c>
       <c r="BP82" s="11"/>
       <c r="BQ82" s="11"/>
       <c r="BR82" s="11"/>
@@ -19917,27 +20685,27 @@
       </c>
       <c r="N83" s="8">
         <f t="shared" si="18"/>
-        <v>2359682.0714285714</v>
+        <v>2363512.0625</v>
       </c>
       <c r="O83" s="8">
         <f t="shared" si="19"/>
-        <v>67984.857142857145</v>
+        <v>67211.125</v>
       </c>
       <c r="P83" s="8">
         <f t="shared" si="20"/>
-        <v>478</v>
+        <v>538</v>
       </c>
       <c r="Q83" s="9">
         <f t="shared" si="21"/>
-        <v>103668.04079497908</v>
+        <v>105435.48234200744</v>
       </c>
       <c r="R83" s="9">
         <f t="shared" si="22"/>
-        <v>2986.7824267782426</v>
+        <v>2998.2657992565055</v>
       </c>
       <c r="S83" s="10">
         <f t="shared" si="23"/>
-        <v>2.1601420552063963</v>
+        <v>2.1459182613547423</v>
       </c>
       <c r="T83" s="11">
         <v>3362634.5</v>
@@ -20065,12 +20833,24 @@
       <c r="BI83" s="13">
         <v>2.2957450113742661</v>
       </c>
-      <c r="BJ83" s="11"/>
-      <c r="BK83" s="11"/>
-      <c r="BL83" s="11"/>
-      <c r="BM83" s="12"/>
-      <c r="BN83" s="12"/>
-      <c r="BO83" s="13"/>
+      <c r="BJ83" s="11">
+        <v>2390322</v>
+      </c>
+      <c r="BK83" s="11">
+        <v>61795</v>
+      </c>
+      <c r="BL83" s="11">
+        <v>60</v>
+      </c>
+      <c r="BM83" s="12">
+        <v>119516.1</v>
+      </c>
+      <c r="BN83" s="12">
+        <v>3089.75</v>
+      </c>
+      <c r="BO83" s="13">
+        <v>2.0463517043931652</v>
+      </c>
       <c r="BP83" s="11"/>
       <c r="BQ83" s="11"/>
       <c r="BR83" s="11"/>
@@ -20139,27 +20919,27 @@
       </c>
       <c r="N84" s="8">
         <f t="shared" si="18"/>
-        <v>2194994.2142857141</v>
+        <v>2168226.9375</v>
       </c>
       <c r="O84" s="8">
         <f t="shared" si="19"/>
-        <v>156378.85714285713</v>
+        <v>152215.5</v>
       </c>
       <c r="P84" s="8">
         <f t="shared" si="20"/>
-        <v>516</v>
+        <v>578</v>
       </c>
       <c r="Q84" s="9">
         <f t="shared" si="21"/>
-        <v>89331.159883720931</v>
+        <v>90030.184256055363</v>
       </c>
       <c r="R84" s="9">
         <f t="shared" si="22"/>
-        <v>6364.2558139534885</v>
+        <v>6320.3667820069204</v>
       </c>
       <c r="S84" s="10">
         <f t="shared" si="23"/>
-        <v>3.3974354641212599</v>
+        <v>3.369441639362365</v>
       </c>
       <c r="T84" s="11">
         <v>2176614</v>
@@ -20287,12 +21067,24 @@
       <c r="BI84" s="13">
         <v>3.391589906579862</v>
       </c>
-      <c r="BJ84" s="11"/>
-      <c r="BK84" s="11"/>
-      <c r="BL84" s="11"/>
-      <c r="BM84" s="12"/>
-      <c r="BN84" s="12"/>
-      <c r="BO84" s="13"/>
+      <c r="BJ84" s="11">
+        <v>1980856</v>
+      </c>
+      <c r="BK84" s="11">
+        <v>123072</v>
+      </c>
+      <c r="BL84" s="11">
+        <v>62</v>
+      </c>
+      <c r="BM84" s="12">
+        <v>95847.870967741939</v>
+      </c>
+      <c r="BN84" s="12">
+        <v>5955.0967741935483</v>
+      </c>
+      <c r="BO84" s="13">
+        <v>3.1734848660500981</v>
+      </c>
       <c r="BP84" s="11"/>
       <c r="BQ84" s="11"/>
       <c r="BR84" s="11"/>
@@ -20361,27 +21153,27 @@
       </c>
       <c r="N85" s="8">
         <f t="shared" si="18"/>
-        <v>1250646.2857142857</v>
+        <v>1240022.5</v>
       </c>
       <c r="O85" s="8">
         <f t="shared" si="19"/>
-        <v>127335.57142857143</v>
+        <v>123738</v>
       </c>
       <c r="P85" s="8">
         <f t="shared" si="20"/>
-        <v>500</v>
+        <v>561</v>
       </c>
       <c r="Q85" s="9">
         <f t="shared" si="21"/>
-        <v>52527.144</v>
+        <v>53049.090909090912</v>
       </c>
       <c r="R85" s="9">
         <f t="shared" si="22"/>
-        <v>5348.0940000000001</v>
+        <v>5293.6042780748667</v>
       </c>
       <c r="S85" s="10">
         <f t="shared" si="23"/>
-        <v>4.1293735513478831</v>
+        <v>4.07597647651298</v>
       </c>
       <c r="T85" s="11">
         <v>1663594</v>
@@ -20509,12 +21301,24 @@
       <c r="BI85" s="13">
         <v>4.2518793262059331</v>
       </c>
-      <c r="BJ85" s="11"/>
-      <c r="BK85" s="11"/>
-      <c r="BL85" s="11"/>
-      <c r="BM85" s="12"/>
-      <c r="BN85" s="12"/>
-      <c r="BO85" s="13"/>
+      <c r="BJ85" s="11">
+        <v>1165656</v>
+      </c>
+      <c r="BK85" s="11">
+        <v>98555</v>
+      </c>
+      <c r="BL85" s="11">
+        <v>61</v>
+      </c>
+      <c r="BM85" s="12">
+        <v>57327.344262295082</v>
+      </c>
+      <c r="BN85" s="12">
+        <v>4846.9672131147536</v>
+      </c>
+      <c r="BO85" s="13">
+        <v>3.7021969526686598</v>
+      </c>
       <c r="BP85" s="11"/>
       <c r="BQ85" s="11"/>
       <c r="BR85" s="11"/>
@@ -20583,27 +21387,27 @@
       </c>
       <c r="N86" s="8">
         <f t="shared" si="18"/>
-        <v>3039042</v>
+        <v>2917235</v>
       </c>
       <c r="O86" s="8">
         <f t="shared" si="19"/>
-        <v>73537.142857142855</v>
+        <v>70208.625</v>
       </c>
       <c r="P86" s="8">
         <f t="shared" si="20"/>
-        <v>516</v>
+        <v>576</v>
       </c>
       <c r="Q86" s="9">
         <f t="shared" si="21"/>
-        <v>123681.94186046513</v>
+        <v>121551.45833333334</v>
       </c>
       <c r="R86" s="9">
         <f t="shared" si="22"/>
-        <v>2992.7906976744184</v>
+        <v>2925.359375</v>
       </c>
       <c r="S86" s="10">
         <f t="shared" si="23"/>
-        <v>1.9735126805530421</v>
+        <v>1.9666467086251602</v>
       </c>
       <c r="T86" s="11">
         <v>3712214</v>
@@ -20731,12 +21535,24 @@
       <c r="BI86" s="13">
         <v>1.930866143520318</v>
       </c>
-      <c r="BJ86" s="11"/>
-      <c r="BK86" s="11"/>
-      <c r="BL86" s="11"/>
-      <c r="BM86" s="12"/>
-      <c r="BN86" s="12"/>
-      <c r="BO86" s="13"/>
+      <c r="BJ86" s="11">
+        <v>2064586</v>
+      </c>
+      <c r="BK86" s="11">
+        <v>46909</v>
+      </c>
+      <c r="BL86" s="11">
+        <v>60</v>
+      </c>
+      <c r="BM86" s="12">
+        <v>103229.3</v>
+      </c>
+      <c r="BN86" s="12">
+        <v>2345.4499999999998</v>
+      </c>
+      <c r="BO86" s="13">
+        <v>1.9185849051299879</v>
+      </c>
       <c r="BP86" s="11"/>
       <c r="BQ86" s="11"/>
       <c r="BR86" s="11"/>
@@ -20805,27 +21621,27 @@
       </c>
       <c r="N87" s="8">
         <f t="shared" si="18"/>
-        <v>2927838.4285714286</v>
+        <v>2849558</v>
       </c>
       <c r="O87" s="8">
         <f t="shared" si="19"/>
-        <v>71327</v>
+        <v>68955.875</v>
       </c>
       <c r="P87" s="8">
         <f t="shared" si="20"/>
-        <v>510</v>
+        <v>569</v>
       </c>
       <c r="Q87" s="9">
         <f t="shared" si="21"/>
-        <v>120558.05294117649</v>
+        <v>120192.25307557118</v>
       </c>
       <c r="R87" s="9">
         <f t="shared" si="22"/>
-        <v>2936.9941176470588</v>
+        <v>2908.5079086115993</v>
       </c>
       <c r="S87" s="10">
         <f t="shared" si="23"/>
-        <v>1.9857395315727995</v>
+        <v>1.9775068976203878</v>
       </c>
       <c r="T87" s="11">
         <v>2997988</v>
@@ -20953,12 +21769,24 @@
       <c r="BI87" s="13">
         <v>2.0642103617339611</v>
       </c>
-      <c r="BJ87" s="11"/>
-      <c r="BK87" s="11"/>
-      <c r="BL87" s="11"/>
-      <c r="BM87" s="12"/>
-      <c r="BN87" s="12"/>
-      <c r="BO87" s="13"/>
+      <c r="BJ87" s="11">
+        <v>2301595</v>
+      </c>
+      <c r="BK87" s="11">
+        <v>52358</v>
+      </c>
+      <c r="BL87" s="11">
+        <v>59</v>
+      </c>
+      <c r="BM87" s="12">
+        <v>117030.2542372881</v>
+      </c>
+      <c r="BN87" s="12">
+        <v>2662.2711864406779</v>
+      </c>
+      <c r="BO87" s="13">
+        <v>1.919878459953505</v>
+      </c>
       <c r="BP87" s="11"/>
       <c r="BQ87" s="11"/>
       <c r="BR87" s="11"/>
@@ -21027,27 +21855,27 @@
       </c>
       <c r="N88" s="8">
         <f t="shared" si="18"/>
-        <v>2714721.1428571427</v>
+        <v>2611175.5</v>
       </c>
       <c r="O88" s="8">
         <f t="shared" si="19"/>
-        <v>68419.28571428571</v>
+        <v>66507.375</v>
       </c>
       <c r="P88" s="8">
         <f t="shared" si="20"/>
-        <v>512</v>
+        <v>572</v>
       </c>
       <c r="Q88" s="9">
         <f t="shared" si="21"/>
-        <v>111345.984375</v>
+        <v>109559.81118881117</v>
       </c>
       <c r="R88" s="9">
         <f t="shared" si="22"/>
-        <v>2806.259765625</v>
+        <v>2790.5192307692305</v>
       </c>
       <c r="S88" s="10">
         <f t="shared" si="23"/>
-        <v>2.0329731409740215</v>
+        <v>2.0458126236914707</v>
       </c>
       <c r="T88" s="11">
         <v>2265706</v>
@@ -21175,12 +22003,24 @@
       <c r="BI88" s="13">
         <v>2.0138742375502932</v>
       </c>
-      <c r="BJ88" s="11"/>
-      <c r="BK88" s="11"/>
-      <c r="BL88" s="11"/>
-      <c r="BM88" s="12"/>
-      <c r="BN88" s="12"/>
-      <c r="BO88" s="13"/>
+      <c r="BJ88" s="11">
+        <v>1886356</v>
+      </c>
+      <c r="BK88" s="11">
+        <v>53124</v>
+      </c>
+      <c r="BL88" s="11">
+        <v>60</v>
+      </c>
+      <c r="BM88" s="12">
+        <v>94317.8</v>
+      </c>
+      <c r="BN88" s="12">
+        <v>2656.2</v>
+      </c>
+      <c r="BO88" s="13">
+        <v>2.1356890027136139</v>
+      </c>
       <c r="BP88" s="11"/>
       <c r="BQ88" s="11"/>
       <c r="BR88" s="11"/>
@@ -21249,27 +22089,27 @@
       </c>
       <c r="N89" s="8">
         <f t="shared" si="18"/>
-        <v>3163622.9485714287</v>
+        <v>3099417.08</v>
       </c>
       <c r="O89" s="8">
         <f t="shared" si="19"/>
-        <v>30090.142857142859</v>
+        <v>29559.125</v>
       </c>
       <c r="P89" s="8">
         <f t="shared" si="20"/>
-        <v>514</v>
+        <v>572</v>
       </c>
       <c r="Q89" s="9">
         <f t="shared" si="21"/>
-        <v>129253.07766536965</v>
+        <v>130045.47188811189</v>
       </c>
       <c r="R89" s="9">
         <f t="shared" si="22"/>
-        <v>1229.3638132295719</v>
+        <v>1240.2430069930069</v>
       </c>
       <c r="S89" s="10">
         <f t="shared" si="23"/>
-        <v>1.2299359483897219</v>
+        <v>1.2331715249914792</v>
       </c>
       <c r="T89" s="11">
         <v>3721474.08</v>
@@ -21397,12 +22237,24 @@
       <c r="BI89" s="13">
         <v>1.306321844939752</v>
       </c>
-      <c r="BJ89" s="11"/>
-      <c r="BK89" s="11"/>
-      <c r="BL89" s="11"/>
-      <c r="BM89" s="12"/>
-      <c r="BN89" s="12"/>
-      <c r="BO89" s="13"/>
+      <c r="BJ89" s="11">
+        <v>2649976</v>
+      </c>
+      <c r="BK89" s="11">
+        <v>25842</v>
+      </c>
+      <c r="BL89" s="11">
+        <v>58</v>
+      </c>
+      <c r="BM89" s="12">
+        <v>137067.72413793101</v>
+      </c>
+      <c r="BN89" s="12">
+        <v>1336.655172413793</v>
+      </c>
+      <c r="BO89" s="13">
+        <v>1.2558205612037801</v>
+      </c>
       <c r="BP89" s="11"/>
       <c r="BQ89" s="11"/>
       <c r="BR89" s="11"/>
@@ -21471,27 +22323,27 @@
       </c>
       <c r="N90" s="8">
         <f t="shared" si="18"/>
-        <v>4691708.2857142854</v>
+        <v>4584779.5</v>
       </c>
       <c r="O90" s="8">
         <f t="shared" si="19"/>
-        <v>55058.142857142855</v>
+        <v>54039.5</v>
       </c>
       <c r="P90" s="8">
         <f t="shared" si="20"/>
-        <v>516</v>
+        <v>578</v>
       </c>
       <c r="Q90" s="9">
         <f t="shared" si="21"/>
-        <v>190941.61627906977</v>
+        <v>190371.46712802767</v>
       </c>
       <c r="R90" s="9">
         <f t="shared" si="22"/>
-        <v>2240.7383720930229</v>
+        <v>2243.8546712802768</v>
       </c>
       <c r="S90" s="10">
         <f t="shared" si="23"/>
-        <v>1.3856510678694072</v>
+        <v>1.3882855496773163</v>
       </c>
       <c r="T90" s="11">
         <v>4835277</v>
@@ -21619,12 +22471,24 @@
       <c r="BI90" s="13">
         <v>1.3640739320601829</v>
       </c>
-      <c r="BJ90" s="11"/>
-      <c r="BK90" s="11"/>
-      <c r="BL90" s="11"/>
-      <c r="BM90" s="12"/>
-      <c r="BN90" s="12"/>
-      <c r="BO90" s="13"/>
+      <c r="BJ90" s="11">
+        <v>3836278</v>
+      </c>
+      <c r="BK90" s="11">
+        <v>46909</v>
+      </c>
+      <c r="BL90" s="11">
+        <v>62</v>
+      </c>
+      <c r="BM90" s="12">
+        <v>185626.3548387097</v>
+      </c>
+      <c r="BN90" s="12">
+        <v>2269.7903225806449</v>
+      </c>
+      <c r="BO90" s="13">
+        <v>1.4067269223326799</v>
+      </c>
       <c r="BP90" s="11"/>
       <c r="BQ90" s="11"/>
       <c r="BR90" s="11"/>
@@ -21693,27 +22557,27 @@
       </c>
       <c r="N91" s="8">
         <f t="shared" si="18"/>
-        <v>6425648.4857142856</v>
+        <v>6342279.1749999998</v>
       </c>
       <c r="O91" s="8">
         <f t="shared" si="19"/>
-        <v>51484.571428571428</v>
+        <v>52493.75</v>
       </c>
       <c r="P91" s="8">
         <f t="shared" si="20"/>
-        <v>502</v>
+        <v>564</v>
       </c>
       <c r="Q91" s="9">
         <f t="shared" si="21"/>
-        <v>268802.02828685258</v>
+        <v>269884.22021276597</v>
       </c>
       <c r="R91" s="9">
         <f t="shared" si="22"/>
-        <v>2153.7370517928289</v>
+        <v>2233.7765957446809</v>
       </c>
       <c r="S91" s="10">
         <f t="shared" si="23"/>
-        <v>1.1403160241845023</v>
+        <v>1.1598192319406273</v>
       </c>
       <c r="T91" s="11">
         <v>7274414.3999999994</v>
@@ -21841,12 +22705,24 @@
       <c r="BI91" s="13">
         <v>1.159647761914365</v>
       </c>
-      <c r="BJ91" s="11"/>
-      <c r="BK91" s="11"/>
-      <c r="BL91" s="11"/>
-      <c r="BM91" s="12"/>
-      <c r="BN91" s="12"/>
-      <c r="BO91" s="13"/>
+      <c r="BJ91" s="11">
+        <v>5758694</v>
+      </c>
+      <c r="BK91" s="11">
+        <v>59558</v>
+      </c>
+      <c r="BL91" s="11">
+        <v>62</v>
+      </c>
+      <c r="BM91" s="12">
+        <v>278646.48387096782</v>
+      </c>
+      <c r="BN91" s="12">
+        <v>2881.83870967742</v>
+      </c>
+      <c r="BO91" s="13">
+        <v>1.2963416862335031</v>
+      </c>
       <c r="BP91" s="11"/>
       <c r="BQ91" s="11"/>
       <c r="BR91" s="11"/>
@@ -21915,27 +22791,27 @@
       </c>
       <c r="N92" s="8">
         <f t="shared" si="18"/>
-        <v>5459214.7142857146</v>
+        <v>5329734.25</v>
       </c>
       <c r="O92" s="8">
         <f t="shared" si="19"/>
-        <v>31590.285714285714</v>
+        <v>30422</v>
       </c>
       <c r="P92" s="8">
         <f t="shared" si="20"/>
-        <v>509</v>
+        <v>571</v>
       </c>
       <c r="Q92" s="9">
         <f t="shared" si="21"/>
-        <v>225232.82711198425</v>
+        <v>224016.85113835376</v>
       </c>
       <c r="R92" s="9">
         <f t="shared" si="22"/>
-        <v>1303.3320235756385</v>
+        <v>1278.6830122591944</v>
       </c>
       <c r="S92" s="10">
         <f t="shared" si="23"/>
-        <v>0.96663592200382986</v>
+        <v>0.95841364981033839</v>
       </c>
       <c r="T92" s="11">
         <v>5879996</v>
@@ -22063,12 +22939,24 @@
       <c r="BI92" s="13">
         <v>0.96487011769276232</v>
       </c>
-      <c r="BJ92" s="11"/>
-      <c r="BK92" s="11"/>
-      <c r="BL92" s="11"/>
-      <c r="BM92" s="12"/>
-      <c r="BN92" s="12"/>
-      <c r="BO92" s="13"/>
+      <c r="BJ92" s="11">
+        <v>4423371</v>
+      </c>
+      <c r="BK92" s="11">
+        <v>22244</v>
+      </c>
+      <c r="BL92" s="11">
+        <v>62</v>
+      </c>
+      <c r="BM92" s="12">
+        <v>214034.0806451613</v>
+      </c>
+      <c r="BN92" s="12">
+        <v>1076.322580645161</v>
+      </c>
+      <c r="BO92" s="13">
+        <v>0.90085774445589761</v>
+      </c>
       <c r="BP92" s="11"/>
       <c r="BQ92" s="11"/>
       <c r="BR92" s="11"/>
@@ -22137,27 +23025,27 @@
       </c>
       <c r="N93" s="8">
         <f t="shared" si="18"/>
-        <v>3518429.8171428568</v>
+        <v>3364380.6399999997</v>
       </c>
       <c r="O93" s="8">
         <f t="shared" si="19"/>
-        <v>18812.142857142859</v>
+        <v>18417</v>
       </c>
       <c r="P93" s="8">
         <f t="shared" si="20"/>
-        <v>495</v>
+        <v>557</v>
       </c>
       <c r="Q93" s="9">
         <f t="shared" si="21"/>
-        <v>149266.71951515149</v>
+        <v>144964.33637342908</v>
       </c>
       <c r="R93" s="9">
         <f t="shared" si="22"/>
-        <v>798.09090909090901</v>
+        <v>793.5511669658888</v>
       </c>
       <c r="S93" s="10">
         <f t="shared" si="23"/>
-        <v>0.91972047566423709</v>
+        <v>0.93616028900984749</v>
       </c>
       <c r="T93" s="11">
         <v>4307185.76</v>
@@ -22285,12 +23173,24 @@
       <c r="BI93" s="13">
         <v>0.97570328648023741</v>
       </c>
-      <c r="BJ93" s="11"/>
-      <c r="BK93" s="11"/>
-      <c r="BL93" s="11"/>
-      <c r="BM93" s="12"/>
-      <c r="BN93" s="12"/>
-      <c r="BO93" s="13"/>
+      <c r="BJ93" s="11">
+        <v>2286036.4</v>
+      </c>
+      <c r="BK93" s="11">
+        <v>15651</v>
+      </c>
+      <c r="BL93" s="11">
+        <v>62</v>
+      </c>
+      <c r="BM93" s="12">
+        <v>110614.66451612901</v>
+      </c>
+      <c r="BN93" s="12">
+        <v>757.30645161290317</v>
+      </c>
+      <c r="BO93" s="13">
+        <v>1.05123898242912</v>
+      </c>
       <c r="BP93" s="11"/>
       <c r="BQ93" s="11"/>
       <c r="BR93" s="11"/>
@@ -22359,27 +23259,27 @@
       </c>
       <c r="N94" s="8">
         <f t="shared" si="18"/>
-        <v>3813173.3942857138</v>
+        <v>3617827.7199999997</v>
       </c>
       <c r="O94" s="8">
         <f t="shared" si="19"/>
-        <v>13135.857142857143</v>
+        <v>12669.875</v>
       </c>
       <c r="P94" s="8">
         <f t="shared" si="20"/>
-        <v>475</v>
+        <v>533</v>
       </c>
       <c r="Q94" s="9">
         <f t="shared" si="21"/>
-        <v>168582.40269473684</v>
+        <v>162904.06243902439</v>
       </c>
       <c r="R94" s="9">
         <f t="shared" si="22"/>
-        <v>580.7431578947369</v>
+        <v>570.5009380863039</v>
       </c>
       <c r="S94" s="10">
         <f t="shared" si="23"/>
-        <v>0.74559570146365284</v>
+        <v>0.75512892895906358</v>
       </c>
       <c r="T94" s="11">
         <v>5182499.76</v>
@@ -22507,12 +23407,24 @@
       <c r="BI94" s="13">
         <v>0.80732386766920949</v>
       </c>
-      <c r="BJ94" s="11"/>
-      <c r="BK94" s="11"/>
-      <c r="BL94" s="11"/>
-      <c r="BM94" s="12"/>
-      <c r="BN94" s="12"/>
-      <c r="BO94" s="13"/>
+      <c r="BJ94" s="11">
+        <v>2250408</v>
+      </c>
+      <c r="BK94" s="11">
+        <v>9408</v>
+      </c>
+      <c r="BL94" s="11">
+        <v>58</v>
+      </c>
+      <c r="BM94" s="12">
+        <v>116400.41379310341</v>
+      </c>
+      <c r="BN94" s="12">
+        <v>486.62068965517238</v>
+      </c>
+      <c r="BO94" s="13">
+        <v>0.8218615214269388</v>
+      </c>
       <c r="BP94" s="11"/>
       <c r="BQ94" s="11"/>
       <c r="BR94" s="11"/>
@@ -22581,27 +23493,27 @@
       </c>
       <c r="N95" s="8">
         <f t="shared" si="18"/>
-        <v>2620015.2857142859</v>
+        <v>2461523.375</v>
       </c>
       <c r="O95" s="8">
         <f t="shared" si="19"/>
-        <v>16769.571428571428</v>
+        <v>15717.5</v>
       </c>
       <c r="P95" s="8">
         <f t="shared" si="20"/>
-        <v>402</v>
+        <v>441</v>
       </c>
       <c r="Q95" s="9">
         <f t="shared" si="21"/>
-        <v>136866.47014925373</v>
+        <v>133960.45578231293</v>
       </c>
       <c r="R95" s="9">
         <f t="shared" si="22"/>
-        <v>876.0223880597016</v>
+        <v>855.37414965986386</v>
       </c>
       <c r="S95" s="10">
         <f t="shared" si="23"/>
-        <v>1.01888844324309</v>
+        <v>1.016608116680072</v>
       </c>
       <c r="T95" s="11">
         <v>3447426</v>
@@ -22729,12 +23641,24 @@
       <c r="BI95" s="13">
         <v>0.98031193507352066</v>
       </c>
-      <c r="BJ95" s="11"/>
-      <c r="BK95" s="11"/>
-      <c r="BL95" s="11"/>
-      <c r="BM95" s="12"/>
-      <c r="BN95" s="12"/>
-      <c r="BO95" s="13"/>
+      <c r="BJ95" s="11">
+        <v>1352080</v>
+      </c>
+      <c r="BK95" s="11">
+        <v>8353</v>
+      </c>
+      <c r="BL95" s="11">
+        <v>39</v>
+      </c>
+      <c r="BM95" s="12">
+        <v>104006.1538461538</v>
+      </c>
+      <c r="BN95" s="12">
+        <v>642.53846153846155</v>
+      </c>
+      <c r="BO95" s="13">
+        <v>1.000645830738945</v>
+      </c>
       <c r="BP95" s="11"/>
       <c r="BQ95" s="11"/>
       <c r="BR95" s="11"/>
@@ -22803,27 +23727,27 @@
       </c>
       <c r="N96" s="8">
         <f t="shared" si="18"/>
-        <v>1639744.5714285714</v>
+        <v>1660127.625</v>
       </c>
       <c r="O96" s="8">
         <f t="shared" si="19"/>
-        <v>10644</v>
+        <v>10819</v>
       </c>
       <c r="P96" s="8">
         <f t="shared" si="20"/>
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="Q96" s="9">
         <f t="shared" si="21"/>
-        <v>115552.46979865771</v>
+        <v>117878.88461538462</v>
       </c>
       <c r="R96" s="9">
         <f t="shared" si="22"/>
-        <v>750.08053691275177</v>
+        <v>768.21301775147936</v>
       </c>
       <c r="S96" s="10">
         <f t="shared" si="23"/>
-        <v>1.0151477572689813</v>
+        <v>1.0181764603039896</v>
       </c>
       <c r="T96" s="11">
         <v>224676</v>
@@ -22951,12 +23875,24 @@
       <c r="BI96" s="13">
         <v>1.0930190479466979</v>
       </c>
-      <c r="BJ96" s="11"/>
-      <c r="BK96" s="11"/>
-      <c r="BL96" s="11"/>
-      <c r="BM96" s="12"/>
-      <c r="BN96" s="12"/>
-      <c r="BO96" s="13"/>
+      <c r="BJ96" s="11">
+        <v>1802809</v>
+      </c>
+      <c r="BK96" s="11">
+        <v>12044</v>
+      </c>
+      <c r="BL96" s="11">
+        <v>40</v>
+      </c>
+      <c r="BM96" s="12">
+        <v>135210.67499999999</v>
+      </c>
+      <c r="BN96" s="12">
+        <v>903.30000000000007</v>
+      </c>
+      <c r="BO96" s="13">
+        <v>1.039377381549047</v>
+      </c>
       <c r="BP96" s="11"/>
       <c r="BQ96" s="11"/>
       <c r="BR96" s="11"/>
@@ -23025,27 +23961,27 @@
       </c>
       <c r="N97" s="8">
         <f t="shared" si="18"/>
-        <v>3173129.2857142859</v>
+        <v>3026496.625</v>
       </c>
       <c r="O97" s="8">
         <f t="shared" si="19"/>
-        <v>13335</v>
+        <v>12784.625</v>
       </c>
       <c r="P97" s="8">
         <f t="shared" si="20"/>
-        <v>362</v>
+        <v>402</v>
       </c>
       <c r="Q97" s="9">
         <f t="shared" si="21"/>
-        <v>184076.56077348068</v>
+        <v>180686.36567164178</v>
       </c>
       <c r="R97" s="9">
         <f t="shared" si="22"/>
-        <v>773.57734806629833</v>
+        <v>763.26119402985069</v>
       </c>
       <c r="S97" s="10">
         <f t="shared" si="23"/>
-        <v>0.82015598502444809</v>
+        <v>0.82361263763801462</v>
       </c>
       <c r="T97" s="11">
         <v>3842266</v>
@@ -23173,12 +24109,24 @@
       <c r="BI97" s="13">
         <v>0.82009666849148333</v>
       </c>
-      <c r="BJ97" s="11"/>
-      <c r="BK97" s="11"/>
-      <c r="BL97" s="11"/>
-      <c r="BM97" s="12"/>
-      <c r="BN97" s="12"/>
-      <c r="BO97" s="13"/>
+      <c r="BJ97" s="11">
+        <v>2000068</v>
+      </c>
+      <c r="BK97" s="11">
+        <v>8932</v>
+      </c>
+      <c r="BL97" s="11">
+        <v>40</v>
+      </c>
+      <c r="BM97" s="12">
+        <v>150005.1</v>
+      </c>
+      <c r="BN97" s="12">
+        <v>669.90000000000009</v>
+      </c>
+      <c r="BO97" s="13">
+        <v>0.8478092059329807</v>
+      </c>
       <c r="BP97" s="11"/>
       <c r="BQ97" s="11"/>
       <c r="BR97" s="11"/>
@@ -23247,27 +24195,27 @@
       </c>
       <c r="N98" s="8">
         <f t="shared" si="18"/>
-        <v>3244265.0558571429</v>
+        <v>3061773.0488749999</v>
       </c>
       <c r="O98" s="8">
         <f t="shared" si="19"/>
-        <v>23932.571428571428</v>
+        <v>22908.75</v>
       </c>
       <c r="P98" s="8">
         <f t="shared" si="20"/>
-        <v>439</v>
+        <v>478</v>
       </c>
       <c r="Q98" s="9">
         <f t="shared" si="21"/>
-        <v>155192.63365148063</v>
+        <v>153729.19073849369</v>
       </c>
       <c r="R98" s="9">
         <f t="shared" si="22"/>
-        <v>1144.8382687927108</v>
+        <v>1150.2301255230125</v>
       </c>
       <c r="S98" s="10">
         <f t="shared" si="23"/>
-        <v>1.1061986890904687</v>
+        <v>1.1174100564859273</v>
       </c>
       <c r="T98" s="11">
         <v>5398924</v>
@@ -23395,12 +24343,24 @@
       <c r="BI98" s="13">
         <v>1.09206487346998</v>
       </c>
-      <c r="BJ98" s="11"/>
-      <c r="BK98" s="11"/>
-      <c r="BL98" s="11"/>
-      <c r="BM98" s="12"/>
-      <c r="BN98" s="12"/>
-      <c r="BO98" s="13"/>
+      <c r="BJ98" s="11">
+        <v>1784329</v>
+      </c>
+      <c r="BK98" s="11">
+        <v>15742</v>
+      </c>
+      <c r="BL98" s="11">
+        <v>39</v>
+      </c>
+      <c r="BM98" s="12">
+        <v>137256.07692307691</v>
+      </c>
+      <c r="BN98" s="12">
+        <v>1210.9230769230769</v>
+      </c>
+      <c r="BO98" s="13">
+        <v>1.195889628254138</v>
+      </c>
       <c r="BP98" s="11"/>
       <c r="BQ98" s="11"/>
       <c r="BR98" s="11"/>
@@ -23469,27 +24429,27 @@
       </c>
       <c r="N99" s="8">
         <f t="shared" si="18"/>
-        <v>4945053.8571428573</v>
+        <v>4814646.125</v>
       </c>
       <c r="O99" s="8">
         <f t="shared" si="19"/>
-        <v>25546.714285714286</v>
+        <v>24469.5</v>
       </c>
       <c r="P99" s="8">
         <f t="shared" si="20"/>
-        <v>512</v>
+        <v>573</v>
       </c>
       <c r="Q99" s="9">
         <f t="shared" si="21"/>
-        <v>202824.474609375</v>
+        <v>201660.57068062827</v>
       </c>
       <c r="R99" s="9">
         <f t="shared" si="22"/>
-        <v>1047.814453125</v>
+        <v>1024.9005235602094</v>
       </c>
       <c r="S99" s="10">
         <f t="shared" si="23"/>
-        <v>0.90813428706015287</v>
+        <v>0.89911874221086763</v>
       </c>
       <c r="T99" s="11">
         <v>4901698</v>
@@ -23617,12 +24577,24 @@
       <c r="BI99" s="13">
         <v>0.88830710588891093</v>
       </c>
-      <c r="BJ99" s="11"/>
-      <c r="BK99" s="11"/>
-      <c r="BL99" s="11"/>
-      <c r="BM99" s="12"/>
-      <c r="BN99" s="12"/>
-      <c r="BO99" s="13"/>
+      <c r="BJ99" s="11">
+        <v>3901792</v>
+      </c>
+      <c r="BK99" s="11">
+        <v>16929</v>
+      </c>
+      <c r="BL99" s="11">
+        <v>61</v>
+      </c>
+      <c r="BM99" s="12">
+        <v>191891.40983606561</v>
+      </c>
+      <c r="BN99" s="12">
+        <v>832.57377049180332</v>
+      </c>
+      <c r="BO99" s="13">
+        <v>0.83600992826587073</v>
+      </c>
       <c r="BP99" s="11"/>
       <c r="BQ99" s="11"/>
       <c r="BR99" s="11"/>
@@ -23691,27 +24663,27 @@
       </c>
       <c r="N100" s="8">
         <f t="shared" si="18"/>
-        <v>5098965.2857142854</v>
+        <v>4901312.25</v>
       </c>
       <c r="O100" s="8">
         <f t="shared" si="19"/>
-        <v>41944.857142857145</v>
+        <v>40531</v>
       </c>
       <c r="P100" s="8">
         <f t="shared" si="20"/>
-        <v>514</v>
+        <v>574</v>
       </c>
       <c r="Q100" s="9">
         <f t="shared" si="21"/>
-        <v>208323.48443579767</v>
+        <v>204932.91637630662</v>
       </c>
       <c r="R100" s="9">
         <f t="shared" si="22"/>
-        <v>1713.7003891050583</v>
+        <v>1694.6759581881533</v>
       </c>
       <c r="S100" s="10">
         <f t="shared" si="23"/>
-        <v>1.1611067884095243</v>
+        <v>1.1645773797258969</v>
       </c>
       <c r="T100" s="11">
         <v>5648674</v>
@@ -23839,12 +24811,24 @@
       <c r="BI100" s="13">
         <v>1.0681743008241891</v>
       </c>
-      <c r="BJ100" s="11"/>
-      <c r="BK100" s="11"/>
-      <c r="BL100" s="11"/>
-      <c r="BM100" s="12"/>
-      <c r="BN100" s="12"/>
-      <c r="BO100" s="13"/>
+      <c r="BJ100" s="11">
+        <v>3517741</v>
+      </c>
+      <c r="BK100" s="11">
+        <v>30634</v>
+      </c>
+      <c r="BL100" s="11">
+        <v>60</v>
+      </c>
+      <c r="BM100" s="12">
+        <v>175887.05</v>
+      </c>
+      <c r="BN100" s="12">
+        <v>1531.7</v>
+      </c>
+      <c r="BO100" s="13">
+        <v>1.1888715189405059</v>
+      </c>
       <c r="BP100" s="11"/>
       <c r="BQ100" s="11"/>
       <c r="BR100" s="11"/>
@@ -23913,27 +24897,27 @@
       </c>
       <c r="N101" s="8">
         <f t="shared" si="18"/>
-        <v>4543410.8571428573</v>
+        <v>4463566</v>
       </c>
       <c r="O101" s="8">
         <f t="shared" si="19"/>
-        <v>23226.571428571428</v>
+        <v>22357.375</v>
       </c>
       <c r="P101" s="8">
         <f t="shared" si="20"/>
-        <v>514</v>
+        <v>576</v>
       </c>
       <c r="Q101" s="9">
         <f t="shared" si="21"/>
-        <v>185625.73540856031</v>
+        <v>185981.91666666666</v>
       </c>
       <c r="R101" s="9">
         <f t="shared" si="22"/>
-        <v>948.94552529182874</v>
+        <v>931.55729166666674</v>
       </c>
       <c r="S101" s="10">
         <f t="shared" si="23"/>
-        <v>0.91225391260496991</v>
+        <v>0.90081165426203269</v>
       </c>
       <c r="T101" s="11">
         <v>5198390</v>
@@ -24061,12 +25045,24 @@
       <c r="BI101" s="13">
         <v>0.86309568936798775</v>
       </c>
-      <c r="BJ101" s="11"/>
-      <c r="BK101" s="11"/>
-      <c r="BL101" s="11"/>
-      <c r="BM101" s="12"/>
-      <c r="BN101" s="12"/>
-      <c r="BO101" s="13"/>
+      <c r="BJ101" s="11">
+        <v>3904652</v>
+      </c>
+      <c r="BK101" s="11">
+        <v>16273</v>
+      </c>
+      <c r="BL101" s="11">
+        <v>62</v>
+      </c>
+      <c r="BM101" s="12">
+        <v>188934.77419354839</v>
+      </c>
+      <c r="BN101" s="12">
+        <v>787.40322580645147</v>
+      </c>
+      <c r="BO101" s="13">
+        <v>0.82071584586147228</v>
+      </c>
       <c r="BP101" s="11"/>
       <c r="BQ101" s="11"/>
       <c r="BR101" s="11"/>
@@ -24135,27 +25131,27 @@
       </c>
       <c r="N102" s="8">
         <f t="shared" si="18"/>
-        <v>2235847.4571428569</v>
+        <v>2190201.0249999999</v>
       </c>
       <c r="O102" s="8">
         <f t="shared" si="19"/>
-        <v>67272.28571428571</v>
+        <v>64543.75</v>
       </c>
       <c r="P102" s="8">
         <f t="shared" si="20"/>
-        <v>501</v>
+        <v>563</v>
       </c>
       <c r="Q102" s="9">
         <f t="shared" si="21"/>
-        <v>93718.156886227545</v>
+        <v>93365.58543516873</v>
       </c>
       <c r="R102" s="9">
         <f t="shared" si="22"/>
-        <v>2819.7964071856286</v>
+        <v>2751.4209591474246</v>
       </c>
       <c r="S102" s="10">
         <f t="shared" si="23"/>
-        <v>2.1924297337966427</v>
+        <v>2.1661118335774807</v>
       </c>
       <c r="T102" s="11">
         <v>2396165.2000000002</v>
@@ -24283,12 +25279,24 @@
       <c r="BI102" s="13">
         <v>2.100478741136024</v>
       </c>
-      <c r="BJ102" s="11"/>
-      <c r="BK102" s="11"/>
-      <c r="BL102" s="11"/>
-      <c r="BM102" s="12"/>
-      <c r="BN102" s="12"/>
-      <c r="BO102" s="13"/>
+      <c r="BJ102" s="11">
+        <v>1870676</v>
+      </c>
+      <c r="BK102" s="11">
+        <v>45444</v>
+      </c>
+      <c r="BL102" s="11">
+        <v>62</v>
+      </c>
+      <c r="BM102" s="12">
+        <v>90516.580645161303</v>
+      </c>
+      <c r="BN102" s="12">
+        <v>2198.9032258064522</v>
+      </c>
+      <c r="BO102" s="13">
+        <v>1.981886532043349</v>
+      </c>
       <c r="BP102" s="11"/>
       <c r="BQ102" s="11"/>
       <c r="BR102" s="11"/>
@@ -24357,27 +25365,27 @@
       </c>
       <c r="N103" s="8">
         <f t="shared" si="18"/>
-        <v>234127.14285714287</v>
+        <v>213526.75</v>
       </c>
       <c r="O103" s="8">
         <f t="shared" si="19"/>
-        <v>114155.28571428571</v>
+        <v>106360.375</v>
       </c>
       <c r="P103" s="8">
         <f t="shared" si="20"/>
-        <v>488</v>
+        <v>531</v>
       </c>
       <c r="Q103" s="9">
         <f t="shared" si="21"/>
-        <v>10075.14344262295</v>
+        <v>9650.926553672316</v>
       </c>
       <c r="R103" s="9">
         <f t="shared" si="22"/>
-        <v>4912.4200819672133</v>
+        <v>4807.2485875706216</v>
       </c>
       <c r="S103" s="10">
         <f t="shared" si="23"/>
-        <v>9.1222961948439529</v>
+        <v>9.3575282912081903</v>
       </c>
       <c r="T103" s="11">
         <v>274124</v>
@@ -24505,12 +25513,24 @@
       <c r="BI103" s="13">
         <v>10.066592570121109</v>
       </c>
-      <c r="BJ103" s="11"/>
-      <c r="BK103" s="11"/>
-      <c r="BL103" s="11"/>
-      <c r="BM103" s="12"/>
-      <c r="BN103" s="12"/>
-      <c r="BO103" s="13"/>
+      <c r="BJ103" s="11">
+        <v>69324</v>
+      </c>
+      <c r="BK103" s="11">
+        <v>51796</v>
+      </c>
+      <c r="BL103" s="11">
+        <v>43</v>
+      </c>
+      <c r="BM103" s="12">
+        <v>4836.5581395348836</v>
+      </c>
+      <c r="BN103" s="12">
+        <v>3613.6744186046521</v>
+      </c>
+      <c r="BO103" s="13">
+        <v>11.00415296575785</v>
+      </c>
       <c r="BP103" s="11"/>
       <c r="BQ103" s="11"/>
       <c r="BR103" s="11"/>
@@ -24579,27 +25599,27 @@
       </c>
       <c r="N104" s="8">
         <f t="shared" si="18"/>
-        <v>5597219.2400000002</v>
+        <v>5479698.71</v>
       </c>
       <c r="O104" s="8">
         <f t="shared" si="19"/>
-        <v>9508.8571428571431</v>
+        <v>9729.75</v>
       </c>
       <c r="P104" s="8">
         <f t="shared" si="20"/>
-        <v>451</v>
+        <v>511</v>
       </c>
       <c r="Q104" s="9">
         <f t="shared" si="21"/>
-        <v>260624.39920177381</v>
+        <v>257363.54019569472</v>
       </c>
       <c r="R104" s="9">
         <f t="shared" si="22"/>
-        <v>442.76274944567626</v>
+        <v>456.97455968688843</v>
       </c>
       <c r="S104" s="10">
         <f t="shared" si="23"/>
-        <v>0.4894729305488289</v>
+        <v>0.50652471148026379</v>
       </c>
       <c r="T104" s="11">
         <v>2471269.08</v>
@@ -24727,12 +25747,24 @@
       <c r="BI104" s="13">
         <v>0.65101582764249166</v>
       </c>
-      <c r="BJ104" s="11"/>
-      <c r="BK104" s="11"/>
-      <c r="BL104" s="11"/>
-      <c r="BM104" s="12"/>
-      <c r="BN104" s="12"/>
-      <c r="BO104" s="13"/>
+      <c r="BJ104" s="11">
+        <v>4657055</v>
+      </c>
+      <c r="BK104" s="11">
+        <v>11276</v>
+      </c>
+      <c r="BL104" s="11">
+        <v>60</v>
+      </c>
+      <c r="BM104" s="12">
+        <v>232852.75</v>
+      </c>
+      <c r="BN104" s="12">
+        <v>563.79999999999995</v>
+      </c>
+      <c r="BO104" s="13">
+        <v>0.62588717800030746</v>
+      </c>
       <c r="BP104" s="11"/>
       <c r="BQ104" s="11"/>
       <c r="BR104" s="11"/>
@@ -24801,27 +25833,27 @@
       </c>
       <c r="N105" s="8">
         <f t="shared" si="18"/>
-        <v>5585726.0900000008</v>
+        <v>5537901.0787500003</v>
       </c>
       <c r="O105" s="8">
         <f t="shared" si="19"/>
-        <v>7100.7142857142853</v>
+        <v>6847.5</v>
       </c>
       <c r="P105" s="8">
         <f t="shared" si="20"/>
-        <v>472</v>
+        <v>528</v>
       </c>
       <c r="Q105" s="9">
         <f t="shared" si="21"/>
-        <v>248517.47434322035</v>
+        <v>251722.77630681818</v>
       </c>
       <c r="R105" s="9">
         <f t="shared" si="22"/>
-        <v>315.92161016949149</v>
+        <v>311.25</v>
       </c>
       <c r="S105" s="10">
         <f t="shared" si="23"/>
-        <v>0.47576924262714954</v>
+        <v>0.46563626266399716</v>
       </c>
       <c r="T105" s="11">
         <v>2163577.9500000002</v>
@@ -24949,12 +25981,24 @@
       <c r="BI105" s="13">
         <v>0.38</v>
       </c>
-      <c r="BJ105" s="11"/>
-      <c r="BK105" s="11"/>
-      <c r="BL105" s="11"/>
-      <c r="BM105" s="12"/>
-      <c r="BN105" s="12"/>
-      <c r="BO105" s="13"/>
+      <c r="BJ105" s="11">
+        <v>5203126</v>
+      </c>
+      <c r="BK105" s="11">
+        <v>5075</v>
+      </c>
+      <c r="BL105" s="11">
+        <v>56</v>
+      </c>
+      <c r="BM105" s="12">
+        <v>278738.89285714278</v>
+      </c>
+      <c r="BN105" s="12">
+        <v>271.875</v>
+      </c>
+      <c r="BO105" s="13">
+        <v>0.39470540292193063</v>
+      </c>
       <c r="BP105" s="11"/>
       <c r="BQ105" s="11"/>
       <c r="BR105" s="11"/>
@@ -25023,27 +26067,27 @@
       </c>
       <c r="N106" s="8">
         <f t="shared" si="18"/>
-        <v>9577969.5714285709</v>
+        <v>9257114.75</v>
       </c>
       <c r="O106" s="8">
         <f t="shared" si="19"/>
-        <v>175108.85714285713</v>
+        <v>168999.25</v>
       </c>
       <c r="P106" s="8">
         <f t="shared" si="20"/>
-        <v>486</v>
+        <v>541</v>
       </c>
       <c r="Q106" s="9">
         <f t="shared" si="21"/>
-        <v>413862.88271604938</v>
+        <v>410666.82809611829</v>
       </c>
       <c r="R106" s="9">
         <f t="shared" si="22"/>
-        <v>7566.4320987654319</v>
+        <v>7497.1940850277269</v>
       </c>
       <c r="S106" s="10">
         <f t="shared" si="23"/>
-        <v>1.7163697000864959</v>
+        <v>1.7150686517967852</v>
       </c>
       <c r="T106" s="11">
         <v>10039950</v>
@@ -25171,12 +26215,24 @@
       <c r="BI106" s="13">
         <v>1.737843223904411</v>
       </c>
-      <c r="BJ106" s="11"/>
-      <c r="BK106" s="11"/>
-      <c r="BL106" s="11"/>
-      <c r="BM106" s="12"/>
-      <c r="BN106" s="12"/>
-      <c r="BO106" s="13"/>
+      <c r="BJ106" s="11">
+        <v>7011131</v>
+      </c>
+      <c r="BK106" s="11">
+        <v>126232</v>
+      </c>
+      <c r="BL106" s="11">
+        <v>55</v>
+      </c>
+      <c r="BM106" s="12">
+        <v>382425.32727272733</v>
+      </c>
+      <c r="BN106" s="12">
+        <v>6885.3818181818178</v>
+      </c>
+      <c r="BO106" s="13">
+        <v>1.7059613137688101</v>
+      </c>
       <c r="BP106" s="11"/>
       <c r="BQ106" s="11"/>
       <c r="BR106" s="11"/>
@@ -25245,27 +26301,27 @@
       </c>
       <c r="N107" s="8">
         <f t="shared" si="18"/>
-        <v>3753002.7142857141</v>
+        <v>3745351.375</v>
       </c>
       <c r="O107" s="8">
         <f t="shared" si="19"/>
-        <v>195057</v>
+        <v>192956.625</v>
       </c>
       <c r="P107" s="8">
         <f t="shared" si="20"/>
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="Q107" s="9">
         <f t="shared" si="21"/>
-        <v>164193.86874999999</v>
+        <v>166460.06111111111</v>
       </c>
       <c r="R107" s="9">
         <f t="shared" si="22"/>
-        <v>8533.7437500000015</v>
+        <v>8575.85</v>
       </c>
       <c r="S107" s="10">
         <f t="shared" si="23"/>
-        <v>2.9195157116708201</v>
+        <v>2.9041784896671095</v>
       </c>
       <c r="T107" s="11">
         <v>4508101</v>
@@ -25393,12 +26449,24 @@
       <c r="BI107" s="13">
         <v>2.545182458105077</v>
       </c>
-      <c r="BJ107" s="11"/>
-      <c r="BK107" s="11"/>
-      <c r="BL107" s="11"/>
-      <c r="BM107" s="12"/>
-      <c r="BN107" s="12"/>
-      <c r="BO107" s="13"/>
+      <c r="BJ107" s="11">
+        <v>3691792</v>
+      </c>
+      <c r="BK107" s="11">
+        <v>178254</v>
+      </c>
+      <c r="BL107" s="11">
+        <v>60</v>
+      </c>
+      <c r="BM107" s="12">
+        <v>184589.6</v>
+      </c>
+      <c r="BN107" s="12">
+        <v>8912.7000000000007</v>
+      </c>
+      <c r="BO107" s="13">
+        <v>2.7968179356411329</v>
+      </c>
       <c r="BP107" s="11"/>
       <c r="BQ107" s="11"/>
       <c r="BR107" s="11"/>
@@ -25467,27 +26535,27 @@
       </c>
       <c r="N108" s="8">
         <f t="shared" si="18"/>
-        <v>4466628.2857142854</v>
+        <v>4271973.875</v>
       </c>
       <c r="O108" s="8">
         <f t="shared" si="19"/>
-        <v>198562.42857142858</v>
+        <v>197350.25</v>
       </c>
       <c r="P108" s="8">
         <f t="shared" si="20"/>
-        <v>483</v>
+        <v>544</v>
       </c>
       <c r="Q108" s="9">
         <f t="shared" si="21"/>
-        <v>194201.2298136646</v>
+        <v>188469.4356617647</v>
       </c>
       <c r="R108" s="9">
         <f t="shared" si="22"/>
-        <v>8633.1490683229822</v>
+        <v>8706.6286764705874</v>
       </c>
       <c r="S108" s="10">
         <f t="shared" si="23"/>
-        <v>2.7068605191912409</v>
+        <v>2.7739512419795811</v>
       </c>
       <c r="T108" s="11">
         <v>3557826</v>
@@ -25615,12 +26683,24 @@
       <c r="BI108" s="13">
         <v>3.0719841193364918</v>
       </c>
-      <c r="BJ108" s="11"/>
-      <c r="BK108" s="11"/>
-      <c r="BL108" s="11"/>
-      <c r="BM108" s="12"/>
-      <c r="BN108" s="12"/>
-      <c r="BO108" s="13"/>
+      <c r="BJ108" s="11">
+        <v>2909393</v>
+      </c>
+      <c r="BK108" s="11">
+        <v>188865</v>
+      </c>
+      <c r="BL108" s="11">
+        <v>61</v>
+      </c>
+      <c r="BM108" s="12">
+        <v>143084.90163934429</v>
+      </c>
+      <c r="BN108" s="12">
+        <v>9288.4426229508208</v>
+      </c>
+      <c r="BO108" s="13">
+        <v>3.2435863014979631</v>
+      </c>
       <c r="BP108" s="11"/>
       <c r="BQ108" s="11"/>
       <c r="BR108" s="11"/>
@@ -25689,27 +26769,27 @@
       </c>
       <c r="N109" s="8">
         <f t="shared" si="18"/>
-        <v>2045165.2857142857</v>
+        <v>1995662</v>
       </c>
       <c r="O109" s="8">
         <f t="shared" si="19"/>
-        <v>233699</v>
+        <v>228993.125</v>
       </c>
       <c r="P109" s="8">
         <f t="shared" si="20"/>
-        <v>325</v>
+        <v>371</v>
       </c>
       <c r="Q109" s="9">
         <f t="shared" si="21"/>
-        <v>132149.14153846155</v>
+        <v>129099.42857142857</v>
       </c>
       <c r="R109" s="9">
         <f t="shared" si="22"/>
-        <v>15100.550769230769</v>
+        <v>14813.571428571429</v>
       </c>
       <c r="S109" s="10">
         <f t="shared" si="23"/>
-        <v>4.3043069683353252</v>
+        <v>4.3150608342486212</v>
       </c>
       <c r="T109" s="11">
         <v>3150735</v>
@@ -25837,12 +26917,24 @@
       <c r="BI109" s="13">
         <v>4.4572918929751886</v>
       </c>
-      <c r="BJ109" s="11"/>
-      <c r="BK109" s="11"/>
-      <c r="BL109" s="11"/>
-      <c r="BM109" s="12"/>
-      <c r="BN109" s="12"/>
-      <c r="BO109" s="13"/>
+      <c r="BJ109" s="11">
+        <v>1649139</v>
+      </c>
+      <c r="BK109" s="11">
+        <v>196052</v>
+      </c>
+      <c r="BL109" s="11">
+        <v>46</v>
+      </c>
+      <c r="BM109" s="12">
+        <v>107552.54347826089</v>
+      </c>
+      <c r="BN109" s="12">
+        <v>12786</v>
+      </c>
+      <c r="BO109" s="13">
+        <v>4.3903378956416939</v>
+      </c>
       <c r="BP109" s="11"/>
       <c r="BQ109" s="11"/>
       <c r="BR109" s="11"/>
@@ -25911,27 +27003,27 @@
       </c>
       <c r="N110" s="8">
         <f t="shared" si="18"/>
-        <v>800987.14285714284</v>
+        <v>775127.25</v>
       </c>
       <c r="O110" s="8">
         <f t="shared" si="19"/>
-        <v>188087.85714285713</v>
+        <v>182631.75</v>
       </c>
       <c r="P110" s="8">
         <f t="shared" si="20"/>
-        <v>329</v>
+        <v>369</v>
       </c>
       <c r="Q110" s="9">
         <f t="shared" ref="Q110:Q111" si="24">IFERROR(SUM(T110,Z110,AF110,AL110,AR110,AX110,BD110,BJ110,BP110,BV110,CB110,CH110)/P110*3," ")</f>
-        <v>51126.838905775076</v>
+        <v>50414.780487804877</v>
       </c>
       <c r="R110" s="9">
         <f t="shared" si="22"/>
-        <v>12005.607902735563</v>
+        <v>11878.487804878048</v>
       </c>
       <c r="S110" s="10">
         <f t="shared" si="23"/>
-        <v>6.3115558071003681</v>
+        <v>6.307499284715389</v>
       </c>
       <c r="T110" s="11">
         <v>1383825</v>
@@ -26059,12 +27151,24 @@
       <c r="BI110" s="13">
         <v>6.2255438391914524</v>
       </c>
-      <c r="BJ110" s="11"/>
-      <c r="BK110" s="11"/>
-      <c r="BL110" s="11"/>
-      <c r="BM110" s="12"/>
-      <c r="BN110" s="12"/>
-      <c r="BO110" s="13"/>
+      <c r="BJ110" s="11">
+        <v>594108</v>
+      </c>
+      <c r="BK110" s="11">
+        <v>144439</v>
+      </c>
+      <c r="BL110" s="11">
+        <v>40</v>
+      </c>
+      <c r="BM110" s="12">
+        <v>44558.100000000013</v>
+      </c>
+      <c r="BN110" s="12">
+        <v>10832.924999999999</v>
+      </c>
+      <c r="BO110" s="13">
+        <v>6.2791036280205379</v>
+      </c>
       <c r="BP110" s="11"/>
       <c r="BQ110" s="11"/>
       <c r="BR110" s="11"/>
@@ -26133,27 +27237,27 @@
       </c>
       <c r="N111" s="8">
         <f t="shared" si="18"/>
-        <v>2940522.5</v>
+        <v>2725725.1428571427</v>
       </c>
       <c r="O111" s="8">
         <f t="shared" si="19"/>
-        <v>13332.333333333334</v>
+        <v>12414.285714285714</v>
       </c>
       <c r="P111" s="8">
         <f t="shared" si="20"/>
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="Q111" s="9">
         <f t="shared" si="24"/>
-        <v>155674.7205882353</v>
+        <v>149843.52879581152</v>
       </c>
       <c r="R111" s="9">
         <f t="shared" si="22"/>
-        <v>705.82941176470592</v>
+        <v>682.46073298429314</v>
       </c>
       <c r="S111" s="10">
         <f t="shared" si="23"/>
-        <v>0.87181350554336268</v>
+        <v>0.87271450987163413</v>
       </c>
       <c r="T111" s="11">
         <v>3953686</v>
@@ -26269,12 +27373,24 @@
       <c r="BI111" s="13">
         <v>0.82121565578064293</v>
       </c>
-      <c r="BJ111" s="11"/>
-      <c r="BK111" s="11"/>
-      <c r="BL111" s="11"/>
-      <c r="BM111" s="12"/>
-      <c r="BN111" s="12"/>
-      <c r="BO111" s="13"/>
+      <c r="BJ111" s="11">
+        <v>1436941</v>
+      </c>
+      <c r="BK111" s="11">
+        <v>6906</v>
+      </c>
+      <c r="BL111" s="11">
+        <v>42</v>
+      </c>
+      <c r="BM111" s="12">
+        <v>102638.6428571429</v>
+      </c>
+      <c r="BN111" s="12">
+        <v>493.28571428571422</v>
+      </c>
+      <c r="BO111" s="13">
+        <v>0.87812053584126271</v>
+      </c>
       <c r="BP111" s="11"/>
       <c r="BQ111" s="11"/>
       <c r="BR111" s="11"/>
@@ -26329,11 +27445,11 @@
       <c r="M112" s="22"/>
       <c r="N112" s="14">
         <f>SUM(N57:N111)</f>
-        <v>219899698.23252383</v>
+        <v>213814666.75941074</v>
       </c>
       <c r="O112" s="14">
         <f>SUM(O57:O111)</f>
-        <v>2906134.1190476194</v>
+        <v>2825351.9642857146</v>
       </c>
       <c r="P112" s="14"/>
       <c r="Q112" s="14"/>
@@ -26425,11 +27541,11 @@
       <c r="BI112" s="24"/>
       <c r="BJ112" s="14">
         <f>SUM(BJ57:BJ111)</f>
-        <v>0</v>
+        <v>168631907.40000001</v>
       </c>
       <c r="BK112" s="14">
         <f>SUM(BK57:BK111)</f>
-        <v>0</v>
+        <v>2262832</v>
       </c>
       <c r="BL112" s="14"/>
       <c r="BM112" s="14"/>
@@ -26943,27 +28059,27 @@
       </c>
       <c r="N116" s="8">
         <f t="shared" ref="N116:O118" si="25">IFERROR(AVERAGE(T116,Z116,AF116,AL116,AR116,AX116,BD116,BJ116,BP116,BV116,CB116,CH116)," ")</f>
-        <v>2791632.5714285714</v>
+        <v>2920251</v>
       </c>
       <c r="O116" s="8">
         <f t="shared" si="25"/>
-        <v>427427.57142857142</v>
+        <v>449799.875</v>
       </c>
       <c r="P116" s="8">
         <f>IFERROR(SUM(V116,AB116,AH116,AN116,AT116,AZ116,BF116,BL116,BR116,BX116,CD116,CJ116)," ")</f>
-        <v>216</v>
+        <v>259</v>
       </c>
       <c r="Q116" s="9">
         <f>IFERROR(SUM(T116,Z116,AF116,AL116,AR116,AX116,BD116,BJ116,BP116,BV116,CB116,CH116)/P116*3," ")</f>
-        <v>271408.72222222225</v>
+        <v>270602.40926640929</v>
       </c>
       <c r="R116" s="9">
         <f>IFERROR(SUM(U116,AA116,AG116,AM116,AS116,AY116,BE116,BK116,BQ116,BW116,CC116,CI116)/P116*3," ")</f>
-        <v>41555.458333333336</v>
+        <v>41680.297297297293</v>
       </c>
       <c r="S116" s="10">
         <f>IFERROR(AVERAGE(Y116,AE116,AK116,AQ116,AW116,BC116,BI116,BO116,BU116,CA116,CG116,CM116)," ")</f>
-        <v>4.9972561875085395</v>
+        <v>5.0066806090271978</v>
       </c>
       <c r="T116" s="11">
         <v>3772092</v>
@@ -27091,12 +28207,24 @@
       <c r="BI116" s="13">
         <v>5.0591650460887978</v>
       </c>
-      <c r="BJ116" s="11"/>
-      <c r="BK116" s="11"/>
-      <c r="BL116" s="11"/>
-      <c r="BM116" s="12"/>
-      <c r="BN116" s="12"/>
-      <c r="BO116" s="13"/>
+      <c r="BJ116" s="11">
+        <v>3820580</v>
+      </c>
+      <c r="BK116" s="11">
+        <v>606406</v>
+      </c>
+      <c r="BL116" s="11">
+        <v>43</v>
+      </c>
+      <c r="BM116" s="12">
+        <v>266552.09302325582</v>
+      </c>
+      <c r="BN116" s="12">
+        <v>42307.395348837214</v>
+      </c>
+      <c r="BO116" s="13">
+        <v>5.0726515596578103</v>
+      </c>
       <c r="BP116" s="11"/>
       <c r="BQ116" s="11"/>
       <c r="BR116" s="11"/>
@@ -27163,27 +28291,27 @@
       </c>
       <c r="N117" s="8">
         <f t="shared" si="25"/>
-        <v>2920205.5714285714</v>
+        <v>3072419</v>
       </c>
       <c r="O117" s="8">
         <f t="shared" si="25"/>
-        <v>447181.85714285716</v>
+        <v>473358.25</v>
       </c>
       <c r="P117" s="8">
         <f>IFERROR(SUM(V117,AB117,AH117,AN117,AT117,AZ117,BF117,BL117,BR117,BX117,CD117,CJ117)," ")</f>
-        <v>223</v>
+        <v>272</v>
       </c>
       <c r="Q117" s="9">
         <f>IFERROR(SUM(T117,Z117,AF117,AL117,AR117,AX117,BD117,BJ117,BP117,BV117,CB117,CH117)/P117*3," ")</f>
-        <v>274996.93721973093</v>
+        <v>271095.79411764705</v>
       </c>
       <c r="R117" s="9">
         <f>IFERROR(SUM(U117,AA117,AG117,AM117,AS117,AY117,BE117,BK117,BQ117,BW117,CC117,CI117)/P117*3," ")</f>
-        <v>42111.295964125558</v>
+        <v>41766.904411764706</v>
       </c>
       <c r="S117" s="10">
         <f>IFERROR(AVERAGE(Y117,AE117,AK117,AQ117,AW117,BC117,BI117,BO117,BU117,CA117,CG117,CM117)," ")</f>
-        <v>4.9953776079595871</v>
+        <v>5.0049489170965842</v>
       </c>
       <c r="T117" s="11">
         <v>4072469</v>
@@ -27311,12 +28439,24 @@
       <c r="BI117" s="13">
         <v>5.0786917071940882</v>
       </c>
-      <c r="BJ117" s="11"/>
-      <c r="BK117" s="11"/>
-      <c r="BL117" s="11"/>
-      <c r="BM117" s="12"/>
-      <c r="BN117" s="12"/>
-      <c r="BO117" s="13"/>
+      <c r="BJ117" s="11">
+        <v>4137913</v>
+      </c>
+      <c r="BK117" s="11">
+        <v>656593</v>
+      </c>
+      <c r="BL117" s="11">
+        <v>49</v>
+      </c>
+      <c r="BM117" s="12">
+        <v>253341.6122448979</v>
+      </c>
+      <c r="BN117" s="12">
+        <v>40199.571428571428</v>
+      </c>
+      <c r="BO117" s="13">
+        <v>5.0719480810555648</v>
+      </c>
       <c r="BP117" s="11"/>
       <c r="BQ117" s="11"/>
       <c r="BR117" s="11"/>
@@ -27382,27 +28522,27 @@
       </c>
       <c r="N118" s="8">
         <f t="shared" si="25"/>
-        <v>790865.05714285723</v>
+        <v>847911.92500000005</v>
       </c>
       <c r="O118" s="8">
         <f t="shared" si="25"/>
-        <v>886548.71428571432</v>
+        <v>955210.625</v>
       </c>
       <c r="P118" s="8">
         <f>IFERROR(SUM(V118,AB118,AH118,AN118,AT118,AZ118,BF118,BL118,BR118,BX118,CD118,CJ118)," ")</f>
-        <v>199</v>
+        <v>247</v>
       </c>
       <c r="Q118" s="9">
         <f>IFERROR(SUM(T118,Z118,AF118,AL118,AR118,AX118,BD118,BJ118,BP118,BV118,CB118,CH118)/P118*3," ")</f>
-        <v>83458.121608040208</v>
+        <v>82388.203238866394</v>
       </c>
       <c r="R118" s="9">
         <f>IFERROR(SUM(U118,AA118,AG118,AM118,AS118,AY118,BE118,BK118,BQ118,BW118,CC118,CI118)/P118*3," ")</f>
-        <v>93555.391959799003</v>
+        <v>92813.987854251012</v>
       </c>
       <c r="S118" s="10">
         <f>IFERROR(AVERAGE(Y118,AE118,AK118,AQ118,AW118,BC118,BI118,BO118,BU118,CA118,CG118,CM118)," ")</f>
-        <v>14.989240452855627</v>
+        <v>15.012529392729311</v>
       </c>
       <c r="T118" s="11">
         <v>1050265</v>
@@ -27530,12 +28670,24 @@
       <c r="BI118" s="13">
         <v>15.269679339309819</v>
       </c>
-      <c r="BJ118" s="11"/>
-      <c r="BK118" s="11"/>
-      <c r="BL118" s="11"/>
-      <c r="BM118" s="12"/>
-      <c r="BN118" s="12"/>
-      <c r="BO118" s="13"/>
+      <c r="BJ118" s="11">
+        <v>1247240</v>
+      </c>
+      <c r="BK118" s="11">
+        <v>1435844</v>
+      </c>
+      <c r="BL118" s="11">
+        <v>48</v>
+      </c>
+      <c r="BM118" s="12">
+        <v>77952.5</v>
+      </c>
+      <c r="BN118" s="12">
+        <v>89740.25</v>
+      </c>
+      <c r="BO118" s="13">
+        <v>15.175551971845101</v>
+      </c>
       <c r="BP118" s="11"/>
       <c r="BQ118" s="11"/>
       <c r="BR118" s="11"/>
@@ -27587,11 +28739,11 @@
       <c r="M119" s="22"/>
       <c r="N119" s="14">
         <f>SUM(N116:N118)</f>
-        <v>6502703.2000000002</v>
+        <v>6840581.9249999998</v>
       </c>
       <c r="O119" s="14">
         <f>SUM(O116:O118)</f>
-        <v>1761158.142857143</v>
+        <v>1878368.75</v>
       </c>
       <c r="P119" s="14"/>
       <c r="Q119" s="14"/>
@@ -27683,11 +28835,11 @@
       <c r="BI119" s="14"/>
       <c r="BJ119" s="14">
         <f>SUM(BJ116:BJ118)</f>
-        <v>0</v>
+        <v>9205733</v>
       </c>
       <c r="BK119" s="14">
         <f>SUM(BK116:BK118)</f>
-        <v>0</v>
+        <v>2698843</v>
       </c>
       <c r="BL119" s="14"/>
       <c r="BM119" s="14"/>
@@ -27757,35 +28909,6 @@
   </sheetData>
   <autoFilter ref="A2:CM53" xr:uid="{B264AC42-3408-4CC4-A254-80BEFA0AA9F5}"/>
   <mergeCells count="45">
-    <mergeCell ref="CB114:CG114"/>
-    <mergeCell ref="CH114:CM114"/>
-    <mergeCell ref="N114:S114"/>
-    <mergeCell ref="AX114:BC114"/>
-    <mergeCell ref="BD114:BI114"/>
-    <mergeCell ref="BJ114:BO114"/>
-    <mergeCell ref="BP114:BU114"/>
-    <mergeCell ref="BV114:CA114"/>
-    <mergeCell ref="T114:Y114"/>
-    <mergeCell ref="Z114:AE114"/>
-    <mergeCell ref="AF114:AK114"/>
-    <mergeCell ref="AL114:AQ114"/>
-    <mergeCell ref="AR114:AW114"/>
-    <mergeCell ref="BP55:BU55"/>
-    <mergeCell ref="BV55:CA55"/>
-    <mergeCell ref="CB55:CG55"/>
-    <mergeCell ref="CH55:CM55"/>
-    <mergeCell ref="N55:S55"/>
-    <mergeCell ref="AL55:AQ55"/>
-    <mergeCell ref="AR55:AW55"/>
-    <mergeCell ref="AX55:BC55"/>
-    <mergeCell ref="BD55:BI55"/>
-    <mergeCell ref="BJ55:BO55"/>
-    <mergeCell ref="T1:Y1"/>
-    <mergeCell ref="Z1:AE1"/>
-    <mergeCell ref="AF1:AK1"/>
-    <mergeCell ref="T55:Y55"/>
-    <mergeCell ref="Z55:AE55"/>
-    <mergeCell ref="AF55:AK55"/>
     <mergeCell ref="B114:G114"/>
     <mergeCell ref="H114:M114"/>
     <mergeCell ref="CB1:CG1"/>
@@ -27802,6 +28925,35 @@
     <mergeCell ref="AL1:AQ1"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H1:M1"/>
+    <mergeCell ref="T1:Y1"/>
+    <mergeCell ref="Z1:AE1"/>
+    <mergeCell ref="AF1:AK1"/>
+    <mergeCell ref="T55:Y55"/>
+    <mergeCell ref="Z55:AE55"/>
+    <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="BP55:BU55"/>
+    <mergeCell ref="BV55:CA55"/>
+    <mergeCell ref="CB55:CG55"/>
+    <mergeCell ref="CH55:CM55"/>
+    <mergeCell ref="N55:S55"/>
+    <mergeCell ref="AL55:AQ55"/>
+    <mergeCell ref="AR55:AW55"/>
+    <mergeCell ref="AX55:BC55"/>
+    <mergeCell ref="BD55:BI55"/>
+    <mergeCell ref="BJ55:BO55"/>
+    <mergeCell ref="CB114:CG114"/>
+    <mergeCell ref="CH114:CM114"/>
+    <mergeCell ref="N114:S114"/>
+    <mergeCell ref="AX114:BC114"/>
+    <mergeCell ref="BD114:BI114"/>
+    <mergeCell ref="BJ114:BO114"/>
+    <mergeCell ref="BP114:BU114"/>
+    <mergeCell ref="BV114:CA114"/>
+    <mergeCell ref="T114:Y114"/>
+    <mergeCell ref="Z114:AE114"/>
+    <mergeCell ref="AF114:AK114"/>
+    <mergeCell ref="AL114:AQ114"/>
+    <mergeCell ref="AR114:AW114"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
